--- a/data/raw/October_26_Utilities_Tracking.xlsx
+++ b/data/raw/October_26_Utilities_Tracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UTILITIES\Tracking\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF201F5-DF6D-4289-B945-4E09D419E07C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A76A303-FCD3-4720-8682-33E8AEBAE1F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="579" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,6 +53,40 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>Alexander Dominguez-Ramon</author>
+  </authors>
+  <commentList>
+    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{DA31AF73-2349-4F00-99F0-13F01ABAE50C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Alexander Dominguez-Ramon:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Diesel Meter Not Working</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
     <author>boyd</author>
   </authors>
   <commentList>
@@ -74,7 +108,7 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>boyd</author>
@@ -99,7 +133,7 @@
 </comments>
 </file>
 
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Anthony Foresyth</author>
@@ -133,7 +167,7 @@
 </comments>
 </file>
 
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Alexander Dominguez-Ramon</author>
@@ -277,7 +311,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="309">
   <si>
     <t>UTILITY ANALYSIS</t>
   </si>
@@ -2801,9 +2835,6 @@
     <t>Boiler 1. (AF Control)</t>
   </si>
   <si>
-    <t>Electricity PV System Target= 1373 (Kwh)</t>
-  </si>
-  <si>
     <t>KPI WITH ORIGINAL METER</t>
   </si>
   <si>
@@ -2832,6 +2863,15 @@
   </si>
   <si>
     <t>ST/VM</t>
+  </si>
+  <si>
+    <t>Electricity PV System Target= 1332 (Kwh)</t>
+  </si>
+  <si>
+    <t>CB</t>
+  </si>
+  <si>
+    <t>VM/VMg</t>
   </si>
 </sst>
 </file>
@@ -8338,9 +8378,6 @@
     <xf numFmtId="3" fontId="76" fillId="31" borderId="104" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="31" borderId="130" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="75" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -8356,6 +8393,12 @@
     <xf numFmtId="1" fontId="131" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="75" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="31" borderId="130" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8741,9 +8784,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="69" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="75" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -10080,13 +10120,13 @@
                   <c:v>7369</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>7089</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>3772</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>4062</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -10406,6 +10446,15 @@
                 <c:pt idx="0">
                   <c:v>1057.5</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>1571.3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>801.3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>694.6</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -10525,13 +10574,13 @@
                   <c:v>0.12549694416424376</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.18143713266284078</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.17521264732250233</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>0.14602867594500274</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -11971,7 +12020,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr transitionEvaluation="1" codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -12020,53 +12069,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="18" x14ac:dyDescent="0.2">
-      <c r="B1" s="898" t="s">
+      <c r="B1" s="899" t="s">
         <v>209</v>
       </c>
-      <c r="C1" s="898"/>
-      <c r="D1" s="898"/>
-      <c r="E1" s="898"/>
-      <c r="F1" s="898"/>
-      <c r="G1" s="898"/>
-      <c r="H1" s="898"/>
-      <c r="I1" s="898"/>
-      <c r="J1" s="898"/>
-      <c r="K1" s="898"/>
-      <c r="L1" s="898"/>
-      <c r="M1" s="898"/>
+      <c r="C1" s="899"/>
+      <c r="D1" s="899"/>
+      <c r="E1" s="899"/>
+      <c r="F1" s="899"/>
+      <c r="G1" s="899"/>
+      <c r="H1" s="899"/>
+      <c r="I1" s="899"/>
+      <c r="J1" s="899"/>
+      <c r="K1" s="899"/>
+      <c r="L1" s="899"/>
+      <c r="M1" s="899"/>
       <c r="N1" s="363"/>
-      <c r="O1" s="899" t="str">
+      <c r="O1" s="900" t="str">
         <f>B1</f>
         <v>ENTRIES FOR DAILY CONS. MONITOR</v>
       </c>
-      <c r="P1" s="899"/>
-      <c r="Q1" s="899"/>
-      <c r="R1" s="899"/>
-      <c r="S1" s="899"/>
-      <c r="T1" s="899"/>
-      <c r="U1" s="899"/>
-      <c r="V1" s="899"/>
-      <c r="W1" s="899"/>
-      <c r="X1" s="899"/>
-      <c r="Y1" s="899"/>
-      <c r="Z1" s="899"/>
-      <c r="AA1" s="899"/>
-      <c r="AB1" s="899"/>
+      <c r="P1" s="900"/>
+      <c r="Q1" s="900"/>
+      <c r="R1" s="900"/>
+      <c r="S1" s="900"/>
+      <c r="T1" s="900"/>
+      <c r="U1" s="900"/>
+      <c r="V1" s="900"/>
+      <c r="W1" s="900"/>
+      <c r="X1" s="900"/>
+      <c r="Y1" s="900"/>
+      <c r="Z1" s="900"/>
+      <c r="AA1" s="900"/>
+      <c r="AB1" s="900"/>
     </row>
     <row r="2" spans="1:44" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C2" s="814"/>
       <c r="F2" s="364"/>
       <c r="G2" s="365"/>
-      <c r="O2" s="907" t="s">
+      <c r="O2" s="908" t="s">
         <v>231</v>
       </c>
-      <c r="P2" s="907"/>
-      <c r="Q2" s="907"/>
-      <c r="R2" s="907"/>
-      <c r="S2" s="907"/>
-      <c r="T2" s="907"/>
-      <c r="U2" s="907"/>
-      <c r="V2" s="907"/>
+      <c r="P2" s="908"/>
+      <c r="Q2" s="908"/>
+      <c r="R2" s="908"/>
+      <c r="S2" s="908"/>
+      <c r="T2" s="908"/>
+      <c r="U2" s="908"/>
+      <c r="V2" s="908"/>
     </row>
     <row r="3" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="366"/>
@@ -12084,50 +12133,50 @@
         <v>22</v>
       </c>
       <c r="K3" s="369"/>
-      <c r="L3" s="912" t="s">
+      <c r="L3" s="913" t="s">
         <v>53</v>
       </c>
-      <c r="M3" s="913"/>
-      <c r="N3" s="914"/>
-      <c r="O3" s="900" t="s">
+      <c r="M3" s="914"/>
+      <c r="N3" s="915"/>
+      <c r="O3" s="901" t="s">
         <v>3</v>
       </c>
-      <c r="P3" s="900"/>
-      <c r="Q3" s="900"/>
-      <c r="R3" s="900"/>
-      <c r="S3" s="900"/>
-      <c r="T3" s="900"/>
-      <c r="U3" s="900"/>
-      <c r="V3" s="900"/>
-      <c r="W3" s="900"/>
-      <c r="X3" s="900"/>
-      <c r="Y3" s="900"/>
-      <c r="Z3" s="900"/>
-      <c r="AA3" s="900"/>
-      <c r="AB3" s="900"/>
-      <c r="AC3" s="900"/>
+      <c r="P3" s="901"/>
+      <c r="Q3" s="901"/>
+      <c r="R3" s="901"/>
+      <c r="S3" s="901"/>
+      <c r="T3" s="901"/>
+      <c r="U3" s="901"/>
+      <c r="V3" s="901"/>
+      <c r="W3" s="901"/>
+      <c r="X3" s="901"/>
+      <c r="Y3" s="901"/>
+      <c r="Z3" s="901"/>
+      <c r="AA3" s="901"/>
+      <c r="AB3" s="901"/>
+      <c r="AC3" s="901"/>
       <c r="AD3" s="372"/>
       <c r="AE3" s="373"/>
       <c r="AF3" s="372"/>
-      <c r="AG3" s="920" t="s">
+      <c r="AG3" s="921" t="s">
         <v>206</v>
       </c>
-      <c r="AH3" s="918" t="s">
+      <c r="AH3" s="919" t="s">
         <v>204</v>
       </c>
-      <c r="AI3" s="918" t="s">
+      <c r="AI3" s="919" t="s">
         <v>205</v>
       </c>
-      <c r="AJ3" s="921" t="s">
+      <c r="AJ3" s="922" t="s">
         <v>233</v>
       </c>
       <c r="AK3" s="416"/>
-      <c r="AL3" s="922" t="s">
+      <c r="AL3" s="923" t="s">
         <v>178</v>
       </c>
-      <c r="AM3" s="922"/>
-      <c r="AN3" s="922"/>
-      <c r="AO3" s="922"/>
+      <c r="AM3" s="923"/>
+      <c r="AN3" s="923"/>
+      <c r="AO3" s="923"/>
     </row>
     <row r="4" spans="1:44" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="374"/>
@@ -12161,40 +12210,40 @@
       <c r="K4" s="372" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="908" t="s">
+      <c r="L4" s="909" t="s">
         <v>289</v>
       </c>
       <c r="M4" s="376" t="s">
         <v>260</v>
       </c>
-      <c r="N4" s="915" t="s">
+      <c r="N4" s="916" t="s">
         <v>167</v>
       </c>
-      <c r="O4" s="896" t="s">
+      <c r="O4" s="897" t="s">
         <v>100</v>
       </c>
-      <c r="P4" s="896" t="s">
+      <c r="P4" s="897" t="s">
         <v>101</v>
       </c>
-      <c r="Q4" s="896" t="s">
+      <c r="Q4" s="897" t="s">
         <v>160</v>
       </c>
-      <c r="R4" s="896" t="s">
+      <c r="R4" s="897" t="s">
         <v>171</v>
       </c>
-      <c r="S4" s="896" t="s">
+      <c r="S4" s="897" t="s">
         <v>102</v>
       </c>
-      <c r="T4" s="896" t="s">
+      <c r="T4" s="897" t="s">
         <v>172</v>
       </c>
-      <c r="U4" s="896" t="s">
+      <c r="U4" s="897" t="s">
         <v>103</v>
       </c>
-      <c r="V4" s="905" t="s">
+      <c r="V4" s="906" t="s">
         <v>236</v>
       </c>
-      <c r="W4" s="896" t="s">
+      <c r="W4" s="897" t="s">
         <v>177</v>
       </c>
       <c r="X4" s="372" t="s">
@@ -12206,28 +12255,28 @@
       <c r="Z4" s="372" t="s">
         <v>98</v>
       </c>
-      <c r="AA4" s="900" t="s">
+      <c r="AA4" s="901" t="s">
         <v>68</v>
       </c>
-      <c r="AB4" s="902" t="s">
+      <c r="AB4" s="903" t="s">
         <v>69</v>
       </c>
-      <c r="AC4" s="906" t="s">
+      <c r="AC4" s="907" t="s">
         <v>151</v>
       </c>
-      <c r="AD4" s="896" t="s">
+      <c r="AD4" s="897" t="s">
         <v>154</v>
       </c>
-      <c r="AE4" s="896" t="s">
+      <c r="AE4" s="897" t="s">
         <v>155</v>
       </c>
-      <c r="AF4" s="896" t="s">
+      <c r="AF4" s="897" t="s">
         <v>159</v>
       </c>
-      <c r="AG4" s="920"/>
-      <c r="AH4" s="919"/>
-      <c r="AI4" s="919"/>
-      <c r="AJ4" s="921"/>
+      <c r="AG4" s="921"/>
+      <c r="AH4" s="920"/>
+      <c r="AI4" s="920"/>
+      <c r="AJ4" s="922"/>
       <c r="AK4" s="416"/>
       <c r="AL4" s="378" t="s">
         <v>276</v>
@@ -12276,20 +12325,20 @@
       <c r="K5" s="465" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="909"/>
+      <c r="L5" s="910"/>
       <c r="M5" s="466" t="s">
         <v>261</v>
       </c>
-      <c r="N5" s="916"/>
-      <c r="O5" s="904"/>
-      <c r="P5" s="896"/>
-      <c r="Q5" s="896"/>
-      <c r="R5" s="896"/>
-      <c r="S5" s="904"/>
-      <c r="T5" s="904"/>
-      <c r="U5" s="904"/>
-      <c r="V5" s="905"/>
-      <c r="W5" s="917"/>
+      <c r="N5" s="917"/>
+      <c r="O5" s="905"/>
+      <c r="P5" s="897"/>
+      <c r="Q5" s="897"/>
+      <c r="R5" s="897"/>
+      <c r="S5" s="905"/>
+      <c r="T5" s="905"/>
+      <c r="U5" s="905"/>
+      <c r="V5" s="906"/>
+      <c r="W5" s="918"/>
       <c r="X5" s="372" t="s">
         <v>104</v>
       </c>
@@ -12299,16 +12348,16 @@
       <c r="Z5" s="372" t="s">
         <v>104</v>
       </c>
-      <c r="AA5" s="901"/>
-      <c r="AB5" s="903"/>
-      <c r="AC5" s="906"/>
-      <c r="AD5" s="896"/>
-      <c r="AE5" s="896"/>
-      <c r="AF5" s="897"/>
-      <c r="AG5" s="920"/>
-      <c r="AH5" s="919"/>
-      <c r="AI5" s="919"/>
-      <c r="AJ5" s="921"/>
+      <c r="AA5" s="902"/>
+      <c r="AB5" s="904"/>
+      <c r="AC5" s="907"/>
+      <c r="AD5" s="897"/>
+      <c r="AE5" s="897"/>
+      <c r="AF5" s="898"/>
+      <c r="AG5" s="921"/>
+      <c r="AH5" s="920"/>
+      <c r="AI5" s="920"/>
+      <c r="AJ5" s="922"/>
       <c r="AK5" s="416"/>
       <c r="AL5" s="378" t="s">
         <v>263</v>
@@ -12421,7 +12470,7 @@
       <c r="B7" s="819">
         <v>8522020</v>
       </c>
-      <c r="C7" s="888">
+      <c r="C7" s="894">
         <v>1667565.2</v>
       </c>
       <c r="D7" s="821"/>
@@ -12509,41 +12558,87 @@
       <c r="A8" s="378">
         <v>3</v>
       </c>
-      <c r="B8" s="819"/>
-      <c r="C8" s="820"/>
+      <c r="B8" s="819">
+        <v>8522020</v>
+      </c>
+      <c r="C8" s="820">
+        <v>1669800.3</v>
+      </c>
       <c r="D8" s="821"/>
-      <c r="E8" s="821"/>
-      <c r="F8" s="821"/>
-      <c r="G8" s="821"/>
+      <c r="E8" s="821">
+        <v>64</v>
+      </c>
+      <c r="F8" s="821">
+        <v>11294.9</v>
+      </c>
+      <c r="G8" s="821">
+        <v>68225</v>
+      </c>
       <c r="H8" s="822"/>
-      <c r="I8" s="823"/>
+      <c r="I8" s="823">
+        <v>1893824</v>
+      </c>
       <c r="J8" s="824"/>
-      <c r="K8" s="822"/>
-      <c r="L8" s="821"/>
-      <c r="M8" s="825"/>
-      <c r="N8" s="823"/>
-      <c r="O8" s="826"/>
-      <c r="P8" s="827"/>
-      <c r="Q8" s="821"/>
+      <c r="K8" s="822">
+        <v>468000</v>
+      </c>
+      <c r="L8" s="821">
+        <v>87657.8</v>
+      </c>
+      <c r="M8" s="825">
+        <v>633066.25</v>
+      </c>
+      <c r="N8" s="823">
+        <v>84975.92</v>
+      </c>
+      <c r="O8" s="826">
+        <v>253181</v>
+      </c>
+      <c r="P8" s="827">
+        <v>86136</v>
+      </c>
+      <c r="Q8" s="821">
+        <v>989942</v>
+      </c>
       <c r="R8" s="821"/>
-      <c r="S8" s="821"/>
+      <c r="S8" s="821">
+        <v>97516</v>
+      </c>
       <c r="T8" s="821"/>
-      <c r="U8" s="821"/>
-      <c r="V8" s="828"/>
+      <c r="U8" s="821">
+        <v>543</v>
+      </c>
+      <c r="V8" s="828">
+        <v>1366475</v>
+      </c>
       <c r="W8" s="821"/>
-      <c r="X8" s="829"/>
-      <c r="Y8" s="821"/>
-      <c r="Z8" s="821"/>
-      <c r="AA8" s="821"/>
+      <c r="X8" s="829">
+        <v>49233</v>
+      </c>
+      <c r="Y8" s="821">
+        <v>70953</v>
+      </c>
+      <c r="Z8" s="821">
+        <v>15732</v>
+      </c>
+      <c r="AA8" s="821">
+        <v>97122</v>
+      </c>
       <c r="AB8" s="821"/>
-      <c r="AC8" s="821"/>
-      <c r="AD8" s="821"/>
+      <c r="AC8" s="821">
+        <v>6781</v>
+      </c>
+      <c r="AD8" s="821">
+        <v>263787</v>
+      </c>
       <c r="AE8" s="821"/>
       <c r="AF8" s="823"/>
       <c r="AG8" s="821"/>
       <c r="AH8" s="821"/>
       <c r="AI8" s="830"/>
-      <c r="AJ8" s="885"/>
+      <c r="AJ8" s="885">
+        <v>7383497.2000000002</v>
+      </c>
       <c r="AK8" s="443"/>
       <c r="AL8" s="458"/>
       <c r="AM8" s="457"/>
@@ -12554,41 +12649,87 @@
       <c r="A9" s="378">
         <v>4</v>
       </c>
-      <c r="B9" s="819"/>
-      <c r="C9" s="820"/>
+      <c r="B9" s="819">
+        <v>8522020</v>
+      </c>
+      <c r="C9" s="820">
+        <v>1670038.6</v>
+      </c>
       <c r="D9" s="821"/>
-      <c r="E9" s="821"/>
-      <c r="F9" s="821"/>
-      <c r="G9" s="821"/>
+      <c r="E9" s="821">
+        <v>64</v>
+      </c>
+      <c r="F9" s="821">
+        <v>11296.5</v>
+      </c>
+      <c r="G9" s="821">
+        <v>68225</v>
+      </c>
       <c r="H9" s="822"/>
-      <c r="I9" s="823"/>
+      <c r="I9" s="823">
+        <v>1897596</v>
+      </c>
       <c r="J9" s="824"/>
-      <c r="K9" s="822"/>
-      <c r="L9" s="821"/>
-      <c r="M9" s="825"/>
-      <c r="N9" s="823"/>
-      <c r="O9" s="826"/>
-      <c r="P9" s="827"/>
-      <c r="Q9" s="821"/>
+      <c r="K9" s="822">
+        <v>468000</v>
+      </c>
+      <c r="L9" s="821">
+        <v>87657.8</v>
+      </c>
+      <c r="M9" s="825">
+        <v>633066.25</v>
+      </c>
+      <c r="N9" s="823">
+        <v>84975.92</v>
+      </c>
+      <c r="O9" s="826">
+        <v>253181</v>
+      </c>
+      <c r="P9" s="827">
+        <v>86263</v>
+      </c>
+      <c r="Q9" s="821">
+        <v>989987</v>
+      </c>
       <c r="R9" s="821"/>
-      <c r="S9" s="821"/>
+      <c r="S9" s="821">
+        <v>97516</v>
+      </c>
       <c r="T9" s="821"/>
-      <c r="U9" s="821"/>
-      <c r="V9" s="828"/>
+      <c r="U9" s="821">
+        <v>543</v>
+      </c>
+      <c r="V9" s="828">
+        <v>1366609</v>
+      </c>
       <c r="W9" s="821"/>
-      <c r="X9" s="829"/>
-      <c r="Y9" s="821"/>
-      <c r="Z9" s="821"/>
-      <c r="AA9" s="821"/>
+      <c r="X9" s="829">
+        <v>49233</v>
+      </c>
+      <c r="Y9" s="821">
+        <v>70953</v>
+      </c>
+      <c r="Z9" s="821">
+        <v>15735</v>
+      </c>
+      <c r="AA9" s="821">
+        <v>97122</v>
+      </c>
       <c r="AB9" s="821"/>
-      <c r="AC9" s="821"/>
-      <c r="AD9" s="876"/>
+      <c r="AC9" s="821">
+        <v>6781</v>
+      </c>
+      <c r="AD9" s="821">
+        <v>263787</v>
+      </c>
       <c r="AE9" s="821"/>
       <c r="AF9" s="823"/>
       <c r="AG9" s="821"/>
       <c r="AH9" s="821"/>
       <c r="AI9" s="821"/>
-      <c r="AJ9" s="885"/>
+      <c r="AJ9" s="885">
+        <v>7383497.2000000002</v>
+      </c>
       <c r="AK9" s="442"/>
       <c r="AL9" s="459"/>
       <c r="AM9" s="457"/>
@@ -12599,41 +12740,87 @@
       <c r="A10" s="378">
         <v>5</v>
       </c>
-      <c r="B10" s="819"/>
-      <c r="C10" s="820"/>
+      <c r="B10" s="819">
+        <v>8522020</v>
+      </c>
+      <c r="C10" s="820">
+        <v>1670373.5</v>
+      </c>
       <c r="D10" s="821"/>
-      <c r="E10" s="821"/>
-      <c r="F10" s="821"/>
-      <c r="G10" s="821"/>
+      <c r="E10" s="821">
+        <v>64</v>
+      </c>
+      <c r="F10" s="821">
+        <v>11298.4</v>
+      </c>
+      <c r="G10" s="821">
+        <v>68225</v>
+      </c>
       <c r="H10" s="822"/>
-      <c r="I10" s="823"/>
+      <c r="I10" s="823">
+        <v>1901658</v>
+      </c>
       <c r="J10" s="824"/>
-      <c r="K10" s="822"/>
-      <c r="L10" s="821"/>
-      <c r="M10" s="825"/>
-      <c r="N10" s="823"/>
-      <c r="O10" s="826"/>
-      <c r="P10" s="827"/>
-      <c r="Q10" s="821"/>
+      <c r="K10" s="822">
+        <v>468000</v>
+      </c>
+      <c r="L10" s="821">
+        <v>87657.8</v>
+      </c>
+      <c r="M10" s="825">
+        <v>633066.25</v>
+      </c>
+      <c r="N10" s="823">
+        <v>84975.92</v>
+      </c>
+      <c r="O10" s="826">
+        <v>253245</v>
+      </c>
+      <c r="P10" s="827">
+        <v>86263</v>
+      </c>
+      <c r="Q10" s="821">
+        <v>990034</v>
+      </c>
       <c r="R10" s="821"/>
-      <c r="S10" s="821"/>
+      <c r="S10" s="821">
+        <v>97516</v>
+      </c>
       <c r="T10" s="821"/>
-      <c r="U10" s="821"/>
-      <c r="V10" s="828"/>
+      <c r="U10" s="821">
+        <v>543</v>
+      </c>
+      <c r="V10" s="828">
+        <v>1366609</v>
+      </c>
       <c r="W10" s="821"/>
-      <c r="X10" s="829"/>
-      <c r="Y10" s="821"/>
-      <c r="Z10" s="821"/>
-      <c r="AA10" s="821"/>
+      <c r="X10" s="829">
+        <v>49233</v>
+      </c>
+      <c r="Y10" s="821">
+        <v>70953</v>
+      </c>
+      <c r="Z10" s="821">
+        <v>15737</v>
+      </c>
+      <c r="AA10" s="821">
+        <v>97122</v>
+      </c>
       <c r="AB10" s="821"/>
-      <c r="AC10" s="821"/>
-      <c r="AD10" s="876"/>
+      <c r="AC10" s="821">
+        <v>6781</v>
+      </c>
+      <c r="AD10" s="821">
+        <v>263787</v>
+      </c>
       <c r="AE10" s="821"/>
       <c r="AF10" s="823"/>
       <c r="AG10" s="821"/>
       <c r="AH10" s="821"/>
       <c r="AI10" s="821"/>
-      <c r="AJ10" s="885"/>
+      <c r="AJ10" s="885">
+        <v>7383497.2000000002</v>
+      </c>
       <c r="AK10" s="442"/>
       <c r="AL10" s="459"/>
       <c r="AM10" s="457"/>
@@ -13611,7 +13798,7 @@
       <c r="P32" s="827"/>
       <c r="Q32" s="821"/>
       <c r="R32" s="821"/>
-      <c r="S32" s="890"/>
+      <c r="S32" s="889"/>
       <c r="T32" s="821"/>
       <c r="U32" s="821"/>
       <c r="V32" s="828"/>
@@ -13656,7 +13843,7 @@
       <c r="P33" s="827"/>
       <c r="Q33" s="821"/>
       <c r="R33" s="821"/>
-      <c r="S33" s="890"/>
+      <c r="S33" s="889"/>
       <c r="T33" s="821"/>
       <c r="U33" s="821"/>
       <c r="V33" s="828"/>
@@ -13863,8 +14050,8 @@
     <row r="38" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B38" s="190"/>
       <c r="G38" s="190"/>
-      <c r="I38" s="910"/>
-      <c r="J38" s="910"/>
+      <c r="I38" s="911"/>
+      <c r="J38" s="911"/>
       <c r="R38" s="190"/>
       <c r="S38" s="190"/>
       <c r="T38" s="190"/>
@@ -13872,8 +14059,8 @@
       <c r="V38" s="190"/>
       <c r="W38" s="190"/>
       <c r="Z38" s="190"/>
-      <c r="AA38" s="911"/>
-      <c r="AB38" s="911"/>
+      <c r="AA38" s="912"/>
+      <c r="AB38" s="912"/>
       <c r="AC38" s="190"/>
       <c r="AD38" s="190"/>
       <c r="AI38" s="380"/>
@@ -15581,7 +15768,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11:B12">
-    <cfRule type="expression" dxfId="116" priority="65">
+    <cfRule type="expression" dxfId="116" priority="105">
       <formula>B11&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15596,17 +15783,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8:D14">
-    <cfRule type="expression" dxfId="113" priority="56">
+    <cfRule type="expression" dxfId="113" priority="35">
       <formula>C8&lt;C7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36:D37">
-    <cfRule type="expression" dxfId="112" priority="1120">
+    <cfRule type="expression" dxfId="112" priority="1160">
       <formula>C36&lt;C35</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D35 B36:B37">
-    <cfRule type="expression" dxfId="111" priority="1107">
+    <cfRule type="expression" dxfId="111" priority="1147">
       <formula>B35&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15626,7 +15813,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G36:J37 L36:O37">
-    <cfRule type="expression" dxfId="107" priority="954">
+    <cfRule type="expression" dxfId="107" priority="994">
       <formula>G36&lt;G35</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15636,71 +15823,71 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H19:I34">
-    <cfRule type="expression" dxfId="105" priority="68">
+    <cfRule type="expression" dxfId="105" priority="108">
       <formula>H19&lt;H18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H35:I35 R35 T35 W35 AB35 AE35:AI35 P36:P37 S36:S37 X36:Y37">
-    <cfRule type="expression" dxfId="104" priority="1106">
+    <cfRule type="expression" dxfId="104" priority="1146">
       <formula>H35&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8:J18">
-    <cfRule type="expression" dxfId="103" priority="57">
+    <cfRule type="expression" dxfId="103" priority="36">
       <formula>H8&lt;H7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J19:J35">
-    <cfRule type="expression" dxfId="102" priority="69">
+    <cfRule type="expression" dxfId="102" priority="109">
       <formula>J19&lt;J18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K9:L21">
-    <cfRule type="expression" dxfId="101" priority="60">
-      <formula>K9&lt;K8</formula>
+  <conditionalFormatting sqref="K11:L21">
+    <cfRule type="expression" dxfId="101" priority="100">
+      <formula>K11&lt;K10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K22:M22">
-    <cfRule type="expression" dxfId="100" priority="70">
+    <cfRule type="expression" dxfId="100" priority="110">
       <formula>K22&lt;K21</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K7:O8">
+  <conditionalFormatting sqref="K7:O10">
     <cfRule type="expression" dxfId="99" priority="23">
       <formula>K7&lt;K6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K23:Z23 K24:K37">
-    <cfRule type="expression" dxfId="98" priority="71">
+    <cfRule type="expression" dxfId="98" priority="111">
       <formula>K23&lt;K22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L24:Z27 L28:AC28">
-    <cfRule type="expression" dxfId="97" priority="73">
+    <cfRule type="expression" dxfId="97" priority="113">
       <formula>L24&lt;L23</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M9:M17">
-    <cfRule type="expression" dxfId="96" priority="62">
-      <formula>M9&lt;#REF!</formula>
+  <conditionalFormatting sqref="M11:M17">
+    <cfRule type="expression" dxfId="96" priority="102">
+      <formula>M11&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N9:O12">
-    <cfRule type="expression" dxfId="95" priority="61">
-      <formula>N9&lt;N8</formula>
+  <conditionalFormatting sqref="N11:O12">
+    <cfRule type="expression" dxfId="95" priority="101">
+      <formula>N11&lt;N10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N13:T22">
-    <cfRule type="expression" dxfId="94" priority="64">
+    <cfRule type="expression" dxfId="94" priority="104">
       <formula>N13&lt;N12</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P8:P12 V8:V12">
-    <cfRule type="expression" dxfId="93" priority="59">
+    <cfRule type="expression" dxfId="93" priority="38">
       <formula>P8&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P6:Q6 X6:Y6 S6:S8">
+  <conditionalFormatting sqref="P6:Q6 X6:Y6 S6:S10">
     <cfRule type="expression" dxfId="92" priority="13">
       <formula>P6&lt;#REF!</formula>
     </cfRule>
@@ -15711,18 +15898,18 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q36">
-    <cfRule type="expression" dxfId="90" priority="1123">
+    <cfRule type="expression" dxfId="90" priority="1163">
       <formula>Q36&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q8:R8">
-    <cfRule type="expression" dxfId="89" priority="58">
+  <conditionalFormatting sqref="Q8:R10">
+    <cfRule type="expression" dxfId="89" priority="37">
       <formula>Q8&lt;Q7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q9:T12">
-    <cfRule type="expression" dxfId="88" priority="63">
-      <formula>Q9&lt;Q8</formula>
+  <conditionalFormatting sqref="Q11:T12">
+    <cfRule type="expression" dxfId="88" priority="103">
+      <formula>Q11&lt;Q10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R6">
@@ -15731,12 +15918,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R36">
-    <cfRule type="expression" dxfId="86" priority="1119">
+    <cfRule type="expression" dxfId="86" priority="1159">
       <formula>R36&lt;R35</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T8 AB8:AC8 AE8:AI8 AB9:AI27">
-    <cfRule type="expression" dxfId="85" priority="54">
+  <conditionalFormatting sqref="T8:T10 AB8:AC10 AE8:AI10">
+    <cfRule type="expression" dxfId="85" priority="33">
       <formula>T8&lt;T7</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15756,22 +15943,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V13:X14 C15:E34 C35 E35:E37">
-    <cfRule type="expression" dxfId="81" priority="67">
+    <cfRule type="expression" dxfId="81" priority="107">
       <formula>C13&lt;C12</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V15:Z22 M18:M21">
-    <cfRule type="expression" dxfId="80" priority="66">
+    <cfRule type="expression" dxfId="80" priority="106">
       <formula>M15&lt;M14</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V29:AC29 AA30:AC30 Z30:Z31 V30:Y34 AA31:AB31 AC31:AC37 Z32:AB34 V35 X35:AA35">
-    <cfRule type="expression" dxfId="79" priority="77">
+    <cfRule type="expression" dxfId="79" priority="117">
       <formula>V29&lt;V28</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W8:W12">
-    <cfRule type="expression" dxfId="78" priority="55">
+    <cfRule type="expression" dxfId="78" priority="34">
       <formula>W8&lt;W7</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15791,22 +15978,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA28:AA37">
-    <cfRule type="expression" dxfId="74" priority="75">
+    <cfRule type="expression" dxfId="74" priority="115">
       <formula>AA28&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AB11:AI27">
+    <cfRule type="expression" dxfId="73" priority="94">
+      <formula>AB11&lt;AB10</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AC6:AC7">
-    <cfRule type="expression" dxfId="73" priority="10">
+    <cfRule type="expression" dxfId="72" priority="10">
       <formula>AC6&lt;AC5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD8">
-    <cfRule type="expression" dxfId="72" priority="47">
-      <formula>AD8&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="AD28:AD37">
-    <cfRule type="expression" dxfId="71" priority="72">
+    <cfRule type="expression" dxfId="71" priority="112">
       <formula>AD28&lt;AD27</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15815,13 +16002,13 @@
       <formula>AD6&lt;AD5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD7:AI7 X7:X12">
+  <conditionalFormatting sqref="AD7:AI7 X7:X12 AD8:AD10">
     <cfRule type="expression" dxfId="69" priority="27">
       <formula>X7&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE28:AI34 L29:T34 U29:U37 L35:Q35 S35">
-    <cfRule type="expression" dxfId="68" priority="76">
+    <cfRule type="expression" dxfId="68" priority="116">
       <formula>L28&lt;L27</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15831,22 +16018,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK6:AK12">
-    <cfRule type="expression" dxfId="66" priority="996">
+    <cfRule type="expression" dxfId="66" priority="1036">
       <formula>AK6&lt;AK5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK13:AL15">
-    <cfRule type="expression" dxfId="65" priority="1076">
+    <cfRule type="expression" dxfId="65" priority="1116">
       <formula>AK13&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL9:AL14 AL15:AN34 AK16:AK37 AK20:AN21 T36:W37 Z36:Z37 AB36:AB37 AE36:AI37 Q37:R37">
-    <cfRule type="expression" dxfId="64" priority="1013">
+    <cfRule type="expression" dxfId="64" priority="1053">
       <formula>Q9&lt;Q8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO9:AO34">
-    <cfRule type="expression" dxfId="63" priority="1021">
+    <cfRule type="expression" dxfId="63" priority="1061">
       <formula>AO9&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15859,6 +16046,7 @@
   <colBreaks count="1" manualBreakCount="1">
     <brk id="39" max="39" man="1"/>
   </colBreaks>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -15914,8 +16102,8 @@
       </c>
       <c r="B3" s="468"/>
       <c r="C3" s="468"/>
-      <c r="K3" s="895"/>
-      <c r="L3" s="895"/>
+      <c r="K3" s="896"/>
+      <c r="L3" s="896"/>
       <c r="M3" s="498"/>
       <c r="AH3" s="291"/>
       <c r="AI3" s="291"/>
@@ -16061,7 +16249,7 @@
         <v>31</v>
       </c>
       <c r="AG6" s="291"/>
-      <c r="AI6" s="894" t="s">
+      <c r="AI6" s="895" t="s">
         <v>216</v>
       </c>
     </row>
@@ -16166,7 +16354,7 @@
       <c r="AH7" s="477" t="s">
         <v>19</v>
       </c>
-      <c r="AI7" s="894"/>
+      <c r="AI7" s="895"/>
       <c r="AJ7" s="292" t="s">
         <v>229</v>
       </c>
@@ -16204,7 +16392,10 @@
         <f>4313+(1171)</f>
         <v>5484</v>
       </c>
-      <c r="C8" s="678"/>
+      <c r="C8" s="678">
+        <f>2895+1401</f>
+        <v>4296</v>
+      </c>
       <c r="D8" s="782"/>
       <c r="E8" s="678"/>
       <c r="F8" s="678"/>
@@ -16233,18 +16424,18 @@
       <c r="AC8" s="678"/>
       <c r="AD8" s="678"/>
       <c r="AE8" s="678"/>
-      <c r="AF8" s="892"/>
+      <c r="AF8" s="891"/>
       <c r="AG8" s="747"/>
       <c r="AH8" s="480">
         <f>SUM(B8:AG8)</f>
-        <v>5484</v>
+        <v>9780</v>
       </c>
       <c r="AI8" s="526">
         <v>123950</v>
       </c>
       <c r="AJ8" s="294">
         <f>AH8-AI8</f>
-        <v>-118466</v>
+        <v>-114170</v>
       </c>
       <c r="AK8" s="481"/>
       <c r="AL8" s="481"/>
@@ -16280,7 +16471,7 @@
       </c>
       <c r="C9" s="678">
         <f t="shared" ref="C9:E9" si="0">C8*0.066</f>
-        <v>0</v>
+        <v>283.536</v>
       </c>
       <c r="D9" s="678">
         <f t="shared" si="0"/>
@@ -16386,7 +16577,7 @@
       <c r="AG9" s="748"/>
       <c r="AH9" s="484">
         <f>SUM(B9:AG9)</f>
-        <v>367.56479999999999</v>
+        <v>651.10079999999994</v>
       </c>
       <c r="AI9" s="484"/>
       <c r="AL9" s="291" t="s">
@@ -16399,9 +16590,11 @@
         <v>132</v>
       </c>
       <c r="B10" s="752" t="s">
-        <v>306</v>
-      </c>
-      <c r="C10" s="875"/>
+        <v>305</v>
+      </c>
+      <c r="C10" s="752" t="s">
+        <v>308</v>
+      </c>
       <c r="D10" s="752"/>
       <c r="E10" s="800"/>
       <c r="F10" s="681"/>
@@ -16430,7 +16623,7 @@
       <c r="AC10" s="883"/>
       <c r="AD10" s="883"/>
       <c r="AE10" s="875"/>
-      <c r="AF10" s="893"/>
+      <c r="AF10" s="892"/>
       <c r="AG10" s="749"/>
       <c r="AH10" s="487"/>
       <c r="AI10" s="487"/>
@@ -16620,7 +16813,12 @@
       <c r="A12" s="492" t="s">
         <v>210</v>
       </c>
-      <c r="C12" s="494"/>
+      <c r="B12" s="291">
+        <v>249.3</v>
+      </c>
+      <c r="C12" s="291">
+        <v>151.19999999999999</v>
+      </c>
       <c r="D12" s="494"/>
       <c r="E12" s="494"/>
       <c r="F12" s="494"/>
@@ -16652,7 +16850,7 @@
       <c r="AG12" s="494"/>
       <c r="AH12" s="495">
         <f>SUM(B12:AF12)</f>
-        <v>0</v>
+        <v>400.5</v>
       </c>
       <c r="AI12" s="496"/>
       <c r="AJ12" s="469"/>
@@ -16664,8 +16862,12 @@
       <c r="A13" s="497" t="s">
         <v>211</v>
       </c>
-      <c r="B13" s="774"/>
-      <c r="C13" s="669"/>
+      <c r="B13" s="774" t="s">
+        <v>307</v>
+      </c>
+      <c r="C13" s="774" t="s">
+        <v>307</v>
+      </c>
       <c r="D13" s="669"/>
       <c r="E13" s="803"/>
       <c r="F13" s="802"/>
@@ -16692,7 +16894,7 @@
       <c r="AA13" s="669"/>
       <c r="AB13" s="798"/>
       <c r="AC13" s="883"/>
-      <c r="AD13" s="891"/>
+      <c r="AD13" s="890"/>
       <c r="AE13" s="682"/>
       <c r="AF13" s="682"/>
       <c r="AG13" s="685"/>
@@ -16710,7 +16912,12 @@
       <c r="A14" s="467" t="s">
         <v>213</v>
       </c>
-      <c r="C14" s="498"/>
+      <c r="B14" s="291">
+        <v>5</v>
+      </c>
+      <c r="C14" s="291">
+        <v>3</v>
+      </c>
       <c r="D14" s="498"/>
       <c r="E14" s="498"/>
       <c r="F14" s="498"/>
@@ -16742,7 +16949,7 @@
       <c r="AG14" s="498"/>
       <c r="AH14" s="468">
         <f>SUM(B14:AF14)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:149" s="504" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -16781,9 +16988,9 @@
       <c r="AE15" s="501"/>
       <c r="AF15" s="501"/>
       <c r="AG15" s="718"/>
-      <c r="AH15" s="500" t="str">
+      <c r="AH15" s="500">
         <f>IF(AH12=0,"",+(AH36*10)/AH12)</f>
-        <v/>
+        <v>7.0661672908863924</v>
       </c>
       <c r="AI15" s="502"/>
       <c r="AJ15" s="503"/>
@@ -17121,17 +17328,17 @@
         <f>+'Water '!$D7</f>
         <v>55</v>
       </c>
-      <c r="C20" s="508" t="str">
+      <c r="C20" s="508">
         <f>+'Water '!$D8</f>
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="D20" s="508" t="str">
         <f>+'Water '!$D9</f>
         <v>0</v>
       </c>
-      <c r="E20" s="508" t="str">
+      <c r="E20" s="508">
         <f>+'Water '!$D10</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="F20" s="508" t="str">
         <f>+'Water '!$D11</f>
@@ -17244,7 +17451,7 @@
       <c r="AG20" s="509"/>
       <c r="AH20" s="484">
         <f>SUM($B20:AF20)</f>
-        <v>55</v>
+        <v>251</v>
       </c>
       <c r="AI20" s="484"/>
       <c r="AJ20" s="485"/>
@@ -17257,13 +17464,13 @@
         <f>+'Water '!$E7</f>
         <v>180</v>
       </c>
-      <c r="C21" s="511" t="str">
+      <c r="C21" s="511">
         <f>+'Water '!$E8</f>
-        <v>0</v>
-      </c>
-      <c r="D21" s="511" t="str">
+        <v>180</v>
+      </c>
+      <c r="D21" s="511">
         <f>+'Water '!$E9</f>
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="E21" s="511" t="str">
         <f>+'Water '!$E10</f>
@@ -17380,7 +17587,7 @@
       <c r="AG21" s="509"/>
       <c r="AH21" s="484">
         <f>SUM($B21:AF21)</f>
-        <v>180</v>
+        <v>487</v>
       </c>
       <c r="AI21" s="484"/>
     </row>
@@ -17394,15 +17601,15 @@
       </c>
       <c r="C22" s="514">
         <f>SUM(C19:C21)</f>
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="D22" s="514">
         <f>SUM(D19:D21)</f>
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="E22" s="514">
         <f>SUM(E19:E21)</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="F22" s="514">
         <f t="shared" ref="F22:AF22" si="3">SUM(F19:F21)</f>
@@ -17515,7 +17722,7 @@
       <c r="AG22" s="515"/>
       <c r="AH22" s="516">
         <f>SUM($B22:AF22)</f>
-        <v>235</v>
+        <v>738</v>
       </c>
       <c r="AI22" s="514"/>
       <c r="AJ22" s="517"/>
@@ -17758,11 +17965,11 @@
       </c>
       <c r="C26" s="485">
         <f>0.73*(C112+C19)</f>
-        <v>0</v>
+        <v>139.43</v>
       </c>
       <c r="D26" s="485">
         <f t="shared" ref="D26:AF26" si="4">0.73*(D71+D19)</f>
-        <v>0</v>
+        <v>97.82</v>
       </c>
       <c r="E26" s="485">
         <f t="shared" si="4"/>
@@ -17879,21 +18086,21 @@
       <c r="AG26" s="521"/>
       <c r="AH26" s="484">
         <f>SUM($B26:AF26)</f>
-        <v>181.04</v>
+        <v>418.29</v>
       </c>
       <c r="AI26" s="523">
         <f>AH29+AH45+AH36</f>
-        <v>425</v>
+        <v>854</v>
       </c>
       <c r="AK26" s="524">
         <f>(AI26*10)/AH9</f>
-        <v>11.562587059479036</v>
+        <v>13.116248666873087</v>
       </c>
     </row>
     <row r="27" spans="1:149" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="E27" s="485">
         <f>0.73*(E112+E20)</f>
-        <v>0</v>
+        <v>46.72</v>
       </c>
       <c r="M27" s="469"/>
       <c r="AI27" s="484"/>
@@ -18046,15 +18253,15 @@
       </c>
       <c r="C29" s="508">
         <f>'Water '!H8</f>
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="D29" s="508">
         <f>'Water '!H9</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E29" s="508">
         <f>'Water '!H10</f>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="F29" s="508">
         <f>'Water '!H11</f>
@@ -18167,7 +18374,7 @@
       <c r="AG29" s="509"/>
       <c r="AH29" s="484">
         <f>SUM($B29:AF29)</f>
-        <v>249</v>
+        <v>531</v>
       </c>
       <c r="AI29" s="484"/>
       <c r="AJ29" s="484"/>
@@ -18181,9 +18388,9 @@
         <f t="shared" si="5"/>
         <v>157</v>
       </c>
-      <c r="C30" s="508" t="str">
+      <c r="C30" s="508">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="D30" s="508" t="str">
         <f t="shared" si="5"/>
@@ -18304,7 +18511,7 @@
       <c r="AG30" s="509"/>
       <c r="AH30" s="484">
         <f>AH36</f>
-        <v>157</v>
+        <v>283</v>
       </c>
       <c r="AI30" s="484"/>
       <c r="AJ30" s="484"/>
@@ -18318,17 +18525,17 @@
         <f t="shared" si="6"/>
         <v>19</v>
       </c>
-      <c r="C31" s="508" t="str">
+      <c r="C31" s="508">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="D31" s="508" t="str">
+        <v>16</v>
+      </c>
+      <c r="D31" s="508">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E31" s="508" t="str">
+        <v>3</v>
+      </c>
+      <c r="E31" s="508">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F31" s="508" t="str">
         <f t="shared" si="6"/>
@@ -18441,7 +18648,7 @@
       <c r="AG31" s="509"/>
       <c r="AH31" s="484">
         <f>AH45</f>
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="AI31" s="484"/>
       <c r="AJ31" s="484"/>
@@ -18456,15 +18663,15 @@
       </c>
       <c r="C32" s="526">
         <f>SUM(C28:C31)</f>
-        <v>0</v>
+        <v>332</v>
       </c>
       <c r="D32" s="526">
         <f t="shared" ref="D32:AF32" si="7">SUM(D28:D31)</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="E32" s="526">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="F32" s="526">
         <f t="shared" si="7"/>
@@ -18577,7 +18784,7 @@
       <c r="AG32" s="527"/>
       <c r="AH32" s="526">
         <f>SUM($B32:AF32)</f>
-        <v>425</v>
+        <v>854</v>
       </c>
       <c r="AI32" s="526"/>
       <c r="AJ32" s="528"/>
@@ -18730,9 +18937,9 @@
         <f>+'Water '!$J7</f>
         <v>157</v>
       </c>
-      <c r="C36" s="535" t="str">
+      <c r="C36" s="535">
         <f>+'Water '!$J8</f>
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="D36" s="535" t="str">
         <f>+'Water '!$J9</f>
@@ -18853,7 +19060,7 @@
       <c r="AG36" s="508"/>
       <c r="AH36" s="484">
         <f>SUM($B36:AF36)</f>
-        <v>157</v>
+        <v>283</v>
       </c>
       <c r="AI36" s="484"/>
     </row>
@@ -19540,9 +19747,9 @@
         <f>+'Water '!$N7</f>
         <v>59</v>
       </c>
-      <c r="C41" s="539" t="str">
+      <c r="C41" s="539">
         <f>+'Water '!$N8</f>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="D41" s="539" t="str">
         <f>+'Water '!$N9</f>
@@ -19663,7 +19870,7 @@
       <c r="AG41" s="539"/>
       <c r="AH41" s="514">
         <f>SUM($B41:AF41)</f>
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="AI41" s="514"/>
       <c r="AJ41" s="514"/>
@@ -19789,9 +19996,9 @@
         <f>+'Water '!$O7</f>
         <v>99</v>
       </c>
-      <c r="C42" s="508" t="str">
+      <c r="C42" s="508">
         <f>+'Water '!$O8</f>
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="D42" s="508" t="str">
         <f>+'Water '!$O9</f>
@@ -19912,7 +20119,7 @@
       <c r="AG42" s="508"/>
       <c r="AH42" s="540">
         <f>SUM($B42:AF42)</f>
-        <v>99</v>
+        <v>180</v>
       </c>
       <c r="AI42" s="508"/>
       <c r="AJ42" s="508"/>
@@ -20038,8 +20245,8 @@
         <f t="array" ref="B43:AF43">TRANSPOSE('Water '!P7:P37)</f>
         <v>16</v>
       </c>
-      <c r="C43" s="541" t="str">
-        <v>0</v>
+      <c r="C43" s="541">
+        <v>15</v>
       </c>
       <c r="D43" s="541" t="str">
         <v>0</v>
@@ -20131,7 +20338,7 @@
       <c r="AG43" s="542"/>
       <c r="AH43" s="543">
         <f>SUM($B43:AF43)</f>
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="AI43" s="544"/>
       <c r="AJ43" s="474"/>
@@ -20257,9 +20464,9 @@
         <f>+'Water '!$M7</f>
         <v>2</v>
       </c>
-      <c r="C44" s="508" t="str">
+      <c r="C44" s="508">
         <f>+'Water '!$M8</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D44" s="508" t="str">
         <f>+'Water '!$M9</f>
@@ -20380,7 +20587,7 @@
       <c r="AG44" s="508"/>
       <c r="AH44" s="484">
         <f>SUM($B44:AF44)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AI44" s="484"/>
       <c r="AJ44" s="291"/>
@@ -20506,17 +20713,17 @@
         <f>+'Water '!$Q7</f>
         <v>19</v>
       </c>
-      <c r="C45" s="539" t="str">
+      <c r="C45" s="539">
         <f>+'Water '!$Q8</f>
-        <v>0</v>
-      </c>
-      <c r="D45" s="539" t="str">
+        <v>16</v>
+      </c>
+      <c r="D45" s="539">
         <f>+'Water '!$Q9</f>
-        <v>0</v>
-      </c>
-      <c r="E45" s="539" t="str">
+        <v>3</v>
+      </c>
+      <c r="E45" s="539">
         <f>+'Water '!$Q10</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F45" s="539" t="str">
         <f>+'Water '!$Q11</f>
@@ -20629,7 +20836,7 @@
       <c r="AG45" s="539"/>
       <c r="AH45" s="514">
         <f>SUM($B45:AF45)</f>
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="AI45" s="514"/>
       <c r="AJ45" s="514"/>
@@ -21223,15 +21430,15 @@
       </c>
       <c r="C50" s="484">
         <f t="shared" ref="C50:AE50" si="8">SUM(C36:C48)</f>
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="D50" s="484">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E50" s="484">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F50" s="484">
         <f t="shared" si="8"/>
@@ -21344,7 +21551,7 @@
       <c r="AG50" s="484"/>
       <c r="AH50" s="484">
         <f>SUM($B50:AF50)</f>
-        <v>352</v>
+        <v>642</v>
       </c>
       <c r="AI50" s="484"/>
     </row>
@@ -21444,9 +21651,9 @@
         <f t="shared" ref="B54:F54" si="9">IF(B$9=0,"",+(B36*10)/B$9)</f>
         <v>4.2713556902075496</v>
       </c>
-      <c r="C54" s="545" t="str">
+      <c r="C54" s="545">
         <f t="shared" si="9"/>
-        <v/>
+        <v>4.4438801422041649</v>
       </c>
       <c r="D54" s="545" t="str">
         <f t="shared" si="9"/>
@@ -21567,14 +21774,14 @@
       <c r="AG54" s="545"/>
       <c r="AH54" s="546">
         <f>+(AH36*10)/AH$9</f>
-        <v>4.2713556902075496</v>
+        <v>4.3464852139637982</v>
       </c>
       <c r="AI54" s="546">
         <v>3.2</v>
       </c>
       <c r="AJ54" s="547">
         <f t="shared" ref="AJ54:AJ67" si="11">AI54-AH54</f>
-        <v>-1.0713556902075494</v>
+        <v>-1.146485213963798</v>
       </c>
     </row>
     <row r="55" spans="1:59" s="553" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -21656,9 +21863,9 @@
         <f t="shared" ref="B56:C63" si="13">IF(B$9=0,"",+(B38*10)/B$9)</f>
         <v>0</v>
       </c>
-      <c r="C56" s="545" t="str">
+      <c r="C56" s="545">
         <f t="shared" si="13"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D56" s="545" t="str">
         <f t="shared" ref="D56:F62" si="14">IF(D$9=0,"",+(D38*10)/D$9)</f>
@@ -21820,9 +22027,9 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="C57" s="549" t="str">
+      <c r="C57" s="549">
         <f t="shared" si="13"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D57" s="549" t="str">
         <f t="shared" si="14"/>
@@ -21984,9 +22191,9 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="C58" s="545" t="str">
+      <c r="C58" s="545">
         <f t="shared" si="13"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D58" s="545" t="str">
         <f t="shared" si="14"/>
@@ -22150,9 +22357,9 @@
         <f t="shared" si="13"/>
         <v>1.6051591447276781</v>
       </c>
-      <c r="C59" s="549" t="str">
+      <c r="C59" s="549">
         <f t="shared" si="13"/>
-        <v/>
+        <v>1.5518311607697082</v>
       </c>
       <c r="D59" s="549" t="str">
         <f t="shared" si="14"/>
@@ -22273,14 +22480,14 @@
       <c r="AG59" s="549"/>
       <c r="AH59" s="549">
         <f t="shared" si="12"/>
-        <v>1.6051591447276781</v>
+        <v>1.5819363146228664</v>
       </c>
       <c r="AI59" s="550">
         <v>0.7</v>
       </c>
       <c r="AJ59" s="551">
         <f t="shared" si="11"/>
-        <v>-0.90515914472767811</v>
+        <v>-0.88193631462286648</v>
       </c>
       <c r="AK59" s="474"/>
       <c r="AL59" s="474"/>
@@ -22314,9 +22521,9 @@
         <f t="shared" si="13"/>
         <v>2.6934026326786462</v>
       </c>
-      <c r="C60" s="545" t="str">
+      <c r="C60" s="545">
         <f t="shared" si="13"/>
-        <v/>
+        <v>2.856780091416963</v>
       </c>
       <c r="D60" s="545" t="str">
         <f t="shared" si="14"/>
@@ -22437,14 +22644,14 @@
       <c r="AG60" s="545"/>
       <c r="AH60" s="568">
         <f t="shared" si="12"/>
-        <v>2.6934026326786462</v>
+        <v>2.764548899340932</v>
       </c>
       <c r="AI60" s="555">
         <v>2.1</v>
       </c>
       <c r="AJ60" s="547">
         <f t="shared" si="11"/>
-        <v>-0.59340263267864612</v>
+        <v>-0.66454889934093186</v>
       </c>
     </row>
     <row r="61" spans="1:59" s="504" customFormat="1" x14ac:dyDescent="0.35">
@@ -22455,9 +22662,9 @@
         <f t="shared" si="13"/>
         <v>0.43529739518038724</v>
       </c>
-      <c r="C61" s="549" t="str">
+      <c r="C61" s="549">
         <f t="shared" si="13"/>
-        <v/>
+        <v>0.5290333502624005</v>
       </c>
       <c r="D61" s="549" t="str">
         <f t="shared" si="14"/>
@@ -22578,14 +22785,14 @@
       <c r="AG61" s="549"/>
       <c r="AH61" s="550">
         <f t="shared" si="12"/>
-        <v>0.43529739518038724</v>
+        <v>0.4761167548864938</v>
       </c>
       <c r="AI61" s="550">
         <v>0.7</v>
       </c>
       <c r="AJ61" s="551">
         <f t="shared" si="11"/>
-        <v>0.26470260481961272</v>
+        <v>0.22388324511350616</v>
       </c>
       <c r="AK61" s="474"/>
       <c r="AL61" s="474"/>
@@ -22619,9 +22826,9 @@
         <f>IF(B$9=0,"",+(B44*10)/B$9)</f>
         <v>5.4412174397548405E-2</v>
       </c>
-      <c r="C62" s="545" t="str">
+      <c r="C62" s="545">
         <f>IF(C$9=0,"",+(C44*10)/C$9)</f>
-        <v/>
+        <v>0.10580667005248011</v>
       </c>
       <c r="D62" s="545" t="str">
         <f t="shared" si="14"/>
@@ -22742,14 +22949,14 @@
       <c r="AG62" s="545"/>
       <c r="AH62" s="555">
         <f>+(AH44*10)/AH$9</f>
-        <v>5.4412174397548405E-2</v>
+        <v>7.6793024981692548E-2</v>
       </c>
       <c r="AI62" s="555">
         <v>0.1</v>
       </c>
       <c r="AJ62" s="547">
         <f t="shared" si="11"/>
-        <v>4.5587825602451601E-2</v>
+        <v>2.3206975018307457E-2</v>
       </c>
     </row>
     <row r="63" spans="1:59" s="504" customFormat="1" x14ac:dyDescent="0.35">
@@ -22760,9 +22967,9 @@
         <f t="shared" si="13"/>
         <v>0.51691565677670981</v>
       </c>
-      <c r="C63" s="549" t="str">
+      <c r="C63" s="549">
         <f t="shared" si="13"/>
-        <v/>
+        <v>0.56430224027989395</v>
       </c>
       <c r="D63" s="549" t="str">
         <f>IF(D$9=0,"",+(D45*10)/D$9)</f>
@@ -22883,14 +23090,14 @@
       <c r="AG63" s="549"/>
       <c r="AH63" s="550">
         <f>+(AH45*10)/AH$9</f>
-        <v>0.51691565677670981</v>
+        <v>0.61434419985354038</v>
       </c>
       <c r="AI63" s="550">
         <v>0.6</v>
       </c>
       <c r="AJ63" s="551">
         <f t="shared" si="11"/>
-        <v>8.3084343223290169E-2</v>
+        <v>-1.4344199853540407E-2</v>
       </c>
       <c r="AK63" s="474"/>
       <c r="AL63" s="474"/>
@@ -22992,9 +23199,9 @@
         <f>IF(B$9=0,"",+(B46*10)/B$9)</f>
         <v>0</v>
       </c>
-      <c r="C65" s="549" t="str">
+      <c r="C65" s="549">
         <f>IF(C$9=0,"",+(C46*10)/C$9)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D65" s="549" t="str">
         <f>IF(D$9=0,"",+(D46*10)/D$9)</f>
@@ -23294,7 +23501,7 @@
       </c>
       <c r="C68" s="584">
         <f>SUM(C54:C63,C65)</f>
-        <v>0</v>
+        <v>10.051633654985611</v>
       </c>
       <c r="D68" s="584">
         <f>SUM(D54:D63,D65)</f>
@@ -23415,7 +23622,7 @@
       <c r="AG68" s="585"/>
       <c r="AH68" s="584">
         <f t="shared" si="27"/>
-        <v>9.5765426939685181</v>
+        <v>9.8602244076493228</v>
       </c>
       <c r="AI68" s="584">
         <f>SUM(AI54:AI63,AI65)</f>
@@ -23423,7 +23630,7 @@
       </c>
       <c r="AJ68" s="547">
         <f t="shared" si="27"/>
-        <v>2.3457306031480774E-2</v>
+        <v>-0.26022440764932314</v>
       </c>
       <c r="AK68" s="468"/>
       <c r="AL68" s="291"/>
@@ -23459,7 +23666,7 @@
       </c>
       <c r="C69" s="587">
         <f>SUM(C60:C62)</f>
-        <v>0</v>
+        <v>3.4916201117318435</v>
       </c>
       <c r="D69" s="587">
         <f t="shared" ref="D69:AJ69" si="28">SUM(D60:D62)</f>
@@ -23580,7 +23787,7 @@
       <c r="AG69" s="588"/>
       <c r="AH69" s="587">
         <f t="shared" si="28"/>
-        <v>3.1831122022565821</v>
+        <v>3.3174586792091185</v>
       </c>
       <c r="AI69" s="587">
         <f t="shared" si="28"/>
@@ -23588,7 +23795,7 @@
       </c>
       <c r="AJ69" s="587">
         <f t="shared" si="28"/>
-        <v>-0.28311220225658179</v>
+        <v>-0.41745867920911828</v>
       </c>
       <c r="AK69" s="589"/>
       <c r="AL69" s="291"/>
@@ -23657,13 +23864,13 @@
         <f>+'Water '!$F7</f>
         <v>248</v>
       </c>
-      <c r="C71" s="592" t="str">
+      <c r="C71" s="592">
         <f>+'Water '!$F8</f>
-        <v>0</v>
-      </c>
-      <c r="D71" s="592" t="str">
+        <v>191</v>
+      </c>
+      <c r="D71" s="592">
         <f>+'Water '!$F9</f>
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="E71" s="592" t="str">
         <f>+'Water '!$F10</f>
@@ -23780,7 +23987,7 @@
       <c r="AG71" s="593"/>
       <c r="AH71" s="594">
         <f>SUM($B71:AF71)</f>
-        <v>248</v>
+        <v>573</v>
       </c>
       <c r="AI71" s="594"/>
       <c r="AJ71" s="595"/>
@@ -23892,8 +24099,8 @@
       <c r="B74" s="795">
         <v>1600</v>
       </c>
-      <c r="C74" s="1023">
-        <v>0</v>
+      <c r="C74" s="893">
+        <v>1142</v>
       </c>
       <c r="D74" s="882">
         <v>0</v>
@@ -23918,7 +24125,7 @@
       <c r="T74" s="794"/>
       <c r="U74" s="794"/>
       <c r="V74" s="794"/>
-      <c r="W74" s="889"/>
+      <c r="W74" s="888"/>
       <c r="X74" s="882"/>
       <c r="Y74" s="882"/>
       <c r="Z74" s="882"/>
@@ -23931,7 +24138,7 @@
       <c r="AG74" s="794"/>
       <c r="AH74" s="516">
         <f>SUM(B74:AF74)</f>
-        <v>1600</v>
+        <v>2742</v>
       </c>
       <c r="AI74" s="537"/>
       <c r="AJ74" s="537"/>
@@ -23967,8 +24174,8 @@
         <f t="array" ref="B75:AF75">TRANSPOSE('CO2'!D7:D37)</f>
         <v>1579.4799999999814</v>
       </c>
-      <c r="C75" s="601" t="str">
-        <v>0</v>
+      <c r="C75" s="601">
+        <v>1141.6199999999953</v>
       </c>
       <c r="D75" s="601" t="str">
         <v>0</v>
@@ -24060,7 +24267,7 @@
       <c r="AG75" s="599"/>
       <c r="AH75" s="516">
         <f>SUM(B75:AF75)</f>
-        <v>1579.4799999999814</v>
+        <v>2721.0999999999767</v>
       </c>
       <c r="AI75" s="600"/>
       <c r="AJ75" s="600"/>
@@ -24095,8 +24302,8 @@
         <f t="array" ref="B76:AF76">TRANSPOSE('CO2'!B7:B37)</f>
         <v>194.34000000001106</v>
       </c>
-      <c r="C76" s="604" t="str">
-        <v>0</v>
+      <c r="C76" s="604">
+        <v>146.09999999999127</v>
       </c>
       <c r="D76" s="604" t="str">
         <v>0</v>
@@ -24188,7 +24395,7 @@
       <c r="AG76" s="604"/>
       <c r="AH76" s="604">
         <f>SUM($B76:AF76)</f>
-        <v>194.34000000001106</v>
+        <v>340.44000000000233</v>
       </c>
       <c r="AI76" s="605"/>
       <c r="AJ76" s="606"/>
@@ -24224,8 +24431,8 @@
         <f t="array" ref="B77:AF77">TRANSPOSE('CO2'!C7:C37)</f>
         <v>564.13000000000466</v>
       </c>
-      <c r="C77" s="789" t="str">
-        <v>0</v>
+      <c r="C77" s="789">
+        <v>475.41000000000349</v>
       </c>
       <c r="D77" s="789" t="str">
         <v>0</v>
@@ -24317,7 +24524,7 @@
       <c r="AG77" s="607"/>
       <c r="AH77" s="604">
         <f>SUM($B77:AF77)</f>
-        <v>564.13000000000466</v>
+        <v>1039.5400000000081</v>
       </c>
       <c r="AI77" s="757"/>
       <c r="AJ77" s="757" t="s">
@@ -24356,7 +24563,7 @@
       </c>
       <c r="C78" s="792">
         <f t="shared" ref="C78:T78" si="29">C75-C76-C77</f>
-        <v>0</v>
+        <v>520.11000000000058</v>
       </c>
       <c r="D78" s="792">
         <f t="shared" si="29"/>
@@ -24480,7 +24687,7 @@
       </c>
       <c r="AH78" s="484">
         <f>AH75-AH76-AH77</f>
-        <v>821.00999999996566</v>
+        <v>1341.1199999999662</v>
       </c>
       <c r="AI78" s="484"/>
     </row>
@@ -24494,7 +24701,7 @@
       </c>
       <c r="C79" s="609">
         <f>'Daily KPIs CO2'!C47</f>
-        <v>0</v>
+        <v>1141.6199999999953</v>
       </c>
       <c r="D79" s="609">
         <f>'Daily KPIs CO2'!D47</f>
@@ -24622,13 +24829,13 @@
         <v>7369</v>
       </c>
       <c r="C80" s="612">
-        <v>0</v>
+        <v>7089</v>
       </c>
       <c r="D80" s="612">
-        <v>0</v>
+        <v>3772</v>
       </c>
       <c r="E80" s="612">
-        <v>0</v>
+        <v>4062</v>
       </c>
       <c r="F80" s="612">
         <v>0</v>
@@ -24714,7 +24921,7 @@
       <c r="AG80" s="613"/>
       <c r="AH80" s="594">
         <f>SUM(B80:AF80)</f>
-        <v>7369</v>
+        <v>22292</v>
       </c>
       <c r="AI80" s="594"/>
       <c r="AJ80" s="614"/>
@@ -24815,10 +25022,10 @@
       <c r="A82" s="596"/>
       <c r="B82" s="612" cm="1">
         <f t="array" ref="B82:AF82">TRANSPOSE('Elec.OCTOBER 2026'!E9:E39)</f>
-        <v>0</v>
+        <v>4573.3</v>
       </c>
       <c r="C82" s="614">
-        <v>0</v>
+        <v>4756.6000000000004</v>
       </c>
       <c r="D82" s="614">
         <v>0</v>
@@ -24902,7 +25109,7 @@
         <v>0</v>
       </c>
       <c r="AE82" s="617">
-        <v>8426.5</v>
+        <v>26416.699999999997</v>
       </c>
       <c r="AF82" s="617">
         <v>0</v>
@@ -24910,7 +25117,7 @@
       <c r="AG82" s="617"/>
       <c r="AH82" s="594">
         <f>SUM(B82:AF82)</f>
-        <v>8426.5</v>
+        <v>35746.6</v>
       </c>
       <c r="AI82" s="594"/>
       <c r="AJ82" s="614"/>
@@ -24940,20 +25147,20 @@
     </row>
     <row r="83" spans="1:59" s="796" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A83" s="797" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="B83" s="594" cm="1">
         <f t="array" ref="B83:AF83">TRANSPOSE('Elec.OCTOBER 2026'!D7:D37)</f>
         <v>1057.5</v>
       </c>
       <c r="C83" s="594">
-        <v>0</v>
+        <v>1571.3</v>
       </c>
       <c r="D83" s="594">
-        <v>0</v>
+        <v>801.3</v>
       </c>
       <c r="E83" s="594">
-        <v>0</v>
+        <v>694.6</v>
       </c>
       <c r="F83" s="594">
         <v>0</v>
@@ -25039,7 +25246,7 @@
       <c r="AG83" s="621"/>
       <c r="AH83" s="594">
         <f>SUM(B83:AF83)</f>
-        <v>1057.5</v>
+        <v>4124.7000000000007</v>
       </c>
       <c r="AI83" s="594"/>
       <c r="AJ83" s="594"/>
@@ -25579,9 +25786,9 @@
         <f t="shared" ref="B90:AF90" si="33">IF(B$9=0,"",+(B22*10)/B$9)</f>
         <v>6.3934304917119373</v>
       </c>
-      <c r="C90" s="653" t="str">
+      <c r="C90" s="653">
         <f>IF(C$9=0,"",+(C22*10)/C$9)</f>
-        <v/>
+        <v>11.003893685457932</v>
       </c>
       <c r="D90" s="653" t="str">
         <f t="shared" si="33"/>
@@ -25702,18 +25909,18 @@
       <c r="AG90" s="627"/>
       <c r="AH90" s="659">
         <f>IF(AH$9=0,"0",+(AH22*10)/AH$9)</f>
-        <v>6.3934304917119373</v>
+        <v>11.33465048729782</v>
       </c>
       <c r="AI90" s="662">
         <v>10.199999999999999</v>
       </c>
       <c r="AJ90" s="665">
         <f>+AI90-AH90</f>
-        <v>3.806569508288062</v>
+        <v>-1.1346504872978205</v>
       </c>
       <c r="AK90" s="667">
         <f>AH90/AI90*100</f>
-        <v>62.680691095215082</v>
+        <v>111.12402438527276</v>
       </c>
       <c r="AL90" s="629"/>
       <c r="AM90" s="630"/>
@@ -25813,9 +26020,9 @@
         <f t="shared" ref="B92:AF92" si="35">IF(B$9=0,"",+B74/B$9)</f>
         <v>4.3529739518038726</v>
       </c>
-      <c r="C92" s="653" t="str">
+      <c r="C92" s="653">
         <f t="shared" si="35"/>
-        <v/>
+        <v>4.0277072399977429</v>
       </c>
       <c r="D92" s="653" t="str">
         <f t="shared" si="35"/>
@@ -25936,18 +26143,18 @@
       <c r="AG92" s="628"/>
       <c r="AH92" s="670">
         <f>IF(AH$9=0,"0",+(AH74)/AH$9)</f>
-        <v>4.3529739518038726</v>
+        <v>4.2113294899960199</v>
       </c>
       <c r="AI92" s="674">
         <v>5</v>
       </c>
       <c r="AJ92" s="675">
         <f>AI92-AH92</f>
-        <v>0.64702604819612741</v>
+        <v>0.78867051000398014</v>
       </c>
       <c r="AK92" s="673">
         <f t="shared" si="34"/>
-        <v>87.059479036077448</v>
+        <v>84.22658979992039</v>
       </c>
       <c r="AL92" s="629"/>
       <c r="AM92" s="630"/>
@@ -25982,9 +26189,9 @@
         <f>IF(B$9=0,"",+B76/B$9)</f>
         <v>0.52872309862100797</v>
       </c>
-      <c r="C93" s="653" t="str">
+      <c r="C93" s="653">
         <f t="shared" ref="C93:AF93" si="36">IF(C$9=0,"",+C76/C$9)</f>
-        <v/>
+        <v>0.51527848315554736</v>
       </c>
       <c r="D93" s="653" t="str">
         <f t="shared" si="36"/>
@@ -26105,18 +26312,18 @@
       <c r="AG93" s="628"/>
       <c r="AH93" s="670">
         <f>IF(AH$9=0,"0",+AH76/AH$9)</f>
-        <v>0.52872309862100797</v>
+        <v>0.5228683484953518</v>
       </c>
       <c r="AI93" s="674">
         <v>1.7</v>
       </c>
       <c r="AJ93" s="676">
         <f>AI93-AH93</f>
-        <v>1.1712769013789921</v>
+        <v>1.1771316515046482</v>
       </c>
       <c r="AK93" s="673">
         <f t="shared" si="34"/>
-        <v>31.101358742412234</v>
+        <v>30.756961676197164</v>
       </c>
       <c r="AL93" s="635"/>
       <c r="AM93" s="636"/>
@@ -26149,9 +26356,9 @@
         <f>IF(B$9=0,"",(B80+B83)/B$9)</f>
         <v>22.925209378047082</v>
       </c>
-      <c r="C94" s="653" t="str">
+      <c r="C94" s="653">
         <f>IF(C$9=0,"",(C80+C83)/C$9)</f>
-        <v/>
+        <v>30.543916821849781</v>
       </c>
       <c r="D94" s="653" t="str">
         <f>IF(D$9=0,"",(D80+D83)/D$9)</f>
@@ -26272,18 +26479,18 @@
       <c r="AG94" s="627"/>
       <c r="AH94" s="670">
         <f>IF(AH$9=0,"0",+(AH80+AH83)/AH$9)</f>
-        <v>22.925209378047082</v>
+        <v>40.572366060677552</v>
       </c>
       <c r="AI94" s="674">
         <v>22</v>
       </c>
       <c r="AJ94" s="675">
         <f>AI94-AH94</f>
-        <v>-0.92520937804708225</v>
+        <v>-18.572366060677552</v>
       </c>
       <c r="AK94" s="673">
         <f>AH94/AI94*100</f>
-        <v>104.20549717294128</v>
+        <v>184.41984573035251</v>
       </c>
       <c r="AL94" s="629"/>
       <c r="AM94" s="630"/>
@@ -26343,7 +26550,7 @@
       <c r="AG95" s="637"/>
       <c r="AH95" s="670">
         <f>IF(AH$9=0,"0",+(AH78*10)/AH$9)</f>
-        <v>22.336469651064675</v>
+        <v>20.597732332688985</v>
       </c>
       <c r="AI95" s="674"/>
       <c r="AJ95" s="676"/>
@@ -26382,9 +26589,9 @@
         <f t="shared" ref="B96:I96" si="38">IF(B$9=0,"",B84/B$9)</f>
         <v>2.6117843710823236</v>
       </c>
-      <c r="C96" s="653" t="str">
+      <c r="C96" s="653">
         <f t="shared" si="38"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D96" s="654" t="str">
         <f t="shared" si="38"/>
@@ -26505,18 +26712,18 @@
       <c r="AG96" s="627"/>
       <c r="AH96" s="660">
         <f>IF(AH$9=0,"0",+(AH84)/AH$9)</f>
-        <v>2.6117843710823236</v>
+        <v>1.4744260796484969</v>
       </c>
       <c r="AI96" s="663">
         <v>7.2</v>
       </c>
       <c r="AJ96" s="677">
         <f>AI96-AH96</f>
-        <v>4.588215628917677</v>
+        <v>5.7255739203515033</v>
       </c>
       <c r="AK96" s="668">
         <f t="shared" si="34"/>
-        <v>36.274782931698937</v>
+        <v>20.47813999511801</v>
       </c>
       <c r="AL96" s="629"/>
       <c r="AM96" s="630"/>
@@ -26976,7 +27183,7 @@
       </c>
       <c r="C103" s="649">
         <f>IF('Entries October 2026'!L8-'Entries October 2026'!L7&lt;1,0,'Entries October 2026'!L8-'Entries October 2026'!L7)</f>
-        <v>0</v>
+        <v>475.41000000000349</v>
       </c>
       <c r="D103" s="649">
         <f>IF('Entries October 2026'!L9-'Entries October 2026'!L8&lt;1,0,'Entries October 2026'!L9-'Entries October 2026'!L8)</f>
@@ -27122,9 +27329,9 @@
         <f t="shared" ref="B105:AF105" si="41">IF(B103=0,"",B104/B103)</f>
         <v>0</v>
       </c>
-      <c r="C105" s="651" t="str">
+      <c r="C105" s="651">
         <f>IF(C103=0,"",C104/C103)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D105" s="651" t="str">
         <f t="shared" si="41"/>
@@ -27407,9 +27614,9 @@
       <c r="B112" s="524" t="s">
         <v>147</v>
       </c>
-      <c r="C112" s="508" t="str">
+      <c r="C112" s="508">
         <f>+'Water '!$F8</f>
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="M112" s="469"/>
       <c r="AB112" s="469" t="s">
@@ -27423,7 +27630,7 @@
       </c>
       <c r="AH112" s="484">
         <f>SUM($B112:AC112)</f>
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="AI112" s="484"/>
     </row>
@@ -27443,11 +27650,11 @@
       </c>
       <c r="D116" s="649">
         <f>'Daily KPIs'!D80</f>
-        <v>0</v>
+        <v>3772</v>
       </c>
       <c r="E116" s="649">
         <f>'Daily KPIs'!E80</f>
-        <v>0</v>
+        <v>4062</v>
       </c>
       <c r="F116" s="649">
         <f>'Daily KPIs'!F80</f>
@@ -27560,13 +27767,13 @@
       <c r="AG116" s="650"/>
       <c r="AH116" s="649">
         <f>'Daily KPIs'!AH80</f>
-        <v>7369</v>
+        <v>22292</v>
       </c>
     </row>
     <row r="117" spans="2:34" hidden="1" x14ac:dyDescent="0.35">
       <c r="C117" s="649">
         <f>'Daily KPIs'!C80</f>
-        <v>0</v>
+        <v>7089</v>
       </c>
       <c r="M117" s="469"/>
     </row>
@@ -27650,7 +27857,7 @@
       </c>
       <c r="AH140" s="874">
         <f>AH83/(AH83+AH80)</f>
-        <v>0.12549694416424376</v>
+        <v>0.15613986606956964</v>
       </c>
       <c r="AM140" s="751"/>
     </row>
@@ -28008,7 +28215,7 @@
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
       <c r="F1" s="66" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G1" s="9"/>
       <c r="H1" s="9"/>
@@ -28268,11 +28475,11 @@
       </c>
       <c r="C8" s="55">
         <f t="shared" ref="C8:C34" si="1">B9-B8</f>
-        <v>-253049</v>
+        <v>132</v>
       </c>
       <c r="D8" s="55">
         <f t="shared" ref="D8:D35" si="2">C8-G8</f>
-        <v>1113235</v>
+        <v>-59</v>
       </c>
       <c r="E8" s="56">
         <f>'Entries October 2026'!W7</f>
@@ -28284,7 +28491,7 @@
       </c>
       <c r="G8" s="43">
         <f>F9-F8</f>
-        <v>-1366284</v>
+        <v>191</v>
       </c>
       <c r="H8" s="57">
         <f>'Entries October 2026'!AA7</f>
@@ -28292,7 +28499,7 @@
       </c>
       <c r="I8" s="58">
         <f t="shared" ref="I8:I34" si="3">H9-H8</f>
-        <v>-97122</v>
+        <v>0</v>
       </c>
       <c r="J8" s="57">
         <f>'Entries October 2026'!T7</f>
@@ -28304,7 +28511,7 @@
       </c>
       <c r="L8" s="58">
         <f>K8+I8</f>
-        <v>-97122</v>
+        <v>0</v>
       </c>
       <c r="M8" s="57">
         <f>'Entries October 2026'!R7</f>
@@ -28312,11 +28519,11 @@
       </c>
       <c r="N8" s="57">
         <f>'Entries October 2026'!AC8-'Entries October 2026'!AC7</f>
-        <v>-6766</v>
+        <v>15</v>
       </c>
       <c r="O8" s="57">
         <f t="shared" ref="O8:O34" si="5">C8+D8+G8</f>
-        <v>-506098</v>
+        <v>264</v>
       </c>
       <c r="P8" s="62"/>
       <c r="Q8" s="42"/>
@@ -28331,7 +28538,7 @@
       </c>
       <c r="B9" s="55">
         <f>'Entries October 2026'!O8</f>
-        <v>0</v>
+        <v>253181</v>
       </c>
       <c r="C9" s="55">
         <f t="shared" si="1"/>
@@ -28339,7 +28546,7 @@
       </c>
       <c r="D9" s="55">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-134</v>
       </c>
       <c r="E9" s="56">
         <f>'Entries October 2026'!W8</f>
@@ -28347,15 +28554,15 @@
       </c>
       <c r="F9" s="57">
         <f>'Entries October 2026'!V8</f>
-        <v>0</v>
+        <v>1366475</v>
       </c>
       <c r="G9" s="57">
         <f>F10-F9</f>
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="H9" s="57">
         <f>'Entries October 2026'!AA8</f>
-        <v>0</v>
+        <v>97122</v>
       </c>
       <c r="I9" s="58">
         <f t="shared" si="3"/>
@@ -28398,15 +28605,15 @@
       </c>
       <c r="B10" s="55">
         <f>'Entries October 2026'!O9</f>
-        <v>0</v>
+        <v>253181</v>
       </c>
       <c r="C10" s="55">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="D10" s="55">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="E10" s="56">
         <f>'Entries October 2026'!W9</f>
@@ -28414,7 +28621,7 @@
       </c>
       <c r="F10" s="57">
         <f>'Entries October 2026'!V9</f>
-        <v>0</v>
+        <v>1366609</v>
       </c>
       <c r="G10" s="43">
         <f t="shared" ref="G10:G34" si="7">F11-F10</f>
@@ -28422,7 +28629,7 @@
       </c>
       <c r="H10" s="57">
         <f>'Entries October 2026'!AA9</f>
-        <v>0</v>
+        <v>97122</v>
       </c>
       <c r="I10" s="58">
         <f t="shared" si="3"/>
@@ -28450,7 +28657,7 @@
       </c>
       <c r="O10" s="57">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="P10" s="62"/>
       <c r="Q10" s="42"/>
@@ -28465,15 +28672,15 @@
       </c>
       <c r="B11" s="55">
         <f>'Entries October 2026'!O10</f>
-        <v>0</v>
+        <v>253245</v>
       </c>
       <c r="C11" s="55">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-253245</v>
       </c>
       <c r="D11" s="55">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1113364</v>
       </c>
       <c r="E11" s="56">
         <f>'Entries October 2026'!W10</f>
@@ -28481,19 +28688,19 @@
       </c>
       <c r="F11" s="57">
         <f>'Entries October 2026'!V10</f>
-        <v>0</v>
+        <v>1366609</v>
       </c>
       <c r="G11" s="57">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-1366609</v>
       </c>
       <c r="H11" s="57">
         <f>'Entries October 2026'!AA10</f>
-        <v>0</v>
+        <v>97122</v>
       </c>
       <c r="I11" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-97122</v>
       </c>
       <c r="J11" s="57">
         <f>'Entries October 2026'!T10</f>
@@ -28505,7 +28712,7 @@
       </c>
       <c r="L11" s="58">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-97122</v>
       </c>
       <c r="M11" s="57">
         <f>'Entries October 2026'!R10</f>
@@ -28513,11 +28720,11 @@
       </c>
       <c r="N11" s="57">
         <f>'Entries October 2026'!AC11-'Entries October 2026'!AC10</f>
-        <v>0</v>
+        <v>-6781</v>
       </c>
       <c r="O11" s="57">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-506490</v>
       </c>
       <c r="P11" s="62"/>
       <c r="Q11" s="45"/>
@@ -30265,24 +30472,24 @@
     </row>
     <row r="6" spans="1:20" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="923" t="s">
+      <c r="A7" s="924" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="383"/>
       <c r="C7" s="383"/>
-      <c r="D7" s="936" t="s">
+      <c r="D7" s="937" t="s">
         <v>254</v>
       </c>
-      <c r="E7" s="939" t="s">
+      <c r="E7" s="940" t="s">
         <v>286</v>
       </c>
-      <c r="F7" s="933" t="s">
+      <c r="F7" s="934" t="s">
         <v>287</v>
       </c>
-      <c r="G7" s="929" t="s">
+      <c r="G7" s="930" t="s">
         <v>255</v>
       </c>
-      <c r="H7" s="929" t="s">
+      <c r="H7" s="930" t="s">
         <v>256</v>
       </c>
       <c r="I7" s="383" t="s">
@@ -30294,33 +30501,33 @@
       <c r="K7" s="390" t="s">
         <v>53</v>
       </c>
-      <c r="L7" s="930" t="s">
+      <c r="L7" s="931" t="s">
         <v>17</v>
       </c>
-      <c r="M7" s="931"/>
-      <c r="N7" s="931"/>
-      <c r="O7" s="931"/>
-      <c r="P7" s="932"/>
-      <c r="Q7" s="927" t="s">
+      <c r="M7" s="932"/>
+      <c r="N7" s="932"/>
+      <c r="O7" s="932"/>
+      <c r="P7" s="933"/>
+      <c r="Q7" s="928" t="s">
         <v>11</v>
       </c>
-      <c r="R7" s="928"/>
-      <c r="S7" s="928"/>
-      <c r="T7" s="928"/>
+      <c r="R7" s="929"/>
+      <c r="S7" s="929"/>
+      <c r="T7" s="929"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="924"/>
+      <c r="A8" s="925"/>
       <c r="B8" s="384" t="s">
         <v>257</v>
       </c>
       <c r="C8" s="384" t="s">
         <v>258</v>
       </c>
-      <c r="D8" s="937"/>
-      <c r="E8" s="940"/>
-      <c r="F8" s="934"/>
-      <c r="G8" s="929"/>
-      <c r="H8" s="929"/>
+      <c r="D8" s="938"/>
+      <c r="E8" s="941"/>
+      <c r="F8" s="935"/>
+      <c r="G8" s="930"/>
+      <c r="H8" s="930"/>
       <c r="I8" s="383"/>
       <c r="J8" s="383"/>
       <c r="K8" s="390"/>
@@ -30343,12 +30550,12 @@
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A9" s="925"/>
+      <c r="A9" s="926"/>
       <c r="B9" s="385"/>
       <c r="C9" s="385"/>
-      <c r="D9" s="938"/>
-      <c r="E9" s="941"/>
-      <c r="F9" s="935"/>
+      <c r="D9" s="939"/>
+      <c r="E9" s="942"/>
+      <c r="F9" s="936"/>
       <c r="G9" s="383" t="s">
         <v>56</v>
       </c>
@@ -30476,9 +30683,9 @@
       <c r="A11" s="719">
         <v>2</v>
       </c>
-      <c r="B11" s="719" t="str">
+      <c r="B11" s="719">
         <f>IF('Entries October 2026'!I8&lt;'Entries October 2026'!I7,"0",(IF('Entries October 2026'!I8&gt;='Entries October 2026'!I7,'Entries October 2026'!I8-'Entries October 2026'!I7,(999999-'Entries October 2026'!I7)+'Entries October 2026'!I8+1)))</f>
-        <v>0</v>
+        <v>7089</v>
       </c>
       <c r="C11" s="719" t="str">
         <f>IF('Entries October 2026'!J8&lt;='Entries October 2026'!J7,"0",IF('Entries October 2026'!J8&gt;='Entries October 2026'!J7,'Entries October 2026'!J8-'Entries October 2026'!J7,(999999-'Entries October 2026'!J7)+'Entries October 2026'!J8+1))</f>
@@ -30486,24 +30693,26 @@
       </c>
       <c r="D11" s="720">
         <f t="shared" ref="D11:D40" si="0">B11+C11</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="877"/>
-      <c r="F11" s="721" t="str">
+        <v>7089</v>
+      </c>
+      <c r="E11" s="877">
+        <v>1571.3</v>
+      </c>
+      <c r="F11" s="721">
         <f t="shared" ref="F11:F40" si="1">IF((E11+D11)=0,"0",E11/(D11+E11))</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="737" t="str">
+        <v>0.18143713266284078</v>
+      </c>
+      <c r="G11" s="737">
         <f>IF('Entries October 2026'!K8&lt;'Entries October 2026'!K7,"0",IF('Entries October 2026'!K8&gt;='Entries October 2026'!K7,'Entries October 2026'!K8-'Entries October 2026'!K7,(999999-'Entries October 2026'!K7)+'Entries October 2026'!K8+1))</f>
         <v>0</v>
       </c>
       <c r="H11" s="720">
         <f t="shared" ref="H11:H40" si="2">D11+G11+E11</f>
-        <v>0</v>
+        <v>8660.2999999999993</v>
       </c>
       <c r="I11" s="737">
         <f>'Water '!Z8*10</f>
-        <v>0</v>
+        <v>3120</v>
       </c>
       <c r="J11" s="720" t="str">
         <f>IF('Entries October 2026'!B8-'Entries October 2026'!B7&lt;1,"0",'Entries October 2026'!B8-'Entries October 2026'!B7)</f>
@@ -30511,7 +30720,7 @@
       </c>
       <c r="K11" s="722">
         <f>'CO2'!E8</f>
-        <v>0</v>
+        <v>1142</v>
       </c>
       <c r="L11" s="723">
         <f>+'PROD.FIG. '!F6</f>
@@ -30530,15 +30739,15 @@
         <v>0</v>
       </c>
       <c r="P11" s="724">
-        <v>0</v>
+        <v>283.536</v>
       </c>
       <c r="Q11" s="393">
         <f t="shared" ref="Q11:Q40" si="3">IF(P11=0,0,H11/P11)</f>
-        <v>0</v>
+        <v>30.543916821849781</v>
       </c>
       <c r="R11" s="393">
         <f t="shared" ref="R11:R40" si="4">IF(Q11=0,0,I11/P11)</f>
-        <v>0</v>
+        <v>11.003893685457932</v>
       </c>
       <c r="S11" s="393">
         <f t="shared" ref="S11:S40" si="5">IF(R11=0,0,J11/P11)</f>
@@ -30555,7 +30764,7 @@
       </c>
       <c r="B12" s="719">
         <f>IF('Entries October 2026'!I9&lt;'Entries October 2026'!I8,"0",(IF('Entries October 2026'!I9&gt;='Entries October 2026'!I8,'Entries October 2026'!I9-'Entries October 2026'!I8,(999999-'Entries October 2026'!I8)+'Entries October 2026'!I9+1)))</f>
-        <v>0</v>
+        <v>3772</v>
       </c>
       <c r="C12" s="719" t="str">
         <f>IF('Entries October 2026'!J9&lt;='Entries October 2026'!J8,"0",IF('Entries October 2026'!J9&gt;='Entries October 2026'!J8,'Entries October 2026'!J9-'Entries October 2026'!J8,(999999-'Entries October 2026'!J8)+'Entries October 2026'!J9+1))</f>
@@ -30563,12 +30772,14 @@
       </c>
       <c r="D12" s="720">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E12" s="877"/>
-      <c r="F12" s="721" t="str">
+        <v>3772</v>
+      </c>
+      <c r="E12" s="879">
+        <v>801.3</v>
+      </c>
+      <c r="F12" s="721">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.17521264732250233</v>
       </c>
       <c r="G12" s="737">
         <f>IF('Entries October 2026'!K9&lt;'Entries October 2026'!K8,"0",IF('Entries October 2026'!K9&gt;='Entries October 2026'!K8,'Entries October 2026'!K9-'Entries October 2026'!K8,(999999-'Entries October 2026'!K8)+'Entries October 2026'!K9+1))</f>
@@ -30576,11 +30787,11 @@
       </c>
       <c r="H12" s="720">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4573.3</v>
       </c>
       <c r="I12" s="737">
         <f>'Water '!Z9*10</f>
-        <v>0</v>
+        <v>1270</v>
       </c>
       <c r="J12" s="720" t="str">
         <f>IF('Entries October 2026'!B9-'Entries October 2026'!B8&lt;1,"0",'Entries October 2026'!B9-'Entries October 2026'!B8)</f>
@@ -30632,7 +30843,7 @@
       </c>
       <c r="B13" s="719">
         <f>IF('Entries October 2026'!I10&lt;'Entries October 2026'!I9,"0",(IF('Entries October 2026'!I10&gt;='Entries October 2026'!I9,'Entries October 2026'!I10-'Entries October 2026'!I9,(999999-'Entries October 2026'!I9)+'Entries October 2026'!I10+1)))</f>
-        <v>0</v>
+        <v>4062</v>
       </c>
       <c r="C13" s="719" t="str">
         <f>IF('Entries October 2026'!J10&lt;='Entries October 2026'!J9,"0",IF('Entries October 2026'!J10&gt;='Entries October 2026'!J9,'Entries October 2026'!J10-'Entries October 2026'!J9,(999999-'Entries October 2026'!J9)+'Entries October 2026'!J10+1))</f>
@@ -30640,12 +30851,14 @@
       </c>
       <c r="D13" s="720">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E13" s="877"/>
-      <c r="F13" s="721" t="str">
+        <v>4062</v>
+      </c>
+      <c r="E13" s="879">
+        <v>694.6</v>
+      </c>
+      <c r="F13" s="721">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.14602867594500274</v>
       </c>
       <c r="G13" s="737">
         <f>IF('Entries October 2026'!K10&lt;'Entries October 2026'!K9,"0",IF('Entries October 2026'!K10&gt;='Entries October 2026'!K9,'Entries October 2026'!K10-'Entries October 2026'!K9,(999999-'Entries October 2026'!K9)+'Entries October 2026'!K10+1))</f>
@@ -30653,11 +30866,11 @@
       </c>
       <c r="H13" s="720">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4756.6000000000004</v>
       </c>
       <c r="I13" s="737">
         <f>'Water '!Z10*10</f>
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="J13" s="720" t="str">
         <f>IF('Entries October 2026'!B10-'Entries October 2026'!B9&lt;1,"0",'Entries October 2026'!B10-'Entries October 2026'!B9)</f>
@@ -30707,7 +30920,7 @@
       <c r="A14" s="775">
         <v>5</v>
       </c>
-      <c r="B14" s="775">
+      <c r="B14" s="775" t="str">
         <f>IF('Entries October 2026'!I11&lt;'Entries October 2026'!I10,"0",(IF('Entries October 2026'!I11&gt;='Entries October 2026'!I10,'Entries October 2026'!I11-'Entries October 2026'!I10,(999999-'Entries October 2026'!I10)+'Entries October 2026'!I11+1)))</f>
         <v>0</v>
       </c>
@@ -30724,7 +30937,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G14" s="778">
+      <c r="G14" s="778" t="str">
         <f>IF('Entries October 2026'!K11&lt;'Entries October 2026'!K10,"0",IF('Entries October 2026'!K11&gt;='Entries October 2026'!K10,'Entries October 2026'!K11-'Entries October 2026'!K10,(999999-'Entries October 2026'!K10)+'Entries October 2026'!K11+1))</f>
         <v>0</v>
       </c>
@@ -32863,15 +33076,15 @@
       <c r="C43" s="19"/>
       <c r="D43" s="20">
         <f>SUM(D10:D40)</f>
-        <v>7369</v>
+        <v>22292</v>
       </c>
       <c r="E43" s="741">
         <f>SUM(E10:E40)</f>
-        <v>1057.5</v>
+        <v>4124.7000000000007</v>
       </c>
       <c r="F43" s="754">
         <f>IF((E43+D43)=0,"0",E43/(D43+E43))</f>
-        <v>0.12549694416424376</v>
+        <v>0.15613986606956964</v>
       </c>
       <c r="G43" s="20">
         <f t="shared" ref="G43:P43" si="7">SUM(G10:G40)</f>
@@ -32879,11 +33092,11 @@
       </c>
       <c r="H43" s="20">
         <f t="shared" si="7"/>
-        <v>8426.5</v>
+        <v>26416.699999999997</v>
       </c>
       <c r="I43" s="20">
         <f t="shared" si="7"/>
-        <v>2350</v>
+        <v>7380</v>
       </c>
       <c r="J43" s="20">
         <f t="shared" si="7"/>
@@ -32891,7 +33104,7 @@
       </c>
       <c r="K43" s="20">
         <f t="shared" si="7"/>
-        <v>1600</v>
+        <v>2742</v>
       </c>
       <c r="L43" s="20">
         <f t="shared" si="7"/>
@@ -32911,7 +33124,7 @@
       </c>
       <c r="P43" s="403">
         <f t="shared" si="7"/>
-        <v>367.56479999999999</v>
+        <v>651.10079999999994</v>
       </c>
       <c r="Q43" s="408" t="s">
         <v>13</v>
@@ -32939,7 +33152,7 @@
       </c>
       <c r="E44" s="728">
         <f>D43+E43</f>
-        <v>8426.5</v>
+        <v>26416.7</v>
       </c>
       <c r="F44" s="708"/>
       <c r="G44" s="7"/>
@@ -32954,19 +33167,19 @@
       <c r="P44" s="401"/>
       <c r="Q44" s="397">
         <f>IF(P43=0,0,H43/P43)</f>
-        <v>22.925209378047082</v>
+        <v>40.572366060677545</v>
       </c>
       <c r="R44" s="398">
         <f>IF(Q44=0,0,I43/P43)</f>
-        <v>6.3934304917119373</v>
+        <v>11.33465048729782</v>
       </c>
       <c r="S44" s="398">
         <f>IF(R44=0,0,J43/P43)</f>
-        <v>2.6117843710823236</v>
+        <v>1.4744260796484969</v>
       </c>
       <c r="T44" s="399">
         <f>IF(S44=0,0,K43/P43)</f>
-        <v>4.3529739518038726</v>
+        <v>4.2113294899960199</v>
       </c>
     </row>
     <row r="45" spans="1:32" ht="15" x14ac:dyDescent="0.2">
@@ -32999,12 +33212,12 @@
       <c r="T46" s="2"/>
     </row>
     <row r="47" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="D47" s="926"/>
-      <c r="E47" s="926"/>
-      <c r="F47" s="926"/>
-      <c r="G47" s="926"/>
-      <c r="H47" s="926"/>
-      <c r="I47" s="926"/>
+      <c r="D47" s="927"/>
+      <c r="E47" s="927"/>
+      <c r="F47" s="927"/>
+      <c r="G47" s="927"/>
+      <c r="H47" s="927"/>
+      <c r="I47" s="927"/>
       <c r="AF47" t="s">
         <v>55</v>
       </c>
@@ -33109,16 +33322,16 @@
       <c r="B2" s="8"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="942" t="s">
+      <c r="A3" s="943" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="944" t="s">
+      <c r="B3" s="945" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="943"/>
-      <c r="B4" s="945"/>
+      <c r="A4" s="944"/>
+      <c r="B4" s="946"/>
     </row>
     <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="36">
@@ -33482,32 +33695,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="954" t="s">
-        <v>305</v>
-      </c>
-      <c r="B1" s="955"/>
-      <c r="C1" s="955"/>
-      <c r="D1" s="955"/>
-      <c r="E1" s="955"/>
-      <c r="F1" s="955"/>
-      <c r="G1" s="955"/>
-      <c r="H1" s="955"/>
-      <c r="I1" s="955"/>
-      <c r="J1" s="955"/>
-      <c r="K1" s="955"/>
-      <c r="L1" s="955"/>
-      <c r="M1" s="955"/>
+      <c r="A1" s="955" t="s">
+        <v>304</v>
+      </c>
+      <c r="B1" s="956"/>
+      <c r="C1" s="956"/>
+      <c r="D1" s="956"/>
+      <c r="E1" s="956"/>
+      <c r="F1" s="956"/>
+      <c r="G1" s="956"/>
+      <c r="H1" s="956"/>
+      <c r="I1" s="956"/>
+      <c r="J1" s="956"/>
+      <c r="K1" s="956"/>
+      <c r="L1" s="956"/>
+      <c r="M1" s="956"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
       <c r="F2" s="9"/>
-      <c r="M2" s="946" t="s">
+      <c r="M2" s="947" t="s">
+        <v>296</v>
+      </c>
+      <c r="N2" s="947" t="s">
         <v>297</v>
-      </c>
-      <c r="N2" s="946" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -33515,11 +33728,11 @@
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="9"/>
-      <c r="M3" s="947"/>
-      <c r="N3" s="947"/>
+      <c r="M3" s="948"/>
+      <c r="N3" s="948"/>
     </row>
     <row r="4" spans="1:17" s="339" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="960" t="s">
+      <c r="A4" s="961" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="851" t="s">
@@ -33544,7 +33757,7 @@
         <v>39</v>
       </c>
       <c r="I4" s="852" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J4" s="852" t="s">
         <v>38</v>
@@ -33552,22 +33765,22 @@
       <c r="K4" s="852" t="s">
         <v>40</v>
       </c>
-      <c r="L4" s="956" t="s">
+      <c r="L4" s="957" t="s">
         <v>243</v>
       </c>
-      <c r="M4" s="958" t="s">
+      <c r="M4" s="959" t="s">
         <v>246</v>
       </c>
-      <c r="N4" s="948" t="s">
+      <c r="N4" s="949" t="s">
         <v>246</v>
       </c>
-      <c r="O4" s="951" t="s">
-        <v>299</v>
+      <c r="O4" s="952" t="s">
+        <v>298</v>
       </c>
       <c r="P4" s="350"/>
     </row>
     <row r="5" spans="1:17" s="339" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="961"/>
+      <c r="A5" s="962"/>
       <c r="B5" s="868" t="s">
         <v>41</v>
       </c>
@@ -33598,10 +33811,10 @@
       <c r="K5" s="869" t="s">
         <v>44</v>
       </c>
-      <c r="L5" s="957"/>
-      <c r="M5" s="959"/>
-      <c r="N5" s="949"/>
-      <c r="O5" s="952"/>
+      <c r="L5" s="958"/>
+      <c r="M5" s="960"/>
+      <c r="N5" s="950"/>
+      <c r="O5" s="953"/>
       <c r="P5" s="350"/>
     </row>
     <row r="6" spans="1:17" s="73" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -33618,8 +33831,8 @@
       <c r="K6" s="840"/>
       <c r="L6" s="873"/>
       <c r="M6" s="837"/>
-      <c r="N6" s="950"/>
-      <c r="O6" s="953"/>
+      <c r="N6" s="951"/>
+      <c r="O6" s="954"/>
       <c r="P6" s="350"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
@@ -33686,13 +33899,13 @@
         <f>IF('Entries October 2026'!B8-'Entries October 2026'!B7&lt;1,"0",'Entries October 2026'!B8-'Entries October 2026'!B7)</f>
         <v>0</v>
       </c>
-      <c r="C8" s="739" t="str">
+      <c r="C8" s="739">
         <f>IF('Entries October 2026'!F8-'Entries October 2026'!F7&lt;1,"0",'Entries October 2026'!F8-'Entries October 2026'!F7)</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="843" t="str">
+        <v>16.600000000000364</v>
+      </c>
+      <c r="D8" s="843">
         <f>IF('Entries October 2026'!C8-'Entries October 2026'!C7&lt;1,"0",'Entries October 2026'!C8-'Entries October 2026'!C7)</f>
-        <v>0</v>
+        <v>2235.1000000000931</v>
       </c>
       <c r="E8" s="847" t="str">
         <f t="shared" si="0"/>
@@ -33704,7 +33917,7 @@
       </c>
       <c r="G8" s="841"/>
       <c r="H8" s="739"/>
-      <c r="I8" s="740" t="str">
+      <c r="I8" s="740">
         <f t="shared" ref="I8:I37" si="4">IF(C8=0,"0", B8/(C8))</f>
         <v>0</v>
       </c>
@@ -33716,20 +33929,20 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L8" s="835" t="str">
-        <v>0</v>
-      </c>
-      <c r="M8" s="833" t="str">
+      <c r="L8" s="835">
+        <v>283.536</v>
+      </c>
+      <c r="M8" s="833">
         <f t="shared" ref="M8:M37" si="5">IF(L8=0,"0",(K8/L8))</f>
         <v>0</v>
       </c>
-      <c r="N8" s="833" t="str">
+      <c r="N8" s="833">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.8829496078102714</v>
       </c>
       <c r="O8" s="834">
         <f t="shared" ref="O8:O37" si="6">B8-D8</f>
-        <v>0</v>
+        <v>-2235.1000000000931</v>
       </c>
       <c r="P8" s="333"/>
     </row>
@@ -33741,13 +33954,13 @@
         <f>IF('Entries October 2026'!B9-'Entries October 2026'!B8&lt;1,"0",'Entries October 2026'!B9-'Entries October 2026'!B8)</f>
         <v>0</v>
       </c>
-      <c r="C9" s="739" t="str">
+      <c r="C9" s="739">
         <f>IF('Entries October 2026'!F9-'Entries October 2026'!F8&lt;1,"0",'Entries October 2026'!F9-'Entries October 2026'!F8)</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="843" t="str">
+        <v>1.6000000000003638</v>
+      </c>
+      <c r="D9" s="843">
         <f>IF('Entries October 2026'!C9-'Entries October 2026'!C8&lt;1,"0",'Entries October 2026'!C9-'Entries October 2026'!C8)</f>
-        <v>0</v>
+        <v>238.30000000004657</v>
       </c>
       <c r="E9" s="847" t="str">
         <f t="shared" si="0"/>
@@ -33759,7 +33972,7 @@
       </c>
       <c r="G9" s="841"/>
       <c r="H9" s="739"/>
-      <c r="I9" s="740" t="str">
+      <c r="I9" s="740">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -33784,7 +33997,7 @@
       </c>
       <c r="O9" s="834">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-238.30000000004657</v>
       </c>
       <c r="P9" s="333"/>
     </row>
@@ -33796,13 +34009,13 @@
         <f>IF('Entries October 2026'!B10-'Entries October 2026'!B9&lt;1,"0",'Entries October 2026'!B10-'Entries October 2026'!B9)</f>
         <v>0</v>
       </c>
-      <c r="C10" s="739" t="str">
+      <c r="C10" s="739">
         <f>IF('Entries October 2026'!F10-'Entries October 2026'!F9&lt;1,"0",'Entries October 2026'!F10-'Entries October 2026'!F9)</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="843" t="str">
+        <v>1.8999999999996362</v>
+      </c>
+      <c r="D10" s="843">
         <f>IF('Entries October 2026'!C10-'Entries October 2026'!C9&lt;1,"0",'Entries October 2026'!C10-'Entries October 2026'!C9)</f>
-        <v>0</v>
+        <v>334.89999999990687</v>
       </c>
       <c r="E10" s="847" t="str">
         <f t="shared" si="0"/>
@@ -33814,7 +34027,7 @@
       </c>
       <c r="G10" s="841"/>
       <c r="H10" s="739"/>
-      <c r="I10" s="740" t="str">
+      <c r="I10" s="740">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -33839,7 +34052,7 @@
       </c>
       <c r="O10" s="834">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-334.89999999990687</v>
       </c>
       <c r="P10" s="333"/>
     </row>
@@ -35337,11 +35550,11 @@
       </c>
       <c r="C38" s="388">
         <f>SUM(C7:C37)</f>
-        <v>20.5</v>
+        <v>40.600000000000364</v>
       </c>
       <c r="D38" s="844">
         <f t="shared" si="7"/>
-        <v>3317.1999999999534</v>
+        <v>6125.5</v>
       </c>
       <c r="E38" s="849"/>
       <c r="F38" s="850">
@@ -35358,7 +35571,7 @@
       </c>
       <c r="I38" s="801">
         <f>B38/C38</f>
-        <v>46.829268292682926</v>
+        <v>23.645320197044121</v>
       </c>
       <c r="J38" s="355"/>
       <c r="K38" s="356">
@@ -35367,15 +35580,15 @@
       </c>
       <c r="L38" s="832">
         <f>SUM(L7:L37)</f>
-        <v>367.56479999999999</v>
+        <v>651.10079999999994</v>
       </c>
       <c r="M38" s="838">
         <f>IF(L38=0,"0",(K38/L38))</f>
-        <v>2.6117843710823236</v>
+        <v>1.4744260796484969</v>
       </c>
       <c r="N38" s="838">
         <f>IF(L38=0,"0",(D38/L38))</f>
-        <v>9.0248032455772513</v>
+        <v>9.4079134905071538</v>
       </c>
       <c r="O38" s="839"/>
     </row>
@@ -35389,7 +35602,7 @@
       </c>
       <c r="C39" s="806">
         <f>AVERAGE(C7:C37)</f>
-        <v>20.5</v>
+        <v>10.150000000000091</v>
       </c>
       <c r="D39" s="30"/>
       <c r="E39" s="30"/>
@@ -36073,120 +36286,120 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="954"/>
-      <c r="B1" s="955"/>
-      <c r="C1" s="955"/>
-      <c r="D1" s="955"/>
-      <c r="E1" s="955"/>
-      <c r="F1" s="955"/>
-      <c r="G1" s="955"/>
-      <c r="H1" s="955"/>
-      <c r="I1" s="955"/>
-      <c r="J1" s="955"/>
-      <c r="K1" s="955"/>
-      <c r="L1" s="955"/>
-      <c r="M1" s="955"/>
-      <c r="N1" s="955"/>
-      <c r="O1" s="955"/>
-      <c r="P1" s="955"/>
-      <c r="Q1" s="955"/>
-      <c r="R1" s="955"/>
-      <c r="S1" s="955"/>
-      <c r="T1" s="955"/>
-      <c r="U1" s="955"/>
-      <c r="V1" s="955"/>
-      <c r="W1" s="955"/>
-      <c r="X1" s="955"/>
-      <c r="Y1" s="955"/>
-      <c r="Z1" s="955"/>
-      <c r="AA1" s="955"/>
+      <c r="A1" s="955"/>
+      <c r="B1" s="956"/>
+      <c r="C1" s="956"/>
+      <c r="D1" s="956"/>
+      <c r="E1" s="956"/>
+      <c r="F1" s="956"/>
+      <c r="G1" s="956"/>
+      <c r="H1" s="956"/>
+      <c r="I1" s="956"/>
+      <c r="J1" s="956"/>
+      <c r="K1" s="956"/>
+      <c r="L1" s="956"/>
+      <c r="M1" s="956"/>
+      <c r="N1" s="956"/>
+      <c r="O1" s="956"/>
+      <c r="P1" s="956"/>
+      <c r="Q1" s="956"/>
+      <c r="R1" s="956"/>
+      <c r="S1" s="956"/>
+      <c r="T1" s="956"/>
+      <c r="U1" s="956"/>
+      <c r="V1" s="956"/>
+      <c r="W1" s="956"/>
+      <c r="X1" s="956"/>
+      <c r="Y1" s="956"/>
+      <c r="Z1" s="956"/>
+      <c r="AA1" s="956"/>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C2" s="17"/>
     </row>
     <row r="3" spans="1:31" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="966" t="s">
+      <c r="B4" s="967" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="964" t="s">
+      <c r="C4" s="965" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="962" t="s">
+      <c r="D4" s="963" t="s">
         <v>106</v>
       </c>
-      <c r="E4" s="964" t="s">
+      <c r="E4" s="965" t="s">
         <v>107</v>
       </c>
-      <c r="F4" s="962" t="s">
+      <c r="F4" s="963" t="s">
         <v>239</v>
       </c>
-      <c r="G4" s="962" t="s">
+      <c r="G4" s="963" t="s">
         <v>108</v>
       </c>
-      <c r="H4" s="962" t="s">
+      <c r="H4" s="963" t="s">
         <v>161</v>
       </c>
-      <c r="I4" s="964" t="s">
+      <c r="I4" s="965" t="s">
         <v>207</v>
       </c>
-      <c r="J4" s="964" t="s">
+      <c r="J4" s="965" t="s">
         <v>109</v>
       </c>
-      <c r="K4" s="964" t="s">
+      <c r="K4" s="965" t="s">
         <v>174</v>
       </c>
-      <c r="L4" s="964" t="s">
+      <c r="L4" s="965" t="s">
         <v>173</v>
       </c>
-      <c r="M4" s="964" t="s">
+      <c r="M4" s="965" t="s">
         <v>103</v>
       </c>
       <c r="N4" s="48"/>
       <c r="O4" s="48"/>
       <c r="P4" s="48"/>
       <c r="Q4" s="48"/>
-      <c r="R4" s="962" t="s">
+      <c r="R4" s="963" t="s">
         <v>110</v>
       </c>
-      <c r="S4" s="962" t="s">
+      <c r="S4" s="963" t="s">
         <v>240</v>
       </c>
       <c r="T4" s="48"/>
-      <c r="U4" s="964" t="s">
+      <c r="U4" s="965" t="s">
         <v>153</v>
       </c>
       <c r="V4" s="48"/>
       <c r="W4" s="48"/>
-      <c r="X4" s="964" t="s">
+      <c r="X4" s="965" t="s">
         <v>175</v>
       </c>
-      <c r="Y4" s="964" t="s">
+      <c r="Y4" s="965" t="s">
         <v>176</v>
       </c>
-      <c r="Z4" s="971" t="s">
+      <c r="Z4" s="972" t="s">
         <v>247</v>
       </c>
-      <c r="AA4" s="973" t="s">
+      <c r="AA4" s="974" t="s">
         <v>243</v>
       </c>
-      <c r="AB4" s="969" t="s">
+      <c r="AB4" s="970" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:31" s="300" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="967"/>
-      <c r="C5" s="965"/>
-      <c r="D5" s="963"/>
-      <c r="E5" s="968"/>
-      <c r="F5" s="963"/>
-      <c r="G5" s="963"/>
-      <c r="H5" s="963"/>
-      <c r="I5" s="968"/>
-      <c r="J5" s="968"/>
-      <c r="K5" s="968"/>
-      <c r="L5" s="968"/>
-      <c r="M5" s="968"/>
+      <c r="B5" s="968"/>
+      <c r="C5" s="966"/>
+      <c r="D5" s="964"/>
+      <c r="E5" s="969"/>
+      <c r="F5" s="964"/>
+      <c r="G5" s="964"/>
+      <c r="H5" s="964"/>
+      <c r="I5" s="969"/>
+      <c r="J5" s="969"/>
+      <c r="K5" s="969"/>
+      <c r="L5" s="969"/>
+      <c r="M5" s="969"/>
       <c r="N5" s="50" t="s">
         <v>111</v>
       </c>
@@ -36199,23 +36412,23 @@
       <c r="Q5" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="R5" s="963"/>
-      <c r="S5" s="963"/>
+      <c r="R5" s="964"/>
+      <c r="S5" s="964"/>
       <c r="T5" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="U5" s="975"/>
+      <c r="U5" s="976"/>
       <c r="V5" s="80" t="s">
         <v>156</v>
       </c>
       <c r="W5" s="80" t="s">
         <v>157</v>
       </c>
-      <c r="X5" s="968"/>
-      <c r="Y5" s="968"/>
-      <c r="Z5" s="972"/>
-      <c r="AA5" s="974"/>
-      <c r="AB5" s="970"/>
+      <c r="X5" s="969"/>
+      <c r="Y5" s="969"/>
+      <c r="Z5" s="973"/>
+      <c r="AA5" s="975"/>
+      <c r="AB5" s="971"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="21" t="s">
@@ -36365,33 +36578,33 @@
         <f>IF('Entries October 2026'!W8-'Entries October 2026'!W7&lt;1,"0",'Entries October 2026'!W8-'Entries October 2026'!W7)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="31" t="str">
+      <c r="D8" s="31">
         <f>IF('Entries October 2026'!O8-'Entries October 2026'!O7&lt;1,"0",'Entries October 2026'!O8-'Entries October 2026'!O7)</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="31" t="str">
+        <v>132</v>
+      </c>
+      <c r="E8" s="31">
         <f>IF('Entries October 2026'!P8-'Entries October 2026'!P7&lt;1,"0",'Entries October 2026'!P8-'Entries October 2026'!P7)</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="31" t="str">
+        <v>180</v>
+      </c>
+      <c r="F8" s="31">
         <f>IF('Entries October 2026'!V8-'Entries October 2026'!V7&lt;1,"0",'Entries October 2026'!V8-'Entries October 2026'!V7)</f>
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="G8" s="31">
         <f t="shared" ref="G8:G37" si="0">(D8+E8)-F8</f>
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="H8" s="31">
         <f>IF('Entries October 2026'!Q8-'Entries October 2026'!Q7&lt;1,0,'Entries October 2026'!Q8-'Entries October 2026'!Q7)</f>
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="I8" s="31">
         <f>IF('Entries October 2026'!AG8-'Entries October 2026'!AG7&lt;1,0,'Entries October 2026'!AG8-'Entries October 2026'!AG7)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="31" t="str">
+      <c r="J8" s="31">
         <f>IF('Entries October 2026'!S8-'Entries October 2026'!S7&lt;1,"0",'Entries October 2026'!S8-'Entries October 2026'!S7)</f>
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="K8" s="31" t="str">
         <f>IF('Entries October 2026'!R8-'Entries October 2026'!R7&lt;1,"0",'Entries October 2026'!R8-'Entries October 2026'!R7)</f>
@@ -36401,25 +36614,25 @@
         <f>IF('Entries October 2026'!T8-'Entries October 2026'!T7&lt;1,"0",'Entries October 2026'!T8-'Entries October 2026'!T7)</f>
         <v>0</v>
       </c>
-      <c r="M8" s="31" t="str">
+      <c r="M8" s="31">
         <f>IF('Entries October 2026'!U8-'Entries October 2026'!U7&lt;1,"0",'Entries October 2026'!U8-'Entries October 2026'!U7)</f>
-        <v>0</v>
-      </c>
-      <c r="N8" s="31" t="str">
+        <v>3</v>
+      </c>
+      <c r="N8" s="31">
         <f>IF('Entries October 2026'!X8-'Entries October 2026'!X7&lt;1,"0",'Entries October 2026'!X8-'Entries October 2026'!X7)</f>
-        <v>0</v>
-      </c>
-      <c r="O8" s="31" t="str">
+        <v>44</v>
+      </c>
+      <c r="O8" s="31">
         <f>IF('Entries October 2026'!Y8-'Entries October 2026'!Y7&lt;1,"0",'Entries October 2026'!Y8-'Entries October 2026'!Y7)</f>
-        <v>0</v>
-      </c>
-      <c r="P8" s="31" t="str">
+        <v>81</v>
+      </c>
+      <c r="P8" s="31">
         <f>IF('Entries October 2026'!AC8-'Entries October 2026'!AC7&lt;1,"0",'Entries October 2026'!AC8-'Entries October 2026'!AC7)</f>
-        <v>0</v>
-      </c>
-      <c r="Q8" s="31" t="str">
+        <v>15</v>
+      </c>
+      <c r="Q8" s="31">
         <f>IF('Entries October 2026'!Z8-'Entries October 2026'!Z7&lt;1,"0",'Entries October 2026'!Z8-'Entries October 2026'!Z7)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R8" s="31" t="str">
         <f>IF(('Entries October 2026'!AA8-'Entries October 2026'!AA7)+('Entries October 2026'!AB8-'Entries October 2026'!AB7)&lt;1,"0",('Entries October 2026'!AA8-'Entries October 2026'!AA7)+('Entries October 2026'!AB8-'Entries October 2026'!AB7))</f>
@@ -36427,15 +36640,15 @@
       </c>
       <c r="S8" s="52">
         <f>(R8+G8)*10</f>
-        <v>0</v>
+        <v>1210</v>
       </c>
       <c r="T8" s="52">
         <f t="shared" ref="T8:T36" si="1">O8+N8+M8+L8</f>
-        <v>0</v>
-      </c>
-      <c r="U8" s="31" t="str">
+        <v>128</v>
+      </c>
+      <c r="U8" s="31">
         <f>IF('Entries October 2026'!AC8-'Entries October 2026'!AC7&lt;1,"0",'Entries October 2026'!AC8-'Entries October 2026'!AC7)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V8" s="31" t="str">
         <f>IF('Entries October 2026'!AD8-'Entries October 2026'!AD7&lt;1,"0",'Entries October 2026'!AD8-'Entries October 2026'!AD7)</f>
@@ -36455,14 +36668,14 @@
       </c>
       <c r="Z8" s="329">
         <f t="shared" ref="Z8:Z37" si="2">C8+D8+E8</f>
-        <v>0</v>
-      </c>
-      <c r="AA8" s="330" t="str">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="331" t="str">
+        <v>312</v>
+      </c>
+      <c r="AA8" s="330">
+        <v>283.536</v>
+      </c>
+      <c r="AB8" s="331">
         <f t="shared" ref="AB8:AB36" si="3">IF(AA8=0,"0",(Z8*10/AA8))</f>
-        <v>0</v>
+        <v>11.003893685457932</v>
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.2">
@@ -36477,21 +36690,21 @@
         <f>IF('Entries October 2026'!O9-'Entries October 2026'!O8&lt;1,"0",'Entries October 2026'!O9-'Entries October 2026'!O8)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="31" t="str">
+      <c r="E9" s="31">
         <f>IF('Entries October 2026'!P9-'Entries October 2026'!P8&lt;1,"0",'Entries October 2026'!P9-'Entries October 2026'!P8)</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="31" t="str">
+        <v>127</v>
+      </c>
+      <c r="F9" s="31">
         <f>IF('Entries October 2026'!V9-'Entries October 2026'!V8&lt;1,"0",'Entries October 2026'!V9-'Entries October 2026'!V8)</f>
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="G9" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="H9" s="31">
         <f>IF('Entries October 2026'!Q9-'Entries October 2026'!Q8&lt;1,0,'Entries October 2026'!Q9-'Entries October 2026'!Q8)</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I9" s="31">
         <f>IF('Entries October 2026'!AG9-'Entries October 2026'!AG8&lt;1,0,'Entries October 2026'!AG9-'Entries October 2026'!AG8)</f>
@@ -36525,9 +36738,9 @@
         <f>IF('Entries October 2026'!AC9-'Entries October 2026'!AC8&lt;1,"0",'Entries October 2026'!AC9-'Entries October 2026'!AC8)</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="31" t="str">
+      <c r="Q9" s="31">
         <f>IF('Entries October 2026'!Z9-'Entries October 2026'!Z8&lt;1,"0",'Entries October 2026'!Z9-'Entries October 2026'!Z8)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R9" s="31" t="str">
         <f>IF(('Entries October 2026'!AA9-'Entries October 2026'!AA8)+('Entries October 2026'!AB9-'Entries October 2026'!AB8)&lt;1,"0",('Entries October 2026'!AA9-'Entries October 2026'!AA8)+('Entries October 2026'!AB9-'Entries October 2026'!AB8))</f>
@@ -36535,7 +36748,7 @@
       </c>
       <c r="S9" s="52">
         <f t="shared" ref="S9:S37" si="4">(R9+G9)*10</f>
-        <v>0</v>
+        <v>-70</v>
       </c>
       <c r="T9" s="52">
         <f t="shared" si="1"/>
@@ -36563,7 +36776,7 @@
       </c>
       <c r="Z9" s="329">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="AA9" s="330" t="str">
         <v>0</v>
@@ -36581,9 +36794,9 @@
         <f>IF('Entries October 2026'!W10-'Entries October 2026'!W9&lt;1,"0",'Entries October 2026'!W10-'Entries October 2026'!W9)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="693" t="str">
+      <c r="D10" s="693">
         <f>IF('Entries October 2026'!O10-'Entries October 2026'!O9&lt;1,"0",'Entries October 2026'!O10-'Entries October 2026'!O9)</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="E10" s="693" t="str">
         <f>IF('Entries October 2026'!P10-'Entries October 2026'!P9&lt;1,"0",'Entries October 2026'!P10-'Entries October 2026'!P9)</f>
@@ -36595,11 +36808,11 @@
       </c>
       <c r="G10" s="693">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H10" s="693">
         <f>IF('Entries October 2026'!Q10-'Entries October 2026'!Q9&lt;1,0,'Entries October 2026'!Q10-'Entries October 2026'!Q9)</f>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="I10" s="693">
         <f>IF('Entries October 2026'!AG10-'Entries October 2026'!AG9&lt;1,0,'Entries October 2026'!AG10-'Entries October 2026'!AG9)</f>
@@ -36633,9 +36846,9 @@
         <f>IF('Entries October 2026'!AC10-'Entries October 2026'!AC9&lt;1,"0",'Entries October 2026'!AC10-'Entries October 2026'!AC9)</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="693" t="str">
+      <c r="Q10" s="693">
         <f>IF('Entries October 2026'!Z10-'Entries October 2026'!Z9&lt;1,"0",'Entries October 2026'!Z10-'Entries October 2026'!Z9)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R10" s="693" t="str">
         <f>IF(('Entries October 2026'!AA10-'Entries October 2026'!AA9)+('Entries October 2026'!AB10-'Entries October 2026'!AB9)&lt;1,"0",('Entries October 2026'!AA10-'Entries October 2026'!AA9)+('Entries October 2026'!AB10-'Entries October 2026'!AB9))</f>
@@ -36643,7 +36856,7 @@
       </c>
       <c r="S10" s="692">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="T10" s="692">
         <f t="shared" si="1"/>
@@ -36671,7 +36884,7 @@
       </c>
       <c r="Z10" s="329">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AA10" s="330" t="str">
         <v>0</v>
@@ -39617,28 +39830,28 @@
       </c>
       <c r="D38" s="303">
         <f>SUM(D7:D37)</f>
-        <v>55</v>
+        <v>251</v>
       </c>
       <c r="E38" s="303">
         <f>SUM(E7:E37)</f>
-        <v>180</v>
+        <v>487</v>
       </c>
       <c r="F38" s="303">
         <f>SUM(F7:F37)</f>
-        <v>248</v>
+        <v>573</v>
       </c>
       <c r="G38" s="304">
         <f>SUM(G7:G37)</f>
-        <v>-13</v>
+        <v>165</v>
       </c>
       <c r="H38" s="303">
         <f t="shared" si="5"/>
-        <v>249</v>
+        <v>531</v>
       </c>
       <c r="I38" s="303"/>
       <c r="J38" s="303">
         <f t="shared" si="5"/>
-        <v>157</v>
+        <v>283</v>
       </c>
       <c r="K38" s="303"/>
       <c r="L38" s="303">
@@ -39647,23 +39860,23 @@
       </c>
       <c r="M38" s="303">
         <f>SUM(M7:M37)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N38" s="303">
         <f t="shared" si="5"/>
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="O38" s="303">
         <f t="shared" si="5"/>
-        <v>99</v>
+        <v>180</v>
       </c>
       <c r="P38" s="303">
         <f>SUM(P7:P37)</f>
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="Q38" s="303">
         <f>SUM(Q7:Q37)</f>
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="R38" s="303">
         <f>SUM(R7:R34)</f>
@@ -39671,15 +39884,15 @@
       </c>
       <c r="S38" s="304">
         <f>SUM(S7:S37)</f>
-        <v>-130</v>
+        <v>1650</v>
       </c>
       <c r="T38" s="304">
         <f>SUM(T7:T37)</f>
-        <v>160</v>
+        <v>288</v>
       </c>
       <c r="U38" s="303">
         <f>SUM(U7:U37)</f>
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="V38" s="303">
         <f>SUM(V7:V37)</f>
@@ -39690,22 +39903,22 @@
       <c r="Y38" s="303"/>
       <c r="Z38" s="332">
         <f>SUM(Z7:Z37)</f>
-        <v>235</v>
+        <v>738</v>
       </c>
       <c r="AA38" s="332">
         <f>SUM(AA7:AA37)</f>
-        <v>367.56479999999999</v>
+        <v>651.10079999999994</v>
       </c>
       <c r="AB38" s="331">
         <f>IF(AA38=0,"0",(Z38*10/AA38))</f>
-        <v>6.3934304917119373</v>
+        <v>11.33465048729782</v>
       </c>
       <c r="AC38" s="321">
         <v>10.199999999999999</v>
       </c>
       <c r="AD38" s="340">
         <f>AB38/AC38*100</f>
-        <v>62.680691095215082</v>
+        <v>111.12402438527276</v>
       </c>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.2">
@@ -39744,7 +39957,7 @@
       <c r="C40" s="15"/>
       <c r="D40" s="15">
         <f>D38*220</f>
-        <v>12100</v>
+        <v>55220</v>
       </c>
       <c r="E40" s="15"/>
       <c r="F40" s="15"/>
@@ -39836,7 +40049,7 @@
       <c r="C43" s="17"/>
       <c r="D43" s="17">
         <f>+D41*D40</f>
-        <v>191.30100000000002</v>
+        <v>873.02820000000008</v>
       </c>
       <c r="E43" s="17"/>
       <c r="F43" s="36"/>
@@ -39889,7 +40102,7 @@
     <row r="45" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D45" s="17">
         <f>SUM(D43:D44)</f>
-        <v>470.27100000000007</v>
+        <v>1151.9982</v>
       </c>
       <c r="E45" s="17"/>
       <c r="F45" s="36"/>
@@ -39911,7 +40124,7 @@
       </c>
       <c r="D47" s="23">
         <f>+D45*2/3</f>
-        <v>313.51400000000007</v>
+        <v>767.99879999999996</v>
       </c>
       <c r="E47" s="324"/>
       <c r="F47" s="36"/>
@@ -39934,7 +40147,7 @@
       <c r="C49" s="24"/>
       <c r="D49" s="28">
         <f>SUM(D47,D45)</f>
-        <v>783.78500000000008</v>
+        <v>1919.9969999999998</v>
       </c>
       <c r="E49" s="325"/>
       <c r="F49" s="36"/>
@@ -40357,15 +40570,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="976" t="s">
-        <v>304</v>
-      </c>
-      <c r="B1" s="977"/>
-      <c r="C1" s="977"/>
-      <c r="D1" s="978"/>
-      <c r="E1" s="977"/>
-      <c r="F1" s="977"/>
-      <c r="G1" s="979"/>
+      <c r="A1" s="977" t="s">
+        <v>303</v>
+      </c>
+      <c r="B1" s="978"/>
+      <c r="C1" s="978"/>
+      <c r="D1" s="979"/>
+      <c r="E1" s="978"/>
+      <c r="F1" s="978"/>
+      <c r="G1" s="980"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B2" s="9"/>
@@ -40378,7 +40591,7 @@
       <c r="D3" s="359"/>
     </row>
     <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="990" t="s">
+      <c r="A4" s="991" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="39" t="s">
@@ -40390,19 +40603,19 @@
       <c r="D4" s="361" t="s">
         <v>285</v>
       </c>
-      <c r="E4" s="980" t="s">
+      <c r="E4" s="981" t="s">
         <v>245</v>
       </c>
-      <c r="F4" s="983" t="s">
+      <c r="F4" s="984" t="s">
         <v>243</v>
       </c>
-      <c r="G4" s="986" t="s">
+      <c r="G4" s="987" t="s">
         <v>253</v>
       </c>
-      <c r="H4" s="989"/>
+      <c r="H4" s="990"/>
     </row>
     <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="991"/>
+      <c r="A5" s="992"/>
       <c r="B5" s="34" t="s">
         <v>48</v>
       </c>
@@ -40412,20 +40625,20 @@
       <c r="D5" s="361" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="981"/>
-      <c r="F5" s="984"/>
-      <c r="G5" s="987"/>
-      <c r="H5" s="989"/>
+      <c r="E5" s="982"/>
+      <c r="F5" s="985"/>
+      <c r="G5" s="988"/>
+      <c r="H5" s="990"/>
     </row>
     <row r="6" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="992"/>
+      <c r="A6" s="993"/>
       <c r="B6" s="40"/>
       <c r="C6" s="362"/>
       <c r="D6" s="361"/>
-      <c r="E6" s="982"/>
-      <c r="F6" s="985"/>
-      <c r="G6" s="988"/>
-      <c r="H6" s="989"/>
+      <c r="E6" s="983"/>
+      <c r="F6" s="986"/>
+      <c r="G6" s="989"/>
+      <c r="H6" s="990"/>
     </row>
     <row r="7" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A7" s="686">
@@ -40464,27 +40677,27 @@
       </c>
       <c r="B8" s="742">
         <f>'Utility Analysis October 2026'!D11</f>
-        <v>0</v>
-      </c>
-      <c r="C8" s="743" t="str">
+        <v>7089</v>
+      </c>
+      <c r="C8" s="743">
         <f>'Utility Analysis October 2026'!G11</f>
         <v>0</v>
       </c>
       <c r="D8" s="744">
         <f>'Utility Analysis October 2026'!E11</f>
-        <v>0</v>
+        <v>1571.3</v>
       </c>
       <c r="E8" s="745">
         <f t="shared" ref="E8:E36" si="0">B8+D8</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="746" t="str">
+        <v>8660.2999999999993</v>
+      </c>
+      <c r="F8" s="746">
         <f>'PROD.FIG. '!H6</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="336" t="str">
+        <v>283.536</v>
+      </c>
+      <c r="G8" s="336">
         <f t="shared" ref="G8:G36" si="1">IF(F8=0,"0",(E8/F8))</f>
-        <v>0</v>
+        <v>30.543916821849781</v>
       </c>
       <c r="I8" s="30"/>
       <c r="J8" s="30"/>
@@ -40495,7 +40708,7 @@
       </c>
       <c r="B9" s="742">
         <f>'Utility Analysis October 2026'!D12</f>
-        <v>0</v>
+        <v>3772</v>
       </c>
       <c r="C9" s="743">
         <f>'Utility Analysis October 2026'!G12</f>
@@ -40503,11 +40716,11 @@
       </c>
       <c r="D9" s="744">
         <f>'Utility Analysis October 2026'!E12</f>
-        <v>0</v>
+        <v>801.3</v>
       </c>
       <c r="E9" s="745">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4573.3</v>
       </c>
       <c r="F9" s="746" t="str">
         <f>'PROD.FIG. '!H7</f>
@@ -40525,7 +40738,7 @@
       </c>
       <c r="B10" s="742">
         <f>'Utility Analysis October 2026'!D13</f>
-        <v>0</v>
+        <v>4062</v>
       </c>
       <c r="C10" s="743">
         <f>'Utility Analysis October 2026'!G13</f>
@@ -40533,11 +40746,11 @@
       </c>
       <c r="D10" s="744">
         <f>'Utility Analysis October 2026'!E13</f>
-        <v>0</v>
+        <v>694.6</v>
       </c>
       <c r="E10" s="745">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4756.6000000000004</v>
       </c>
       <c r="F10" s="746" t="str">
         <f>'PROD.FIG. '!H8</f>
@@ -40557,7 +40770,7 @@
         <f>'Utility Analysis October 2026'!D14</f>
         <v>0</v>
       </c>
-      <c r="C11" s="766">
+      <c r="C11" s="766" t="str">
         <f>'Utility Analysis October 2026'!G14</f>
         <v>0</v>
       </c>
@@ -41362,7 +41575,7 @@
       </c>
       <c r="B38" s="308">
         <f>SUM(B7:B37)</f>
-        <v>7369</v>
+        <v>22292</v>
       </c>
       <c r="C38" s="308">
         <f>SUM(C7:C37)</f>
@@ -41370,26 +41583,26 @@
       </c>
       <c r="D38" s="308">
         <f>SUM(D7:D37)</f>
-        <v>1057.5</v>
+        <v>4124.7000000000007</v>
       </c>
       <c r="E38" s="337">
         <f>SUM(E7:E37)</f>
-        <v>8426.5</v>
+        <v>26416.699999999997</v>
       </c>
       <c r="F38" s="358">
         <f>SUM(F7:F37)</f>
-        <v>367.56479999999999</v>
+        <v>651.10079999999994</v>
       </c>
       <c r="G38" s="338">
         <f>IF(F38=0,"0",(E38/F38))</f>
-        <v>22.925209378047082</v>
+        <v>40.572366060677545</v>
       </c>
       <c r="H38" s="335">
         <v>22</v>
       </c>
       <c r="I38" s="340">
         <f>G38/H38*100</f>
-        <v>104.20549717294128</v>
+        <v>184.41984573035248</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
@@ -41466,16 +41679,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="993" t="s">
-        <v>303</v>
-      </c>
-      <c r="B1" s="955"/>
-      <c r="C1" s="955"/>
-      <c r="D1" s="955"/>
-      <c r="E1" s="955"/>
-      <c r="F1" s="955"/>
-      <c r="G1" s="955"/>
-      <c r="H1" s="955"/>
+      <c r="A1" s="994" t="s">
+        <v>302</v>
+      </c>
+      <c r="B1" s="956"/>
+      <c r="C1" s="956"/>
+      <c r="D1" s="956"/>
+      <c r="E1" s="956"/>
+      <c r="F1" s="956"/>
+      <c r="G1" s="956"/>
+      <c r="H1" s="956"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D2" s="12"/>
@@ -41547,8 +41760,8 @@
       <c r="E6" s="770"/>
       <c r="F6" s="688"/>
       <c r="G6" s="686"/>
-      <c r="H6" s="689" t="str">
-        <v>0</v>
+      <c r="H6" s="689">
+        <v>283.536</v>
       </c>
       <c r="I6" s="33"/>
       <c r="J6" s="297"/>
@@ -42088,7 +42301,7 @@
       </c>
       <c r="H36" s="736">
         <f>SUM(H5:H35)</f>
-        <v>367.56479999999999</v>
+        <v>651.10079999999994</v>
       </c>
       <c r="I36" s="298"/>
       <c r="J36" s="299"/>
@@ -42197,18 +42410,18 @@
     </row>
     <row r="3" spans="1:24" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="344" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="85"/>
       <c r="E3" s="85"/>
       <c r="F3" s="1"/>
-      <c r="I3" s="998" t="s">
+      <c r="I3" s="999" t="s">
         <v>267</v>
       </c>
-      <c r="J3" s="999"/>
-      <c r="K3" s="1000"/>
+      <c r="J3" s="1000"/>
+      <c r="K3" s="1001"/>
     </row>
     <row r="4" spans="1:24" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
@@ -42221,46 +42434,46 @@
         <v>250</v>
       </c>
       <c r="H4" s="347"/>
-      <c r="I4" s="1001" t="s">
+      <c r="I4" s="1002" t="s">
         <v>262</v>
       </c>
-      <c r="J4" s="1002"/>
-      <c r="K4" s="1003"/>
+      <c r="J4" s="1003"/>
+      <c r="K4" s="1004"/>
       <c r="M4" s="417"/>
       <c r="N4" s="417"/>
       <c r="O4" s="418"/>
       <c r="P4" s="418"/>
-      <c r="Q4" s="1013" t="s">
+      <c r="Q4" s="1014" t="s">
         <v>283</v>
       </c>
-      <c r="R4" s="1013"/>
-      <c r="S4" s="1013"/>
-      <c r="T4" s="1013"/>
+      <c r="R4" s="1014"/>
+      <c r="S4" s="1014"/>
+      <c r="T4" s="1014"/>
       <c r="U4" s="191"/>
       <c r="V4" s="417"/>
       <c r="W4" s="191"/>
       <c r="X4" s="191"/>
     </row>
     <row r="5" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="942" t="s">
+      <c r="A5" s="943" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="944" t="s">
+      <c r="B5" s="945" t="s">
         <v>251</v>
       </c>
-      <c r="C5" s="944" t="s">
+      <c r="C5" s="945" t="s">
         <v>282</v>
       </c>
-      <c r="D5" s="1020" t="s">
+      <c r="D5" s="1021" t="s">
         <v>279</v>
       </c>
-      <c r="E5" s="1020" t="s">
+      <c r="E5" s="1021" t="s">
         <v>280</v>
       </c>
-      <c r="F5" s="1018" t="s">
+      <c r="F5" s="1019" t="s">
         <v>243</v>
       </c>
-      <c r="G5" s="1015" t="s">
+      <c r="G5" s="1016" t="s">
         <v>249</v>
       </c>
       <c r="I5" s="419" t="s">
@@ -42272,43 +42485,43 @@
       <c r="K5" s="421" t="s">
         <v>265</v>
       </c>
-      <c r="M5" s="1004" t="s">
+      <c r="M5" s="1005" t="s">
         <v>266</v>
       </c>
-      <c r="N5" s="1005"/>
-      <c r="O5" s="1006"/>
+      <c r="N5" s="1006"/>
+      <c r="O5" s="1007"/>
       <c r="P5" s="422"/>
-      <c r="Q5" s="1007" t="s">
+      <c r="Q5" s="1008" t="s">
         <v>7</v>
       </c>
-      <c r="R5" s="1009" t="s">
+      <c r="R5" s="1010" t="s">
         <v>267</v>
       </c>
-      <c r="S5" s="1010"/>
+      <c r="S5" s="1011"/>
       <c r="T5" s="452" t="s">
         <v>268</v>
       </c>
       <c r="U5" s="423" t="s">
         <v>269</v>
       </c>
-      <c r="V5" s="1011" t="s">
+      <c r="V5" s="1012" t="s">
         <v>277</v>
       </c>
-      <c r="W5" s="994" t="s">
+      <c r="W5" s="995" t="s">
         <v>270</v>
       </c>
-      <c r="X5" s="996" t="s">
+      <c r="X5" s="997" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1014"/>
-      <c r="B6" s="1017"/>
-      <c r="C6" s="1017"/>
-      <c r="D6" s="1021"/>
-      <c r="E6" s="1021"/>
-      <c r="F6" s="1019"/>
-      <c r="G6" s="1016"/>
+      <c r="A6" s="1015"/>
+      <c r="B6" s="1018"/>
+      <c r="C6" s="1018"/>
+      <c r="D6" s="1022"/>
+      <c r="E6" s="1022"/>
+      <c r="F6" s="1020"/>
+      <c r="G6" s="1017"/>
       <c r="I6" s="424">
         <v>10</v>
       </c>
@@ -42327,7 +42540,7 @@
         <v>273</v>
       </c>
       <c r="P6" s="418"/>
-      <c r="Q6" s="1008"/>
+      <c r="Q6" s="1009"/>
       <c r="R6" s="448" t="s">
         <v>274</v>
       </c>
@@ -42340,9 +42553,9 @@
       <c r="U6" s="429" t="s">
         <v>275</v>
       </c>
-      <c r="V6" s="1012"/>
-      <c r="W6" s="995"/>
-      <c r="X6" s="997"/>
+      <c r="V6" s="1013"/>
+      <c r="W6" s="996"/>
+      <c r="X6" s="998"/>
     </row>
     <row r="7" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="715">
@@ -42432,27 +42645,27 @@
       <c r="A8" s="715">
         <v>2</v>
       </c>
-      <c r="B8" s="716" t="str">
+      <c r="B8" s="716">
         <f>IF('Entries October 2026'!N8-'Entries October 2026'!N7&lt;1,"0",'Entries October 2026'!N8-'Entries October 2026'!N7)</f>
-        <v>0</v>
-      </c>
-      <c r="C8" s="716" t="str">
+        <v>146.09999999999127</v>
+      </c>
+      <c r="C8" s="716">
         <f>IF('Entries October 2026'!L8-'Entries October 2026'!L7&lt;1,"0",'Entries October 2026'!L8-'Entries October 2026'!L7)</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="716" t="str">
+        <v>475.41000000000349</v>
+      </c>
+      <c r="D8" s="716">
         <f>IF('Entries October 2026'!M8-'Entries October 2026'!M7&lt;1,"0",'Entries October 2026'!M8-'Entries October 2026'!M7)</f>
-        <v>0</v>
+        <v>1141.6199999999953</v>
       </c>
       <c r="E8" s="716">
-        <v>0</v>
+        <v>1142</v>
       </c>
       <c r="F8" s="717">
-        <v>0</v>
-      </c>
-      <c r="G8" s="336" t="str">
+        <v>283.536</v>
+      </c>
+      <c r="G8" s="336">
         <f t="shared" ref="G8:G37" si="1">IF(F8=0,"0",(E8/F8))</f>
-        <v>0</v>
+        <v>4.0277072399977429</v>
       </c>
       <c r="I8" s="430">
         <v>30</v>
@@ -44629,27 +44842,27 @@
       </c>
       <c r="B38" s="713">
         <f>SUM(B7:B37)</f>
-        <v>194.34000000001106</v>
+        <v>340.44000000000233</v>
       </c>
       <c r="C38" s="713">
         <f>SUM(C7:C37)</f>
-        <v>564.13000000000466</v>
+        <v>1039.5400000000081</v>
       </c>
       <c r="D38" s="713">
         <f>SUM(D7:D37)</f>
-        <v>1579.4799999999814</v>
+        <v>2721.0999999999767</v>
       </c>
       <c r="E38" s="713">
         <f>SUM(E7:E37)</f>
-        <v>1600</v>
+        <v>2742</v>
       </c>
       <c r="F38" s="714">
         <f>SUM(F7:F37)</f>
-        <v>367.56479999999999</v>
+        <v>651.10079999999994</v>
       </c>
       <c r="G38" s="345">
         <f>IF(F38=0,"0",(E38/F38))</f>
-        <v>4.3529739518038726</v>
+        <v>4.2113294899960199</v>
       </c>
       <c r="H38" s="348">
         <v>5</v>
@@ -45127,7 +45340,7 @@
         <v>31</v>
       </c>
       <c r="AG6" s="293"/>
-      <c r="AH6" s="894" t="s">
+      <c r="AH6" s="895" t="s">
         <v>216</v>
       </c>
       <c r="AI6" s="291"/>
@@ -45232,7 +45445,7 @@
       <c r="AG7" s="212" t="s">
         <v>19</v>
       </c>
-      <c r="AH7" s="894"/>
+      <c r="AH7" s="895"/>
       <c r="AI7" s="292" t="s">
         <v>229</v>
       </c>
@@ -45246,7 +45459,7 @@
       <c r="B8" s="99"/>
       <c r="C8" s="99">
         <f>'Daily KPIs'!C8</f>
-        <v>0</v>
+        <v>4296</v>
       </c>
       <c r="D8" s="99">
         <f>'Daily KPIs'!D8</f>
@@ -45360,14 +45573,14 @@
       </c>
       <c r="AG8" s="213">
         <f>SUM($B8:AF8)</f>
-        <v>0</v>
+        <v>4296</v>
       </c>
       <c r="AH8" s="293">
         <v>96325</v>
       </c>
       <c r="AI8" s="294">
         <f>AG8-AH8</f>
-        <v>-96325</v>
+        <v>-92029</v>
       </c>
       <c r="AJ8" s="266"/>
       <c r="AK8" s="266"/>
@@ -45382,7 +45595,7 @@
       </c>
       <c r="C9" s="99">
         <f>'Daily KPIs'!C9</f>
-        <v>0</v>
+        <v>283.536</v>
       </c>
       <c r="D9" s="99">
         <f>'Daily KPIs'!D9</f>
@@ -45496,7 +45709,7 @@
       </c>
       <c r="AG9" s="215">
         <f>SUM($B9:AF9)</f>
-        <v>367.56479999999999</v>
+        <v>651.10079999999994</v>
       </c>
       <c r="AH9" s="214"/>
       <c r="AI9" s="265"/>
@@ -45509,9 +45722,9 @@
         <f>'Daily KPIs'!B10</f>
         <v>ST/VM</v>
       </c>
-      <c r="C10" s="163">
+      <c r="C10" s="163" t="str">
         <f>'Daily KPIs'!C10</f>
-        <v>0</v>
+        <v>VM/VMg</v>
       </c>
       <c r="D10" s="163">
         <f>'Daily KPIs'!D10</f>
@@ -45597,11 +45810,11 @@
         <f>'Daily KPIs'!X10</f>
         <v>0</v>
       </c>
-      <c r="Y10" s="1022">
+      <c r="Y10" s="1023">
         <f>'Daily KPIs'!Y10</f>
         <v>0</v>
       </c>
-      <c r="Z10" s="1022"/>
+      <c r="Z10" s="1023"/>
       <c r="AA10" s="163">
         <f>'Daily KPIs'!AA10</f>
         <v>0</v>
@@ -45956,17 +46169,17 @@
         <f>+'Water '!$D7</f>
         <v>55</v>
       </c>
-      <c r="C16" s="110" t="str">
+      <c r="C16" s="110">
         <f>+'Water '!$D8</f>
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="D16" s="110" t="str">
         <f>+'Water '!$D9</f>
         <v>0</v>
       </c>
-      <c r="E16" s="110" t="str">
+      <c r="E16" s="110">
         <f>+'Water '!$D10</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="F16" s="110" t="str">
         <f>+'Water '!$D11</f>
@@ -46078,7 +46291,7 @@
       </c>
       <c r="AG16" s="220">
         <f>SUM($B16:AF16)</f>
-        <v>55</v>
+        <v>251</v>
       </c>
       <c r="AH16" s="221"/>
     </row>
@@ -46090,13 +46303,13 @@
         <f>+'Water '!$E7</f>
         <v>180</v>
       </c>
-      <c r="C17" s="113" t="str">
+      <c r="C17" s="113">
         <f>+'Water '!$E8</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="112" t="str">
+        <v>180</v>
+      </c>
+      <c r="D17" s="112">
         <f>+'Water '!$E9</f>
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="E17" s="112" t="str">
         <f>+'Water '!$E10</f>
@@ -46212,7 +46425,7 @@
       </c>
       <c r="AG17" s="222">
         <f>SUM($B17:AF17)</f>
-        <v>180</v>
+        <v>487</v>
       </c>
       <c r="AH17" s="223"/>
       <c r="AI17" s="268"/>
@@ -46227,15 +46440,15 @@
       </c>
       <c r="C18" s="118">
         <f t="shared" ref="C18:AC18" si="0">SUM(C15:C17)</f>
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="D18" s="118">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="E18" s="118">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="F18" s="118">
         <f t="shared" si="0"/>
@@ -46347,7 +46560,7 @@
       </c>
       <c r="AG18" s="224">
         <f>SUM($B18:AF18)</f>
-        <v>235</v>
+        <v>738</v>
       </c>
       <c r="AH18" s="224"/>
       <c r="AI18" s="269"/>
@@ -46441,11 +46654,11 @@
       </c>
       <c r="C21" s="119">
         <f t="shared" ref="C21:AC21" si="1">0.73*(C96+C15)</f>
-        <v>0</v>
+        <v>139.43</v>
       </c>
       <c r="D21" s="119">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>97.82</v>
       </c>
       <c r="E21" s="119">
         <f>0.73*(E96+E15)</f>
@@ -46561,16 +46774,16 @@
       </c>
       <c r="AG21" s="220">
         <f>SUM($B21:AF21)</f>
-        <v>181.04</v>
+        <v>418.29</v>
       </c>
       <c r="AH21" s="225">
         <f>AG24+AG37+AG28</f>
-        <v>425</v>
+        <v>854</v>
       </c>
       <c r="AI21" s="271"/>
       <c r="AJ21" s="272">
         <f>(AH21*10)/AG9</f>
-        <v>11.562587059479036</v>
+        <v>13.116248666873087</v>
       </c>
     </row>
     <row r="22" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -46580,7 +46793,7 @@
       <c r="D22" s="95"/>
       <c r="E22" s="119">
         <f>0.73*(E97+E16)</f>
-        <v>0</v>
+        <v>46.72</v>
       </c>
       <c r="F22" s="95"/>
       <c r="G22" s="95"/>
@@ -46758,15 +46971,15 @@
       </c>
       <c r="C24" s="112">
         <f>'Water '!H8</f>
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="D24" s="112">
         <f>'Water '!H9</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E24" s="112">
         <f>'Water '!H10</f>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="F24" s="112">
         <f>'Water '!H11</f>
@@ -46878,7 +47091,7 @@
       </c>
       <c r="AG24" s="222">
         <f>SUM($B24:AF24)</f>
-        <v>249</v>
+        <v>531</v>
       </c>
       <c r="AH24" s="222"/>
       <c r="AI24" s="222"/>
@@ -46893,15 +47106,15 @@
       </c>
       <c r="C25" s="118">
         <f t="shared" ref="C25:AC25" si="2">SUM(C23:C24)</f>
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="D25" s="118">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E25" s="118">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="F25" s="118">
         <f t="shared" si="2"/>
@@ -47013,7 +47226,7 @@
       </c>
       <c r="AG25" s="224">
         <f>SUM($B25:AF25)</f>
-        <v>249</v>
+        <v>531</v>
       </c>
       <c r="AH25" s="224"/>
       <c r="AI25" s="269"/>
@@ -47026,9 +47239,9 @@
         <f>IF(B$9=0,"",+(B25*10)/B$9)</f>
         <v>6.7743157124947766</v>
       </c>
-      <c r="C26" s="125" t="str">
+      <c r="C26" s="125">
         <f t="shared" ref="C26:AC26" si="3">IF(C$9=0,"",+(C25*10)/C$9)</f>
-        <v/>
+        <v>6.7010891033237403</v>
       </c>
       <c r="D26" s="125" t="str">
         <f t="shared" si="3"/>
@@ -47200,9 +47413,9 @@
         <f>+'Water '!$J7</f>
         <v>157</v>
       </c>
-      <c r="C28" s="127" t="str">
+      <c r="C28" s="127">
         <f>+'Water '!$J8</f>
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="D28" s="127" t="str">
         <f>+'Water '!$J9</f>
@@ -47322,7 +47535,7 @@
       </c>
       <c r="AG28" s="220">
         <f>SUM($B28:AF28)</f>
-        <v>157</v>
+        <v>283</v>
       </c>
       <c r="AH28" s="220"/>
       <c r="AI28" s="271"/>
@@ -47779,9 +47992,9 @@
         <f>+'Water '!$N7</f>
         <v>59</v>
       </c>
-      <c r="C33" s="131" t="str">
+      <c r="C33" s="131">
         <f>+'Water '!$N8</f>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="D33" s="131" t="str">
         <f>+'Water '!$N9</f>
@@ -47901,7 +48114,7 @@
       </c>
       <c r="AG33" s="227">
         <f>SUM($B33:AF33)</f>
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="AH33" s="227"/>
       <c r="AI33" s="227"/>
@@ -47918,9 +48131,9 @@
         <f>+'Water '!$O7</f>
         <v>99</v>
       </c>
-      <c r="C34" s="134" t="str">
+      <c r="C34" s="134">
         <f>+'Water '!$O8</f>
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="D34" s="134" t="str">
         <f>+'Water '!$O9</f>
@@ -48040,7 +48253,7 @@
       </c>
       <c r="AG34" s="228">
         <f>SUM($B34:AF34)</f>
-        <v>99</v>
+        <v>180</v>
       </c>
       <c r="AH34" s="228"/>
       <c r="AI34" s="228"/>
@@ -48055,7 +48268,7 @@
       </c>
       <c r="C35" s="119">
         <f>IF('Entries October 2026'!AC8-'Entries October 2026'!AC7&lt;1,0,'Entries October 2026'!AC8-'Entries October 2026'!AC7)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D35" s="119">
         <f>IF('Entries October 2026'!AC9-'Entries October 2026'!AC8&lt;1,0,'Entries October 2026'!AC9-'Entries October 2026'!AC8)</f>
@@ -48175,7 +48388,7 @@
       </c>
       <c r="AG35" s="220">
         <f>SUM($B35:AF35)</f>
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="AH35" s="220"/>
       <c r="AI35" s="271"/>
@@ -48188,9 +48401,9 @@
         <f>+'Water '!$M7</f>
         <v>2</v>
       </c>
-      <c r="C36" s="110" t="str">
+      <c r="C36" s="110">
         <f>+'Water '!$M8</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D36" s="110" t="str">
         <f>+'Water '!$M9</f>
@@ -48310,7 +48523,7 @@
       </c>
       <c r="AG36" s="220">
         <f>SUM($B36:AF36)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AH36" s="220"/>
       <c r="AI36" s="271"/>
@@ -48323,17 +48536,17 @@
         <f>+'Water '!$Q7</f>
         <v>19</v>
       </c>
-      <c r="C37" s="131" t="str">
+      <c r="C37" s="131">
         <f>+'Water '!$Q8</f>
-        <v>0</v>
-      </c>
-      <c r="D37" s="131" t="str">
+        <v>16</v>
+      </c>
+      <c r="D37" s="131">
         <f>+'Water '!$Q9</f>
-        <v>0</v>
-      </c>
-      <c r="E37" s="131" t="str">
+        <v>3</v>
+      </c>
+      <c r="E37" s="131">
         <f>+'Water '!$Q10</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F37" s="131" t="str">
         <f>+'Water '!$Q11</f>
@@ -48445,7 +48658,7 @@
       </c>
       <c r="AG37" s="227">
         <f>SUM($B37:AF37)</f>
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="AH37" s="227"/>
       <c r="AI37" s="227"/>
@@ -48813,15 +49026,15 @@
       </c>
       <c r="C42" s="138">
         <f>SUM(C28:C41)</f>
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="D42" s="138">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E42" s="138">
         <f>SUM(E28:E41)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F42" s="138">
         <f t="shared" si="4"/>
@@ -48933,7 +49146,7 @@
       </c>
       <c r="AG42" s="230">
         <f>SUM($B42:AF42)</f>
-        <v>352</v>
+        <v>642</v>
       </c>
       <c r="AH42" s="230"/>
       <c r="AI42" s="276"/>
@@ -49096,7 +49309,7 @@
       </c>
       <c r="C47" s="178">
         <f>IF('Entries October 2026'!M8-'Entries October 2026'!M7&lt;1,0,'Entries October 2026'!M8-'Entries October 2026'!M7)</f>
-        <v>0</v>
+        <v>1141.6199999999953</v>
       </c>
       <c r="D47" s="178">
         <f>IF('Entries October 2026'!M9-'Entries October 2026'!M8&lt;1,0,'Entries October 2026'!M9-'Entries October 2026'!M8)</f>
@@ -49268,9 +49481,9 @@
         <f>'Daily KPIs'!B76</f>
         <v>194.34000000001106</v>
       </c>
-      <c r="C49" s="187" t="str">
+      <c r="C49" s="187">
         <f>'Daily KPIs'!C76</f>
-        <v>0</v>
+        <v>146.09999999999127</v>
       </c>
       <c r="D49" s="187" t="str">
         <f>'Daily KPIs'!D76</f>
@@ -49390,7 +49603,7 @@
       </c>
       <c r="AG49" s="235">
         <f>SUM($B49:AF49)</f>
-        <v>194.34000000001106</v>
+        <v>340.44000000000233</v>
       </c>
       <c r="AH49" s="236"/>
       <c r="AI49" s="280"/>
@@ -49479,15 +49692,15 @@
       </c>
       <c r="C52" s="141">
         <f>'Elec.OCTOBER 2026'!$B$8</f>
-        <v>0</v>
+        <v>7089</v>
       </c>
       <c r="D52" s="141">
         <f>'Elec.OCTOBER 2026'!$B$9</f>
-        <v>0</v>
+        <v>3772</v>
       </c>
       <c r="E52" s="141">
         <f>'Elec.OCTOBER 2026'!$B$10</f>
-        <v>0</v>
+        <v>4062</v>
       </c>
       <c r="F52" s="141">
         <f>'Elec.OCTOBER 2026'!$B$11</f>
@@ -49599,7 +49812,7 @@
       </c>
       <c r="AG52" s="224">
         <f>SUM(B52:AC52)</f>
-        <v>7369</v>
+        <v>22292</v>
       </c>
       <c r="AH52" s="224"/>
       <c r="AI52" s="276"/>
@@ -50005,9 +50218,9 @@
         <f>IF(B$9=0,"",+(B18*10)/B$9)</f>
         <v>6.3934304917119373</v>
       </c>
-      <c r="C59" s="144" t="str">
+      <c r="C59" s="144">
         <f>IF(C$9=0,"",+(C18*10)/C$9)</f>
-        <v/>
+        <v>11.003893685457932</v>
       </c>
       <c r="D59" s="144" t="str">
         <f t="shared" ref="D59:Y59" si="5">IF(D$9=0,"",+(D18*10)/D$9)</f>
@@ -50127,7 +50340,7 @@
       </c>
       <c r="AG59" s="238">
         <f>IF(AG$9=0,"",+(AG18*10)/AG$9)</f>
-        <v>6.3934304917119373</v>
+        <v>11.33465048729782</v>
       </c>
       <c r="AH59" s="239">
         <f>'Daily KPIs'!AI90</f>
@@ -50135,7 +50348,7 @@
       </c>
       <c r="AI59" s="282">
         <f>+AH59-AG59</f>
-        <v>3.806569508288062</v>
+        <v>-1.1346504872978205</v>
       </c>
       <c r="AJ59" s="270"/>
       <c r="AK59" s="270"/>
@@ -50170,9 +50383,9 @@
         <f>IF(B$9=0,"",+(B28*10)/B$9)</f>
         <v>4.2713556902075496</v>
       </c>
-      <c r="C62" s="145" t="str">
+      <c r="C62" s="145">
         <f>IF(C$9=0,"",+(C28*10)/C$9)</f>
-        <v/>
+        <v>4.4438801422041649</v>
       </c>
       <c r="D62" s="145" t="str">
         <f t="shared" ref="D62:W62" si="8">IF(D$9=0,"",+(D28*10)/D$9)</f>
@@ -50292,27 +50505,27 @@
       </c>
       <c r="AG62" s="241">
         <f>IF(+(AG28*10)/AG$9&lt;1,0,+(AG28*10)/AG$9)</f>
-        <v>4.2713556902075496</v>
+        <v>4.3464852139637982</v>
       </c>
       <c r="AH62" s="241">
         <v>2.5</v>
       </c>
       <c r="AI62" s="242">
         <f t="shared" ref="AI62:AI78" si="11">AH62-AG62</f>
-        <v>-1.7713556902075496</v>
+        <v>-1.8464852139637982</v>
       </c>
     </row>
     <row r="63" spans="1:37" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A63" s="167" t="s">
         <v>212</v>
       </c>
-      <c r="B63" s="168" t="str">
+      <c r="B63" s="168">
         <f>IF(B$93=0,"",+(B28*10)/B$93)</f>
-        <v/>
-      </c>
-      <c r="C63" s="168" t="str">
+        <v>6.2976333734456471</v>
+      </c>
+      <c r="C63" s="168">
         <f t="shared" ref="C63:X63" si="12">IF(C$93=0,"",+(C28*10)/C$93)</f>
-        <v/>
+        <v>8.3333333333333339</v>
       </c>
       <c r="D63" s="168" t="str">
         <f t="shared" si="12"/>
@@ -50430,16 +50643,16 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AG63" s="243" t="e">
+      <c r="AG63" s="243">
         <f>IF(+(AG28*10)/AG$93&lt;1,0,+(AG28*10)/AG$93)</f>
-        <v>#DIV/0!</v>
+        <v>7.0661672908863924</v>
       </c>
       <c r="AH63" s="243">
         <v>2.5</v>
       </c>
-      <c r="AI63" s="244" t="e">
+      <c r="AI63" s="244">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
+        <v>-4.5661672908863924</v>
       </c>
     </row>
     <row r="64" spans="1:37" s="90" customFormat="1" ht="18" x14ac:dyDescent="0.25">
@@ -50450,9 +50663,9 @@
         <f>IF(B$9=0,"",+(B29*10)/B$9)</f>
         <v>0</v>
       </c>
-      <c r="C64" s="147" t="str">
+      <c r="C64" s="147">
         <f t="shared" ref="C64:X64" si="14">IF(C$9=0,"",+(C29*10)/C$9)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D64" s="147" t="str">
         <f t="shared" si="14"/>
@@ -50638,9 +50851,9 @@
         <f t="shared" ref="B66:V66" si="16">IF(B$9=0,"",+(B31*10)/B$9)</f>
         <v>0</v>
       </c>
-      <c r="C66" s="145" t="str">
+      <c r="C66" s="145">
         <f t="shared" si="16"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D66" s="145" t="str">
         <f t="shared" si="16"/>
@@ -50750,9 +50963,9 @@
         <f t="shared" ref="B67:X67" si="18">IF(B$9=0,"",+(B32*10)/B$9)</f>
         <v>0</v>
       </c>
-      <c r="C67" s="150" t="str">
+      <c r="C67" s="150">
         <f t="shared" si="18"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D67" s="150" t="str">
         <f t="shared" si="18"/>
@@ -50892,9 +51105,9 @@
         <f t="shared" ref="B68:X68" si="20">IF(B$9=0,"",+(B33*10)/B$9)</f>
         <v>1.6051591447276781</v>
       </c>
-      <c r="C68" s="145" t="str">
+      <c r="C68" s="145">
         <f t="shared" si="20"/>
-        <v/>
+        <v>1.5518311607697082</v>
       </c>
       <c r="D68" s="145" t="str">
         <f t="shared" si="20"/>
@@ -51014,14 +51227,14 @@
       </c>
       <c r="AG68" s="241">
         <f>+(AG33*10)/AG$9</f>
-        <v>1.6051591447276781</v>
+        <v>1.5819363146228664</v>
       </c>
       <c r="AH68" s="241">
         <v>0.7</v>
       </c>
       <c r="AI68" s="242">
         <f t="shared" si="11"/>
-        <v>-0.90515914472767811</v>
+        <v>-0.88193631462286648</v>
       </c>
     </row>
     <row r="69" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -51032,9 +51245,9 @@
         <f t="shared" ref="B69:X69" si="22">IF(B$9=0,"",+(B34*10)/B$9)</f>
         <v>2.6934026326786462</v>
       </c>
-      <c r="C69" s="145" t="str">
+      <c r="C69" s="145">
         <f t="shared" si="22"/>
-        <v/>
+        <v>2.856780091416963</v>
       </c>
       <c r="D69" s="145" t="str">
         <f t="shared" si="22"/>
@@ -51154,14 +51367,14 @@
       </c>
       <c r="AG69" s="241">
         <f>+(AG34*10)/AG$9</f>
-        <v>2.6934026326786462</v>
+        <v>2.764548899340932</v>
       </c>
       <c r="AH69" s="241">
         <v>2.6</v>
       </c>
       <c r="AI69" s="242">
         <f t="shared" si="11"/>
-        <v>-9.3402632678646125E-2</v>
+        <v>-0.16454889934093186</v>
       </c>
     </row>
     <row r="70" spans="1:37" ht="18.75" x14ac:dyDescent="0.3">
@@ -51309,9 +51522,9 @@
         <f t="shared" ref="B71:X71" si="26">IF(B$9=0,"",+(B35*10)/B$9)</f>
         <v>0.43529739518038724</v>
       </c>
-      <c r="C71" s="145" t="str">
+      <c r="C71" s="145">
         <f t="shared" si="26"/>
-        <v/>
+        <v>0.5290333502624005</v>
       </c>
       <c r="D71" s="145" t="str">
         <f t="shared" si="26"/>
@@ -51431,14 +51644,14 @@
       </c>
       <c r="AG71" s="241">
         <f>+(AG35*10)/AG$9</f>
-        <v>0.43529739518038724</v>
+        <v>0.4761167548864938</v>
       </c>
       <c r="AH71" s="241">
         <v>0.7</v>
       </c>
       <c r="AI71" s="242">
         <f>AH71-AG71</f>
-        <v>0.26470260481961272</v>
+        <v>0.22388324511350616</v>
       </c>
     </row>
     <row r="72" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -51449,9 +51662,9 @@
         <f t="shared" ref="B72:X72" si="29">IF(B$9=0,"",+(B36*10)/B$9)</f>
         <v>5.4412174397548405E-2</v>
       </c>
-      <c r="C72" s="145" t="str">
+      <c r="C72" s="145">
         <f t="shared" si="29"/>
-        <v/>
+        <v>0.10580667005248011</v>
       </c>
       <c r="D72" s="145" t="str">
         <f t="shared" si="29"/>
@@ -51571,14 +51784,14 @@
       </c>
       <c r="AG72" s="241">
         <f>+(AG36*10)/AG$9</f>
-        <v>5.4412174397548405E-2</v>
+        <v>7.6793024981692548E-2</v>
       </c>
       <c r="AH72" s="241">
         <v>0.1</v>
       </c>
       <c r="AI72" s="242">
         <f>AH72-AG72</f>
-        <v>4.5587825602451601E-2</v>
+        <v>2.3206975018307457E-2</v>
       </c>
     </row>
     <row r="73" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -51589,9 +51802,9 @@
         <f t="shared" ref="B73:X73" si="31">IF(B$9=0,"",+(B37*10)/B$9)</f>
         <v>0.51691565677670981</v>
       </c>
-      <c r="C73" s="145" t="str">
+      <c r="C73" s="145">
         <f t="shared" si="31"/>
-        <v/>
+        <v>0.56430224027989395</v>
       </c>
       <c r="D73" s="145" t="str">
         <f t="shared" si="31"/>
@@ -51711,14 +51924,14 @@
       </c>
       <c r="AG73" s="241">
         <f>+(AG37*10)/AG$9</f>
-        <v>0.51691565677670981</v>
+        <v>0.61434419985354038</v>
       </c>
       <c r="AH73" s="241">
         <v>0.6</v>
       </c>
       <c r="AI73" s="242">
         <f t="shared" si="11"/>
-        <v>8.3084343223290169E-2</v>
+        <v>-1.4344199853540407E-2</v>
       </c>
     </row>
     <row r="74" spans="1:37" s="91" customFormat="1" ht="18" x14ac:dyDescent="0.25">
@@ -51729,9 +51942,9 @@
         <f t="shared" ref="B74:X74" si="33">IF(B$9=0,"",+(B38*10)/B$9)</f>
         <v>0</v>
       </c>
-      <c r="C74" s="150" t="str">
+      <c r="C74" s="150">
         <f t="shared" si="33"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D74" s="150" t="str">
         <f t="shared" si="33"/>
@@ -51871,9 +52084,9 @@
         <f t="shared" ref="B75:X75" si="35">IF(B$9=0,"",+(B39*10)/B$9)</f>
         <v>0</v>
       </c>
-      <c r="C75" s="145" t="str">
+      <c r="C75" s="145">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D75" s="145" t="str">
         <f t="shared" si="35"/>
@@ -52101,11 +52314,11 @@
       </c>
       <c r="B78" s="152">
         <f t="shared" ref="B78:AH78" si="37">SUM(B62:B77)</f>
-        <v>9.5765426939685181</v>
+        <v>15.874176067414165</v>
       </c>
       <c r="C78" s="152">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>18.384966988318943</v>
       </c>
       <c r="D78" s="152">
         <f t="shared" si="37"/>
@@ -52223,17 +52436,17 @@
         <f>SUM(AF62:AF77)</f>
         <v>0</v>
       </c>
-      <c r="AG78" s="253" t="e">
+      <c r="AG78" s="253">
         <f>SUM(AG62:AG77)</f>
-        <v>#DIV/0!</v>
+        <v>16.926391698535717</v>
       </c>
       <c r="AH78" s="253">
         <f t="shared" si="37"/>
         <v>15.599999999999998</v>
       </c>
-      <c r="AI78" s="253" t="e">
+      <c r="AI78" s="253">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
+        <v>-1.3263916985357191</v>
       </c>
       <c r="AJ78" s="210"/>
       <c r="AK78" s="210"/>
@@ -52248,7 +52461,7 @@
       </c>
       <c r="C79" s="154">
         <f t="shared" ref="C79:AI79" si="38">SUM(C69:C72)</f>
-        <v>0</v>
+        <v>3.4916201117318435</v>
       </c>
       <c r="D79" s="154">
         <f>SUM(D69:D72)</f>
@@ -52368,7 +52581,7 @@
       </c>
       <c r="AG79" s="254">
         <f t="shared" si="38"/>
-        <v>3.1831122022565821</v>
+        <v>3.3174586792091185</v>
       </c>
       <c r="AH79" s="254">
         <f t="shared" si="38"/>
@@ -52376,7 +52589,7 @@
       </c>
       <c r="AI79" s="254">
         <f t="shared" si="38"/>
-        <v>2.8168877977434184</v>
+        <v>2.6825413207908819</v>
       </c>
       <c r="AJ79" s="285"/>
       <c r="AK79" s="285"/>
@@ -52389,9 +52602,9 @@
         <f t="shared" ref="B80:W80" si="39">IF(B$9=0,"",+B47/B$9)</f>
         <v>4.2971470608719375</v>
       </c>
-      <c r="C80" s="155" t="str">
+      <c r="C80" s="155">
         <f>IF(C$9=0,"",+C47/C$9)</f>
-        <v/>
+        <v>4.0263670221770615</v>
       </c>
       <c r="D80" s="155" t="str">
         <f t="shared" si="39"/>
@@ -52532,9 +52745,9 @@
         <f t="shared" ref="B81:Z81" si="41">IF(B$9=0,"",+B49/B$9)</f>
         <v>0.52872309862100797</v>
       </c>
-      <c r="C81" s="157" t="str">
+      <c r="C81" s="157">
         <f>IF(C$9=0,"",+C49/C$9)</f>
-        <v/>
+        <v>0.51527848315554736</v>
       </c>
       <c r="D81" s="157" t="str">
         <f>IF(D$9=0,"",+D49/D$9)</f>
@@ -52654,7 +52867,7 @@
       </c>
       <c r="AG81" s="287">
         <f>IF(AG$9=0,"",+AG49/AG$9)</f>
-        <v>0.52872309862100797</v>
+        <v>0.5228683484953518</v>
       </c>
       <c r="AH81" s="287">
         <f>'Daily KPIs'!AI93</f>
@@ -52662,7 +52875,7 @@
       </c>
       <c r="AI81" s="286">
         <f>AH81-AG81</f>
-        <v>1.1712769013789921</v>
+        <v>1.1771316515046482</v>
       </c>
       <c r="AJ81" s="210"/>
       <c r="AK81" s="210"/>
@@ -52675,9 +52888,9 @@
         <f>IF(B$9=0,"",B52/B$9)</f>
         <v>20.04816565677671</v>
       </c>
-      <c r="C82" s="144" t="str">
+      <c r="C82" s="144">
         <f t="shared" ref="C82:Y82" si="43">IF(C$9=0,"",C52/C$9)</f>
-        <v/>
+        <v>25.002116133401049</v>
       </c>
       <c r="D82" s="144" t="str">
         <f t="shared" si="43"/>
@@ -52797,7 +53010,7 @@
       </c>
       <c r="AG82" s="238">
         <f>+(AG52)/AG$9</f>
-        <v>20.04816565677671</v>
+        <v>34.237402257837807</v>
       </c>
       <c r="AH82" s="239">
         <f>'Daily KPIs'!AI94</f>
@@ -52805,7 +53018,7 @@
       </c>
       <c r="AI82" s="286">
         <f>AH82-AG82</f>
-        <v>1.9518343432232896</v>
+        <v>-12.237402257837807</v>
       </c>
       <c r="AJ82" s="270"/>
       <c r="AK82" s="270"/>
@@ -52863,9 +53076,9 @@
         <f>IF(B$9=0,"",B54/B$9)</f>
         <v>2.6117843710823236</v>
       </c>
-      <c r="C84" s="144" t="str">
+      <c r="C84" s="144">
         <f t="shared" ref="C84:Z84" si="46">IF(C$9=0,"",C54/C$9)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D84" s="144" t="str">
         <f t="shared" si="46"/>
@@ -52985,7 +53198,7 @@
       </c>
       <c r="AG84" s="255">
         <f>+(AG54)/AG$9</f>
-        <v>2.6117843710823236</v>
+        <v>1.4744260796484969</v>
       </c>
       <c r="AH84" s="256">
         <f>'Daily KPIs'!AI96</f>
@@ -52993,7 +53206,7 @@
       </c>
       <c r="AI84" s="286">
         <f>AH84-AG84</f>
-        <v>4.588215628917677</v>
+        <v>5.7255739203515033</v>
       </c>
       <c r="AJ84" s="270"/>
       <c r="AK84" s="270"/>
@@ -53184,7 +53397,7 @@
       </c>
       <c r="C87" s="159">
         <f>IF('Entries October 2026'!L8-'Entries October 2026'!L7&lt;1,0,'Entries October 2026'!L8-'Entries October 2026'!L7)</f>
-        <v>0</v>
+        <v>475.41000000000349</v>
       </c>
       <c r="D87" s="159">
         <f>IF('Entries October 2026'!L9-'Entries October 2026'!L8&lt;1,0,'Entries October 2026'!L9-'Entries October 2026'!L8)</f>
@@ -53304,7 +53517,7 @@
       </c>
       <c r="AG87" s="220">
         <f>SUM($B87:AF87)</f>
-        <v>564.13000000000466</v>
+        <v>1039.5400000000081</v>
       </c>
       <c r="AH87" s="220"/>
       <c r="AI87" s="271"/>
@@ -53359,9 +53572,9 @@
         <f t="shared" ref="B89:AD89" si="49">IF(B87=0,"",B88/B87)</f>
         <v>0</v>
       </c>
-      <c r="C89" s="160" t="str">
+      <c r="C89" s="160">
         <f t="shared" si="49"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D89" s="160" t="str">
         <f t="shared" si="49"/>
@@ -53703,11 +53916,11 @@
       </c>
       <c r="B93" s="165">
         <f>'Daily KPIs'!B12</f>
-        <v>0</v>
+        <v>249.3</v>
       </c>
       <c r="C93" s="165">
         <f>'Daily KPIs'!C12</f>
-        <v>0</v>
+        <v>151.19999999999999</v>
       </c>
       <c r="D93" s="165">
         <f>'Daily KPIs'!D12</f>
@@ -53827,7 +54040,7 @@
       </c>
       <c r="AG93" s="260">
         <f>SUM(B93:AF93)</f>
-        <v>0</v>
+        <v>400.5</v>
       </c>
       <c r="AH93" s="261"/>
       <c r="AI93" s="289"/>
@@ -53836,13 +54049,13 @@
       <c r="A94" s="164" t="s">
         <v>211</v>
       </c>
-      <c r="B94" s="166">
+      <c r="B94" s="166" t="str">
         <f>'Daily KPIs'!B13</f>
-        <v>0</v>
-      </c>
-      <c r="C94" s="166">
+        <v>CB</v>
+      </c>
+      <c r="C94" s="166" t="str">
         <f>'Daily KPIs'!C13</f>
-        <v>0</v>
+        <v>CB</v>
       </c>
       <c r="D94" s="166">
         <f>'Daily KPIs'!D13</f>
@@ -53970,11 +54183,11 @@
       </c>
       <c r="B95" s="174">
         <f>'Daily KPIs'!B14</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C95" s="174">
         <f>'Daily KPIs'!C14</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D95" s="174">
         <f>'Daily KPIs'!D14</f>
@@ -54094,7 +54307,7 @@
       </c>
       <c r="AG95" s="262">
         <f>SUM($B95:AF95)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AH95" s="262"/>
       <c r="AI95" s="290"/>
@@ -54107,13 +54320,13 @@
         <f>+'Water '!$F7</f>
         <v>248</v>
       </c>
-      <c r="C96" s="110" t="str">
+      <c r="C96" s="110">
         <f>+'Water '!$F8</f>
-        <v>0</v>
-      </c>
-      <c r="D96" s="110" t="str">
+        <v>191</v>
+      </c>
+      <c r="D96" s="110">
         <f>+'Water '!$F9</f>
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="E96" s="110" t="str">
         <f>+'Water '!$F10</f>
@@ -54229,7 +54442,7 @@
       </c>
       <c r="AG96" s="220">
         <f>SUM($B96:AF96)</f>
-        <v>248</v>
+        <v>573</v>
       </c>
       <c r="AH96" s="220"/>
       <c r="AI96" s="271"/>
@@ -54397,15 +54610,15 @@
       </c>
       <c r="C101" s="159">
         <f>'Daily KPIs CO2'!C52</f>
-        <v>0</v>
+        <v>7089</v>
       </c>
       <c r="D101" s="159">
         <f>'Daily KPIs CO2'!D52</f>
-        <v>0</v>
+        <v>3772</v>
       </c>
       <c r="E101" s="159">
         <f>'Daily KPIs CO2'!E52</f>
-        <v>0</v>
+        <v>4062</v>
       </c>
       <c r="F101" s="159">
         <f>'Daily KPIs CO2'!F52</f>
@@ -54517,7 +54730,7 @@
       </c>
       <c r="AG101" s="263">
         <f>'Daily KPIs CO2'!AG52</f>
-        <v>7369</v>
+        <v>22292</v>
       </c>
       <c r="AH101" s="211"/>
       <c r="AI101" s="271"/>

--- a/data/raw/October_26_Utilities_Tracking.xlsx
+++ b/data/raw/October_26_Utilities_Tracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UTILITIES\Tracking\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A76A303-FCD3-4720-8682-33E8AEBAE1F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B8A8E6-1A74-4A7D-AE34-E58500E8BECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="579" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
     <author>Alexander Dominguez-Ramon</author>
   </authors>
   <commentList>
-    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{DA31AF73-2349-4F00-99F0-13F01ABAE50C}">
+    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{89924D7F-CED0-4C3F-9C04-88723B3A5DE9}">
       <text>
         <r>
           <rPr>
@@ -311,7 +311,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="309">
   <si>
     <t>UTILITY ANALYSIS</t>
   </si>
@@ -5967,7 +5967,7 @@
     <xf numFmtId="9" fontId="49" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1024">
+  <cellXfs count="1023">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8348,9 +8348,6 @@
     <xf numFmtId="3" fontId="7" fillId="31" borderId="131" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="95" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="3" fontId="7" fillId="18" borderId="131" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -8405,9 +8402,51 @@
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="50" fillId="10" borderId="43" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="10" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="10" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="29" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="124" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="77" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="78" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="79" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="100" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="41" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8429,9 +8468,6 @@
     <xf numFmtId="0" fontId="19" fillId="4" borderId="42" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="41" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8447,45 +8483,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="124" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="77" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="78" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="79" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="100" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="10" borderId="43" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="10" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="10" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="29" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="118" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8603,15 +8600,39 @@
     <xf numFmtId="0" fontId="70" fillId="12" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="52" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="53" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="49" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8621,30 +8642,6 @@
     <xf numFmtId="0" fontId="19" fillId="4" borderId="33" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="52" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="53" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -8699,6 +8696,30 @@
     <xf numFmtId="2" fontId="17" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="47" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="72" fillId="18" borderId="56" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="72" fillId="18" borderId="123" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="32" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="32" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="122" fillId="16" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8758,30 +8779,6 @@
     </xf>
     <xf numFmtId="0" fontId="95" fillId="16" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="47" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="72" fillId="18" borderId="56" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="72" fillId="18" borderId="123" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="32" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="32" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="69" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -8795,7 +8792,437 @@
     <cellStyle name="Normal_February04" xfId="3" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
     <cellStyle name="Percent" xfId="4" builtinId="5"/>
   </cellStyles>
-  <dxfs count="119">
+  <dxfs count="162">
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -10129,7 +10556,7 @@
                   <c:v>4062</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>4774</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -10455,6 +10882,9 @@
                 <c:pt idx="3">
                   <c:v>694.6</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>1421</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -10583,7 +11013,7 @@
                   <c:v>0.14602867594500274</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.22937853107344633</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -12069,53 +12499,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="18" x14ac:dyDescent="0.2">
-      <c r="B1" s="899" t="s">
+      <c r="B1" s="912" t="s">
         <v>209</v>
       </c>
-      <c r="C1" s="899"/>
-      <c r="D1" s="899"/>
-      <c r="E1" s="899"/>
-      <c r="F1" s="899"/>
-      <c r="G1" s="899"/>
-      <c r="H1" s="899"/>
-      <c r="I1" s="899"/>
-      <c r="J1" s="899"/>
-      <c r="K1" s="899"/>
-      <c r="L1" s="899"/>
-      <c r="M1" s="899"/>
+      <c r="C1" s="912"/>
+      <c r="D1" s="912"/>
+      <c r="E1" s="912"/>
+      <c r="F1" s="912"/>
+      <c r="G1" s="912"/>
+      <c r="H1" s="912"/>
+      <c r="I1" s="912"/>
+      <c r="J1" s="912"/>
+      <c r="K1" s="912"/>
+      <c r="L1" s="912"/>
+      <c r="M1" s="912"/>
       <c r="N1" s="363"/>
-      <c r="O1" s="900" t="str">
+      <c r="O1" s="913" t="str">
         <f>B1</f>
         <v>ENTRIES FOR DAILY CONS. MONITOR</v>
       </c>
-      <c r="P1" s="900"/>
-      <c r="Q1" s="900"/>
-      <c r="R1" s="900"/>
-      <c r="S1" s="900"/>
-      <c r="T1" s="900"/>
-      <c r="U1" s="900"/>
-      <c r="V1" s="900"/>
-      <c r="W1" s="900"/>
-      <c r="X1" s="900"/>
-      <c r="Y1" s="900"/>
-      <c r="Z1" s="900"/>
-      <c r="AA1" s="900"/>
-      <c r="AB1" s="900"/>
+      <c r="P1" s="913"/>
+      <c r="Q1" s="913"/>
+      <c r="R1" s="913"/>
+      <c r="S1" s="913"/>
+      <c r="T1" s="913"/>
+      <c r="U1" s="913"/>
+      <c r="V1" s="913"/>
+      <c r="W1" s="913"/>
+      <c r="X1" s="913"/>
+      <c r="Y1" s="913"/>
+      <c r="Z1" s="913"/>
+      <c r="AA1" s="913"/>
+      <c r="AB1" s="913"/>
     </row>
     <row r="2" spans="1:44" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C2" s="814"/>
       <c r="F2" s="364"/>
       <c r="G2" s="365"/>
-      <c r="O2" s="908" t="s">
+      <c r="O2" s="920" t="s">
         <v>231</v>
       </c>
-      <c r="P2" s="908"/>
-      <c r="Q2" s="908"/>
-      <c r="R2" s="908"/>
-      <c r="S2" s="908"/>
-      <c r="T2" s="908"/>
-      <c r="U2" s="908"/>
-      <c r="V2" s="908"/>
+      <c r="P2" s="920"/>
+      <c r="Q2" s="920"/>
+      <c r="R2" s="920"/>
+      <c r="S2" s="920"/>
+      <c r="T2" s="920"/>
+      <c r="U2" s="920"/>
+      <c r="V2" s="920"/>
     </row>
     <row r="3" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="366"/>
@@ -12133,50 +12563,50 @@
         <v>22</v>
       </c>
       <c r="K3" s="369"/>
-      <c r="L3" s="913" t="s">
+      <c r="L3" s="903" t="s">
         <v>53</v>
       </c>
-      <c r="M3" s="914"/>
-      <c r="N3" s="915"/>
-      <c r="O3" s="901" t="s">
+      <c r="M3" s="904"/>
+      <c r="N3" s="905"/>
+      <c r="O3" s="914" t="s">
         <v>3</v>
       </c>
-      <c r="P3" s="901"/>
-      <c r="Q3" s="901"/>
-      <c r="R3" s="901"/>
-      <c r="S3" s="901"/>
-      <c r="T3" s="901"/>
-      <c r="U3" s="901"/>
-      <c r="V3" s="901"/>
-      <c r="W3" s="901"/>
-      <c r="X3" s="901"/>
-      <c r="Y3" s="901"/>
-      <c r="Z3" s="901"/>
-      <c r="AA3" s="901"/>
-      <c r="AB3" s="901"/>
-      <c r="AC3" s="901"/>
+      <c r="P3" s="914"/>
+      <c r="Q3" s="914"/>
+      <c r="R3" s="914"/>
+      <c r="S3" s="914"/>
+      <c r="T3" s="914"/>
+      <c r="U3" s="914"/>
+      <c r="V3" s="914"/>
+      <c r="W3" s="914"/>
+      <c r="X3" s="914"/>
+      <c r="Y3" s="914"/>
+      <c r="Z3" s="914"/>
+      <c r="AA3" s="914"/>
+      <c r="AB3" s="914"/>
+      <c r="AC3" s="914"/>
       <c r="AD3" s="372"/>
       <c r="AE3" s="373"/>
       <c r="AF3" s="372"/>
-      <c r="AG3" s="921" t="s">
+      <c r="AG3" s="898" t="s">
         <v>206</v>
       </c>
-      <c r="AH3" s="919" t="s">
+      <c r="AH3" s="896" t="s">
         <v>204</v>
       </c>
-      <c r="AI3" s="919" t="s">
+      <c r="AI3" s="896" t="s">
         <v>205</v>
       </c>
-      <c r="AJ3" s="922" t="s">
+      <c r="AJ3" s="899" t="s">
         <v>233</v>
       </c>
       <c r="AK3" s="416"/>
-      <c r="AL3" s="923" t="s">
+      <c r="AL3" s="900" t="s">
         <v>178</v>
       </c>
-      <c r="AM3" s="923"/>
-      <c r="AN3" s="923"/>
-      <c r="AO3" s="923"/>
+      <c r="AM3" s="900"/>
+      <c r="AN3" s="900"/>
+      <c r="AO3" s="900"/>
     </row>
     <row r="4" spans="1:44" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="374"/>
@@ -12210,40 +12640,40 @@
       <c r="K4" s="372" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="909" t="s">
+      <c r="L4" s="921" t="s">
         <v>289</v>
       </c>
       <c r="M4" s="376" t="s">
         <v>260</v>
       </c>
-      <c r="N4" s="916" t="s">
+      <c r="N4" s="906" t="s">
         <v>167</v>
       </c>
-      <c r="O4" s="897" t="s">
+      <c r="O4" s="908" t="s">
         <v>100</v>
       </c>
-      <c r="P4" s="897" t="s">
+      <c r="P4" s="908" t="s">
         <v>101</v>
       </c>
-      <c r="Q4" s="897" t="s">
+      <c r="Q4" s="908" t="s">
         <v>160</v>
       </c>
-      <c r="R4" s="897" t="s">
+      <c r="R4" s="908" t="s">
         <v>171</v>
       </c>
-      <c r="S4" s="897" t="s">
+      <c r="S4" s="908" t="s">
         <v>102</v>
       </c>
-      <c r="T4" s="897" t="s">
+      <c r="T4" s="908" t="s">
         <v>172</v>
       </c>
-      <c r="U4" s="897" t="s">
+      <c r="U4" s="908" t="s">
         <v>103</v>
       </c>
-      <c r="V4" s="906" t="s">
+      <c r="V4" s="918" t="s">
         <v>236</v>
       </c>
-      <c r="W4" s="897" t="s">
+      <c r="W4" s="908" t="s">
         <v>177</v>
       </c>
       <c r="X4" s="372" t="s">
@@ -12255,28 +12685,28 @@
       <c r="Z4" s="372" t="s">
         <v>98</v>
       </c>
-      <c r="AA4" s="901" t="s">
+      <c r="AA4" s="914" t="s">
         <v>68</v>
       </c>
-      <c r="AB4" s="903" t="s">
+      <c r="AB4" s="916" t="s">
         <v>69</v>
       </c>
-      <c r="AC4" s="907" t="s">
+      <c r="AC4" s="919" t="s">
         <v>151</v>
       </c>
-      <c r="AD4" s="897" t="s">
+      <c r="AD4" s="908" t="s">
         <v>154</v>
       </c>
-      <c r="AE4" s="897" t="s">
+      <c r="AE4" s="908" t="s">
         <v>155</v>
       </c>
-      <c r="AF4" s="897" t="s">
+      <c r="AF4" s="908" t="s">
         <v>159</v>
       </c>
-      <c r="AG4" s="921"/>
-      <c r="AH4" s="920"/>
-      <c r="AI4" s="920"/>
-      <c r="AJ4" s="922"/>
+      <c r="AG4" s="898"/>
+      <c r="AH4" s="897"/>
+      <c r="AI4" s="897"/>
+      <c r="AJ4" s="899"/>
       <c r="AK4" s="416"/>
       <c r="AL4" s="378" t="s">
         <v>276</v>
@@ -12325,20 +12755,20 @@
       <c r="K5" s="465" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="910"/>
+      <c r="L5" s="922"/>
       <c r="M5" s="466" t="s">
         <v>261</v>
       </c>
-      <c r="N5" s="917"/>
-      <c r="O5" s="905"/>
-      <c r="P5" s="897"/>
-      <c r="Q5" s="897"/>
-      <c r="R5" s="897"/>
-      <c r="S5" s="905"/>
-      <c r="T5" s="905"/>
-      <c r="U5" s="905"/>
-      <c r="V5" s="906"/>
-      <c r="W5" s="918"/>
+      <c r="N5" s="907"/>
+      <c r="O5" s="909"/>
+      <c r="P5" s="908"/>
+      <c r="Q5" s="908"/>
+      <c r="R5" s="908"/>
+      <c r="S5" s="909"/>
+      <c r="T5" s="909"/>
+      <c r="U5" s="909"/>
+      <c r="V5" s="918"/>
+      <c r="W5" s="910"/>
       <c r="X5" s="372" t="s">
         <v>104</v>
       </c>
@@ -12348,16 +12778,16 @@
       <c r="Z5" s="372" t="s">
         <v>104</v>
       </c>
-      <c r="AA5" s="902"/>
-      <c r="AB5" s="904"/>
-      <c r="AC5" s="907"/>
-      <c r="AD5" s="897"/>
-      <c r="AE5" s="897"/>
-      <c r="AF5" s="898"/>
-      <c r="AG5" s="921"/>
-      <c r="AH5" s="920"/>
-      <c r="AI5" s="920"/>
-      <c r="AJ5" s="922"/>
+      <c r="AA5" s="915"/>
+      <c r="AB5" s="917"/>
+      <c r="AC5" s="919"/>
+      <c r="AD5" s="908"/>
+      <c r="AE5" s="908"/>
+      <c r="AF5" s="911"/>
+      <c r="AG5" s="898"/>
+      <c r="AH5" s="897"/>
+      <c r="AI5" s="897"/>
+      <c r="AJ5" s="899"/>
       <c r="AK5" s="416"/>
       <c r="AL5" s="378" t="s">
         <v>263</v>
@@ -12396,7 +12826,7 @@
       <c r="I6" s="823">
         <v>1879366</v>
       </c>
-      <c r="J6" s="881"/>
+      <c r="J6" s="880"/>
       <c r="K6" s="822">
         <v>468000</v>
       </c>
@@ -12454,7 +12884,7 @@
       <c r="AG6" s="821"/>
       <c r="AH6" s="821"/>
       <c r="AI6" s="830"/>
-      <c r="AJ6" s="885">
+      <c r="AJ6" s="884">
         <v>7383497.2000000002</v>
       </c>
       <c r="AK6" s="442"/>
@@ -12470,7 +12900,7 @@
       <c r="B7" s="819">
         <v>8522020</v>
       </c>
-      <c r="C7" s="894">
+      <c r="C7" s="893">
         <v>1667565.2</v>
       </c>
       <c r="D7" s="821"/>
@@ -12545,7 +12975,7 @@
       <c r="AG7" s="821"/>
       <c r="AH7" s="821"/>
       <c r="AI7" s="830"/>
-      <c r="AJ7" s="885">
+      <c r="AJ7" s="884">
         <v>7383497.2000000002</v>
       </c>
       <c r="AK7" s="443"/>
@@ -12636,7 +13066,7 @@
       <c r="AG8" s="821"/>
       <c r="AH8" s="821"/>
       <c r="AI8" s="830"/>
-      <c r="AJ8" s="885">
+      <c r="AJ8" s="884">
         <v>7383497.2000000002</v>
       </c>
       <c r="AK8" s="443"/>
@@ -12727,7 +13157,7 @@
       <c r="AG9" s="821"/>
       <c r="AH9" s="821"/>
       <c r="AI9" s="821"/>
-      <c r="AJ9" s="885">
+      <c r="AJ9" s="884">
         <v>7383497.2000000002</v>
       </c>
       <c r="AK9" s="442"/>
@@ -12818,7 +13248,7 @@
       <c r="AG10" s="821"/>
       <c r="AH10" s="821"/>
       <c r="AI10" s="821"/>
-      <c r="AJ10" s="885">
+      <c r="AJ10" s="884">
         <v>7383497.2000000002</v>
       </c>
       <c r="AK10" s="442"/>
@@ -12831,41 +13261,87 @@
       <c r="A11" s="378">
         <v>6</v>
       </c>
-      <c r="B11" s="819"/>
-      <c r="C11" s="820"/>
+      <c r="B11" s="819">
+        <v>8522020</v>
+      </c>
+      <c r="C11" s="820">
+        <v>1673725.1</v>
+      </c>
       <c r="D11" s="821"/>
-      <c r="E11" s="821"/>
-      <c r="F11" s="821"/>
-      <c r="G11" s="821"/>
+      <c r="E11" s="821">
+        <v>64</v>
+      </c>
+      <c r="F11" s="821">
+        <v>11318.3</v>
+      </c>
+      <c r="G11" s="821">
+        <v>68225</v>
+      </c>
       <c r="H11" s="822"/>
-      <c r="I11" s="823"/>
+      <c r="I11" s="823">
+        <v>1906432</v>
+      </c>
       <c r="J11" s="824"/>
-      <c r="K11" s="822"/>
-      <c r="L11" s="821"/>
-      <c r="M11" s="825"/>
-      <c r="N11" s="823"/>
-      <c r="O11" s="826"/>
-      <c r="P11" s="827"/>
-      <c r="Q11" s="821"/>
+      <c r="K11" s="822">
+        <v>468000</v>
+      </c>
+      <c r="L11" s="821">
+        <v>88065.59</v>
+      </c>
+      <c r="M11" s="825">
+        <v>634649.56000000006</v>
+      </c>
+      <c r="N11" s="823">
+        <v>85154.74</v>
+      </c>
+      <c r="O11" s="826">
+        <v>253318</v>
+      </c>
+      <c r="P11" s="827">
+        <v>86332</v>
+      </c>
+      <c r="Q11" s="821">
+        <v>990220</v>
+      </c>
       <c r="R11" s="821"/>
-      <c r="S11" s="821"/>
+      <c r="S11" s="821">
+        <v>97698</v>
+      </c>
       <c r="T11" s="821"/>
-      <c r="U11" s="821"/>
-      <c r="V11" s="828"/>
+      <c r="U11" s="821">
+        <v>544</v>
+      </c>
+      <c r="V11" s="828">
+        <v>1366609</v>
+      </c>
       <c r="W11" s="821"/>
-      <c r="X11" s="829"/>
-      <c r="Y11" s="821"/>
-      <c r="Z11" s="821"/>
-      <c r="AA11" s="821"/>
+      <c r="X11" s="829">
+        <v>49271</v>
+      </c>
+      <c r="Y11" s="821">
+        <v>71065</v>
+      </c>
+      <c r="Z11" s="821">
+        <v>15757</v>
+      </c>
+      <c r="AA11" s="821">
+        <v>97122</v>
+      </c>
       <c r="AB11" s="821"/>
-      <c r="AC11" s="821"/>
-      <c r="AD11" s="876"/>
+      <c r="AC11" s="821">
+        <v>6798</v>
+      </c>
+      <c r="AD11" s="876">
+        <v>263787</v>
+      </c>
       <c r="AE11" s="821"/>
       <c r="AF11" s="823"/>
       <c r="AG11" s="821"/>
       <c r="AH11" s="821"/>
       <c r="AI11" s="821"/>
-      <c r="AJ11" s="885"/>
+      <c r="AJ11" s="884">
+        <v>7383497.2000000002</v>
+      </c>
       <c r="AK11" s="442"/>
       <c r="AL11" s="459"/>
       <c r="AM11" s="457"/>
@@ -12910,7 +13386,7 @@
       <c r="AG12" s="821"/>
       <c r="AH12" s="821"/>
       <c r="AI12" s="821"/>
-      <c r="AJ12" s="885"/>
+      <c r="AJ12" s="884"/>
       <c r="AK12" s="442"/>
       <c r="AL12" s="459"/>
       <c r="AM12" s="457"/>
@@ -12955,7 +13431,7 @@
       <c r="AG13" s="821"/>
       <c r="AH13" s="821"/>
       <c r="AI13" s="821"/>
-      <c r="AJ13" s="885"/>
+      <c r="AJ13" s="884"/>
       <c r="AK13" s="192"/>
       <c r="AL13" s="459"/>
       <c r="AM13" s="457"/>
@@ -13000,7 +13476,7 @@
       <c r="AG14" s="821"/>
       <c r="AH14" s="821"/>
       <c r="AI14" s="821"/>
-      <c r="AJ14" s="885"/>
+      <c r="AJ14" s="884"/>
       <c r="AK14" s="192"/>
       <c r="AL14" s="459"/>
       <c r="AM14" s="457"/>
@@ -13021,8 +13497,8 @@
       <c r="F15" s="821"/>
       <c r="G15" s="821"/>
       <c r="H15" s="822"/>
-      <c r="I15" s="880"/>
-      <c r="J15" s="881"/>
+      <c r="I15" s="879"/>
+      <c r="J15" s="880"/>
       <c r="K15" s="822"/>
       <c r="L15" s="821"/>
       <c r="M15" s="825"/>
@@ -13048,7 +13524,7 @@
       <c r="AG15" s="821"/>
       <c r="AH15" s="821"/>
       <c r="AI15" s="821"/>
-      <c r="AJ15" s="885"/>
+      <c r="AJ15" s="884"/>
       <c r="AK15" s="192"/>
       <c r="AL15" s="459"/>
       <c r="AM15" s="387"/>
@@ -13067,7 +13543,7 @@
       <c r="G16" s="821"/>
       <c r="H16" s="822"/>
       <c r="I16" s="823"/>
-      <c r="J16" s="881"/>
+      <c r="J16" s="880"/>
       <c r="K16" s="822"/>
       <c r="L16" s="821"/>
       <c r="M16" s="825"/>
@@ -13093,7 +13569,7 @@
       <c r="AG16" s="821"/>
       <c r="AH16" s="821"/>
       <c r="AI16" s="821"/>
-      <c r="AJ16" s="885"/>
+      <c r="AJ16" s="884"/>
       <c r="AK16" s="192"/>
       <c r="AL16" s="459"/>
       <c r="AM16" s="387"/>
@@ -13112,7 +13588,7 @@
       <c r="G17" s="821"/>
       <c r="H17" s="822"/>
       <c r="I17" s="823"/>
-      <c r="J17" s="881"/>
+      <c r="J17" s="880"/>
       <c r="K17" s="822"/>
       <c r="L17" s="821"/>
       <c r="M17" s="825"/>
@@ -13138,7 +13614,7 @@
       <c r="AG17" s="821"/>
       <c r="AH17" s="821"/>
       <c r="AI17" s="821"/>
-      <c r="AJ17" s="885"/>
+      <c r="AJ17" s="884"/>
       <c r="AK17" s="192"/>
       <c r="AL17" s="459"/>
       <c r="AM17" s="387"/>
@@ -13157,7 +13633,7 @@
       <c r="G18" s="821"/>
       <c r="H18" s="822"/>
       <c r="I18" s="823"/>
-      <c r="J18" s="881"/>
+      <c r="J18" s="880"/>
       <c r="K18" s="822"/>
       <c r="L18" s="821"/>
       <c r="M18" s="825"/>
@@ -13183,7 +13659,7 @@
       <c r="AG18" s="821"/>
       <c r="AH18" s="821"/>
       <c r="AI18" s="821"/>
-      <c r="AJ18" s="885"/>
+      <c r="AJ18" s="884"/>
       <c r="AK18" s="192"/>
       <c r="AL18" s="459"/>
       <c r="AM18" s="387"/>
@@ -13202,7 +13678,7 @@
       <c r="G19" s="821"/>
       <c r="H19" s="822"/>
       <c r="I19" s="823"/>
-      <c r="J19" s="881"/>
+      <c r="J19" s="880"/>
       <c r="K19" s="822"/>
       <c r="L19" s="821"/>
       <c r="M19" s="825"/>
@@ -13228,7 +13704,7 @@
       <c r="AG19" s="821"/>
       <c r="AH19" s="821"/>
       <c r="AI19" s="821"/>
-      <c r="AJ19" s="885"/>
+      <c r="AJ19" s="884"/>
       <c r="AK19" s="192"/>
       <c r="AL19" s="387"/>
       <c r="AM19" s="387"/>
@@ -13247,7 +13723,7 @@
       <c r="G20" s="821"/>
       <c r="H20" s="822"/>
       <c r="I20" s="823"/>
-      <c r="J20" s="881"/>
+      <c r="J20" s="880"/>
       <c r="K20" s="822"/>
       <c r="L20" s="821"/>
       <c r="M20" s="825"/>
@@ -13273,7 +13749,7 @@
       <c r="AG20" s="821"/>
       <c r="AH20" s="821"/>
       <c r="AI20" s="821"/>
-      <c r="AJ20" s="885"/>
+      <c r="AJ20" s="884"/>
       <c r="AK20" s="192"/>
       <c r="AL20" s="387"/>
       <c r="AM20" s="387"/>
@@ -13292,7 +13768,7 @@
       <c r="G21" s="821"/>
       <c r="H21" s="822"/>
       <c r="I21" s="823"/>
-      <c r="J21" s="881"/>
+      <c r="J21" s="880"/>
       <c r="K21" s="822"/>
       <c r="L21" s="821"/>
       <c r="M21" s="825"/>
@@ -13318,7 +13794,7 @@
       <c r="AG21" s="821"/>
       <c r="AH21" s="821"/>
       <c r="AI21" s="821"/>
-      <c r="AJ21" s="885"/>
+      <c r="AJ21" s="884"/>
       <c r="AK21" s="192"/>
       <c r="AL21" s="387"/>
       <c r="AM21" s="387"/>
@@ -13337,7 +13813,7 @@
       <c r="G22" s="821"/>
       <c r="H22" s="822"/>
       <c r="I22" s="823"/>
-      <c r="J22" s="881"/>
+      <c r="J22" s="880"/>
       <c r="K22" s="822"/>
       <c r="L22" s="821"/>
       <c r="M22" s="825"/>
@@ -13363,7 +13839,7 @@
       <c r="AG22" s="821"/>
       <c r="AH22" s="821"/>
       <c r="AI22" s="821"/>
-      <c r="AJ22" s="885"/>
+      <c r="AJ22" s="884"/>
       <c r="AK22" s="192"/>
       <c r="AL22" s="387"/>
       <c r="AM22" s="387"/>
@@ -13382,7 +13858,7 @@
       <c r="G23" s="821"/>
       <c r="H23" s="822"/>
       <c r="I23" s="823"/>
-      <c r="J23" s="881"/>
+      <c r="J23" s="880"/>
       <c r="K23" s="822"/>
       <c r="L23" s="821"/>
       <c r="M23" s="825"/>
@@ -13408,7 +13884,7 @@
       <c r="AG23" s="821"/>
       <c r="AH23" s="821"/>
       <c r="AI23" s="821"/>
-      <c r="AJ23" s="885"/>
+      <c r="AJ23" s="884"/>
       <c r="AK23" s="192"/>
       <c r="AL23" s="387"/>
       <c r="AM23" s="387"/>
@@ -13427,7 +13903,7 @@
       <c r="G24" s="821"/>
       <c r="H24" s="822"/>
       <c r="I24" s="823"/>
-      <c r="J24" s="881"/>
+      <c r="J24" s="880"/>
       <c r="K24" s="822"/>
       <c r="L24" s="821"/>
       <c r="M24" s="825"/>
@@ -13453,7 +13929,7 @@
       <c r="AG24" s="821"/>
       <c r="AH24" s="821"/>
       <c r="AI24" s="821"/>
-      <c r="AJ24" s="885"/>
+      <c r="AJ24" s="884"/>
       <c r="AK24" s="192"/>
       <c r="AL24" s="387"/>
       <c r="AM24" s="387"/>
@@ -13472,7 +13948,7 @@
       <c r="G25" s="821"/>
       <c r="H25" s="822"/>
       <c r="I25" s="823"/>
-      <c r="J25" s="881"/>
+      <c r="J25" s="880"/>
       <c r="K25" s="822"/>
       <c r="L25" s="821"/>
       <c r="M25" s="825"/>
@@ -13498,7 +13974,7 @@
       <c r="AG25" s="821"/>
       <c r="AH25" s="821"/>
       <c r="AI25" s="821"/>
-      <c r="AJ25" s="885"/>
+      <c r="AJ25" s="884"/>
       <c r="AK25" s="192"/>
       <c r="AL25" s="387"/>
       <c r="AM25" s="387"/>
@@ -13517,7 +13993,7 @@
       <c r="G26" s="821"/>
       <c r="H26" s="822"/>
       <c r="I26" s="823"/>
-      <c r="J26" s="881"/>
+      <c r="J26" s="880"/>
       <c r="K26" s="822"/>
       <c r="L26" s="821"/>
       <c r="M26" s="825"/>
@@ -13543,7 +14019,7 @@
       <c r="AG26" s="821"/>
       <c r="AH26" s="821"/>
       <c r="AI26" s="821"/>
-      <c r="AJ26" s="885"/>
+      <c r="AJ26" s="884"/>
       <c r="AK26" s="192"/>
       <c r="AL26" s="387"/>
       <c r="AM26" s="387"/>
@@ -13562,7 +14038,7 @@
       <c r="G27" s="821"/>
       <c r="H27" s="822"/>
       <c r="I27" s="823"/>
-      <c r="J27" s="881"/>
+      <c r="J27" s="880"/>
       <c r="K27" s="822"/>
       <c r="L27" s="821"/>
       <c r="M27" s="825"/>
@@ -13588,7 +14064,7 @@
       <c r="AG27" s="821"/>
       <c r="AH27" s="821"/>
       <c r="AI27" s="821"/>
-      <c r="AJ27" s="885"/>
+      <c r="AJ27" s="884"/>
       <c r="AK27" s="192"/>
       <c r="AL27" s="387"/>
       <c r="AM27" s="387"/>
@@ -13607,7 +14083,7 @@
       <c r="G28" s="821"/>
       <c r="H28" s="822"/>
       <c r="I28" s="823"/>
-      <c r="J28" s="881"/>
+      <c r="J28" s="880"/>
       <c r="K28" s="822"/>
       <c r="L28" s="821"/>
       <c r="M28" s="825"/>
@@ -13633,7 +14109,7 @@
       <c r="AG28" s="821"/>
       <c r="AH28" s="821"/>
       <c r="AI28" s="821"/>
-      <c r="AJ28" s="885"/>
+      <c r="AJ28" s="884"/>
       <c r="AK28" s="192"/>
       <c r="AL28" s="387" t="s">
         <v>55</v>
@@ -13654,7 +14130,7 @@
       <c r="G29" s="821"/>
       <c r="H29" s="822"/>
       <c r="I29" s="823"/>
-      <c r="J29" s="881"/>
+      <c r="J29" s="880"/>
       <c r="K29" s="822"/>
       <c r="L29" s="821"/>
       <c r="M29" s="825"/>
@@ -13680,7 +14156,7 @@
       <c r="AG29" s="821"/>
       <c r="AH29" s="821"/>
       <c r="AI29" s="821"/>
-      <c r="AJ29" s="885"/>
+      <c r="AJ29" s="884"/>
       <c r="AK29" s="192"/>
       <c r="AL29" s="387"/>
       <c r="AM29" s="387"/>
@@ -13699,7 +14175,7 @@
       <c r="G30" s="821"/>
       <c r="H30" s="822"/>
       <c r="I30" s="823"/>
-      <c r="J30" s="881"/>
+      <c r="J30" s="880"/>
       <c r="K30" s="822"/>
       <c r="L30" s="821"/>
       <c r="M30" s="825"/>
@@ -13725,7 +14201,7 @@
       <c r="AG30" s="821"/>
       <c r="AH30" s="821"/>
       <c r="AI30" s="821"/>
-      <c r="AJ30" s="885"/>
+      <c r="AJ30" s="884"/>
       <c r="AK30" s="192"/>
       <c r="AL30" s="387"/>
       <c r="AM30" s="387"/>
@@ -13744,7 +14220,7 @@
       <c r="G31" s="821"/>
       <c r="H31" s="822"/>
       <c r="I31" s="823"/>
-      <c r="J31" s="881"/>
+      <c r="J31" s="880"/>
       <c r="K31" s="822"/>
       <c r="L31" s="821"/>
       <c r="M31" s="825"/>
@@ -13770,7 +14246,7 @@
       <c r="AG31" s="821"/>
       <c r="AH31" s="821"/>
       <c r="AI31" s="821"/>
-      <c r="AJ31" s="885"/>
+      <c r="AJ31" s="884"/>
       <c r="AK31" s="192"/>
       <c r="AL31" s="387"/>
       <c r="AM31" s="387"/>
@@ -13789,7 +14265,7 @@
       <c r="G32" s="821"/>
       <c r="H32" s="822"/>
       <c r="I32" s="823"/>
-      <c r="J32" s="881"/>
+      <c r="J32" s="880"/>
       <c r="K32" s="822"/>
       <c r="L32" s="821"/>
       <c r="M32" s="825"/>
@@ -13798,7 +14274,7 @@
       <c r="P32" s="827"/>
       <c r="Q32" s="821"/>
       <c r="R32" s="821"/>
-      <c r="S32" s="889"/>
+      <c r="S32" s="888"/>
       <c r="T32" s="821"/>
       <c r="U32" s="821"/>
       <c r="V32" s="828"/>
@@ -13815,7 +14291,7 @@
       <c r="AG32" s="821"/>
       <c r="AH32" s="821"/>
       <c r="AI32" s="821"/>
-      <c r="AJ32" s="885"/>
+      <c r="AJ32" s="884"/>
       <c r="AK32" s="192"/>
       <c r="AL32" s="387"/>
       <c r="AM32" s="387"/>
@@ -13834,7 +14310,7 @@
       <c r="G33" s="821"/>
       <c r="H33" s="822"/>
       <c r="I33" s="823"/>
-      <c r="J33" s="881"/>
+      <c r="J33" s="880"/>
       <c r="K33" s="822"/>
       <c r="L33" s="821"/>
       <c r="M33" s="825"/>
@@ -13843,7 +14319,7 @@
       <c r="P33" s="827"/>
       <c r="Q33" s="821"/>
       <c r="R33" s="821"/>
-      <c r="S33" s="889"/>
+      <c r="S33" s="888"/>
       <c r="T33" s="821"/>
       <c r="U33" s="821"/>
       <c r="V33" s="828"/>
@@ -13860,7 +14336,7 @@
       <c r="AG33" s="821"/>
       <c r="AH33" s="821"/>
       <c r="AI33" s="821"/>
-      <c r="AJ33" s="885"/>
+      <c r="AJ33" s="884"/>
       <c r="AK33" s="192"/>
       <c r="AL33" s="387"/>
       <c r="AM33" s="387"/>
@@ -13879,7 +14355,7 @@
       <c r="G34" s="821"/>
       <c r="H34" s="822"/>
       <c r="I34" s="823"/>
-      <c r="J34" s="881"/>
+      <c r="J34" s="880"/>
       <c r="K34" s="822"/>
       <c r="L34" s="821"/>
       <c r="M34" s="825"/>
@@ -13905,7 +14381,7 @@
       <c r="AG34" s="821"/>
       <c r="AH34" s="821"/>
       <c r="AI34" s="821"/>
-      <c r="AJ34" s="885"/>
+      <c r="AJ34" s="884"/>
       <c r="AK34" s="192"/>
       <c r="AL34" s="387"/>
       <c r="AM34" s="387"/>
@@ -13950,7 +14426,7 @@
       <c r="AG35" s="192"/>
       <c r="AH35" s="192"/>
       <c r="AI35" s="199"/>
-      <c r="AJ35" s="885"/>
+      <c r="AJ35" s="884"/>
       <c r="AK35" s="322"/>
       <c r="AL35" s="457"/>
       <c r="AM35" s="460"/>
@@ -14050,8 +14526,8 @@
     <row r="38" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B38" s="190"/>
       <c r="G38" s="190"/>
-      <c r="I38" s="911"/>
-      <c r="J38" s="911"/>
+      <c r="I38" s="901"/>
+      <c r="J38" s="901"/>
       <c r="R38" s="190"/>
       <c r="S38" s="190"/>
       <c r="T38" s="190"/>
@@ -14059,8 +14535,8 @@
       <c r="V38" s="190"/>
       <c r="W38" s="190"/>
       <c r="Z38" s="190"/>
-      <c r="AA38" s="912"/>
-      <c r="AB38" s="912"/>
+      <c r="AA38" s="902"/>
+      <c r="AB38" s="902"/>
       <c r="AC38" s="190"/>
       <c r="AD38" s="190"/>
       <c r="AI38" s="380"/>
@@ -15726,19 +16202,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="AH3:AH5"/>
-    <mergeCell ref="AG3:AG5"/>
-    <mergeCell ref="AI3:AI5"/>
-    <mergeCell ref="AJ3:AJ5"/>
-    <mergeCell ref="AL3:AO3"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="AA38:AB38"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="S4:S5"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="P4:P5"/>
-    <mergeCell ref="W4:W5"/>
     <mergeCell ref="AF4:AF5"/>
     <mergeCell ref="AE4:AE5"/>
     <mergeCell ref="AD4:AD5"/>
@@ -15755,286 +16218,444 @@
     <mergeCell ref="AC4:AC5"/>
     <mergeCell ref="O2:V2"/>
     <mergeCell ref="L4:L5"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="AA38:AB38"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="S4:S5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="P4:P5"/>
+    <mergeCell ref="W4:W5"/>
+    <mergeCell ref="AH3:AH5"/>
+    <mergeCell ref="AG3:AG5"/>
+    <mergeCell ref="AI3:AI5"/>
+    <mergeCell ref="AJ3:AJ5"/>
+    <mergeCell ref="AL3:AO3"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="expression" dxfId="118" priority="14">
-      <formula>B6&lt;#REF!</formula>
+  <conditionalFormatting sqref="B12:B35">
+    <cfRule type="expression" dxfId="160" priority="71">
+      <formula>B12&lt;B11</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7:B35">
-    <cfRule type="expression" dxfId="117" priority="28">
-      <formula>B7&lt;B6</formula>
+  <conditionalFormatting sqref="B12">
+    <cfRule type="expression" dxfId="159" priority="148">
+      <formula>B12&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B11:B12">
-    <cfRule type="expression" dxfId="116" priority="105">
-      <formula>B11&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C6:D6">
-    <cfRule type="expression" dxfId="115" priority="16">
-      <formula>C6&lt;C5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C7:D7 H7:J7 R7 T7 W7 AB7">
-    <cfRule type="expression" dxfId="114" priority="31">
-      <formula>C7&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C8:D14">
-    <cfRule type="expression" dxfId="113" priority="35">
-      <formula>C8&lt;C7</formula>
+  <conditionalFormatting sqref="C12:D14">
+    <cfRule type="expression" dxfId="156" priority="78">
+      <formula>C12&lt;C11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36:D37">
-    <cfRule type="expression" dxfId="112" priority="1160">
+    <cfRule type="expression" dxfId="155" priority="1203">
       <formula>C36&lt;C35</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D35 B36:B37">
-    <cfRule type="expression" dxfId="111" priority="1147">
+    <cfRule type="expression" dxfId="154" priority="1190">
       <formula>B35&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E6:E14">
-    <cfRule type="expression" dxfId="110" priority="5">
-      <formula>E6&lt;E5</formula>
+  <conditionalFormatting sqref="E12:E14">
+    <cfRule type="expression" dxfId="153" priority="48">
+      <formula>E12&lt;E11</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6:F37">
-    <cfRule type="expression" dxfId="109" priority="4">
-      <formula>F6&lt;#REF!</formula>
+  <conditionalFormatting sqref="F12:F37">
+    <cfRule type="expression" dxfId="152" priority="47">
+      <formula>F12&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G6:G37">
-    <cfRule type="expression" dxfId="108" priority="2">
-      <formula>G6&lt;G5</formula>
+  <conditionalFormatting sqref="G12:G37">
+    <cfRule type="expression" dxfId="151" priority="45">
+      <formula>G12&lt;G11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G36:J37 L36:O37">
-    <cfRule type="expression" dxfId="107" priority="994">
+    <cfRule type="expression" dxfId="150" priority="1037">
       <formula>G36&lt;G35</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G6:O6">
-    <cfRule type="expression" dxfId="106" priority="6">
-      <formula>G6&lt;G5</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H19:I34">
-    <cfRule type="expression" dxfId="105" priority="108">
+    <cfRule type="expression" dxfId="148" priority="151">
       <formula>H19&lt;H18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H35:I35 R35 T35 W35 AB35 AE35:AI35 P36:P37 S36:S37 X36:Y37">
-    <cfRule type="expression" dxfId="104" priority="1146">
+    <cfRule type="expression" dxfId="147" priority="1189">
       <formula>H35&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H8:J18">
-    <cfRule type="expression" dxfId="103" priority="36">
-      <formula>H8&lt;H7</formula>
+  <conditionalFormatting sqref="H12:J18">
+    <cfRule type="expression" dxfId="146" priority="79">
+      <formula>H12&lt;H11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J19:J35">
-    <cfRule type="expression" dxfId="102" priority="109">
+    <cfRule type="expression" dxfId="145" priority="152">
       <formula>J19&lt;J18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K11:L21">
-    <cfRule type="expression" dxfId="101" priority="100">
-      <formula>K11&lt;K10</formula>
+  <conditionalFormatting sqref="K12:L21">
+    <cfRule type="expression" dxfId="144" priority="143">
+      <formula>K12&lt;K11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K22:M22">
-    <cfRule type="expression" dxfId="100" priority="110">
+    <cfRule type="expression" dxfId="143" priority="153">
       <formula>K22&lt;K21</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K7:O10">
-    <cfRule type="expression" dxfId="99" priority="23">
-      <formula>K7&lt;K6</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="K23:Z23 K24:K37">
-    <cfRule type="expression" dxfId="98" priority="111">
+    <cfRule type="expression" dxfId="141" priority="154">
       <formula>K23&lt;K22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L24:Z27 L28:AC28">
-    <cfRule type="expression" dxfId="97" priority="113">
+    <cfRule type="expression" dxfId="140" priority="156">
       <formula>L24&lt;L23</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M11:M17">
-    <cfRule type="expression" dxfId="96" priority="102">
-      <formula>M11&lt;#REF!</formula>
+  <conditionalFormatting sqref="M12:M17">
+    <cfRule type="expression" dxfId="139" priority="145">
+      <formula>M12&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N11:O12">
-    <cfRule type="expression" dxfId="95" priority="101">
-      <formula>N11&lt;N10</formula>
+  <conditionalFormatting sqref="N12:O12">
+    <cfRule type="expression" dxfId="138" priority="144">
+      <formula>N12&lt;N11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N13:T22">
-    <cfRule type="expression" dxfId="94" priority="104">
+    <cfRule type="expression" dxfId="137" priority="147">
       <formula>N13&lt;N12</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P8:P12 V8:V12">
-    <cfRule type="expression" dxfId="93" priority="38">
-      <formula>P8&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P6:Q6 X6:Y6 S6:S10">
-    <cfRule type="expression" dxfId="92" priority="13">
-      <formula>P6&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P7:Q7">
-    <cfRule type="expression" dxfId="91" priority="30">
-      <formula>P7&lt;P6</formula>
+  <conditionalFormatting sqref="P12 V12">
+    <cfRule type="expression" dxfId="136" priority="81">
+      <formula>P12&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q36">
-    <cfRule type="expression" dxfId="90" priority="1163">
+    <cfRule type="expression" dxfId="133" priority="1206">
       <formula>Q36&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q8:R10">
-    <cfRule type="expression" dxfId="89" priority="37">
-      <formula>Q8&lt;Q7</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q11:T12">
-    <cfRule type="expression" dxfId="88" priority="103">
-      <formula>Q11&lt;Q10</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R6">
-    <cfRule type="expression" dxfId="87" priority="15">
-      <formula>R6&lt;R5</formula>
+  <conditionalFormatting sqref="Q12:T12">
+    <cfRule type="expression" dxfId="131" priority="146">
+      <formula>Q12&lt;Q11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R36">
-    <cfRule type="expression" dxfId="86" priority="1159">
+    <cfRule type="expression" dxfId="129" priority="1202">
       <formula>R36&lt;R35</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T8:T10 AB8:AC10 AE8:AI10">
-    <cfRule type="expression" dxfId="85" priority="33">
-      <formula>T8&lt;T7</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T6:W6 Z6 AB6">
-    <cfRule type="expression" dxfId="84" priority="12">
-      <formula>T6&lt;T5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U6:U22">
-    <cfRule type="expression" dxfId="83" priority="9">
-      <formula>U6&lt;U5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V7">
-    <cfRule type="expression" dxfId="82" priority="25">
-      <formula>V7&lt;V6</formula>
+  <conditionalFormatting sqref="U12:U22">
+    <cfRule type="expression" dxfId="126" priority="52">
+      <formula>U12&lt;U11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V13:X14 C15:E34 C35 E35:E37">
-    <cfRule type="expression" dxfId="81" priority="107">
+    <cfRule type="expression" dxfId="124" priority="150">
       <formula>C13&lt;C12</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V15:Z22 M18:M21">
-    <cfRule type="expression" dxfId="80" priority="106">
+    <cfRule type="expression" dxfId="123" priority="149">
       <formula>M15&lt;M14</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V29:AC29 AA30:AC30 Z30:Z31 V30:Y34 AA31:AB31 AC31:AC37 Z32:AB34 V35 X35:AA35">
-    <cfRule type="expression" dxfId="79" priority="117">
+    <cfRule type="expression" dxfId="122" priority="160">
       <formula>V29&lt;V28</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W8:W12">
-    <cfRule type="expression" dxfId="78" priority="34">
-      <formula>W8&lt;W7</formula>
+  <conditionalFormatting sqref="W12">
+    <cfRule type="expression" dxfId="121" priority="77">
+      <formula>W12&lt;W11</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y7:Z14">
-    <cfRule type="expression" dxfId="77" priority="26">
-      <formula>Y7&lt;Y6</formula>
+  <conditionalFormatting sqref="Y12:Z14">
+    <cfRule type="expression" dxfId="120" priority="69">
+      <formula>Y12&lt;Y11</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA6:AA12">
-    <cfRule type="expression" dxfId="76" priority="8">
-      <formula>AA6&lt;#REF!</formula>
+  <conditionalFormatting sqref="AA12">
+    <cfRule type="expression" dxfId="119" priority="51">
+      <formula>AA12&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA6:AA37">
-    <cfRule type="expression" dxfId="75" priority="1">
-      <formula>AA6&lt;AA5</formula>
+  <conditionalFormatting sqref="AA12:AA37">
+    <cfRule type="expression" dxfId="118" priority="44">
+      <formula>AA12&lt;AA11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA28:AA37">
-    <cfRule type="expression" dxfId="74" priority="115">
+    <cfRule type="expression" dxfId="117" priority="158">
       <formula>AA28&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB11:AI27">
-    <cfRule type="expression" dxfId="73" priority="94">
-      <formula>AB11&lt;AB10</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC6:AC7">
-    <cfRule type="expression" dxfId="72" priority="10">
-      <formula>AC6&lt;AC5</formula>
+  <conditionalFormatting sqref="AB12:AI27">
+    <cfRule type="expression" dxfId="116" priority="137">
+      <formula>AB12&lt;AB11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD28:AD37">
-    <cfRule type="expression" dxfId="71" priority="112">
+    <cfRule type="expression" dxfId="114" priority="155">
       <formula>AD28&lt;AD27</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD6:AI6">
-    <cfRule type="expression" dxfId="70" priority="7">
-      <formula>AD6&lt;AD5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD7:AI7 X7:X12 AD8:AD10">
-    <cfRule type="expression" dxfId="69" priority="27">
-      <formula>X7&lt;#REF!</formula>
+  <conditionalFormatting sqref="X12">
+    <cfRule type="expression" dxfId="112" priority="70">
+      <formula>X12&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE28:AI34 L29:T34 U29:U37 L35:Q35 S35">
-    <cfRule type="expression" dxfId="68" priority="116">
+    <cfRule type="expression" dxfId="111" priority="159">
       <formula>L28&lt;L27</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AJ6:AJ37">
-    <cfRule type="expression" dxfId="67" priority="3">
-      <formula>AJ6&lt;AJ5</formula>
+  <conditionalFormatting sqref="AJ12:AJ37">
+    <cfRule type="expression" dxfId="110" priority="46">
+      <formula>AJ12&lt;AJ11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK6:AK12">
-    <cfRule type="expression" dxfId="66" priority="1036">
+    <cfRule type="expression" dxfId="109" priority="1079">
       <formula>AK6&lt;AK5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK13:AL15">
-    <cfRule type="expression" dxfId="65" priority="1116">
+    <cfRule type="expression" dxfId="108" priority="1159">
       <formula>AK13&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL9:AL14 AL15:AN34 AK16:AK37 AK20:AN21 T36:W37 Z36:Z37 AB36:AB37 AE36:AI37 Q37:R37">
-    <cfRule type="expression" dxfId="64" priority="1053">
+    <cfRule type="expression" dxfId="107" priority="1096">
       <formula>Q9&lt;Q8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO9:AO34">
-    <cfRule type="expression" dxfId="63" priority="1061">
+    <cfRule type="expression" dxfId="106" priority="1104">
       <formula>AO9&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:B11">
+    <cfRule type="expression" dxfId="42" priority="28">
+      <formula>B7&lt;B6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11">
+    <cfRule type="expression" dxfId="41" priority="43">
+      <formula>B11&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7:D7 H7:J7 R7 T7 W7 AB7">
+    <cfRule type="expression" dxfId="40" priority="31">
+      <formula>C7&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8:D11">
+    <cfRule type="expression" dxfId="39" priority="35">
+      <formula>C8&lt;C7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7:E11">
+    <cfRule type="expression" dxfId="38" priority="18">
+      <formula>E7&lt;E6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:F11">
+    <cfRule type="expression" dxfId="37" priority="32">
+      <formula>F7&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G7:G11">
+    <cfRule type="expression" dxfId="36" priority="29">
+      <formula>G7&lt;G6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H8:J11">
+    <cfRule type="expression" dxfId="35" priority="36">
+      <formula>H8&lt;H7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K11:L11">
+    <cfRule type="expression" dxfId="34" priority="39">
+      <formula>K11&lt;K10</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7:O8 K9:N10 O9">
+    <cfRule type="expression" dxfId="33" priority="23">
+      <formula>K7&lt;K6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M11">
+    <cfRule type="expression" dxfId="32" priority="41">
+      <formula>M11&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N11:O11 O10">
+    <cfRule type="expression" dxfId="31" priority="40">
+      <formula>N10&lt;N9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S7:S10">
+    <cfRule type="expression" dxfId="30" priority="22">
+      <formula>S7&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P8:P11 V8:V11">
+    <cfRule type="expression" dxfId="29" priority="38">
+      <formula>P8&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P7:Q7">
+    <cfRule type="expression" dxfId="28" priority="30">
+      <formula>P7&lt;P6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q8:R8">
+    <cfRule type="expression" dxfId="27" priority="37">
+      <formula>Q8&lt;Q7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q11:T11 Q9:R10 T9:T10">
+    <cfRule type="expression" dxfId="26" priority="42">
+      <formula>Q9&lt;Q8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T8 AB11:AI11 AB8:AC10 AE8:AI10">
+    <cfRule type="expression" dxfId="25" priority="33">
+      <formula>T8&lt;T7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U7:U11">
+    <cfRule type="expression" dxfId="24" priority="20">
+      <formula>U7&lt;U6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V7">
+    <cfRule type="expression" dxfId="23" priority="25">
+      <formula>V7&lt;V6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W8:W11">
+    <cfRule type="expression" dxfId="22" priority="34">
+      <formula>W8&lt;W7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y7:Z11">
+    <cfRule type="expression" dxfId="21" priority="26">
+      <formula>Y7&lt;Y6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA7:AA11">
+    <cfRule type="expression" dxfId="20" priority="19">
+      <formula>AA7&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA7:AA11">
+    <cfRule type="expression" dxfId="19" priority="24">
+      <formula>AA7&lt;AA6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC7">
+    <cfRule type="expression" dxfId="18" priority="21">
+      <formula>AC7&lt;AC6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD7:AI7 X7:X11 AD8:AD10">
+    <cfRule type="expression" dxfId="17" priority="27">
+      <formula>X7&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C6:D6">
+    <cfRule type="expression" dxfId="16" priority="16">
+      <formula>C6&lt;C5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="expression" dxfId="15" priority="14">
+      <formula>B6&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
+    <cfRule type="expression" dxfId="14" priority="4">
+      <formula>F6&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6">
+    <cfRule type="expression" dxfId="13" priority="2">
+      <formula>G6&lt;G5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6:J6 L6:O6">
+    <cfRule type="expression" dxfId="12" priority="11">
+      <formula>G6&lt;G5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P6 S6 X6:Y6">
+    <cfRule type="expression" dxfId="11" priority="13">
+      <formula>P6&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6">
+    <cfRule type="expression" dxfId="10" priority="6">
+      <formula>K6&lt;K5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q6">
+    <cfRule type="expression" dxfId="9" priority="17">
+      <formula>Q6&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R6">
+    <cfRule type="expression" dxfId="8" priority="15">
+      <formula>R6&lt;R5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6">
+    <cfRule type="expression" dxfId="7" priority="5">
+      <formula>E6&lt;E5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC6">
+    <cfRule type="expression" dxfId="6" priority="10">
+      <formula>AC6&lt;AC5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA6">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>AA6&lt;AA5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA6">
+    <cfRule type="expression" dxfId="4" priority="8">
+      <formula>AA6&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD6">
+    <cfRule type="expression" dxfId="3" priority="7">
+      <formula>AD6&lt;AD5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U6">
+    <cfRule type="expression" dxfId="2" priority="9">
+      <formula>U6&lt;U5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ6:AJ11">
+    <cfRule type="expression" dxfId="1" priority="3">
+      <formula>AJ6&lt;AJ5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T6:W6 Z6 AB6 AE6:AI6">
+    <cfRule type="expression" dxfId="0" priority="12">
+      <formula>T6&lt;T5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.1" right="0.5" top="0.32" bottom="0.25" header="0.25" footer="0.25"/>
@@ -16064,15 +16685,16 @@
     <col min="3" max="3" width="24.140625" style="291" customWidth="1"/>
     <col min="4" max="4" width="27.28515625" style="291" customWidth="1"/>
     <col min="5" max="5" width="23.28515625" style="291" customWidth="1"/>
-    <col min="6" max="6" width="30.140625" style="291" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="36.42578125" style="291" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="35.5703125" style="291" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="30.140625" style="291" customWidth="1"/>
+    <col min="7" max="7" width="36.42578125" style="291" customWidth="1"/>
+    <col min="8" max="8" width="35.5703125" style="291" customWidth="1"/>
     <col min="9" max="9" width="23.7109375" style="291" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="22.140625" style="469" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="29.7109375" style="469" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="30.5703125" style="469" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="29.7109375" style="470" hidden="1" customWidth="1"/>
-    <col min="14" max="33" width="29.7109375" style="469" hidden="1" customWidth="1"/>
+    <col min="14" max="32" width="29.7109375" style="469" hidden="1" customWidth="1"/>
+    <col min="33" max="33" width="29.7109375" style="469" customWidth="1"/>
     <col min="34" max="34" width="29.7109375" style="468" customWidth="1"/>
     <col min="35" max="35" width="24.7109375" style="468" customWidth="1"/>
     <col min="36" max="36" width="24.7109375" style="291" customWidth="1"/>
@@ -16102,8 +16724,8 @@
       </c>
       <c r="B3" s="468"/>
       <c r="C3" s="468"/>
-      <c r="K3" s="896"/>
-      <c r="L3" s="896"/>
+      <c r="K3" s="895"/>
+      <c r="L3" s="895"/>
       <c r="M3" s="498"/>
       <c r="AH3" s="291"/>
       <c r="AI3" s="291"/>
@@ -16249,7 +16871,7 @@
         <v>31</v>
       </c>
       <c r="AG6" s="291"/>
-      <c r="AI6" s="895" t="s">
+      <c r="AI6" s="894" t="s">
         <v>216</v>
       </c>
     </row>
@@ -16354,7 +16976,7 @@
       <c r="AH7" s="477" t="s">
         <v>19</v>
       </c>
-      <c r="AI7" s="895"/>
+      <c r="AI7" s="894"/>
       <c r="AJ7" s="292" t="s">
         <v>229</v>
       </c>
@@ -16398,7 +17020,10 @@
       </c>
       <c r="D8" s="782"/>
       <c r="E8" s="678"/>
-      <c r="F8" s="678"/>
+      <c r="F8" s="678">
+        <f>4947</f>
+        <v>4947</v>
+      </c>
       <c r="G8" s="678"/>
       <c r="H8" s="678"/>
       <c r="I8" s="678"/>
@@ -16424,18 +17049,18 @@
       <c r="AC8" s="678"/>
       <c r="AD8" s="678"/>
       <c r="AE8" s="678"/>
-      <c r="AF8" s="891"/>
+      <c r="AF8" s="890"/>
       <c r="AG8" s="747"/>
       <c r="AH8" s="480">
         <f>SUM(B8:AG8)</f>
-        <v>9780</v>
+        <v>14727</v>
       </c>
       <c r="AI8" s="526">
         <v>123950</v>
       </c>
       <c r="AJ8" s="294">
         <f>AH8-AI8</f>
-        <v>-114170</v>
+        <v>-109223</v>
       </c>
       <c r="AK8" s="481"/>
       <c r="AL8" s="481"/>
@@ -16470,7 +17095,7 @@
         <v>367.56479999999999</v>
       </c>
       <c r="C9" s="678">
-        <f t="shared" ref="C9:E9" si="0">C8*0.066</f>
+        <f t="shared" ref="C9:F9" si="0">C8*0.066</f>
         <v>283.536</v>
       </c>
       <c r="D9" s="678">
@@ -16481,7 +17106,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F9" s="678"/>
+      <c r="F9" s="678">
+        <f t="shared" si="0"/>
+        <v>326.50200000000001</v>
+      </c>
       <c r="G9" s="678"/>
       <c r="H9" s="678">
         <f>H8*0.066</f>
@@ -16577,7 +17205,7 @@
       <c r="AG9" s="748"/>
       <c r="AH9" s="484">
         <f>SUM(B9:AG9)</f>
-        <v>651.10079999999994</v>
+        <v>977.60279999999989</v>
       </c>
       <c r="AI9" s="484"/>
       <c r="AL9" s="291" t="s">
@@ -16597,7 +17225,9 @@
       </c>
       <c r="D10" s="752"/>
       <c r="E10" s="800"/>
-      <c r="F10" s="681"/>
+      <c r="F10" s="774" t="s">
+        <v>307</v>
+      </c>
       <c r="G10" s="681"/>
       <c r="H10" s="875"/>
       <c r="I10" s="875"/>
@@ -16606,24 +17236,24 @@
       <c r="L10" s="875"/>
       <c r="M10" s="681"/>
       <c r="N10" s="681"/>
-      <c r="O10" s="883"/>
-      <c r="P10" s="883"/>
+      <c r="O10" s="882"/>
+      <c r="P10" s="882"/>
       <c r="Q10" s="875"/>
-      <c r="R10" s="884"/>
+      <c r="R10" s="883"/>
       <c r="S10" s="681"/>
       <c r="T10" s="681"/>
       <c r="U10" s="804"/>
       <c r="V10" s="800"/>
-      <c r="W10" s="886"/>
-      <c r="X10" s="886"/>
+      <c r="W10" s="885"/>
+      <c r="X10" s="885"/>
       <c r="Y10" s="875"/>
       <c r="Z10" s="875"/>
       <c r="AA10" s="800"/>
       <c r="AB10" s="805"/>
-      <c r="AC10" s="883"/>
-      <c r="AD10" s="883"/>
+      <c r="AC10" s="882"/>
+      <c r="AD10" s="882"/>
       <c r="AE10" s="875"/>
-      <c r="AF10" s="892"/>
+      <c r="AF10" s="891"/>
       <c r="AG10" s="749"/>
       <c r="AH10" s="487"/>
       <c r="AI10" s="487"/>
@@ -16893,8 +17523,8 @@
       <c r="Z13" s="669"/>
       <c r="AA13" s="669"/>
       <c r="AB13" s="798"/>
-      <c r="AC13" s="883"/>
-      <c r="AD13" s="890"/>
+      <c r="AC13" s="882"/>
+      <c r="AD13" s="889"/>
       <c r="AE13" s="682"/>
       <c r="AF13" s="682"/>
       <c r="AG13" s="685"/>
@@ -16990,7 +17620,7 @@
       <c r="AG15" s="718"/>
       <c r="AH15" s="500">
         <f>IF(AH12=0,"",+(AH36*10)/AH12)</f>
-        <v>7.0661672908863924</v>
+        <v>11.610486891385769</v>
       </c>
       <c r="AI15" s="502"/>
       <c r="AJ15" s="503"/>
@@ -17340,9 +17970,9 @@
         <f>+'Water '!$D10</f>
         <v>64</v>
       </c>
-      <c r="F20" s="508" t="str">
+      <c r="F20" s="508">
         <f>+'Water '!$D11</f>
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G20" s="508" t="str">
         <f>+'Water '!$D12</f>
@@ -17451,7 +18081,7 @@
       <c r="AG20" s="509"/>
       <c r="AH20" s="484">
         <f>SUM($B20:AF20)</f>
-        <v>251</v>
+        <v>324</v>
       </c>
       <c r="AI20" s="484"/>
       <c r="AJ20" s="485"/>
@@ -17476,9 +18106,9 @@
         <f>+'Water '!$E10</f>
         <v>0</v>
       </c>
-      <c r="F21" s="511" t="str">
+      <c r="F21" s="511">
         <f>+'Water '!$E11</f>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G21" s="511" t="str">
         <f>+'Water '!$E12</f>
@@ -17587,7 +18217,7 @@
       <c r="AG21" s="509"/>
       <c r="AH21" s="484">
         <f>SUM($B21:AF21)</f>
-        <v>487</v>
+        <v>556</v>
       </c>
       <c r="AI21" s="484"/>
     </row>
@@ -17613,7 +18243,7 @@
       </c>
       <c r="F22" s="514">
         <f t="shared" ref="F22:AF22" si="3">SUM(F19:F21)</f>
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="G22" s="514">
         <f t="shared" si="3"/>
@@ -17722,7 +18352,7 @@
       <c r="AG22" s="515"/>
       <c r="AH22" s="516">
         <f>SUM($B22:AF22)</f>
-        <v>738</v>
+        <v>880</v>
       </c>
       <c r="AI22" s="514"/>
       <c r="AJ22" s="517"/>
@@ -18090,11 +18720,11 @@
       </c>
       <c r="AI26" s="523">
         <f>AH29+AH45+AH36</f>
-        <v>854</v>
+        <v>1242</v>
       </c>
       <c r="AK26" s="524">
         <f>(AI26*10)/AH9</f>
-        <v>13.116248666873087</v>
+        <v>12.704546263574533</v>
       </c>
     </row>
     <row r="27" spans="1:149" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -18265,7 +18895,7 @@
       </c>
       <c r="F29" s="508">
         <f>'Water '!H11</f>
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="G29" s="508">
         <f>'Water '!H12</f>
@@ -18374,7 +19004,7 @@
       <c r="AG29" s="509"/>
       <c r="AH29" s="484">
         <f>SUM($B29:AF29)</f>
-        <v>531</v>
+        <v>717</v>
       </c>
       <c r="AI29" s="484"/>
       <c r="AJ29" s="484"/>
@@ -18400,9 +19030,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F30" s="508" t="str">
+      <c r="F30" s="508">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="G30" s="508" t="str">
         <f t="shared" si="5"/>
@@ -18511,7 +19141,7 @@
       <c r="AG30" s="509"/>
       <c r="AH30" s="484">
         <f>AH36</f>
-        <v>283</v>
+        <v>465</v>
       </c>
       <c r="AI30" s="484"/>
       <c r="AJ30" s="484"/>
@@ -18537,9 +19167,9 @@
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="F31" s="508" t="str">
+      <c r="F31" s="508">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G31" s="508" t="str">
         <f t="shared" si="6"/>
@@ -18648,7 +19278,7 @@
       <c r="AG31" s="509"/>
       <c r="AH31" s="484">
         <f>AH45</f>
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AI31" s="484"/>
       <c r="AJ31" s="484"/>
@@ -18675,7 +19305,7 @@
       </c>
       <c r="F32" s="526">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>388</v>
       </c>
       <c r="G32" s="526">
         <f t="shared" si="7"/>
@@ -18784,7 +19414,7 @@
       <c r="AG32" s="527"/>
       <c r="AH32" s="526">
         <f>SUM($B32:AF32)</f>
-        <v>854</v>
+        <v>1242</v>
       </c>
       <c r="AI32" s="526"/>
       <c r="AJ32" s="528"/>
@@ -18949,9 +19579,9 @@
         <f>+'Water '!$J10</f>
         <v>0</v>
       </c>
-      <c r="F36" s="535" t="str">
+      <c r="F36" s="535">
         <f>+'Water '!$J11</f>
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="G36" s="535" t="str">
         <f>+'Water '!$J12</f>
@@ -19060,7 +19690,7 @@
       <c r="AG36" s="508"/>
       <c r="AH36" s="484">
         <f>SUM($B36:AF36)</f>
-        <v>283</v>
+        <v>465</v>
       </c>
       <c r="AI36" s="484"/>
     </row>
@@ -19759,9 +20389,9 @@
         <f>+'Water '!$N10</f>
         <v>0</v>
       </c>
-      <c r="F41" s="539" t="str">
+      <c r="F41" s="539">
         <f>+'Water '!$N11</f>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G41" s="539" t="str">
         <f>+'Water '!$N12</f>
@@ -19870,7 +20500,7 @@
       <c r="AG41" s="539"/>
       <c r="AH41" s="514">
         <f>SUM($B41:AF41)</f>
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="AI41" s="514"/>
       <c r="AJ41" s="514"/>
@@ -20008,9 +20638,9 @@
         <f>+'Water '!$O10</f>
         <v>0</v>
       </c>
-      <c r="F42" s="508" t="str">
+      <c r="F42" s="508">
         <f>+'Water '!$O11</f>
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="G42" s="508" t="str">
         <f>+'Water '!$O12</f>
@@ -20119,7 +20749,7 @@
       <c r="AG42" s="508"/>
       <c r="AH42" s="540">
         <f>SUM($B42:AF42)</f>
-        <v>180</v>
+        <v>292</v>
       </c>
       <c r="AI42" s="508"/>
       <c r="AJ42" s="508"/>
@@ -20254,8 +20884,8 @@
       <c r="E43" s="541" t="str">
         <v>0</v>
       </c>
-      <c r="F43" s="542" t="str">
-        <v>0</v>
+      <c r="F43" s="542">
+        <v>17</v>
       </c>
       <c r="G43" s="542" t="str">
         <v>0</v>
@@ -20338,7 +20968,7 @@
       <c r="AG43" s="542"/>
       <c r="AH43" s="543">
         <f>SUM($B43:AF43)</f>
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="AI43" s="544"/>
       <c r="AJ43" s="474"/>
@@ -20476,9 +21106,9 @@
         <f>+'Water '!$M10</f>
         <v>0</v>
       </c>
-      <c r="F44" s="508" t="str">
+      <c r="F44" s="508">
         <f>+'Water '!$M11</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" s="508" t="str">
         <f>+'Water '!$M12</f>
@@ -20587,7 +21217,7 @@
       <c r="AG44" s="508"/>
       <c r="AH44" s="484">
         <f>SUM($B44:AF44)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI44" s="484"/>
       <c r="AJ44" s="291"/>
@@ -20725,9 +21355,9 @@
         <f>+'Water '!$Q10</f>
         <v>2</v>
       </c>
-      <c r="F45" s="539" t="str">
+      <c r="F45" s="539">
         <f>+'Water '!$Q11</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G45" s="539" t="str">
         <f>+'Water '!$Q12</f>
@@ -20836,7 +21466,7 @@
       <c r="AG45" s="539"/>
       <c r="AH45" s="514">
         <f>SUM($B45:AF45)</f>
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AI45" s="514"/>
       <c r="AJ45" s="514"/>
@@ -21442,7 +22072,7 @@
       </c>
       <c r="F50" s="484">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>370</v>
       </c>
       <c r="G50" s="484">
         <f>SUM(G36:G48)</f>
@@ -21551,7 +22181,7 @@
       <c r="AG50" s="484"/>
       <c r="AH50" s="484">
         <f>SUM($B50:AF50)</f>
-        <v>642</v>
+        <v>1012</v>
       </c>
       <c r="AI50" s="484"/>
     </row>
@@ -21663,9 +22293,9 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="F54" s="545" t="str">
+      <c r="F54" s="545">
         <f t="shared" si="9"/>
-        <v/>
+        <v>5.5742384426435363</v>
       </c>
       <c r="G54" s="545" t="str">
         <f>IF(G$9=0,"",+(G36*10)/G$9)</f>
@@ -21774,14 +22404,14 @@
       <c r="AG54" s="545"/>
       <c r="AH54" s="546">
         <f>+(AH36*10)/AH$9</f>
-        <v>4.3464852139637982</v>
+        <v>4.7565330213866002</v>
       </c>
       <c r="AI54" s="546">
         <v>3.2</v>
       </c>
       <c r="AJ54" s="547">
         <f t="shared" ref="AJ54:AJ67" si="11">AI54-AH54</f>
-        <v>-1.146485213963798</v>
+        <v>-1.5565330213866</v>
       </c>
     </row>
     <row r="55" spans="1:59" s="553" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -21875,9 +22505,9 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="F56" s="545" t="str">
+      <c r="F56" s="545">
         <f t="shared" si="14"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G56" s="545" t="str">
         <f t="shared" ref="G56:H63" si="15">IF(G$9=0,"",+(G38*10)/G$9)</f>
@@ -22039,9 +22669,9 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="F57" s="549" t="str">
+      <c r="F57" s="549">
         <f t="shared" si="14"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G57" s="549" t="str">
         <f t="shared" si="15"/>
@@ -22203,9 +22833,9 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="F58" s="545" t="str">
+      <c r="F58" s="545">
         <f t="shared" si="14"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G58" s="545" t="str">
         <f t="shared" si="15"/>
@@ -22369,9 +22999,9 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="F59" s="549" t="str">
+      <c r="F59" s="549">
         <f t="shared" si="14"/>
-        <v/>
+        <v>1.1638519825299691</v>
       </c>
       <c r="G59" s="549" t="str">
         <f t="shared" si="15"/>
@@ -22480,14 +23110,14 @@
       <c r="AG59" s="549"/>
       <c r="AH59" s="549">
         <f t="shared" si="12"/>
-        <v>1.5819363146228664</v>
+        <v>1.4423035613236788</v>
       </c>
       <c r="AI59" s="550">
         <v>0.7</v>
       </c>
       <c r="AJ59" s="551">
         <f t="shared" si="11"/>
-        <v>-0.88193631462286648</v>
+        <v>-0.74230356132367881</v>
       </c>
       <c r="AK59" s="474"/>
       <c r="AL59" s="474"/>
@@ -22533,9 +23163,9 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="F60" s="567" t="str">
+      <c r="F60" s="567">
         <f t="shared" si="14"/>
-        <v/>
+        <v>3.4303005800883302</v>
       </c>
       <c r="G60" s="545" t="str">
         <f t="shared" si="15"/>
@@ -22644,14 +23274,14 @@
       <c r="AG60" s="545"/>
       <c r="AH60" s="568">
         <f t="shared" si="12"/>
-        <v>2.764548899340932</v>
+        <v>2.9868981553653491</v>
       </c>
       <c r="AI60" s="555">
         <v>2.1</v>
       </c>
       <c r="AJ60" s="547">
         <f t="shared" si="11"/>
-        <v>-0.66454889934093186</v>
+        <v>-0.88689815536534899</v>
       </c>
     </row>
     <row r="61" spans="1:59" s="504" customFormat="1" x14ac:dyDescent="0.35">
@@ -22674,9 +23304,9 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="F61" s="549" t="str">
+      <c r="F61" s="549">
         <f t="shared" si="14"/>
-        <v/>
+        <v>0.52067062376340723</v>
       </c>
       <c r="G61" s="549" t="str">
         <f t="shared" si="15"/>
@@ -22785,14 +23415,14 @@
       <c r="AG61" s="549"/>
       <c r="AH61" s="550">
         <f t="shared" si="12"/>
-        <v>0.4761167548864938</v>
+        <v>0.49099695704635876</v>
       </c>
       <c r="AI61" s="550">
         <v>0.7</v>
       </c>
       <c r="AJ61" s="551">
         <f t="shared" si="11"/>
-        <v>0.22388324511350616</v>
+        <v>0.20900304295364119</v>
       </c>
       <c r="AK61" s="474"/>
       <c r="AL61" s="474"/>
@@ -22838,9 +23468,9 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="F62" s="545" t="str">
+      <c r="F62" s="545">
         <f t="shared" si="14"/>
-        <v/>
+        <v>3.0627683750788663E-2</v>
       </c>
       <c r="G62" s="545" t="str">
         <f t="shared" si="15"/>
@@ -22949,14 +23579,14 @@
       <c r="AG62" s="545"/>
       <c r="AH62" s="555">
         <f>+(AH44*10)/AH$9</f>
-        <v>7.6793024981692548E-2</v>
+        <v>6.1374619630794845E-2</v>
       </c>
       <c r="AI62" s="555">
         <v>0.1</v>
       </c>
       <c r="AJ62" s="547">
         <f t="shared" si="11"/>
-        <v>2.3206975018307457E-2</v>
+        <v>3.862538036920516E-2</v>
       </c>
     </row>
     <row r="63" spans="1:59" s="504" customFormat="1" x14ac:dyDescent="0.35">
@@ -22979,9 +23609,9 @@
         <f t="shared" ref="E63:AF63" si="25">IF(E$9=0,"",+(E45*10)/E$9)</f>
         <v/>
       </c>
-      <c r="F63" s="569" t="str">
+      <c r="F63" s="569">
         <f t="shared" si="25"/>
-        <v/>
+        <v>0.61255367501577329</v>
       </c>
       <c r="G63" s="569" t="str">
         <f t="shared" si="15"/>
@@ -23090,14 +23720,14 @@
       <c r="AG63" s="549"/>
       <c r="AH63" s="550">
         <f>+(AH45*10)/AH$9</f>
-        <v>0.61434419985354038</v>
+        <v>0.61374619630794847</v>
       </c>
       <c r="AI63" s="550">
         <v>0.6</v>
       </c>
       <c r="AJ63" s="551">
         <f t="shared" si="11"/>
-        <v>-1.4344199853540407E-2</v>
+        <v>-1.3746196307948488E-2</v>
       </c>
       <c r="AK63" s="474"/>
       <c r="AL63" s="474"/>
@@ -23211,9 +23841,9 @@
         <f t="shared" ref="E65:AF65" si="26">IF(E$9=0,"",+(E46*10)/E$9)</f>
         <v/>
       </c>
-      <c r="F65" s="575" t="str">
+      <c r="F65" s="575">
         <f t="shared" si="26"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G65" s="575" t="str">
         <f>IF(G$9=0,"",+(G46*10)/G$9)</f>
@@ -23513,7 +24143,7 @@
       </c>
       <c r="F68" s="584">
         <f t="shared" ref="F68:AJ68" si="27">SUM(F54:F63,F65)</f>
-        <v>0</v>
+        <v>11.332242987791805</v>
       </c>
       <c r="G68" s="584">
         <f t="shared" si="27"/>
@@ -23622,7 +24252,7 @@
       <c r="AG68" s="585"/>
       <c r="AH68" s="584">
         <f t="shared" si="27"/>
-        <v>9.8602244076493228</v>
+        <v>10.351852511060731</v>
       </c>
       <c r="AI68" s="584">
         <f>SUM(AI54:AI63,AI65)</f>
@@ -23630,7 +24260,7 @@
       </c>
       <c r="AJ68" s="547">
         <f t="shared" si="27"/>
-        <v>-0.26022440764932314</v>
+        <v>-0.75185251106072992</v>
       </c>
       <c r="AK68" s="468"/>
       <c r="AL68" s="291"/>
@@ -23678,7 +24308,7 @@
       </c>
       <c r="F69" s="587">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>3.9815988876025261</v>
       </c>
       <c r="G69" s="587">
         <f t="shared" si="28"/>
@@ -23787,7 +24417,7 @@
       <c r="AG69" s="588"/>
       <c r="AH69" s="587">
         <f t="shared" si="28"/>
-        <v>3.3174586792091185</v>
+        <v>3.5392697320425026</v>
       </c>
       <c r="AI69" s="587">
         <f t="shared" si="28"/>
@@ -23795,7 +24425,7 @@
       </c>
       <c r="AJ69" s="587">
         <f t="shared" si="28"/>
-        <v>-0.41745867920911828</v>
+        <v>-0.6392697320425027</v>
       </c>
       <c r="AK69" s="589"/>
       <c r="AL69" s="291"/>
@@ -24099,46 +24729,48 @@
       <c r="B74" s="795">
         <v>1600</v>
       </c>
-      <c r="C74" s="893">
+      <c r="C74" s="892">
         <v>1142</v>
       </c>
-      <c r="D74" s="882">
-        <v>0</v>
-      </c>
-      <c r="E74" s="882">
-        <v>0</v>
-      </c>
-      <c r="F74" s="878"/>
+      <c r="D74" s="881">
+        <v>0</v>
+      </c>
+      <c r="E74" s="881">
+        <v>0</v>
+      </c>
+      <c r="F74" s="794">
+        <v>1583</v>
+      </c>
       <c r="G74" s="794"/>
       <c r="H74" s="794"/>
       <c r="I74" s="794"/>
       <c r="J74" s="795"/>
-      <c r="K74" s="882"/>
-      <c r="L74" s="882"/>
-      <c r="M74" s="882"/>
-      <c r="N74" s="882"/>
-      <c r="O74" s="882"/>
-      <c r="P74" s="882"/>
+      <c r="K74" s="881"/>
+      <c r="L74" s="881"/>
+      <c r="M74" s="881"/>
+      <c r="N74" s="881"/>
+      <c r="O74" s="881"/>
+      <c r="P74" s="881"/>
       <c r="Q74" s="795"/>
-      <c r="R74" s="882"/>
+      <c r="R74" s="881"/>
       <c r="S74" s="794"/>
       <c r="T74" s="794"/>
       <c r="U74" s="794"/>
       <c r="V74" s="794"/>
-      <c r="W74" s="888"/>
-      <c r="X74" s="882"/>
-      <c r="Y74" s="882"/>
-      <c r="Z74" s="882"/>
-      <c r="AA74" s="882"/>
-      <c r="AB74" s="882"/>
-      <c r="AC74" s="882"/>
-      <c r="AD74" s="882"/>
-      <c r="AE74" s="882"/>
-      <c r="AF74" s="882"/>
+      <c r="W74" s="887"/>
+      <c r="X74" s="881"/>
+      <c r="Y74" s="881"/>
+      <c r="Z74" s="881"/>
+      <c r="AA74" s="881"/>
+      <c r="AB74" s="881"/>
+      <c r="AC74" s="881"/>
+      <c r="AD74" s="881"/>
+      <c r="AE74" s="881"/>
+      <c r="AF74" s="881"/>
       <c r="AG74" s="794"/>
       <c r="AH74" s="516">
         <f>SUM(B74:AF74)</f>
-        <v>2742</v>
+        <v>4325</v>
       </c>
       <c r="AI74" s="537"/>
       <c r="AJ74" s="537"/>
@@ -24183,8 +24815,8 @@
       <c r="E75" s="601" t="str">
         <v>0</v>
       </c>
-      <c r="F75" s="601" t="str">
-        <v>0</v>
+      <c r="F75" s="601">
+        <v>1583.3100000000559</v>
       </c>
       <c r="G75" s="601" t="str">
         <v>0</v>
@@ -24267,7 +24899,7 @@
       <c r="AG75" s="599"/>
       <c r="AH75" s="516">
         <f>SUM(B75:AF75)</f>
-        <v>2721.0999999999767</v>
+        <v>4304.4100000000326</v>
       </c>
       <c r="AI75" s="600"/>
       <c r="AJ75" s="600"/>
@@ -24311,8 +24943,8 @@
       <c r="E76" s="604" t="str">
         <v>0</v>
       </c>
-      <c r="F76" s="604" t="str">
-        <v>0</v>
+      <c r="F76" s="604">
+        <v>178.82000000000698</v>
       </c>
       <c r="G76" s="604" t="str">
         <v>0</v>
@@ -24395,7 +25027,7 @@
       <c r="AG76" s="604"/>
       <c r="AH76" s="604">
         <f>SUM($B76:AF76)</f>
-        <v>340.44000000000233</v>
+        <v>519.26000000000931</v>
       </c>
       <c r="AI76" s="605"/>
       <c r="AJ76" s="606"/>
@@ -24440,8 +25072,8 @@
       <c r="E77" s="789" t="str">
         <v>0</v>
       </c>
-      <c r="F77" s="789" t="str">
-        <v>0</v>
+      <c r="F77" s="789">
+        <v>407.7899999999936</v>
       </c>
       <c r="G77" s="789" t="str">
         <v>0</v>
@@ -24524,7 +25156,7 @@
       <c r="AG77" s="607"/>
       <c r="AH77" s="604">
         <f>SUM($B77:AF77)</f>
-        <v>1039.5400000000081</v>
+        <v>1447.3300000000017</v>
       </c>
       <c r="AI77" s="757"/>
       <c r="AJ77" s="757" t="s">
@@ -24575,7 +25207,7 @@
       </c>
       <c r="F78" s="792">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>996.7000000000553</v>
       </c>
       <c r="G78" s="792">
         <f t="shared" si="29"/>
@@ -24641,7 +25273,7 @@
         <f>V75-V76-V77</f>
         <v>0</v>
       </c>
-      <c r="W78" s="887">
+      <c r="W78" s="886">
         <f t="shared" ref="W78:AB78" si="30">W75-W76-W77</f>
         <v>0</v>
       </c>
@@ -24687,7 +25319,7 @@
       </c>
       <c r="AH78" s="484">
         <f>AH75-AH76-AH77</f>
-        <v>1341.1199999999662</v>
+        <v>2337.8200000000215</v>
       </c>
       <c r="AI78" s="484"/>
     </row>
@@ -24713,7 +25345,7 @@
       </c>
       <c r="F79" s="609">
         <f>'Daily KPIs CO2'!F47</f>
-        <v>0</v>
+        <v>1583.3100000000559</v>
       </c>
       <c r="G79" s="609" t="e">
         <f>'Daily KPIs CO2'!G47</f>
@@ -24838,7 +25470,7 @@
         <v>4062</v>
       </c>
       <c r="F80" s="612">
-        <v>0</v>
+        <v>4774</v>
       </c>
       <c r="G80" s="612">
         <v>0</v>
@@ -24921,7 +25553,7 @@
       <c r="AG80" s="613"/>
       <c r="AH80" s="594">
         <f>SUM(B80:AF80)</f>
-        <v>22292</v>
+        <v>27066</v>
       </c>
       <c r="AI80" s="594"/>
       <c r="AJ80" s="614"/>
@@ -25028,7 +25660,7 @@
         <v>4756.6000000000004</v>
       </c>
       <c r="D82" s="614">
-        <v>0</v>
+        <v>6195</v>
       </c>
       <c r="E82" s="614">
         <v>0</v>
@@ -25109,7 +25741,7 @@
         <v>0</v>
       </c>
       <c r="AE82" s="617">
-        <v>26416.699999999997</v>
+        <v>32611.699999999997</v>
       </c>
       <c r="AF82" s="617">
         <v>0</v>
@@ -25117,7 +25749,7 @@
       <c r="AG82" s="617"/>
       <c r="AH82" s="594">
         <f>SUM(B82:AF82)</f>
-        <v>35746.6</v>
+        <v>48136.6</v>
       </c>
       <c r="AI82" s="594"/>
       <c r="AJ82" s="614"/>
@@ -25163,7 +25795,7 @@
         <v>694.6</v>
       </c>
       <c r="F83" s="594">
-        <v>0</v>
+        <v>1421</v>
       </c>
       <c r="G83" s="594">
         <v>0</v>
@@ -25246,7 +25878,7 @@
       <c r="AG83" s="621"/>
       <c r="AH83" s="594">
         <f>SUM(B83:AF83)</f>
-        <v>4124.7000000000007</v>
+        <v>5545.7000000000007</v>
       </c>
       <c r="AI83" s="594"/>
       <c r="AJ83" s="594"/>
@@ -25278,134 +25910,104 @@
       <c r="A84" s="596" t="s">
         <v>130</v>
       </c>
-      <c r="B84" s="619">
-        <f>+'Fuel '!$K7</f>
-        <v>960</v>
+      <c r="B84" s="619" cm="1">
+        <f t="array" ref="B84:AF84">TRANSPOSE('Fuel '!D7:D37)</f>
+        <v>3317.1999999999534</v>
       </c>
       <c r="C84" s="619">
-        <f>+'Fuel '!$K8</f>
-        <v>0</v>
+        <v>2235.1000000000931</v>
       </c>
       <c r="D84" s="619">
-        <f>+'Fuel '!$K9</f>
-        <v>0</v>
+        <v>238.30000000004657</v>
       </c>
       <c r="E84" s="619">
-        <f>+'Fuel '!$K10</f>
-        <v>0</v>
+        <v>334.89999999990687</v>
       </c>
       <c r="F84" s="619">
-        <f>+'Fuel '!$K11</f>
-        <v>0</v>
-      </c>
-      <c r="G84" s="619">
-        <f>+'Fuel '!$K12</f>
-        <v>0</v>
-      </c>
-      <c r="H84" s="619">
-        <f>+'Fuel '!$K13</f>
-        <v>0</v>
-      </c>
-      <c r="I84" s="619">
-        <f>+'Fuel '!$K14</f>
-        <v>0</v>
-      </c>
-      <c r="J84" s="620">
-        <f>+'Fuel '!$K15</f>
-        <v>0</v>
-      </c>
-      <c r="K84" s="620">
-        <f>+'Fuel '!$K16</f>
-        <v>0</v>
-      </c>
-      <c r="L84" s="620">
-        <f>+'Fuel '!$K17</f>
-        <v>0</v>
-      </c>
-      <c r="M84" s="620">
-        <f>+'Fuel '!$K18</f>
-        <v>0</v>
-      </c>
-      <c r="N84" s="620">
-        <f>+'Fuel '!$K19</f>
-        <v>0</v>
-      </c>
-      <c r="O84" s="620">
-        <f>+'Fuel '!$K20</f>
-        <v>0</v>
-      </c>
-      <c r="P84" s="620">
-        <f>+'Fuel '!$K21</f>
-        <v>0</v>
-      </c>
-      <c r="Q84" s="620">
-        <f>+'Fuel '!$K22</f>
-        <v>0</v>
-      </c>
-      <c r="R84" s="620">
-        <f>+'Fuel '!$K23</f>
-        <v>0</v>
-      </c>
-      <c r="S84" s="620">
-        <f>+'Fuel '!$K24</f>
-        <v>0</v>
-      </c>
-      <c r="T84" s="620">
-        <f>+'Fuel '!$K25</f>
-        <v>0</v>
-      </c>
-      <c r="U84" s="620">
-        <f>+'Fuel '!$K26</f>
-        <v>0</v>
-      </c>
-      <c r="V84" s="620">
-        <f>+'Fuel '!$K27</f>
-        <v>0</v>
-      </c>
-      <c r="W84" s="620">
-        <f>+'Fuel '!$K28</f>
-        <v>0</v>
-      </c>
-      <c r="X84" s="620">
-        <f>+'Fuel '!$K29</f>
-        <v>0</v>
-      </c>
-      <c r="Y84" s="620">
-        <f>+'Fuel '!$K30</f>
-        <v>0</v>
-      </c>
-      <c r="Z84" s="620">
-        <f>+'Fuel '!$K31</f>
-        <v>0</v>
-      </c>
-      <c r="AA84" s="620">
-        <f>+'Fuel '!$K32</f>
-        <v>0</v>
-      </c>
-      <c r="AB84" s="620">
-        <f>+'Fuel '!$K33</f>
-        <v>0</v>
-      </c>
-      <c r="AC84" s="620">
-        <f>+'Fuel '!$K34</f>
-        <v>0</v>
-      </c>
-      <c r="AD84" s="620">
-        <f>+'Fuel '!$K35</f>
-        <v>0</v>
-      </c>
-      <c r="AE84" s="620">
-        <f>+'Fuel '!$K36</f>
-        <v>0</v>
-      </c>
-      <c r="AF84" s="620">
-        <f>+'Fuel '!$K37</f>
+        <v>3351.6000000000931</v>
+      </c>
+      <c r="G84" s="619" t="str">
+        <v>0</v>
+      </c>
+      <c r="H84" s="619" t="str">
+        <v>0</v>
+      </c>
+      <c r="I84" s="619" t="str">
+        <v>0</v>
+      </c>
+      <c r="J84" s="620" t="str">
+        <v>0</v>
+      </c>
+      <c r="K84" s="620" t="str">
+        <v>0</v>
+      </c>
+      <c r="L84" s="620" t="str">
+        <v>0</v>
+      </c>
+      <c r="M84" s="620" t="str">
+        <v>0</v>
+      </c>
+      <c r="N84" s="620" t="str">
+        <v>0</v>
+      </c>
+      <c r="O84" s="620" t="str">
+        <v>0</v>
+      </c>
+      <c r="P84" s="620" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="620" t="str">
+        <v>0</v>
+      </c>
+      <c r="R84" s="620" t="str">
+        <v>0</v>
+      </c>
+      <c r="S84" s="620" t="str">
+        <v>0</v>
+      </c>
+      <c r="T84" s="620" t="str">
+        <v>0</v>
+      </c>
+      <c r="U84" s="620" t="str">
+        <v>0</v>
+      </c>
+      <c r="V84" s="620" t="str">
+        <v>0</v>
+      </c>
+      <c r="W84" s="620" t="str">
+        <v>0</v>
+      </c>
+      <c r="X84" s="620" t="str">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="620" t="str">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="620" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="620" t="str">
+        <v>0</v>
+      </c>
+      <c r="AB84" s="620" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="620" t="str">
+        <v>0</v>
+      </c>
+      <c r="AD84" s="620" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="620" t="str">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="620" t="str">
         <v>0</v>
       </c>
       <c r="AG84" s="620"/>
       <c r="AH84" s="621">
         <f>SUM($B84:AF84)</f>
-        <v>960</v>
+        <v>9477.1000000000931</v>
       </c>
       <c r="AI84" s="594"/>
       <c r="AJ84" s="614"/>
@@ -25798,9 +26400,9 @@
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="F90" s="653" t="str">
+      <c r="F90" s="653">
         <f t="shared" si="33"/>
-        <v/>
+        <v>4.3491310926119899</v>
       </c>
       <c r="G90" s="653" t="str">
         <f>IF(G$9=0,"",+(G22*10)/G$9)</f>
@@ -25909,18 +26511,18 @@
       <c r="AG90" s="627"/>
       <c r="AH90" s="659">
         <f>IF(AH$9=0,"0",+(AH22*10)/AH$9)</f>
-        <v>11.33465048729782</v>
+        <v>9.0016108791832448</v>
       </c>
       <c r="AI90" s="662">
         <v>10.199999999999999</v>
       </c>
       <c r="AJ90" s="665">
         <f>+AI90-AH90</f>
-        <v>-1.1346504872978205</v>
+        <v>1.1983891208167545</v>
       </c>
       <c r="AK90" s="667">
         <f>AH90/AI90*100</f>
-        <v>111.12402438527276</v>
+        <v>88.251087050816139</v>
       </c>
       <c r="AL90" s="629"/>
       <c r="AM90" s="630"/>
@@ -26032,9 +26634,9 @@
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F92" s="653" t="str">
+      <c r="F92" s="653">
         <f t="shared" si="35"/>
-        <v/>
+        <v>4.8483623377498448</v>
       </c>
       <c r="G92" s="653" t="str">
         <f>IF(G$9=0,"",+G74/G$9)</f>
@@ -26143,18 +26745,18 @@
       <c r="AG92" s="628"/>
       <c r="AH92" s="670">
         <f>IF(AH$9=0,"0",+(AH74)/AH$9)</f>
-        <v>4.2113294899960199</v>
+        <v>4.4240871650531286</v>
       </c>
       <c r="AI92" s="674">
         <v>5</v>
       </c>
       <c r="AJ92" s="675">
         <f>AI92-AH92</f>
-        <v>0.78867051000398014</v>
+        <v>0.5759128349468714</v>
       </c>
       <c r="AK92" s="673">
         <f t="shared" si="34"/>
-        <v>84.22658979992039</v>
+        <v>88.481743301062579</v>
       </c>
       <c r="AL92" s="629"/>
       <c r="AM92" s="630"/>
@@ -26201,9 +26803,9 @@
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="F93" s="653" t="str">
+      <c r="F93" s="653">
         <f t="shared" si="36"/>
-        <v/>
+        <v>0.54768424083162426</v>
       </c>
       <c r="G93" s="653" t="str">
         <f>IF(G$9=0,"",+G76/G$9)</f>
@@ -26312,18 +26914,18 @@
       <c r="AG93" s="628"/>
       <c r="AH93" s="670">
         <f>IF(AH$9=0,"0",+AH76/AH$9)</f>
-        <v>0.5228683484953518</v>
+        <v>0.53115641649145173</v>
       </c>
       <c r="AI93" s="674">
         <v>1.7</v>
       </c>
       <c r="AJ93" s="676">
         <f>AI93-AH93</f>
-        <v>1.1771316515046482</v>
+        <v>1.1688435835085482</v>
       </c>
       <c r="AK93" s="673">
         <f t="shared" si="34"/>
-        <v>30.756961676197164</v>
+        <v>31.244495087732453</v>
       </c>
       <c r="AL93" s="635"/>
       <c r="AM93" s="636"/>
@@ -26368,9 +26970,9 @@
         <f t="shared" ref="E94:AF94" si="37">IF(E$9=0,"",(E80+E83)/E$9)</f>
         <v/>
       </c>
-      <c r="F94" s="653" t="str">
+      <c r="F94" s="653">
         <f t="shared" si="37"/>
-        <v/>
+        <v>18.973850083613577</v>
       </c>
       <c r="G94" s="653" t="str">
         <f>IF(G$9=0,"",(G80+G83)/G$9)</f>
@@ -26479,18 +27081,18 @@
       <c r="AG94" s="627"/>
       <c r="AH94" s="670">
         <f>IF(AH$9=0,"0",+(AH80+AH83)/AH$9)</f>
-        <v>40.572366060677552</v>
+        <v>33.358844716893202</v>
       </c>
       <c r="AI94" s="674">
         <v>22</v>
       </c>
       <c r="AJ94" s="675">
         <f>AI94-AH94</f>
-        <v>-18.572366060677552</v>
+        <v>-11.358844716893202</v>
       </c>
       <c r="AK94" s="673">
         <f>AH94/AI94*100</f>
-        <v>184.41984573035251</v>
+        <v>151.63111234951455</v>
       </c>
       <c r="AL94" s="629"/>
       <c r="AM94" s="630"/>
@@ -26550,7 +27152,7 @@
       <c r="AG95" s="637"/>
       <c r="AH95" s="670">
         <f>IF(AH$9=0,"0",+(AH78*10)/AH$9)</f>
-        <v>20.597732332688985</v>
+        <v>23.913802210877687</v>
       </c>
       <c r="AI95" s="674"/>
       <c r="AJ95" s="676"/>
@@ -26587,11 +27189,11 @@
       </c>
       <c r="B96" s="653">
         <f t="shared" ref="B96:I96" si="38">IF(B$9=0,"",B84/B$9)</f>
-        <v>2.6117843710823236</v>
+        <v>9.0248032455772513</v>
       </c>
       <c r="C96" s="653">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>7.8829496078102714</v>
       </c>
       <c r="D96" s="654" t="str">
         <f t="shared" si="38"/>
@@ -26601,9 +27203,9 @@
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="F96" s="653" t="str">
+      <c r="F96" s="653">
         <f t="shared" si="38"/>
-        <v/>
+        <v>10.265174485914613</v>
       </c>
       <c r="G96" s="653" t="str">
         <f>IF(G$9=0,"",G84/G$9)</f>
@@ -26712,18 +27314,18 @@
       <c r="AG96" s="627"/>
       <c r="AH96" s="660">
         <f>IF(AH$9=0,"0",+(AH84)/AH$9)</f>
-        <v>1.4744260796484969</v>
+        <v>9.6942234617168594</v>
       </c>
       <c r="AI96" s="663">
         <v>7.2</v>
       </c>
       <c r="AJ96" s="677">
         <f>AI96-AH96</f>
-        <v>5.7255739203515033</v>
+        <v>-2.4942234617168593</v>
       </c>
       <c r="AK96" s="668">
         <f t="shared" si="34"/>
-        <v>20.47813999511801</v>
+        <v>134.64199252384529</v>
       </c>
       <c r="AL96" s="629"/>
       <c r="AM96" s="630"/>
@@ -27195,7 +27797,7 @@
       </c>
       <c r="F103" s="649">
         <f>IF('Entries October 2026'!L11-'Entries October 2026'!L10&lt;1,0,'Entries October 2026'!L11-'Entries October 2026'!L10)</f>
-        <v>0</v>
+        <v>407.7899999999936</v>
       </c>
       <c r="G103" s="649">
         <f>IF('Entries October 2026'!L12-'Entries October 2026'!L11&lt;1,0,'Entries October 2026'!L12-'Entries October 2026'!L11)</f>
@@ -27341,9 +27943,9 @@
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="F105" s="651" t="str">
+      <c r="F105" s="651">
         <f t="shared" si="41"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G105" s="651" t="s">
         <v>55</v>
@@ -27658,7 +28260,7 @@
       </c>
       <c r="F116" s="649">
         <f>'Daily KPIs'!F80</f>
-        <v>0</v>
+        <v>4774</v>
       </c>
       <c r="G116" s="649">
         <f>'Daily KPIs'!G80</f>
@@ -27767,7 +28369,7 @@
       <c r="AG116" s="650"/>
       <c r="AH116" s="649">
         <f>'Daily KPIs'!AH80</f>
-        <v>22292</v>
+        <v>27066</v>
       </c>
     </row>
     <row r="117" spans="2:34" hidden="1" x14ac:dyDescent="0.35">
@@ -27857,7 +28459,7 @@
       </c>
       <c r="AH140" s="874">
         <f>AH83/(AH83+AH80)</f>
-        <v>0.15613986606956964</v>
+        <v>0.17005246583281461</v>
       </c>
       <c r="AM140" s="751"/>
     </row>
@@ -27994,45 +28596,45 @@
   </mergeCells>
   <phoneticPr fontId="32" type="noConversion"/>
   <conditionalFormatting sqref="B93:C93 AH93">
-    <cfRule type="cellIs" dxfId="35" priority="127" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="78" priority="127" operator="greaterThan">
       <formula>$AI$93</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B90:AF90">
-    <cfRule type="cellIs" dxfId="34" priority="36" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="77" priority="36" operator="greaterThan">
       <formula>10.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92:AF92">
-    <cfRule type="cellIs" dxfId="33" priority="26" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="76" priority="26" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="27" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="75" priority="27" operator="lessThanOrEqual">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:AF93">
-    <cfRule type="cellIs" dxfId="31" priority="34" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="74" priority="34" operator="greaterThan">
       <formula>1.7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B94:AF94">
-    <cfRule type="cellIs" dxfId="30" priority="33" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="73" priority="33" operator="greaterThan">
       <formula>22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96:AF96">
-    <cfRule type="cellIs" dxfId="29" priority="32" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="72" priority="32" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:AG22">
-    <cfRule type="cellIs" dxfId="28" priority="101" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="71" priority="101" operator="greaterThan">
       <formula>400</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42:AG42">
-    <cfRule type="cellIs" dxfId="27" priority="47" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="70" priority="47" operator="greaterThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28047,129 +28649,129 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B94:AG94">
-    <cfRule type="cellIs" dxfId="26" priority="1174" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="69" priority="1174" operator="greaterThan">
       <formula>$AI$94</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96:AG96">
-    <cfRule type="cellIs" dxfId="25" priority="1176" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="68" priority="1176" operator="greaterThan">
       <formula>$AI$96</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:AH15">
-    <cfRule type="cellIs" dxfId="24" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="67" priority="1" operator="greaterThan">
       <formula>3.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54:AH54">
-    <cfRule type="cellIs" dxfId="23" priority="123" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="66" priority="123" operator="greaterThan">
       <formula>3.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B56:AH56">
-    <cfRule type="cellIs" dxfId="22" priority="61" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="65" priority="61" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B57:AH57 B59:AH59 B61:AH61">
-    <cfRule type="cellIs" dxfId="21" priority="62" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="64" priority="62" operator="greaterThan">
       <formula>0.7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58:AH58 B62:AH62">
-    <cfRule type="cellIs" dxfId="20" priority="63" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="63" priority="63" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B60:AH60">
-    <cfRule type="cellIs" dxfId="19" priority="22" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="62" priority="22" operator="greaterThan">
       <formula>2.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B65:AH65">
-    <cfRule type="cellIs" dxfId="18" priority="56" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="61" priority="56" operator="greaterThan">
       <formula>0.3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68:AH68">
-    <cfRule type="cellIs" dxfId="17" priority="58" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="60" priority="58" operator="greaterThan">
       <formula>9.6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69:AH69">
-    <cfRule type="cellIs" dxfId="16" priority="59" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="59" priority="59" operator="greaterThan">
       <formula>2.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92:AH92">
-    <cfRule type="cellIs" dxfId="15" priority="48" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="48" operator="greaterThan">
       <formula>5.04</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:AH93">
-    <cfRule type="cellIs" dxfId="14" priority="44" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="57" priority="44" operator="greaterThan">
       <formula>1.7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="43" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="56" priority="43" operator="greaterThan">
       <formula>1.7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96:AH96">
-    <cfRule type="cellIs" dxfId="12" priority="37" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="55" priority="37" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E96">
-    <cfRule type="cellIs" dxfId="11" priority="39" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="54" priority="39" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I63:AH63">
-    <cfRule type="cellIs" dxfId="10" priority="68" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="53" priority="68" operator="greaterThan">
       <formula>0.6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC54:AG54">
-    <cfRule type="cellIs" dxfId="9" priority="82" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="52" priority="82" operator="greaterThan">
       <formula>$AI$54</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC55:AG59 AC61:AG61 AC63:AG63 B64:AG64">
-    <cfRule type="cellIs" dxfId="8" priority="1135" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="51" priority="1135" operator="greaterThan">
       <formula>$AI59</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH94">
-    <cfRule type="cellIs" dxfId="7" priority="28" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="50" priority="28" operator="lessThanOrEqual">
       <formula>22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH94:AH96 B90:AH90 AH91">
-    <cfRule type="cellIs" dxfId="6" priority="1168" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="49" priority="1168" operator="greaterThan">
       <formula>$AI$90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH96">
-    <cfRule type="cellIs" dxfId="5" priority="29" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="48" priority="29" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="30" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="30" operator="lessThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="40" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="46" priority="40" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ8">
-    <cfRule type="cellIs" dxfId="2" priority="105" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="45" priority="105" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="106" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="106" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK90:AK96">
-    <cfRule type="cellIs" dxfId="0" priority="50" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="43" priority="50" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28676,11 +29278,11 @@
       </c>
       <c r="C11" s="55">
         <f t="shared" si="1"/>
-        <v>-253245</v>
+        <v>73</v>
       </c>
       <c r="D11" s="55">
         <f t="shared" si="2"/>
-        <v>1113364</v>
+        <v>73</v>
       </c>
       <c r="E11" s="56">
         <f>'Entries October 2026'!W10</f>
@@ -28692,7 +29294,7 @@
       </c>
       <c r="G11" s="57">
         <f t="shared" si="7"/>
-        <v>-1366609</v>
+        <v>0</v>
       </c>
       <c r="H11" s="57">
         <f>'Entries October 2026'!AA10</f>
@@ -28700,7 +29302,7 @@
       </c>
       <c r="I11" s="58">
         <f t="shared" si="3"/>
-        <v>-97122</v>
+        <v>0</v>
       </c>
       <c r="J11" s="57">
         <f>'Entries October 2026'!T10</f>
@@ -28712,7 +29314,7 @@
       </c>
       <c r="L11" s="58">
         <f t="shared" si="6"/>
-        <v>-97122</v>
+        <v>0</v>
       </c>
       <c r="M11" s="57">
         <f>'Entries October 2026'!R10</f>
@@ -28720,11 +29322,11 @@
       </c>
       <c r="N11" s="57">
         <f>'Entries October 2026'!AC11-'Entries October 2026'!AC10</f>
-        <v>-6781</v>
+        <v>17</v>
       </c>
       <c r="O11" s="57">
         <f t="shared" si="5"/>
-        <v>-506490</v>
+        <v>146</v>
       </c>
       <c r="P11" s="62"/>
       <c r="Q11" s="45"/>
@@ -28739,15 +29341,15 @@
       </c>
       <c r="B12" s="55">
         <f>'Entries October 2026'!O11</f>
-        <v>0</v>
+        <v>253318</v>
       </c>
       <c r="C12" s="55">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-253318</v>
       </c>
       <c r="D12" s="55">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1113291</v>
       </c>
       <c r="E12" s="56">
         <f>'Entries October 2026'!W11</f>
@@ -28755,19 +29357,19 @@
       </c>
       <c r="F12" s="57">
         <f>'Entries October 2026'!V11</f>
-        <v>0</v>
+        <v>1366609</v>
       </c>
       <c r="G12" s="57">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-1366609</v>
       </c>
       <c r="H12" s="57">
         <f>'Entries October 2026'!AA11</f>
-        <v>0</v>
+        <v>97122</v>
       </c>
       <c r="I12" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-97122</v>
       </c>
       <c r="J12" s="57">
         <f>'Entries October 2026'!T11</f>
@@ -28779,7 +29381,7 @@
       </c>
       <c r="L12" s="58">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-97122</v>
       </c>
       <c r="M12" s="57">
         <f>'Entries October 2026'!R11</f>
@@ -28787,11 +29389,11 @@
       </c>
       <c r="N12" s="57">
         <f>'Entries October 2026'!AC12-'Entries October 2026'!AC11</f>
-        <v>0</v>
+        <v>-6798</v>
       </c>
       <c r="O12" s="57">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-506636</v>
       </c>
       <c r="P12" s="62"/>
       <c r="Q12" s="45"/>
@@ -30472,24 +31074,24 @@
     </row>
     <row r="6" spans="1:20" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="924" t="s">
+      <c r="A7" s="923" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="383"/>
       <c r="C7" s="383"/>
-      <c r="D7" s="937" t="s">
+      <c r="D7" s="936" t="s">
         <v>254</v>
       </c>
-      <c r="E7" s="940" t="s">
+      <c r="E7" s="939" t="s">
         <v>286</v>
       </c>
-      <c r="F7" s="934" t="s">
+      <c r="F7" s="933" t="s">
         <v>287</v>
       </c>
-      <c r="G7" s="930" t="s">
+      <c r="G7" s="929" t="s">
         <v>255</v>
       </c>
-      <c r="H7" s="930" t="s">
+      <c r="H7" s="929" t="s">
         <v>256</v>
       </c>
       <c r="I7" s="383" t="s">
@@ -30501,33 +31103,33 @@
       <c r="K7" s="390" t="s">
         <v>53</v>
       </c>
-      <c r="L7" s="931" t="s">
+      <c r="L7" s="930" t="s">
         <v>17</v>
       </c>
-      <c r="M7" s="932"/>
-      <c r="N7" s="932"/>
-      <c r="O7" s="932"/>
-      <c r="P7" s="933"/>
-      <c r="Q7" s="928" t="s">
+      <c r="M7" s="931"/>
+      <c r="N7" s="931"/>
+      <c r="O7" s="931"/>
+      <c r="P7" s="932"/>
+      <c r="Q7" s="927" t="s">
         <v>11</v>
       </c>
-      <c r="R7" s="929"/>
-      <c r="S7" s="929"/>
-      <c r="T7" s="929"/>
+      <c r="R7" s="928"/>
+      <c r="S7" s="928"/>
+      <c r="T7" s="928"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="925"/>
+      <c r="A8" s="924"/>
       <c r="B8" s="384" t="s">
         <v>257</v>
       </c>
       <c r="C8" s="384" t="s">
         <v>258</v>
       </c>
-      <c r="D8" s="938"/>
-      <c r="E8" s="941"/>
-      <c r="F8" s="935"/>
-      <c r="G8" s="930"/>
-      <c r="H8" s="930"/>
+      <c r="D8" s="937"/>
+      <c r="E8" s="940"/>
+      <c r="F8" s="934"/>
+      <c r="G8" s="929"/>
+      <c r="H8" s="929"/>
       <c r="I8" s="383"/>
       <c r="J8" s="383"/>
       <c r="K8" s="390"/>
@@ -30550,12 +31152,12 @@
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A9" s="926"/>
+      <c r="A9" s="925"/>
       <c r="B9" s="385"/>
       <c r="C9" s="385"/>
-      <c r="D9" s="939"/>
-      <c r="E9" s="942"/>
-      <c r="F9" s="936"/>
+      <c r="D9" s="938"/>
+      <c r="E9" s="941"/>
+      <c r="F9" s="935"/>
       <c r="G9" s="383" t="s">
         <v>56</v>
       </c>
@@ -30774,7 +31376,7 @@
         <f t="shared" si="0"/>
         <v>3772</v>
       </c>
-      <c r="E12" s="879">
+      <c r="E12" s="878">
         <v>801.3</v>
       </c>
       <c r="F12" s="721">
@@ -30853,7 +31455,7 @@
         <f t="shared" si="0"/>
         <v>4062</v>
       </c>
-      <c r="E13" s="879">
+      <c r="E13" s="878">
         <v>694.6</v>
       </c>
       <c r="F13" s="721">
@@ -30920,9 +31522,9 @@
       <c r="A14" s="775">
         <v>5</v>
       </c>
-      <c r="B14" s="775" t="str">
+      <c r="B14" s="775">
         <f>IF('Entries October 2026'!I11&lt;'Entries October 2026'!I10,"0",(IF('Entries October 2026'!I11&gt;='Entries October 2026'!I10,'Entries October 2026'!I11-'Entries October 2026'!I10,(999999-'Entries October 2026'!I10)+'Entries October 2026'!I11+1)))</f>
-        <v>0</v>
+        <v>4774</v>
       </c>
       <c r="C14" s="775" t="str">
         <f>IF('Entries October 2026'!J11&lt;='Entries October 2026'!J10,"0",IF('Entries October 2026'!J11&gt;='Entries October 2026'!J10,'Entries October 2026'!J11-'Entries October 2026'!J10,(999999-'Entries October 2026'!J10)+'Entries October 2026'!J11+1))</f>
@@ -30930,24 +31532,26 @@
       </c>
       <c r="D14" s="776">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E14" s="879"/>
-      <c r="F14" s="777" t="str">
+        <v>4774</v>
+      </c>
+      <c r="E14" s="877">
+        <v>1421</v>
+      </c>
+      <c r="F14" s="777">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="778" t="str">
+        <v>0.22937853107344633</v>
+      </c>
+      <c r="G14" s="778">
         <f>IF('Entries October 2026'!K11&lt;'Entries October 2026'!K10,"0",IF('Entries October 2026'!K11&gt;='Entries October 2026'!K10,'Entries October 2026'!K11-'Entries October 2026'!K10,(999999-'Entries October 2026'!K10)+'Entries October 2026'!K11+1))</f>
         <v>0</v>
       </c>
       <c r="H14" s="776">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6195</v>
       </c>
       <c r="I14" s="778">
         <f>'Water '!Z11*10</f>
-        <v>0</v>
+        <v>1420</v>
       </c>
       <c r="J14" s="776" t="str">
         <f>IF('Entries October 2026'!B11-'Entries October 2026'!B10&lt;1,"0",'Entries October 2026'!B11-'Entries October 2026'!B10)</f>
@@ -30955,7 +31559,7 @@
       </c>
       <c r="K14" s="779">
         <f>'CO2'!E11</f>
-        <v>0</v>
+        <v>1583</v>
       </c>
       <c r="L14" s="780">
         <f>+'PROD.FIG. '!F9</f>
@@ -30974,15 +31578,15 @@
         <v>0</v>
       </c>
       <c r="P14" s="781">
-        <v>0</v>
+        <v>326.50200000000001</v>
       </c>
       <c r="Q14" s="393">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>18.973850083613577</v>
       </c>
       <c r="R14" s="393">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4.3491310926119899</v>
       </c>
       <c r="S14" s="393">
         <f t="shared" si="5"/>
@@ -30997,7 +31601,7 @@
       <c r="A15" s="775">
         <v>6</v>
       </c>
-      <c r="B15" s="775">
+      <c r="B15" s="775" t="str">
         <f>IF('Entries October 2026'!I12&lt;'Entries October 2026'!I11,"0",(IF('Entries October 2026'!I12&gt;='Entries October 2026'!I11,'Entries October 2026'!I12-'Entries October 2026'!I11,(999999-'Entries October 2026'!I11)+'Entries October 2026'!I12+1)))</f>
         <v>0</v>
       </c>
@@ -31009,12 +31613,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E15" s="879"/>
+      <c r="E15" s="878"/>
       <c r="F15" s="777" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G15" s="778">
+      <c r="G15" s="778" t="str">
         <f>IF('Entries October 2026'!K12&lt;'Entries October 2026'!K11,"0",IF('Entries October 2026'!K12&gt;='Entries October 2026'!K11,'Entries October 2026'!K12-'Entries October 2026'!K11,(999999-'Entries October 2026'!K11)+'Entries October 2026'!K12+1))</f>
         <v>0</v>
       </c>
@@ -31471,7 +32075,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E21" s="879"/>
+      <c r="E21" s="878"/>
       <c r="F21" s="777" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -31548,7 +32152,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E22" s="879"/>
+      <c r="E22" s="878"/>
       <c r="F22" s="777" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -32013,7 +32617,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E28" s="879"/>
+      <c r="E28" s="878"/>
       <c r="F28" s="777" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -32090,7 +32694,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E29" s="879"/>
+      <c r="E29" s="878"/>
       <c r="F29" s="777" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -32555,7 +33159,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E35" s="879"/>
+      <c r="E35" s="878"/>
       <c r="F35" s="777" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -32632,7 +33236,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E36" s="879"/>
+      <c r="E36" s="878"/>
       <c r="F36" s="777" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -33076,15 +33680,15 @@
       <c r="C43" s="19"/>
       <c r="D43" s="20">
         <f>SUM(D10:D40)</f>
-        <v>22292</v>
+        <v>27066</v>
       </c>
       <c r="E43" s="741">
         <f>SUM(E10:E40)</f>
-        <v>4124.7000000000007</v>
+        <v>5545.7000000000007</v>
       </c>
       <c r="F43" s="754">
         <f>IF((E43+D43)=0,"0",E43/(D43+E43))</f>
-        <v>0.15613986606956964</v>
+        <v>0.17005246583281461</v>
       </c>
       <c r="G43" s="20">
         <f t="shared" ref="G43:P43" si="7">SUM(G10:G40)</f>
@@ -33092,11 +33696,11 @@
       </c>
       <c r="H43" s="20">
         <f t="shared" si="7"/>
-        <v>26416.699999999997</v>
+        <v>32611.699999999997</v>
       </c>
       <c r="I43" s="20">
         <f t="shared" si="7"/>
-        <v>7380</v>
+        <v>8800</v>
       </c>
       <c r="J43" s="20">
         <f t="shared" si="7"/>
@@ -33104,7 +33708,7 @@
       </c>
       <c r="K43" s="20">
         <f t="shared" si="7"/>
-        <v>2742</v>
+        <v>4325</v>
       </c>
       <c r="L43" s="20">
         <f t="shared" si="7"/>
@@ -33124,7 +33728,7 @@
       </c>
       <c r="P43" s="403">
         <f t="shared" si="7"/>
-        <v>651.10079999999994</v>
+        <v>977.60279999999989</v>
       </c>
       <c r="Q43" s="408" t="s">
         <v>13</v>
@@ -33152,7 +33756,7 @@
       </c>
       <c r="E44" s="728">
         <f>D43+E43</f>
-        <v>26416.7</v>
+        <v>32611.7</v>
       </c>
       <c r="F44" s="708"/>
       <c r="G44" s="7"/>
@@ -33167,19 +33771,19 @@
       <c r="P44" s="401"/>
       <c r="Q44" s="397">
         <f>IF(P43=0,0,H43/P43)</f>
-        <v>40.572366060677545</v>
+        <v>33.358844716893202</v>
       </c>
       <c r="R44" s="398">
         <f>IF(Q44=0,0,I43/P43)</f>
-        <v>11.33465048729782</v>
+        <v>9.0016108791832448</v>
       </c>
       <c r="S44" s="398">
         <f>IF(R44=0,0,J43/P43)</f>
-        <v>1.4744260796484969</v>
+        <v>0.98199391409271752</v>
       </c>
       <c r="T44" s="399">
         <f>IF(S44=0,0,K43/P43)</f>
-        <v>4.2113294899960199</v>
+        <v>4.4240871650531286</v>
       </c>
     </row>
     <row r="45" spans="1:32" ht="15" x14ac:dyDescent="0.2">
@@ -33212,12 +33816,12 @@
       <c r="T46" s="2"/>
     </row>
     <row r="47" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="D47" s="927"/>
-      <c r="E47" s="927"/>
-      <c r="F47" s="927"/>
-      <c r="G47" s="927"/>
-      <c r="H47" s="927"/>
-      <c r="I47" s="927"/>
+      <c r="D47" s="926"/>
+      <c r="E47" s="926"/>
+      <c r="F47" s="926"/>
+      <c r="G47" s="926"/>
+      <c r="H47" s="926"/>
+      <c r="I47" s="926"/>
       <c r="AF47" t="s">
         <v>55</v>
       </c>
@@ -33256,41 +33860,41 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="Q10:Q44">
-    <cfRule type="cellIs" dxfId="62" priority="7" operator="between">
+    <cfRule type="cellIs" dxfId="105" priority="7" operator="between">
       <formula>0</formula>
       <formula>22</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="104" priority="8" operator="greaterThan">
       <formula>22</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="103" priority="9" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:R44">
-    <cfRule type="cellIs" dxfId="59" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="102" priority="1" operator="between">
       <formula>0</formula>
       <formula>10.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="101" priority="2" operator="greaterThan">
       <formula>10.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S10:S44">
-    <cfRule type="cellIs" dxfId="57" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="100" priority="3" operator="between">
       <formula>0</formula>
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="99" priority="4" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T10:T44">
-    <cfRule type="cellIs" dxfId="55" priority="5" operator="between">
+    <cfRule type="cellIs" dxfId="98" priority="5" operator="between">
       <formula>0</formula>
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="97" priority="6" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -33322,16 +33926,16 @@
       <c r="B2" s="8"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="943" t="s">
+      <c r="A3" s="942" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="945" t="s">
+      <c r="B3" s="944" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="944"/>
-      <c r="B4" s="946"/>
+      <c r="A4" s="943"/>
+      <c r="B4" s="945"/>
     </row>
     <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="36">
@@ -33695,31 +34299,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="955" t="s">
+      <c r="A1" s="954" t="s">
         <v>304</v>
       </c>
-      <c r="B1" s="956"/>
-      <c r="C1" s="956"/>
-      <c r="D1" s="956"/>
-      <c r="E1" s="956"/>
-      <c r="F1" s="956"/>
-      <c r="G1" s="956"/>
-      <c r="H1" s="956"/>
-      <c r="I1" s="956"/>
-      <c r="J1" s="956"/>
-      <c r="K1" s="956"/>
-      <c r="L1" s="956"/>
-      <c r="M1" s="956"/>
+      <c r="B1" s="955"/>
+      <c r="C1" s="955"/>
+      <c r="D1" s="955"/>
+      <c r="E1" s="955"/>
+      <c r="F1" s="955"/>
+      <c r="G1" s="955"/>
+      <c r="H1" s="955"/>
+      <c r="I1" s="955"/>
+      <c r="J1" s="955"/>
+      <c r="K1" s="955"/>
+      <c r="L1" s="955"/>
+      <c r="M1" s="955"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
       <c r="F2" s="9"/>
-      <c r="M2" s="947" t="s">
+      <c r="M2" s="946" t="s">
         <v>296</v>
       </c>
-      <c r="N2" s="947" t="s">
+      <c r="N2" s="946" t="s">
         <v>297</v>
       </c>
     </row>
@@ -33728,11 +34332,11 @@
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="9"/>
-      <c r="M3" s="948"/>
-      <c r="N3" s="948"/>
+      <c r="M3" s="947"/>
+      <c r="N3" s="947"/>
     </row>
     <row r="4" spans="1:17" s="339" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="961" t="s">
+      <c r="A4" s="960" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="851" t="s">
@@ -33765,22 +34369,22 @@
       <c r="K4" s="852" t="s">
         <v>40</v>
       </c>
-      <c r="L4" s="957" t="s">
+      <c r="L4" s="956" t="s">
         <v>243</v>
       </c>
-      <c r="M4" s="959" t="s">
+      <c r="M4" s="958" t="s">
         <v>246</v>
       </c>
-      <c r="N4" s="949" t="s">
+      <c r="N4" s="948" t="s">
         <v>246</v>
       </c>
-      <c r="O4" s="952" t="s">
+      <c r="O4" s="951" t="s">
         <v>298</v>
       </c>
       <c r="P4" s="350"/>
     </row>
     <row r="5" spans="1:17" s="339" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="962"/>
+      <c r="A5" s="961"/>
       <c r="B5" s="868" t="s">
         <v>41</v>
       </c>
@@ -33811,10 +34415,10 @@
       <c r="K5" s="869" t="s">
         <v>44</v>
       </c>
-      <c r="L5" s="958"/>
-      <c r="M5" s="960"/>
-      <c r="N5" s="950"/>
-      <c r="O5" s="953"/>
+      <c r="L5" s="957"/>
+      <c r="M5" s="959"/>
+      <c r="N5" s="949"/>
+      <c r="O5" s="952"/>
       <c r="P5" s="350"/>
     </row>
     <row r="6" spans="1:17" s="73" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -33831,8 +34435,8 @@
       <c r="K6" s="840"/>
       <c r="L6" s="873"/>
       <c r="M6" s="837"/>
-      <c r="N6" s="951"/>
-      <c r="O6" s="954"/>
+      <c r="N6" s="950"/>
+      <c r="O6" s="953"/>
       <c r="P6" s="350"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
@@ -33870,7 +34474,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="860">
-        <f t="shared" ref="K7:K37" si="2">B7+E7+G7</f>
+        <f>B7+E7+G7</f>
         <v>960</v>
       </c>
       <c r="L7" s="746" cm="1">
@@ -33882,7 +34486,7 @@
         <v>2.6117843710823236</v>
       </c>
       <c r="N7" s="836">
-        <f t="shared" ref="N7:N37" si="3">IF(L7=0,"0",(D7/L7))</f>
+        <f t="shared" ref="N7:N37" si="2">IF(L7=0,"0",(D7/L7))</f>
         <v>9.0248032455772513</v>
       </c>
       <c r="O7" s="866">
@@ -33918,7 +34522,7 @@
       <c r="G8" s="841"/>
       <c r="H8" s="739"/>
       <c r="I8" s="740">
-        <f t="shared" ref="I8:I37" si="4">IF(C8=0,"0", B8/(C8))</f>
+        <f t="shared" ref="I8:I37" si="3">IF(C8=0,"0", B8/(C8))</f>
         <v>0</v>
       </c>
       <c r="J8" s="740" t="str">
@@ -33926,7 +34530,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="K7:K37" si="4">B8+E8+G8</f>
         <v>0</v>
       </c>
       <c r="L8" s="835">
@@ -33937,7 +34541,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="833">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>7.8829496078102714</v>
       </c>
       <c r="O8" s="834">
@@ -33973,7 +34577,7 @@
       <c r="G9" s="841"/>
       <c r="H9" s="739"/>
       <c r="I9" s="740">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J9" s="740" t="str">
@@ -33981,7 +34585,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L9" s="835" t="str">
@@ -33992,7 +34596,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="833" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O9" s="834">
@@ -34028,7 +34632,7 @@
       <c r="G10" s="841"/>
       <c r="H10" s="739"/>
       <c r="I10" s="740">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J10" s="740" t="str">
@@ -34036,7 +34640,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L10" s="835" t="str">
@@ -34047,7 +34651,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="833" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O10" s="834">
@@ -34064,13 +34668,13 @@
         <f>IF('Entries October 2026'!B11-'Entries October 2026'!B10&lt;1,"0",'Entries October 2026'!B11-'Entries October 2026'!B10)</f>
         <v>0</v>
       </c>
-      <c r="C11" s="739" t="str">
+      <c r="C11" s="739">
         <f>IF('Entries October 2026'!F11-'Entries October 2026'!F10&lt;1,"0",'Entries October 2026'!F11-'Entries October 2026'!F10)</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="843" t="str">
+        <v>19.899999999999636</v>
+      </c>
+      <c r="D11" s="843">
         <f>IF('Entries October 2026'!C11-'Entries October 2026'!C10&lt;1,"0",'Entries October 2026'!C11-'Entries October 2026'!C10)</f>
-        <v>0</v>
+        <v>3351.6000000000931</v>
       </c>
       <c r="E11" s="847" t="str">
         <f t="shared" si="0"/>
@@ -34082,8 +34686,8 @@
       </c>
       <c r="G11" s="841"/>
       <c r="H11" s="739"/>
-      <c r="I11" s="740" t="str">
-        <f t="shared" si="4"/>
+      <c r="I11" s="740">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J11" s="740" t="str">
@@ -34091,23 +34695,23 @@
         <v>0</v>
       </c>
       <c r="K11" s="739">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="835">
+        <v>326.50200000000001</v>
+      </c>
+      <c r="M11" s="833">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N11" s="833">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L11" s="835" t="str">
-        <v>0</v>
-      </c>
-      <c r="M11" s="833" t="str">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N11" s="833" t="str">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10.265174485914613</v>
       </c>
       <c r="O11" s="834">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-3351.6000000000931</v>
       </c>
       <c r="P11" s="333"/>
     </row>
@@ -34138,7 +34742,7 @@
       <c r="G12" s="841"/>
       <c r="H12" s="739"/>
       <c r="I12" s="740" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J12" s="740" t="str">
@@ -34146,7 +34750,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L12" s="835" t="str">
@@ -34157,7 +34761,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="833" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O12" s="834">
@@ -34193,7 +34797,7 @@
       <c r="G13" s="841"/>
       <c r="H13" s="739"/>
       <c r="I13" s="740" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J13" s="740" t="str">
@@ -34201,7 +34805,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L13" s="835" t="str">
@@ -34212,7 +34816,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="833" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O13" s="834">
@@ -34248,7 +34852,7 @@
       <c r="G14" s="841"/>
       <c r="H14" s="739"/>
       <c r="I14" s="740" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J14" s="740" t="str">
@@ -34256,7 +34860,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L14" s="835" t="str">
@@ -34267,7 +34871,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="833" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O14" s="834">
@@ -34304,7 +34908,7 @@
       <c r="G15" s="841"/>
       <c r="H15" s="739"/>
       <c r="I15" s="740" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J15" s="740" t="str">
@@ -34312,7 +34916,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L15" s="835" t="str">
@@ -34323,7 +34927,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="833" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O15" s="834">
@@ -34359,7 +34963,7 @@
       <c r="G16" s="841"/>
       <c r="H16" s="739"/>
       <c r="I16" s="740" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J16" s="740" t="str">
@@ -34367,7 +34971,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L16" s="835" t="str">
@@ -34378,7 +34982,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="833" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O16" s="834">
@@ -34414,7 +35018,7 @@
       <c r="G17" s="841"/>
       <c r="H17" s="739"/>
       <c r="I17" s="740" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J17" s="740" t="str">
@@ -34422,7 +35026,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L17" s="835" t="str">
@@ -34433,7 +35037,7 @@
         <v>0</v>
       </c>
       <c r="N17" s="833" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O17" s="834">
@@ -34469,7 +35073,7 @@
       <c r="G18" s="841"/>
       <c r="H18" s="739"/>
       <c r="I18" s="740" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J18" s="740" t="str">
@@ -34477,7 +35081,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L18" s="835" t="str">
@@ -34488,7 +35092,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="833" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O18" s="834">
@@ -34527,7 +35131,7 @@
       <c r="G19" s="841"/>
       <c r="H19" s="739"/>
       <c r="I19" s="740" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J19" s="740" t="str">
@@ -34535,7 +35139,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L19" s="835" t="str">
@@ -34546,7 +35150,7 @@
         <v>0</v>
       </c>
       <c r="N19" s="833" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O19" s="834">
@@ -34582,7 +35186,7 @@
       <c r="G20" s="841"/>
       <c r="H20" s="739"/>
       <c r="I20" s="740" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J20" s="740" t="str">
@@ -34590,7 +35194,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L20" s="835" t="str">
@@ -34601,7 +35205,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="833" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O20" s="834">
@@ -34637,7 +35241,7 @@
       <c r="G21" s="841"/>
       <c r="H21" s="739"/>
       <c r="I21" s="740" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J21" s="740" t="str">
@@ -34645,7 +35249,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L21" s="835" t="str">
@@ -34656,7 +35260,7 @@
         <v>0</v>
       </c>
       <c r="N21" s="833" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O21" s="834">
@@ -34692,7 +35296,7 @@
       <c r="G22" s="841"/>
       <c r="H22" s="739"/>
       <c r="I22" s="740" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J22" s="740" t="str">
@@ -34700,7 +35304,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L22" s="835" t="str">
@@ -34711,7 +35315,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="833" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O22" s="834">
@@ -34747,7 +35351,7 @@
       <c r="G23" s="841"/>
       <c r="H23" s="739"/>
       <c r="I23" s="740" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J23" s="740" t="str">
@@ -34755,7 +35359,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L23" s="835" t="str">
@@ -34766,7 +35370,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="833" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O23" s="834">
@@ -34802,7 +35406,7 @@
       <c r="G24" s="841"/>
       <c r="H24" s="739"/>
       <c r="I24" s="740" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J24" s="740" t="str">
@@ -34810,7 +35414,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L24" s="835" t="str">
@@ -34821,7 +35425,7 @@
         <v>0</v>
       </c>
       <c r="N24" s="833" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O24" s="834">
@@ -34857,7 +35461,7 @@
       <c r="G25" s="841"/>
       <c r="H25" s="739"/>
       <c r="I25" s="740" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J25" s="740" t="str">
@@ -34865,7 +35469,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L25" s="835" t="str">
@@ -34876,7 +35480,7 @@
         <v>0</v>
       </c>
       <c r="N25" s="833" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O25" s="834">
@@ -34912,7 +35516,7 @@
       <c r="G26" s="841"/>
       <c r="H26" s="739"/>
       <c r="I26" s="740" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J26" s="740" t="str">
@@ -34920,7 +35524,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L26" s="835" t="str">
@@ -34931,7 +35535,7 @@
         <v>0</v>
       </c>
       <c r="N26" s="833" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O26" s="834">
@@ -34967,7 +35571,7 @@
       <c r="G27" s="841"/>
       <c r="H27" s="739"/>
       <c r="I27" s="740" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J27" s="740" t="str">
@@ -34975,7 +35579,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L27" s="835" t="str">
@@ -34986,7 +35590,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="833" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O27" s="834">
@@ -35022,7 +35626,7 @@
       <c r="G28" s="841"/>
       <c r="H28" s="739"/>
       <c r="I28" s="740" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J28" s="740" t="str">
@@ -35030,7 +35634,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L28" s="835" t="str">
@@ -35041,7 +35645,7 @@
         <v>0</v>
       </c>
       <c r="N28" s="833" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O28" s="834">
@@ -35077,7 +35681,7 @@
       <c r="G29" s="841"/>
       <c r="H29" s="739"/>
       <c r="I29" s="740" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J29" s="740" t="str">
@@ -35085,7 +35689,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L29" s="835" t="str">
@@ -35096,7 +35700,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="833" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O29" s="834">
@@ -35132,7 +35736,7 @@
       <c r="G30" s="841"/>
       <c r="H30" s="739"/>
       <c r="I30" s="740" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J30" s="740" t="str">
@@ -35140,7 +35744,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L30" s="835" t="str">
@@ -35151,7 +35755,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="833" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O30" s="834">
@@ -35187,7 +35791,7 @@
       <c r="G31" s="841"/>
       <c r="H31" s="739"/>
       <c r="I31" s="740" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J31" s="740" t="str">
@@ -35195,7 +35799,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L31" s="835" t="str">
@@ -35206,7 +35810,7 @@
         <v>0</v>
       </c>
       <c r="N31" s="833" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O31" s="834">
@@ -35242,7 +35846,7 @@
       <c r="G32" s="841"/>
       <c r="H32" s="739"/>
       <c r="I32" s="740" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J32" s="740" t="str">
@@ -35250,7 +35854,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L32" s="835" t="str">
@@ -35261,7 +35865,7 @@
         <v>0</v>
       </c>
       <c r="N32" s="833" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O32" s="834">
@@ -35297,7 +35901,7 @@
       <c r="G33" s="841"/>
       <c r="H33" s="739"/>
       <c r="I33" s="740" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J33" s="740" t="str">
@@ -35305,7 +35909,7 @@
         <v>0</v>
       </c>
       <c r="K33" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L33" s="835" t="str">
@@ -35316,7 +35920,7 @@
         <v>0</v>
       </c>
       <c r="N33" s="833" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O33" s="834">
@@ -35352,7 +35956,7 @@
       <c r="G34" s="841"/>
       <c r="H34" s="739"/>
       <c r="I34" s="740" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J34" s="740" t="str">
@@ -35360,7 +35964,7 @@
         <v>0</v>
       </c>
       <c r="K34" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L34" s="835" t="str">
@@ -35371,7 +35975,7 @@
         <v>0</v>
       </c>
       <c r="N34" s="833" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O34" s="834">
@@ -35407,7 +36011,7 @@
       <c r="G35" s="841"/>
       <c r="H35" s="739"/>
       <c r="I35" s="740" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J35" s="740" t="str">
@@ -35415,7 +36019,7 @@
         <v>0</v>
       </c>
       <c r="K35" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L35" s="835" t="str">
@@ -35426,7 +36030,7 @@
         <v>0</v>
       </c>
       <c r="N35" s="833" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O35" s="834">
@@ -35461,7 +36065,7 @@
       <c r="G36" s="841"/>
       <c r="H36" s="739"/>
       <c r="I36" s="740" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J36" s="740" t="str">
@@ -35469,7 +36073,7 @@
         <v>0</v>
       </c>
       <c r="K36" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L36" s="835" t="str">
@@ -35480,7 +36084,7 @@
         <v>0</v>
       </c>
       <c r="N36" s="833" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O36" s="834">
@@ -35515,7 +36119,7 @@
       <c r="G37" s="841"/>
       <c r="H37" s="739"/>
       <c r="I37" s="740" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J37" s="740" t="str">
@@ -35523,7 +36127,7 @@
         <v>0</v>
       </c>
       <c r="K37" s="739">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L37" s="835" t="str">
@@ -35534,7 +36138,7 @@
         <v>0</v>
       </c>
       <c r="N37" s="833" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O37" s="834">
@@ -35550,11 +36154,11 @@
       </c>
       <c r="C38" s="388">
         <f>SUM(C7:C37)</f>
-        <v>40.600000000000364</v>
+        <v>60.5</v>
       </c>
       <c r="D38" s="844">
         <f t="shared" si="7"/>
-        <v>6125.5</v>
+        <v>9477.1000000000931</v>
       </c>
       <c r="E38" s="849"/>
       <c r="F38" s="850">
@@ -35571,7 +36175,7 @@
       </c>
       <c r="I38" s="801">
         <f>B38/C38</f>
-        <v>23.645320197044121</v>
+        <v>15.867768595041323</v>
       </c>
       <c r="J38" s="355"/>
       <c r="K38" s="356">
@@ -35580,15 +36184,15 @@
       </c>
       <c r="L38" s="832">
         <f>SUM(L7:L37)</f>
-        <v>651.10079999999994</v>
+        <v>977.60279999999989</v>
       </c>
       <c r="M38" s="838">
         <f>IF(L38=0,"0",(K38/L38))</f>
-        <v>1.4744260796484969</v>
+        <v>0.98199391409271752</v>
       </c>
       <c r="N38" s="838">
         <f>IF(L38=0,"0",(D38/L38))</f>
-        <v>9.4079134905071538</v>
+        <v>9.6942234617168594</v>
       </c>
       <c r="O38" s="839"/>
     </row>
@@ -35602,7 +36206,7 @@
       </c>
       <c r="C39" s="806">
         <f>AVERAGE(C7:C37)</f>
-        <v>10.150000000000091</v>
+        <v>12.1</v>
       </c>
       <c r="D39" s="30"/>
       <c r="E39" s="30"/>
@@ -36222,27 +36826,27 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="C7:C37">
-    <cfRule type="cellIs" dxfId="53" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="96" priority="13" operator="greaterThan">
       <formula>24</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7:N37">
-    <cfRule type="cellIs" dxfId="52" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="95" priority="9" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="11" operator="between">
+    <cfRule type="cellIs" dxfId="94" priority="11" operator="between">
       <formula>0</formula>
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7:N38">
-    <cfRule type="cellIs" dxfId="50" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="93" priority="1" operator="lessThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="92" priority="2" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="91" priority="4" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36286,120 +36890,120 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="955"/>
-      <c r="B1" s="956"/>
-      <c r="C1" s="956"/>
-      <c r="D1" s="956"/>
-      <c r="E1" s="956"/>
-      <c r="F1" s="956"/>
-      <c r="G1" s="956"/>
-      <c r="H1" s="956"/>
-      <c r="I1" s="956"/>
-      <c r="J1" s="956"/>
-      <c r="K1" s="956"/>
-      <c r="L1" s="956"/>
-      <c r="M1" s="956"/>
-      <c r="N1" s="956"/>
-      <c r="O1" s="956"/>
-      <c r="P1" s="956"/>
-      <c r="Q1" s="956"/>
-      <c r="R1" s="956"/>
-      <c r="S1" s="956"/>
-      <c r="T1" s="956"/>
-      <c r="U1" s="956"/>
-      <c r="V1" s="956"/>
-      <c r="W1" s="956"/>
-      <c r="X1" s="956"/>
-      <c r="Y1" s="956"/>
-      <c r="Z1" s="956"/>
-      <c r="AA1" s="956"/>
+      <c r="A1" s="954"/>
+      <c r="B1" s="955"/>
+      <c r="C1" s="955"/>
+      <c r="D1" s="955"/>
+      <c r="E1" s="955"/>
+      <c r="F1" s="955"/>
+      <c r="G1" s="955"/>
+      <c r="H1" s="955"/>
+      <c r="I1" s="955"/>
+      <c r="J1" s="955"/>
+      <c r="K1" s="955"/>
+      <c r="L1" s="955"/>
+      <c r="M1" s="955"/>
+      <c r="N1" s="955"/>
+      <c r="O1" s="955"/>
+      <c r="P1" s="955"/>
+      <c r="Q1" s="955"/>
+      <c r="R1" s="955"/>
+      <c r="S1" s="955"/>
+      <c r="T1" s="955"/>
+      <c r="U1" s="955"/>
+      <c r="V1" s="955"/>
+      <c r="W1" s="955"/>
+      <c r="X1" s="955"/>
+      <c r="Y1" s="955"/>
+      <c r="Z1" s="955"/>
+      <c r="AA1" s="955"/>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C2" s="17"/>
     </row>
     <row r="3" spans="1:31" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="967" t="s">
+      <c r="B4" s="974" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="965" t="s">
+      <c r="C4" s="966" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="963" t="s">
+      <c r="D4" s="971" t="s">
         <v>106</v>
       </c>
-      <c r="E4" s="965" t="s">
+      <c r="E4" s="966" t="s">
         <v>107</v>
       </c>
-      <c r="F4" s="963" t="s">
+      <c r="F4" s="971" t="s">
         <v>239</v>
       </c>
-      <c r="G4" s="963" t="s">
+      <c r="G4" s="971" t="s">
         <v>108</v>
       </c>
-      <c r="H4" s="963" t="s">
+      <c r="H4" s="971" t="s">
         <v>161</v>
       </c>
-      <c r="I4" s="965" t="s">
+      <c r="I4" s="966" t="s">
         <v>207</v>
       </c>
-      <c r="J4" s="965" t="s">
+      <c r="J4" s="966" t="s">
         <v>109</v>
       </c>
-      <c r="K4" s="965" t="s">
+      <c r="K4" s="966" t="s">
         <v>174</v>
       </c>
-      <c r="L4" s="965" t="s">
+      <c r="L4" s="966" t="s">
         <v>173</v>
       </c>
-      <c r="M4" s="965" t="s">
+      <c r="M4" s="966" t="s">
         <v>103</v>
       </c>
       <c r="N4" s="48"/>
       <c r="O4" s="48"/>
       <c r="P4" s="48"/>
       <c r="Q4" s="48"/>
-      <c r="R4" s="963" t="s">
+      <c r="R4" s="971" t="s">
         <v>110</v>
       </c>
-      <c r="S4" s="963" t="s">
+      <c r="S4" s="971" t="s">
         <v>240</v>
       </c>
       <c r="T4" s="48"/>
-      <c r="U4" s="965" t="s">
+      <c r="U4" s="966" t="s">
         <v>153</v>
       </c>
       <c r="V4" s="48"/>
       <c r="W4" s="48"/>
-      <c r="X4" s="965" t="s">
+      <c r="X4" s="966" t="s">
         <v>175</v>
       </c>
-      <c r="Y4" s="965" t="s">
+      <c r="Y4" s="966" t="s">
         <v>176</v>
       </c>
-      <c r="Z4" s="972" t="s">
+      <c r="Z4" s="964" t="s">
         <v>247</v>
       </c>
-      <c r="AA4" s="974" t="s">
+      <c r="AA4" s="968" t="s">
         <v>243</v>
       </c>
-      <c r="AB4" s="970" t="s">
+      <c r="AB4" s="962" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:31" s="300" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="968"/>
-      <c r="C5" s="966"/>
-      <c r="D5" s="964"/>
-      <c r="E5" s="969"/>
-      <c r="F5" s="964"/>
-      <c r="G5" s="964"/>
-      <c r="H5" s="964"/>
-      <c r="I5" s="969"/>
-      <c r="J5" s="969"/>
-      <c r="K5" s="969"/>
-      <c r="L5" s="969"/>
-      <c r="M5" s="969"/>
+      <c r="B5" s="975"/>
+      <c r="C5" s="973"/>
+      <c r="D5" s="972"/>
+      <c r="E5" s="967"/>
+      <c r="F5" s="972"/>
+      <c r="G5" s="972"/>
+      <c r="H5" s="972"/>
+      <c r="I5" s="967"/>
+      <c r="J5" s="967"/>
+      <c r="K5" s="967"/>
+      <c r="L5" s="967"/>
+      <c r="M5" s="967"/>
       <c r="N5" s="50" t="s">
         <v>111</v>
       </c>
@@ -36412,23 +37016,23 @@
       <c r="Q5" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="R5" s="964"/>
-      <c r="S5" s="964"/>
+      <c r="R5" s="972"/>
+      <c r="S5" s="972"/>
       <c r="T5" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="U5" s="976"/>
+      <c r="U5" s="970"/>
       <c r="V5" s="80" t="s">
         <v>156</v>
       </c>
       <c r="W5" s="80" t="s">
         <v>157</v>
       </c>
-      <c r="X5" s="969"/>
-      <c r="Y5" s="969"/>
-      <c r="Z5" s="973"/>
-      <c r="AA5" s="975"/>
-      <c r="AB5" s="971"/>
+      <c r="X5" s="967"/>
+      <c r="Y5" s="967"/>
+      <c r="Z5" s="965"/>
+      <c r="AA5" s="969"/>
+      <c r="AB5" s="963"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="21" t="s">
@@ -36905,13 +37509,13 @@
         <f>IF('Entries October 2026'!W11-'Entries October 2026'!W10&lt;1,"0",'Entries October 2026'!W11-'Entries October 2026'!W10)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="693" t="str">
+      <c r="D11" s="693">
         <f>IF('Entries October 2026'!O11-'Entries October 2026'!O10&lt;1,"0",'Entries October 2026'!O11-'Entries October 2026'!O10)</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="693" t="str">
+        <v>73</v>
+      </c>
+      <c r="E11" s="693">
         <f>IF('Entries October 2026'!P11-'Entries October 2026'!P10&lt;1,"0",'Entries October 2026'!P11-'Entries October 2026'!P10)</f>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="F11" s="693" t="str">
         <f>IF('Entries October 2026'!V11-'Entries October 2026'!V10&lt;1,"0",'Entries October 2026'!V11-'Entries October 2026'!V10)</f>
@@ -36919,19 +37523,19 @@
       </c>
       <c r="G11" s="693">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="H11" s="693">
         <f>IF('Entries October 2026'!Q11-'Entries October 2026'!Q10&lt;1,0,'Entries October 2026'!Q11-'Entries October 2026'!Q10)</f>
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="I11" s="693">
         <f>IF('Entries October 2026'!AG11-'Entries October 2026'!AG10&lt;1,0,'Entries October 2026'!AG11-'Entries October 2026'!AG10)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="693" t="str">
+      <c r="J11" s="693">
         <f>IF('Entries October 2026'!S11-'Entries October 2026'!S10&lt;1,"0",'Entries October 2026'!S11-'Entries October 2026'!S10)</f>
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="K11" s="693" t="str">
         <f>IF('Entries October 2026'!R11-'Entries October 2026'!R10&lt;1,"0",'Entries October 2026'!R11-'Entries October 2026'!R10)</f>
@@ -36941,25 +37545,25 @@
         <f>IF('Entries October 2026'!T11-'Entries October 2026'!T10&lt;1,"0",'Entries October 2026'!T11-'Entries October 2026'!T10)</f>
         <v>0</v>
       </c>
-      <c r="M11" s="693" t="str">
+      <c r="M11" s="693">
         <f>IF('Entries October 2026'!U11-'Entries October 2026'!U10&lt;1,"0",'Entries October 2026'!U11-'Entries October 2026'!U10)</f>
-        <v>0</v>
-      </c>
-      <c r="N11" s="693" t="str">
+        <v>1</v>
+      </c>
+      <c r="N11" s="693">
         <f>IF('Entries October 2026'!X11-'Entries October 2026'!X10&lt;1,"0",'Entries October 2026'!X11-'Entries October 2026'!X10)</f>
-        <v>0</v>
-      </c>
-      <c r="O11" s="693" t="str">
+        <v>38</v>
+      </c>
+      <c r="O11" s="693">
         <f>IF('Entries October 2026'!Y11-'Entries October 2026'!Y10&lt;1,"0",'Entries October 2026'!Y11-'Entries October 2026'!Y10)</f>
-        <v>0</v>
-      </c>
-      <c r="P11" s="693" t="str">
+        <v>112</v>
+      </c>
+      <c r="P11" s="693">
         <f>IF('Entries October 2026'!AC11-'Entries October 2026'!AC10&lt;1,"0",'Entries October 2026'!AC11-'Entries October 2026'!AC10)</f>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="693" t="str">
+        <v>17</v>
+      </c>
+      <c r="Q11" s="693">
         <f>IF('Entries October 2026'!Z11-'Entries October 2026'!Z10&lt;1,"0",'Entries October 2026'!Z11-'Entries October 2026'!Z10)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R11" s="693" t="str">
         <f>IF(('Entries October 2026'!AA11-'Entries October 2026'!AA10)+('Entries October 2026'!AB11-'Entries October 2026'!AB10)&lt;1,"0",('Entries October 2026'!AA11-'Entries October 2026'!AA10)+('Entries October 2026'!AB11-'Entries October 2026'!AB10))</f>
@@ -36967,15 +37571,15 @@
       </c>
       <c r="S11" s="692">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1420</v>
       </c>
       <c r="T11" s="692">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U11" s="693" t="str">
+        <v>151</v>
+      </c>
+      <c r="U11" s="693">
         <f>IF('Entries October 2026'!AC11-'Entries October 2026'!AC10&lt;1,"0",'Entries October 2026'!AC11-'Entries October 2026'!AC10)</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="V11" s="693" t="str">
         <f>IF('Entries October 2026'!AD11-'Entries October 2026'!AD10&lt;1,"0",'Entries October 2026'!AD11-'Entries October 2026'!AD10)</f>
@@ -36995,14 +37599,14 @@
       </c>
       <c r="Z11" s="329">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AA11" s="330" t="str">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="331" t="str">
+        <v>142</v>
+      </c>
+      <c r="AA11" s="330">
+        <v>326.50200000000001</v>
+      </c>
+      <c r="AB11" s="331">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4.3491310926119899</v>
       </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
@@ -39830,11 +40434,11 @@
       </c>
       <c r="D38" s="303">
         <f>SUM(D7:D37)</f>
-        <v>251</v>
+        <v>324</v>
       </c>
       <c r="E38" s="303">
         <f>SUM(E7:E37)</f>
-        <v>487</v>
+        <v>556</v>
       </c>
       <c r="F38" s="303">
         <f>SUM(F7:F37)</f>
@@ -39842,16 +40446,16 @@
       </c>
       <c r="G38" s="304">
         <f>SUM(G7:G37)</f>
-        <v>165</v>
+        <v>307</v>
       </c>
       <c r="H38" s="303">
         <f t="shared" si="5"/>
-        <v>531</v>
+        <v>717</v>
       </c>
       <c r="I38" s="303"/>
       <c r="J38" s="303">
         <f t="shared" si="5"/>
-        <v>283</v>
+        <v>465</v>
       </c>
       <c r="K38" s="303"/>
       <c r="L38" s="303">
@@ -39860,23 +40464,23 @@
       </c>
       <c r="M38" s="303">
         <f>SUM(M7:M37)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N38" s="303">
         <f t="shared" si="5"/>
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="O38" s="303">
         <f t="shared" si="5"/>
-        <v>180</v>
+        <v>292</v>
       </c>
       <c r="P38" s="303">
         <f>SUM(P7:P37)</f>
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="Q38" s="303">
         <f>SUM(Q7:Q37)</f>
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="R38" s="303">
         <f>SUM(R7:R34)</f>
@@ -39884,15 +40488,15 @@
       </c>
       <c r="S38" s="304">
         <f>SUM(S7:S37)</f>
-        <v>1650</v>
+        <v>3070</v>
       </c>
       <c r="T38" s="304">
         <f>SUM(T7:T37)</f>
-        <v>288</v>
+        <v>439</v>
       </c>
       <c r="U38" s="303">
         <f>SUM(U7:U37)</f>
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="V38" s="303">
         <f>SUM(V7:V37)</f>
@@ -39903,22 +40507,22 @@
       <c r="Y38" s="303"/>
       <c r="Z38" s="332">
         <f>SUM(Z7:Z37)</f>
-        <v>738</v>
+        <v>880</v>
       </c>
       <c r="AA38" s="332">
         <f>SUM(AA7:AA37)</f>
-        <v>651.10079999999994</v>
+        <v>977.60279999999989</v>
       </c>
       <c r="AB38" s="331">
         <f>IF(AA38=0,"0",(Z38*10/AA38))</f>
-        <v>11.33465048729782</v>
+        <v>9.0016108791832448</v>
       </c>
       <c r="AC38" s="321">
         <v>10.199999999999999</v>
       </c>
       <c r="AD38" s="340">
         <f>AB38/AC38*100</f>
-        <v>111.12402438527276</v>
+        <v>88.251087050816139</v>
       </c>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.2">
@@ -39957,7 +40561,7 @@
       <c r="C40" s="15"/>
       <c r="D40" s="15">
         <f>D38*220</f>
-        <v>55220</v>
+        <v>71280</v>
       </c>
       <c r="E40" s="15"/>
       <c r="F40" s="15"/>
@@ -40049,7 +40653,7 @@
       <c r="C43" s="17"/>
       <c r="D43" s="17">
         <f>+D41*D40</f>
-        <v>873.02820000000008</v>
+        <v>1126.9368000000002</v>
       </c>
       <c r="E43" s="17"/>
       <c r="F43" s="36"/>
@@ -40102,7 +40706,7 @@
     <row r="45" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D45" s="17">
         <f>SUM(D43:D44)</f>
-        <v>1151.9982</v>
+        <v>1405.9068000000002</v>
       </c>
       <c r="E45" s="17"/>
       <c r="F45" s="36"/>
@@ -40124,7 +40728,7 @@
       </c>
       <c r="D47" s="23">
         <f>+D45*2/3</f>
-        <v>767.99879999999996</v>
+        <v>937.27120000000014</v>
       </c>
       <c r="E47" s="324"/>
       <c r="F47" s="36"/>
@@ -40147,7 +40751,7 @@
       <c r="C49" s="24"/>
       <c r="D49" s="28">
         <f>SUM(D47,D45)</f>
-        <v>1919.9969999999998</v>
+        <v>2343.1780000000003</v>
       </c>
       <c r="E49" s="325"/>
       <c r="F49" s="36"/>
@@ -40512,6 +41116,16 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:AA1"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="R4:R5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="E4:E5"/>
     <mergeCell ref="AB4:AB5"/>
     <mergeCell ref="Z4:Z5"/>
     <mergeCell ref="L4:L5"/>
@@ -40523,23 +41137,13 @@
     <mergeCell ref="Y4:Y5"/>
     <mergeCell ref="S4:S5"/>
     <mergeCell ref="M4:M5"/>
-    <mergeCell ref="A1:AA1"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="R4:R5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="E4:E5"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="AB6:AB38">
-    <cfRule type="cellIs" dxfId="47" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="90" priority="1" operator="lessThan">
       <formula>10.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="89" priority="2" operator="greaterThan">
       <formula>10.2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -40570,15 +41174,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="977" t="s">
+      <c r="A1" s="976" t="s">
         <v>303</v>
       </c>
-      <c r="B1" s="978"/>
-      <c r="C1" s="978"/>
-      <c r="D1" s="979"/>
-      <c r="E1" s="978"/>
-      <c r="F1" s="978"/>
-      <c r="G1" s="980"/>
+      <c r="B1" s="977"/>
+      <c r="C1" s="977"/>
+      <c r="D1" s="978"/>
+      <c r="E1" s="977"/>
+      <c r="F1" s="977"/>
+      <c r="G1" s="979"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B2" s="9"/>
@@ -40591,7 +41195,7 @@
       <c r="D3" s="359"/>
     </row>
     <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="991" t="s">
+      <c r="A4" s="990" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="39" t="s">
@@ -40603,19 +41207,19 @@
       <c r="D4" s="361" t="s">
         <v>285</v>
       </c>
-      <c r="E4" s="981" t="s">
+      <c r="E4" s="980" t="s">
         <v>245</v>
       </c>
-      <c r="F4" s="984" t="s">
+      <c r="F4" s="983" t="s">
         <v>243</v>
       </c>
-      <c r="G4" s="987" t="s">
+      <c r="G4" s="986" t="s">
         <v>253</v>
       </c>
-      <c r="H4" s="990"/>
+      <c r="H4" s="989"/>
     </row>
     <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="992"/>
+      <c r="A5" s="991"/>
       <c r="B5" s="34" t="s">
         <v>48</v>
       </c>
@@ -40625,20 +41229,20 @@
       <c r="D5" s="361" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="982"/>
-      <c r="F5" s="985"/>
-      <c r="G5" s="988"/>
-      <c r="H5" s="990"/>
+      <c r="E5" s="981"/>
+      <c r="F5" s="984"/>
+      <c r="G5" s="987"/>
+      <c r="H5" s="989"/>
     </row>
     <row r="6" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="993"/>
+      <c r="A6" s="992"/>
       <c r="B6" s="40"/>
       <c r="C6" s="362"/>
       <c r="D6" s="361"/>
-      <c r="E6" s="983"/>
-      <c r="F6" s="986"/>
-      <c r="G6" s="989"/>
-      <c r="H6" s="990"/>
+      <c r="E6" s="982"/>
+      <c r="F6" s="985"/>
+      <c r="G6" s="988"/>
+      <c r="H6" s="989"/>
     </row>
     <row r="7" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A7" s="686">
@@ -40768,27 +41372,27 @@
       </c>
       <c r="B11" s="765">
         <f>'Utility Analysis October 2026'!D14</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="766" t="str">
+        <v>4774</v>
+      </c>
+      <c r="C11" s="766">
         <f>'Utility Analysis October 2026'!G14</f>
         <v>0</v>
       </c>
       <c r="D11" s="767">
         <f>'Utility Analysis October 2026'!E14</f>
-        <v>0</v>
+        <v>1421</v>
       </c>
       <c r="E11" s="768">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F11" s="769" t="str">
+        <v>6195</v>
+      </c>
+      <c r="F11" s="769">
         <f>'PROD.FIG. '!H9</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="456" t="str">
+        <v>326.50200000000001</v>
+      </c>
+      <c r="G11" s="456">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>18.973850083613577</v>
       </c>
       <c r="J11" s="30"/>
     </row>
@@ -40800,7 +41404,7 @@
         <f>'Utility Analysis October 2026'!D15</f>
         <v>0</v>
       </c>
-      <c r="C12" s="766">
+      <c r="C12" s="766" t="str">
         <f>'Utility Analysis October 2026'!G15</f>
         <v>0</v>
       </c>
@@ -41575,7 +42179,7 @@
       </c>
       <c r="B38" s="308">
         <f>SUM(B7:B37)</f>
-        <v>22292</v>
+        <v>27066</v>
       </c>
       <c r="C38" s="308">
         <f>SUM(C7:C37)</f>
@@ -41583,26 +42187,26 @@
       </c>
       <c r="D38" s="308">
         <f>SUM(D7:D37)</f>
-        <v>4124.7000000000007</v>
+        <v>5545.7000000000007</v>
       </c>
       <c r="E38" s="337">
         <f>SUM(E7:E37)</f>
-        <v>26416.699999999997</v>
+        <v>32611.699999999997</v>
       </c>
       <c r="F38" s="358">
         <f>SUM(F7:F37)</f>
-        <v>651.10079999999994</v>
+        <v>977.60279999999989</v>
       </c>
       <c r="G38" s="338">
         <f>IF(F38=0,"0",(E38/F38))</f>
-        <v>40.572366060677545</v>
+        <v>33.358844716893202</v>
       </c>
       <c r="H38" s="335">
         <v>22</v>
       </c>
       <c r="I38" s="340">
         <f>G38/H38*100</f>
-        <v>184.41984573035248</v>
+        <v>151.63111234951455</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
@@ -41643,12 +42247,12 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="cellIs" dxfId="45" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="88" priority="1" operator="lessThan">
       <formula>22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7:G38">
-    <cfRule type="cellIs" dxfId="44" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="87" priority="2" operator="greaterThan">
       <formula>21</formula>
     </cfRule>
   </conditionalFormatting>
@@ -41679,16 +42283,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="994" t="s">
+      <c r="A1" s="993" t="s">
         <v>302</v>
       </c>
-      <c r="B1" s="956"/>
-      <c r="C1" s="956"/>
-      <c r="D1" s="956"/>
-      <c r="E1" s="956"/>
-      <c r="F1" s="956"/>
-      <c r="G1" s="956"/>
-      <c r="H1" s="956"/>
+      <c r="B1" s="955"/>
+      <c r="C1" s="955"/>
+      <c r="D1" s="955"/>
+      <c r="E1" s="955"/>
+      <c r="F1" s="955"/>
+      <c r="G1" s="955"/>
+      <c r="H1" s="955"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D2" s="12"/>
@@ -41814,8 +42418,8 @@
       <c r="E9" s="756"/>
       <c r="F9" s="756"/>
       <c r="G9" s="756"/>
-      <c r="H9" s="812" t="str">
-        <v>0</v>
+      <c r="H9" s="812">
+        <v>326.50200000000001</v>
       </c>
       <c r="I9" s="298"/>
       <c r="J9" s="299"/>
@@ -42301,7 +42905,7 @@
       </c>
       <c r="H36" s="736">
         <f>SUM(H5:H35)</f>
-        <v>651.10079999999994</v>
+        <v>977.60279999999989</v>
       </c>
       <c r="I36" s="298"/>
       <c r="J36" s="299"/>
@@ -42417,11 +43021,11 @@
       <c r="D3" s="85"/>
       <c r="E3" s="85"/>
       <c r="F3" s="1"/>
-      <c r="I3" s="999" t="s">
+      <c r="I3" s="1006" t="s">
         <v>267</v>
       </c>
-      <c r="J3" s="1000"/>
-      <c r="K3" s="1001"/>
+      <c r="J3" s="1007"/>
+      <c r="K3" s="1008"/>
     </row>
     <row r="4" spans="1:24" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
@@ -42434,46 +43038,46 @@
         <v>250</v>
       </c>
       <c r="H4" s="347"/>
-      <c r="I4" s="1002" t="s">
+      <c r="I4" s="1009" t="s">
         <v>262</v>
       </c>
-      <c r="J4" s="1003"/>
-      <c r="K4" s="1004"/>
+      <c r="J4" s="1010"/>
+      <c r="K4" s="1011"/>
       <c r="M4" s="417"/>
       <c r="N4" s="417"/>
       <c r="O4" s="418"/>
       <c r="P4" s="418"/>
-      <c r="Q4" s="1014" t="s">
+      <c r="Q4" s="1021" t="s">
         <v>283</v>
       </c>
-      <c r="R4" s="1014"/>
-      <c r="S4" s="1014"/>
-      <c r="T4" s="1014"/>
+      <c r="R4" s="1021"/>
+      <c r="S4" s="1021"/>
+      <c r="T4" s="1021"/>
       <c r="U4" s="191"/>
       <c r="V4" s="417"/>
       <c r="W4" s="191"/>
       <c r="X4" s="191"/>
     </row>
     <row r="5" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="943" t="s">
+      <c r="A5" s="942" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="945" t="s">
+      <c r="B5" s="944" t="s">
         <v>251</v>
       </c>
-      <c r="C5" s="945" t="s">
+      <c r="C5" s="944" t="s">
         <v>282</v>
       </c>
-      <c r="D5" s="1021" t="s">
+      <c r="D5" s="1000" t="s">
         <v>279</v>
       </c>
-      <c r="E5" s="1021" t="s">
+      <c r="E5" s="1000" t="s">
         <v>280</v>
       </c>
-      <c r="F5" s="1019" t="s">
+      <c r="F5" s="998" t="s">
         <v>243</v>
       </c>
-      <c r="G5" s="1016" t="s">
+      <c r="G5" s="995" t="s">
         <v>249</v>
       </c>
       <c r="I5" s="419" t="s">
@@ -42485,43 +43089,43 @@
       <c r="K5" s="421" t="s">
         <v>265</v>
       </c>
-      <c r="M5" s="1005" t="s">
+      <c r="M5" s="1012" t="s">
         <v>266</v>
       </c>
-      <c r="N5" s="1006"/>
-      <c r="O5" s="1007"/>
+      <c r="N5" s="1013"/>
+      <c r="O5" s="1014"/>
       <c r="P5" s="422"/>
-      <c r="Q5" s="1008" t="s">
+      <c r="Q5" s="1015" t="s">
         <v>7</v>
       </c>
-      <c r="R5" s="1010" t="s">
+      <c r="R5" s="1017" t="s">
         <v>267</v>
       </c>
-      <c r="S5" s="1011"/>
+      <c r="S5" s="1018"/>
       <c r="T5" s="452" t="s">
         <v>268</v>
       </c>
       <c r="U5" s="423" t="s">
         <v>269</v>
       </c>
-      <c r="V5" s="1012" t="s">
+      <c r="V5" s="1019" t="s">
         <v>277</v>
       </c>
-      <c r="W5" s="995" t="s">
+      <c r="W5" s="1002" t="s">
         <v>270</v>
       </c>
-      <c r="X5" s="997" t="s">
+      <c r="X5" s="1004" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1015"/>
-      <c r="B6" s="1018"/>
-      <c r="C6" s="1018"/>
-      <c r="D6" s="1022"/>
-      <c r="E6" s="1022"/>
-      <c r="F6" s="1020"/>
-      <c r="G6" s="1017"/>
+      <c r="A6" s="994"/>
+      <c r="B6" s="997"/>
+      <c r="C6" s="997"/>
+      <c r="D6" s="1001"/>
+      <c r="E6" s="1001"/>
+      <c r="F6" s="999"/>
+      <c r="G6" s="996"/>
       <c r="I6" s="424">
         <v>10</v>
       </c>
@@ -42540,7 +43144,7 @@
         <v>273</v>
       </c>
       <c r="P6" s="418"/>
-      <c r="Q6" s="1009"/>
+      <c r="Q6" s="1016"/>
       <c r="R6" s="448" t="s">
         <v>274</v>
       </c>
@@ -42553,9 +43157,9 @@
       <c r="U6" s="429" t="s">
         <v>275</v>
       </c>
-      <c r="V6" s="1013"/>
-      <c r="W6" s="996"/>
-      <c r="X6" s="998"/>
+      <c r="V6" s="1020"/>
+      <c r="W6" s="1003"/>
+      <c r="X6" s="1005"/>
     </row>
     <row r="7" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="715">
@@ -42872,27 +43476,27 @@
       <c r="A11" s="771">
         <v>5</v>
       </c>
-      <c r="B11" s="772" t="str">
+      <c r="B11" s="772">
         <f>IF('Entries October 2026'!N11-'Entries October 2026'!N10&lt;1,"0",'Entries October 2026'!N11-'Entries October 2026'!N10)</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="772" t="str">
+        <v>178.82000000000698</v>
+      </c>
+      <c r="C11" s="772">
         <f>IF('Entries October 2026'!L11-'Entries October 2026'!L10&lt;1,"0",'Entries October 2026'!L11-'Entries October 2026'!L10)</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="772" t="str">
+        <v>407.7899999999936</v>
+      </c>
+      <c r="D11" s="772">
         <f>IF('Entries October 2026'!M11-'Entries October 2026'!M10&lt;1,"0",'Entries October 2026'!M11-'Entries October 2026'!M10)</f>
-        <v>0</v>
+        <v>1583.3100000000559</v>
       </c>
       <c r="E11" s="772">
-        <v>0</v>
+        <v>1583</v>
       </c>
       <c r="F11" s="773">
-        <v>0</v>
-      </c>
-      <c r="G11" s="336" t="str">
+        <v>326.50200000000001</v>
+      </c>
+      <c r="G11" s="336">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4.8483623377498448</v>
       </c>
       <c r="I11" s="430">
         <v>60</v>
@@ -44842,27 +45446,27 @@
       </c>
       <c r="B38" s="713">
         <f>SUM(B7:B37)</f>
-        <v>340.44000000000233</v>
+        <v>519.26000000000931</v>
       </c>
       <c r="C38" s="713">
         <f>SUM(C7:C37)</f>
-        <v>1039.5400000000081</v>
+        <v>1447.3300000000017</v>
       </c>
       <c r="D38" s="713">
         <f>SUM(D7:D37)</f>
-        <v>2721.0999999999767</v>
+        <v>4304.4100000000326</v>
       </c>
       <c r="E38" s="713">
         <f>SUM(E7:E37)</f>
-        <v>2742</v>
+        <v>4325</v>
       </c>
       <c r="F38" s="714">
         <f>SUM(F7:F37)</f>
-        <v>651.10079999999994</v>
+        <v>977.60279999999989</v>
       </c>
       <c r="G38" s="345">
         <f>IF(F38=0,"0",(E38/F38))</f>
-        <v>4.2113294899960199</v>
+        <v>4.4240871650531286</v>
       </c>
       <c r="H38" s="348">
         <v>5</v>
@@ -45024,13 +45628,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="C5:C6"/>
     <mergeCell ref="W5:W6"/>
     <mergeCell ref="X5:X6"/>
     <mergeCell ref="I3:K3"/>
@@ -45040,13 +45637,20 @@
     <mergeCell ref="R5:S5"/>
     <mergeCell ref="V5:V6"/>
     <mergeCell ref="Q4:T4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="C5:C6"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="G7:G38">
-    <cfRule type="cellIs" dxfId="43" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="86" priority="1" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="85" priority="3" operator="greaterThan">
       <formula>21</formula>
     </cfRule>
   </conditionalFormatting>
@@ -45340,7 +45944,7 @@
         <v>31</v>
       </c>
       <c r="AG6" s="293"/>
-      <c r="AH6" s="895" t="s">
+      <c r="AH6" s="894" t="s">
         <v>216</v>
       </c>
       <c r="AI6" s="291"/>
@@ -45445,7 +46049,7 @@
       <c r="AG7" s="212" t="s">
         <v>19</v>
       </c>
-      <c r="AH7" s="895"/>
+      <c r="AH7" s="894"/>
       <c r="AI7" s="292" t="s">
         <v>229</v>
       </c>
@@ -45471,7 +46075,7 @@
       </c>
       <c r="F8" s="99">
         <f>'Daily KPIs'!F8</f>
-        <v>0</v>
+        <v>4947</v>
       </c>
       <c r="G8" s="99">
         <f>'Daily KPIs'!G8</f>
@@ -45573,14 +46177,14 @@
       </c>
       <c r="AG8" s="213">
         <f>SUM($B8:AF8)</f>
-        <v>4296</v>
+        <v>9243</v>
       </c>
       <c r="AH8" s="293">
         <v>96325</v>
       </c>
       <c r="AI8" s="294">
         <f>AG8-AH8</f>
-        <v>-92029</v>
+        <v>-87082</v>
       </c>
       <c r="AJ8" s="266"/>
       <c r="AK8" s="266"/>
@@ -45607,7 +46211,7 @@
       </c>
       <c r="F9" s="99">
         <f>'Daily KPIs'!F9</f>
-        <v>0</v>
+        <v>326.50200000000001</v>
       </c>
       <c r="G9" s="99">
         <f>'Daily KPIs'!G9</f>
@@ -45709,7 +46313,7 @@
       </c>
       <c r="AG9" s="215">
         <f>SUM($B9:AF9)</f>
-        <v>651.10079999999994</v>
+        <v>977.60279999999989</v>
       </c>
       <c r="AH9" s="214"/>
       <c r="AI9" s="265"/>
@@ -45734,9 +46338,9 @@
         <f>'Daily KPIs'!E10</f>
         <v>0</v>
       </c>
-      <c r="F10" s="163">
+      <c r="F10" s="163" t="str">
         <f>'Daily KPIs'!F10</f>
-        <v>0</v>
+        <v>CB</v>
       </c>
       <c r="G10" s="163">
         <f>'Daily KPIs'!G10</f>
@@ -45810,11 +46414,11 @@
         <f>'Daily KPIs'!X10</f>
         <v>0</v>
       </c>
-      <c r="Y10" s="1023">
+      <c r="Y10" s="1022">
         <f>'Daily KPIs'!Y10</f>
         <v>0</v>
       </c>
-      <c r="Z10" s="1023"/>
+      <c r="Z10" s="1022"/>
       <c r="AA10" s="163">
         <f>'Daily KPIs'!AA10</f>
         <v>0</v>
@@ -46181,9 +46785,9 @@
         <f>+'Water '!$D10</f>
         <v>64</v>
       </c>
-      <c r="F16" s="110" t="str">
+      <c r="F16" s="110">
         <f>+'Water '!$D11</f>
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G16" s="110" t="str">
         <f>+'Water '!$D12</f>
@@ -46291,7 +46895,7 @@
       </c>
       <c r="AG16" s="220">
         <f>SUM($B16:AF16)</f>
-        <v>251</v>
+        <v>324</v>
       </c>
       <c r="AH16" s="221"/>
     </row>
@@ -46315,9 +46919,9 @@
         <f>+'Water '!$E10</f>
         <v>0</v>
       </c>
-      <c r="F17" s="112" t="str">
+      <c r="F17" s="112">
         <f>+'Water '!$E11</f>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G17" s="112" t="str">
         <f>+'Water '!$E12</f>
@@ -46425,7 +47029,7 @@
       </c>
       <c r="AG17" s="222">
         <f>SUM($B17:AF17)</f>
-        <v>487</v>
+        <v>556</v>
       </c>
       <c r="AH17" s="223"/>
       <c r="AI17" s="268"/>
@@ -46452,7 +47056,7 @@
       </c>
       <c r="F18" s="118">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="G18" s="118">
         <f t="shared" si="0"/>
@@ -46560,7 +47164,7 @@
       </c>
       <c r="AG18" s="224">
         <f>SUM($B18:AF18)</f>
-        <v>738</v>
+        <v>880</v>
       </c>
       <c r="AH18" s="224"/>
       <c r="AI18" s="269"/>
@@ -46778,12 +47382,12 @@
       </c>
       <c r="AH21" s="225">
         <f>AG24+AG37+AG28</f>
-        <v>854</v>
+        <v>1242</v>
       </c>
       <c r="AI21" s="271"/>
       <c r="AJ21" s="272">
         <f>(AH21*10)/AG9</f>
-        <v>13.116248666873087</v>
+        <v>12.704546263574533</v>
       </c>
     </row>
     <row r="22" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -46983,7 +47587,7 @@
       </c>
       <c r="F24" s="112">
         <f>'Water '!H11</f>
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="G24" s="112">
         <f>'Water '!H12</f>
@@ -47091,7 +47695,7 @@
       </c>
       <c r="AG24" s="222">
         <f>SUM($B24:AF24)</f>
-        <v>531</v>
+        <v>717</v>
       </c>
       <c r="AH24" s="222"/>
       <c r="AI24" s="222"/>
@@ -47118,7 +47722,7 @@
       </c>
       <c r="F25" s="118">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="G25" s="118">
         <f t="shared" si="2"/>
@@ -47226,7 +47830,7 @@
       </c>
       <c r="AG25" s="224">
         <f>SUM($B25:AF25)</f>
-        <v>531</v>
+        <v>717</v>
       </c>
       <c r="AH25" s="224"/>
       <c r="AI25" s="269"/>
@@ -47251,9 +47855,9 @@
         <f>IF(E$9=0,"",+(E25*10)/E$9)</f>
         <v/>
       </c>
-      <c r="F26" s="125" t="str">
+      <c r="F26" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>5.6967491776466908</v>
       </c>
       <c r="G26" s="125" t="str">
         <f t="shared" si="3"/>
@@ -47425,9 +48029,9 @@
         <f>+'Water '!$J10</f>
         <v>0</v>
       </c>
-      <c r="F28" s="127" t="str">
+      <c r="F28" s="127">
         <f>+'Water '!$J11</f>
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="G28" s="127" t="str">
         <f>+'Water '!$J12</f>
@@ -47535,7 +48139,7 @@
       </c>
       <c r="AG28" s="220">
         <f>SUM($B28:AF28)</f>
-        <v>283</v>
+        <v>465</v>
       </c>
       <c r="AH28" s="220"/>
       <c r="AI28" s="271"/>
@@ -48004,9 +48608,9 @@
         <f>+'Water '!$N10</f>
         <v>0</v>
       </c>
-      <c r="F33" s="131" t="str">
+      <c r="F33" s="131">
         <f>+'Water '!$N11</f>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G33" s="131" t="str">
         <f>+'Water '!$N12</f>
@@ -48114,7 +48718,7 @@
       </c>
       <c r="AG33" s="227">
         <f>SUM($B33:AF33)</f>
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="AH33" s="227"/>
       <c r="AI33" s="227"/>
@@ -48143,9 +48747,9 @@
         <f>+'Water '!$O10</f>
         <v>0</v>
       </c>
-      <c r="F34" s="134" t="str">
+      <c r="F34" s="134">
         <f>+'Water '!$O11</f>
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="G34" s="134" t="str">
         <f>+'Water '!$O12</f>
@@ -48253,7 +48857,7 @@
       </c>
       <c r="AG34" s="228">
         <f>SUM($B34:AF34)</f>
-        <v>180</v>
+        <v>292</v>
       </c>
       <c r="AH34" s="228"/>
       <c r="AI34" s="228"/>
@@ -48280,7 +48884,7 @@
       </c>
       <c r="F35" s="119">
         <f>IF('Entries October 2026'!AC11-'Entries October 2026'!AC10&lt;1,0,'Entries October 2026'!AC11-'Entries October 2026'!AC10)</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G35" s="119">
         <f>IF('Entries October 2026'!AC12-'Entries October 2026'!AC11&lt;1,0,'Entries October 2026'!AC12-'Entries October 2026'!AC11)</f>
@@ -48388,7 +48992,7 @@
       </c>
       <c r="AG35" s="220">
         <f>SUM($B35:AF35)</f>
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="AH35" s="220"/>
       <c r="AI35" s="271"/>
@@ -48413,9 +49017,9 @@
         <f>+'Water '!$M10</f>
         <v>0</v>
       </c>
-      <c r="F36" s="110" t="str">
+      <c r="F36" s="110">
         <f>+'Water '!$M11</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" s="110" t="str">
         <f>+'Water '!$M12</f>
@@ -48523,7 +49127,7 @@
       </c>
       <c r="AG36" s="220">
         <f>SUM($B36:AF36)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH36" s="220"/>
       <c r="AI36" s="271"/>
@@ -48548,9 +49152,9 @@
         <f>+'Water '!$Q10</f>
         <v>2</v>
       </c>
-      <c r="F37" s="131" t="str">
+      <c r="F37" s="131">
         <f>+'Water '!$Q11</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G37" s="131" t="str">
         <f>+'Water '!$Q12</f>
@@ -48658,7 +49262,7 @@
       </c>
       <c r="AG37" s="227">
         <f>SUM($B37:AF37)</f>
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AH37" s="227"/>
       <c r="AI37" s="227"/>
@@ -49038,7 +49642,7 @@
       </c>
       <c r="F42" s="138">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>370</v>
       </c>
       <c r="G42" s="138">
         <f>SUM(G28:G41)</f>
@@ -49146,7 +49750,7 @@
       </c>
       <c r="AG42" s="230">
         <f>SUM($B42:AF42)</f>
-        <v>642</v>
+        <v>1012</v>
       </c>
       <c r="AH42" s="230"/>
       <c r="AI42" s="276"/>
@@ -49321,7 +49925,7 @@
       </c>
       <c r="F47" s="178">
         <f>IF('Entries October 2026'!M11-'Entries October 2026'!M10&lt;1,0,'Entries October 2026'!M11-'Entries October 2026'!M10)</f>
-        <v>0</v>
+        <v>1583.3100000000559</v>
       </c>
       <c r="G47" s="178" t="e">
         <f>IF('Entries October 2026'!#REF!-'Entries October 2026'!M11&lt;1,0,'Entries October 2026'!#REF!-'Entries October 2026'!M11)</f>
@@ -49493,9 +50097,9 @@
         <f>'Daily KPIs'!E76</f>
         <v>0</v>
       </c>
-      <c r="F49" s="187" t="str">
+      <c r="F49" s="187">
         <f>'Daily KPIs'!F76</f>
-        <v>0</v>
+        <v>178.82000000000698</v>
       </c>
       <c r="G49" s="187" t="str">
         <f>'Daily KPIs'!G76</f>
@@ -49603,7 +50207,7 @@
       </c>
       <c r="AG49" s="235">
         <f>SUM($B49:AF49)</f>
-        <v>340.44000000000233</v>
+        <v>519.26000000000931</v>
       </c>
       <c r="AH49" s="236"/>
       <c r="AI49" s="280"/>
@@ -49704,7 +50308,7 @@
       </c>
       <c r="F52" s="141">
         <f>'Elec.OCTOBER 2026'!$B$11</f>
-        <v>0</v>
+        <v>4774</v>
       </c>
       <c r="G52" s="141">
         <f>'Elec.OCTOBER 2026'!$B$12</f>
@@ -49812,7 +50416,7 @@
       </c>
       <c r="AG52" s="224">
         <f>SUM(B52:AC52)</f>
-        <v>22292</v>
+        <v>27066</v>
       </c>
       <c r="AH52" s="224"/>
       <c r="AI52" s="276"/>
@@ -50230,9 +50834,9 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="F59" s="144" t="str">
+      <c r="F59" s="144">
         <f t="shared" si="5"/>
-        <v/>
+        <v>4.3491310926119899</v>
       </c>
       <c r="G59" s="144" t="str">
         <f t="shared" si="5"/>
@@ -50340,7 +50944,7 @@
       </c>
       <c r="AG59" s="238">
         <f>IF(AG$9=0,"",+(AG18*10)/AG$9)</f>
-        <v>11.33465048729782</v>
+        <v>9.0016108791832448</v>
       </c>
       <c r="AH59" s="239">
         <f>'Daily KPIs'!AI90</f>
@@ -50348,7 +50952,7 @@
       </c>
       <c r="AI59" s="282">
         <f>+AH59-AG59</f>
-        <v>-1.1346504872978205</v>
+        <v>1.1983891208167545</v>
       </c>
       <c r="AJ59" s="270"/>
       <c r="AK59" s="270"/>
@@ -50395,9 +50999,9 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="F62" s="145" t="str">
+      <c r="F62" s="145">
         <f t="shared" si="8"/>
-        <v/>
+        <v>5.5742384426435363</v>
       </c>
       <c r="G62" s="145" t="str">
         <f t="shared" si="8"/>
@@ -50505,14 +51109,14 @@
       </c>
       <c r="AG62" s="241">
         <f>IF(+(AG28*10)/AG$9&lt;1,0,+(AG28*10)/AG$9)</f>
-        <v>4.3464852139637982</v>
+        <v>4.7565330213866002</v>
       </c>
       <c r="AH62" s="241">
         <v>2.5</v>
       </c>
       <c r="AI62" s="242">
         <f t="shared" ref="AI62:AI78" si="11">AH62-AG62</f>
-        <v>-1.8464852139637982</v>
+        <v>-2.2565330213866002</v>
       </c>
     </row>
     <row r="63" spans="1:37" ht="18.75" x14ac:dyDescent="0.3">
@@ -50645,14 +51249,14 @@
       </c>
       <c r="AG63" s="243">
         <f>IF(+(AG28*10)/AG$93&lt;1,0,+(AG28*10)/AG$93)</f>
-        <v>7.0661672908863924</v>
+        <v>11.610486891385769</v>
       </c>
       <c r="AH63" s="243">
         <v>2.5</v>
       </c>
       <c r="AI63" s="244">
         <f t="shared" si="11"/>
-        <v>-4.5661672908863924</v>
+        <v>-9.1104868913857686</v>
       </c>
     </row>
     <row r="64" spans="1:37" s="90" customFormat="1" ht="18" x14ac:dyDescent="0.25">
@@ -50675,9 +51279,9 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="F64" s="147" t="str">
+      <c r="F64" s="147">
         <f t="shared" si="14"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G64" s="147" t="str">
         <f t="shared" si="14"/>
@@ -50863,9 +51467,9 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="F66" s="145" t="str">
+      <c r="F66" s="145">
         <f t="shared" si="16"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G66" s="145" t="str">
         <f t="shared" si="16"/>
@@ -50975,9 +51579,9 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="F67" s="150" t="str">
+      <c r="F67" s="150">
         <f t="shared" si="18"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G67" s="150" t="str">
         <f t="shared" si="18"/>
@@ -51117,9 +51721,9 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="F68" s="145" t="str">
+      <c r="F68" s="145">
         <f t="shared" si="20"/>
-        <v/>
+        <v>1.1638519825299691</v>
       </c>
       <c r="G68" s="145" t="str">
         <f t="shared" si="20"/>
@@ -51227,14 +51831,14 @@
       </c>
       <c r="AG68" s="241">
         <f>+(AG33*10)/AG$9</f>
-        <v>1.5819363146228664</v>
+        <v>1.4423035613236788</v>
       </c>
       <c r="AH68" s="241">
         <v>0.7</v>
       </c>
       <c r="AI68" s="242">
         <f t="shared" si="11"/>
-        <v>-0.88193631462286648</v>
+        <v>-0.74230356132367881</v>
       </c>
     </row>
     <row r="69" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -51257,9 +51861,9 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="F69" s="145" t="str">
+      <c r="F69" s="145">
         <f t="shared" si="22"/>
-        <v/>
+        <v>3.4303005800883302</v>
       </c>
       <c r="G69" s="145" t="str">
         <f t="shared" si="22"/>
@@ -51367,14 +51971,14 @@
       </c>
       <c r="AG69" s="241">
         <f>+(AG34*10)/AG$9</f>
-        <v>2.764548899340932</v>
+        <v>2.9868981553653491</v>
       </c>
       <c r="AH69" s="241">
         <v>2.6</v>
       </c>
       <c r="AI69" s="242">
         <f t="shared" si="11"/>
-        <v>-0.16454889934093186</v>
+        <v>-0.38689815536534899</v>
       </c>
     </row>
     <row r="70" spans="1:37" ht="18.75" x14ac:dyDescent="0.3">
@@ -51534,9 +52138,9 @@
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="F71" s="145" t="str">
+      <c r="F71" s="145">
         <f t="shared" si="26"/>
-        <v/>
+        <v>0.52067062376340723</v>
       </c>
       <c r="G71" s="145" t="str">
         <f t="shared" si="26"/>
@@ -51644,14 +52248,14 @@
       </c>
       <c r="AG71" s="241">
         <f>+(AG35*10)/AG$9</f>
-        <v>0.4761167548864938</v>
+        <v>0.49099695704635876</v>
       </c>
       <c r="AH71" s="241">
         <v>0.7</v>
       </c>
       <c r="AI71" s="242">
         <f>AH71-AG71</f>
-        <v>0.22388324511350616</v>
+        <v>0.20900304295364119</v>
       </c>
     </row>
     <row r="72" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -51674,9 +52278,9 @@
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="F72" s="145" t="str">
+      <c r="F72" s="145">
         <f t="shared" si="29"/>
-        <v/>
+        <v>3.0627683750788663E-2</v>
       </c>
       <c r="G72" s="145" t="str">
         <f t="shared" si="29"/>
@@ -51784,14 +52388,14 @@
       </c>
       <c r="AG72" s="241">
         <f>+(AG36*10)/AG$9</f>
-        <v>7.6793024981692548E-2</v>
+        <v>6.1374619630794845E-2</v>
       </c>
       <c r="AH72" s="241">
         <v>0.1</v>
       </c>
       <c r="AI72" s="242">
         <f>AH72-AG72</f>
-        <v>2.3206975018307457E-2</v>
+        <v>3.862538036920516E-2</v>
       </c>
     </row>
     <row r="73" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -51814,9 +52418,9 @@
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="F73" s="145" t="str">
+      <c r="F73" s="145">
         <f t="shared" si="31"/>
-        <v/>
+        <v>0.61255367501577329</v>
       </c>
       <c r="G73" s="145" t="str">
         <f t="shared" si="31"/>
@@ -51924,14 +52528,14 @@
       </c>
       <c r="AG73" s="241">
         <f>+(AG37*10)/AG$9</f>
-        <v>0.61434419985354038</v>
+        <v>0.61374619630794847</v>
       </c>
       <c r="AH73" s="241">
         <v>0.6</v>
       </c>
       <c r="AI73" s="242">
         <f t="shared" si="11"/>
-        <v>-1.4344199853540407E-2</v>
+        <v>-1.3746196307948488E-2</v>
       </c>
     </row>
     <row r="74" spans="1:37" s="91" customFormat="1" ht="18" x14ac:dyDescent="0.25">
@@ -51954,9 +52558,9 @@
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="F74" s="150" t="str">
+      <c r="F74" s="150">
         <f t="shared" si="33"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G74" s="150" t="str">
         <f t="shared" si="33"/>
@@ -52096,9 +52700,9 @@
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="F75" s="145" t="str">
+      <c r="F75" s="145">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G75" s="145" t="str">
         <f t="shared" si="35"/>
@@ -52330,7 +52934,7 @@
       </c>
       <c r="F78" s="152">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>11.332242987791805</v>
       </c>
       <c r="G78" s="152">
         <f t="shared" si="37"/>
@@ -52438,7 +53042,7 @@
       </c>
       <c r="AG78" s="253">
         <f>SUM(AG62:AG77)</f>
-        <v>16.926391698535717</v>
+        <v>21.962339402446503</v>
       </c>
       <c r="AH78" s="253">
         <f t="shared" si="37"/>
@@ -52446,7 +53050,7 @@
       </c>
       <c r="AI78" s="253">
         <f t="shared" si="11"/>
-        <v>-1.3263916985357191</v>
+        <v>-6.362339402446505</v>
       </c>
       <c r="AJ78" s="210"/>
       <c r="AK78" s="210"/>
@@ -52473,7 +53077,7 @@
       </c>
       <c r="F79" s="154">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>3.9815988876025261</v>
       </c>
       <c r="G79" s="154">
         <f t="shared" si="38"/>
@@ -52581,7 +53185,7 @@
       </c>
       <c r="AG79" s="254">
         <f t="shared" si="38"/>
-        <v>3.3174586792091185</v>
+        <v>3.5392697320425026</v>
       </c>
       <c r="AH79" s="254">
         <f t="shared" si="38"/>
@@ -52589,7 +53193,7 @@
       </c>
       <c r="AI79" s="254">
         <f t="shared" si="38"/>
-        <v>2.6825413207908819</v>
+        <v>2.4607302679574974</v>
       </c>
       <c r="AJ79" s="285"/>
       <c r="AK79" s="285"/>
@@ -52614,9 +53218,9 @@
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="F80" s="155" t="str">
+      <c r="F80" s="155">
         <f t="shared" si="39"/>
-        <v/>
+        <v>4.8493117959462904</v>
       </c>
       <c r="G80" s="155" t="str">
         <f t="shared" si="39"/>
@@ -52757,9 +53361,9 @@
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="F81" s="157" t="str">
+      <c r="F81" s="157">
         <f t="shared" si="41"/>
-        <v/>
+        <v>0.54768424083162426</v>
       </c>
       <c r="G81" s="157" t="str">
         <f t="shared" si="41"/>
@@ -52867,7 +53471,7 @@
       </c>
       <c r="AG81" s="287">
         <f>IF(AG$9=0,"",+AG49/AG$9)</f>
-        <v>0.5228683484953518</v>
+        <v>0.53115641649145173</v>
       </c>
       <c r="AH81" s="287">
         <f>'Daily KPIs'!AI93</f>
@@ -52875,7 +53479,7 @@
       </c>
       <c r="AI81" s="286">
         <f>AH81-AG81</f>
-        <v>1.1771316515046482</v>
+        <v>1.1688435835085482</v>
       </c>
       <c r="AJ81" s="210"/>
       <c r="AK81" s="210"/>
@@ -52900,9 +53504,9 @@
         <f t="shared" si="43"/>
         <v/>
       </c>
-      <c r="F82" s="144" t="str">
+      <c r="F82" s="144">
         <f t="shared" si="43"/>
-        <v/>
+        <v>14.621656222626507</v>
       </c>
       <c r="G82" s="144" t="str">
         <f t="shared" si="43"/>
@@ -53010,7 +53614,7 @@
       </c>
       <c r="AG82" s="238">
         <f>+(AG52)/AG$9</f>
-        <v>34.237402257837807</v>
+        <v>27.686090915451555</v>
       </c>
       <c r="AH82" s="239">
         <f>'Daily KPIs'!AI94</f>
@@ -53018,7 +53622,7 @@
       </c>
       <c r="AI82" s="286">
         <f>AH82-AG82</f>
-        <v>-12.237402257837807</v>
+        <v>-5.6860909154515547</v>
       </c>
       <c r="AJ82" s="270"/>
       <c r="AK82" s="270"/>
@@ -53088,9 +53692,9 @@
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="F84" s="144" t="str">
+      <c r="F84" s="144">
         <f t="shared" si="46"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G84" s="144" t="str">
         <f>IF(G$9=0,"",G54/G$9)</f>
@@ -53198,7 +53802,7 @@
       </c>
       <c r="AG84" s="255">
         <f>+(AG54)/AG$9</f>
-        <v>1.4744260796484969</v>
+        <v>0.98199391409271752</v>
       </c>
       <c r="AH84" s="256">
         <f>'Daily KPIs'!AI96</f>
@@ -53206,7 +53810,7 @@
       </c>
       <c r="AI84" s="286">
         <f>AH84-AG84</f>
-        <v>5.7255739203515033</v>
+        <v>6.218006085907283</v>
       </c>
       <c r="AJ84" s="270"/>
       <c r="AK84" s="270"/>
@@ -53409,7 +54013,7 @@
       </c>
       <c r="F87" s="159">
         <f>IF('Entries October 2026'!L11-'Entries October 2026'!L10&lt;1,0,'Entries October 2026'!L11-'Entries October 2026'!L10)</f>
-        <v>0</v>
+        <v>407.7899999999936</v>
       </c>
       <c r="G87" s="159">
         <f>IF('Entries October 2026'!L12-'Entries October 2026'!L11&lt;1,0,'Entries October 2026'!L12-'Entries October 2026'!L11)</f>
@@ -53517,7 +54121,7 @@
       </c>
       <c r="AG87" s="220">
         <f>SUM($B87:AF87)</f>
-        <v>1039.5400000000081</v>
+        <v>1447.3300000000017</v>
       </c>
       <c r="AH87" s="220"/>
       <c r="AI87" s="271"/>
@@ -53584,9 +54188,9 @@
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="F89" s="160" t="str">
+      <c r="F89" s="160">
         <f t="shared" si="49"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G89" s="160" t="str">
         <f t="shared" si="49"/>
@@ -54622,7 +55226,7 @@
       </c>
       <c r="F101" s="159">
         <f>'Daily KPIs CO2'!F52</f>
-        <v>0</v>
+        <v>4774</v>
       </c>
       <c r="G101" s="159">
         <f>'Daily KPIs CO2'!G52</f>
@@ -54730,7 +55334,7 @@
       </c>
       <c r="AG101" s="263">
         <f>'Daily KPIs CO2'!AG52</f>
-        <v>22292</v>
+        <v>27066</v>
       </c>
       <c r="AH101" s="211"/>
       <c r="AI101" s="271"/>
@@ -54871,30 +55475,30 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B82:AF82">
-    <cfRule type="cellIs" dxfId="41" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="84" priority="3" operator="greaterThan">
       <formula>26</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B84:AF84">
-    <cfRule type="cellIs" dxfId="40" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="83" priority="4" operator="greaterThan">
       <formula>6.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D64:D65 D67 T69:AI70 D71 D73:D77">
-    <cfRule type="cellIs" dxfId="39" priority="5" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="82" priority="5" stopIfTrue="1" operator="greaterThan">
       <formula>3.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D69:S69 B70:S70">
-    <cfRule type="cellIs" dxfId="38" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="81" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>3.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI8">
-    <cfRule type="cellIs" dxfId="37" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="80" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="79" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/data/raw/October_26_Utilities_Tracking.xlsx
+++ b/data/raw/October_26_Utilities_Tracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UTILITIES\Tracking\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A259EF2-C984-4A33-A30F-104467CF8A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E195DE0C-E5FE-4C9B-9882-799333DE5E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="579" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
     <author>Alexander Dominguez-Ramon</author>
   </authors>
   <commentList>
-    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{BB566128-F737-494A-864E-AB446633861F}">
+    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{B9508B97-D489-4C75-97C6-F503E155CB62}">
       <text>
         <r>
           <rPr>
@@ -311,7 +311,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="310">
   <si>
     <t>UTILITY ANALYSIS</t>
   </si>
@@ -2872,6 +2872,9 @@
   </si>
   <si>
     <t>VM/VMg</t>
+  </si>
+  <si>
+    <t>CB/ST</t>
   </si>
 </sst>
 </file>
@@ -8384,15 +8387,69 @@
     <xf numFmtId="165" fontId="15" fillId="31" borderId="130" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="7" fillId="18" borderId="115" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="18" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="18" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="18" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="50" fillId="10" borderId="43" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="10" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="10" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="29" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="124" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="77" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="78" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="79" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="100" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="41" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8414,9 +8471,6 @@
     <xf numFmtId="0" fontId="19" fillId="4" borderId="42" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="41" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8432,45 +8486,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="124" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="77" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="78" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="79" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="100" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="10" borderId="43" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="10" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="10" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="29" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="118" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8588,15 +8603,39 @@
     <xf numFmtId="0" fontId="70" fillId="12" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="52" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="53" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="49" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8606,30 +8645,6 @@
     <xf numFmtId="0" fontId="19" fillId="4" borderId="33" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="52" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="53" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -8684,6 +8699,30 @@
     <xf numFmtId="2" fontId="17" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="47" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="72" fillId="18" borderId="56" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="72" fillId="18" borderId="123" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="32" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="32" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="122" fillId="16" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8744,43 +8783,7 @@
     <xf numFmtId="0" fontId="95" fillId="16" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="47" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="72" fillId="18" borderId="56" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="72" fillId="18" borderId="123" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="32" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="32" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="167" fontId="69" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="18" borderId="115" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="18" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="18" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="18" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -8792,7 +8795,27 @@
     <cellStyle name="Normal_February04" xfId="3" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
     <cellStyle name="Percent" xfId="4" builtinId="5"/>
   </cellStyles>
-  <dxfs count="162">
+  <dxfs count="164">
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color auto="1"/>
@@ -10562,7 +10585,7 @@
                   <c:v>7226</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>6606</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -10888,6 +10911,9 @@
                 <c:pt idx="5">
                   <c:v>1201.9000000000001</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>1346.2</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -11022,7 +11048,7 @@
                   <c:v>0.14260966551572754</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>0.16928648675838134</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -12502,53 +12528,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="18" x14ac:dyDescent="0.2">
-      <c r="B1" s="894" t="s">
+      <c r="B1" s="912" t="s">
         <v>209</v>
       </c>
-      <c r="C1" s="894"/>
-      <c r="D1" s="894"/>
-      <c r="E1" s="894"/>
-      <c r="F1" s="894"/>
-      <c r="G1" s="894"/>
-      <c r="H1" s="894"/>
-      <c r="I1" s="894"/>
-      <c r="J1" s="894"/>
-      <c r="K1" s="894"/>
-      <c r="L1" s="894"/>
-      <c r="M1" s="894"/>
+      <c r="C1" s="912"/>
+      <c r="D1" s="912"/>
+      <c r="E1" s="912"/>
+      <c r="F1" s="912"/>
+      <c r="G1" s="912"/>
+      <c r="H1" s="912"/>
+      <c r="I1" s="912"/>
+      <c r="J1" s="912"/>
+      <c r="K1" s="912"/>
+      <c r="L1" s="912"/>
+      <c r="M1" s="912"/>
       <c r="N1" s="363"/>
-      <c r="O1" s="895" t="str">
+      <c r="O1" s="913" t="str">
         <f>B1</f>
         <v>ENTRIES FOR DAILY CONS. MONITOR</v>
       </c>
-      <c r="P1" s="895"/>
-      <c r="Q1" s="895"/>
-      <c r="R1" s="895"/>
-      <c r="S1" s="895"/>
-      <c r="T1" s="895"/>
-      <c r="U1" s="895"/>
-      <c r="V1" s="895"/>
-      <c r="W1" s="895"/>
-      <c r="X1" s="895"/>
-      <c r="Y1" s="895"/>
-      <c r="Z1" s="895"/>
-      <c r="AA1" s="895"/>
-      <c r="AB1" s="895"/>
+      <c r="P1" s="913"/>
+      <c r="Q1" s="913"/>
+      <c r="R1" s="913"/>
+      <c r="S1" s="913"/>
+      <c r="T1" s="913"/>
+      <c r="U1" s="913"/>
+      <c r="V1" s="913"/>
+      <c r="W1" s="913"/>
+      <c r="X1" s="913"/>
+      <c r="Y1" s="913"/>
+      <c r="Z1" s="913"/>
+      <c r="AA1" s="913"/>
+      <c r="AB1" s="913"/>
     </row>
     <row r="2" spans="1:44" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C2" s="810"/>
       <c r="F2" s="364"/>
       <c r="G2" s="365"/>
-      <c r="O2" s="903" t="s">
+      <c r="O2" s="920" t="s">
         <v>231</v>
       </c>
-      <c r="P2" s="903"/>
-      <c r="Q2" s="903"/>
-      <c r="R2" s="903"/>
-      <c r="S2" s="903"/>
-      <c r="T2" s="903"/>
-      <c r="U2" s="903"/>
-      <c r="V2" s="903"/>
+      <c r="P2" s="920"/>
+      <c r="Q2" s="920"/>
+      <c r="R2" s="920"/>
+      <c r="S2" s="920"/>
+      <c r="T2" s="920"/>
+      <c r="U2" s="920"/>
+      <c r="V2" s="920"/>
     </row>
     <row r="3" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="366"/>
@@ -12566,50 +12592,50 @@
         <v>22</v>
       </c>
       <c r="K3" s="369"/>
-      <c r="L3" s="908" t="s">
+      <c r="L3" s="903" t="s">
         <v>53</v>
       </c>
-      <c r="M3" s="909"/>
-      <c r="N3" s="910"/>
-      <c r="O3" s="896" t="s">
+      <c r="M3" s="904"/>
+      <c r="N3" s="905"/>
+      <c r="O3" s="914" t="s">
         <v>3</v>
       </c>
-      <c r="P3" s="896"/>
-      <c r="Q3" s="896"/>
-      <c r="R3" s="896"/>
-      <c r="S3" s="896"/>
-      <c r="T3" s="896"/>
-      <c r="U3" s="896"/>
-      <c r="V3" s="896"/>
-      <c r="W3" s="896"/>
-      <c r="X3" s="896"/>
-      <c r="Y3" s="896"/>
-      <c r="Z3" s="896"/>
-      <c r="AA3" s="896"/>
-      <c r="AB3" s="896"/>
-      <c r="AC3" s="896"/>
+      <c r="P3" s="914"/>
+      <c r="Q3" s="914"/>
+      <c r="R3" s="914"/>
+      <c r="S3" s="914"/>
+      <c r="T3" s="914"/>
+      <c r="U3" s="914"/>
+      <c r="V3" s="914"/>
+      <c r="W3" s="914"/>
+      <c r="X3" s="914"/>
+      <c r="Y3" s="914"/>
+      <c r="Z3" s="914"/>
+      <c r="AA3" s="914"/>
+      <c r="AB3" s="914"/>
+      <c r="AC3" s="914"/>
       <c r="AD3" s="372"/>
       <c r="AE3" s="373"/>
       <c r="AF3" s="372"/>
-      <c r="AG3" s="916" t="s">
+      <c r="AG3" s="898" t="s">
         <v>206</v>
       </c>
-      <c r="AH3" s="914" t="s">
+      <c r="AH3" s="896" t="s">
         <v>204</v>
       </c>
-      <c r="AI3" s="914" t="s">
+      <c r="AI3" s="896" t="s">
         <v>205</v>
       </c>
-      <c r="AJ3" s="917" t="s">
+      <c r="AJ3" s="899" t="s">
         <v>233</v>
       </c>
       <c r="AK3" s="416"/>
-      <c r="AL3" s="918" t="s">
+      <c r="AL3" s="900" t="s">
         <v>178</v>
       </c>
-      <c r="AM3" s="918"/>
-      <c r="AN3" s="918"/>
-      <c r="AO3" s="918"/>
+      <c r="AM3" s="900"/>
+      <c r="AN3" s="900"/>
+      <c r="AO3" s="900"/>
     </row>
     <row r="4" spans="1:44" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="374"/>
@@ -12643,40 +12669,40 @@
       <c r="K4" s="372" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="904" t="s">
+      <c r="L4" s="921" t="s">
         <v>289</v>
       </c>
       <c r="M4" s="376" t="s">
         <v>260</v>
       </c>
-      <c r="N4" s="911" t="s">
+      <c r="N4" s="906" t="s">
         <v>167</v>
       </c>
-      <c r="O4" s="892" t="s">
+      <c r="O4" s="908" t="s">
         <v>100</v>
       </c>
-      <c r="P4" s="892" t="s">
+      <c r="P4" s="908" t="s">
         <v>101</v>
       </c>
-      <c r="Q4" s="892" t="s">
+      <c r="Q4" s="908" t="s">
         <v>160</v>
       </c>
-      <c r="R4" s="892" t="s">
+      <c r="R4" s="908" t="s">
         <v>171</v>
       </c>
-      <c r="S4" s="892" t="s">
+      <c r="S4" s="908" t="s">
         <v>102</v>
       </c>
-      <c r="T4" s="892" t="s">
+      <c r="T4" s="908" t="s">
         <v>172</v>
       </c>
-      <c r="U4" s="892" t="s">
+      <c r="U4" s="908" t="s">
         <v>103</v>
       </c>
-      <c r="V4" s="901" t="s">
+      <c r="V4" s="918" t="s">
         <v>236</v>
       </c>
-      <c r="W4" s="892" t="s">
+      <c r="W4" s="908" t="s">
         <v>177</v>
       </c>
       <c r="X4" s="372" t="s">
@@ -12688,28 +12714,28 @@
       <c r="Z4" s="372" t="s">
         <v>98</v>
       </c>
-      <c r="AA4" s="896" t="s">
+      <c r="AA4" s="914" t="s">
         <v>68</v>
       </c>
-      <c r="AB4" s="898" t="s">
+      <c r="AB4" s="916" t="s">
         <v>69</v>
       </c>
-      <c r="AC4" s="902" t="s">
+      <c r="AC4" s="919" t="s">
         <v>151</v>
       </c>
-      <c r="AD4" s="892" t="s">
+      <c r="AD4" s="908" t="s">
         <v>154</v>
       </c>
-      <c r="AE4" s="892" t="s">
+      <c r="AE4" s="908" t="s">
         <v>155</v>
       </c>
-      <c r="AF4" s="892" t="s">
+      <c r="AF4" s="908" t="s">
         <v>159</v>
       </c>
-      <c r="AG4" s="916"/>
-      <c r="AH4" s="915"/>
-      <c r="AI4" s="915"/>
-      <c r="AJ4" s="917"/>
+      <c r="AG4" s="898"/>
+      <c r="AH4" s="897"/>
+      <c r="AI4" s="897"/>
+      <c r="AJ4" s="899"/>
       <c r="AK4" s="416"/>
       <c r="AL4" s="378" t="s">
         <v>276</v>
@@ -12758,20 +12784,20 @@
       <c r="K5" s="465" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="905"/>
+      <c r="L5" s="922"/>
       <c r="M5" s="466" t="s">
         <v>261</v>
       </c>
-      <c r="N5" s="912"/>
-      <c r="O5" s="900"/>
-      <c r="P5" s="892"/>
-      <c r="Q5" s="892"/>
-      <c r="R5" s="892"/>
-      <c r="S5" s="900"/>
-      <c r="T5" s="900"/>
-      <c r="U5" s="900"/>
-      <c r="V5" s="901"/>
-      <c r="W5" s="913"/>
+      <c r="N5" s="907"/>
+      <c r="O5" s="909"/>
+      <c r="P5" s="908"/>
+      <c r="Q5" s="908"/>
+      <c r="R5" s="908"/>
+      <c r="S5" s="909"/>
+      <c r="T5" s="909"/>
+      <c r="U5" s="909"/>
+      <c r="V5" s="918"/>
+      <c r="W5" s="910"/>
       <c r="X5" s="372" t="s">
         <v>104</v>
       </c>
@@ -12781,16 +12807,16 @@
       <c r="Z5" s="372" t="s">
         <v>104</v>
       </c>
-      <c r="AA5" s="897"/>
-      <c r="AB5" s="899"/>
-      <c r="AC5" s="902"/>
-      <c r="AD5" s="892"/>
-      <c r="AE5" s="892"/>
-      <c r="AF5" s="893"/>
-      <c r="AG5" s="916"/>
-      <c r="AH5" s="915"/>
-      <c r="AI5" s="915"/>
-      <c r="AJ5" s="917"/>
+      <c r="AA5" s="915"/>
+      <c r="AB5" s="917"/>
+      <c r="AC5" s="919"/>
+      <c r="AD5" s="908"/>
+      <c r="AE5" s="908"/>
+      <c r="AF5" s="911"/>
+      <c r="AG5" s="898"/>
+      <c r="AH5" s="897"/>
+      <c r="AI5" s="897"/>
+      <c r="AJ5" s="899"/>
       <c r="AK5" s="416"/>
       <c r="AL5" s="378" t="s">
         <v>263</v>
@@ -13446,41 +13472,89 @@
       <c r="A13" s="378">
         <v>8</v>
       </c>
-      <c r="B13" s="815"/>
-      <c r="C13" s="816"/>
+      <c r="B13" s="815">
+        <v>8522020</v>
+      </c>
+      <c r="C13" s="816">
+        <v>1679130.4</v>
+      </c>
       <c r="D13" s="817"/>
-      <c r="E13" s="817"/>
-      <c r="F13" s="817"/>
-      <c r="G13" s="817"/>
+      <c r="E13" s="817">
+        <v>64</v>
+      </c>
+      <c r="F13" s="817">
+        <v>11357.9</v>
+      </c>
+      <c r="G13" s="817">
+        <v>68225</v>
+      </c>
       <c r="H13" s="818"/>
-      <c r="I13" s="819"/>
+      <c r="I13" s="819">
+        <v>1920264</v>
+      </c>
       <c r="J13" s="820"/>
-      <c r="K13" s="818"/>
-      <c r="L13" s="817"/>
-      <c r="M13" s="821"/>
-      <c r="N13" s="819"/>
-      <c r="O13" s="822"/>
-      <c r="P13" s="823"/>
-      <c r="Q13" s="817"/>
+      <c r="K13" s="818">
+        <v>468000</v>
+      </c>
+      <c r="L13" s="817">
+        <v>88837.55</v>
+      </c>
+      <c r="M13" s="821">
+        <v>637569.31000000006</v>
+      </c>
+      <c r="N13" s="819">
+        <v>85576.66</v>
+      </c>
+      <c r="O13" s="822">
+        <v>253802</v>
+      </c>
+      <c r="P13" s="823">
+        <v>86571</v>
+      </c>
+      <c r="Q13" s="817">
+        <v>990642</v>
+      </c>
       <c r="R13" s="817"/>
-      <c r="S13" s="817"/>
+      <c r="S13" s="817">
+        <v>98159</v>
+      </c>
       <c r="T13" s="817"/>
-      <c r="U13" s="817"/>
-      <c r="V13" s="824"/>
+      <c r="U13" s="817">
+        <v>550</v>
+      </c>
+      <c r="V13" s="824">
+        <v>1366929</v>
+      </c>
       <c r="W13" s="817"/>
-      <c r="X13" s="825"/>
-      <c r="Y13" s="817"/>
-      <c r="Z13" s="817"/>
-      <c r="AA13" s="817"/>
+      <c r="X13" s="825">
+        <v>49360</v>
+      </c>
+      <c r="Y13" s="817">
+        <v>71255</v>
+      </c>
+      <c r="Z13" s="817">
+        <v>15789</v>
+      </c>
+      <c r="AA13" s="817">
+        <v>97122</v>
+      </c>
       <c r="AB13" s="817"/>
-      <c r="AC13" s="817"/>
-      <c r="AD13" s="817"/>
+      <c r="AC13" s="817">
+        <v>6832</v>
+      </c>
+      <c r="AD13" s="817">
+        <v>263787</v>
+      </c>
       <c r="AE13" s="817"/>
       <c r="AF13" s="819"/>
-      <c r="AG13" s="817"/>
+      <c r="AG13" s="817" t="s">
+        <v>55</v>
+      </c>
       <c r="AH13" s="817"/>
       <c r="AI13" s="817"/>
-      <c r="AJ13" s="880"/>
+      <c r="AJ13" s="880">
+        <v>7383613.8779999996</v>
+      </c>
       <c r="AK13" s="192"/>
       <c r="AL13" s="459"/>
       <c r="AM13" s="457"/>
@@ -14575,8 +14649,8 @@
     <row r="38" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B38" s="190"/>
       <c r="G38" s="190"/>
-      <c r="I38" s="906"/>
-      <c r="J38" s="906"/>
+      <c r="I38" s="901"/>
+      <c r="J38" s="901"/>
       <c r="R38" s="190"/>
       <c r="S38" s="190"/>
       <c r="T38" s="190"/>
@@ -14584,8 +14658,8 @@
       <c r="V38" s="190"/>
       <c r="W38" s="190"/>
       <c r="Z38" s="190"/>
-      <c r="AA38" s="907"/>
-      <c r="AB38" s="907"/>
+      <c r="AA38" s="902"/>
+      <c r="AB38" s="902"/>
       <c r="AC38" s="190"/>
       <c r="AD38" s="190"/>
       <c r="AI38" s="380"/>
@@ -16251,19 +16325,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="AH3:AH5"/>
-    <mergeCell ref="AG3:AG5"/>
-    <mergeCell ref="AI3:AI5"/>
-    <mergeCell ref="AJ3:AJ5"/>
-    <mergeCell ref="AL3:AO3"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="AA38:AB38"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="S4:S5"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="P4:P5"/>
-    <mergeCell ref="W4:W5"/>
     <mergeCell ref="AF4:AF5"/>
     <mergeCell ref="AE4:AE5"/>
     <mergeCell ref="AD4:AD5"/>
@@ -16280,281 +16341,304 @@
     <mergeCell ref="AC4:AC5"/>
     <mergeCell ref="O2:V2"/>
     <mergeCell ref="L4:L5"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="AA38:AB38"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="S4:S5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="P4:P5"/>
+    <mergeCell ref="W4:W5"/>
+    <mergeCell ref="AH3:AH5"/>
+    <mergeCell ref="AG3:AG5"/>
+    <mergeCell ref="AI3:AI5"/>
+    <mergeCell ref="AJ3:AJ5"/>
+    <mergeCell ref="AL3:AO3"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
-  <conditionalFormatting sqref="B13:B35">
-    <cfRule type="expression" dxfId="160" priority="72">
-      <formula>B13&lt;B12</formula>
+  <conditionalFormatting sqref="B14:B35">
+    <cfRule type="expression" dxfId="162" priority="74">
+      <formula>B14&lt;B13</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C13:D14">
-    <cfRule type="expression" dxfId="156" priority="79">
-      <formula>C13&lt;C12</formula>
+  <conditionalFormatting sqref="C14:D14">
+    <cfRule type="expression" dxfId="158" priority="82">
+      <formula>C14&lt;C13</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36:D37">
-    <cfRule type="expression" dxfId="155" priority="1247">
+    <cfRule type="expression" dxfId="157" priority="1293">
       <formula>C36&lt;C35</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D35 B36:B37">
-    <cfRule type="expression" dxfId="154" priority="1234">
+    <cfRule type="expression" dxfId="156" priority="1280">
       <formula>B35&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E13:E14">
-    <cfRule type="expression" dxfId="153" priority="49">
-      <formula>E13&lt;E12</formula>
+  <conditionalFormatting sqref="E14">
+    <cfRule type="expression" dxfId="155" priority="51">
+      <formula>E14&lt;E13</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F13:F37">
-    <cfRule type="expression" dxfId="152" priority="48">
-      <formula>F13&lt;#REF!</formula>
+  <conditionalFormatting sqref="F14:F37">
+    <cfRule type="expression" dxfId="154" priority="50">
+      <formula>F14&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G13:G37">
-    <cfRule type="expression" dxfId="151" priority="46">
-      <formula>G13&lt;G12</formula>
+  <conditionalFormatting sqref="G14:G37">
+    <cfRule type="expression" dxfId="153" priority="48">
+      <formula>G14&lt;G13</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G36:J37 L36:O37">
-    <cfRule type="expression" dxfId="150" priority="1081">
+    <cfRule type="expression" dxfId="152" priority="1127">
       <formula>G36&lt;G35</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H19:I34">
-    <cfRule type="expression" dxfId="148" priority="195">
+    <cfRule type="expression" dxfId="150" priority="241">
       <formula>H19&lt;H18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H35:I35 R35 T35 W35 AB35 AE35:AI35 P36:P37 S36:S37 X36:Y37">
-    <cfRule type="expression" dxfId="147" priority="1233">
+    <cfRule type="expression" dxfId="149" priority="1279">
       <formula>H35&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H13:J18">
-    <cfRule type="expression" dxfId="146" priority="80">
-      <formula>H13&lt;H12</formula>
+  <conditionalFormatting sqref="H14:J18">
+    <cfRule type="expression" dxfId="148" priority="83">
+      <formula>H14&lt;H13</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J19:J35">
-    <cfRule type="expression" dxfId="145" priority="196">
+    <cfRule type="expression" dxfId="147" priority="242">
       <formula>J19&lt;J18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K13:L21">
-    <cfRule type="expression" dxfId="144" priority="83">
-      <formula>K13&lt;K12</formula>
+  <conditionalFormatting sqref="K14:L21">
+    <cfRule type="expression" dxfId="146" priority="86">
+      <formula>K14&lt;K13</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K22:M22">
-    <cfRule type="expression" dxfId="143" priority="197">
+    <cfRule type="expression" dxfId="145" priority="243">
       <formula>K22&lt;K21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K23:Z23 K24:K37">
-    <cfRule type="expression" dxfId="141" priority="198">
+    <cfRule type="expression" dxfId="143" priority="244">
       <formula>K23&lt;K22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L24:Z27 L28:AC28">
-    <cfRule type="expression" dxfId="140" priority="200">
+    <cfRule type="expression" dxfId="142" priority="246">
       <formula>L24&lt;L23</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M13:M17">
-    <cfRule type="expression" dxfId="139" priority="85">
-      <formula>M13&lt;#REF!</formula>
+  <conditionalFormatting sqref="M14:M17">
+    <cfRule type="expression" dxfId="141" priority="88">
+      <formula>M14&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N13:T22">
-    <cfRule type="expression" dxfId="137" priority="191">
-      <formula>N13&lt;N12</formula>
+  <conditionalFormatting sqref="N14:T22">
+    <cfRule type="expression" dxfId="139" priority="237">
+      <formula>N14&lt;N13</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q36">
-    <cfRule type="expression" dxfId="133" priority="1250">
+    <cfRule type="expression" dxfId="135" priority="1296">
       <formula>Q36&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R36">
-    <cfRule type="expression" dxfId="129" priority="1246">
+    <cfRule type="expression" dxfId="131" priority="1292">
       <formula>R36&lt;R35</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB13:AI27">
-    <cfRule type="expression" dxfId="128" priority="77">
-      <formula>AB13&lt;AB12</formula>
+  <conditionalFormatting sqref="AB14:AI27">
+    <cfRule type="expression" dxfId="130" priority="80">
+      <formula>AB14&lt;AB13</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U13:U22">
-    <cfRule type="expression" dxfId="126" priority="53">
-      <formula>U13&lt;U12</formula>
+  <conditionalFormatting sqref="U14:U22">
+    <cfRule type="expression" dxfId="128" priority="55">
+      <formula>U14&lt;U13</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V13:X14 C15:E34 C35 E35:E37">
-    <cfRule type="expression" dxfId="124" priority="194">
-      <formula>C13&lt;C12</formula>
+  <conditionalFormatting sqref="V14:X14 C15:E34 C35 E35:E37">
+    <cfRule type="expression" dxfId="126" priority="240">
+      <formula>C14&lt;C13</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V15:Z22 M18:M21">
-    <cfRule type="expression" dxfId="123" priority="193">
+    <cfRule type="expression" dxfId="125" priority="239">
       <formula>M15&lt;M14</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V29:AC29 AA30:AC30 Z30:Z31 V30:Y34 AA31:AB31 AC31:AC37 Z32:AB34 V35 X35:AA35">
-    <cfRule type="expression" dxfId="122" priority="204">
+    <cfRule type="expression" dxfId="124" priority="250">
       <formula>V29&lt;V28</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y13:Z14">
-    <cfRule type="expression" dxfId="120" priority="70">
-      <formula>Y13&lt;Y12</formula>
+  <conditionalFormatting sqref="Y14:Z14">
+    <cfRule type="expression" dxfId="122" priority="72">
+      <formula>Y14&lt;Y13</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA13:AA37">
-    <cfRule type="expression" dxfId="118" priority="45">
-      <formula>AA13&lt;AA12</formula>
+  <conditionalFormatting sqref="AA14:AA37">
+    <cfRule type="expression" dxfId="120" priority="47">
+      <formula>AA14&lt;AA13</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA28:AA37">
-    <cfRule type="expression" dxfId="117" priority="202">
+    <cfRule type="expression" dxfId="119" priority="248">
       <formula>AA28&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD28:AD37">
-    <cfRule type="expression" dxfId="115" priority="199">
+    <cfRule type="expression" dxfId="117" priority="245">
       <formula>AD28&lt;AD27</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE28:AI34 L29:T34 U29:U37 L35:Q35 S35">
-    <cfRule type="expression" dxfId="112" priority="203">
+    <cfRule type="expression" dxfId="114" priority="249">
       <formula>L28&lt;L27</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AJ13:AJ37">
-    <cfRule type="expression" dxfId="111" priority="47">
-      <formula>AJ13&lt;AJ12</formula>
+  <conditionalFormatting sqref="AJ14:AJ37">
+    <cfRule type="expression" dxfId="113" priority="49">
+      <formula>AJ14&lt;AJ13</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK6:AK12">
-    <cfRule type="expression" dxfId="110" priority="1123">
+    <cfRule type="expression" dxfId="112" priority="1169">
       <formula>AK6&lt;AK5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK13:AL15">
-    <cfRule type="expression" dxfId="109" priority="1203">
+    <cfRule type="expression" dxfId="111" priority="1249">
       <formula>AK13&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL9:AL14 AL15:AN34 AK16:AK37 AK20:AN21 T36:W37 Z36:Z37 AB36:AB37 AE36:AI37 Q37:R37">
-    <cfRule type="expression" dxfId="108" priority="1140">
+    <cfRule type="expression" dxfId="110" priority="1186">
       <formula>Q9&lt;Q8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO9:AO34">
-    <cfRule type="expression" dxfId="107" priority="1148">
+    <cfRule type="expression" dxfId="109" priority="1194">
       <formula>AO9&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7:B12">
-    <cfRule type="expression" dxfId="43" priority="28">
+  <conditionalFormatting sqref="B7:B13">
+    <cfRule type="expression" dxfId="45" priority="28">
       <formula>B7&lt;B6</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B11:B12">
-    <cfRule type="expression" dxfId="42" priority="44">
+  <conditionalFormatting sqref="B11:B13">
+    <cfRule type="expression" dxfId="44" priority="45">
       <formula>B11&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7:D7 H7:J7 R7 T7 W7 AB7">
-    <cfRule type="expression" dxfId="41" priority="32">
+    <cfRule type="expression" dxfId="43" priority="32">
       <formula>C7&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C8:D12">
-    <cfRule type="expression" dxfId="40" priority="36">
+  <conditionalFormatting sqref="C8:D13">
+    <cfRule type="expression" dxfId="42" priority="36">
       <formula>C8&lt;C7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E7:E12">
-    <cfRule type="expression" dxfId="39" priority="18">
+  <conditionalFormatting sqref="E7:E13">
+    <cfRule type="expression" dxfId="41" priority="18">
       <formula>E7&lt;E6</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F12">
-    <cfRule type="expression" dxfId="38" priority="33">
+  <conditionalFormatting sqref="F7:F13">
+    <cfRule type="expression" dxfId="40" priority="33">
       <formula>F7&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G7:G12">
-    <cfRule type="expression" dxfId="37" priority="29">
+  <conditionalFormatting sqref="G7:G13">
+    <cfRule type="expression" dxfId="39" priority="29">
       <formula>G7&lt;G6</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H8:J12">
-    <cfRule type="expression" dxfId="36" priority="37">
+  <conditionalFormatting sqref="H8:J13">
+    <cfRule type="expression" dxfId="38" priority="37">
       <formula>H8&lt;H7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K11:L12">
-    <cfRule type="expression" dxfId="35" priority="40">
+  <conditionalFormatting sqref="K11:L13">
+    <cfRule type="expression" dxfId="37" priority="40">
       <formula>K11&lt;K10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7:O8 K9:N10 O9">
-    <cfRule type="expression" dxfId="34" priority="23">
+    <cfRule type="expression" dxfId="36" priority="23">
       <formula>K7&lt;K6</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M11:M12">
-    <cfRule type="expression" dxfId="33" priority="42">
+  <conditionalFormatting sqref="M11:M13">
+    <cfRule type="expression" dxfId="35" priority="42">
       <formula>M11&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N11:O12 O10">
-    <cfRule type="expression" dxfId="32" priority="41">
+    <cfRule type="expression" dxfId="34" priority="41">
       <formula>N10&lt;N9</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="N13:T13">
+    <cfRule type="expression" dxfId="33" priority="44">
+      <formula>N13&lt;N12</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="S7:S10">
-    <cfRule type="expression" dxfId="31" priority="22">
+    <cfRule type="expression" dxfId="32" priority="22">
       <formula>S7&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P8:P12 V8:V12">
-    <cfRule type="expression" dxfId="30" priority="39">
+    <cfRule type="expression" dxfId="31" priority="39">
       <formula>P8&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P7:Q7">
-    <cfRule type="expression" dxfId="29" priority="30">
+    <cfRule type="expression" dxfId="30" priority="30">
       <formula>P7&lt;P6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q8:R8">
-    <cfRule type="expression" dxfId="28" priority="38">
+    <cfRule type="expression" dxfId="29" priority="38">
       <formula>Q8&lt;Q7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q11:T12 Q9:R10 T9:T10">
-    <cfRule type="expression" dxfId="27" priority="43">
+    <cfRule type="expression" dxfId="28" priority="43">
       <formula>Q9&lt;Q8</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T8 AB11:AI12 AB8:AC10 AE8:AI10">
-    <cfRule type="expression" dxfId="26" priority="34">
+  <conditionalFormatting sqref="T8 AB11:AI13 AB8:AC10 AE8:AI10">
+    <cfRule type="expression" dxfId="27" priority="34">
       <formula>T8&lt;T7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U7:U12">
-    <cfRule type="expression" dxfId="25" priority="20">
+  <conditionalFormatting sqref="U7:U13">
+    <cfRule type="expression" dxfId="26" priority="20">
       <formula>U7&lt;U6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V7">
-    <cfRule type="expression" dxfId="24" priority="25">
+    <cfRule type="expression" dxfId="25" priority="25">
       <formula>V7&lt;V6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V13:X13">
+    <cfRule type="expression" dxfId="24" priority="46">
+      <formula>V13&lt;V12</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W8:W12">
@@ -16562,7 +16646,7 @@
       <formula>W8&lt;W7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y7:Z12">
+  <conditionalFormatting sqref="Y7:Z13">
     <cfRule type="expression" dxfId="22" priority="26">
       <formula>Y7&lt;Y6</formula>
     </cfRule>
@@ -16572,7 +16656,7 @@
       <formula>AA7&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA7:AA12">
+  <conditionalFormatting sqref="AA7:AA13">
     <cfRule type="expression" dxfId="20" priority="24">
       <formula>AA7&lt;AA6</formula>
     </cfRule>
@@ -16587,7 +16671,7 @@
       <formula>X7&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AJ12">
+  <conditionalFormatting sqref="AJ12:AJ13">
     <cfRule type="expression" dxfId="17" priority="31">
       <formula>AJ12&lt;AJ11</formula>
     </cfRule>
@@ -16712,8 +16796,7 @@
     <col min="11" max="11" width="29.7109375" style="469" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="30.5703125" style="469" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="29.7109375" style="470" hidden="1" customWidth="1"/>
-    <col min="14" max="32" width="29.7109375" style="469" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="29.7109375" style="469" customWidth="1"/>
+    <col min="14" max="33" width="29.7109375" style="469" hidden="1" customWidth="1"/>
     <col min="34" max="34" width="29.7109375" style="468" customWidth="1"/>
     <col min="35" max="35" width="24.7109375" style="468" customWidth="1"/>
     <col min="36" max="36" width="24.7109375" style="291" customWidth="1"/>
@@ -16743,8 +16826,8 @@
       </c>
       <c r="B3" s="468"/>
       <c r="C3" s="468"/>
-      <c r="K3" s="891"/>
-      <c r="L3" s="891"/>
+      <c r="K3" s="895"/>
+      <c r="L3" s="895"/>
       <c r="M3" s="498"/>
       <c r="AH3" s="291"/>
       <c r="AI3" s="291"/>
@@ -16890,7 +16973,7 @@
         <v>31</v>
       </c>
       <c r="AG6" s="291"/>
-      <c r="AI6" s="890" t="s">
+      <c r="AI6" s="894" t="s">
         <v>216</v>
       </c>
     </row>
@@ -16995,7 +17078,7 @@
       <c r="AH7" s="477" t="s">
         <v>19</v>
       </c>
-      <c r="AI7" s="890"/>
+      <c r="AI7" s="894"/>
       <c r="AJ7" s="292" t="s">
         <v>229</v>
       </c>
@@ -17046,7 +17129,9 @@
       <c r="G8" s="678">
         <v>5412</v>
       </c>
-      <c r="H8" s="678"/>
+      <c r="H8" s="678">
+        <v>6158</v>
+      </c>
       <c r="I8" s="678"/>
       <c r="J8" s="678"/>
       <c r="K8" s="678"/>
@@ -17074,14 +17159,14 @@
       <c r="AG8" s="747"/>
       <c r="AH8" s="480">
         <f>SUM(B8:AG8)</f>
-        <v>20139</v>
+        <v>26297</v>
       </c>
       <c r="AI8" s="526">
         <v>123950</v>
       </c>
       <c r="AJ8" s="294">
         <f>AH8-AI8</f>
-        <v>-103811</v>
+        <v>-97653</v>
       </c>
       <c r="AK8" s="481"/>
       <c r="AL8" s="481"/>
@@ -17116,7 +17201,7 @@
         <v>367.56479999999999</v>
       </c>
       <c r="C9" s="678">
-        <f t="shared" ref="C9:G9" si="0">C8*0.066</f>
+        <f t="shared" ref="C9:H9" si="0">C8*0.066</f>
         <v>283.536</v>
       </c>
       <c r="D9" s="678">
@@ -17136,8 +17221,8 @@
         <v>357.19200000000001</v>
       </c>
       <c r="H9" s="678">
-        <f>H8*0.066</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>406.428</v>
       </c>
       <c r="I9" s="678">
         <f>I8*0.066</f>
@@ -17229,7 +17314,7 @@
       <c r="AG9" s="748"/>
       <c r="AH9" s="484">
         <f>SUM(B9:AG9)</f>
-        <v>1334.7947999999999</v>
+        <v>1741.2228</v>
       </c>
       <c r="AI9" s="484"/>
       <c r="AL9" s="291" t="s">
@@ -17255,7 +17340,9 @@
       <c r="G10" s="770" t="s">
         <v>307</v>
       </c>
-      <c r="H10" s="871"/>
+      <c r="H10" s="770" t="s">
+        <v>307</v>
+      </c>
       <c r="I10" s="871"/>
       <c r="J10" s="871"/>
       <c r="K10" s="871"/>
@@ -17477,8 +17564,12 @@
       </c>
       <c r="D12" s="494"/>
       <c r="E12" s="494"/>
-      <c r="F12" s="494"/>
-      <c r="G12" s="494"/>
+      <c r="F12" s="494">
+        <v>397.8</v>
+      </c>
+      <c r="G12" s="494">
+        <v>446.2</v>
+      </c>
       <c r="H12" s="494"/>
       <c r="I12" s="494"/>
       <c r="J12" s="494"/>
@@ -17506,7 +17597,7 @@
       <c r="AG12" s="494"/>
       <c r="AH12" s="495">
         <f>SUM(B12:AF12)</f>
-        <v>400.5</v>
+        <v>1244.5</v>
       </c>
       <c r="AI12" s="496"/>
       <c r="AJ12" s="469"/>
@@ -17526,8 +17617,12 @@
       </c>
       <c r="D13" s="669"/>
       <c r="E13" s="799"/>
-      <c r="F13" s="798"/>
-      <c r="G13" s="669"/>
+      <c r="F13" s="669" t="s">
+        <v>307</v>
+      </c>
+      <c r="G13" s="669" t="s">
+        <v>309</v>
+      </c>
       <c r="H13" s="682"/>
       <c r="I13" s="752"/>
       <c r="J13" s="669"/>
@@ -17576,8 +17671,13 @@
       </c>
       <c r="D14" s="498"/>
       <c r="E14" s="498"/>
-      <c r="F14" s="498"/>
-      <c r="G14" s="498"/>
+      <c r="F14" s="498">
+        <v>8</v>
+      </c>
+      <c r="G14" s="498">
+        <f>4+5</f>
+        <v>9</v>
+      </c>
       <c r="H14" s="498"/>
       <c r="I14" s="498"/>
       <c r="J14" s="498"/>
@@ -17605,7 +17705,7 @@
       <c r="AG14" s="498"/>
       <c r="AH14" s="468">
         <f>SUM(B14:AF14)</f>
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:149" s="504" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -17646,7 +17746,7 @@
       <c r="AG15" s="718"/>
       <c r="AH15" s="500">
         <f>IF(AH12=0,"",+(AH36*10)/AH12)</f>
-        <v>17.45318352059925</v>
+        <v>7.4407392527119329</v>
       </c>
       <c r="AI15" s="502"/>
       <c r="AJ15" s="503"/>
@@ -18004,9 +18104,9 @@
         <f>+'Water '!$D12</f>
         <v>250</v>
       </c>
-      <c r="H20" s="508" t="str">
+      <c r="H20" s="508">
         <f>+'Water '!$D13</f>
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="I20" s="508" t="str">
         <f>+'Water '!$D14</f>
@@ -18107,7 +18207,7 @@
       <c r="AG20" s="509"/>
       <c r="AH20" s="484">
         <f>SUM($B20:AF20)</f>
-        <v>574</v>
+        <v>808</v>
       </c>
       <c r="AI20" s="484"/>
       <c r="AJ20" s="485"/>
@@ -18140,9 +18240,9 @@
         <f>+'Water '!$E12</f>
         <v>92</v>
       </c>
-      <c r="H21" s="511" t="str">
+      <c r="H21" s="511">
         <f>+'Water '!$E13</f>
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="I21" s="511" t="str">
         <f>+'Water '!$E14</f>
@@ -18243,7 +18343,7 @@
       <c r="AG21" s="509"/>
       <c r="AH21" s="484">
         <f>SUM($B21:AF21)</f>
-        <v>648</v>
+        <v>795</v>
       </c>
       <c r="AI21" s="484"/>
     </row>
@@ -18277,7 +18377,7 @@
       </c>
       <c r="H22" s="514">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="I22" s="514">
         <f>SUM(I19:I21)</f>
@@ -18378,7 +18478,7 @@
       <c r="AG22" s="515"/>
       <c r="AH22" s="516">
         <f>SUM($B22:AF22)</f>
-        <v>1222</v>
+        <v>1603</v>
       </c>
       <c r="AI22" s="514"/>
       <c r="AJ22" s="517"/>
@@ -18641,7 +18741,7 @@
       </c>
       <c r="H26" s="485">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>110.23</v>
       </c>
       <c r="I26" s="485">
         <f t="shared" si="4"/>
@@ -18742,15 +18842,15 @@
       <c r="AG26" s="521"/>
       <c r="AH26" s="484">
         <f>SUM($B26:AF26)</f>
-        <v>541.66</v>
+        <v>651.89</v>
       </c>
       <c r="AI26" s="523">
         <f>AH29+AH45+AH36</f>
-        <v>1695</v>
+        <v>2157</v>
       </c>
       <c r="AK26" s="524">
         <f>(AI26*10)/AH9</f>
-        <v>12.698581085272433</v>
+        <v>12.387846058528524</v>
       </c>
     </row>
     <row r="27" spans="1:149" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -18929,7 +19029,7 @@
       </c>
       <c r="H29" s="508">
         <f>'Water '!H13</f>
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="I29" s="508">
         <f>'Water '!H14</f>
@@ -19030,7 +19130,7 @@
       <c r="AG29" s="509"/>
       <c r="AH29" s="484">
         <f>SUM($B29:AF29)</f>
-        <v>920</v>
+        <v>1139</v>
       </c>
       <c r="AI29" s="484"/>
       <c r="AJ29" s="484"/>
@@ -19064,9 +19164,9 @@
         <f t="shared" si="5"/>
         <v>234</v>
       </c>
-      <c r="H30" s="508" t="str">
+      <c r="H30" s="508">
         <f>H36</f>
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="I30" s="508" t="str">
         <f t="shared" si="5"/>
@@ -19167,7 +19267,7 @@
       <c r="AG30" s="509"/>
       <c r="AH30" s="484">
         <f>AH36</f>
-        <v>699</v>
+        <v>926</v>
       </c>
       <c r="AI30" s="484"/>
       <c r="AJ30" s="484"/>
@@ -19201,9 +19301,9 @@
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="H31" s="508" t="str">
+      <c r="H31" s="508">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I31" s="508" t="str">
         <f t="shared" si="6"/>
@@ -19304,7 +19404,7 @@
       <c r="AG31" s="509"/>
       <c r="AH31" s="484">
         <f>AH45</f>
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="AI31" s="484"/>
       <c r="AJ31" s="484"/>
@@ -19339,7 +19439,7 @@
       </c>
       <c r="H32" s="526">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>462</v>
       </c>
       <c r="I32" s="526">
         <f t="shared" si="7"/>
@@ -19440,7 +19540,7 @@
       <c r="AG32" s="527"/>
       <c r="AH32" s="526">
         <f>SUM($B32:AF32)</f>
-        <v>1695</v>
+        <v>2157</v>
       </c>
       <c r="AI32" s="526"/>
       <c r="AJ32" s="528"/>
@@ -19613,9 +19713,9 @@
         <f>+'Water '!$J12</f>
         <v>234</v>
       </c>
-      <c r="H36" s="508" t="str">
+      <c r="H36" s="508">
         <f>+'Water '!$J13</f>
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="I36" s="535" t="str">
         <f>+'Water '!$J14</f>
@@ -19716,7 +19816,7 @@
       <c r="AG36" s="508"/>
       <c r="AH36" s="484">
         <f>SUM($B36:AF36)</f>
-        <v>699</v>
+        <v>926</v>
       </c>
       <c r="AI36" s="484"/>
     </row>
@@ -20423,9 +20523,9 @@
         <f>+'Water '!$N12</f>
         <v>39</v>
       </c>
-      <c r="H41" s="539" t="str">
+      <c r="H41" s="539">
         <f>+'Water '!$N13</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I41" s="539" t="str">
         <f>+'Water '!$N14</f>
@@ -20526,7 +20626,7 @@
       <c r="AG41" s="539"/>
       <c r="AH41" s="514">
         <f>SUM($B41:AF41)</f>
-        <v>180</v>
+        <v>230</v>
       </c>
       <c r="AI41" s="514"/>
       <c r="AJ41" s="514"/>
@@ -20672,9 +20772,9 @@
         <f>+'Water '!$O12</f>
         <v>99</v>
       </c>
-      <c r="H42" s="508" t="str">
+      <c r="H42" s="508">
         <f>+'Water '!$O13</f>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="I42" s="508" t="str">
         <f>+'Water '!$O14</f>
@@ -20775,7 +20875,7 @@
       <c r="AG42" s="508"/>
       <c r="AH42" s="540">
         <f>SUM($B42:AF42)</f>
-        <v>391</v>
+        <v>482</v>
       </c>
       <c r="AI42" s="508"/>
       <c r="AJ42" s="508"/>
@@ -20916,8 +21016,8 @@
       <c r="G43" s="542">
         <v>17</v>
       </c>
-      <c r="H43" s="542" t="str">
-        <v>0</v>
+      <c r="H43" s="542">
+        <v>17</v>
       </c>
       <c r="I43" s="542" t="str">
         <v>0</v>
@@ -20994,7 +21094,7 @@
       <c r="AG43" s="542"/>
       <c r="AH43" s="543">
         <f>SUM($B43:AF43)</f>
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="AI43" s="544"/>
       <c r="AJ43" s="474"/>
@@ -21140,9 +21240,9 @@
         <f>+'Water '!$M12</f>
         <v>3</v>
       </c>
-      <c r="H44" s="508" t="str">
+      <c r="H44" s="508">
         <f>+'Water '!$M13</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I44" s="508" t="str">
         <f>+'Water '!$M14</f>
@@ -21243,7 +21343,7 @@
       <c r="AG44" s="508"/>
       <c r="AH44" s="484">
         <f>SUM($B44:AF44)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AI44" s="484"/>
       <c r="AJ44" s="291"/>
@@ -21389,9 +21489,9 @@
         <f>+'Water '!$Q12</f>
         <v>16</v>
       </c>
-      <c r="H45" s="539" t="str">
+      <c r="H45" s="539">
         <f>+'Water '!$Q13</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I45" s="539" t="str">
         <f>+'Water '!$Q14</f>
@@ -21492,7 +21592,7 @@
       <c r="AG45" s="539"/>
       <c r="AH45" s="514">
         <f>SUM($B45:AF45)</f>
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="AI45" s="514"/>
       <c r="AJ45" s="514"/>
@@ -22106,7 +22206,7 @@
       </c>
       <c r="H50" s="484">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="I50" s="484">
         <f t="shared" si="8"/>
@@ -22207,7 +22307,7 @@
       <c r="AG50" s="484"/>
       <c r="AH50" s="484">
         <f>SUM($B50:AF50)</f>
-        <v>1420</v>
+        <v>1824</v>
       </c>
       <c r="AI50" s="484"/>
     </row>
@@ -22327,9 +22427,9 @@
         <f>IF(G$9=0,"",+(G36*10)/G$9)</f>
         <v>6.5510985688369283</v>
       </c>
-      <c r="H54" s="545" t="str">
+      <c r="H54" s="545">
         <f>IF(H$9=0,"",+(H36*10)/H$9)</f>
-        <v/>
+        <v>5.5852451110651824</v>
       </c>
       <c r="I54" s="545" t="str">
         <f t="shared" ref="I54:AF54" si="10">IF(I$9=0,"",+(I36*10)/I$9)</f>
@@ -22430,14 +22530,14 @@
       <c r="AG54" s="545"/>
       <c r="AH54" s="546">
         <f>+(AH36*10)/AH$9</f>
-        <v>5.2367599873778357</v>
+        <v>5.3181017386172522</v>
       </c>
       <c r="AI54" s="546">
         <v>3.2</v>
       </c>
       <c r="AJ54" s="547">
         <f t="shared" ref="AJ54:AJ67" si="11">AI54-AH54</f>
-        <v>-2.0367599873778355</v>
+        <v>-2.118101738617252</v>
       </c>
     </row>
     <row r="55" spans="1:59" s="553" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -22539,9 +22639,9 @@
         <f t="shared" ref="G56:H63" si="15">IF(G$9=0,"",+(G38*10)/G$9)</f>
         <v>0</v>
       </c>
-      <c r="H56" s="545" t="str">
+      <c r="H56" s="545">
         <f t="shared" si="15"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I56" s="545" t="str">
         <f t="shared" ref="I56:AF56" si="16">IF(I$9=0,"",+(I38*10)/I$9)</f>
@@ -22703,9 +22803,9 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="H57" s="549" t="str">
+      <c r="H57" s="549">
         <f t="shared" si="15"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I57" s="549" t="str">
         <f t="shared" ref="I57:AE57" si="19">IF(I$9=0,"",+(I39*10)/I$9)</f>
@@ -22867,9 +22967,9 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="H58" s="545" t="str">
+      <c r="H58" s="545">
         <f t="shared" si="15"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I58" s="545" t="str">
         <f t="shared" ref="I58:AF58" si="20">IF(I$9=0,"",+(I40*10)/I$9)</f>
@@ -23033,9 +23133,9 @@
         <f t="shared" si="15"/>
         <v>1.0918497614728213</v>
       </c>
-      <c r="H59" s="549" t="str">
+      <c r="H59" s="549">
         <f t="shared" si="15"/>
-        <v/>
+        <v>1.2302302006751504</v>
       </c>
       <c r="I59" s="549" t="str">
         <f t="shared" ref="I59:AF59" si="21">IF(I$9=0,"",+(I41*10)/I$9)</f>
@@ -23136,14 +23236,14 @@
       <c r="AG59" s="549"/>
       <c r="AH59" s="549">
         <f t="shared" si="12"/>
-        <v>1.3485218851616745</v>
+        <v>1.3209107990086049</v>
       </c>
       <c r="AI59" s="550">
         <v>0.7</v>
       </c>
       <c r="AJ59" s="551">
         <f t="shared" si="11"/>
-        <v>-0.64852188516167453</v>
+        <v>-0.62091079900860491</v>
       </c>
       <c r="AK59" s="474"/>
       <c r="AL59" s="474"/>
@@ -23197,9 +23297,9 @@
         <f t="shared" si="15"/>
         <v>2.7716186252771617</v>
       </c>
-      <c r="H60" s="545" t="str">
+      <c r="H60" s="545">
         <f t="shared" si="15"/>
-        <v/>
+        <v>2.2390189652287735</v>
       </c>
       <c r="I60" s="545" t="str">
         <f t="shared" ref="I60:AF60" si="22">IF(I$9=0,"",+(I42*10)/I$9)</f>
@@ -23300,14 +23400,14 @@
       <c r="AG60" s="545"/>
       <c r="AH60" s="568">
         <f t="shared" si="12"/>
-        <v>2.9292892061011928</v>
+        <v>2.768169587487598</v>
       </c>
       <c r="AI60" s="555">
         <v>2.1</v>
       </c>
       <c r="AJ60" s="547">
         <f t="shared" si="11"/>
-        <v>-0.82928920610119272</v>
+        <v>-0.66816958748759792</v>
       </c>
     </row>
     <row r="61" spans="1:59" s="504" customFormat="1" x14ac:dyDescent="0.35">
@@ -23338,9 +23438,9 @@
         <f t="shared" si="15"/>
         <v>0.47593451141122983</v>
       </c>
-      <c r="H61" s="549" t="str">
+      <c r="H61" s="549">
         <f t="shared" si="15"/>
-        <v/>
+        <v>0.41827826822955111</v>
       </c>
       <c r="I61" s="549" t="str">
         <f t="shared" ref="I61:AF61" si="23">IF(I$9=0,"",+(I43*10)/I$9)</f>
@@ -23441,14 +23541,14 @@
       <c r="AG61" s="549"/>
       <c r="AH61" s="550">
         <f t="shared" si="12"/>
-        <v>0.48696623630838243</v>
+        <v>0.47093341529871996</v>
       </c>
       <c r="AI61" s="550">
         <v>0.7</v>
       </c>
       <c r="AJ61" s="551">
         <f t="shared" si="11"/>
-        <v>0.21303376369161753</v>
+        <v>0.22906658470128</v>
       </c>
       <c r="AK61" s="474"/>
       <c r="AL61" s="474"/>
@@ -23502,9 +23602,9 @@
         <f t="shared" si="15"/>
         <v>8.3988443190217019E-2</v>
       </c>
-      <c r="H62" s="545" t="str">
+      <c r="H62" s="545">
         <f t="shared" si="15"/>
-        <v/>
+        <v>7.3813812040509019E-2</v>
       </c>
       <c r="I62" s="545" t="str">
         <f t="shared" ref="I62:AF62" si="24">IF(I$9=0,"",+(I44*10)/I$9)</f>
@@ -23605,14 +23705,14 @@
       <c r="AG62" s="545"/>
       <c r="AH62" s="555">
         <f>+(AH44*10)/AH$9</f>
-        <v>6.7426094258083713E-2</v>
+        <v>6.8917085165666331E-2</v>
       </c>
       <c r="AI62" s="555">
         <v>0.1</v>
       </c>
       <c r="AJ62" s="547">
         <f t="shared" si="11"/>
-        <v>3.2573905741916293E-2</v>
+        <v>3.1082914834333675E-2</v>
       </c>
     </row>
     <row r="63" spans="1:59" s="504" customFormat="1" x14ac:dyDescent="0.35">
@@ -23643,9 +23743,9 @@
         <f t="shared" si="15"/>
         <v>0.44793836368115747</v>
       </c>
-      <c r="H63" s="569" t="str">
+      <c r="H63" s="569">
         <f t="shared" si="15"/>
-        <v/>
+        <v>0.3936736642160481</v>
       </c>
       <c r="I63" s="569" t="str">
         <f t="shared" si="25"/>
@@ -23746,14 +23846,14 @@
       <c r="AG63" s="549"/>
       <c r="AH63" s="550">
         <f>+(AH45*10)/AH$9</f>
-        <v>0.56937590706826258</v>
+        <v>0.52836431960344188</v>
       </c>
       <c r="AI63" s="550">
         <v>0.6</v>
       </c>
       <c r="AJ63" s="551">
         <f t="shared" si="11"/>
-        <v>3.0624092931737401E-2</v>
+        <v>7.1635680396558099E-2</v>
       </c>
       <c r="AK63" s="474"/>
       <c r="AL63" s="474"/>
@@ -23875,9 +23975,9 @@
         <f>IF(G$9=0,"",+(G46*10)/G$9)</f>
         <v>0</v>
       </c>
-      <c r="H65" s="549" t="str">
+      <c r="H65" s="549">
         <f>IF(H$9=0,"",+(H46*10)/H$9)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I65" s="549" t="str">
         <f t="shared" si="26"/>
@@ -24177,7 +24277,7 @@
       </c>
       <c r="H68" s="584">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>9.940260021455213</v>
       </c>
       <c r="I68" s="584">
         <f t="shared" si="27"/>
@@ -24278,7 +24378,7 @@
       <c r="AG68" s="585"/>
       <c r="AH68" s="584">
         <f t="shared" si="27"/>
-        <v>10.638339316275433</v>
+        <v>10.475396945181283</v>
       </c>
       <c r="AI68" s="584">
         <f>SUM(AI54:AI63,AI65)</f>
@@ -24286,7 +24386,7 @@
       </c>
       <c r="AJ68" s="547">
         <f t="shared" si="27"/>
-        <v>-1.0383393162754313</v>
+        <v>-0.87539694518128286</v>
       </c>
       <c r="AK68" s="468"/>
       <c r="AL68" s="291"/>
@@ -24342,7 +24442,7 @@
       </c>
       <c r="H69" s="587">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>2.7311110454988334</v>
       </c>
       <c r="I69" s="587">
         <f t="shared" si="28"/>
@@ -24443,7 +24543,7 @@
       <c r="AG69" s="588"/>
       <c r="AH69" s="587">
         <f t="shared" si="28"/>
-        <v>3.483681536667659</v>
+        <v>3.3080200879519843</v>
       </c>
       <c r="AI69" s="587">
         <f t="shared" si="28"/>
@@ -24451,7 +24551,7 @@
       </c>
       <c r="AJ69" s="587">
         <f t="shared" si="28"/>
-        <v>-0.58368153666765887</v>
+        <v>-0.40802008795198424</v>
       </c>
       <c r="AK69" s="589"/>
       <c r="AL69" s="291"/>
@@ -24540,9 +24640,9 @@
         <f>+'Water '!$F12</f>
         <v>169</v>
       </c>
-      <c r="H71" s="592" t="str">
+      <c r="H71" s="592">
         <f>+'Water '!$F13</f>
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="I71" s="592" t="str">
         <f>+'Water '!$F14</f>
@@ -24643,7 +24743,7 @@
       <c r="AG71" s="593"/>
       <c r="AH71" s="594">
         <f>SUM($B71:AF71)</f>
-        <v>742</v>
+        <v>893</v>
       </c>
       <c r="AI71" s="594"/>
       <c r="AJ71" s="595"/>
@@ -24770,7 +24870,9 @@
       <c r="G74" s="790">
         <v>1504</v>
       </c>
-      <c r="H74" s="790"/>
+      <c r="H74" s="790">
+        <v>1416</v>
+      </c>
       <c r="I74" s="790"/>
       <c r="J74" s="791"/>
       <c r="K74" s="877"/>
@@ -24798,7 +24900,7 @@
       <c r="AG74" s="790"/>
       <c r="AH74" s="516">
         <f>SUM(B74:AF74)</f>
-        <v>5829</v>
+        <v>7245</v>
       </c>
       <c r="AI74" s="537"/>
       <c r="AJ74" s="537"/>
@@ -24849,8 +24951,8 @@
       <c r="G75" s="601">
         <v>1503.5599999999395</v>
       </c>
-      <c r="H75" s="601" t="str">
-        <v>0</v>
+      <c r="H75" s="601">
+        <v>1416.1900000000605</v>
       </c>
       <c r="I75" s="601" t="str">
         <v>0</v>
@@ -24927,7 +25029,7 @@
       <c r="AG75" s="599"/>
       <c r="AH75" s="516">
         <f>SUM(B75:AF75)</f>
-        <v>5807.9699999999721</v>
+        <v>7224.1600000000326</v>
       </c>
       <c r="AI75" s="600"/>
       <c r="AJ75" s="600"/>
@@ -24977,8 +25079,8 @@
       <c r="G76" s="604">
         <v>201.50999999999476</v>
       </c>
-      <c r="H76" s="604" t="str">
-        <v>0</v>
+      <c r="H76" s="604">
+        <v>220.41000000000349</v>
       </c>
       <c r="I76" s="604" t="str">
         <v>0</v>
@@ -25055,7 +25157,7 @@
       <c r="AG76" s="604"/>
       <c r="AH76" s="604">
         <f>SUM($B76:AF76)</f>
-        <v>720.77000000000407</v>
+        <v>941.18000000000757</v>
       </c>
       <c r="AI76" s="605"/>
       <c r="AJ76" s="606"/>
@@ -25106,8 +25208,8 @@
       <c r="G77" s="785">
         <v>467.24000000000524</v>
       </c>
-      <c r="H77" s="785" t="str">
-        <v>0</v>
+      <c r="H77" s="785">
+        <v>304.72000000000116</v>
       </c>
       <c r="I77" s="785" t="str">
         <v>0</v>
@@ -25184,7 +25286,7 @@
       <c r="AG77" s="607"/>
       <c r="AH77" s="604">
         <f>SUM($B77:AF77)</f>
-        <v>1914.570000000007</v>
+        <v>2219.2900000000081</v>
       </c>
       <c r="AI77" s="757"/>
       <c r="AJ77" s="757" t="s">
@@ -25243,7 +25345,7 @@
       </c>
       <c r="H78" s="788">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>891.06000000005588</v>
       </c>
       <c r="I78" s="788">
         <f t="shared" si="29"/>
@@ -25347,7 +25449,7 @@
       </c>
       <c r="AH78" s="484">
         <f>AH75-AH76-AH77</f>
-        <v>3172.629999999961</v>
+        <v>4063.6900000000169</v>
       </c>
       <c r="AI78" s="484"/>
     </row>
@@ -25504,7 +25606,7 @@
         <v>7226</v>
       </c>
       <c r="H80" s="612">
-        <v>0</v>
+        <v>6606</v>
       </c>
       <c r="I80" s="612">
         <v>0</v>
@@ -25581,7 +25683,7 @@
       <c r="AG80" s="613"/>
       <c r="AH80" s="594">
         <f>SUM(B80:AF80)</f>
-        <v>34292</v>
+        <v>40898</v>
       </c>
       <c r="AI80" s="594"/>
       <c r="AJ80" s="614"/>
@@ -25694,7 +25796,7 @@
         <v>8427.9</v>
       </c>
       <c r="F82" s="614">
-        <v>0</v>
+        <v>7952.2</v>
       </c>
       <c r="G82" s="614">
         <v>0</v>
@@ -25769,7 +25871,7 @@
         <v>0</v>
       </c>
       <c r="AE82" s="617">
-        <v>41039.599999999999</v>
+        <v>48991.799999999996</v>
       </c>
       <c r="AF82" s="617">
         <v>0</v>
@@ -25777,7 +25879,7 @@
       <c r="AG82" s="617"/>
       <c r="AH82" s="594">
         <f>SUM(B82:AF82)</f>
-        <v>64992.4</v>
+        <v>80896.800000000003</v>
       </c>
       <c r="AI82" s="594"/>
       <c r="AJ82" s="614"/>
@@ -25829,7 +25931,7 @@
         <v>1201.9000000000001</v>
       </c>
       <c r="H83" s="594">
-        <v>0</v>
+        <v>1346.2</v>
       </c>
       <c r="I83" s="594">
         <v>0</v>
@@ -25906,7 +26008,7 @@
       <c r="AG83" s="621"/>
       <c r="AH83" s="594">
         <f>SUM(B83:AF83)</f>
-        <v>6747.6</v>
+        <v>8093.8</v>
       </c>
       <c r="AI83" s="594"/>
       <c r="AJ83" s="594"/>
@@ -25957,8 +26059,8 @@
       <c r="G84" s="619">
         <v>2654.6999999999534</v>
       </c>
-      <c r="H84" s="619" t="str">
-        <v>0</v>
+      <c r="H84" s="619">
+        <v>2750.5999999998603</v>
       </c>
       <c r="I84" s="619" t="str">
         <v>0</v>
@@ -26035,7 +26137,7 @@
       <c r="AG84" s="620"/>
       <c r="AH84" s="621">
         <f>SUM($B84:AF84)</f>
-        <v>12131.800000000047</v>
+        <v>14882.399999999907</v>
       </c>
       <c r="AI84" s="594"/>
       <c r="AJ84" s="614"/>
@@ -26436,9 +26538,9 @@
         <f>IF(G$9=0,"",+(G22*10)/G$9)</f>
         <v>9.574682523684741</v>
       </c>
-      <c r="H90" s="653" t="str">
+      <c r="H90" s="653">
         <f>IF(H$9=0,"",+(H22*10)/H$9)</f>
-        <v/>
+        <v>9.3743541291446455</v>
       </c>
       <c r="I90" s="653" t="str">
         <f t="shared" si="33"/>
@@ -26539,18 +26641,18 @@
       <c r="AG90" s="627"/>
       <c r="AH90" s="659">
         <f>IF(AH$9=0,"0",+(AH22*10)/AH$9)</f>
-        <v>9.1549652425975889</v>
+        <v>9.2061739600469288</v>
       </c>
       <c r="AI90" s="662">
         <v>10.199999999999999</v>
       </c>
       <c r="AJ90" s="665">
         <f>+AI90-AH90</f>
-        <v>1.0450347574024104</v>
+        <v>0.99382603995307051</v>
       </c>
       <c r="AK90" s="667">
         <f>AH90/AI90*100</f>
-        <v>89.75456120193715</v>
+        <v>90.256607451440487</v>
       </c>
       <c r="AL90" s="629"/>
       <c r="AM90" s="630"/>
@@ -26670,9 +26772,9 @@
         <f>IF(G$9=0,"",+G74/G$9)</f>
         <v>4.2106206186028805</v>
       </c>
-      <c r="H92" s="653" t="str">
+      <c r="H92" s="653">
         <f>IF(H$9=0,"",+H74/H$9)</f>
-        <v/>
+        <v>3.4840119283120257</v>
       </c>
       <c r="I92" s="653" t="str">
         <f t="shared" si="35"/>
@@ -26773,18 +26875,18 @@
       <c r="AG92" s="628"/>
       <c r="AH92" s="670">
         <f>IF(AH$9=0,"0",+(AH74)/AH$9)</f>
-        <v>4.3669633714485556</v>
+        <v>4.160869016877105</v>
       </c>
       <c r="AI92" s="674">
         <v>5</v>
       </c>
       <c r="AJ92" s="675">
         <f>AI92-AH92</f>
-        <v>0.63303662855144438</v>
+        <v>0.83913098312289502</v>
       </c>
       <c r="AK92" s="673">
         <f t="shared" si="34"/>
-        <v>87.339267428971112</v>
+        <v>83.217380337542096</v>
       </c>
       <c r="AL92" s="629"/>
       <c r="AM92" s="630"/>
@@ -26839,9 +26941,9 @@
         <f>IF(G$9=0,"",+G76/G$9)</f>
         <v>0.56415037290867309</v>
       </c>
-      <c r="H93" s="653" t="str">
+      <c r="H93" s="653">
         <f>IF(H$9=0,"",+H76/H$9)</f>
-        <v/>
+        <v>0.54231007706162837</v>
       </c>
       <c r="I93" s="653" t="str">
         <f t="shared" si="36"/>
@@ -26942,18 +27044,18 @@
       <c r="AG93" s="628"/>
       <c r="AH93" s="670">
         <f>IF(AH$9=0,"0",+AH76/AH$9)</f>
-        <v>0.53998562175999198</v>
+        <v>0.5405281851351863</v>
       </c>
       <c r="AI93" s="674">
         <v>1.7</v>
       </c>
       <c r="AJ93" s="676">
         <f>AI93-AH93</f>
-        <v>1.1600143782400081</v>
+        <v>1.1594718148648138</v>
       </c>
       <c r="AK93" s="673">
         <f t="shared" si="34"/>
-        <v>31.763860103528941</v>
+        <v>31.795775596187433</v>
       </c>
       <c r="AL93" s="635"/>
       <c r="AM93" s="636"/>
@@ -27006,9 +27108,9 @@
         <f>IF(G$9=0,"",(G80+G83)/G$9)</f>
         <v>23.594873345427668</v>
       </c>
-      <c r="H94" s="653" t="str">
+      <c r="H94" s="653">
         <f>IF(H$9=0,"",(H80+H83)/H$9)</f>
-        <v/>
+        <v>19.566073203617862</v>
       </c>
       <c r="I94" s="653" t="str">
         <f t="shared" si="37"/>
@@ -27109,18 +27211,18 @@
       <c r="AG94" s="627"/>
       <c r="AH94" s="670">
         <f>IF(AH$9=0,"0",+(AH80+AH83)/AH$9)</f>
-        <v>30.74599931015614</v>
+        <v>28.136433775160768</v>
       </c>
       <c r="AI94" s="674">
         <v>22</v>
       </c>
       <c r="AJ94" s="675">
         <f>AI94-AH94</f>
-        <v>-8.7459993101561402</v>
+        <v>-6.1364337751607678</v>
       </c>
       <c r="AK94" s="673">
         <f>AH94/AI94*100</f>
-        <v>139.75454231889154</v>
+        <v>127.89288079618531</v>
       </c>
       <c r="AL94" s="629"/>
       <c r="AM94" s="630"/>
@@ -27180,7 +27282,7 @@
       <c r="AG95" s="637"/>
       <c r="AH95" s="670">
         <f>IF(AH$9=0,"0",+(AH78*10)/AH$9)</f>
-        <v>23.768672158446837</v>
+        <v>23.338139151405649</v>
       </c>
       <c r="AI95" s="674"/>
       <c r="AJ95" s="676"/>
@@ -27239,9 +27341,9 @@
         <f>IF(G$9=0,"",G84/G$9)</f>
         <v>7.4321373379021738</v>
       </c>
-      <c r="H96" s="654" t="str">
+      <c r="H96" s="654">
         <f>IF(H$9=0,"",H84/H$9)</f>
-        <v/>
+        <v>6.767742379953793</v>
       </c>
       <c r="I96" s="654" t="str">
         <f t="shared" si="38"/>
@@ -27342,18 +27444,18 @@
       <c r="AG96" s="627"/>
       <c r="AH96" s="660">
         <f>IF(AH$9=0,"0",+(AH84)/AH$9)</f>
-        <v>9.0888876702247021</v>
+        <v>8.5470969022458849</v>
       </c>
       <c r="AI96" s="663">
         <v>7.2</v>
       </c>
       <c r="AJ96" s="677">
         <f>AI96-AH96</f>
-        <v>-1.8888876702247019</v>
+        <v>-1.3470969022458847</v>
       </c>
       <c r="AK96" s="668">
         <f t="shared" si="34"/>
-        <v>126.23455097534308</v>
+        <v>118.70967919785951</v>
       </c>
       <c r="AL96" s="629"/>
       <c r="AM96" s="630"/>
@@ -28296,7 +28398,7 @@
       </c>
       <c r="H116" s="649">
         <f>'Daily KPIs'!H80</f>
-        <v>0</v>
+        <v>6606</v>
       </c>
       <c r="I116" s="649">
         <f>'Daily KPIs'!I80</f>
@@ -28397,7 +28499,7 @@
       <c r="AG116" s="650"/>
       <c r="AH116" s="649">
         <f>'Daily KPIs'!AH80</f>
-        <v>34292</v>
+        <v>40898</v>
       </c>
     </row>
     <row r="117" spans="2:34" hidden="1" x14ac:dyDescent="0.35">
@@ -28487,7 +28589,7 @@
       </c>
       <c r="AH140" s="870">
         <f>AH83/(AH83+AH80)</f>
-        <v>0.16441680718135657</v>
+        <v>0.16520723876240512</v>
       </c>
       <c r="AM140" s="751"/>
     </row>
@@ -28624,45 +28726,45 @@
   </mergeCells>
   <phoneticPr fontId="32" type="noConversion"/>
   <conditionalFormatting sqref="B93:C93 AH93">
-    <cfRule type="cellIs" dxfId="79" priority="127" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="81" priority="127" operator="greaterThan">
       <formula>$AI$93</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B90:AF90">
-    <cfRule type="cellIs" dxfId="78" priority="36" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="80" priority="36" operator="greaterThan">
       <formula>10.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92:AF92">
-    <cfRule type="cellIs" dxfId="77" priority="26" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="79" priority="26" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="27" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="78" priority="27" operator="lessThanOrEqual">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:AF93">
-    <cfRule type="cellIs" dxfId="75" priority="34" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="77" priority="34" operator="greaterThan">
       <formula>1.7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B94:AF94">
-    <cfRule type="cellIs" dxfId="74" priority="33" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="76" priority="33" operator="greaterThan">
       <formula>22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96:AF96">
-    <cfRule type="cellIs" dxfId="73" priority="32" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="75" priority="32" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:AG22">
-    <cfRule type="cellIs" dxfId="72" priority="101" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="74" priority="101" operator="greaterThan">
       <formula>400</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42:AG42">
-    <cfRule type="cellIs" dxfId="71" priority="47" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="73" priority="47" operator="greaterThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28677,129 +28779,129 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B94:AG94">
-    <cfRule type="cellIs" dxfId="70" priority="1174" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="72" priority="1174" operator="greaterThan">
       <formula>$AI$94</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96:AG96">
-    <cfRule type="cellIs" dxfId="69" priority="1176" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="71" priority="1176" operator="greaterThan">
       <formula>$AI$96</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:AH15">
-    <cfRule type="cellIs" dxfId="68" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="70" priority="1" operator="greaterThan">
       <formula>3.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54:AH54">
-    <cfRule type="cellIs" dxfId="67" priority="123" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="69" priority="123" operator="greaterThan">
       <formula>3.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B56:AH56">
-    <cfRule type="cellIs" dxfId="66" priority="61" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="68" priority="61" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B57:AH57 B59:AH59 B61:AH61">
-    <cfRule type="cellIs" dxfId="65" priority="62" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="67" priority="62" operator="greaterThan">
       <formula>0.7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58:AH58 B62:AH62">
-    <cfRule type="cellIs" dxfId="64" priority="63" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="66" priority="63" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B60:AH60">
-    <cfRule type="cellIs" dxfId="63" priority="22" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="65" priority="22" operator="greaterThan">
       <formula>2.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B65:AH65">
-    <cfRule type="cellIs" dxfId="62" priority="56" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="64" priority="56" operator="greaterThan">
       <formula>0.3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68:AH68">
-    <cfRule type="cellIs" dxfId="61" priority="58" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="63" priority="58" operator="greaterThan">
       <formula>9.6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69:AH69">
-    <cfRule type="cellIs" dxfId="60" priority="59" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="62" priority="59" operator="greaterThan">
       <formula>2.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92:AH92">
-    <cfRule type="cellIs" dxfId="59" priority="48" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="61" priority="48" operator="greaterThan">
       <formula>5.04</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:AH93">
-    <cfRule type="cellIs" dxfId="58" priority="44" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="60" priority="44" operator="greaterThan">
       <formula>1.7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="43" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="59" priority="43" operator="greaterThan">
       <formula>1.7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96:AH96">
-    <cfRule type="cellIs" dxfId="56" priority="37" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="37" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E96">
-    <cfRule type="cellIs" dxfId="55" priority="39" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="57" priority="39" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I63:AH63">
-    <cfRule type="cellIs" dxfId="54" priority="68" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="56" priority="68" operator="greaterThan">
       <formula>0.6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC54:AG54">
-    <cfRule type="cellIs" dxfId="53" priority="82" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="55" priority="82" operator="greaterThan">
       <formula>$AI$54</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC55:AG59 AC61:AG61 AC63:AG63 B64:AG64">
-    <cfRule type="cellIs" dxfId="52" priority="1135" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="54" priority="1135" operator="greaterThan">
       <formula>$AI59</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH94">
-    <cfRule type="cellIs" dxfId="51" priority="28" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="53" priority="28" operator="lessThanOrEqual">
       <formula>22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH94:AH96 B90:AH90 AH91">
-    <cfRule type="cellIs" dxfId="50" priority="1168" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="52" priority="1168" operator="greaterThan">
       <formula>$AI$90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH96">
-    <cfRule type="cellIs" dxfId="49" priority="29" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="51" priority="29" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="30" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="30" operator="lessThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="40" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="49" priority="40" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ8">
-    <cfRule type="cellIs" dxfId="46" priority="105" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="48" priority="105" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="106" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="106" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK90:AK96">
-    <cfRule type="cellIs" dxfId="44" priority="50" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="46" priority="50" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29440,11 +29542,11 @@
       </c>
       <c r="C13" s="55">
         <f t="shared" si="1"/>
-        <v>-253568</v>
+        <v>234</v>
       </c>
       <c r="D13" s="55">
         <f t="shared" si="2"/>
-        <v>1113210</v>
+        <v>83</v>
       </c>
       <c r="E13" s="56">
         <f>'Entries October 2026'!W12</f>
@@ -29456,7 +29558,7 @@
       </c>
       <c r="G13" s="57">
         <f t="shared" si="7"/>
-        <v>-1366778</v>
+        <v>151</v>
       </c>
       <c r="H13" s="57">
         <f>'Entries October 2026'!AA12</f>
@@ -29464,7 +29566,7 @@
       </c>
       <c r="I13" s="58">
         <f t="shared" si="3"/>
-        <v>-97122</v>
+        <v>0</v>
       </c>
       <c r="J13" s="57">
         <f>'Entries October 2026'!U12</f>
@@ -29476,7 +29578,7 @@
       </c>
       <c r="L13" s="58">
         <f t="shared" si="6"/>
-        <v>-97669</v>
+        <v>-547</v>
       </c>
       <c r="M13" s="57">
         <f>'Entries October 2026'!R12</f>
@@ -29484,11 +29586,11 @@
       </c>
       <c r="N13" s="57">
         <f>'Entries October 2026'!AC13-'Entries October 2026'!AC12</f>
-        <v>-6815</v>
+        <v>17</v>
       </c>
       <c r="O13" s="57">
         <f t="shared" si="5"/>
-        <v>-507136</v>
+        <v>468</v>
       </c>
       <c r="P13" s="62"/>
       <c r="Q13" s="45"/>
@@ -29503,15 +29605,15 @@
       </c>
       <c r="B14" s="55">
         <f>'Entries October 2026'!O13</f>
-        <v>0</v>
+        <v>253802</v>
       </c>
       <c r="C14" s="55">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-253802</v>
       </c>
       <c r="D14" s="55">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1113127</v>
       </c>
       <c r="E14" s="56">
         <f>'Entries October 2026'!W13</f>
@@ -29519,19 +29621,19 @@
       </c>
       <c r="F14" s="57">
         <f>'Entries October 2026'!V13</f>
-        <v>0</v>
+        <v>1366929</v>
       </c>
       <c r="G14" s="57">
         <f>F15-F14</f>
-        <v>0</v>
+        <v>-1366929</v>
       </c>
       <c r="H14" s="57">
         <f>'Entries October 2026'!AA13</f>
-        <v>0</v>
+        <v>97122</v>
       </c>
       <c r="I14" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-97122</v>
       </c>
       <c r="J14" s="57">
         <f>'Entries October 2026'!T13</f>
@@ -29543,7 +29645,7 @@
       </c>
       <c r="L14" s="58">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-97122</v>
       </c>
       <c r="M14" s="57">
         <f>'Entries October 2026'!R13</f>
@@ -29551,11 +29653,11 @@
       </c>
       <c r="N14" s="57">
         <f>'Entries October 2026'!AC14-'Entries October 2026'!AC13</f>
-        <v>0</v>
+        <v>-6832</v>
       </c>
       <c r="O14" s="57">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-507604</v>
       </c>
       <c r="P14" s="62"/>
       <c r="Q14" s="45"/>
@@ -31102,24 +31204,24 @@
     </row>
     <row r="6" spans="1:20" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="919" t="s">
+      <c r="A7" s="923" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="383"/>
       <c r="C7" s="383"/>
-      <c r="D7" s="932" t="s">
+      <c r="D7" s="936" t="s">
         <v>254</v>
       </c>
-      <c r="E7" s="935" t="s">
+      <c r="E7" s="939" t="s">
         <v>286</v>
       </c>
-      <c r="F7" s="929" t="s">
+      <c r="F7" s="933" t="s">
         <v>287</v>
       </c>
-      <c r="G7" s="925" t="s">
+      <c r="G7" s="929" t="s">
         <v>255</v>
       </c>
-      <c r="H7" s="925" t="s">
+      <c r="H7" s="929" t="s">
         <v>256</v>
       </c>
       <c r="I7" s="383" t="s">
@@ -31131,33 +31233,33 @@
       <c r="K7" s="390" t="s">
         <v>53</v>
       </c>
-      <c r="L7" s="926" t="s">
+      <c r="L7" s="930" t="s">
         <v>17</v>
       </c>
-      <c r="M7" s="927"/>
-      <c r="N7" s="927"/>
-      <c r="O7" s="927"/>
-      <c r="P7" s="928"/>
-      <c r="Q7" s="923" t="s">
+      <c r="M7" s="931"/>
+      <c r="N7" s="931"/>
+      <c r="O7" s="931"/>
+      <c r="P7" s="932"/>
+      <c r="Q7" s="927" t="s">
         <v>11</v>
       </c>
-      <c r="R7" s="924"/>
-      <c r="S7" s="924"/>
-      <c r="T7" s="924"/>
+      <c r="R7" s="928"/>
+      <c r="S7" s="928"/>
+      <c r="T7" s="928"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="920"/>
+      <c r="A8" s="924"/>
       <c r="B8" s="384" t="s">
         <v>257</v>
       </c>
       <c r="C8" s="384" t="s">
         <v>258</v>
       </c>
-      <c r="D8" s="933"/>
-      <c r="E8" s="936"/>
-      <c r="F8" s="930"/>
-      <c r="G8" s="925"/>
-      <c r="H8" s="925"/>
+      <c r="D8" s="937"/>
+      <c r="E8" s="940"/>
+      <c r="F8" s="934"/>
+      <c r="G8" s="929"/>
+      <c r="H8" s="929"/>
       <c r="I8" s="383"/>
       <c r="J8" s="383"/>
       <c r="K8" s="390"/>
@@ -31180,12 +31282,12 @@
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A9" s="921"/>
+      <c r="A9" s="925"/>
       <c r="B9" s="385"/>
       <c r="C9" s="385"/>
-      <c r="D9" s="934"/>
-      <c r="E9" s="937"/>
-      <c r="F9" s="931"/>
+      <c r="D9" s="938"/>
+      <c r="E9" s="941"/>
+      <c r="F9" s="935"/>
       <c r="G9" s="383" t="s">
         <v>56</v>
       </c>
@@ -31708,9 +31810,9 @@
       <c r="A16" s="719">
         <v>7</v>
       </c>
-      <c r="B16" s="719" t="str">
+      <c r="B16" s="719">
         <f>IF('Entries October 2026'!I13&lt;'Entries October 2026'!I12,"0",(IF('Entries October 2026'!I13&gt;='Entries October 2026'!I12,'Entries October 2026'!I13-'Entries October 2026'!I12,(999999-'Entries October 2026'!I12)+'Entries October 2026'!I13+1)))</f>
-        <v>0</v>
+        <v>6606</v>
       </c>
       <c r="C16" s="719" t="str">
         <f>IF('Entries October 2026'!J13&lt;='Entries October 2026'!J12,"0",IF('Entries October 2026'!J13&gt;='Entries October 2026'!J12,'Entries October 2026'!J13-'Entries October 2026'!J12,(999999-'Entries October 2026'!J12)+'Entries October 2026'!J13+1))</f>
@@ -31718,24 +31820,26 @@
       </c>
       <c r="D16" s="720">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E16" s="873"/>
-      <c r="F16" s="721" t="str">
+        <v>6606</v>
+      </c>
+      <c r="E16" s="873">
+        <v>1346.2</v>
+      </c>
+      <c r="F16" s="721">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="737" t="str">
+        <v>0.16928648675838134</v>
+      </c>
+      <c r="G16" s="737">
         <f>IF('Entries October 2026'!K13&lt;'Entries October 2026'!K12,"0",IF('Entries October 2026'!K13&gt;='Entries October 2026'!K12,'Entries October 2026'!K13-'Entries October 2026'!K12,(999999-'Entries October 2026'!K12)+'Entries October 2026'!K13+1))</f>
         <v>0</v>
       </c>
       <c r="H16" s="720">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7952.2</v>
       </c>
       <c r="I16" s="737">
         <f>'Water '!Z13*10</f>
-        <v>0</v>
+        <v>3810</v>
       </c>
       <c r="J16" s="720" t="str">
         <f>IF('Entries October 2026'!B13-'Entries October 2026'!B12&lt;1,"0",'Entries October 2026'!B13-'Entries October 2026'!B12)</f>
@@ -31743,7 +31847,7 @@
       </c>
       <c r="K16" s="722">
         <f>'CO2'!E13</f>
-        <v>0</v>
+        <v>1416</v>
       </c>
       <c r="L16" s="723">
         <f>+'PROD.FIG. '!F11</f>
@@ -31762,15 +31866,15 @@
         <v>0</v>
       </c>
       <c r="P16" s="724">
-        <v>0</v>
+        <v>406.428</v>
       </c>
       <c r="Q16" s="393">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>19.566073203617862</v>
       </c>
       <c r="R16" s="393">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9.3743541291446455</v>
       </c>
       <c r="S16" s="393">
         <f t="shared" si="5"/>
@@ -31785,7 +31889,7 @@
       <c r="A17" s="719">
         <v>8</v>
       </c>
-      <c r="B17" s="719">
+      <c r="B17" s="719" t="str">
         <f>IF('Entries October 2026'!I14&lt;'Entries October 2026'!I13,"0",(IF('Entries October 2026'!I14&gt;='Entries October 2026'!I13,'Entries October 2026'!I14-'Entries October 2026'!I13,(999999-'Entries October 2026'!I13)+'Entries October 2026'!I14+1)))</f>
         <v>0</v>
       </c>
@@ -31802,7 +31906,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G17" s="737">
+      <c r="G17" s="737" t="str">
         <f>IF('Entries October 2026'!K14&lt;'Entries October 2026'!K13,"0",IF('Entries October 2026'!K14&gt;='Entries October 2026'!K13,'Entries October 2026'!K14-'Entries October 2026'!K13,(999999-'Entries October 2026'!K13)+'Entries October 2026'!K14+1))</f>
         <v>0</v>
       </c>
@@ -33574,7 +33678,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E40" s="1019"/>
+      <c r="E40" s="890"/>
       <c r="F40" s="773" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -33599,11 +33703,11 @@
         <f>'CO2'!E37</f>
         <v>0</v>
       </c>
-      <c r="L40" s="1020"/>
-      <c r="M40" s="1021"/>
-      <c r="N40" s="1021"/>
-      <c r="O40" s="1021"/>
-      <c r="P40" s="1022">
+      <c r="L40" s="891"/>
+      <c r="M40" s="892"/>
+      <c r="N40" s="892"/>
+      <c r="O40" s="892"/>
+      <c r="P40" s="893">
         <v>0</v>
       </c>
       <c r="Q40" s="394">
@@ -33710,15 +33814,15 @@
       <c r="C43" s="19"/>
       <c r="D43" s="20">
         <f>SUM(D10:D40)</f>
-        <v>34292</v>
+        <v>40898</v>
       </c>
       <c r="E43" s="741">
         <f>SUM(E10:E40)</f>
-        <v>6747.6</v>
+        <v>8093.8</v>
       </c>
       <c r="F43" s="754">
         <f>IF((E43+D43)=0,"0",E43/(D43+E43))</f>
-        <v>0.16441680718135657</v>
+        <v>0.16520723876240512</v>
       </c>
       <c r="G43" s="20">
         <f t="shared" ref="G43:P43" si="7">SUM(G10:G40)</f>
@@ -33726,11 +33830,11 @@
       </c>
       <c r="H43" s="20">
         <f t="shared" si="7"/>
-        <v>41039.599999999999</v>
+        <v>48991.799999999996</v>
       </c>
       <c r="I43" s="20">
         <f t="shared" si="7"/>
-        <v>12220</v>
+        <v>16030</v>
       </c>
       <c r="J43" s="20">
         <f t="shared" si="7"/>
@@ -33738,7 +33842,7 @@
       </c>
       <c r="K43" s="20">
         <f t="shared" si="7"/>
-        <v>5829</v>
+        <v>7245</v>
       </c>
       <c r="L43" s="20">
         <f t="shared" si="7"/>
@@ -33758,7 +33862,7 @@
       </c>
       <c r="P43" s="403">
         <f t="shared" si="7"/>
-        <v>1334.7947999999999</v>
+        <v>1741.2228</v>
       </c>
       <c r="Q43" s="408" t="s">
         <v>13</v>
@@ -33786,7 +33890,7 @@
       </c>
       <c r="E44" s="728">
         <f>D43+E43</f>
-        <v>41039.599999999999</v>
+        <v>48991.8</v>
       </c>
       <c r="F44" s="708"/>
       <c r="G44" s="7"/>
@@ -33801,19 +33905,19 @@
       <c r="P44" s="401"/>
       <c r="Q44" s="397">
         <f>IF(P43=0,0,H43/P43)</f>
-        <v>30.74599931015614</v>
+        <v>28.136433775160764</v>
       </c>
       <c r="R44" s="398">
         <f>IF(Q44=0,0,I43/P43)</f>
-        <v>9.1549652425975889</v>
+        <v>9.2061739600469288</v>
       </c>
       <c r="S44" s="398">
         <f>IF(R44=0,0,J43/P43)</f>
-        <v>0.71921167208622638</v>
+        <v>0.55133668132533065</v>
       </c>
       <c r="T44" s="399">
         <f>IF(S44=0,0,K43/P43)</f>
-        <v>4.3669633714485556</v>
+        <v>4.160869016877105</v>
       </c>
     </row>
     <row r="45" spans="1:32" ht="15" x14ac:dyDescent="0.2">
@@ -33846,12 +33950,12 @@
       <c r="T46" s="2"/>
     </row>
     <row r="47" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="D47" s="922"/>
-      <c r="E47" s="922"/>
-      <c r="F47" s="922"/>
-      <c r="G47" s="922"/>
-      <c r="H47" s="922"/>
-      <c r="I47" s="922"/>
+      <c r="D47" s="926"/>
+      <c r="E47" s="926"/>
+      <c r="F47" s="926"/>
+      <c r="G47" s="926"/>
+      <c r="H47" s="926"/>
+      <c r="I47" s="926"/>
       <c r="AF47" t="s">
         <v>55</v>
       </c>
@@ -33890,41 +33994,41 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="Q10:Q44">
-    <cfRule type="cellIs" dxfId="106" priority="7" operator="between">
+    <cfRule type="cellIs" dxfId="108" priority="7" operator="between">
       <formula>0</formula>
       <formula>22</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="107" priority="8" operator="greaterThan">
       <formula>22</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="104" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="106" priority="9" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:R44">
-    <cfRule type="cellIs" dxfId="103" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="105" priority="1" operator="between">
       <formula>0</formula>
       <formula>10.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="104" priority="2" operator="greaterThan">
       <formula>10.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S10:S44">
-    <cfRule type="cellIs" dxfId="101" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="103" priority="3" operator="between">
       <formula>0</formula>
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="102" priority="4" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T10:T44">
-    <cfRule type="cellIs" dxfId="99" priority="5" operator="between">
+    <cfRule type="cellIs" dxfId="101" priority="5" operator="between">
       <formula>0</formula>
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="100" priority="6" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -33956,16 +34060,16 @@
       <c r="B2" s="8"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="938" t="s">
+      <c r="A3" s="942" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="940" t="s">
+      <c r="B3" s="944" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="939"/>
-      <c r="B4" s="941"/>
+      <c r="A4" s="943"/>
+      <c r="B4" s="945"/>
     </row>
     <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="36">
@@ -34329,31 +34433,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="950" t="s">
+      <c r="A1" s="954" t="s">
         <v>304</v>
       </c>
-      <c r="B1" s="951"/>
-      <c r="C1" s="951"/>
-      <c r="D1" s="951"/>
-      <c r="E1" s="951"/>
-      <c r="F1" s="951"/>
-      <c r="G1" s="951"/>
-      <c r="H1" s="951"/>
-      <c r="I1" s="951"/>
-      <c r="J1" s="951"/>
-      <c r="K1" s="951"/>
-      <c r="L1" s="951"/>
-      <c r="M1" s="951"/>
+      <c r="B1" s="955"/>
+      <c r="C1" s="955"/>
+      <c r="D1" s="955"/>
+      <c r="E1" s="955"/>
+      <c r="F1" s="955"/>
+      <c r="G1" s="955"/>
+      <c r="H1" s="955"/>
+      <c r="I1" s="955"/>
+      <c r="J1" s="955"/>
+      <c r="K1" s="955"/>
+      <c r="L1" s="955"/>
+      <c r="M1" s="955"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
       <c r="F2" s="9"/>
-      <c r="M2" s="942" t="s">
+      <c r="M2" s="946" t="s">
         <v>296</v>
       </c>
-      <c r="N2" s="942" t="s">
+      <c r="N2" s="946" t="s">
         <v>297</v>
       </c>
     </row>
@@ -34362,11 +34466,11 @@
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="9"/>
-      <c r="M3" s="943"/>
-      <c r="N3" s="943"/>
+      <c r="M3" s="947"/>
+      <c r="N3" s="947"/>
     </row>
     <row r="4" spans="1:17" s="339" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="956" t="s">
+      <c r="A4" s="960" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="847" t="s">
@@ -34399,22 +34503,22 @@
       <c r="K4" s="848" t="s">
         <v>40</v>
       </c>
-      <c r="L4" s="952" t="s">
+      <c r="L4" s="956" t="s">
         <v>243</v>
       </c>
-      <c r="M4" s="954" t="s">
+      <c r="M4" s="958" t="s">
         <v>246</v>
       </c>
-      <c r="N4" s="944" t="s">
+      <c r="N4" s="948" t="s">
         <v>246</v>
       </c>
-      <c r="O4" s="947" t="s">
+      <c r="O4" s="951" t="s">
         <v>298</v>
       </c>
       <c r="P4" s="350"/>
     </row>
     <row r="5" spans="1:17" s="339" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="957"/>
+      <c r="A5" s="961"/>
       <c r="B5" s="864" t="s">
         <v>41</v>
       </c>
@@ -34445,10 +34549,10 @@
       <c r="K5" s="865" t="s">
         <v>44</v>
       </c>
-      <c r="L5" s="953"/>
-      <c r="M5" s="955"/>
-      <c r="N5" s="945"/>
-      <c r="O5" s="948"/>
+      <c r="L5" s="957"/>
+      <c r="M5" s="959"/>
+      <c r="N5" s="949"/>
+      <c r="O5" s="952"/>
       <c r="P5" s="350"/>
     </row>
     <row r="6" spans="1:17" s="73" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -34465,8 +34569,8 @@
       <c r="K6" s="836"/>
       <c r="L6" s="869"/>
       <c r="M6" s="833"/>
-      <c r="N6" s="946"/>
-      <c r="O6" s="949"/>
+      <c r="N6" s="950"/>
+      <c r="O6" s="953"/>
       <c r="P6" s="350"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
@@ -34808,13 +34912,13 @@
         <f>IF('Entries October 2026'!B13-'Entries October 2026'!B12&lt;1,"0",'Entries October 2026'!B13-'Entries October 2026'!B12)</f>
         <v>0</v>
       </c>
-      <c r="C13" s="739" t="str">
+      <c r="C13" s="739">
         <f>IF('Entries October 2026'!F13-'Entries October 2026'!F12&lt;1,"0",'Entries October 2026'!F13-'Entries October 2026'!F12)</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="839" t="str">
+        <v>19.199999999998909</v>
+      </c>
+      <c r="D13" s="839">
         <f>IF('Entries October 2026'!C13-'Entries October 2026'!C12&lt;1,"0",'Entries October 2026'!C13-'Entries October 2026'!C12)</f>
-        <v>0</v>
+        <v>2750.5999999998603</v>
       </c>
       <c r="E13" s="843" t="str">
         <f t="shared" si="0"/>
@@ -34826,7 +34930,7 @@
       </c>
       <c r="G13" s="837"/>
       <c r="H13" s="739"/>
-      <c r="I13" s="740" t="str">
+      <c r="I13" s="740">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -34838,20 +34942,20 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L13" s="831" t="str">
-        <v>0</v>
-      </c>
-      <c r="M13" s="829" t="str">
+      <c r="L13" s="831">
+        <v>406.428</v>
+      </c>
+      <c r="M13" s="829">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N13" s="829" t="str">
+      <c r="N13" s="829">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.767742379953793</v>
       </c>
       <c r="O13" s="830">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-2750.5999999998603</v>
       </c>
       <c r="P13" s="333"/>
     </row>
@@ -36184,11 +36288,11 @@
       </c>
       <c r="C38" s="388">
         <f>SUM(C7:C37)</f>
-        <v>80.900000000001455</v>
+        <v>100.10000000000036</v>
       </c>
       <c r="D38" s="840">
         <f t="shared" si="7"/>
-        <v>12131.800000000047</v>
+        <v>14882.399999999907</v>
       </c>
       <c r="E38" s="845"/>
       <c r="F38" s="846">
@@ -36205,7 +36309,7 @@
       </c>
       <c r="I38" s="797">
         <f>B38/C38</f>
-        <v>11.866501854140701</v>
+        <v>9.5904095904095552</v>
       </c>
       <c r="J38" s="355"/>
       <c r="K38" s="356">
@@ -36214,15 +36318,15 @@
       </c>
       <c r="L38" s="828">
         <f>SUM(L7:L37)</f>
-        <v>1334.7947999999999</v>
+        <v>1741.2228</v>
       </c>
       <c r="M38" s="834">
         <f>IF(L38=0,"0",(K38/L38))</f>
-        <v>0.71921167208622638</v>
+        <v>0.55133668132533065</v>
       </c>
       <c r="N38" s="834">
         <f>IF(L38=0,"0",(D38/L38))</f>
-        <v>9.0888876702247021</v>
+        <v>8.5470969022458849</v>
       </c>
       <c r="O38" s="835"/>
     </row>
@@ -36236,7 +36340,7 @@
       </c>
       <c r="C39" s="802">
         <f>AVERAGE(C7:C37)</f>
-        <v>13.483333333333576</v>
+        <v>14.300000000000052</v>
       </c>
       <c r="D39" s="30"/>
       <c r="E39" s="30"/>
@@ -36856,27 +36960,27 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="C7:C37">
-    <cfRule type="cellIs" dxfId="97" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="99" priority="13" operator="greaterThan">
       <formula>24</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7:N37">
-    <cfRule type="cellIs" dxfId="96" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="98" priority="9" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="95" priority="11" operator="between">
+    <cfRule type="cellIs" dxfId="97" priority="11" operator="between">
       <formula>0</formula>
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7:N38">
-    <cfRule type="cellIs" dxfId="94" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="96" priority="1" operator="lessThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="95" priority="2" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="94" priority="4" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36920,120 +37024,120 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="950"/>
-      <c r="B1" s="951"/>
-      <c r="C1" s="951"/>
-      <c r="D1" s="951"/>
-      <c r="E1" s="951"/>
-      <c r="F1" s="951"/>
-      <c r="G1" s="951"/>
-      <c r="H1" s="951"/>
-      <c r="I1" s="951"/>
-      <c r="J1" s="951"/>
-      <c r="K1" s="951"/>
-      <c r="L1" s="951"/>
-      <c r="M1" s="951"/>
-      <c r="N1" s="951"/>
-      <c r="O1" s="951"/>
-      <c r="P1" s="951"/>
-      <c r="Q1" s="951"/>
-      <c r="R1" s="951"/>
-      <c r="S1" s="951"/>
-      <c r="T1" s="951"/>
-      <c r="U1" s="951"/>
-      <c r="V1" s="951"/>
-      <c r="W1" s="951"/>
-      <c r="X1" s="951"/>
-      <c r="Y1" s="951"/>
-      <c r="Z1" s="951"/>
-      <c r="AA1" s="951"/>
+      <c r="A1" s="954"/>
+      <c r="B1" s="955"/>
+      <c r="C1" s="955"/>
+      <c r="D1" s="955"/>
+      <c r="E1" s="955"/>
+      <c r="F1" s="955"/>
+      <c r="G1" s="955"/>
+      <c r="H1" s="955"/>
+      <c r="I1" s="955"/>
+      <c r="J1" s="955"/>
+      <c r="K1" s="955"/>
+      <c r="L1" s="955"/>
+      <c r="M1" s="955"/>
+      <c r="N1" s="955"/>
+      <c r="O1" s="955"/>
+      <c r="P1" s="955"/>
+      <c r="Q1" s="955"/>
+      <c r="R1" s="955"/>
+      <c r="S1" s="955"/>
+      <c r="T1" s="955"/>
+      <c r="U1" s="955"/>
+      <c r="V1" s="955"/>
+      <c r="W1" s="955"/>
+      <c r="X1" s="955"/>
+      <c r="Y1" s="955"/>
+      <c r="Z1" s="955"/>
+      <c r="AA1" s="955"/>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C2" s="17"/>
     </row>
     <row r="3" spans="1:31" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="962" t="s">
+      <c r="B4" s="974" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="960" t="s">
+      <c r="C4" s="966" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="958" t="s">
+      <c r="D4" s="971" t="s">
         <v>106</v>
       </c>
-      <c r="E4" s="960" t="s">
+      <c r="E4" s="966" t="s">
         <v>107</v>
       </c>
-      <c r="F4" s="958" t="s">
+      <c r="F4" s="971" t="s">
         <v>239</v>
       </c>
-      <c r="G4" s="958" t="s">
+      <c r="G4" s="971" t="s">
         <v>108</v>
       </c>
-      <c r="H4" s="958" t="s">
+      <c r="H4" s="971" t="s">
         <v>161</v>
       </c>
-      <c r="I4" s="960" t="s">
+      <c r="I4" s="966" t="s">
         <v>207</v>
       </c>
-      <c r="J4" s="960" t="s">
+      <c r="J4" s="966" t="s">
         <v>109</v>
       </c>
-      <c r="K4" s="960" t="s">
+      <c r="K4" s="966" t="s">
         <v>174</v>
       </c>
-      <c r="L4" s="960" t="s">
+      <c r="L4" s="966" t="s">
         <v>173</v>
       </c>
-      <c r="M4" s="960" t="s">
+      <c r="M4" s="966" t="s">
         <v>103</v>
       </c>
       <c r="N4" s="48"/>
       <c r="O4" s="48"/>
       <c r="P4" s="48"/>
       <c r="Q4" s="48"/>
-      <c r="R4" s="958" t="s">
+      <c r="R4" s="971" t="s">
         <v>110</v>
       </c>
-      <c r="S4" s="958" t="s">
+      <c r="S4" s="971" t="s">
         <v>240</v>
       </c>
       <c r="T4" s="48"/>
-      <c r="U4" s="960" t="s">
+      <c r="U4" s="966" t="s">
         <v>153</v>
       </c>
       <c r="V4" s="48"/>
       <c r="W4" s="48"/>
-      <c r="X4" s="960" t="s">
+      <c r="X4" s="966" t="s">
         <v>175</v>
       </c>
-      <c r="Y4" s="960" t="s">
+      <c r="Y4" s="966" t="s">
         <v>176</v>
       </c>
-      <c r="Z4" s="967" t="s">
+      <c r="Z4" s="964" t="s">
         <v>247</v>
       </c>
-      <c r="AA4" s="969" t="s">
+      <c r="AA4" s="968" t="s">
         <v>243</v>
       </c>
-      <c r="AB4" s="965" t="s">
+      <c r="AB4" s="962" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:31" s="300" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="963"/>
-      <c r="C5" s="961"/>
-      <c r="D5" s="959"/>
-      <c r="E5" s="964"/>
-      <c r="F5" s="959"/>
-      <c r="G5" s="959"/>
-      <c r="H5" s="959"/>
-      <c r="I5" s="964"/>
-      <c r="J5" s="964"/>
-      <c r="K5" s="964"/>
-      <c r="L5" s="964"/>
-      <c r="M5" s="964"/>
+      <c r="B5" s="975"/>
+      <c r="C5" s="973"/>
+      <c r="D5" s="972"/>
+      <c r="E5" s="967"/>
+      <c r="F5" s="972"/>
+      <c r="G5" s="972"/>
+      <c r="H5" s="972"/>
+      <c r="I5" s="967"/>
+      <c r="J5" s="967"/>
+      <c r="K5" s="967"/>
+      <c r="L5" s="967"/>
+      <c r="M5" s="967"/>
       <c r="N5" s="50" t="s">
         <v>111</v>
       </c>
@@ -37046,23 +37150,23 @@
       <c r="Q5" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="R5" s="959"/>
-      <c r="S5" s="959"/>
+      <c r="R5" s="972"/>
+      <c r="S5" s="972"/>
       <c r="T5" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="U5" s="971"/>
+      <c r="U5" s="970"/>
       <c r="V5" s="80" t="s">
         <v>156</v>
       </c>
       <c r="W5" s="80" t="s">
         <v>157</v>
       </c>
-      <c r="X5" s="964"/>
-      <c r="Y5" s="964"/>
-      <c r="Z5" s="968"/>
-      <c r="AA5" s="970"/>
-      <c r="AB5" s="966"/>
+      <c r="X5" s="967"/>
+      <c r="Y5" s="967"/>
+      <c r="Z5" s="965"/>
+      <c r="AA5" s="969"/>
+      <c r="AB5" s="963"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="21" t="s">
@@ -37760,33 +37864,33 @@
         <f>IF('Entries October 2026'!W13-'Entries October 2026'!W12&lt;1,"0",'Entries October 2026'!W13-'Entries October 2026'!W12)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="693" t="str">
+      <c r="D13" s="693">
         <f>IF('Entries October 2026'!O13-'Entries October 2026'!O12&lt;1,"0",'Entries October 2026'!O13-'Entries October 2026'!O12)</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="693" t="str">
+        <v>234</v>
+      </c>
+      <c r="E13" s="693">
         <f>IF('Entries October 2026'!P13-'Entries October 2026'!P12&lt;1,"0",'Entries October 2026'!P13-'Entries October 2026'!P12)</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="693" t="str">
+        <v>147</v>
+      </c>
+      <c r="F13" s="693">
         <f>IF('Entries October 2026'!V13-'Entries October 2026'!V12&lt;1,"0",'Entries October 2026'!V13-'Entries October 2026'!V12)</f>
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="G13" s="693">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="H13" s="693">
         <f>IF('Entries October 2026'!Q13-'Entries October 2026'!Q12&lt;1,0,'Entries October 2026'!Q13-'Entries October 2026'!Q12)</f>
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="I13" s="693">
         <f>IF('Entries October 2026'!AG13-'Entries October 2026'!AG12&lt;1,0,'Entries October 2026'!AG13-'Entries October 2026'!AG12)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="693" t="str">
+      <c r="J13" s="693">
         <f>IF('Entries October 2026'!S13-'Entries October 2026'!S12&lt;1,"0",'Entries October 2026'!S13-'Entries October 2026'!S12)</f>
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="K13" s="693" t="str">
         <f>IF('Entries October 2026'!R13-'Entries October 2026'!R12&lt;1,"0",'Entries October 2026'!R13-'Entries October 2026'!R12)</f>
@@ -37796,25 +37900,25 @@
         <f>IF('Entries October 2026'!T13-'Entries October 2026'!T12&lt;1,"0",'Entries October 2026'!T13-'Entries October 2026'!T12)</f>
         <v>0</v>
       </c>
-      <c r="M13" s="693" t="str">
+      <c r="M13" s="693">
         <f>IF('Entries October 2026'!U13-'Entries October 2026'!U12&lt;1,"0",'Entries October 2026'!U13-'Entries October 2026'!U12)</f>
-        <v>0</v>
-      </c>
-      <c r="N13" s="693" t="str">
+        <v>3</v>
+      </c>
+      <c r="N13" s="693">
         <f>IF('Entries October 2026'!X13-'Entries October 2026'!X12&lt;1,"0",'Entries October 2026'!X13-'Entries October 2026'!X12)</f>
-        <v>0</v>
-      </c>
-      <c r="O13" s="693" t="str">
+        <v>50</v>
+      </c>
+      <c r="O13" s="693">
         <f>IF('Entries October 2026'!Y13-'Entries October 2026'!Y12&lt;1,"0",'Entries October 2026'!Y13-'Entries October 2026'!Y12)</f>
-        <v>0</v>
-      </c>
-      <c r="P13" s="693" t="str">
+        <v>91</v>
+      </c>
+      <c r="P13" s="693">
         <f>IF('Entries October 2026'!AC13-'Entries October 2026'!AC12&lt;1,"0",'Entries October 2026'!AC13-'Entries October 2026'!AC12)</f>
-        <v>0</v>
-      </c>
-      <c r="Q13" s="693" t="str">
+        <v>17</v>
+      </c>
+      <c r="Q13" s="693">
         <f>IF('Entries October 2026'!Z13-'Entries October 2026'!Z12&lt;1,"0",'Entries October 2026'!Z13-'Entries October 2026'!Z12)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R13" s="693" t="str">
         <f>IF(('Entries October 2026'!AA13-'Entries October 2026'!AA12)+('Entries October 2026'!AB13-'Entries October 2026'!AB12)&lt;1,"0",('Entries October 2026'!AA13-'Entries October 2026'!AA12)+('Entries October 2026'!AB13-'Entries October 2026'!AB12))</f>
@@ -37822,15 +37926,15 @@
       </c>
       <c r="S13" s="692">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="T13" s="692">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U13" s="693" t="str">
+        <v>144</v>
+      </c>
+      <c r="U13" s="693">
         <f>IF('Entries October 2026'!AC13-'Entries October 2026'!AC12&lt;1,"0",'Entries October 2026'!AC13-'Entries October 2026'!AC12)</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="V13" s="693" t="str">
         <f>IF('Entries October 2026'!AD13-'Entries October 2026'!AD12&lt;1,"0",'Entries October 2026'!AD13-'Entries October 2026'!AD12)</f>
@@ -37850,14 +37954,14 @@
       </c>
       <c r="Z13" s="329">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AA13" s="330" t="str">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="331" t="str">
+        <v>381</v>
+      </c>
+      <c r="AA13" s="330">
+        <v>406.428</v>
+      </c>
+      <c r="AB13" s="331">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.3743541291446455</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
@@ -40464,28 +40568,28 @@
       </c>
       <c r="D38" s="303">
         <f>SUM(D7:D37)</f>
-        <v>574</v>
+        <v>808</v>
       </c>
       <c r="E38" s="303">
         <f>SUM(E7:E37)</f>
-        <v>648</v>
+        <v>795</v>
       </c>
       <c r="F38" s="303">
         <f>SUM(F7:F37)</f>
-        <v>742</v>
+        <v>893</v>
       </c>
       <c r="G38" s="304">
         <f>SUM(G7:G37)</f>
-        <v>480</v>
+        <v>710</v>
       </c>
       <c r="H38" s="303">
         <f t="shared" si="5"/>
-        <v>920</v>
+        <v>1139</v>
       </c>
       <c r="I38" s="303"/>
       <c r="J38" s="303">
         <f t="shared" si="5"/>
-        <v>699</v>
+        <v>926</v>
       </c>
       <c r="K38" s="303"/>
       <c r="L38" s="303">
@@ -40494,23 +40598,23 @@
       </c>
       <c r="M38" s="303">
         <f>SUM(M7:M37)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N38" s="303">
         <f t="shared" si="5"/>
-        <v>180</v>
+        <v>230</v>
       </c>
       <c r="O38" s="303">
         <f t="shared" si="5"/>
-        <v>391</v>
+        <v>482</v>
       </c>
       <c r="P38" s="303">
         <f>SUM(P7:P37)</f>
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="Q38" s="303">
         <f>SUM(Q7:Q37)</f>
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="R38" s="303">
         <f>SUM(R7:R34)</f>
@@ -40518,15 +40622,15 @@
       </c>
       <c r="S38" s="304">
         <f>SUM(S7:S37)</f>
-        <v>4800</v>
+        <v>7100</v>
       </c>
       <c r="T38" s="304">
         <f>SUM(T7:T37)</f>
-        <v>580</v>
+        <v>724</v>
       </c>
       <c r="U38" s="303">
         <f>SUM(U7:U37)</f>
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="V38" s="303">
         <f>SUM(V7:V37)</f>
@@ -40537,22 +40641,22 @@
       <c r="Y38" s="303"/>
       <c r="Z38" s="332">
         <f>SUM(Z7:Z37)</f>
-        <v>1222</v>
+        <v>1603</v>
       </c>
       <c r="AA38" s="332">
         <f>SUM(AA7:AA37)</f>
-        <v>1334.7947999999999</v>
+        <v>1741.2228</v>
       </c>
       <c r="AB38" s="331">
         <f>IF(AA38=0,"0",(Z38*10/AA38))</f>
-        <v>9.1549652425975889</v>
+        <v>9.2061739600469288</v>
       </c>
       <c r="AC38" s="321">
         <v>10.199999999999999</v>
       </c>
       <c r="AD38" s="340">
         <f>AB38/AC38*100</f>
-        <v>89.75456120193715</v>
+        <v>90.256607451440487</v>
       </c>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.2">
@@ -40591,7 +40695,7 @@
       <c r="C40" s="15"/>
       <c r="D40" s="15">
         <f>D38*220</f>
-        <v>126280</v>
+        <v>177760</v>
       </c>
       <c r="E40" s="15"/>
       <c r="F40" s="15"/>
@@ -40683,7 +40787,7 @@
       <c r="C43" s="17"/>
       <c r="D43" s="17">
         <f>+D41*D40</f>
-        <v>1996.4868000000001</v>
+        <v>2810.3856000000001</v>
       </c>
       <c r="E43" s="17"/>
       <c r="F43" s="36"/>
@@ -40736,7 +40840,7 @@
     <row r="45" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D45" s="17">
         <f>SUM(D43:D44)</f>
-        <v>2275.4567999999999</v>
+        <v>3089.3555999999999</v>
       </c>
       <c r="E45" s="17"/>
       <c r="F45" s="36"/>
@@ -40758,7 +40862,7 @@
       </c>
       <c r="D47" s="23">
         <f>+D45*2/3</f>
-        <v>1516.9712</v>
+        <v>2059.5704000000001</v>
       </c>
       <c r="E47" s="324"/>
       <c r="F47" s="36"/>
@@ -40781,7 +40885,7 @@
       <c r="C49" s="24"/>
       <c r="D49" s="28">
         <f>SUM(D47,D45)</f>
-        <v>3792.4279999999999</v>
+        <v>5148.9259999999995</v>
       </c>
       <c r="E49" s="325"/>
       <c r="F49" s="36"/>
@@ -41146,6 +41250,16 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:AA1"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="R4:R5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="E4:E5"/>
     <mergeCell ref="AB4:AB5"/>
     <mergeCell ref="Z4:Z5"/>
     <mergeCell ref="L4:L5"/>
@@ -41157,23 +41271,13 @@
     <mergeCell ref="Y4:Y5"/>
     <mergeCell ref="S4:S5"/>
     <mergeCell ref="M4:M5"/>
-    <mergeCell ref="A1:AA1"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="R4:R5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="E4:E5"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="AB6:AB38">
-    <cfRule type="cellIs" dxfId="91" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="93" priority="1" operator="lessThan">
       <formula>10.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="92" priority="2" operator="greaterThan">
       <formula>10.2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -41204,15 +41308,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="972" t="s">
+      <c r="A1" s="976" t="s">
         <v>303</v>
       </c>
-      <c r="B1" s="973"/>
-      <c r="C1" s="973"/>
-      <c r="D1" s="974"/>
-      <c r="E1" s="973"/>
-      <c r="F1" s="973"/>
-      <c r="G1" s="975"/>
+      <c r="B1" s="977"/>
+      <c r="C1" s="977"/>
+      <c r="D1" s="978"/>
+      <c r="E1" s="977"/>
+      <c r="F1" s="977"/>
+      <c r="G1" s="979"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B2" s="9"/>
@@ -41225,7 +41329,7 @@
       <c r="D3" s="359"/>
     </row>
     <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="986" t="s">
+      <c r="A4" s="990" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="39" t="s">
@@ -41237,19 +41341,19 @@
       <c r="D4" s="361" t="s">
         <v>285</v>
       </c>
-      <c r="E4" s="976" t="s">
+      <c r="E4" s="980" t="s">
         <v>245</v>
       </c>
-      <c r="F4" s="979" t="s">
+      <c r="F4" s="983" t="s">
         <v>243</v>
       </c>
-      <c r="G4" s="982" t="s">
+      <c r="G4" s="986" t="s">
         <v>253</v>
       </c>
-      <c r="H4" s="985"/>
+      <c r="H4" s="989"/>
     </row>
     <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="987"/>
+      <c r="A5" s="991"/>
       <c r="B5" s="34" t="s">
         <v>48</v>
       </c>
@@ -41259,20 +41363,20 @@
       <c r="D5" s="361" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="977"/>
-      <c r="F5" s="980"/>
-      <c r="G5" s="983"/>
-      <c r="H5" s="985"/>
+      <c r="E5" s="981"/>
+      <c r="F5" s="984"/>
+      <c r="G5" s="987"/>
+      <c r="H5" s="989"/>
     </row>
     <row r="6" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="988"/>
+      <c r="A6" s="992"/>
       <c r="B6" s="40"/>
       <c r="C6" s="362"/>
       <c r="D6" s="361"/>
-      <c r="E6" s="978"/>
-      <c r="F6" s="981"/>
-      <c r="G6" s="984"/>
-      <c r="H6" s="985"/>
+      <c r="E6" s="982"/>
+      <c r="F6" s="985"/>
+      <c r="G6" s="988"/>
+      <c r="H6" s="989"/>
     </row>
     <row r="7" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A7" s="686">
@@ -41462,27 +41566,27 @@
       </c>
       <c r="B13" s="742">
         <f>'Utility Analysis October 2026'!D16</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="743" t="str">
+        <v>6606</v>
+      </c>
+      <c r="C13" s="743">
         <f>'Utility Analysis October 2026'!G16</f>
         <v>0</v>
       </c>
       <c r="D13" s="744">
         <f>'Utility Analysis October 2026'!E16</f>
-        <v>0</v>
+        <v>1346.2</v>
       </c>
       <c r="E13" s="745">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F13" s="746" t="str">
+        <v>7952.2</v>
+      </c>
+      <c r="F13" s="746">
         <f>'PROD.FIG. '!H11</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="336" t="str">
+        <v>406.428</v>
+      </c>
+      <c r="G13" s="336">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>19.566073203617862</v>
       </c>
       <c r="J13" s="30"/>
     </row>
@@ -41494,7 +41598,7 @@
         <f>'Utility Analysis October 2026'!D17</f>
         <v>0</v>
       </c>
-      <c r="C14" s="743">
+      <c r="C14" s="743" t="str">
         <f>'Utility Analysis October 2026'!G17</f>
         <v>0</v>
       </c>
@@ -42209,7 +42313,7 @@
       </c>
       <c r="B38" s="308">
         <f>SUM(B7:B37)</f>
-        <v>34292</v>
+        <v>40898</v>
       </c>
       <c r="C38" s="308">
         <f>SUM(C7:C37)</f>
@@ -42217,26 +42321,26 @@
       </c>
       <c r="D38" s="308">
         <f>SUM(D7:D37)</f>
-        <v>6747.6</v>
+        <v>8093.8</v>
       </c>
       <c r="E38" s="337">
         <f>SUM(E7:E37)</f>
-        <v>41039.599999999999</v>
+        <v>48991.799999999996</v>
       </c>
       <c r="F38" s="358">
         <f>SUM(F7:F37)</f>
-        <v>1334.7947999999999</v>
+        <v>1741.2228</v>
       </c>
       <c r="G38" s="338">
         <f>IF(F38=0,"0",(E38/F38))</f>
-        <v>30.74599931015614</v>
+        <v>28.136433775160764</v>
       </c>
       <c r="H38" s="335">
         <v>22</v>
       </c>
       <c r="I38" s="340">
         <f>G38/H38*100</f>
-        <v>139.75454231889154</v>
+        <v>127.89288079618528</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
@@ -42277,12 +42381,12 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="cellIs" dxfId="89" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="91" priority="1" operator="lessThan">
       <formula>22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7:G38">
-    <cfRule type="cellIs" dxfId="88" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="90" priority="2" operator="greaterThan">
       <formula>21</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42313,16 +42417,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="989" t="s">
+      <c r="A1" s="993" t="s">
         <v>302</v>
       </c>
-      <c r="B1" s="951"/>
-      <c r="C1" s="951"/>
-      <c r="D1" s="951"/>
-      <c r="E1" s="951"/>
-      <c r="F1" s="951"/>
-      <c r="G1" s="951"/>
-      <c r="H1" s="951"/>
+      <c r="B1" s="955"/>
+      <c r="C1" s="955"/>
+      <c r="D1" s="955"/>
+      <c r="E1" s="955"/>
+      <c r="F1" s="955"/>
+      <c r="G1" s="955"/>
+      <c r="H1" s="955"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D2" s="12"/>
@@ -42484,8 +42588,8 @@
       <c r="E11" s="686"/>
       <c r="F11" s="690"/>
       <c r="G11" s="686"/>
-      <c r="H11" s="689" t="str">
-        <v>0</v>
+      <c r="H11" s="689">
+        <v>406.428</v>
       </c>
       <c r="I11" s="298"/>
       <c r="J11" s="299"/>
@@ -42935,7 +43039,7 @@
       </c>
       <c r="H36" s="736">
         <f>SUM(H5:H35)</f>
-        <v>1334.7947999999999</v>
+        <v>1741.2228</v>
       </c>
       <c r="I36" s="298"/>
       <c r="J36" s="299"/>
@@ -43051,11 +43155,11 @@
       <c r="D3" s="85"/>
       <c r="E3" s="85"/>
       <c r="F3" s="1"/>
-      <c r="I3" s="994" t="s">
+      <c r="I3" s="1006" t="s">
         <v>267</v>
       </c>
-      <c r="J3" s="995"/>
-      <c r="K3" s="996"/>
+      <c r="J3" s="1007"/>
+      <c r="K3" s="1008"/>
     </row>
     <row r="4" spans="1:24" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
@@ -43068,46 +43172,46 @@
         <v>250</v>
       </c>
       <c r="H4" s="347"/>
-      <c r="I4" s="997" t="s">
+      <c r="I4" s="1009" t="s">
         <v>262</v>
       </c>
-      <c r="J4" s="998"/>
-      <c r="K4" s="999"/>
+      <c r="J4" s="1010"/>
+      <c r="K4" s="1011"/>
       <c r="M4" s="417"/>
       <c r="N4" s="417"/>
       <c r="O4" s="418"/>
       <c r="P4" s="418"/>
-      <c r="Q4" s="1009" t="s">
+      <c r="Q4" s="1021" t="s">
         <v>283</v>
       </c>
-      <c r="R4" s="1009"/>
-      <c r="S4" s="1009"/>
-      <c r="T4" s="1009"/>
+      <c r="R4" s="1021"/>
+      <c r="S4" s="1021"/>
+      <c r="T4" s="1021"/>
       <c r="U4" s="191"/>
       <c r="V4" s="417"/>
       <c r="W4" s="191"/>
       <c r="X4" s="191"/>
     </row>
     <row r="5" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="938" t="s">
+      <c r="A5" s="942" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="940" t="s">
+      <c r="B5" s="944" t="s">
         <v>251</v>
       </c>
-      <c r="C5" s="940" t="s">
+      <c r="C5" s="944" t="s">
         <v>282</v>
       </c>
-      <c r="D5" s="1016" t="s">
+      <c r="D5" s="1000" t="s">
         <v>279</v>
       </c>
-      <c r="E5" s="1016" t="s">
+      <c r="E5" s="1000" t="s">
         <v>280</v>
       </c>
-      <c r="F5" s="1014" t="s">
+      <c r="F5" s="998" t="s">
         <v>243</v>
       </c>
-      <c r="G5" s="1011" t="s">
+      <c r="G5" s="995" t="s">
         <v>249</v>
       </c>
       <c r="I5" s="419" t="s">
@@ -43119,43 +43223,43 @@
       <c r="K5" s="421" t="s">
         <v>265</v>
       </c>
-      <c r="M5" s="1000" t="s">
+      <c r="M5" s="1012" t="s">
         <v>266</v>
       </c>
-      <c r="N5" s="1001"/>
-      <c r="O5" s="1002"/>
+      <c r="N5" s="1013"/>
+      <c r="O5" s="1014"/>
       <c r="P5" s="422"/>
-      <c r="Q5" s="1003" t="s">
+      <c r="Q5" s="1015" t="s">
         <v>7</v>
       </c>
-      <c r="R5" s="1005" t="s">
+      <c r="R5" s="1017" t="s">
         <v>267</v>
       </c>
-      <c r="S5" s="1006"/>
+      <c r="S5" s="1018"/>
       <c r="T5" s="452" t="s">
         <v>268</v>
       </c>
       <c r="U5" s="423" t="s">
         <v>269</v>
       </c>
-      <c r="V5" s="1007" t="s">
+      <c r="V5" s="1019" t="s">
         <v>277</v>
       </c>
-      <c r="W5" s="990" t="s">
+      <c r="W5" s="1002" t="s">
         <v>270</v>
       </c>
-      <c r="X5" s="992" t="s">
+      <c r="X5" s="1004" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1010"/>
-      <c r="B6" s="1013"/>
-      <c r="C6" s="1013"/>
-      <c r="D6" s="1017"/>
-      <c r="E6" s="1017"/>
-      <c r="F6" s="1015"/>
-      <c r="G6" s="1012"/>
+      <c r="A6" s="994"/>
+      <c r="B6" s="997"/>
+      <c r="C6" s="997"/>
+      <c r="D6" s="1001"/>
+      <c r="E6" s="1001"/>
+      <c r="F6" s="999"/>
+      <c r="G6" s="996"/>
       <c r="I6" s="424">
         <v>10</v>
       </c>
@@ -43174,7 +43278,7 @@
         <v>273</v>
       </c>
       <c r="P6" s="418"/>
-      <c r="Q6" s="1004"/>
+      <c r="Q6" s="1016"/>
       <c r="R6" s="448" t="s">
         <v>274</v>
       </c>
@@ -43187,9 +43291,9 @@
       <c r="U6" s="429" t="s">
         <v>275</v>
       </c>
-      <c r="V6" s="1008"/>
-      <c r="W6" s="991"/>
-      <c r="X6" s="993"/>
+      <c r="V6" s="1020"/>
+      <c r="W6" s="1003"/>
+      <c r="X6" s="1005"/>
     </row>
     <row r="7" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="715">
@@ -43652,27 +43756,27 @@
       <c r="A13" s="715">
         <v>7</v>
       </c>
-      <c r="B13" s="716" t="str">
+      <c r="B13" s="716">
         <f>IF('Entries October 2026'!N13-'Entries October 2026'!N12&lt;1,"0",'Entries October 2026'!N13-'Entries October 2026'!N12)</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="716" t="str">
+        <v>220.41000000000349</v>
+      </c>
+      <c r="C13" s="716">
         <f>IF('Entries October 2026'!L13-'Entries October 2026'!L12&lt;1,"0",'Entries October 2026'!L13-'Entries October 2026'!L12)</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="716" t="str">
+        <v>304.72000000000116</v>
+      </c>
+      <c r="D13" s="716">
         <f>IF('Entries October 2026'!M13-'Entries October 2026'!M12&lt;1,"0",'Entries October 2026'!M13-'Entries October 2026'!M12)</f>
-        <v>0</v>
+        <v>1416.1900000000605</v>
       </c>
       <c r="E13" s="716">
-        <v>0</v>
+        <v>1416</v>
       </c>
       <c r="F13" s="717">
-        <v>0</v>
-      </c>
-      <c r="G13" s="336" t="str">
+        <v>406.428</v>
+      </c>
+      <c r="G13" s="336">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3.4840119283120257</v>
       </c>
       <c r="I13" s="430">
         <v>80</v>
@@ -45476,27 +45580,27 @@
       </c>
       <c r="B38" s="713">
         <f>SUM(B7:B37)</f>
-        <v>720.77000000000407</v>
+        <v>941.18000000000757</v>
       </c>
       <c r="C38" s="713">
         <f>SUM(C7:C37)</f>
-        <v>1914.570000000007</v>
+        <v>2219.2900000000081</v>
       </c>
       <c r="D38" s="713">
         <f>SUM(D7:D37)</f>
-        <v>5807.9699999999721</v>
+        <v>7224.1600000000326</v>
       </c>
       <c r="E38" s="713">
         <f>SUM(E7:E37)</f>
-        <v>5829</v>
+        <v>7245</v>
       </c>
       <c r="F38" s="714">
         <f>SUM(F7:F37)</f>
-        <v>1334.7947999999999</v>
+        <v>1741.2228</v>
       </c>
       <c r="G38" s="345">
         <f>IF(F38=0,"0",(E38/F38))</f>
-        <v>4.3669633714485556</v>
+        <v>4.160869016877105</v>
       </c>
       <c r="H38" s="348">
         <v>5</v>
@@ -45658,13 +45762,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="C5:C6"/>
     <mergeCell ref="W5:W6"/>
     <mergeCell ref="X5:X6"/>
     <mergeCell ref="I3:K3"/>
@@ -45674,13 +45771,20 @@
     <mergeCell ref="R5:S5"/>
     <mergeCell ref="V5:V6"/>
     <mergeCell ref="Q4:T4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="C5:C6"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="G7:G38">
-    <cfRule type="cellIs" dxfId="87" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="89" priority="1" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="88" priority="3" operator="greaterThan">
       <formula>21</formula>
     </cfRule>
   </conditionalFormatting>
@@ -45974,7 +46078,7 @@
         <v>31</v>
       </c>
       <c r="AG6" s="293"/>
-      <c r="AH6" s="890" t="s">
+      <c r="AH6" s="894" t="s">
         <v>216</v>
       </c>
       <c r="AI6" s="291"/>
@@ -46079,7 +46183,7 @@
       <c r="AG7" s="212" t="s">
         <v>19</v>
       </c>
-      <c r="AH7" s="890"/>
+      <c r="AH7" s="894"/>
       <c r="AI7" s="292" t="s">
         <v>229</v>
       </c>
@@ -46113,7 +46217,7 @@
       </c>
       <c r="H8" s="100">
         <f>'Daily KPIs'!H8</f>
-        <v>0</v>
+        <v>6158</v>
       </c>
       <c r="I8" s="100">
         <f>'Daily KPIs'!I8</f>
@@ -46207,14 +46311,14 @@
       </c>
       <c r="AG8" s="213">
         <f>SUM($B8:AF8)</f>
-        <v>14655</v>
+        <v>20813</v>
       </c>
       <c r="AH8" s="293">
         <v>96325</v>
       </c>
       <c r="AI8" s="294">
         <f>AG8-AH8</f>
-        <v>-81670</v>
+        <v>-75512</v>
       </c>
       <c r="AJ8" s="266"/>
       <c r="AK8" s="266"/>
@@ -46249,7 +46353,7 @@
       </c>
       <c r="H9" s="99">
         <f>'Daily KPIs'!H9</f>
-        <v>0</v>
+        <v>406.428</v>
       </c>
       <c r="I9" s="99">
         <f>'Daily KPIs'!I9</f>
@@ -46343,7 +46447,7 @@
       </c>
       <c r="AG9" s="215">
         <f>SUM($B9:AF9)</f>
-        <v>1334.7947999999999</v>
+        <v>1741.2228</v>
       </c>
       <c r="AH9" s="214"/>
       <c r="AI9" s="265"/>
@@ -46444,11 +46548,11 @@
         <f>'Daily KPIs'!X10</f>
         <v>0</v>
       </c>
-      <c r="Y10" s="1018">
+      <c r="Y10" s="1022">
         <f>'Daily KPIs'!Y10</f>
         <v>0</v>
       </c>
-      <c r="Z10" s="1018"/>
+      <c r="Z10" s="1022"/>
       <c r="AA10" s="163">
         <f>'Daily KPIs'!AA10</f>
         <v>0</v>
@@ -46823,9 +46927,9 @@
         <f>+'Water '!$D12</f>
         <v>250</v>
       </c>
-      <c r="H16" s="110" t="str">
+      <c r="H16" s="110">
         <f>+'Water '!$D13</f>
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="I16" s="110" t="str">
         <f>+'Water '!$D14</f>
@@ -46925,7 +47029,7 @@
       </c>
       <c r="AG16" s="220">
         <f>SUM($B16:AF16)</f>
-        <v>574</v>
+        <v>808</v>
       </c>
       <c r="AH16" s="221"/>
     </row>
@@ -46957,9 +47061,9 @@
         <f>+'Water '!$E12</f>
         <v>92</v>
       </c>
-      <c r="H17" s="114" t="str">
+      <c r="H17" s="114">
         <f>+'Water '!$E13</f>
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="I17" s="113" t="str">
         <f>+'Water '!$E14</f>
@@ -47059,7 +47163,7 @@
       </c>
       <c r="AG17" s="222">
         <f>SUM($B17:AF17)</f>
-        <v>648</v>
+        <v>795</v>
       </c>
       <c r="AH17" s="223"/>
       <c r="AI17" s="268"/>
@@ -47094,7 +47198,7 @@
       </c>
       <c r="H18" s="118">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="I18" s="118">
         <f t="shared" si="0"/>
@@ -47194,7 +47298,7 @@
       </c>
       <c r="AG18" s="224">
         <f>SUM($B18:AF18)</f>
-        <v>1222</v>
+        <v>1603</v>
       </c>
       <c r="AH18" s="224"/>
       <c r="AI18" s="269"/>
@@ -47308,7 +47412,7 @@
       </c>
       <c r="H21" s="119">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>110.23</v>
       </c>
       <c r="I21" s="119">
         <f t="shared" si="1"/>
@@ -47408,16 +47512,16 @@
       </c>
       <c r="AG21" s="220">
         <f>SUM($B21:AF21)</f>
-        <v>541.66</v>
+        <v>651.89</v>
       </c>
       <c r="AH21" s="225">
         <f>AG24+AG37+AG28</f>
-        <v>1695</v>
+        <v>2157</v>
       </c>
       <c r="AI21" s="271"/>
       <c r="AJ21" s="272">
         <f>(AH21*10)/AG9</f>
-        <v>12.698581085272433</v>
+        <v>12.387846058528524</v>
       </c>
     </row>
     <row r="22" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -47625,7 +47729,7 @@
       </c>
       <c r="H24" s="112">
         <f>'Water '!H13</f>
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="I24" s="112">
         <f>'Water '!H14</f>
@@ -47725,7 +47829,7 @@
       </c>
       <c r="AG24" s="222">
         <f>SUM($B24:AF24)</f>
-        <v>920</v>
+        <v>1139</v>
       </c>
       <c r="AH24" s="222"/>
       <c r="AI24" s="222"/>
@@ -47760,7 +47864,7 @@
       </c>
       <c r="H25" s="118">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="I25" s="118">
         <f t="shared" si="2"/>
@@ -47860,7 +47964,7 @@
       </c>
       <c r="AG25" s="224">
         <f>SUM($B25:AF25)</f>
-        <v>920</v>
+        <v>1139</v>
       </c>
       <c r="AH25" s="224"/>
       <c r="AI25" s="269"/>
@@ -47893,9 +47997,9 @@
         <f t="shared" si="3"/>
         <v>5.6832179892046852</v>
       </c>
-      <c r="H26" s="125" t="str">
+      <c r="H26" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>5.3884082789571588</v>
       </c>
       <c r="I26" s="125" t="str">
         <f t="shared" si="3"/>
@@ -48067,9 +48171,9 @@
         <f>+'Water '!$J12</f>
         <v>234</v>
       </c>
-      <c r="H28" s="111" t="str">
+      <c r="H28" s="111">
         <f>+'Water '!$J13</f>
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="I28" s="127" t="str">
         <f>+'Water '!$J14</f>
@@ -48169,7 +48273,7 @@
       </c>
       <c r="AG28" s="220">
         <f>SUM($B28:AF28)</f>
-        <v>699</v>
+        <v>926</v>
       </c>
       <c r="AH28" s="220"/>
       <c r="AI28" s="271"/>
@@ -48646,9 +48750,9 @@
         <f>+'Water '!$N12</f>
         <v>39</v>
       </c>
-      <c r="H33" s="131" t="str">
+      <c r="H33" s="131">
         <f>+'Water '!$N13</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I33" s="131" t="str">
         <f>+'Water '!$N14</f>
@@ -48748,7 +48852,7 @@
       </c>
       <c r="AG33" s="227">
         <f>SUM($B33:AF33)</f>
-        <v>180</v>
+        <v>230</v>
       </c>
       <c r="AH33" s="227"/>
       <c r="AI33" s="227"/>
@@ -48785,9 +48889,9 @@
         <f>+'Water '!$O12</f>
         <v>99</v>
       </c>
-      <c r="H34" s="134" t="str">
+      <c r="H34" s="134">
         <f>+'Water '!$O13</f>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="I34" s="134" t="str">
         <f>+'Water '!$O14</f>
@@ -48887,7 +48991,7 @@
       </c>
       <c r="AG34" s="228">
         <f>SUM($B34:AF34)</f>
-        <v>391</v>
+        <v>482</v>
       </c>
       <c r="AH34" s="228"/>
       <c r="AI34" s="228"/>
@@ -48922,7 +49026,7 @@
       </c>
       <c r="H35" s="119">
         <f>IF('Entries October 2026'!AC13-'Entries October 2026'!AC12&lt;1,0,'Entries October 2026'!AC13-'Entries October 2026'!AC12)</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I35" s="119">
         <f>IF('Entries October 2026'!AC14-'Entries October 2026'!AC13&lt;1,0,'Entries October 2026'!AC14-'Entries October 2026'!AC13)</f>
@@ -49022,7 +49126,7 @@
       </c>
       <c r="AG35" s="220">
         <f>SUM($B35:AF35)</f>
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="AH35" s="220"/>
       <c r="AI35" s="271"/>
@@ -49055,9 +49159,9 @@
         <f>+'Water '!$M12</f>
         <v>3</v>
       </c>
-      <c r="H36" s="110" t="str">
+      <c r="H36" s="110">
         <f>+'Water '!$M13</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I36" s="110" t="str">
         <f>+'Water '!$M14</f>
@@ -49157,7 +49261,7 @@
       </c>
       <c r="AG36" s="220">
         <f>SUM($B36:AF36)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AH36" s="220"/>
       <c r="AI36" s="271"/>
@@ -49190,9 +49294,9 @@
         <f>+'Water '!$Q12</f>
         <v>16</v>
       </c>
-      <c r="H37" s="131" t="str">
+      <c r="H37" s="131">
         <f>+'Water '!$Q13</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I37" s="131" t="str">
         <f>+'Water '!$Q14</f>
@@ -49292,7 +49396,7 @@
       </c>
       <c r="AG37" s="227">
         <f>SUM($B37:AF37)</f>
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="AH37" s="227"/>
       <c r="AI37" s="227"/>
@@ -49680,7 +49784,7 @@
       </c>
       <c r="H42" s="138">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="I42" s="138">
         <f t="shared" si="4"/>
@@ -49780,7 +49884,7 @@
       </c>
       <c r="AG42" s="230">
         <f>SUM($B42:AF42)</f>
-        <v>1420</v>
+        <v>1824</v>
       </c>
       <c r="AH42" s="230"/>
       <c r="AI42" s="276"/>
@@ -50135,9 +50239,9 @@
         <f>'Daily KPIs'!G76</f>
         <v>201.50999999999476</v>
       </c>
-      <c r="H49" s="187" t="str">
+      <c r="H49" s="187">
         <f>'Daily KPIs'!H76</f>
-        <v>0</v>
+        <v>220.41000000000349</v>
       </c>
       <c r="I49" s="187" t="str">
         <f>'Daily KPIs'!I76</f>
@@ -50237,7 +50341,7 @@
       </c>
       <c r="AG49" s="235">
         <f>SUM($B49:AF49)</f>
-        <v>720.77000000000407</v>
+        <v>941.18000000000757</v>
       </c>
       <c r="AH49" s="236"/>
       <c r="AI49" s="280"/>
@@ -50346,7 +50450,7 @@
       </c>
       <c r="H52" s="141">
         <f>'Elec.OCTOBER 2026'!$B$13</f>
-        <v>0</v>
+        <v>6606</v>
       </c>
       <c r="I52" s="141">
         <f>'Elec.OCTOBER 2026'!$B$14</f>
@@ -50446,7 +50550,7 @@
       </c>
       <c r="AG52" s="224">
         <f>SUM(B52:AC52)</f>
-        <v>34292</v>
+        <v>40898</v>
       </c>
       <c r="AH52" s="224"/>
       <c r="AI52" s="276"/>
@@ -50872,9 +50976,9 @@
         <f t="shared" si="5"/>
         <v>9.574682523684741</v>
       </c>
-      <c r="H59" s="144" t="str">
+      <c r="H59" s="144">
         <f t="shared" si="5"/>
-        <v/>
+        <v>9.3743541291446455</v>
       </c>
       <c r="I59" s="144" t="str">
         <f t="shared" si="5"/>
@@ -50974,7 +51078,7 @@
       </c>
       <c r="AG59" s="238">
         <f>IF(AG$9=0,"",+(AG18*10)/AG$9)</f>
-        <v>9.1549652425975889</v>
+        <v>9.2061739600469288</v>
       </c>
       <c r="AH59" s="239">
         <f>'Daily KPIs'!AI90</f>
@@ -50982,7 +51086,7 @@
       </c>
       <c r="AI59" s="282">
         <f>+AH59-AG59</f>
-        <v>1.0450347574024104</v>
+        <v>0.99382603995307051</v>
       </c>
       <c r="AJ59" s="270"/>
       <c r="AK59" s="270"/>
@@ -51037,9 +51141,9 @@
         <f t="shared" si="8"/>
         <v>6.5510985688369283</v>
       </c>
-      <c r="H62" s="145" t="str">
+      <c r="H62" s="145">
         <f t="shared" si="8"/>
-        <v/>
+        <v>5.5852451110651824</v>
       </c>
       <c r="I62" s="145" t="str">
         <f t="shared" si="8"/>
@@ -51139,14 +51243,14 @@
       </c>
       <c r="AG62" s="241">
         <f>IF(+(AG28*10)/AG$9&lt;1,0,+(AG28*10)/AG$9)</f>
-        <v>5.2367599873778357</v>
+        <v>5.3181017386172522</v>
       </c>
       <c r="AH62" s="241">
         <v>2.5</v>
       </c>
       <c r="AI62" s="242">
         <f t="shared" ref="AI62:AI78" si="11">AH62-AG62</f>
-        <v>-2.7367599873778357</v>
+        <v>-2.8181017386172522</v>
       </c>
     </row>
     <row r="63" spans="1:37" ht="18.75" x14ac:dyDescent="0.3">
@@ -51169,13 +51273,13 @@
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="F63" s="168" t="str">
+      <c r="F63" s="168">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="G63" s="168" t="str">
+        <v>4.5751633986928102</v>
+      </c>
+      <c r="G63" s="168">
         <f t="shared" si="12"/>
-        <v/>
+        <v>5.2442850739578661</v>
       </c>
       <c r="H63" s="168" t="str">
         <f t="shared" si="12"/>
@@ -51279,14 +51383,14 @@
       </c>
       <c r="AG63" s="243">
         <f>IF(+(AG28*10)/AG$93&lt;1,0,+(AG28*10)/AG$93)</f>
-        <v>17.45318352059925</v>
+        <v>7.4407392527119329</v>
       </c>
       <c r="AH63" s="243">
         <v>2.5</v>
       </c>
       <c r="AI63" s="244">
         <f t="shared" si="11"/>
-        <v>-14.95318352059925</v>
+        <v>-4.9407392527119329</v>
       </c>
     </row>
     <row r="64" spans="1:37" s="90" customFormat="1" ht="18" x14ac:dyDescent="0.25">
@@ -51317,9 +51421,9 @@
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H64" s="147" t="str">
+      <c r="H64" s="147">
         <f t="shared" si="14"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I64" s="147" t="str">
         <f t="shared" si="14"/>
@@ -51505,9 +51609,9 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H66" s="145" t="str">
+      <c r="H66" s="145">
         <f t="shared" si="16"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I66" s="145" t="str">
         <f t="shared" si="16"/>
@@ -51617,9 +51721,9 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="H67" s="150" t="str">
+      <c r="H67" s="150">
         <f t="shared" si="18"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I67" s="150" t="str">
         <f t="shared" si="18"/>
@@ -51759,9 +51863,9 @@
         <f t="shared" si="20"/>
         <v>1.0918497614728213</v>
       </c>
-      <c r="H68" s="145" t="str">
+      <c r="H68" s="145">
         <f t="shared" si="20"/>
-        <v/>
+        <v>1.2302302006751504</v>
       </c>
       <c r="I68" s="145" t="str">
         <f t="shared" si="20"/>
@@ -51861,14 +51965,14 @@
       </c>
       <c r="AG68" s="241">
         <f>+(AG33*10)/AG$9</f>
-        <v>1.3485218851616745</v>
+        <v>1.3209107990086049</v>
       </c>
       <c r="AH68" s="241">
         <v>0.7</v>
       </c>
       <c r="AI68" s="242">
         <f t="shared" si="11"/>
-        <v>-0.64852188516167453</v>
+        <v>-0.62091079900860491</v>
       </c>
     </row>
     <row r="69" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -51899,9 +52003,9 @@
         <f t="shared" si="22"/>
         <v>2.7716186252771617</v>
       </c>
-      <c r="H69" s="145" t="str">
+      <c r="H69" s="145">
         <f t="shared" si="22"/>
-        <v/>
+        <v>2.2390189652287735</v>
       </c>
       <c r="I69" s="145" t="str">
         <f t="shared" si="22"/>
@@ -52001,14 +52105,14 @@
       </c>
       <c r="AG69" s="241">
         <f>+(AG34*10)/AG$9</f>
-        <v>2.9292892061011928</v>
+        <v>2.768169587487598</v>
       </c>
       <c r="AH69" s="241">
         <v>2.6</v>
       </c>
       <c r="AI69" s="242">
         <f t="shared" si="11"/>
-        <v>-0.32928920610119272</v>
+        <v>-0.16816958748759792</v>
       </c>
     </row>
     <row r="70" spans="1:37" ht="18.75" x14ac:dyDescent="0.3">
@@ -52176,9 +52280,9 @@
         <f t="shared" si="26"/>
         <v>0.47593451141122983</v>
       </c>
-      <c r="H71" s="145" t="str">
+      <c r="H71" s="145">
         <f t="shared" si="26"/>
-        <v/>
+        <v>0.41827826822955111</v>
       </c>
       <c r="I71" s="145" t="str">
         <f t="shared" si="26"/>
@@ -52278,14 +52382,14 @@
       </c>
       <c r="AG71" s="241">
         <f>+(AG35*10)/AG$9</f>
-        <v>0.48696623630838243</v>
+        <v>0.47093341529871996</v>
       </c>
       <c r="AH71" s="241">
         <v>0.7</v>
       </c>
       <c r="AI71" s="242">
         <f>AH71-AG71</f>
-        <v>0.21303376369161753</v>
+        <v>0.22906658470128</v>
       </c>
     </row>
     <row r="72" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -52316,9 +52420,9 @@
         <f t="shared" si="29"/>
         <v>8.3988443190217019E-2</v>
       </c>
-      <c r="H72" s="145" t="str">
+      <c r="H72" s="145">
         <f t="shared" si="29"/>
-        <v/>
+        <v>7.3813812040509019E-2</v>
       </c>
       <c r="I72" s="145" t="str">
         <f t="shared" si="29"/>
@@ -52418,14 +52522,14 @@
       </c>
       <c r="AG72" s="241">
         <f>+(AG36*10)/AG$9</f>
-        <v>6.7426094258083713E-2</v>
+        <v>6.8917085165666331E-2</v>
       </c>
       <c r="AH72" s="241">
         <v>0.1</v>
       </c>
       <c r="AI72" s="242">
         <f>AH72-AG72</f>
-        <v>3.2573905741916293E-2</v>
+        <v>3.1082914834333675E-2</v>
       </c>
     </row>
     <row r="73" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -52456,9 +52560,9 @@
         <f t="shared" si="31"/>
         <v>0.44793836368115747</v>
       </c>
-      <c r="H73" s="145" t="str">
+      <c r="H73" s="145">
         <f t="shared" si="31"/>
-        <v/>
+        <v>0.3936736642160481</v>
       </c>
       <c r="I73" s="145" t="str">
         <f t="shared" si="31"/>
@@ -52558,14 +52662,14 @@
       </c>
       <c r="AG73" s="241">
         <f>+(AG37*10)/AG$9</f>
-        <v>0.56937590706826258</v>
+        <v>0.52836431960344188</v>
       </c>
       <c r="AH73" s="241">
         <v>0.6</v>
       </c>
       <c r="AI73" s="242">
         <f t="shared" si="11"/>
-        <v>3.0624092931737401E-2</v>
+        <v>7.1635680396558099E-2</v>
       </c>
     </row>
     <row r="74" spans="1:37" s="91" customFormat="1" ht="18" x14ac:dyDescent="0.25">
@@ -52596,9 +52700,9 @@
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="H74" s="150" t="str">
+      <c r="H74" s="150">
         <f t="shared" si="33"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I74" s="150" t="str">
         <f t="shared" si="33"/>
@@ -52738,9 +52842,9 @@
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="H75" s="145" t="str">
+      <c r="H75" s="145">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I75" s="145" t="str">
         <f t="shared" si="35"/>
@@ -52964,15 +53068,15 @@
       </c>
       <c r="F78" s="152">
         <f t="shared" si="37"/>
-        <v>11.332242987791805</v>
+        <v>15.907406386484615</v>
       </c>
       <c r="G78" s="152">
         <f t="shared" si="37"/>
-        <v>11.422428273869516</v>
+        <v>16.666713347827383</v>
       </c>
       <c r="H78" s="152">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>9.940260021455213</v>
       </c>
       <c r="I78" s="152">
         <f t="shared" si="37"/>
@@ -53072,7 +53176,7 @@
       </c>
       <c r="AG78" s="253">
         <f>SUM(AG62:AG77)</f>
-        <v>28.091522836874681</v>
+        <v>17.916136197893213</v>
       </c>
       <c r="AH78" s="253">
         <f t="shared" si="37"/>
@@ -53080,7 +53184,7 @@
       </c>
       <c r="AI78" s="253">
         <f t="shared" si="11"/>
-        <v>-12.491522836874683</v>
+        <v>-2.3161361978932149</v>
       </c>
       <c r="AJ78" s="210"/>
       <c r="AK78" s="210"/>
@@ -53115,7 +53219,7 @@
       </c>
       <c r="H79" s="154">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>2.7311110454988334</v>
       </c>
       <c r="I79" s="154">
         <f t="shared" si="38"/>
@@ -53215,7 +53319,7 @@
       </c>
       <c r="AG79" s="254">
         <f t="shared" si="38"/>
-        <v>3.483681536667659</v>
+        <v>3.3080200879519843</v>
       </c>
       <c r="AH79" s="254">
         <f t="shared" si="38"/>
@@ -53223,7 +53327,7 @@
       </c>
       <c r="AI79" s="254">
         <f t="shared" si="38"/>
-        <v>2.5163184633323414</v>
+        <v>2.6919799120480157</v>
       </c>
       <c r="AJ79" s="285"/>
       <c r="AK79" s="285"/>
@@ -53256,9 +53360,9 @@
         <f t="shared" si="39"/>
         <v>#REF!</v>
       </c>
-      <c r="H80" s="155" t="str">
+      <c r="H80" s="155" t="e">
         <f t="shared" si="39"/>
-        <v/>
+        <v>#REF!</v>
       </c>
       <c r="I80" s="155" t="str">
         <f t="shared" si="39"/>
@@ -53399,9 +53503,9 @@
         <f t="shared" si="41"/>
         <v>0.56415037290867309</v>
       </c>
-      <c r="H81" s="157" t="str">
+      <c r="H81" s="157">
         <f t="shared" si="41"/>
-        <v/>
+        <v>0.54231007706162837</v>
       </c>
       <c r="I81" s="157" t="str">
         <f t="shared" si="41"/>
@@ -53501,7 +53605,7 @@
       </c>
       <c r="AG81" s="287">
         <f>IF(AG$9=0,"",+AG49/AG$9)</f>
-        <v>0.53998562175999198</v>
+        <v>0.5405281851351863</v>
       </c>
       <c r="AH81" s="287">
         <f>'Daily KPIs'!AI93</f>
@@ -53509,7 +53613,7 @@
       </c>
       <c r="AI81" s="286">
         <f>AH81-AG81</f>
-        <v>1.1600143782400081</v>
+        <v>1.1594718148648138</v>
       </c>
       <c r="AJ81" s="210"/>
       <c r="AK81" s="210"/>
@@ -53542,9 +53646,9 @@
         <f t="shared" si="43"/>
         <v>20.230016349750272</v>
       </c>
-      <c r="H82" s="144" t="str">
+      <c r="H82" s="144">
         <f t="shared" si="43"/>
-        <v/>
+        <v>16.253801411320087</v>
       </c>
       <c r="I82" s="144" t="str">
         <f t="shared" si="43"/>
@@ -53644,7 +53748,7 @@
       </c>
       <c r="AG82" s="238">
         <f>+(AG52)/AG$9</f>
-        <v>25.690840269980075</v>
+        <v>23.488091242545181</v>
       </c>
       <c r="AH82" s="239">
         <f>'Daily KPIs'!AI94</f>
@@ -53652,7 +53756,7 @@
       </c>
       <c r="AI82" s="286">
         <f>AH82-AG82</f>
-        <v>-3.6908402699800753</v>
+        <v>-1.4880912425451811</v>
       </c>
       <c r="AJ82" s="270"/>
       <c r="AK82" s="270"/>
@@ -53730,9 +53834,9 @@
         <f>IF(G$9=0,"",G54/G$9)</f>
         <v>0</v>
       </c>
-      <c r="H84" s="144" t="str">
+      <c r="H84" s="144">
         <f t="shared" si="46"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I84" s="144" t="str">
         <f t="shared" si="46"/>
@@ -53832,7 +53936,7 @@
       </c>
       <c r="AG84" s="255">
         <f>+(AG54)/AG$9</f>
-        <v>0.71921167208622638</v>
+        <v>0.55133668132533065</v>
       </c>
       <c r="AH84" s="256">
         <f>'Daily KPIs'!AI96</f>
@@ -53840,7 +53944,7 @@
       </c>
       <c r="AI84" s="286">
         <f>AH84-AG84</f>
-        <v>6.4807883279137739</v>
+        <v>6.6486633186746698</v>
       </c>
       <c r="AJ84" s="270"/>
       <c r="AK84" s="270"/>
@@ -54566,11 +54670,11 @@
       </c>
       <c r="F93" s="165">
         <f>'Daily KPIs'!F12</f>
-        <v>0</v>
+        <v>397.8</v>
       </c>
       <c r="G93" s="165">
         <f>'Daily KPIs'!G12</f>
-        <v>0</v>
+        <v>446.2</v>
       </c>
       <c r="H93" s="165">
         <f>'Daily KPIs'!H12</f>
@@ -54674,7 +54778,7 @@
       </c>
       <c r="AG93" s="260">
         <f>SUM(B93:AF93)</f>
-        <v>400.5</v>
+        <v>1244.5</v>
       </c>
       <c r="AH93" s="261"/>
       <c r="AI93" s="289"/>
@@ -54699,9 +54803,9 @@
         <f>'Daily KPIs'!E13</f>
         <v>0</v>
       </c>
-      <c r="F94" s="166">
+      <c r="F94" s="166" t="str">
         <f>'Daily KPIs'!F13</f>
-        <v>0</v>
+        <v>CB</v>
       </c>
       <c r="G94" s="166" t="str">
         <f>'Daily KPIs'!G10</f>
@@ -54833,11 +54937,11 @@
       </c>
       <c r="F95" s="174">
         <f>'Daily KPIs'!F14</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G95" s="174">
         <f>'Daily KPIs'!G14</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H95" s="174">
         <f>'Daily KPIs'!H14</f>
@@ -54941,7 +55045,7 @@
       </c>
       <c r="AG95" s="262">
         <f>SUM($B95:AF95)</f>
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="AH95" s="262"/>
       <c r="AI95" s="290"/>
@@ -54974,9 +55078,9 @@
         <f>+'Water '!$F12</f>
         <v>169</v>
       </c>
-      <c r="H96" s="110" t="str">
+      <c r="H96" s="110">
         <f>+'Water '!$F13</f>
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="I96" s="110" t="str">
         <f>+'Water '!$F14</f>
@@ -55076,7 +55180,7 @@
       </c>
       <c r="AG96" s="220">
         <f>SUM($B96:AF96)</f>
-        <v>742</v>
+        <v>893</v>
       </c>
       <c r="AH96" s="220"/>
       <c r="AI96" s="271"/>
@@ -55264,7 +55368,7 @@
       </c>
       <c r="H101" s="159">
         <f>'Daily KPIs CO2'!H52</f>
-        <v>0</v>
+        <v>6606</v>
       </c>
       <c r="I101" s="159">
         <f>'Daily KPIs CO2'!I52</f>
@@ -55364,7 +55468,7 @@
       </c>
       <c r="AG101" s="263">
         <f>'Daily KPIs CO2'!AG52</f>
-        <v>34292</v>
+        <v>40898</v>
       </c>
       <c r="AH101" s="211"/>
       <c r="AI101" s="271"/>
@@ -55505,30 +55609,30 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B82:AF82">
-    <cfRule type="cellIs" dxfId="85" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="87" priority="3" operator="greaterThan">
       <formula>26</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B84:AF84">
-    <cfRule type="cellIs" dxfId="84" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="86" priority="4" operator="greaterThan">
       <formula>6.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D64:D65 D67 T69:AI70 D71 D73:D77">
-    <cfRule type="cellIs" dxfId="83" priority="5" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="85" priority="5" stopIfTrue="1" operator="greaterThan">
       <formula>3.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D69:S69 B70:S70">
-    <cfRule type="cellIs" dxfId="82" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="84" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>3.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI8">
-    <cfRule type="cellIs" dxfId="81" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="83" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="82" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/data/raw/October_26_Utilities_Tracking.xlsx
+++ b/data/raw/October_26_Utilities_Tracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UTILITIES\Tracking\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{585977AC-6ABF-4180-8504-7477A909231A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAFB328F-B997-47AD-AF4A-C1C938BEF167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="579" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -235,7 +235,7 @@
           <t xml:space="preserve">Tank A 0 kgs 
 Tank B 0 kgs
 Tank C 16300 Kgs
-mobile approx 19600 Kgs
+mobile approx 18900Kgs
 0 kgs after adjustment for MT mobile weight
 </t>
         </r>
@@ -253,7 +253,169 @@
           <t xml:space="preserve">Tank A 0 kgs 
 Tank B 0 kgs
 Tank C 25700 Kgs
-mobile approx 8600 Kgs
+mobile approx 7900 Kgs
+0 kgs after adjustment for MT mobile weight
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D74" authorId="2" shapeId="0" xr:uid="{A9D615D0-28C9-4C13-9020-A7C276975F57}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tank A 0 kgs 
+Tank B 6700 kgs calculated
+Tank C 25700 Kgs
+mobile approx 0 Kgs
+0 kgs after adjustment for MT mobile weight
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F74" authorId="2" shapeId="0" xr:uid="{B1148AEC-E522-4F72-A286-908A2BFB66B0}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tank A 0 kgs 
+Tank B 6700 kgs calculated
+Tank C 25700 Kgs
+mobile approx 0 Kgs
+0 kgs after adjustment for MT mobile weight
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G74" authorId="2" shapeId="0" xr:uid="{72907FFC-D535-40B6-B65A-2A5AE920A761}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tank A 0 kgs 
+Tank B 5100 kgs calculated
+Tank C 25700 Kgs
+mobile approx 0 Kgs
+0 kgs after adjustment for MT mobile weight
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H74" authorId="2" shapeId="0" xr:uid="{A350E13C-FC63-4A46-AEC7-D15BEAB66A89}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tank A 0 kgs 
+Tank B 3600 kgs calculated
+Tank C 25700 Kgs
+mobile approx 0 Kgs
+0 kgs after adjustment for MT mobile weight
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I74" authorId="2" shapeId="0" xr:uid="{70143B87-12C5-483A-9CF2-B1AD2D0FFF73}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tank A 0 kgs 
+Tank B 2200 kgs calculated
+Tank C 25700 Kgs
+mobile approx 0 Kgs
+0 kgs after adjustment for MT mobile weight
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J74" authorId="2" shapeId="0" xr:uid="{F10121C0-B811-45B6-8088-211B562FC585}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tank A 0 kgs 
+Tank B 0 kgs calculated
+Tank C 24900 Kgs
+mobile approx 0 Kgs
+0 kgs after adjustment for MT mobile weight
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K74" authorId="2" shapeId="0" xr:uid="{7E734BED-4455-464B-B3BC-84E273292C6E}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tank A 0 kgs 
+Tank B 0 kgs 
+Tank C 23200 Kgs
+mobile approx 0 Kgs
+0 kgs after adjustment for MT mobile weight
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L74" authorId="2" shapeId="0" xr:uid="{EDC26567-6215-4B13-89B4-8CB9A2D8B046}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tank A 0 kgs 
+Tank B 0 kgs
+Tank C 22400 Kgs
+mobile approx 0 Kgs
+0 kgs after adjustment for MT mobile weight
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M74" authorId="2" shapeId="0" xr:uid="{88951BC3-57B8-4D8F-9300-706887E45023}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tank A 0 kgs 
+Tank B 0 kgs
+Tank C 22400 Kgs
+mobile approx 20800 Kgs
 0 kgs after adjustment for MT mobile weight
 </t>
         </r>
@@ -311,7 +473,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="314">
   <si>
     <t>UTILITY ANALYSIS</t>
   </si>
@@ -2896,6 +3058,9 @@
   </si>
   <si>
     <t>ST/CB</t>
+  </si>
+  <si>
+    <t>GU</t>
   </si>
 </sst>
 </file>
@@ -5991,7 +6156,7 @@
     <xf numFmtId="9" fontId="49" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1024">
+  <cellXfs count="1027">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8423,6 +8588,12 @@
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="75" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="75" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8809,6 +8980,9 @@
     </xf>
     <xf numFmtId="167" fontId="69" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="95" fillId="31" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -8819,477 +8993,7 @@
     <cellStyle name="Normal_February04" xfId="3" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
     <cellStyle name="Percent" xfId="4" builtinId="5"/>
   </cellStyles>
-  <dxfs count="167">
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="120">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -12594,53 +12298,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="18" x14ac:dyDescent="0.2">
-      <c r="B1" s="899" t="s">
+      <c r="B1" s="901" t="s">
         <v>209</v>
       </c>
-      <c r="C1" s="899"/>
-      <c r="D1" s="899"/>
-      <c r="E1" s="899"/>
-      <c r="F1" s="899"/>
-      <c r="G1" s="899"/>
-      <c r="H1" s="899"/>
-      <c r="I1" s="899"/>
-      <c r="J1" s="899"/>
-      <c r="K1" s="899"/>
-      <c r="L1" s="899"/>
-      <c r="M1" s="899"/>
+      <c r="C1" s="901"/>
+      <c r="D1" s="901"/>
+      <c r="E1" s="901"/>
+      <c r="F1" s="901"/>
+      <c r="G1" s="901"/>
+      <c r="H1" s="901"/>
+      <c r="I1" s="901"/>
+      <c r="J1" s="901"/>
+      <c r="K1" s="901"/>
+      <c r="L1" s="901"/>
+      <c r="M1" s="901"/>
       <c r="N1" s="363"/>
-      <c r="O1" s="900" t="str">
+      <c r="O1" s="902" t="str">
         <f>B1</f>
         <v>ENTRIES FOR DAILY CONS. MONITOR</v>
       </c>
-      <c r="P1" s="900"/>
-      <c r="Q1" s="900"/>
-      <c r="R1" s="900"/>
-      <c r="S1" s="900"/>
-      <c r="T1" s="900"/>
-      <c r="U1" s="900"/>
-      <c r="V1" s="900"/>
-      <c r="W1" s="900"/>
-      <c r="X1" s="900"/>
-      <c r="Y1" s="900"/>
-      <c r="Z1" s="900"/>
-      <c r="AA1" s="900"/>
-      <c r="AB1" s="900"/>
+      <c r="P1" s="902"/>
+      <c r="Q1" s="902"/>
+      <c r="R1" s="902"/>
+      <c r="S1" s="902"/>
+      <c r="T1" s="902"/>
+      <c r="U1" s="902"/>
+      <c r="V1" s="902"/>
+      <c r="W1" s="902"/>
+      <c r="X1" s="902"/>
+      <c r="Y1" s="902"/>
+      <c r="Z1" s="902"/>
+      <c r="AA1" s="902"/>
+      <c r="AB1" s="902"/>
     </row>
     <row r="2" spans="1:44" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C2" s="810"/>
       <c r="F2" s="364"/>
       <c r="G2" s="365"/>
-      <c r="O2" s="908" t="s">
+      <c r="O2" s="910" t="s">
         <v>231</v>
       </c>
-      <c r="P2" s="908"/>
-      <c r="Q2" s="908"/>
-      <c r="R2" s="908"/>
-      <c r="S2" s="908"/>
-      <c r="T2" s="908"/>
-      <c r="U2" s="908"/>
-      <c r="V2" s="908"/>
+      <c r="P2" s="910"/>
+      <c r="Q2" s="910"/>
+      <c r="R2" s="910"/>
+      <c r="S2" s="910"/>
+      <c r="T2" s="910"/>
+      <c r="U2" s="910"/>
+      <c r="V2" s="910"/>
     </row>
     <row r="3" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="366"/>
@@ -12658,50 +12362,50 @@
         <v>22</v>
       </c>
       <c r="K3" s="369"/>
-      <c r="L3" s="913" t="s">
+      <c r="L3" s="915" t="s">
         <v>53</v>
       </c>
-      <c r="M3" s="914"/>
-      <c r="N3" s="915"/>
-      <c r="O3" s="901" t="s">
+      <c r="M3" s="916"/>
+      <c r="N3" s="917"/>
+      <c r="O3" s="903" t="s">
         <v>3</v>
       </c>
-      <c r="P3" s="901"/>
-      <c r="Q3" s="901"/>
-      <c r="R3" s="901"/>
-      <c r="S3" s="901"/>
-      <c r="T3" s="901"/>
-      <c r="U3" s="901"/>
-      <c r="V3" s="901"/>
-      <c r="W3" s="901"/>
-      <c r="X3" s="901"/>
-      <c r="Y3" s="901"/>
-      <c r="Z3" s="901"/>
-      <c r="AA3" s="901"/>
-      <c r="AB3" s="901"/>
-      <c r="AC3" s="901"/>
+      <c r="P3" s="903"/>
+      <c r="Q3" s="903"/>
+      <c r="R3" s="903"/>
+      <c r="S3" s="903"/>
+      <c r="T3" s="903"/>
+      <c r="U3" s="903"/>
+      <c r="V3" s="903"/>
+      <c r="W3" s="903"/>
+      <c r="X3" s="903"/>
+      <c r="Y3" s="903"/>
+      <c r="Z3" s="903"/>
+      <c r="AA3" s="903"/>
+      <c r="AB3" s="903"/>
+      <c r="AC3" s="903"/>
       <c r="AD3" s="372"/>
       <c r="AE3" s="373"/>
       <c r="AF3" s="372"/>
-      <c r="AG3" s="921" t="s">
+      <c r="AG3" s="923" t="s">
         <v>206</v>
       </c>
-      <c r="AH3" s="919" t="s">
+      <c r="AH3" s="921" t="s">
         <v>204</v>
       </c>
-      <c r="AI3" s="919" t="s">
+      <c r="AI3" s="921" t="s">
         <v>205</v>
       </c>
-      <c r="AJ3" s="922" t="s">
+      <c r="AJ3" s="924" t="s">
         <v>233</v>
       </c>
       <c r="AK3" s="416"/>
-      <c r="AL3" s="923" t="s">
+      <c r="AL3" s="925" t="s">
         <v>178</v>
       </c>
-      <c r="AM3" s="923"/>
-      <c r="AN3" s="923"/>
-      <c r="AO3" s="923"/>
+      <c r="AM3" s="925"/>
+      <c r="AN3" s="925"/>
+      <c r="AO3" s="925"/>
     </row>
     <row r="4" spans="1:44" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="374"/>
@@ -12735,40 +12439,40 @@
       <c r="K4" s="372" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="909" t="s">
+      <c r="L4" s="911" t="s">
         <v>289</v>
       </c>
       <c r="M4" s="376" t="s">
         <v>260</v>
       </c>
-      <c r="N4" s="916" t="s">
+      <c r="N4" s="918" t="s">
         <v>167</v>
       </c>
-      <c r="O4" s="897" t="s">
+      <c r="O4" s="899" t="s">
         <v>100</v>
       </c>
-      <c r="P4" s="897" t="s">
+      <c r="P4" s="899" t="s">
         <v>101</v>
       </c>
-      <c r="Q4" s="897" t="s">
+      <c r="Q4" s="899" t="s">
         <v>160</v>
       </c>
-      <c r="R4" s="897" t="s">
+      <c r="R4" s="899" t="s">
         <v>171</v>
       </c>
-      <c r="S4" s="897" t="s">
+      <c r="S4" s="899" t="s">
         <v>102</v>
       </c>
-      <c r="T4" s="897" t="s">
+      <c r="T4" s="899" t="s">
         <v>172</v>
       </c>
-      <c r="U4" s="897" t="s">
+      <c r="U4" s="899" t="s">
         <v>103</v>
       </c>
-      <c r="V4" s="906" t="s">
+      <c r="V4" s="908" t="s">
         <v>236</v>
       </c>
-      <c r="W4" s="897" t="s">
+      <c r="W4" s="899" t="s">
         <v>177</v>
       </c>
       <c r="X4" s="372" t="s">
@@ -12780,28 +12484,28 @@
       <c r="Z4" s="372" t="s">
         <v>98</v>
       </c>
-      <c r="AA4" s="901" t="s">
+      <c r="AA4" s="903" t="s">
         <v>68</v>
       </c>
-      <c r="AB4" s="903" t="s">
+      <c r="AB4" s="905" t="s">
         <v>69</v>
       </c>
-      <c r="AC4" s="907" t="s">
+      <c r="AC4" s="909" t="s">
         <v>151</v>
       </c>
-      <c r="AD4" s="897" t="s">
+      <c r="AD4" s="899" t="s">
         <v>154</v>
       </c>
-      <c r="AE4" s="897" t="s">
+      <c r="AE4" s="899" t="s">
         <v>155</v>
       </c>
-      <c r="AF4" s="897" t="s">
+      <c r="AF4" s="899" t="s">
         <v>159</v>
       </c>
-      <c r="AG4" s="921"/>
-      <c r="AH4" s="920"/>
-      <c r="AI4" s="920"/>
-      <c r="AJ4" s="922"/>
+      <c r="AG4" s="923"/>
+      <c r="AH4" s="922"/>
+      <c r="AI4" s="922"/>
+      <c r="AJ4" s="924"/>
       <c r="AK4" s="416"/>
       <c r="AL4" s="378" t="s">
         <v>276</v>
@@ -12850,20 +12554,20 @@
       <c r="K5" s="465" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="910"/>
+      <c r="L5" s="912"/>
       <c r="M5" s="466" t="s">
         <v>261</v>
       </c>
-      <c r="N5" s="917"/>
-      <c r="O5" s="905"/>
-      <c r="P5" s="897"/>
-      <c r="Q5" s="897"/>
-      <c r="R5" s="897"/>
-      <c r="S5" s="905"/>
-      <c r="T5" s="905"/>
-      <c r="U5" s="905"/>
-      <c r="V5" s="906"/>
-      <c r="W5" s="918"/>
+      <c r="N5" s="919"/>
+      <c r="O5" s="907"/>
+      <c r="P5" s="899"/>
+      <c r="Q5" s="899"/>
+      <c r="R5" s="899"/>
+      <c r="S5" s="907"/>
+      <c r="T5" s="907"/>
+      <c r="U5" s="907"/>
+      <c r="V5" s="908"/>
+      <c r="W5" s="920"/>
       <c r="X5" s="372" t="s">
         <v>104</v>
       </c>
@@ -12873,16 +12577,16 @@
       <c r="Z5" s="372" t="s">
         <v>104</v>
       </c>
-      <c r="AA5" s="902"/>
-      <c r="AB5" s="904"/>
-      <c r="AC5" s="907"/>
-      <c r="AD5" s="897"/>
-      <c r="AE5" s="897"/>
-      <c r="AF5" s="898"/>
-      <c r="AG5" s="921"/>
-      <c r="AH5" s="920"/>
-      <c r="AI5" s="920"/>
-      <c r="AJ5" s="922"/>
+      <c r="AA5" s="904"/>
+      <c r="AB5" s="906"/>
+      <c r="AC5" s="909"/>
+      <c r="AD5" s="899"/>
+      <c r="AE5" s="899"/>
+      <c r="AF5" s="900"/>
+      <c r="AG5" s="923"/>
+      <c r="AH5" s="922"/>
+      <c r="AI5" s="922"/>
+      <c r="AJ5" s="924"/>
       <c r="AK5" s="416"/>
       <c r="AL5" s="378" t="s">
         <v>263</v>
@@ -14899,8 +14603,8 @@
     <row r="38" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B38" s="190"/>
       <c r="G38" s="190"/>
-      <c r="I38" s="911"/>
-      <c r="J38" s="911"/>
+      <c r="I38" s="913"/>
+      <c r="J38" s="913"/>
       <c r="R38" s="190"/>
       <c r="S38" s="190"/>
       <c r="T38" s="190"/>
@@ -14908,8 +14612,8 @@
       <c r="V38" s="190"/>
       <c r="W38" s="190"/>
       <c r="Z38" s="190"/>
-      <c r="AA38" s="912"/>
-      <c r="AB38" s="912"/>
+      <c r="AA38" s="914"/>
+      <c r="AB38" s="914"/>
       <c r="AC38" s="190"/>
       <c r="AD38" s="190"/>
       <c r="AI38" s="380"/>
@@ -16606,404 +16310,289 @@
     <mergeCell ref="L4:L5"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
-  <conditionalFormatting sqref="B18:B35">
-    <cfRule type="expression" dxfId="165" priority="75">
-      <formula>B18&lt;B17</formula>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="expression" dxfId="119" priority="14">
+      <formula>B6&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:B35">
+    <cfRule type="expression" dxfId="118" priority="28">
+      <formula>B7&lt;B6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:B17">
+    <cfRule type="expression" dxfId="117" priority="45">
+      <formula>B11&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C35 E35:E37">
-    <cfRule type="expression" dxfId="163" priority="380">
+    <cfRule type="expression" dxfId="116" priority="380">
       <formula>C35&lt;C34</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C6:D6">
+    <cfRule type="expression" dxfId="115" priority="16">
+      <formula>C6&lt;C5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7:D7 H7:J7 R7 T7 W7 AB7">
+    <cfRule type="expression" dxfId="114" priority="32">
+      <formula>C7&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8:D14">
+    <cfRule type="expression" dxfId="113" priority="36">
+      <formula>C8&lt;C7</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C36:D37">
-    <cfRule type="expression" dxfId="159" priority="1433">
+    <cfRule type="expression" dxfId="112" priority="1433">
       <formula>C36&lt;C35</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D35 B36:B37">
-    <cfRule type="expression" dxfId="158" priority="1420">
+    <cfRule type="expression" dxfId="111" priority="1420">
       <formula>B35&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F18:F37">
-    <cfRule type="expression" dxfId="156" priority="51">
-      <formula>F18&lt;#REF!</formula>
+  <conditionalFormatting sqref="E6:E14">
+    <cfRule type="expression" dxfId="110" priority="5">
+      <formula>E6&lt;E5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G18:G37">
-    <cfRule type="expression" dxfId="155" priority="49">
-      <formula>G18&lt;G17</formula>
+  <conditionalFormatting sqref="F6:F37">
+    <cfRule type="expression" dxfId="109" priority="4">
+      <formula>F6&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6:G37">
+    <cfRule type="expression" dxfId="108" priority="2">
+      <formula>G6&lt;G5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G36:J37 L36:O37">
-    <cfRule type="expression" dxfId="154" priority="1267">
+    <cfRule type="expression" dxfId="107" priority="1267">
       <formula>G36&lt;G35</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="G6:O6">
+    <cfRule type="expression" dxfId="106" priority="6">
+      <formula>G6&lt;G5</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="H19:I34">
-    <cfRule type="expression" dxfId="152" priority="381">
+    <cfRule type="expression" dxfId="105" priority="381">
       <formula>H19&lt;H18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H35:I35 R35 T35 W35 AB35 AE35:AI35 P36:P37 S36:S37 X36:Y37">
-    <cfRule type="expression" dxfId="151" priority="1419">
+    <cfRule type="expression" dxfId="104" priority="1419">
       <formula>H35&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H18:J18">
-    <cfRule type="expression" dxfId="150" priority="84">
-      <formula>H18&lt;H17</formula>
+  <conditionalFormatting sqref="H8:J18">
+    <cfRule type="expression" dxfId="103" priority="37">
+      <formula>H8&lt;H7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J19:J35">
-    <cfRule type="expression" dxfId="149" priority="382">
+    <cfRule type="expression" dxfId="102" priority="382">
       <formula>J19&lt;J18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K18:L21">
-    <cfRule type="expression" dxfId="148" priority="87">
-      <formula>K18&lt;K17</formula>
+  <conditionalFormatting sqref="K11:L21">
+    <cfRule type="expression" dxfId="101" priority="40">
+      <formula>K11&lt;K10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K22:M22">
-    <cfRule type="expression" dxfId="147" priority="383">
+    <cfRule type="expression" dxfId="100" priority="383">
       <formula>K22&lt;K21</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K7:O10">
+    <cfRule type="expression" dxfId="99" priority="23">
+      <formula>K7&lt;K6</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="K23:Z23 K24:K37">
-    <cfRule type="expression" dxfId="145" priority="384">
+    <cfRule type="expression" dxfId="98" priority="384">
       <formula>K23&lt;K22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L24:Z27 L28:AC28">
-    <cfRule type="expression" dxfId="144" priority="386">
+    <cfRule type="expression" dxfId="97" priority="386">
       <formula>L24&lt;L23</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="M11:M17">
+    <cfRule type="expression" dxfId="96" priority="42">
+      <formula>M11&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="M18:M21">
-    <cfRule type="expression" dxfId="142" priority="379">
+    <cfRule type="expression" dxfId="95" priority="379">
       <formula>M18&lt;M17</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N18:T22">
-    <cfRule type="expression" dxfId="140" priority="91">
-      <formula>N18&lt;N17</formula>
+  <conditionalFormatting sqref="N11:O12">
+    <cfRule type="expression" dxfId="94" priority="41">
+      <formula>N11&lt;N10</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N13:T22">
+    <cfRule type="expression" dxfId="93" priority="44">
+      <formula>N13&lt;N12</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P8:P12 V8:V12">
+    <cfRule type="expression" dxfId="92" priority="39">
+      <formula>P8&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P6:Q6 X6:Y6 S6:S10">
+    <cfRule type="expression" dxfId="91" priority="13">
+      <formula>P6&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P7:Q7">
+    <cfRule type="expression" dxfId="90" priority="30">
+      <formula>P7&lt;P6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q36">
-    <cfRule type="expression" dxfId="136" priority="1436">
+    <cfRule type="expression" dxfId="89" priority="1436">
       <formula>Q36&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="Q8:R10">
+    <cfRule type="expression" dxfId="88" priority="38">
+      <formula>Q8&lt;Q7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q11:T12">
+    <cfRule type="expression" dxfId="87" priority="43">
+      <formula>Q11&lt;Q10</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R6">
+    <cfRule type="expression" dxfId="86" priority="15">
+      <formula>R6&lt;R5</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="R36">
-    <cfRule type="expression" dxfId="132" priority="1432">
+    <cfRule type="expression" dxfId="85" priority="1432">
       <formula>R36&lt;R35</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB18:AI27">
-    <cfRule type="expression" dxfId="131" priority="81">
-      <formula>AB18&lt;AB17</formula>
+  <conditionalFormatting sqref="T8:T10 AB8:AC10 AE8:AI10 AB11:AI27">
+    <cfRule type="expression" dxfId="84" priority="34">
+      <formula>T8&lt;T7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U18:U22">
-    <cfRule type="expression" dxfId="129" priority="56">
-      <formula>U18&lt;U17</formula>
+  <conditionalFormatting sqref="T6:W6 Z6 AB6">
+    <cfRule type="expression" dxfId="83" priority="12">
+      <formula>T6&lt;T5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:E34">
-    <cfRule type="expression" dxfId="127" priority="94">
-      <formula>C18&lt;C17</formula>
+  <conditionalFormatting sqref="U6:U22">
+    <cfRule type="expression" dxfId="82" priority="9">
+      <formula>U6&lt;U5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V18:Z22">
-    <cfRule type="expression" dxfId="126" priority="93">
-      <formula>V18&lt;V17</formula>
+  <conditionalFormatting sqref="V7">
+    <cfRule type="expression" dxfId="81" priority="25">
+      <formula>V7&lt;V6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V13:X14 C15:E34">
+    <cfRule type="expression" dxfId="80" priority="47">
+      <formula>C13&lt;C12</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V15:Z22">
+    <cfRule type="expression" dxfId="79" priority="46">
+      <formula>V15&lt;V14</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V29:AC29 AA30:AC30 Z30:Z31 V30:Y34 AA31:AB31 AC31:AC37 Z32:AB34 V35 X35:AA35">
-    <cfRule type="expression" dxfId="125" priority="390">
+    <cfRule type="expression" dxfId="78" priority="390">
       <formula>V29&lt;V28</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA18:AA37">
-    <cfRule type="expression" dxfId="121" priority="48">
-      <formula>AA18&lt;AA17</formula>
+  <conditionalFormatting sqref="W8:W12">
+    <cfRule type="expression" dxfId="77" priority="35">
+      <formula>W8&lt;W7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y7:Z14">
+    <cfRule type="expression" dxfId="76" priority="26">
+      <formula>Y7&lt;Y6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA6:AA12">
+    <cfRule type="expression" dxfId="75" priority="8">
+      <formula>AA6&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA6:AA37">
+    <cfRule type="expression" dxfId="74" priority="1">
+      <formula>AA6&lt;AA5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA28:AA37">
-    <cfRule type="expression" dxfId="120" priority="388">
+    <cfRule type="expression" dxfId="73" priority="388">
       <formula>AA28&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AC6:AC7">
+    <cfRule type="expression" dxfId="72" priority="10">
+      <formula>AC6&lt;AC5</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AD28:AD37">
-    <cfRule type="expression" dxfId="118" priority="385">
+    <cfRule type="expression" dxfId="71" priority="385">
       <formula>AD28&lt;AD27</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AD6:AI6">
+    <cfRule type="expression" dxfId="70" priority="7">
+      <formula>AD6&lt;AD5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD7:AI7 X7:X12 AD8:AD10">
+    <cfRule type="expression" dxfId="69" priority="27">
+      <formula>X7&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AE28:AI34 L29:T34 U29:U37 L35:Q35 S35">
-    <cfRule type="expression" dxfId="115" priority="389">
+    <cfRule type="expression" dxfId="68" priority="389">
       <formula>L28&lt;L27</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AJ18:AJ37">
-    <cfRule type="expression" dxfId="114" priority="50">
-      <formula>AJ18&lt;AJ17</formula>
+  <conditionalFormatting sqref="AJ6:AJ37">
+    <cfRule type="expression" dxfId="67" priority="3">
+      <formula>AJ6&lt;AJ5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK6:AK12">
-    <cfRule type="expression" dxfId="113" priority="1309">
+    <cfRule type="expression" dxfId="66" priority="1309">
       <formula>AK6&lt;AK5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK13:AL15">
-    <cfRule type="expression" dxfId="112" priority="1389">
+    <cfRule type="expression" dxfId="65" priority="1389">
       <formula>AK13&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL9:AL14 AL15:AN34 AK16:AK37 AK20:AN21 T36:W37 Z36:Z37 AB36:AB37 AE36:AI37 Q37:R37">
-    <cfRule type="expression" dxfId="111" priority="1326">
+    <cfRule type="expression" dxfId="64" priority="1326">
       <formula>Q9&lt;Q8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO9:AO34">
-    <cfRule type="expression" dxfId="110" priority="1334">
+    <cfRule type="expression" dxfId="63" priority="1334">
       <formula>AO9&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B7:B17">
-    <cfRule type="expression" dxfId="46" priority="28">
-      <formula>B7&lt;B6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B11:B17">
-    <cfRule type="expression" dxfId="45" priority="45">
-      <formula>B11&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C7:D7 H7:J7 R7 T7 W7 AB7">
-    <cfRule type="expression" dxfId="44" priority="32">
-      <formula>C7&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C8:D14">
-    <cfRule type="expression" dxfId="43" priority="36">
-      <formula>C8&lt;C7</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7:E14">
-    <cfRule type="expression" dxfId="42" priority="18">
-      <formula>E7&lt;E6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F17">
-    <cfRule type="expression" dxfId="41" priority="33">
-      <formula>F7&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G7:G17">
-    <cfRule type="expression" dxfId="40" priority="29">
-      <formula>G7&lt;G6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H8:J17">
-    <cfRule type="expression" dxfId="39" priority="37">
-      <formula>H8&lt;H7</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K11:L17">
-    <cfRule type="expression" dxfId="38" priority="40">
-      <formula>K11&lt;K10</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7:O8 K9:N10 O9">
-    <cfRule type="expression" dxfId="37" priority="23">
-      <formula>K7&lt;K6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M11:M17">
-    <cfRule type="expression" dxfId="36" priority="42">
-      <formula>M11&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N11:O12 O10">
-    <cfRule type="expression" dxfId="35" priority="41">
-      <formula>N10&lt;N9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N13:T17">
-    <cfRule type="expression" dxfId="34" priority="44">
-      <formula>N13&lt;N12</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S7:S10">
-    <cfRule type="expression" dxfId="33" priority="22">
-      <formula>S7&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P8:P12 V8:V12">
-    <cfRule type="expression" dxfId="32" priority="39">
-      <formula>P8&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P7:Q7">
-    <cfRule type="expression" dxfId="31" priority="30">
-      <formula>P7&lt;P6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q8:R8">
-    <cfRule type="expression" dxfId="30" priority="38">
-      <formula>Q8&lt;Q7</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q11:T12 Q9:R10 T9:T10">
-    <cfRule type="expression" dxfId="29" priority="43">
-      <formula>Q9&lt;Q8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T8 AB8:AC10 AE8:AI10 AB11:AI17">
-    <cfRule type="expression" dxfId="28" priority="34">
-      <formula>T8&lt;T7</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U7:U17">
-    <cfRule type="expression" dxfId="27" priority="20">
-      <formula>U7&lt;U6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V7">
-    <cfRule type="expression" dxfId="26" priority="25">
-      <formula>V7&lt;V6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V13:X14 C15:E17">
-    <cfRule type="expression" dxfId="25" priority="47">
-      <formula>C13&lt;C12</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V15:Z17">
-    <cfRule type="expression" dxfId="24" priority="46">
-      <formula>V15&lt;V14</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W8:W12">
-    <cfRule type="expression" dxfId="23" priority="35">
-      <formula>W8&lt;W7</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y7:Z14">
-    <cfRule type="expression" dxfId="22" priority="26">
-      <formula>Y7&lt;Y6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA7:AA12">
-    <cfRule type="expression" dxfId="21" priority="19">
-      <formula>AA7&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA7:AA17">
-    <cfRule type="expression" dxfId="20" priority="24">
-      <formula>AA7&lt;AA6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC7">
-    <cfRule type="expression" dxfId="19" priority="21">
-      <formula>AC7&lt;AC6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD7:AI7 X7:X12 AD8:AD10">
-    <cfRule type="expression" dxfId="18" priority="27">
-      <formula>X7&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ12:AJ17">
-    <cfRule type="expression" dxfId="17" priority="31">
-      <formula>AJ12&lt;AJ11</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C6:D6">
-    <cfRule type="expression" dxfId="16" priority="16">
-      <formula>C6&lt;C5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="expression" dxfId="15" priority="14">
-      <formula>B6&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="14" priority="4">
-      <formula>F6&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G6">
-    <cfRule type="expression" dxfId="13" priority="2">
-      <formula>G6&lt;G5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G6:J6 L6:O6">
-    <cfRule type="expression" dxfId="12" priority="11">
-      <formula>G6&lt;G5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P6 S6 X6:Y6">
-    <cfRule type="expression" dxfId="11" priority="13">
-      <formula>P6&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K6">
-    <cfRule type="expression" dxfId="10" priority="6">
-      <formula>K6&lt;K5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q6">
-    <cfRule type="expression" dxfId="9" priority="17">
-      <formula>Q6&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R6">
-    <cfRule type="expression" dxfId="8" priority="15">
-      <formula>R6&lt;R5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="7" priority="5">
-      <formula>E6&lt;E5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC6">
-    <cfRule type="expression" dxfId="6" priority="10">
-      <formula>AC6&lt;AC5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA6">
-    <cfRule type="expression" dxfId="5" priority="1">
-      <formula>AA6&lt;AA5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA6">
-    <cfRule type="expression" dxfId="4" priority="8">
-      <formula>AA6&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD6">
-    <cfRule type="expression" dxfId="3" priority="7">
-      <formula>AD6&lt;AD5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U6">
-    <cfRule type="expression" dxfId="2" priority="9">
-      <formula>U6&lt;U5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ6:AJ11">
-    <cfRule type="expression" dxfId="1" priority="3">
-      <formula>AJ6&lt;AJ5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T6:W6 Z6 AB6 AE6:AI6">
-    <cfRule type="expression" dxfId="0" priority="12">
-      <formula>T6&lt;T5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.1" right="0.5" top="0.32" bottom="0.25" header="0.25" footer="0.25"/>
@@ -17072,8 +16661,8 @@
       </c>
       <c r="B3" s="468"/>
       <c r="C3" s="468"/>
-      <c r="K3" s="896"/>
-      <c r="L3" s="896"/>
+      <c r="K3" s="898"/>
+      <c r="L3" s="898"/>
       <c r="M3" s="498"/>
       <c r="AH3" s="291"/>
       <c r="AI3" s="291"/>
@@ -17219,7 +16808,7 @@
         <v>31</v>
       </c>
       <c r="AG6" s="291"/>
-      <c r="AI6" s="895" t="s">
+      <c r="AI6" s="897" t="s">
         <v>216</v>
       </c>
     </row>
@@ -17324,7 +16913,7 @@
       <c r="AH7" s="477" t="s">
         <v>19</v>
       </c>
-      <c r="AI7" s="895"/>
+      <c r="AI7" s="897"/>
       <c r="AJ7" s="292" t="s">
         <v>229</v>
       </c>
@@ -17831,8 +17420,12 @@
       <c r="I12" s="494">
         <v>345.5</v>
       </c>
-      <c r="J12" s="494"/>
-      <c r="K12" s="494"/>
+      <c r="J12" s="494">
+        <v>343.9</v>
+      </c>
+      <c r="K12" s="494">
+        <v>415.9</v>
+      </c>
       <c r="L12" s="494"/>
       <c r="M12" s="494"/>
       <c r="N12" s="494"/>
@@ -17856,7 +17449,7 @@
       <c r="AG12" s="494"/>
       <c r="AH12" s="495">
         <f>SUM(B12:AF12)</f>
-        <v>1936.2</v>
+        <v>2696</v>
       </c>
       <c r="AI12" s="496"/>
       <c r="AJ12" s="469"/>
@@ -17888,8 +17481,12 @@
       <c r="I13" s="682" t="s">
         <v>312</v>
       </c>
-      <c r="J13" s="669"/>
-      <c r="K13" s="669"/>
+      <c r="J13" s="669" t="s">
+        <v>307</v>
+      </c>
+      <c r="K13" s="1026" t="s">
+        <v>313</v>
+      </c>
       <c r="L13" s="669"/>
       <c r="M13" s="798"/>
       <c r="N13" s="798"/>
@@ -17948,8 +17545,12 @@
         <f>2+5</f>
         <v>7</v>
       </c>
-      <c r="J14" s="498"/>
-      <c r="K14" s="498"/>
+      <c r="J14" s="498">
+        <v>7</v>
+      </c>
+      <c r="K14" s="498">
+        <v>8</v>
+      </c>
       <c r="L14" s="498"/>
       <c r="M14" s="498"/>
       <c r="N14" s="498"/>
@@ -17973,7 +17574,7 @@
       <c r="AG14" s="498"/>
       <c r="AH14" s="468">
         <f>SUM(B14:AF14)</f>
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:149" s="504" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -18014,7 +17615,7 @@
       <c r="AG15" s="718"/>
       <c r="AH15" s="500">
         <f>IF(AH12=0,"",+(AH36*10)/AH12)</f>
-        <v>7.6696622249767588</v>
+        <v>5.508160237388724</v>
       </c>
       <c r="AI15" s="502"/>
       <c r="AJ15" s="503"/>
@@ -25124,34 +24725,39 @@
         <v>1600</v>
       </c>
       <c r="C74" s="888">
-        <v>1142</v>
-      </c>
-      <c r="D74" s="877">
-        <v>0</v>
-      </c>
-      <c r="E74" s="877">
-        <v>0</v>
-      </c>
-      <c r="F74" s="790">
-        <v>1583</v>
-      </c>
-      <c r="G74" s="790">
-        <v>1504</v>
-      </c>
-      <c r="H74" s="790">
-        <v>1416</v>
-      </c>
-      <c r="I74" s="790">
-        <v>1772</v>
-      </c>
-      <c r="J74" s="791">
-        <v>1532</v>
+        <v>1200</v>
+      </c>
+      <c r="D74" s="895">
+        <v>0</v>
+      </c>
+      <c r="E74" s="895">
+        <v>0</v>
+      </c>
+      <c r="F74" s="895">
+        <v>1600</v>
+      </c>
+      <c r="G74" s="895">
+        <v>1500</v>
+      </c>
+      <c r="H74" s="895">
+        <v>1400</v>
+      </c>
+      <c r="I74" s="896">
+        <f>2200+800</f>
+        <v>3000</v>
+      </c>
+      <c r="J74" s="877">
+        <v>1700</v>
       </c>
       <c r="K74" s="877">
-        <v>361</v>
-      </c>
-      <c r="L74" s="877"/>
-      <c r="M74" s="877"/>
+        <v>800</v>
+      </c>
+      <c r="L74" s="877">
+        <v>0</v>
+      </c>
+      <c r="M74" s="877">
+        <v>0</v>
+      </c>
       <c r="N74" s="877"/>
       <c r="O74" s="877"/>
       <c r="P74" s="877"/>
@@ -25174,7 +24780,7 @@
       <c r="AG74" s="790"/>
       <c r="AH74" s="516">
         <f>SUM(B74:AF74)</f>
-        <v>10910</v>
+        <v>12800</v>
       </c>
       <c r="AI74" s="537"/>
       <c r="AJ74" s="537"/>
@@ -27028,7 +26634,7 @@
       </c>
       <c r="C92" s="653">
         <f t="shared" si="35"/>
-        <v>4.0277072399977429</v>
+        <v>4.232266802099204</v>
       </c>
       <c r="D92" s="653" t="str">
         <f t="shared" si="35"/>
@@ -27040,23 +26646,23 @@
       </c>
       <c r="F92" s="653">
         <f t="shared" si="35"/>
-        <v>4.8483623377498448</v>
+        <v>4.9004294001261863</v>
       </c>
       <c r="G92" s="653">
         <f>IF(G$9=0,"",+G74/G$9)</f>
-        <v>4.2106206186028805</v>
+        <v>4.199422159510851</v>
       </c>
       <c r="H92" s="653">
         <f>IF(H$9=0,"",+H74/H$9)</f>
-        <v>3.4840119283120257</v>
+        <v>3.4446445618904211</v>
       </c>
       <c r="I92" s="653">
         <f t="shared" si="35"/>
-        <v>4.9056248581189195</v>
+        <v>8.3052339584406081</v>
       </c>
       <c r="J92" s="653">
         <f t="shared" si="35"/>
-        <v>4.9662219110229371</v>
+        <v>5.5108206584458186</v>
       </c>
       <c r="K92" s="653" t="str">
         <f t="shared" si="35"/>
@@ -27149,18 +26755,18 @@
       <c r="AG92" s="628"/>
       <c r="AH92" s="670">
         <f>IF(AH$9=0,"0",+(AH74)/AH$9)</f>
-        <v>4.5252344660439023</v>
+        <v>5.3091660096573738</v>
       </c>
       <c r="AI92" s="674">
         <v>5</v>
       </c>
       <c r="AJ92" s="675">
         <f>AI92-AH92</f>
-        <v>0.47476553395609766</v>
+        <v>-0.30916600965737384</v>
       </c>
       <c r="AK92" s="673">
         <f t="shared" si="34"/>
-        <v>90.504689320878057</v>
+        <v>106.18332019314747</v>
       </c>
       <c r="AL92" s="629"/>
       <c r="AM92" s="630"/>
@@ -29000,45 +28606,45 @@
   </mergeCells>
   <phoneticPr fontId="32" type="noConversion"/>
   <conditionalFormatting sqref="B93:C93 AH93">
-    <cfRule type="cellIs" dxfId="82" priority="127" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="35" priority="127" operator="greaterThan">
       <formula>$AI$93</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B90:AF90">
-    <cfRule type="cellIs" dxfId="81" priority="36" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="34" priority="36" operator="greaterThan">
       <formula>10.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92:AF92">
-    <cfRule type="cellIs" dxfId="80" priority="26" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="33" priority="26" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="27" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="32" priority="27" operator="lessThanOrEqual">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:AF93">
-    <cfRule type="cellIs" dxfId="78" priority="34" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="34" operator="greaterThan">
       <formula>1.7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B94:AF94">
-    <cfRule type="cellIs" dxfId="77" priority="33" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="30" priority="33" operator="greaterThan">
       <formula>22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96:AF96">
-    <cfRule type="cellIs" dxfId="76" priority="32" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="29" priority="32" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:AG22">
-    <cfRule type="cellIs" dxfId="75" priority="101" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="28" priority="101" operator="greaterThan">
       <formula>400</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42:AG42">
-    <cfRule type="cellIs" dxfId="74" priority="47" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="27" priority="47" operator="greaterThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29053,129 +28659,129 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B94:AG94">
-    <cfRule type="cellIs" dxfId="73" priority="1174" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="1174" operator="greaterThan">
       <formula>$AI$94</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96:AG96">
-    <cfRule type="cellIs" dxfId="72" priority="1176" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="25" priority="1176" operator="greaterThan">
       <formula>$AI$96</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:AH15">
-    <cfRule type="cellIs" dxfId="71" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="greaterThan">
       <formula>3.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54:AH54">
-    <cfRule type="cellIs" dxfId="70" priority="123" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="23" priority="123" operator="greaterThan">
       <formula>3.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B56:AH56">
-    <cfRule type="cellIs" dxfId="69" priority="61" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="22" priority="61" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B57:AH57 B59:AH59 B61:AH61">
-    <cfRule type="cellIs" dxfId="68" priority="62" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="21" priority="62" operator="greaterThan">
       <formula>0.7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58:AH58 B62:AH62">
-    <cfRule type="cellIs" dxfId="67" priority="63" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="63" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B60:AH60">
-    <cfRule type="cellIs" dxfId="66" priority="22" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="19" priority="22" operator="greaterThan">
       <formula>2.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B65:AH65">
-    <cfRule type="cellIs" dxfId="65" priority="56" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="56" operator="greaterThan">
       <formula>0.3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68:AH68">
-    <cfRule type="cellIs" dxfId="64" priority="58" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="58" operator="greaterThan">
       <formula>9.6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69:AH69">
-    <cfRule type="cellIs" dxfId="63" priority="59" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="59" operator="greaterThan">
       <formula>2.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92:AH92">
-    <cfRule type="cellIs" dxfId="62" priority="48" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="48" operator="greaterThan">
       <formula>5.04</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:AH93">
-    <cfRule type="cellIs" dxfId="61" priority="44" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="44" operator="greaterThan">
       <formula>1.7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="43" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="43" operator="greaterThan">
       <formula>1.7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96:AH96">
-    <cfRule type="cellIs" dxfId="59" priority="37" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="37" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E96">
-    <cfRule type="cellIs" dxfId="58" priority="39" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="39" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I63:AH63">
-    <cfRule type="cellIs" dxfId="57" priority="68" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="68" operator="greaterThan">
       <formula>0.6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC54:AG54">
-    <cfRule type="cellIs" dxfId="56" priority="82" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="82" operator="greaterThan">
       <formula>$AI$54</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC55:AG59 AC61:AG61 AC63:AG63 B64:AG64">
-    <cfRule type="cellIs" dxfId="55" priority="1135" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="1135" operator="greaterThan">
       <formula>$AI59</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH94">
-    <cfRule type="cellIs" dxfId="54" priority="28" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="28" operator="lessThanOrEqual">
       <formula>22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH94:AH96 B90:AH90 AH91">
-    <cfRule type="cellIs" dxfId="53" priority="1168" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="1168" operator="greaterThan">
       <formula>$AI$90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH96">
-    <cfRule type="cellIs" dxfId="52" priority="29" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="29" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="30" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="30" operator="lessThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="40" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="40" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ8">
-    <cfRule type="cellIs" dxfId="49" priority="105" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="105" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="106" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="106" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK90:AK96">
-    <cfRule type="cellIs" dxfId="47" priority="50" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="50" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
@@ -31478,24 +31084,24 @@
     </row>
     <row r="6" spans="1:20" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="924" t="s">
+      <c r="A7" s="926" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="383"/>
       <c r="C7" s="383"/>
-      <c r="D7" s="937" t="s">
+      <c r="D7" s="939" t="s">
         <v>254</v>
       </c>
-      <c r="E7" s="940" t="s">
+      <c r="E7" s="942" t="s">
         <v>286</v>
       </c>
-      <c r="F7" s="934" t="s">
+      <c r="F7" s="936" t="s">
         <v>287</v>
       </c>
-      <c r="G7" s="930" t="s">
+      <c r="G7" s="932" t="s">
         <v>255</v>
       </c>
-      <c r="H7" s="930" t="s">
+      <c r="H7" s="932" t="s">
         <v>256</v>
       </c>
       <c r="I7" s="383" t="s">
@@ -31507,33 +31113,33 @@
       <c r="K7" s="390" t="s">
         <v>53</v>
       </c>
-      <c r="L7" s="931" t="s">
+      <c r="L7" s="933" t="s">
         <v>17</v>
       </c>
-      <c r="M7" s="932"/>
-      <c r="N7" s="932"/>
-      <c r="O7" s="932"/>
-      <c r="P7" s="933"/>
-      <c r="Q7" s="928" t="s">
+      <c r="M7" s="934"/>
+      <c r="N7" s="934"/>
+      <c r="O7" s="934"/>
+      <c r="P7" s="935"/>
+      <c r="Q7" s="930" t="s">
         <v>11</v>
       </c>
-      <c r="R7" s="929"/>
-      <c r="S7" s="929"/>
-      <c r="T7" s="929"/>
+      <c r="R7" s="931"/>
+      <c r="S7" s="931"/>
+      <c r="T7" s="931"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="925"/>
+      <c r="A8" s="927"/>
       <c r="B8" s="384" t="s">
         <v>257</v>
       </c>
       <c r="C8" s="384" t="s">
         <v>258</v>
       </c>
-      <c r="D8" s="938"/>
-      <c r="E8" s="941"/>
-      <c r="F8" s="935"/>
-      <c r="G8" s="930"/>
-      <c r="H8" s="930"/>
+      <c r="D8" s="940"/>
+      <c r="E8" s="943"/>
+      <c r="F8" s="937"/>
+      <c r="G8" s="932"/>
+      <c r="H8" s="932"/>
       <c r="I8" s="383"/>
       <c r="J8" s="383"/>
       <c r="K8" s="390"/>
@@ -31556,12 +31162,12 @@
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A9" s="926"/>
+      <c r="A9" s="928"/>
       <c r="B9" s="385"/>
       <c r="C9" s="385"/>
-      <c r="D9" s="939"/>
-      <c r="E9" s="942"/>
-      <c r="F9" s="936"/>
+      <c r="D9" s="941"/>
+      <c r="E9" s="944"/>
+      <c r="F9" s="938"/>
       <c r="G9" s="383" t="s">
         <v>56</v>
       </c>
@@ -31726,7 +31332,7 @@
       </c>
       <c r="K11" s="722">
         <f>'CO2'!E8</f>
-        <v>1142</v>
+        <v>1200</v>
       </c>
       <c r="L11" s="723">
         <f>+'PROD.FIG. '!F6</f>
@@ -31963,7 +31569,7 @@
       </c>
       <c r="K14" s="722">
         <f>'CO2'!E11</f>
-        <v>1583</v>
+        <v>1600</v>
       </c>
       <c r="L14" s="723">
         <f>+'PROD.FIG. '!F9</f>
@@ -32042,7 +31648,7 @@
       </c>
       <c r="K15" s="722">
         <f>'CO2'!E12</f>
-        <v>1504</v>
+        <v>1500</v>
       </c>
       <c r="L15" s="723">
         <f>+'PROD.FIG. '!F10</f>
@@ -32121,7 +31727,7 @@
       </c>
       <c r="K16" s="722">
         <f>'CO2'!E13</f>
-        <v>1416</v>
+        <v>1400</v>
       </c>
       <c r="L16" s="723">
         <f>+'PROD.FIG. '!F11</f>
@@ -32200,7 +31806,7 @@
       </c>
       <c r="K17" s="722">
         <f>'CO2'!E14</f>
-        <v>1772</v>
+        <v>3000</v>
       </c>
       <c r="L17" s="723">
         <f>+'PROD.FIG. '!F12</f>
@@ -32279,7 +31885,7 @@
       </c>
       <c r="K18" s="722">
         <f>'CO2'!E15</f>
-        <v>1532</v>
+        <v>1700</v>
       </c>
       <c r="L18" s="723">
         <f>+'PROD.FIG. '!F13</f>
@@ -32358,7 +31964,7 @@
       </c>
       <c r="K19" s="775">
         <f>'CO2'!E16</f>
-        <v>361</v>
+        <v>800</v>
       </c>
       <c r="L19" s="776">
         <f>+'PROD.FIG. '!F14</f>
@@ -34124,7 +33730,7 @@
       </c>
       <c r="K43" s="20">
         <f t="shared" si="7"/>
-        <v>10910</v>
+        <v>12800</v>
       </c>
       <c r="L43" s="20">
         <f t="shared" si="7"/>
@@ -34199,7 +33805,7 @@
       </c>
       <c r="T44" s="399">
         <f>IF(S44=0,0,K43/P43)</f>
-        <v>4.5252344660439023</v>
+        <v>5.3091660096573738</v>
       </c>
     </row>
     <row r="45" spans="1:32" ht="15" x14ac:dyDescent="0.2">
@@ -34232,12 +33838,12 @@
       <c r="T46" s="2"/>
     </row>
     <row r="47" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="D47" s="927"/>
-      <c r="E47" s="927"/>
-      <c r="F47" s="927"/>
-      <c r="G47" s="927"/>
-      <c r="H47" s="927"/>
-      <c r="I47" s="927"/>
+      <c r="D47" s="929"/>
+      <c r="E47" s="929"/>
+      <c r="F47" s="929"/>
+      <c r="G47" s="929"/>
+      <c r="H47" s="929"/>
+      <c r="I47" s="929"/>
       <c r="AF47" t="s">
         <v>55</v>
       </c>
@@ -34276,41 +33882,41 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="Q10:Q44">
-    <cfRule type="cellIs" dxfId="109" priority="7" operator="between">
+    <cfRule type="cellIs" dxfId="62" priority="7" operator="between">
       <formula>0</formula>
       <formula>22</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="61" priority="8" operator="greaterThan">
       <formula>22</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="107" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="60" priority="9" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:R44">
-    <cfRule type="cellIs" dxfId="106" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="59" priority="1" operator="between">
       <formula>0</formula>
       <formula>10.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="2" operator="greaterThan">
       <formula>10.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S10:S44">
-    <cfRule type="cellIs" dxfId="104" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="57" priority="3" operator="between">
       <formula>0</formula>
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="56" priority="4" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T10:T44">
-    <cfRule type="cellIs" dxfId="102" priority="5" operator="between">
+    <cfRule type="cellIs" dxfId="55" priority="5" operator="between">
       <formula>0</formula>
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="54" priority="6" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34342,16 +33948,16 @@
       <c r="B2" s="8"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="943" t="s">
+      <c r="A3" s="945" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="945" t="s">
+      <c r="B3" s="947" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="944"/>
-      <c r="B4" s="946"/>
+      <c r="A4" s="946"/>
+      <c r="B4" s="948"/>
     </row>
     <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="36">
@@ -34715,31 +34321,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="955" t="s">
+      <c r="A1" s="957" t="s">
         <v>304</v>
       </c>
-      <c r="B1" s="956"/>
-      <c r="C1" s="956"/>
-      <c r="D1" s="956"/>
-      <c r="E1" s="956"/>
-      <c r="F1" s="956"/>
-      <c r="G1" s="956"/>
-      <c r="H1" s="956"/>
-      <c r="I1" s="956"/>
-      <c r="J1" s="956"/>
-      <c r="K1" s="956"/>
-      <c r="L1" s="956"/>
-      <c r="M1" s="956"/>
+      <c r="B1" s="958"/>
+      <c r="C1" s="958"/>
+      <c r="D1" s="958"/>
+      <c r="E1" s="958"/>
+      <c r="F1" s="958"/>
+      <c r="G1" s="958"/>
+      <c r="H1" s="958"/>
+      <c r="I1" s="958"/>
+      <c r="J1" s="958"/>
+      <c r="K1" s="958"/>
+      <c r="L1" s="958"/>
+      <c r="M1" s="958"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
       <c r="F2" s="9"/>
-      <c r="M2" s="947" t="s">
+      <c r="M2" s="949" t="s">
         <v>296</v>
       </c>
-      <c r="N2" s="947" t="s">
+      <c r="N2" s="949" t="s">
         <v>297</v>
       </c>
     </row>
@@ -34748,11 +34354,11 @@
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="9"/>
-      <c r="M3" s="948"/>
-      <c r="N3" s="948"/>
+      <c r="M3" s="950"/>
+      <c r="N3" s="950"/>
     </row>
     <row r="4" spans="1:17" s="339" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="961" t="s">
+      <c r="A4" s="963" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="847" t="s">
@@ -34785,22 +34391,22 @@
       <c r="K4" s="848" t="s">
         <v>40</v>
       </c>
-      <c r="L4" s="957" t="s">
+      <c r="L4" s="959" t="s">
         <v>243</v>
       </c>
-      <c r="M4" s="959" t="s">
+      <c r="M4" s="961" t="s">
         <v>246</v>
       </c>
-      <c r="N4" s="949" t="s">
+      <c r="N4" s="951" t="s">
         <v>246</v>
       </c>
-      <c r="O4" s="952" t="s">
+      <c r="O4" s="954" t="s">
         <v>298</v>
       </c>
       <c r="P4" s="350"/>
     </row>
     <row r="5" spans="1:17" s="339" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="962"/>
+      <c r="A5" s="964"/>
       <c r="B5" s="864" t="s">
         <v>41</v>
       </c>
@@ -34831,10 +34437,10 @@
       <c r="K5" s="865" t="s">
         <v>44</v>
       </c>
-      <c r="L5" s="958"/>
-      <c r="M5" s="960"/>
-      <c r="N5" s="950"/>
-      <c r="O5" s="953"/>
+      <c r="L5" s="960"/>
+      <c r="M5" s="962"/>
+      <c r="N5" s="952"/>
+      <c r="O5" s="955"/>
       <c r="P5" s="350"/>
     </row>
     <row r="6" spans="1:17" s="73" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -34851,8 +34457,8 @@
       <c r="K6" s="836"/>
       <c r="L6" s="869"/>
       <c r="M6" s="833"/>
-      <c r="N6" s="951"/>
-      <c r="O6" s="954"/>
+      <c r="N6" s="953"/>
+      <c r="O6" s="956"/>
       <c r="P6" s="350"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
@@ -37242,27 +36848,27 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="C7:C37">
-    <cfRule type="cellIs" dxfId="100" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="53" priority="13" operator="greaterThan">
       <formula>24</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7:N37">
-    <cfRule type="cellIs" dxfId="99" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="52" priority="9" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="11" operator="between">
+    <cfRule type="cellIs" dxfId="51" priority="11" operator="between">
       <formula>0</formula>
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7:N38">
-    <cfRule type="cellIs" dxfId="97" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="1" operator="lessThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="49" priority="2" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="95" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="48" priority="4" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -37306,120 +36912,120 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="955"/>
-      <c r="B1" s="956"/>
-      <c r="C1" s="956"/>
-      <c r="D1" s="956"/>
-      <c r="E1" s="956"/>
-      <c r="F1" s="956"/>
-      <c r="G1" s="956"/>
-      <c r="H1" s="956"/>
-      <c r="I1" s="956"/>
-      <c r="J1" s="956"/>
-      <c r="K1" s="956"/>
-      <c r="L1" s="956"/>
-      <c r="M1" s="956"/>
-      <c r="N1" s="956"/>
-      <c r="O1" s="956"/>
-      <c r="P1" s="956"/>
-      <c r="Q1" s="956"/>
-      <c r="R1" s="956"/>
-      <c r="S1" s="956"/>
-      <c r="T1" s="956"/>
-      <c r="U1" s="956"/>
-      <c r="V1" s="956"/>
-      <c r="W1" s="956"/>
-      <c r="X1" s="956"/>
-      <c r="Y1" s="956"/>
-      <c r="Z1" s="956"/>
-      <c r="AA1" s="956"/>
+      <c r="A1" s="957"/>
+      <c r="B1" s="958"/>
+      <c r="C1" s="958"/>
+      <c r="D1" s="958"/>
+      <c r="E1" s="958"/>
+      <c r="F1" s="958"/>
+      <c r="G1" s="958"/>
+      <c r="H1" s="958"/>
+      <c r="I1" s="958"/>
+      <c r="J1" s="958"/>
+      <c r="K1" s="958"/>
+      <c r="L1" s="958"/>
+      <c r="M1" s="958"/>
+      <c r="N1" s="958"/>
+      <c r="O1" s="958"/>
+      <c r="P1" s="958"/>
+      <c r="Q1" s="958"/>
+      <c r="R1" s="958"/>
+      <c r="S1" s="958"/>
+      <c r="T1" s="958"/>
+      <c r="U1" s="958"/>
+      <c r="V1" s="958"/>
+      <c r="W1" s="958"/>
+      <c r="X1" s="958"/>
+      <c r="Y1" s="958"/>
+      <c r="Z1" s="958"/>
+      <c r="AA1" s="958"/>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C2" s="17"/>
     </row>
     <row r="3" spans="1:31" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="967" t="s">
+      <c r="B4" s="969" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="965" t="s">
+      <c r="C4" s="967" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="963" t="s">
+      <c r="D4" s="965" t="s">
         <v>106</v>
       </c>
-      <c r="E4" s="965" t="s">
+      <c r="E4" s="967" t="s">
         <v>107</v>
       </c>
-      <c r="F4" s="963" t="s">
+      <c r="F4" s="965" t="s">
         <v>239</v>
       </c>
-      <c r="G4" s="963" t="s">
+      <c r="G4" s="965" t="s">
         <v>108</v>
       </c>
-      <c r="H4" s="963" t="s">
+      <c r="H4" s="965" t="s">
         <v>161</v>
       </c>
-      <c r="I4" s="965" t="s">
+      <c r="I4" s="967" t="s">
         <v>207</v>
       </c>
-      <c r="J4" s="965" t="s">
+      <c r="J4" s="967" t="s">
         <v>109</v>
       </c>
-      <c r="K4" s="965" t="s">
+      <c r="K4" s="967" t="s">
         <v>174</v>
       </c>
-      <c r="L4" s="965" t="s">
+      <c r="L4" s="967" t="s">
         <v>173</v>
       </c>
-      <c r="M4" s="965" t="s">
+      <c r="M4" s="967" t="s">
         <v>103</v>
       </c>
       <c r="N4" s="48"/>
       <c r="O4" s="48"/>
       <c r="P4" s="48"/>
       <c r="Q4" s="48"/>
-      <c r="R4" s="963" t="s">
+      <c r="R4" s="965" t="s">
         <v>110</v>
       </c>
-      <c r="S4" s="963" t="s">
+      <c r="S4" s="965" t="s">
         <v>240</v>
       </c>
       <c r="T4" s="48"/>
-      <c r="U4" s="965" t="s">
+      <c r="U4" s="967" t="s">
         <v>153</v>
       </c>
       <c r="V4" s="48"/>
       <c r="W4" s="48"/>
-      <c r="X4" s="965" t="s">
+      <c r="X4" s="967" t="s">
         <v>175</v>
       </c>
-      <c r="Y4" s="965" t="s">
+      <c r="Y4" s="967" t="s">
         <v>176</v>
       </c>
-      <c r="Z4" s="972" t="s">
+      <c r="Z4" s="974" t="s">
         <v>247</v>
       </c>
-      <c r="AA4" s="974" t="s">
+      <c r="AA4" s="976" t="s">
         <v>243</v>
       </c>
-      <c r="AB4" s="970" t="s">
+      <c r="AB4" s="972" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:31" s="300" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="968"/>
-      <c r="C5" s="966"/>
-      <c r="D5" s="964"/>
-      <c r="E5" s="969"/>
-      <c r="F5" s="964"/>
-      <c r="G5" s="964"/>
-      <c r="H5" s="964"/>
-      <c r="I5" s="969"/>
-      <c r="J5" s="969"/>
-      <c r="K5" s="969"/>
-      <c r="L5" s="969"/>
-      <c r="M5" s="969"/>
+      <c r="B5" s="970"/>
+      <c r="C5" s="968"/>
+      <c r="D5" s="966"/>
+      <c r="E5" s="971"/>
+      <c r="F5" s="966"/>
+      <c r="G5" s="966"/>
+      <c r="H5" s="966"/>
+      <c r="I5" s="971"/>
+      <c r="J5" s="971"/>
+      <c r="K5" s="971"/>
+      <c r="L5" s="971"/>
+      <c r="M5" s="971"/>
       <c r="N5" s="50" t="s">
         <v>111</v>
       </c>
@@ -37432,23 +37038,23 @@
       <c r="Q5" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="R5" s="964"/>
-      <c r="S5" s="964"/>
+      <c r="R5" s="966"/>
+      <c r="S5" s="966"/>
       <c r="T5" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="U5" s="976"/>
+      <c r="U5" s="978"/>
       <c r="V5" s="80" t="s">
         <v>156</v>
       </c>
       <c r="W5" s="80" t="s">
         <v>157</v>
       </c>
-      <c r="X5" s="969"/>
-      <c r="Y5" s="969"/>
-      <c r="Z5" s="973"/>
-      <c r="AA5" s="975"/>
-      <c r="AB5" s="971"/>
+      <c r="X5" s="971"/>
+      <c r="Y5" s="971"/>
+      <c r="Z5" s="975"/>
+      <c r="AA5" s="977"/>
+      <c r="AB5" s="973"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="21" t="s">
@@ -41556,10 +41162,10 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="AB6:AB38">
-    <cfRule type="cellIs" dxfId="94" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="1" operator="lessThan">
       <formula>10.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="46" priority="2" operator="greaterThan">
       <formula>10.2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -41590,15 +41196,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="977" t="s">
+      <c r="A1" s="979" t="s">
         <v>303</v>
       </c>
-      <c r="B1" s="978"/>
-      <c r="C1" s="978"/>
-      <c r="D1" s="979"/>
-      <c r="E1" s="978"/>
-      <c r="F1" s="978"/>
-      <c r="G1" s="980"/>
+      <c r="B1" s="980"/>
+      <c r="C1" s="980"/>
+      <c r="D1" s="981"/>
+      <c r="E1" s="980"/>
+      <c r="F1" s="980"/>
+      <c r="G1" s="982"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B2" s="9"/>
@@ -41611,7 +41217,7 @@
       <c r="D3" s="359"/>
     </row>
     <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="991" t="s">
+      <c r="A4" s="993" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="39" t="s">
@@ -41623,19 +41229,19 @@
       <c r="D4" s="361" t="s">
         <v>285</v>
       </c>
-      <c r="E4" s="981" t="s">
+      <c r="E4" s="983" t="s">
         <v>245</v>
       </c>
-      <c r="F4" s="984" t="s">
+      <c r="F4" s="986" t="s">
         <v>243</v>
       </c>
-      <c r="G4" s="987" t="s">
+      <c r="G4" s="989" t="s">
         <v>253</v>
       </c>
-      <c r="H4" s="990"/>
+      <c r="H4" s="992"/>
     </row>
     <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="992"/>
+      <c r="A5" s="994"/>
       <c r="B5" s="34" t="s">
         <v>48</v>
       </c>
@@ -41645,20 +41251,20 @@
       <c r="D5" s="361" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="982"/>
-      <c r="F5" s="985"/>
-      <c r="G5" s="988"/>
-      <c r="H5" s="990"/>
+      <c r="E5" s="984"/>
+      <c r="F5" s="987"/>
+      <c r="G5" s="990"/>
+      <c r="H5" s="992"/>
     </row>
     <row r="6" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="993"/>
+      <c r="A6" s="995"/>
       <c r="B6" s="40"/>
       <c r="C6" s="362"/>
       <c r="D6" s="361"/>
-      <c r="E6" s="983"/>
-      <c r="F6" s="986"/>
-      <c r="G6" s="989"/>
-      <c r="H6" s="990"/>
+      <c r="E6" s="985"/>
+      <c r="F6" s="988"/>
+      <c r="G6" s="991"/>
+      <c r="H6" s="992"/>
     </row>
     <row r="7" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A7" s="686">
@@ -42663,12 +42269,12 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="cellIs" dxfId="92" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="1" operator="lessThan">
       <formula>22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7:G38">
-    <cfRule type="cellIs" dxfId="91" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="44" priority="2" operator="greaterThan">
       <formula>21</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42699,16 +42305,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="994" t="s">
+      <c r="A1" s="996" t="s">
         <v>302</v>
       </c>
-      <c r="B1" s="956"/>
-      <c r="C1" s="956"/>
-      <c r="D1" s="956"/>
-      <c r="E1" s="956"/>
-      <c r="F1" s="956"/>
-      <c r="G1" s="956"/>
-      <c r="H1" s="956"/>
+      <c r="B1" s="958"/>
+      <c r="C1" s="958"/>
+      <c r="D1" s="958"/>
+      <c r="E1" s="958"/>
+      <c r="F1" s="958"/>
+      <c r="G1" s="958"/>
+      <c r="H1" s="958"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D2" s="12"/>
@@ -43437,11 +43043,11 @@
       <c r="D3" s="85"/>
       <c r="E3" s="85"/>
       <c r="F3" s="1"/>
-      <c r="I3" s="999" t="s">
+      <c r="I3" s="1001" t="s">
         <v>267</v>
       </c>
-      <c r="J3" s="1000"/>
-      <c r="K3" s="1001"/>
+      <c r="J3" s="1002"/>
+      <c r="K3" s="1003"/>
     </row>
     <row r="4" spans="1:24" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
@@ -43454,46 +43060,46 @@
         <v>250</v>
       </c>
       <c r="H4" s="347"/>
-      <c r="I4" s="1002" t="s">
+      <c r="I4" s="1004" t="s">
         <v>262</v>
       </c>
-      <c r="J4" s="1003"/>
-      <c r="K4" s="1004"/>
+      <c r="J4" s="1005"/>
+      <c r="K4" s="1006"/>
       <c r="M4" s="417"/>
       <c r="N4" s="417"/>
       <c r="O4" s="418"/>
       <c r="P4" s="418"/>
-      <c r="Q4" s="1014" t="s">
+      <c r="Q4" s="1016" t="s">
         <v>283</v>
       </c>
-      <c r="R4" s="1014"/>
-      <c r="S4" s="1014"/>
-      <c r="T4" s="1014"/>
+      <c r="R4" s="1016"/>
+      <c r="S4" s="1016"/>
+      <c r="T4" s="1016"/>
       <c r="U4" s="191"/>
       <c r="V4" s="417"/>
       <c r="W4" s="191"/>
       <c r="X4" s="191"/>
     </row>
     <row r="5" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="943" t="s">
+      <c r="A5" s="945" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="945" t="s">
+      <c r="B5" s="947" t="s">
         <v>251</v>
       </c>
-      <c r="C5" s="945" t="s">
+      <c r="C5" s="947" t="s">
         <v>282</v>
       </c>
-      <c r="D5" s="1021" t="s">
+      <c r="D5" s="1023" t="s">
         <v>279</v>
       </c>
-      <c r="E5" s="1021" t="s">
+      <c r="E5" s="1023" t="s">
         <v>280</v>
       </c>
-      <c r="F5" s="1019" t="s">
+      <c r="F5" s="1021" t="s">
         <v>243</v>
       </c>
-      <c r="G5" s="1016" t="s">
+      <c r="G5" s="1018" t="s">
         <v>249</v>
       </c>
       <c r="I5" s="419" t="s">
@@ -43505,43 +43111,43 @@
       <c r="K5" s="421" t="s">
         <v>265</v>
       </c>
-      <c r="M5" s="1005" t="s">
+      <c r="M5" s="1007" t="s">
         <v>266</v>
       </c>
-      <c r="N5" s="1006"/>
-      <c r="O5" s="1007"/>
+      <c r="N5" s="1008"/>
+      <c r="O5" s="1009"/>
       <c r="P5" s="422"/>
-      <c r="Q5" s="1008" t="s">
+      <c r="Q5" s="1010" t="s">
         <v>7</v>
       </c>
-      <c r="R5" s="1010" t="s">
+      <c r="R5" s="1012" t="s">
         <v>267</v>
       </c>
-      <c r="S5" s="1011"/>
+      <c r="S5" s="1013"/>
       <c r="T5" s="452" t="s">
         <v>268</v>
       </c>
       <c r="U5" s="423" t="s">
         <v>269</v>
       </c>
-      <c r="V5" s="1012" t="s">
+      <c r="V5" s="1014" t="s">
         <v>277</v>
       </c>
-      <c r="W5" s="995" t="s">
+      <c r="W5" s="997" t="s">
         <v>270</v>
       </c>
-      <c r="X5" s="997" t="s">
+      <c r="X5" s="999" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1015"/>
-      <c r="B6" s="1018"/>
-      <c r="C6" s="1018"/>
-      <c r="D6" s="1022"/>
-      <c r="E6" s="1022"/>
-      <c r="F6" s="1020"/>
-      <c r="G6" s="1017"/>
+      <c r="A6" s="1017"/>
+      <c r="B6" s="1020"/>
+      <c r="C6" s="1020"/>
+      <c r="D6" s="1024"/>
+      <c r="E6" s="1024"/>
+      <c r="F6" s="1022"/>
+      <c r="G6" s="1019"/>
       <c r="I6" s="424">
         <v>10</v>
       </c>
@@ -43560,7 +43166,7 @@
         <v>273</v>
       </c>
       <c r="P6" s="418"/>
-      <c r="Q6" s="1009"/>
+      <c r="Q6" s="1011"/>
       <c r="R6" s="448" t="s">
         <v>274</v>
       </c>
@@ -43573,9 +43179,9 @@
       <c r="U6" s="429" t="s">
         <v>275</v>
       </c>
-      <c r="V6" s="1013"/>
-      <c r="W6" s="996"/>
-      <c r="X6" s="998"/>
+      <c r="V6" s="1015"/>
+      <c r="W6" s="998"/>
+      <c r="X6" s="1000"/>
     </row>
     <row r="7" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="715">
@@ -43678,14 +43284,14 @@
         <v>1141.6199999999953</v>
       </c>
       <c r="E8" s="716">
-        <v>1142</v>
+        <v>1200</v>
       </c>
       <c r="F8" s="717">
         <v>283.536</v>
       </c>
       <c r="G8" s="336">
         <f t="shared" ref="G8:G37" si="1">IF(F8=0,"0",(E8/F8))</f>
-        <v>4.0277072399977429</v>
+        <v>4.232266802099204</v>
       </c>
       <c r="I8" s="430">
         <v>30</v>
@@ -43905,14 +43511,14 @@
         <v>1583.3100000000559</v>
       </c>
       <c r="E11" s="768">
-        <v>1583</v>
+        <v>1600</v>
       </c>
       <c r="F11" s="769">
         <v>326.50200000000001</v>
       </c>
       <c r="G11" s="336">
         <f t="shared" si="1"/>
-        <v>4.8483623377498448</v>
+        <v>4.9004294001261863</v>
       </c>
       <c r="I11" s="430">
         <v>60</v>
@@ -43978,14 +43584,14 @@
         <v>1503.5599999999395</v>
       </c>
       <c r="E12" s="768">
-        <v>1504</v>
+        <v>1500</v>
       </c>
       <c r="F12" s="769">
         <v>357.19200000000001</v>
       </c>
       <c r="G12" s="336">
         <f>IF(F12=0,"0",(E12/F12))</f>
-        <v>4.2106206186028805</v>
+        <v>4.199422159510851</v>
       </c>
       <c r="I12" s="430">
         <v>70</v>
@@ -44051,14 +43657,14 @@
         <v>1416.1900000000605</v>
       </c>
       <c r="E13" s="716">
-        <v>1416</v>
+        <v>1400</v>
       </c>
       <c r="F13" s="717">
         <v>406.428</v>
       </c>
       <c r="G13" s="336">
         <f t="shared" si="1"/>
-        <v>3.4840119283120257</v>
+        <v>3.4446445618904211</v>
       </c>
       <c r="I13" s="430">
         <v>80</v>
@@ -44121,14 +43727,14 @@
         <v>1771.5</v>
       </c>
       <c r="E14" s="716">
-        <v>1772</v>
+        <v>3000</v>
       </c>
       <c r="F14" s="717">
         <v>361.21800000000002</v>
       </c>
       <c r="G14" s="336">
         <f t="shared" si="1"/>
-        <v>4.9056248581189195</v>
+        <v>8.3052339584406081</v>
       </c>
       <c r="I14" s="430">
         <v>90</v>
@@ -44194,14 +43800,14 @@
         <v>1532</v>
       </c>
       <c r="E15" s="716">
-        <v>1532</v>
+        <v>1700</v>
       </c>
       <c r="F15" s="717">
         <v>308.48400000000004</v>
       </c>
       <c r="G15" s="336">
         <f t="shared" si="1"/>
-        <v>4.9662219110229371</v>
+        <v>5.5108206584458186</v>
       </c>
       <c r="I15" s="430">
         <v>100</v>
@@ -44264,7 +43870,7 @@
         <v>360.76999999990221</v>
       </c>
       <c r="E16" s="716">
-        <v>361</v>
+        <v>800</v>
       </c>
       <c r="F16" s="717">
         <v>0</v>
@@ -45874,7 +45480,7 @@
       </c>
       <c r="E38" s="713">
         <f>SUM(E7:E37)</f>
-        <v>10910</v>
+        <v>12800</v>
       </c>
       <c r="F38" s="714">
         <f>SUM(F7:F37)</f>
@@ -45882,7 +45488,7 @@
       </c>
       <c r="G38" s="345">
         <f>IF(F38=0,"0",(E38/F38))</f>
-        <v>4.5252344660439023</v>
+        <v>5.3091660096573738</v>
       </c>
       <c r="H38" s="348">
         <v>5</v>
@@ -46063,10 +45669,10 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="G7:G38">
-    <cfRule type="cellIs" dxfId="90" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="43" priority="1" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="42" priority="3" operator="greaterThan">
       <formula>21</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46360,7 +45966,7 @@
         <v>31</v>
       </c>
       <c r="AG6" s="293"/>
-      <c r="AH6" s="895" t="s">
+      <c r="AH6" s="897" t="s">
         <v>216</v>
       </c>
       <c r="AI6" s="291"/>
@@ -46465,7 +46071,7 @@
       <c r="AG7" s="212" t="s">
         <v>19</v>
       </c>
-      <c r="AH7" s="895"/>
+      <c r="AH7" s="897"/>
       <c r="AI7" s="292" t="s">
         <v>229</v>
       </c>
@@ -46830,11 +46436,11 @@
         <f>'Daily KPIs'!X10</f>
         <v>0</v>
       </c>
-      <c r="Y10" s="1023">
+      <c r="Y10" s="1025">
         <f>'Daily KPIs'!Y10</f>
         <v>0</v>
       </c>
-      <c r="Z10" s="1023"/>
+      <c r="Z10" s="1025"/>
       <c r="AA10" s="163">
         <f>'Daily KPIs'!AA10</f>
         <v>0</v>
@@ -51571,13 +51177,13 @@
         <f>IF(I$93=0,"",+(I28*10)/I$93)</f>
         <v>5.4124457308248912</v>
       </c>
-      <c r="J63" s="168" t="str">
+      <c r="J63" s="168">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K63" s="168" t="str">
+        <v>5.5830183192788603</v>
+      </c>
+      <c r="K63" s="168">
         <f t="shared" si="12"/>
-        <v/>
+        <v>3.8951671074777594</v>
       </c>
       <c r="L63" s="168" t="str">
         <f t="shared" si="12"/>
@@ -51665,14 +51271,14 @@
       </c>
       <c r="AG63" s="243">
         <f>IF(+(AG28*10)/AG$93&lt;1,0,+(AG28*10)/AG$93)</f>
-        <v>7.6696622249767588</v>
+        <v>5.508160237388724</v>
       </c>
       <c r="AH63" s="243">
         <v>2.5</v>
       </c>
       <c r="AI63" s="244">
         <f t="shared" si="11"/>
-        <v>-5.1696622249767588</v>
+        <v>-3.008160237388724</v>
       </c>
     </row>
     <row r="64" spans="1:37" s="90" customFormat="1" ht="18" x14ac:dyDescent="0.25">
@@ -53366,11 +52972,11 @@
       </c>
       <c r="J78" s="152">
         <f t="shared" si="37"/>
-        <v>11.345807237976683</v>
+        <v>16.928825557255546</v>
       </c>
       <c r="K78" s="152">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>3.8951671074777594</v>
       </c>
       <c r="L78" s="152">
         <f t="shared" si="37"/>
@@ -53458,7 +53064,7 @@
       </c>
       <c r="AG78" s="253">
         <f>SUM(AG62:AG77)</f>
-        <v>19.146585934915784</v>
+        <v>16.985083947327745</v>
       </c>
       <c r="AH78" s="253">
         <f t="shared" si="37"/>
@@ -53466,7 +53072,7 @@
       </c>
       <c r="AI78" s="253">
         <f t="shared" si="11"/>
-        <v>-3.546585934915786</v>
+        <v>-1.3850839473277468</v>
       </c>
       <c r="AJ78" s="210"/>
       <c r="AK78" s="210"/>
@@ -54968,11 +54574,11 @@
       </c>
       <c r="J93" s="165">
         <f>'Daily KPIs'!J12</f>
-        <v>0</v>
+        <v>343.9</v>
       </c>
       <c r="K93" s="165">
         <f>'Daily KPIs'!K12</f>
-        <v>0</v>
+        <v>415.9</v>
       </c>
       <c r="L93" s="165">
         <f>'Daily KPIs'!L12</f>
@@ -55060,7 +54666,7 @@
       </c>
       <c r="AG93" s="260">
         <f>SUM(B93:AF93)</f>
-        <v>1936.2</v>
+        <v>2696</v>
       </c>
       <c r="AH93" s="261"/>
       <c r="AI93" s="289"/>
@@ -55101,13 +54707,13 @@
         <f>'Daily KPIs'!I13</f>
         <v>ST/CB</v>
       </c>
-      <c r="J94" s="166">
+      <c r="J94" s="166" t="str">
         <f>'Daily KPIs'!J13</f>
-        <v>0</v>
-      </c>
-      <c r="K94" s="166">
+        <v>CB</v>
+      </c>
+      <c r="K94" s="166" t="str">
         <f>'Daily KPIs'!K13</f>
-        <v>0</v>
+        <v>GU</v>
       </c>
       <c r="L94" s="166">
         <f>'Daily KPIs'!L13</f>
@@ -55235,11 +54841,11 @@
       </c>
       <c r="J95" s="174">
         <f>'Daily KPIs'!J14</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K95" s="174">
         <f>'Daily KPIs'!K14</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L95" s="174">
         <f>'Daily KPIs'!L14</f>
@@ -55327,7 +54933,7 @@
       </c>
       <c r="AG95" s="262">
         <f>SUM($B95:AF95)</f>
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="AH95" s="262"/>
       <c r="AI95" s="290"/>
@@ -55891,30 +55497,30 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B82:AF82">
-    <cfRule type="cellIs" dxfId="88" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="41" priority="3" operator="greaterThan">
       <formula>26</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B84:AF84">
-    <cfRule type="cellIs" dxfId="87" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="40" priority="4" operator="greaterThan">
       <formula>6.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D64:D65 D67 T69:AI70 D71 D73:D77">
-    <cfRule type="cellIs" dxfId="86" priority="5" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="39" priority="5" stopIfTrue="1" operator="greaterThan">
       <formula>3.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D69:S69 B70:S70">
-    <cfRule type="cellIs" dxfId="85" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>3.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI8">
-    <cfRule type="cellIs" dxfId="84" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="37" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/data/raw/October_26_Utilities_Tracking.xlsx
+++ b/data/raw/October_26_Utilities_Tracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UTILITIES\Tracking\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAFB328F-B997-47AD-AF4A-C1C938BEF167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE9FF72B-664D-4F3F-8D74-B58D0F19F6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="579" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -416,6 +416,24 @@
 Tank B 0 kgs
 Tank C 22400 Kgs
 mobile approx 20800 Kgs
+0 kgs after adjustment for MT mobile weight
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AG74" authorId="2" shapeId="0" xr:uid="{9E9E2207-A18A-4146-9737-6A7919818C19}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tank A 11400 kgs 
+Tank B 6800 kgs
+Tank C 22400 Kgs
+mobile approx 0Kgs
 0 kgs after adjustment for MT mobile weight
 </t>
         </r>
@@ -4042,7 +4060,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4278,6 +4296,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -6156,7 +6180,7 @@
     <xf numFmtId="9" fontId="49" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1027">
+  <cellXfs count="1028">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8594,15 +8618,60 @@
     <xf numFmtId="3" fontId="75" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="167" fontId="95" fillId="31" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="50" fillId="10" borderId="43" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="10" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="10" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="29" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="124" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="77" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="78" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="79" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="100" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="41" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8624,9 +8693,6 @@
     <xf numFmtId="0" fontId="19" fillId="4" borderId="42" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="41" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8642,45 +8708,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="124" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="77" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="78" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="79" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="100" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="10" borderId="43" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="10" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="10" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="29" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="118" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8798,15 +8825,39 @@
     <xf numFmtId="0" fontId="70" fillId="12" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="52" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="53" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="49" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8816,30 +8867,6 @@
     <xf numFmtId="0" fontId="19" fillId="4" borderId="33" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="52" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="53" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -8894,6 +8921,30 @@
     <xf numFmtId="2" fontId="17" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="47" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="72" fillId="18" borderId="56" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="72" fillId="18" borderId="123" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="32" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="32" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="122" fillId="16" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8954,35 +9005,11 @@
     <xf numFmtId="0" fontId="95" fillId="16" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="47" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="72" fillId="18" borderId="56" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="72" fillId="18" borderId="123" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="32" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="32" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="167" fontId="69" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="95" fillId="31" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="3" fontId="75" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -12298,53 +12325,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="18" x14ac:dyDescent="0.2">
-      <c r="B1" s="901" t="s">
+      <c r="B1" s="916" t="s">
         <v>209</v>
       </c>
-      <c r="C1" s="901"/>
-      <c r="D1" s="901"/>
-      <c r="E1" s="901"/>
-      <c r="F1" s="901"/>
-      <c r="G1" s="901"/>
-      <c r="H1" s="901"/>
-      <c r="I1" s="901"/>
-      <c r="J1" s="901"/>
-      <c r="K1" s="901"/>
-      <c r="L1" s="901"/>
-      <c r="M1" s="901"/>
+      <c r="C1" s="916"/>
+      <c r="D1" s="916"/>
+      <c r="E1" s="916"/>
+      <c r="F1" s="916"/>
+      <c r="G1" s="916"/>
+      <c r="H1" s="916"/>
+      <c r="I1" s="916"/>
+      <c r="J1" s="916"/>
+      <c r="K1" s="916"/>
+      <c r="L1" s="916"/>
+      <c r="M1" s="916"/>
       <c r="N1" s="363"/>
-      <c r="O1" s="902" t="str">
+      <c r="O1" s="917" t="str">
         <f>B1</f>
         <v>ENTRIES FOR DAILY CONS. MONITOR</v>
       </c>
-      <c r="P1" s="902"/>
-      <c r="Q1" s="902"/>
-      <c r="R1" s="902"/>
-      <c r="S1" s="902"/>
-      <c r="T1" s="902"/>
-      <c r="U1" s="902"/>
-      <c r="V1" s="902"/>
-      <c r="W1" s="902"/>
-      <c r="X1" s="902"/>
-      <c r="Y1" s="902"/>
-      <c r="Z1" s="902"/>
-      <c r="AA1" s="902"/>
-      <c r="AB1" s="902"/>
+      <c r="P1" s="917"/>
+      <c r="Q1" s="917"/>
+      <c r="R1" s="917"/>
+      <c r="S1" s="917"/>
+      <c r="T1" s="917"/>
+      <c r="U1" s="917"/>
+      <c r="V1" s="917"/>
+      <c r="W1" s="917"/>
+      <c r="X1" s="917"/>
+      <c r="Y1" s="917"/>
+      <c r="Z1" s="917"/>
+      <c r="AA1" s="917"/>
+      <c r="AB1" s="917"/>
     </row>
     <row r="2" spans="1:44" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C2" s="810"/>
       <c r="F2" s="364"/>
       <c r="G2" s="365"/>
-      <c r="O2" s="910" t="s">
+      <c r="O2" s="924" t="s">
         <v>231</v>
       </c>
-      <c r="P2" s="910"/>
-      <c r="Q2" s="910"/>
-      <c r="R2" s="910"/>
-      <c r="S2" s="910"/>
-      <c r="T2" s="910"/>
-      <c r="U2" s="910"/>
-      <c r="V2" s="910"/>
+      <c r="P2" s="924"/>
+      <c r="Q2" s="924"/>
+      <c r="R2" s="924"/>
+      <c r="S2" s="924"/>
+      <c r="T2" s="924"/>
+      <c r="U2" s="924"/>
+      <c r="V2" s="924"/>
     </row>
     <row r="3" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="366"/>
@@ -12362,50 +12389,50 @@
         <v>22</v>
       </c>
       <c r="K3" s="369"/>
-      <c r="L3" s="915" t="s">
+      <c r="L3" s="907" t="s">
         <v>53</v>
       </c>
-      <c r="M3" s="916"/>
-      <c r="N3" s="917"/>
-      <c r="O3" s="903" t="s">
+      <c r="M3" s="908"/>
+      <c r="N3" s="909"/>
+      <c r="O3" s="918" t="s">
         <v>3</v>
       </c>
-      <c r="P3" s="903"/>
-      <c r="Q3" s="903"/>
-      <c r="R3" s="903"/>
-      <c r="S3" s="903"/>
-      <c r="T3" s="903"/>
-      <c r="U3" s="903"/>
-      <c r="V3" s="903"/>
-      <c r="W3" s="903"/>
-      <c r="X3" s="903"/>
-      <c r="Y3" s="903"/>
-      <c r="Z3" s="903"/>
-      <c r="AA3" s="903"/>
-      <c r="AB3" s="903"/>
-      <c r="AC3" s="903"/>
+      <c r="P3" s="918"/>
+      <c r="Q3" s="918"/>
+      <c r="R3" s="918"/>
+      <c r="S3" s="918"/>
+      <c r="T3" s="918"/>
+      <c r="U3" s="918"/>
+      <c r="V3" s="918"/>
+      <c r="W3" s="918"/>
+      <c r="X3" s="918"/>
+      <c r="Y3" s="918"/>
+      <c r="Z3" s="918"/>
+      <c r="AA3" s="918"/>
+      <c r="AB3" s="918"/>
+      <c r="AC3" s="918"/>
       <c r="AD3" s="372"/>
       <c r="AE3" s="373"/>
       <c r="AF3" s="372"/>
-      <c r="AG3" s="923" t="s">
+      <c r="AG3" s="902" t="s">
         <v>206</v>
       </c>
-      <c r="AH3" s="921" t="s">
+      <c r="AH3" s="900" t="s">
         <v>204</v>
       </c>
-      <c r="AI3" s="921" t="s">
+      <c r="AI3" s="900" t="s">
         <v>205</v>
       </c>
-      <c r="AJ3" s="924" t="s">
+      <c r="AJ3" s="903" t="s">
         <v>233</v>
       </c>
       <c r="AK3" s="416"/>
-      <c r="AL3" s="925" t="s">
+      <c r="AL3" s="904" t="s">
         <v>178</v>
       </c>
-      <c r="AM3" s="925"/>
-      <c r="AN3" s="925"/>
-      <c r="AO3" s="925"/>
+      <c r="AM3" s="904"/>
+      <c r="AN3" s="904"/>
+      <c r="AO3" s="904"/>
     </row>
     <row r="4" spans="1:44" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="374"/>
@@ -12439,40 +12466,40 @@
       <c r="K4" s="372" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="911" t="s">
+      <c r="L4" s="925" t="s">
         <v>289</v>
       </c>
       <c r="M4" s="376" t="s">
         <v>260</v>
       </c>
-      <c r="N4" s="918" t="s">
+      <c r="N4" s="910" t="s">
         <v>167</v>
       </c>
-      <c r="O4" s="899" t="s">
+      <c r="O4" s="912" t="s">
         <v>100</v>
       </c>
-      <c r="P4" s="899" t="s">
+      <c r="P4" s="912" t="s">
         <v>101</v>
       </c>
-      <c r="Q4" s="899" t="s">
+      <c r="Q4" s="912" t="s">
         <v>160</v>
       </c>
-      <c r="R4" s="899" t="s">
+      <c r="R4" s="912" t="s">
         <v>171</v>
       </c>
-      <c r="S4" s="899" t="s">
+      <c r="S4" s="912" t="s">
         <v>102</v>
       </c>
-      <c r="T4" s="899" t="s">
+      <c r="T4" s="912" t="s">
         <v>172</v>
       </c>
-      <c r="U4" s="899" t="s">
+      <c r="U4" s="912" t="s">
         <v>103</v>
       </c>
-      <c r="V4" s="908" t="s">
+      <c r="V4" s="922" t="s">
         <v>236</v>
       </c>
-      <c r="W4" s="899" t="s">
+      <c r="W4" s="912" t="s">
         <v>177</v>
       </c>
       <c r="X4" s="372" t="s">
@@ -12484,28 +12511,28 @@
       <c r="Z4" s="372" t="s">
         <v>98</v>
       </c>
-      <c r="AA4" s="903" t="s">
+      <c r="AA4" s="918" t="s">
         <v>68</v>
       </c>
-      <c r="AB4" s="905" t="s">
+      <c r="AB4" s="920" t="s">
         <v>69</v>
       </c>
-      <c r="AC4" s="909" t="s">
+      <c r="AC4" s="923" t="s">
         <v>151</v>
       </c>
-      <c r="AD4" s="899" t="s">
+      <c r="AD4" s="912" t="s">
         <v>154</v>
       </c>
-      <c r="AE4" s="899" t="s">
+      <c r="AE4" s="912" t="s">
         <v>155</v>
       </c>
-      <c r="AF4" s="899" t="s">
+      <c r="AF4" s="912" t="s">
         <v>159</v>
       </c>
-      <c r="AG4" s="923"/>
-      <c r="AH4" s="922"/>
-      <c r="AI4" s="922"/>
-      <c r="AJ4" s="924"/>
+      <c r="AG4" s="902"/>
+      <c r="AH4" s="901"/>
+      <c r="AI4" s="901"/>
+      <c r="AJ4" s="903"/>
       <c r="AK4" s="416"/>
       <c r="AL4" s="378" t="s">
         <v>276</v>
@@ -12554,20 +12581,20 @@
       <c r="K5" s="465" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="912"/>
+      <c r="L5" s="926"/>
       <c r="M5" s="466" t="s">
         <v>261</v>
       </c>
-      <c r="N5" s="919"/>
-      <c r="O5" s="907"/>
-      <c r="P5" s="899"/>
-      <c r="Q5" s="899"/>
-      <c r="R5" s="899"/>
-      <c r="S5" s="907"/>
-      <c r="T5" s="907"/>
-      <c r="U5" s="907"/>
-      <c r="V5" s="908"/>
-      <c r="W5" s="920"/>
+      <c r="N5" s="911"/>
+      <c r="O5" s="913"/>
+      <c r="P5" s="912"/>
+      <c r="Q5" s="912"/>
+      <c r="R5" s="912"/>
+      <c r="S5" s="913"/>
+      <c r="T5" s="913"/>
+      <c r="U5" s="913"/>
+      <c r="V5" s="922"/>
+      <c r="W5" s="914"/>
       <c r="X5" s="372" t="s">
         <v>104</v>
       </c>
@@ -12577,16 +12604,16 @@
       <c r="Z5" s="372" t="s">
         <v>104</v>
       </c>
-      <c r="AA5" s="904"/>
-      <c r="AB5" s="906"/>
-      <c r="AC5" s="909"/>
-      <c r="AD5" s="899"/>
-      <c r="AE5" s="899"/>
-      <c r="AF5" s="900"/>
-      <c r="AG5" s="923"/>
-      <c r="AH5" s="922"/>
-      <c r="AI5" s="922"/>
-      <c r="AJ5" s="924"/>
+      <c r="AA5" s="919"/>
+      <c r="AB5" s="921"/>
+      <c r="AC5" s="923"/>
+      <c r="AD5" s="912"/>
+      <c r="AE5" s="912"/>
+      <c r="AF5" s="915"/>
+      <c r="AG5" s="902"/>
+      <c r="AH5" s="901"/>
+      <c r="AI5" s="901"/>
+      <c r="AJ5" s="903"/>
       <c r="AK5" s="416"/>
       <c r="AL5" s="378" t="s">
         <v>263</v>
@@ -14603,8 +14630,8 @@
     <row r="38" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B38" s="190"/>
       <c r="G38" s="190"/>
-      <c r="I38" s="913"/>
-      <c r="J38" s="913"/>
+      <c r="I38" s="905"/>
+      <c r="J38" s="905"/>
       <c r="R38" s="190"/>
       <c r="S38" s="190"/>
       <c r="T38" s="190"/>
@@ -14612,8 +14639,8 @@
       <c r="V38" s="190"/>
       <c r="W38" s="190"/>
       <c r="Z38" s="190"/>
-      <c r="AA38" s="914"/>
-      <c r="AB38" s="914"/>
+      <c r="AA38" s="906"/>
+      <c r="AB38" s="906"/>
       <c r="AC38" s="190"/>
       <c r="AD38" s="190"/>
       <c r="AI38" s="380"/>
@@ -16279,19 +16306,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="AH3:AH5"/>
-    <mergeCell ref="AG3:AG5"/>
-    <mergeCell ref="AI3:AI5"/>
-    <mergeCell ref="AJ3:AJ5"/>
-    <mergeCell ref="AL3:AO3"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="AA38:AB38"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="S4:S5"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="P4:P5"/>
-    <mergeCell ref="W4:W5"/>
     <mergeCell ref="AF4:AF5"/>
     <mergeCell ref="AE4:AE5"/>
     <mergeCell ref="AD4:AD5"/>
@@ -16308,6 +16322,19 @@
     <mergeCell ref="AC4:AC5"/>
     <mergeCell ref="O2:V2"/>
     <mergeCell ref="L4:L5"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="AA38:AB38"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="S4:S5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="P4:P5"/>
+    <mergeCell ref="W4:W5"/>
+    <mergeCell ref="AH3:AH5"/>
+    <mergeCell ref="AG3:AG5"/>
+    <mergeCell ref="AI3:AI5"/>
+    <mergeCell ref="AJ3:AJ5"/>
+    <mergeCell ref="AL3:AO3"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="B6">
@@ -16661,8 +16688,8 @@
       </c>
       <c r="B3" s="468"/>
       <c r="C3" s="468"/>
-      <c r="K3" s="898"/>
-      <c r="L3" s="898"/>
+      <c r="K3" s="899"/>
+      <c r="L3" s="899"/>
       <c r="M3" s="498"/>
       <c r="AH3" s="291"/>
       <c r="AI3" s="291"/>
@@ -16808,7 +16835,7 @@
         <v>31</v>
       </c>
       <c r="AG6" s="291"/>
-      <c r="AI6" s="897" t="s">
+      <c r="AI6" s="898" t="s">
         <v>216</v>
       </c>
     </row>
@@ -16913,7 +16940,7 @@
       <c r="AH7" s="477" t="s">
         <v>19</v>
       </c>
-      <c r="AI7" s="897"/>
+      <c r="AI7" s="898"/>
       <c r="AJ7" s="292" t="s">
         <v>229</v>
       </c>
@@ -17484,7 +17511,7 @@
       <c r="J13" s="669" t="s">
         <v>307</v>
       </c>
-      <c r="K13" s="1026" t="s">
+      <c r="K13" s="897" t="s">
         <v>313</v>
       </c>
       <c r="L13" s="669"/>
@@ -24755,7 +24782,7 @@
       <c r="L74" s="877">
         <v>0</v>
       </c>
-      <c r="M74" s="877">
+      <c r="M74" s="1027">
         <v>0</v>
       </c>
       <c r="N74" s="877"/>
@@ -24777,7 +24804,9 @@
       <c r="AD74" s="877"/>
       <c r="AE74" s="877"/>
       <c r="AF74" s="877"/>
-      <c r="AG74" s="790"/>
+      <c r="AG74" s="895">
+        <v>0</v>
+      </c>
       <c r="AH74" s="516">
         <f>SUM(B74:AF74)</f>
         <v>12800</v>
@@ -31084,24 +31113,24 @@
     </row>
     <row r="6" spans="1:20" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="926" t="s">
+      <c r="A7" s="927" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="383"/>
       <c r="C7" s="383"/>
-      <c r="D7" s="939" t="s">
+      <c r="D7" s="940" t="s">
         <v>254</v>
       </c>
-      <c r="E7" s="942" t="s">
+      <c r="E7" s="943" t="s">
         <v>286</v>
       </c>
-      <c r="F7" s="936" t="s">
+      <c r="F7" s="937" t="s">
         <v>287</v>
       </c>
-      <c r="G7" s="932" t="s">
+      <c r="G7" s="933" t="s">
         <v>255</v>
       </c>
-      <c r="H7" s="932" t="s">
+      <c r="H7" s="933" t="s">
         <v>256</v>
       </c>
       <c r="I7" s="383" t="s">
@@ -31113,33 +31142,33 @@
       <c r="K7" s="390" t="s">
         <v>53</v>
       </c>
-      <c r="L7" s="933" t="s">
+      <c r="L7" s="934" t="s">
         <v>17</v>
       </c>
-      <c r="M7" s="934"/>
-      <c r="N7" s="934"/>
-      <c r="O7" s="934"/>
-      <c r="P7" s="935"/>
-      <c r="Q7" s="930" t="s">
+      <c r="M7" s="935"/>
+      <c r="N7" s="935"/>
+      <c r="O7" s="935"/>
+      <c r="P7" s="936"/>
+      <c r="Q7" s="931" t="s">
         <v>11</v>
       </c>
-      <c r="R7" s="931"/>
-      <c r="S7" s="931"/>
-      <c r="T7" s="931"/>
+      <c r="R7" s="932"/>
+      <c r="S7" s="932"/>
+      <c r="T7" s="932"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="927"/>
+      <c r="A8" s="928"/>
       <c r="B8" s="384" t="s">
         <v>257</v>
       </c>
       <c r="C8" s="384" t="s">
         <v>258</v>
       </c>
-      <c r="D8" s="940"/>
-      <c r="E8" s="943"/>
-      <c r="F8" s="937"/>
-      <c r="G8" s="932"/>
-      <c r="H8" s="932"/>
+      <c r="D8" s="941"/>
+      <c r="E8" s="944"/>
+      <c r="F8" s="938"/>
+      <c r="G8" s="933"/>
+      <c r="H8" s="933"/>
       <c r="I8" s="383"/>
       <c r="J8" s="383"/>
       <c r="K8" s="390"/>
@@ -31162,12 +31191,12 @@
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A9" s="928"/>
+      <c r="A9" s="929"/>
       <c r="B9" s="385"/>
       <c r="C9" s="385"/>
-      <c r="D9" s="941"/>
-      <c r="E9" s="944"/>
-      <c r="F9" s="938"/>
+      <c r="D9" s="942"/>
+      <c r="E9" s="945"/>
+      <c r="F9" s="939"/>
       <c r="G9" s="383" t="s">
         <v>56</v>
       </c>
@@ -33838,12 +33867,12 @@
       <c r="T46" s="2"/>
     </row>
     <row r="47" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="D47" s="929"/>
-      <c r="E47" s="929"/>
-      <c r="F47" s="929"/>
-      <c r="G47" s="929"/>
-      <c r="H47" s="929"/>
-      <c r="I47" s="929"/>
+      <c r="D47" s="930"/>
+      <c r="E47" s="930"/>
+      <c r="F47" s="930"/>
+      <c r="G47" s="930"/>
+      <c r="H47" s="930"/>
+      <c r="I47" s="930"/>
       <c r="AF47" t="s">
         <v>55</v>
       </c>
@@ -33948,16 +33977,16 @@
       <c r="B2" s="8"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="945" t="s">
+      <c r="A3" s="946" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="947" t="s">
+      <c r="B3" s="948" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="946"/>
-      <c r="B4" s="948"/>
+      <c r="A4" s="947"/>
+      <c r="B4" s="949"/>
     </row>
     <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="36">
@@ -34321,31 +34350,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="957" t="s">
+      <c r="A1" s="958" t="s">
         <v>304</v>
       </c>
-      <c r="B1" s="958"/>
-      <c r="C1" s="958"/>
-      <c r="D1" s="958"/>
-      <c r="E1" s="958"/>
-      <c r="F1" s="958"/>
-      <c r="G1" s="958"/>
-      <c r="H1" s="958"/>
-      <c r="I1" s="958"/>
-      <c r="J1" s="958"/>
-      <c r="K1" s="958"/>
-      <c r="L1" s="958"/>
-      <c r="M1" s="958"/>
+      <c r="B1" s="959"/>
+      <c r="C1" s="959"/>
+      <c r="D1" s="959"/>
+      <c r="E1" s="959"/>
+      <c r="F1" s="959"/>
+      <c r="G1" s="959"/>
+      <c r="H1" s="959"/>
+      <c r="I1" s="959"/>
+      <c r="J1" s="959"/>
+      <c r="K1" s="959"/>
+      <c r="L1" s="959"/>
+      <c r="M1" s="959"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
       <c r="F2" s="9"/>
-      <c r="M2" s="949" t="s">
+      <c r="M2" s="950" t="s">
         <v>296</v>
       </c>
-      <c r="N2" s="949" t="s">
+      <c r="N2" s="950" t="s">
         <v>297</v>
       </c>
     </row>
@@ -34354,11 +34383,11 @@
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="9"/>
-      <c r="M3" s="950"/>
-      <c r="N3" s="950"/>
+      <c r="M3" s="951"/>
+      <c r="N3" s="951"/>
     </row>
     <row r="4" spans="1:17" s="339" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="963" t="s">
+      <c r="A4" s="964" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="847" t="s">
@@ -34391,22 +34420,22 @@
       <c r="K4" s="848" t="s">
         <v>40</v>
       </c>
-      <c r="L4" s="959" t="s">
+      <c r="L4" s="960" t="s">
         <v>243</v>
       </c>
-      <c r="M4" s="961" t="s">
+      <c r="M4" s="962" t="s">
         <v>246</v>
       </c>
-      <c r="N4" s="951" t="s">
+      <c r="N4" s="952" t="s">
         <v>246</v>
       </c>
-      <c r="O4" s="954" t="s">
+      <c r="O4" s="955" t="s">
         <v>298</v>
       </c>
       <c r="P4" s="350"/>
     </row>
     <row r="5" spans="1:17" s="339" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="964"/>
+      <c r="A5" s="965"/>
       <c r="B5" s="864" t="s">
         <v>41</v>
       </c>
@@ -34437,10 +34466,10 @@
       <c r="K5" s="865" t="s">
         <v>44</v>
       </c>
-      <c r="L5" s="960"/>
-      <c r="M5" s="962"/>
-      <c r="N5" s="952"/>
-      <c r="O5" s="955"/>
+      <c r="L5" s="961"/>
+      <c r="M5" s="963"/>
+      <c r="N5" s="953"/>
+      <c r="O5" s="956"/>
       <c r="P5" s="350"/>
     </row>
     <row r="6" spans="1:17" s="73" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -34457,8 +34486,8 @@
       <c r="K6" s="836"/>
       <c r="L6" s="869"/>
       <c r="M6" s="833"/>
-      <c r="N6" s="953"/>
-      <c r="O6" s="956"/>
+      <c r="N6" s="954"/>
+      <c r="O6" s="957"/>
       <c r="P6" s="350"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
@@ -36912,115 +36941,115 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="957"/>
-      <c r="B1" s="958"/>
-      <c r="C1" s="958"/>
-      <c r="D1" s="958"/>
-      <c r="E1" s="958"/>
-      <c r="F1" s="958"/>
-      <c r="G1" s="958"/>
-      <c r="H1" s="958"/>
-      <c r="I1" s="958"/>
-      <c r="J1" s="958"/>
-      <c r="K1" s="958"/>
-      <c r="L1" s="958"/>
-      <c r="M1" s="958"/>
-      <c r="N1" s="958"/>
-      <c r="O1" s="958"/>
-      <c r="P1" s="958"/>
-      <c r="Q1" s="958"/>
-      <c r="R1" s="958"/>
-      <c r="S1" s="958"/>
-      <c r="T1" s="958"/>
-      <c r="U1" s="958"/>
-      <c r="V1" s="958"/>
-      <c r="W1" s="958"/>
-      <c r="X1" s="958"/>
-      <c r="Y1" s="958"/>
-      <c r="Z1" s="958"/>
-      <c r="AA1" s="958"/>
+      <c r="A1" s="958"/>
+      <c r="B1" s="959"/>
+      <c r="C1" s="959"/>
+      <c r="D1" s="959"/>
+      <c r="E1" s="959"/>
+      <c r="F1" s="959"/>
+      <c r="G1" s="959"/>
+      <c r="H1" s="959"/>
+      <c r="I1" s="959"/>
+      <c r="J1" s="959"/>
+      <c r="K1" s="959"/>
+      <c r="L1" s="959"/>
+      <c r="M1" s="959"/>
+      <c r="N1" s="959"/>
+      <c r="O1" s="959"/>
+      <c r="P1" s="959"/>
+      <c r="Q1" s="959"/>
+      <c r="R1" s="959"/>
+      <c r="S1" s="959"/>
+      <c r="T1" s="959"/>
+      <c r="U1" s="959"/>
+      <c r="V1" s="959"/>
+      <c r="W1" s="959"/>
+      <c r="X1" s="959"/>
+      <c r="Y1" s="959"/>
+      <c r="Z1" s="959"/>
+      <c r="AA1" s="959"/>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C2" s="17"/>
     </row>
     <row r="3" spans="1:31" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="969" t="s">
+      <c r="B4" s="978" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="967" t="s">
+      <c r="C4" s="970" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="965" t="s">
+      <c r="D4" s="975" t="s">
         <v>106</v>
       </c>
-      <c r="E4" s="967" t="s">
+      <c r="E4" s="970" t="s">
         <v>107</v>
       </c>
-      <c r="F4" s="965" t="s">
+      <c r="F4" s="975" t="s">
         <v>239</v>
       </c>
-      <c r="G4" s="965" t="s">
+      <c r="G4" s="975" t="s">
         <v>108</v>
       </c>
-      <c r="H4" s="965" t="s">
+      <c r="H4" s="975" t="s">
         <v>161</v>
       </c>
-      <c r="I4" s="967" t="s">
+      <c r="I4" s="970" t="s">
         <v>207</v>
       </c>
-      <c r="J4" s="967" t="s">
+      <c r="J4" s="970" t="s">
         <v>109</v>
       </c>
-      <c r="K4" s="967" t="s">
+      <c r="K4" s="970" t="s">
         <v>174</v>
       </c>
-      <c r="L4" s="967" t="s">
+      <c r="L4" s="970" t="s">
         <v>173</v>
       </c>
-      <c r="M4" s="967" t="s">
+      <c r="M4" s="970" t="s">
         <v>103</v>
       </c>
       <c r="N4" s="48"/>
       <c r="O4" s="48"/>
       <c r="P4" s="48"/>
       <c r="Q4" s="48"/>
-      <c r="R4" s="965" t="s">
+      <c r="R4" s="975" t="s">
         <v>110</v>
       </c>
-      <c r="S4" s="965" t="s">
+      <c r="S4" s="975" t="s">
         <v>240</v>
       </c>
       <c r="T4" s="48"/>
-      <c r="U4" s="967" t="s">
+      <c r="U4" s="970" t="s">
         <v>153</v>
       </c>
       <c r="V4" s="48"/>
       <c r="W4" s="48"/>
-      <c r="X4" s="967" t="s">
+      <c r="X4" s="970" t="s">
         <v>175</v>
       </c>
-      <c r="Y4" s="967" t="s">
+      <c r="Y4" s="970" t="s">
         <v>176</v>
       </c>
-      <c r="Z4" s="974" t="s">
+      <c r="Z4" s="968" t="s">
         <v>247</v>
       </c>
-      <c r="AA4" s="976" t="s">
+      <c r="AA4" s="972" t="s">
         <v>243</v>
       </c>
-      <c r="AB4" s="972" t="s">
+      <c r="AB4" s="966" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:31" s="300" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="970"/>
-      <c r="C5" s="968"/>
-      <c r="D5" s="966"/>
+      <c r="B5" s="979"/>
+      <c r="C5" s="977"/>
+      <c r="D5" s="976"/>
       <c r="E5" s="971"/>
-      <c r="F5" s="966"/>
-      <c r="G5" s="966"/>
-      <c r="H5" s="966"/>
+      <c r="F5" s="976"/>
+      <c r="G5" s="976"/>
+      <c r="H5" s="976"/>
       <c r="I5" s="971"/>
       <c r="J5" s="971"/>
       <c r="K5" s="971"/>
@@ -37038,12 +37067,12 @@
       <c r="Q5" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="R5" s="966"/>
-      <c r="S5" s="966"/>
+      <c r="R5" s="976"/>
+      <c r="S5" s="976"/>
       <c r="T5" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="U5" s="978"/>
+      <c r="U5" s="974"/>
       <c r="V5" s="80" t="s">
         <v>156</v>
       </c>
@@ -37052,9 +37081,9 @@
       </c>
       <c r="X5" s="971"/>
       <c r="Y5" s="971"/>
-      <c r="Z5" s="975"/>
-      <c r="AA5" s="977"/>
-      <c r="AB5" s="973"/>
+      <c r="Z5" s="969"/>
+      <c r="AA5" s="973"/>
+      <c r="AB5" s="967"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="21" t="s">
@@ -41138,6 +41167,16 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:AA1"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="R4:R5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="E4:E5"/>
     <mergeCell ref="AB4:AB5"/>
     <mergeCell ref="Z4:Z5"/>
     <mergeCell ref="L4:L5"/>
@@ -41149,16 +41188,6 @@
     <mergeCell ref="Y4:Y5"/>
     <mergeCell ref="S4:S5"/>
     <mergeCell ref="M4:M5"/>
-    <mergeCell ref="A1:AA1"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="R4:R5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="E4:E5"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="AB6:AB38">
@@ -41196,15 +41225,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="979" t="s">
+      <c r="A1" s="980" t="s">
         <v>303</v>
       </c>
-      <c r="B1" s="980"/>
-      <c r="C1" s="980"/>
-      <c r="D1" s="981"/>
-      <c r="E1" s="980"/>
-      <c r="F1" s="980"/>
-      <c r="G1" s="982"/>
+      <c r="B1" s="981"/>
+      <c r="C1" s="981"/>
+      <c r="D1" s="982"/>
+      <c r="E1" s="981"/>
+      <c r="F1" s="981"/>
+      <c r="G1" s="983"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B2" s="9"/>
@@ -41217,7 +41246,7 @@
       <c r="D3" s="359"/>
     </row>
     <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="993" t="s">
+      <c r="A4" s="994" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="39" t="s">
@@ -41229,19 +41258,19 @@
       <c r="D4" s="361" t="s">
         <v>285</v>
       </c>
-      <c r="E4" s="983" t="s">
+      <c r="E4" s="984" t="s">
         <v>245</v>
       </c>
-      <c r="F4" s="986" t="s">
+      <c r="F4" s="987" t="s">
         <v>243</v>
       </c>
-      <c r="G4" s="989" t="s">
+      <c r="G4" s="990" t="s">
         <v>253</v>
       </c>
-      <c r="H4" s="992"/>
+      <c r="H4" s="993"/>
     </row>
     <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="994"/>
+      <c r="A5" s="995"/>
       <c r="B5" s="34" t="s">
         <v>48</v>
       </c>
@@ -41251,20 +41280,20 @@
       <c r="D5" s="361" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="984"/>
-      <c r="F5" s="987"/>
-      <c r="G5" s="990"/>
-      <c r="H5" s="992"/>
+      <c r="E5" s="985"/>
+      <c r="F5" s="988"/>
+      <c r="G5" s="991"/>
+      <c r="H5" s="993"/>
     </row>
     <row r="6" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="995"/>
+      <c r="A6" s="996"/>
       <c r="B6" s="40"/>
       <c r="C6" s="362"/>
       <c r="D6" s="361"/>
-      <c r="E6" s="985"/>
-      <c r="F6" s="988"/>
-      <c r="G6" s="991"/>
-      <c r="H6" s="992"/>
+      <c r="E6" s="986"/>
+      <c r="F6" s="989"/>
+      <c r="G6" s="992"/>
+      <c r="H6" s="993"/>
     </row>
     <row r="7" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A7" s="686">
@@ -42305,16 +42334,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="996" t="s">
+      <c r="A1" s="997" t="s">
         <v>302</v>
       </c>
-      <c r="B1" s="958"/>
-      <c r="C1" s="958"/>
-      <c r="D1" s="958"/>
-      <c r="E1" s="958"/>
-      <c r="F1" s="958"/>
-      <c r="G1" s="958"/>
-      <c r="H1" s="958"/>
+      <c r="B1" s="959"/>
+      <c r="C1" s="959"/>
+      <c r="D1" s="959"/>
+      <c r="E1" s="959"/>
+      <c r="F1" s="959"/>
+      <c r="G1" s="959"/>
+      <c r="H1" s="959"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D2" s="12"/>
@@ -43043,11 +43072,11 @@
       <c r="D3" s="85"/>
       <c r="E3" s="85"/>
       <c r="F3" s="1"/>
-      <c r="I3" s="1001" t="s">
+      <c r="I3" s="1010" t="s">
         <v>267</v>
       </c>
-      <c r="J3" s="1002"/>
-      <c r="K3" s="1003"/>
+      <c r="J3" s="1011"/>
+      <c r="K3" s="1012"/>
     </row>
     <row r="4" spans="1:24" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
@@ -43060,46 +43089,46 @@
         <v>250</v>
       </c>
       <c r="H4" s="347"/>
-      <c r="I4" s="1004" t="s">
+      <c r="I4" s="1013" t="s">
         <v>262</v>
       </c>
-      <c r="J4" s="1005"/>
-      <c r="K4" s="1006"/>
+      <c r="J4" s="1014"/>
+      <c r="K4" s="1015"/>
       <c r="M4" s="417"/>
       <c r="N4" s="417"/>
       <c r="O4" s="418"/>
       <c r="P4" s="418"/>
-      <c r="Q4" s="1016" t="s">
+      <c r="Q4" s="1025" t="s">
         <v>283</v>
       </c>
-      <c r="R4" s="1016"/>
-      <c r="S4" s="1016"/>
-      <c r="T4" s="1016"/>
+      <c r="R4" s="1025"/>
+      <c r="S4" s="1025"/>
+      <c r="T4" s="1025"/>
       <c r="U4" s="191"/>
       <c r="V4" s="417"/>
       <c r="W4" s="191"/>
       <c r="X4" s="191"/>
     </row>
     <row r="5" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="945" t="s">
+      <c r="A5" s="946" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="947" t="s">
+      <c r="B5" s="948" t="s">
         <v>251</v>
       </c>
-      <c r="C5" s="947" t="s">
+      <c r="C5" s="948" t="s">
         <v>282</v>
       </c>
-      <c r="D5" s="1023" t="s">
+      <c r="D5" s="1004" t="s">
         <v>279</v>
       </c>
-      <c r="E5" s="1023" t="s">
+      <c r="E5" s="1004" t="s">
         <v>280</v>
       </c>
-      <c r="F5" s="1021" t="s">
+      <c r="F5" s="1002" t="s">
         <v>243</v>
       </c>
-      <c r="G5" s="1018" t="s">
+      <c r="G5" s="999" t="s">
         <v>249</v>
       </c>
       <c r="I5" s="419" t="s">
@@ -43111,43 +43140,43 @@
       <c r="K5" s="421" t="s">
         <v>265</v>
       </c>
-      <c r="M5" s="1007" t="s">
+      <c r="M5" s="1016" t="s">
         <v>266</v>
       </c>
-      <c r="N5" s="1008"/>
-      <c r="O5" s="1009"/>
+      <c r="N5" s="1017"/>
+      <c r="O5" s="1018"/>
       <c r="P5" s="422"/>
-      <c r="Q5" s="1010" t="s">
+      <c r="Q5" s="1019" t="s">
         <v>7</v>
       </c>
-      <c r="R5" s="1012" t="s">
+      <c r="R5" s="1021" t="s">
         <v>267</v>
       </c>
-      <c r="S5" s="1013"/>
+      <c r="S5" s="1022"/>
       <c r="T5" s="452" t="s">
         <v>268</v>
       </c>
       <c r="U5" s="423" t="s">
         <v>269</v>
       </c>
-      <c r="V5" s="1014" t="s">
+      <c r="V5" s="1023" t="s">
         <v>277</v>
       </c>
-      <c r="W5" s="997" t="s">
+      <c r="W5" s="1006" t="s">
         <v>270</v>
       </c>
-      <c r="X5" s="999" t="s">
+      <c r="X5" s="1008" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1017"/>
-      <c r="B6" s="1020"/>
-      <c r="C6" s="1020"/>
-      <c r="D6" s="1024"/>
-      <c r="E6" s="1024"/>
-      <c r="F6" s="1022"/>
-      <c r="G6" s="1019"/>
+      <c r="A6" s="998"/>
+      <c r="B6" s="1001"/>
+      <c r="C6" s="1001"/>
+      <c r="D6" s="1005"/>
+      <c r="E6" s="1005"/>
+      <c r="F6" s="1003"/>
+      <c r="G6" s="1000"/>
       <c r="I6" s="424">
         <v>10</v>
       </c>
@@ -43166,7 +43195,7 @@
         <v>273</v>
       </c>
       <c r="P6" s="418"/>
-      <c r="Q6" s="1011"/>
+      <c r="Q6" s="1020"/>
       <c r="R6" s="448" t="s">
         <v>274</v>
       </c>
@@ -43179,9 +43208,9 @@
       <c r="U6" s="429" t="s">
         <v>275</v>
       </c>
-      <c r="V6" s="1015"/>
-      <c r="W6" s="998"/>
-      <c r="X6" s="1000"/>
+      <c r="V6" s="1024"/>
+      <c r="W6" s="1007"/>
+      <c r="X6" s="1009"/>
     </row>
     <row r="7" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="715">
@@ -45650,13 +45679,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="C5:C6"/>
     <mergeCell ref="W5:W6"/>
     <mergeCell ref="X5:X6"/>
     <mergeCell ref="I3:K3"/>
@@ -45666,6 +45688,13 @@
     <mergeCell ref="R5:S5"/>
     <mergeCell ref="V5:V6"/>
     <mergeCell ref="Q4:T4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="C5:C6"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="G7:G38">
@@ -45966,7 +45995,7 @@
         <v>31</v>
       </c>
       <c r="AG6" s="293"/>
-      <c r="AH6" s="897" t="s">
+      <c r="AH6" s="898" t="s">
         <v>216</v>
       </c>
       <c r="AI6" s="291"/>
@@ -46071,7 +46100,7 @@
       <c r="AG7" s="212" t="s">
         <v>19</v>
       </c>
-      <c r="AH7" s="897"/>
+      <c r="AH7" s="898"/>
       <c r="AI7" s="292" t="s">
         <v>229</v>
       </c>
@@ -46436,11 +46465,11 @@
         <f>'Daily KPIs'!X10</f>
         <v>0</v>
       </c>
-      <c r="Y10" s="1025">
+      <c r="Y10" s="1026">
         <f>'Daily KPIs'!Y10</f>
         <v>0</v>
       </c>
-      <c r="Z10" s="1025"/>
+      <c r="Z10" s="1026"/>
       <c r="AA10" s="163">
         <f>'Daily KPIs'!AA10</f>
         <v>0</v>

--- a/data/raw/October_26_Utilities_Tracking.xlsx
+++ b/data/raw/October_26_Utilities_Tracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UTILITIES\Tracking\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE9FF72B-664D-4F3F-8D74-B58D0F19F6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F12A63-4C04-4D16-B520-93C3B609AEC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="579" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
     <author>Alexander Dominguez-Ramon</author>
   </authors>
   <commentList>
-    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{3C6D8AB8-D3CF-44D1-A98B-11EF87531E18}">
+    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{1DBFDD83-D635-4592-90FB-73BF8553290D}">
       <text>
         <r>
           <rPr>
@@ -415,7 +415,7 @@
           <t xml:space="preserve">Tank A 0 kgs 
 Tank B 0 kgs
 Tank C 22400 Kgs
-mobile approx 20800 Kgs
+mobile approx 19800 Kgs
 0 kgs after adjustment for MT mobile weight
 </t>
         </r>
@@ -433,7 +433,8 @@
           <t xml:space="preserve">Tank A 11400 kgs 
 Tank B 6800 kgs
 Tank C 22400 Kgs
-mobile approx 0Kgs
+mobile approx 0 Kgs
+300 Kgs unaccounted for.
 0 kgs after adjustment for MT mobile weight
 </t>
         </r>
@@ -491,7 +492,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="315">
   <si>
     <t>UTILITY ANALYSIS</t>
   </si>
@@ -3080,6 +3081,28 @@
   <si>
     <t>GU</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rose</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/CBfl</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -3100,7 +3123,7 @@
     <numFmt numFmtId="173" formatCode="0.0000000"/>
     <numFmt numFmtId="174" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="146" x14ac:knownFonts="1">
+  <fonts count="147" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -4056,6 +4079,13 @@
       <b/>
       <sz val="20"/>
       <color rgb="FFC00000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFFF00FF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -6180,7 +6210,7 @@
     <xf numFmtId="9" fontId="49" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1028">
+  <cellXfs count="1030">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8621,12 +8651,87 @@
     <xf numFmtId="167" fontId="95" fillId="31" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="75" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="95" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="41" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="42" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="41" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="99" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="124" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="77" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="78" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="79" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="100" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="50" fillId="10" borderId="43" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8642,72 +8747,6 @@
     <xf numFmtId="0" fontId="9" fillId="11" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="124" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="77" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="78" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="79" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="100" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="41" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="41" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="42" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="99" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="118" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8825,6 +8864,27 @@
     <xf numFmtId="0" fontId="70" fillId="12" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="49" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="51" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="33" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="18" borderId="52" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8837,12 +8897,6 @@
     <xf numFmtId="0" fontId="3" fillId="18" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="18" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8852,21 +8906,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="49" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="51" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="33" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -8921,6 +8960,66 @@
     <xf numFmtId="2" fontId="17" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="122" fillId="16" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="16" borderId="88" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="16" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="16" borderId="89" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="16" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="16" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="16" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="16" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="16" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="16" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="120" fillId="16" borderId="83" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="120" fillId="16" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="120" fillId="16" borderId="85" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="16" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="16" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="22" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="22" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="122" fillId="16" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="122" fillId="16" borderId="88" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="16" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8945,70 +9044,7 @@
     <xf numFmtId="0" fontId="111" fillId="32" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="122" fillId="16" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="16" borderId="88" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="16" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="16" borderId="89" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="16" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="16" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="16" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="16" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="16" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="16" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="120" fillId="16" borderId="83" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="120" fillId="16" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="120" fillId="16" borderId="85" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="16" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="16" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="22" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="22" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="122" fillId="16" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="122" fillId="16" borderId="88" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="16" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="167" fontId="69" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="75" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -9020,7 +9056,477 @@
     <cellStyle name="Normal_February04" xfId="3" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
     <cellStyle name="Percent" xfId="4" builtinId="5"/>
   </cellStyles>
-  <dxfs count="120">
+  <dxfs count="167">
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -10076,6 +10582,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF00FF"/>
       <color rgb="FF0000FF"/>
       <color rgb="FF00A44A"/>
       <color rgb="FF170EC2"/>
@@ -10385,7 +10892,7 @@
                   <c:v>2914</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>8829</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
@@ -10711,6 +11218,9 @@
                 <c:pt idx="10">
                   <c:v>1119.5</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>1281.3</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -10860,7 +11370,7 @@
                   <c:v>0.27755051444155199</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>0.12673214444675232</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
@@ -12325,53 +12835,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="18" x14ac:dyDescent="0.2">
-      <c r="B1" s="916" t="s">
+      <c r="B1" s="905" t="s">
         <v>209</v>
       </c>
-      <c r="C1" s="916"/>
-      <c r="D1" s="916"/>
-      <c r="E1" s="916"/>
-      <c r="F1" s="916"/>
-      <c r="G1" s="916"/>
-      <c r="H1" s="916"/>
-      <c r="I1" s="916"/>
-      <c r="J1" s="916"/>
-      <c r="K1" s="916"/>
-      <c r="L1" s="916"/>
-      <c r="M1" s="916"/>
+      <c r="C1" s="905"/>
+      <c r="D1" s="905"/>
+      <c r="E1" s="905"/>
+      <c r="F1" s="905"/>
+      <c r="G1" s="905"/>
+      <c r="H1" s="905"/>
+      <c r="I1" s="905"/>
+      <c r="J1" s="905"/>
+      <c r="K1" s="905"/>
+      <c r="L1" s="905"/>
+      <c r="M1" s="905"/>
       <c r="N1" s="363"/>
-      <c r="O1" s="917" t="str">
+      <c r="O1" s="906" t="str">
         <f>B1</f>
         <v>ENTRIES FOR DAILY CONS. MONITOR</v>
       </c>
-      <c r="P1" s="917"/>
-      <c r="Q1" s="917"/>
-      <c r="R1" s="917"/>
-      <c r="S1" s="917"/>
-      <c r="T1" s="917"/>
-      <c r="U1" s="917"/>
-      <c r="V1" s="917"/>
-      <c r="W1" s="917"/>
-      <c r="X1" s="917"/>
-      <c r="Y1" s="917"/>
-      <c r="Z1" s="917"/>
-      <c r="AA1" s="917"/>
-      <c r="AB1" s="917"/>
+      <c r="P1" s="906"/>
+      <c r="Q1" s="906"/>
+      <c r="R1" s="906"/>
+      <c r="S1" s="906"/>
+      <c r="T1" s="906"/>
+      <c r="U1" s="906"/>
+      <c r="V1" s="906"/>
+      <c r="W1" s="906"/>
+      <c r="X1" s="906"/>
+      <c r="Y1" s="906"/>
+      <c r="Z1" s="906"/>
+      <c r="AA1" s="906"/>
+      <c r="AB1" s="906"/>
     </row>
     <row r="2" spans="1:44" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C2" s="810"/>
       <c r="F2" s="364"/>
       <c r="G2" s="365"/>
-      <c r="O2" s="924" t="s">
+      <c r="O2" s="914" t="s">
         <v>231</v>
       </c>
-      <c r="P2" s="924"/>
-      <c r="Q2" s="924"/>
-      <c r="R2" s="924"/>
-      <c r="S2" s="924"/>
-      <c r="T2" s="924"/>
-      <c r="U2" s="924"/>
-      <c r="V2" s="924"/>
+      <c r="P2" s="914"/>
+      <c r="Q2" s="914"/>
+      <c r="R2" s="914"/>
+      <c r="S2" s="914"/>
+      <c r="T2" s="914"/>
+      <c r="U2" s="914"/>
+      <c r="V2" s="914"/>
     </row>
     <row r="3" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="366"/>
@@ -12389,50 +12899,50 @@
         <v>22</v>
       </c>
       <c r="K3" s="369"/>
-      <c r="L3" s="907" t="s">
+      <c r="L3" s="919" t="s">
         <v>53</v>
       </c>
-      <c r="M3" s="908"/>
-      <c r="N3" s="909"/>
-      <c r="O3" s="918" t="s">
+      <c r="M3" s="920"/>
+      <c r="N3" s="921"/>
+      <c r="O3" s="907" t="s">
         <v>3</v>
       </c>
-      <c r="P3" s="918"/>
-      <c r="Q3" s="918"/>
-      <c r="R3" s="918"/>
-      <c r="S3" s="918"/>
-      <c r="T3" s="918"/>
-      <c r="U3" s="918"/>
-      <c r="V3" s="918"/>
-      <c r="W3" s="918"/>
-      <c r="X3" s="918"/>
-      <c r="Y3" s="918"/>
-      <c r="Z3" s="918"/>
-      <c r="AA3" s="918"/>
-      <c r="AB3" s="918"/>
-      <c r="AC3" s="918"/>
+      <c r="P3" s="907"/>
+      <c r="Q3" s="907"/>
+      <c r="R3" s="907"/>
+      <c r="S3" s="907"/>
+      <c r="T3" s="907"/>
+      <c r="U3" s="907"/>
+      <c r="V3" s="907"/>
+      <c r="W3" s="907"/>
+      <c r="X3" s="907"/>
+      <c r="Y3" s="907"/>
+      <c r="Z3" s="907"/>
+      <c r="AA3" s="907"/>
+      <c r="AB3" s="907"/>
+      <c r="AC3" s="907"/>
       <c r="AD3" s="372"/>
       <c r="AE3" s="373"/>
       <c r="AF3" s="372"/>
-      <c r="AG3" s="902" t="s">
+      <c r="AG3" s="927" t="s">
         <v>206</v>
       </c>
-      <c r="AH3" s="900" t="s">
+      <c r="AH3" s="925" t="s">
         <v>204</v>
       </c>
-      <c r="AI3" s="900" t="s">
+      <c r="AI3" s="925" t="s">
         <v>205</v>
       </c>
-      <c r="AJ3" s="903" t="s">
+      <c r="AJ3" s="928" t="s">
         <v>233</v>
       </c>
       <c r="AK3" s="416"/>
-      <c r="AL3" s="904" t="s">
+      <c r="AL3" s="929" t="s">
         <v>178</v>
       </c>
-      <c r="AM3" s="904"/>
-      <c r="AN3" s="904"/>
-      <c r="AO3" s="904"/>
+      <c r="AM3" s="929"/>
+      <c r="AN3" s="929"/>
+      <c r="AO3" s="929"/>
     </row>
     <row r="4" spans="1:44" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="374"/>
@@ -12466,40 +12976,40 @@
       <c r="K4" s="372" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="925" t="s">
+      <c r="L4" s="915" t="s">
         <v>289</v>
       </c>
       <c r="M4" s="376" t="s">
         <v>260</v>
       </c>
-      <c r="N4" s="910" t="s">
+      <c r="N4" s="922" t="s">
         <v>167</v>
       </c>
-      <c r="O4" s="912" t="s">
+      <c r="O4" s="903" t="s">
         <v>100</v>
       </c>
-      <c r="P4" s="912" t="s">
+      <c r="P4" s="903" t="s">
         <v>101</v>
       </c>
-      <c r="Q4" s="912" t="s">
+      <c r="Q4" s="903" t="s">
         <v>160</v>
       </c>
-      <c r="R4" s="912" t="s">
+      <c r="R4" s="903" t="s">
         <v>171</v>
       </c>
-      <c r="S4" s="912" t="s">
+      <c r="S4" s="903" t="s">
         <v>102</v>
       </c>
-      <c r="T4" s="912" t="s">
+      <c r="T4" s="903" t="s">
         <v>172</v>
       </c>
-      <c r="U4" s="912" t="s">
+      <c r="U4" s="903" t="s">
         <v>103</v>
       </c>
-      <c r="V4" s="922" t="s">
+      <c r="V4" s="912" t="s">
         <v>236</v>
       </c>
-      <c r="W4" s="912" t="s">
+      <c r="W4" s="903" t="s">
         <v>177</v>
       </c>
       <c r="X4" s="372" t="s">
@@ -12511,28 +13021,28 @@
       <c r="Z4" s="372" t="s">
         <v>98</v>
       </c>
-      <c r="AA4" s="918" t="s">
+      <c r="AA4" s="907" t="s">
         <v>68</v>
       </c>
-      <c r="AB4" s="920" t="s">
+      <c r="AB4" s="909" t="s">
         <v>69</v>
       </c>
-      <c r="AC4" s="923" t="s">
+      <c r="AC4" s="913" t="s">
         <v>151</v>
       </c>
-      <c r="AD4" s="912" t="s">
+      <c r="AD4" s="903" t="s">
         <v>154</v>
       </c>
-      <c r="AE4" s="912" t="s">
+      <c r="AE4" s="903" t="s">
         <v>155</v>
       </c>
-      <c r="AF4" s="912" t="s">
+      <c r="AF4" s="903" t="s">
         <v>159</v>
       </c>
-      <c r="AG4" s="902"/>
-      <c r="AH4" s="901"/>
-      <c r="AI4" s="901"/>
-      <c r="AJ4" s="903"/>
+      <c r="AG4" s="927"/>
+      <c r="AH4" s="926"/>
+      <c r="AI4" s="926"/>
+      <c r="AJ4" s="928"/>
       <c r="AK4" s="416"/>
       <c r="AL4" s="378" t="s">
         <v>276</v>
@@ -12581,20 +13091,20 @@
       <c r="K5" s="465" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="926"/>
+      <c r="L5" s="916"/>
       <c r="M5" s="466" t="s">
         <v>261</v>
       </c>
-      <c r="N5" s="911"/>
-      <c r="O5" s="913"/>
-      <c r="P5" s="912"/>
-      <c r="Q5" s="912"/>
-      <c r="R5" s="912"/>
-      <c r="S5" s="913"/>
-      <c r="T5" s="913"/>
-      <c r="U5" s="913"/>
-      <c r="V5" s="922"/>
-      <c r="W5" s="914"/>
+      <c r="N5" s="923"/>
+      <c r="O5" s="911"/>
+      <c r="P5" s="903"/>
+      <c r="Q5" s="903"/>
+      <c r="R5" s="903"/>
+      <c r="S5" s="911"/>
+      <c r="T5" s="911"/>
+      <c r="U5" s="911"/>
+      <c r="V5" s="912"/>
+      <c r="W5" s="924"/>
       <c r="X5" s="372" t="s">
         <v>104</v>
       </c>
@@ -12604,16 +13114,16 @@
       <c r="Z5" s="372" t="s">
         <v>104</v>
       </c>
-      <c r="AA5" s="919"/>
-      <c r="AB5" s="921"/>
-      <c r="AC5" s="923"/>
-      <c r="AD5" s="912"/>
-      <c r="AE5" s="912"/>
-      <c r="AF5" s="915"/>
-      <c r="AG5" s="902"/>
-      <c r="AH5" s="901"/>
-      <c r="AI5" s="901"/>
-      <c r="AJ5" s="903"/>
+      <c r="AA5" s="908"/>
+      <c r="AB5" s="910"/>
+      <c r="AC5" s="913"/>
+      <c r="AD5" s="903"/>
+      <c r="AE5" s="903"/>
+      <c r="AF5" s="904"/>
+      <c r="AG5" s="927"/>
+      <c r="AH5" s="926"/>
+      <c r="AI5" s="926"/>
+      <c r="AJ5" s="928"/>
       <c r="AK5" s="416"/>
       <c r="AL5" s="378" t="s">
         <v>263</v>
@@ -13729,41 +14239,87 @@
       <c r="A18" s="378">
         <v>13</v>
       </c>
-      <c r="B18" s="815"/>
-      <c r="C18" s="816"/>
+      <c r="B18" s="815">
+        <v>8522020</v>
+      </c>
+      <c r="C18" s="816">
+        <v>1690549.3</v>
+      </c>
       <c r="D18" s="817"/>
-      <c r="E18" s="817"/>
-      <c r="F18" s="817"/>
-      <c r="G18" s="817"/>
+      <c r="E18" s="817">
+        <v>64</v>
+      </c>
+      <c r="F18" s="817">
+        <v>11433.7</v>
+      </c>
+      <c r="G18" s="817">
+        <v>68225</v>
+      </c>
       <c r="H18" s="818"/>
-      <c r="I18" s="819"/>
+      <c r="I18" s="819">
+        <v>1950435</v>
+      </c>
       <c r="J18" s="876"/>
-      <c r="K18" s="818"/>
-      <c r="L18" s="817"/>
-      <c r="M18" s="821"/>
-      <c r="N18" s="819"/>
-      <c r="O18" s="822"/>
-      <c r="P18" s="823"/>
-      <c r="Q18" s="817"/>
+      <c r="K18" s="818">
+        <v>468000</v>
+      </c>
+      <c r="L18" s="817">
+        <v>90973.84</v>
+      </c>
+      <c r="M18" s="821">
+        <v>642489.75</v>
+      </c>
+      <c r="N18" s="819">
+        <v>86230.37</v>
+      </c>
+      <c r="O18" s="822">
+        <v>254838</v>
+      </c>
+      <c r="P18" s="823">
+        <v>87322</v>
+      </c>
+      <c r="Q18" s="817">
+        <v>991335</v>
+      </c>
       <c r="R18" s="817"/>
-      <c r="S18" s="817"/>
+      <c r="S18" s="817">
+        <v>98790</v>
+      </c>
       <c r="T18" s="817"/>
-      <c r="U18" s="817"/>
-      <c r="V18" s="824"/>
+      <c r="U18" s="817">
+        <v>562</v>
+      </c>
+      <c r="V18" s="824">
+        <v>1367716</v>
+      </c>
       <c r="W18" s="817"/>
-      <c r="X18" s="825"/>
-      <c r="Y18" s="817"/>
-      <c r="Z18" s="817"/>
-      <c r="AA18" s="817"/>
+      <c r="X18" s="825">
+        <v>49502</v>
+      </c>
+      <c r="Y18" s="817">
+        <v>71544</v>
+      </c>
+      <c r="Z18" s="817">
+        <v>15921</v>
+      </c>
+      <c r="AA18" s="817">
+        <v>97122</v>
+      </c>
       <c r="AB18" s="817"/>
-      <c r="AC18" s="817"/>
-      <c r="AD18" s="817"/>
+      <c r="AC18" s="817">
+        <v>6888</v>
+      </c>
+      <c r="AD18" s="817">
+        <v>263787</v>
+      </c>
       <c r="AE18" s="817"/>
       <c r="AF18" s="819"/>
       <c r="AG18" s="817"/>
       <c r="AH18" s="817"/>
       <c r="AI18" s="817"/>
-      <c r="AJ18" s="880"/>
+      <c r="AJ18" s="880">
+        <v>7383613.8779999996</v>
+      </c>
       <c r="AK18" s="192"/>
       <c r="AL18" s="459"/>
       <c r="AM18" s="387"/>
@@ -14630,8 +15186,8 @@
     <row r="38" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B38" s="190"/>
       <c r="G38" s="190"/>
-      <c r="I38" s="905"/>
-      <c r="J38" s="905"/>
+      <c r="I38" s="917"/>
+      <c r="J38" s="917"/>
       <c r="R38" s="190"/>
       <c r="S38" s="190"/>
       <c r="T38" s="190"/>
@@ -14639,8 +15195,8 @@
       <c r="V38" s="190"/>
       <c r="W38" s="190"/>
       <c r="Z38" s="190"/>
-      <c r="AA38" s="906"/>
-      <c r="AB38" s="906"/>
+      <c r="AA38" s="918"/>
+      <c r="AB38" s="918"/>
       <c r="AC38" s="190"/>
       <c r="AD38" s="190"/>
       <c r="AI38" s="380"/>
@@ -16306,6 +16862,19 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="AH3:AH5"/>
+    <mergeCell ref="AG3:AG5"/>
+    <mergeCell ref="AI3:AI5"/>
+    <mergeCell ref="AJ3:AJ5"/>
+    <mergeCell ref="AL3:AO3"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="AA38:AB38"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="S4:S5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="P4:P5"/>
+    <mergeCell ref="W4:W5"/>
     <mergeCell ref="AF4:AF5"/>
     <mergeCell ref="AE4:AE5"/>
     <mergeCell ref="AD4:AD5"/>
@@ -16322,304 +16891,401 @@
     <mergeCell ref="AC4:AC5"/>
     <mergeCell ref="O2:V2"/>
     <mergeCell ref="L4:L5"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="AA38:AB38"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="S4:S5"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="P4:P5"/>
-    <mergeCell ref="W4:W5"/>
-    <mergeCell ref="AH3:AH5"/>
-    <mergeCell ref="AG3:AG5"/>
-    <mergeCell ref="AI3:AI5"/>
-    <mergeCell ref="AJ3:AJ5"/>
-    <mergeCell ref="AL3:AO3"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="expression" dxfId="119" priority="14">
-      <formula>B6&lt;#REF!</formula>
+  <conditionalFormatting sqref="B19:B35">
+    <cfRule type="expression" dxfId="165" priority="75">
+      <formula>B19&lt;B18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7:B35">
-    <cfRule type="expression" dxfId="118" priority="28">
+  <conditionalFormatting sqref="C35 E35:E37">
+    <cfRule type="expression" dxfId="163" priority="427">
+      <formula>C35&lt;C34</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C36:D37">
+    <cfRule type="expression" dxfId="159" priority="1480">
+      <formula>C36&lt;C35</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D35 B36:B37">
+    <cfRule type="expression" dxfId="158" priority="1467">
+      <formula>B35&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19:F37">
+    <cfRule type="expression" dxfId="156" priority="51">
+      <formula>F19&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19:G37">
+    <cfRule type="expression" dxfId="155" priority="49">
+      <formula>G19&lt;G18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G36:J37 L36:O37">
+    <cfRule type="expression" dxfId="154" priority="1314">
+      <formula>G36&lt;G35</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H19:I34">
+    <cfRule type="expression" dxfId="152" priority="428">
+      <formula>H19&lt;H18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H35:I35 R35 T35 W35 AB35 AE35:AI35 P36:P37 S36:S37 X36:Y37">
+    <cfRule type="expression" dxfId="151" priority="1466">
+      <formula>H35&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J19:J35">
+    <cfRule type="expression" dxfId="149" priority="429">
+      <formula>J19&lt;J18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K19:L21">
+    <cfRule type="expression" dxfId="148" priority="87">
+      <formula>K19&lt;K18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K22:M22">
+    <cfRule type="expression" dxfId="147" priority="430">
+      <formula>K22&lt;K21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K23:Z23 K24:K37">
+    <cfRule type="expression" dxfId="145" priority="431">
+      <formula>K23&lt;K22</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L24:Z27 L28:AC28">
+    <cfRule type="expression" dxfId="144" priority="433">
+      <formula>L24&lt;L23</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M19:M21">
+    <cfRule type="expression" dxfId="142" priority="426">
+      <formula>M19&lt;M18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N19:T22">
+    <cfRule type="expression" dxfId="140" priority="91">
+      <formula>N19&lt;N18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q36">
+    <cfRule type="expression" dxfId="136" priority="1483">
+      <formula>Q36&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R36">
+    <cfRule type="expression" dxfId="132" priority="1479">
+      <formula>R36&lt;R35</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB19:AI27">
+    <cfRule type="expression" dxfId="131" priority="81">
+      <formula>AB19&lt;AB18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U19:U22">
+    <cfRule type="expression" dxfId="129" priority="56">
+      <formula>U19&lt;U18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C19:E34">
+    <cfRule type="expression" dxfId="127" priority="94">
+      <formula>C19&lt;C18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V19:Z22">
+    <cfRule type="expression" dxfId="126" priority="93">
+      <formula>V19&lt;V18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V29:AC29 AA30:AC30 Z30:Z31 V30:Y34 AA31:AB31 AC31:AC37 Z32:AB34 V35 X35:AA35">
+    <cfRule type="expression" dxfId="125" priority="437">
+      <formula>V29&lt;V28</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA19:AA37">
+    <cfRule type="expression" dxfId="121" priority="48">
+      <formula>AA19&lt;AA18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA28:AA37">
+    <cfRule type="expression" dxfId="120" priority="435">
+      <formula>AA28&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD28:AD37">
+    <cfRule type="expression" dxfId="118" priority="432">
+      <formula>AD28&lt;AD27</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE28:AI34 L29:T34 U29:U37 L35:Q35 S35">
+    <cfRule type="expression" dxfId="115" priority="436">
+      <formula>L28&lt;L27</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ19:AJ37">
+    <cfRule type="expression" dxfId="114" priority="50">
+      <formula>AJ19&lt;AJ18</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK6:AK12">
+    <cfRule type="expression" dxfId="113" priority="1356">
+      <formula>AK6&lt;AK5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK13:AL15">
+    <cfRule type="expression" dxfId="112" priority="1436">
+      <formula>AK13&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL9:AL14 AL15:AN34 AK16:AK37 AK20:AN21 T36:W37 Z36:Z37 AB36:AB37 AE36:AI37 Q37:R37">
+    <cfRule type="expression" dxfId="111" priority="1373">
+      <formula>Q9&lt;Q8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AO9:AO34">
+    <cfRule type="expression" dxfId="110" priority="1381">
+      <formula>AO9&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:B18">
+    <cfRule type="expression" dxfId="46" priority="28">
       <formula>B7&lt;B6</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B11:B17">
-    <cfRule type="expression" dxfId="117" priority="45">
+  <conditionalFormatting sqref="B11:B18">
+    <cfRule type="expression" dxfId="45" priority="45">
       <formula>B11&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C35 E35:E37">
-    <cfRule type="expression" dxfId="116" priority="380">
-      <formula>C35&lt;C34</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C6:D6">
-    <cfRule type="expression" dxfId="115" priority="16">
-      <formula>C6&lt;C5</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C7:D7 H7:J7 R7 T7 W7 AB7">
-    <cfRule type="expression" dxfId="114" priority="32">
+    <cfRule type="expression" dxfId="44" priority="32">
       <formula>C7&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8:D14">
-    <cfRule type="expression" dxfId="113" priority="36">
+    <cfRule type="expression" dxfId="43" priority="36">
       <formula>C8&lt;C7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C36:D37">
-    <cfRule type="expression" dxfId="112" priority="1433">
-      <formula>C36&lt;C35</formula>
+  <conditionalFormatting sqref="E7:E14">
+    <cfRule type="expression" dxfId="42" priority="18">
+      <formula>E7&lt;E6</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D35 B36:B37">
-    <cfRule type="expression" dxfId="111" priority="1420">
-      <formula>B35&lt;#REF!</formula>
+  <conditionalFormatting sqref="F7:F18">
+    <cfRule type="expression" dxfId="41" priority="33">
+      <formula>F7&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E6:E14">
-    <cfRule type="expression" dxfId="110" priority="5">
-      <formula>E6&lt;E5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6:F37">
-    <cfRule type="expression" dxfId="109" priority="4">
-      <formula>F6&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G6:G37">
-    <cfRule type="expression" dxfId="108" priority="2">
-      <formula>G6&lt;G5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G36:J37 L36:O37">
-    <cfRule type="expression" dxfId="107" priority="1267">
-      <formula>G36&lt;G35</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G6:O6">
-    <cfRule type="expression" dxfId="106" priority="6">
-      <formula>G6&lt;G5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H19:I34">
-    <cfRule type="expression" dxfId="105" priority="381">
-      <formula>H19&lt;H18</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H35:I35 R35 T35 W35 AB35 AE35:AI35 P36:P37 S36:S37 X36:Y37">
-    <cfRule type="expression" dxfId="104" priority="1419">
-      <formula>H35&lt;#REF!</formula>
+  <conditionalFormatting sqref="G7:G18">
+    <cfRule type="expression" dxfId="40" priority="29">
+      <formula>G7&lt;G6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8:J18">
-    <cfRule type="expression" dxfId="103" priority="37">
+    <cfRule type="expression" dxfId="39" priority="37">
       <formula>H8&lt;H7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J19:J35">
-    <cfRule type="expression" dxfId="102" priority="382">
-      <formula>J19&lt;J18</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K11:L21">
-    <cfRule type="expression" dxfId="101" priority="40">
+  <conditionalFormatting sqref="K11:L18">
+    <cfRule type="expression" dxfId="38" priority="40">
       <formula>K11&lt;K10</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K22:M22">
-    <cfRule type="expression" dxfId="100" priority="383">
-      <formula>K22&lt;K21</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7:O10">
-    <cfRule type="expression" dxfId="99" priority="23">
+  <conditionalFormatting sqref="K7:O8 K9:N10 O9">
+    <cfRule type="expression" dxfId="37" priority="23">
       <formula>K7&lt;K6</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K23:Z23 K24:K37">
-    <cfRule type="expression" dxfId="98" priority="384">
-      <formula>K23&lt;K22</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L24:Z27 L28:AC28">
-    <cfRule type="expression" dxfId="97" priority="386">
-      <formula>L24&lt;L23</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="M11:M17">
-    <cfRule type="expression" dxfId="96" priority="42">
+    <cfRule type="expression" dxfId="36" priority="42">
       <formula>M11&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M18:M21">
-    <cfRule type="expression" dxfId="95" priority="379">
-      <formula>M18&lt;M17</formula>
+  <conditionalFormatting sqref="N11:O12 O10">
+    <cfRule type="expression" dxfId="35" priority="41">
+      <formula>N10&lt;N9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N11:O12">
-    <cfRule type="expression" dxfId="94" priority="41">
-      <formula>N11&lt;N10</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N13:T22">
-    <cfRule type="expression" dxfId="93" priority="44">
+  <conditionalFormatting sqref="N13:T18">
+    <cfRule type="expression" dxfId="34" priority="44">
       <formula>N13&lt;N12</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="S7:S10">
+    <cfRule type="expression" dxfId="33" priority="22">
+      <formula>S7&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="P8:P12 V8:V12">
-    <cfRule type="expression" dxfId="92" priority="39">
+    <cfRule type="expression" dxfId="32" priority="39">
       <formula>P8&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P6:Q6 X6:Y6 S6:S10">
-    <cfRule type="expression" dxfId="91" priority="13">
-      <formula>P6&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="P7:Q7">
-    <cfRule type="expression" dxfId="90" priority="30">
+    <cfRule type="expression" dxfId="31" priority="30">
       <formula>P7&lt;P6</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q36">
-    <cfRule type="expression" dxfId="89" priority="1436">
-      <formula>Q36&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q8:R10">
-    <cfRule type="expression" dxfId="88" priority="38">
+  <conditionalFormatting sqref="Q8:R8">
+    <cfRule type="expression" dxfId="30" priority="38">
       <formula>Q8&lt;Q7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q11:T12">
-    <cfRule type="expression" dxfId="87" priority="43">
-      <formula>Q11&lt;Q10</formula>
+  <conditionalFormatting sqref="Q11:T12 Q9:R10 T9:T10">
+    <cfRule type="expression" dxfId="29" priority="43">
+      <formula>Q9&lt;Q8</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R6">
-    <cfRule type="expression" dxfId="86" priority="15">
-      <formula>R6&lt;R5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R36">
-    <cfRule type="expression" dxfId="85" priority="1432">
-      <formula>R36&lt;R35</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T8:T10 AB8:AC10 AE8:AI10 AB11:AI27">
-    <cfRule type="expression" dxfId="84" priority="34">
+  <conditionalFormatting sqref="T8 AB8:AC10 AE8:AI10 AB11:AI18">
+    <cfRule type="expression" dxfId="28" priority="34">
       <formula>T8&lt;T7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T6:W6 Z6 AB6">
-    <cfRule type="expression" dxfId="83" priority="12">
-      <formula>T6&lt;T5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U6:U22">
-    <cfRule type="expression" dxfId="82" priority="9">
-      <formula>U6&lt;U5</formula>
+  <conditionalFormatting sqref="U7:U18">
+    <cfRule type="expression" dxfId="27" priority="20">
+      <formula>U7&lt;U6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V7">
-    <cfRule type="expression" dxfId="81" priority="25">
+    <cfRule type="expression" dxfId="26" priority="25">
       <formula>V7&lt;V6</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V13:X14 C15:E34">
-    <cfRule type="expression" dxfId="80" priority="47">
+  <conditionalFormatting sqref="V13:X14 C15:E18">
+    <cfRule type="expression" dxfId="25" priority="47">
       <formula>C13&lt;C12</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V15:Z22">
-    <cfRule type="expression" dxfId="79" priority="46">
-      <formula>V15&lt;V14</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V29:AC29 AA30:AC30 Z30:Z31 V30:Y34 AA31:AB31 AC31:AC37 Z32:AB34 V35 X35:AA35">
-    <cfRule type="expression" dxfId="78" priority="390">
-      <formula>V29&lt;V28</formula>
+  <conditionalFormatting sqref="V15:Z18 M18">
+    <cfRule type="expression" dxfId="24" priority="46">
+      <formula>M15&lt;M14</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W8:W12">
-    <cfRule type="expression" dxfId="77" priority="35">
+    <cfRule type="expression" dxfId="23" priority="35">
       <formula>W8&lt;W7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y7:Z14">
-    <cfRule type="expression" dxfId="76" priority="26">
+    <cfRule type="expression" dxfId="22" priority="26">
       <formula>Y7&lt;Y6</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA6:AA12">
-    <cfRule type="expression" dxfId="75" priority="8">
+  <conditionalFormatting sqref="AA7:AA12">
+    <cfRule type="expression" dxfId="21" priority="19">
+      <formula>AA7&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA7:AA18">
+    <cfRule type="expression" dxfId="20" priority="24">
+      <formula>AA7&lt;AA6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC7">
+    <cfRule type="expression" dxfId="19" priority="21">
+      <formula>AC7&lt;AC6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD7:AI7 X7:X12 AD8:AD10">
+    <cfRule type="expression" dxfId="18" priority="27">
+      <formula>X7&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ12:AJ18">
+    <cfRule type="expression" dxfId="17" priority="31">
+      <formula>AJ12&lt;AJ11</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C6:D6">
+    <cfRule type="expression" dxfId="16" priority="16">
+      <formula>C6&lt;C5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="expression" dxfId="15" priority="14">
+      <formula>B6&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
+    <cfRule type="expression" dxfId="14" priority="4">
+      <formula>F6&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6">
+    <cfRule type="expression" dxfId="13" priority="2">
+      <formula>G6&lt;G5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6:J6 L6:O6">
+    <cfRule type="expression" dxfId="12" priority="11">
+      <formula>G6&lt;G5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P6 S6 X6:Y6">
+    <cfRule type="expression" dxfId="11" priority="13">
+      <formula>P6&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6">
+    <cfRule type="expression" dxfId="10" priority="6">
+      <formula>K6&lt;K5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q6">
+    <cfRule type="expression" dxfId="9" priority="17">
+      <formula>Q6&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R6">
+    <cfRule type="expression" dxfId="8" priority="15">
+      <formula>R6&lt;R5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6">
+    <cfRule type="expression" dxfId="7" priority="5">
+      <formula>E6&lt;E5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC6">
+    <cfRule type="expression" dxfId="6" priority="10">
+      <formula>AC6&lt;AC5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA6">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>AA6&lt;AA5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA6">
+    <cfRule type="expression" dxfId="4" priority="8">
       <formula>AA6&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA6:AA37">
-    <cfRule type="expression" dxfId="74" priority="1">
-      <formula>AA6&lt;AA5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA28:AA37">
-    <cfRule type="expression" dxfId="73" priority="388">
-      <formula>AA28&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC6:AC7">
-    <cfRule type="expression" dxfId="72" priority="10">
-      <formula>AC6&lt;AC5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD28:AD37">
-    <cfRule type="expression" dxfId="71" priority="385">
-      <formula>AD28&lt;AD27</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD6:AI6">
-    <cfRule type="expression" dxfId="70" priority="7">
+  <conditionalFormatting sqref="AD6">
+    <cfRule type="expression" dxfId="3" priority="7">
       <formula>AD6&lt;AD5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD7:AI7 X7:X12 AD8:AD10">
-    <cfRule type="expression" dxfId="69" priority="27">
-      <formula>X7&lt;#REF!</formula>
+  <conditionalFormatting sqref="U6">
+    <cfRule type="expression" dxfId="2" priority="9">
+      <formula>U6&lt;U5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE28:AI34 L29:T34 U29:U37 L35:Q35 S35">
-    <cfRule type="expression" dxfId="68" priority="389">
-      <formula>L28&lt;L27</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ6:AJ37">
-    <cfRule type="expression" dxfId="67" priority="3">
+  <conditionalFormatting sqref="AJ6:AJ11">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>AJ6&lt;AJ5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK6:AK12">
-    <cfRule type="expression" dxfId="66" priority="1309">
-      <formula>AK6&lt;AK5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AK13:AL15">
-    <cfRule type="expression" dxfId="65" priority="1389">
-      <formula>AK13&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AL9:AL14 AL15:AN34 AK16:AK37 AK20:AN21 T36:W37 Z36:Z37 AB36:AB37 AE36:AI37 Q37:R37">
-    <cfRule type="expression" dxfId="64" priority="1326">
-      <formula>Q9&lt;Q8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AO9:AO34">
-    <cfRule type="expression" dxfId="63" priority="1334">
-      <formula>AO9&lt;#REF!</formula>
+  <conditionalFormatting sqref="T6:W6 Z6 AB6 AE6:AI6">
+    <cfRule type="expression" dxfId="0" priority="12">
+      <formula>T6&lt;T5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.1" right="0.5" top="0.32" bottom="0.25" header="0.25" footer="0.25"/>
@@ -16688,8 +17354,8 @@
       </c>
       <c r="B3" s="468"/>
       <c r="C3" s="468"/>
-      <c r="K3" s="899"/>
-      <c r="L3" s="899"/>
+      <c r="K3" s="902"/>
+      <c r="L3" s="902"/>
       <c r="M3" s="498"/>
       <c r="AH3" s="291"/>
       <c r="AI3" s="291"/>
@@ -16835,7 +17501,7 @@
         <v>31</v>
       </c>
       <c r="AG6" s="291"/>
-      <c r="AI6" s="898" t="s">
+      <c r="AI6" s="901" t="s">
         <v>216</v>
       </c>
     </row>
@@ -16940,7 +17606,7 @@
       <c r="AH7" s="477" t="s">
         <v>19</v>
       </c>
-      <c r="AI7" s="898"/>
+      <c r="AI7" s="901"/>
       <c r="AJ7" s="292" t="s">
         <v>229</v>
       </c>
@@ -17003,7 +17669,10 @@
       </c>
       <c r="K8" s="678"/>
       <c r="L8" s="680"/>
-      <c r="M8" s="680"/>
+      <c r="M8" s="680">
+        <f>2979+614</f>
+        <v>3593</v>
+      </c>
       <c r="N8" s="678"/>
       <c r="O8" s="678"/>
       <c r="P8" s="678"/>
@@ -17026,14 +17695,14 @@
       <c r="AG8" s="747"/>
       <c r="AH8" s="480">
         <f>SUM(B8:AG8)</f>
-        <v>36444</v>
+        <v>40037</v>
       </c>
       <c r="AI8" s="526">
         <v>123950</v>
       </c>
       <c r="AJ8" s="294">
         <f>AH8-AI8</f>
-        <v>-87506</v>
+        <v>-83913</v>
       </c>
       <c r="AK8" s="481"/>
       <c r="AL8" s="481"/>
@@ -17109,7 +17778,7 @@
       </c>
       <c r="M9" s="678">
         <f t="shared" ref="M9:O9" si="1">M8*0.066</f>
-        <v>0</v>
+        <v>237.13800000000001</v>
       </c>
       <c r="N9" s="678">
         <f t="shared" si="1"/>
@@ -17181,7 +17850,7 @@
       <c r="AG9" s="748"/>
       <c r="AH9" s="484">
         <f>SUM(B9:AG9)</f>
-        <v>2410.9247999999998</v>
+        <v>2648.0627999999997</v>
       </c>
       <c r="AI9" s="484"/>
       <c r="AL9" s="291" t="s">
@@ -17218,7 +17887,9 @@
       </c>
       <c r="K10" s="871"/>
       <c r="L10" s="871"/>
-      <c r="M10" s="681"/>
+      <c r="M10" s="681" t="s">
+        <v>314</v>
+      </c>
       <c r="N10" s="681"/>
       <c r="O10" s="878"/>
       <c r="P10" s="878"/>
@@ -17515,7 +18186,9 @@
         <v>313</v>
       </c>
       <c r="L13" s="669"/>
-      <c r="M13" s="798"/>
+      <c r="M13" s="798" t="s">
+        <v>310</v>
+      </c>
       <c r="N13" s="798"/>
       <c r="O13" s="669"/>
       <c r="P13" s="669"/>
@@ -17575,11 +18248,13 @@
       <c r="J14" s="498">
         <v>7</v>
       </c>
-      <c r="K14" s="498">
+      <c r="K14" s="899">
         <v>8</v>
       </c>
       <c r="L14" s="498"/>
-      <c r="M14" s="498"/>
+      <c r="M14" s="498">
+        <v>1</v>
+      </c>
       <c r="N14" s="498"/>
       <c r="O14" s="498"/>
       <c r="P14" s="498"/>
@@ -17601,7 +18276,7 @@
       <c r="AG14" s="498"/>
       <c r="AH14" s="468">
         <f>SUM(B14:AF14)</f>
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:149" s="504" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -17642,7 +18317,7 @@
       <c r="AG15" s="718"/>
       <c r="AH15" s="500">
         <f>IF(AH12=0,"",+(AH36*10)/AH12)</f>
-        <v>5.508160237388724</v>
+        <v>5.775222551928783</v>
       </c>
       <c r="AI15" s="502"/>
       <c r="AJ15" s="503"/>
@@ -18020,9 +18695,9 @@
         <f>+'Water '!$D17</f>
         <v>0</v>
       </c>
-      <c r="M20" s="509" t="str">
+      <c r="M20" s="509">
         <f>+'Water '!$D18</f>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="N20" s="509" t="str">
         <f>+'Water '!$D19</f>
@@ -18103,7 +18778,7 @@
       <c r="AG20" s="509"/>
       <c r="AH20" s="484">
         <f>SUM($B20:AF20)</f>
-        <v>1700</v>
+        <v>1844</v>
       </c>
       <c r="AI20" s="484"/>
       <c r="AJ20" s="485"/>
@@ -18156,9 +18831,9 @@
         <f>+'Water '!$E17</f>
         <v>3</v>
       </c>
-      <c r="M21" s="511" t="str">
+      <c r="M21" s="511">
         <f>+'Water '!$E18</f>
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="N21" s="511" t="str">
         <f>+'Water '!$E19</f>
@@ -18239,7 +18914,7 @@
       <c r="AG21" s="509"/>
       <c r="AH21" s="484">
         <f>SUM($B21:AF21)</f>
-        <v>1309</v>
+        <v>1546</v>
       </c>
       <c r="AI21" s="484"/>
     </row>
@@ -18293,7 +18968,7 @@
       </c>
       <c r="M22" s="514">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="N22" s="514">
         <f>SUM(N19:N21)</f>
@@ -18374,7 +19049,7 @@
       <c r="AG22" s="515"/>
       <c r="AH22" s="516">
         <f>SUM($B22:AF22)</f>
-        <v>3009</v>
+        <v>3390</v>
       </c>
       <c r="AI22" s="514"/>
       <c r="AJ22" s="517"/>
@@ -18657,7 +19332,7 @@
       </c>
       <c r="M26" s="521">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>180.31</v>
       </c>
       <c r="N26" s="521">
         <f t="shared" si="4"/>
@@ -18738,15 +19413,15 @@
       <c r="AG26" s="521"/>
       <c r="AH26" s="484">
         <f>SUM($B26:AF26)</f>
-        <v>1046.0900000000001</v>
+        <v>1226.4000000000001</v>
       </c>
       <c r="AI26" s="523">
         <f>AH29+AH45+AH36</f>
-        <v>3301</v>
+        <v>3613</v>
       </c>
       <c r="AK26" s="524">
         <f>(AI26*10)/AH9</f>
-        <v>13.69184140459296</v>
+        <v>13.643936238974394</v>
       </c>
     </row>
     <row r="27" spans="1:149" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -18945,7 +19620,7 @@
       </c>
       <c r="M29" s="509">
         <f>'Water '!H18</f>
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="N29" s="509">
         <f>'Water '!H19</f>
@@ -19026,7 +19701,7 @@
       <c r="AG29" s="509"/>
       <c r="AH29" s="484">
         <f>SUM($B29:AF29)</f>
-        <v>1663</v>
+        <v>1832</v>
       </c>
       <c r="AI29" s="484"/>
       <c r="AJ29" s="484"/>
@@ -19080,9 +19755,9 @@
         <f t="shared" si="5"/>
         <v>18</v>
       </c>
-      <c r="M30" s="509" t="str">
+      <c r="M30" s="509">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="N30" s="509" t="str">
         <f t="shared" si="5"/>
@@ -19163,7 +19838,7 @@
       <c r="AG30" s="509"/>
       <c r="AH30" s="484">
         <f>AH36</f>
-        <v>1485</v>
+        <v>1557</v>
       </c>
       <c r="AI30" s="484"/>
       <c r="AJ30" s="484"/>
@@ -19217,9 +19892,9 @@
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="M31" s="509" t="str">
+      <c r="M31" s="509">
         <f>M45</f>
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="N31" s="509" t="str">
         <f t="shared" si="6"/>
@@ -19300,7 +19975,7 @@
       <c r="AG31" s="509"/>
       <c r="AH31" s="484">
         <f>AH45</f>
-        <v>153</v>
+        <v>224</v>
       </c>
       <c r="AI31" s="484"/>
       <c r="AJ31" s="484"/>
@@ -19355,7 +20030,7 @@
       </c>
       <c r="M32" s="527">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="N32" s="527">
         <f t="shared" si="7"/>
@@ -19436,7 +20111,7 @@
       <c r="AG32" s="527"/>
       <c r="AH32" s="526">
         <f>SUM($B32:AF32)</f>
-        <v>3301</v>
+        <v>3613</v>
       </c>
       <c r="AI32" s="526"/>
       <c r="AJ32" s="528"/>
@@ -19629,9 +20304,9 @@
         <f>+'Water '!$J17</f>
         <v>18</v>
       </c>
-      <c r="M36" s="535" t="str">
+      <c r="M36" s="535">
         <f>+'Water '!$J18</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="N36" s="535" t="str">
         <f>+'Water '!$J19</f>
@@ -19712,7 +20387,7 @@
       <c r="AG36" s="508"/>
       <c r="AH36" s="484">
         <f>SUM($B36:AF36)</f>
-        <v>1485</v>
+        <v>1557</v>
       </c>
       <c r="AI36" s="484"/>
     </row>
@@ -20439,9 +21114,9 @@
         <f>+'Water '!$N17</f>
         <v>0</v>
       </c>
-      <c r="M41" s="657" t="str">
+      <c r="M41" s="657">
         <f>+'Water '!$N18</f>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="N41" s="539" t="str">
         <f>+'Water '!$N19</f>
@@ -20522,7 +21197,7 @@
       <c r="AG41" s="539"/>
       <c r="AH41" s="514">
         <f>SUM($B41:AF41)</f>
-        <v>343</v>
+        <v>372</v>
       </c>
       <c r="AI41" s="514"/>
       <c r="AJ41" s="514"/>
@@ -20688,9 +21363,9 @@
         <f>+'Water '!$O17</f>
         <v>0</v>
       </c>
-      <c r="M42" s="508" t="str">
+      <c r="M42" s="508">
         <f>+'Water '!$O18</f>
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="N42" s="508" t="str">
         <f>+'Water '!$O19</f>
@@ -20771,7 +21446,7 @@
       <c r="AG42" s="508"/>
       <c r="AH42" s="540">
         <f>SUM($B42:AF42)</f>
-        <v>652</v>
+        <v>771</v>
       </c>
       <c r="AI42" s="508"/>
       <c r="AJ42" s="508"/>
@@ -20927,8 +21602,8 @@
       <c r="L43" s="542" t="str">
         <v>0</v>
       </c>
-      <c r="M43" s="542" t="str">
-        <v>0</v>
+      <c r="M43" s="542">
+        <v>23</v>
       </c>
       <c r="N43" s="542" t="str">
         <v>0</v>
@@ -20990,7 +21665,7 @@
       <c r="AG43" s="542"/>
       <c r="AH43" s="543">
         <f>SUM($B43:AF43)</f>
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="AI43" s="544"/>
       <c r="AJ43" s="474"/>
@@ -21156,9 +21831,9 @@
         <f>+'Water '!$M17</f>
         <v>0</v>
       </c>
-      <c r="M44" s="508" t="str">
+      <c r="M44" s="508">
         <f>+'Water '!$M18</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N44" s="508" t="str">
         <f>+'Water '!$M19</f>
@@ -21239,7 +21914,7 @@
       <c r="AG44" s="508"/>
       <c r="AH44" s="484">
         <f>SUM($B44:AF44)</f>
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AI44" s="484"/>
       <c r="AJ44" s="291"/>
@@ -21405,9 +22080,9 @@
         <f>+'Water '!$Q17</f>
         <v>9</v>
       </c>
-      <c r="M45" s="539" t="str">
+      <c r="M45" s="539">
         <f>+'Water '!$Q18</f>
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="N45" s="539" t="str">
         <f>+'Water '!$Q19</f>
@@ -21488,7 +22163,7 @@
       <c r="AG45" s="539"/>
       <c r="AH45" s="514">
         <f>SUM($B45:AF45)</f>
-        <v>153</v>
+        <v>224</v>
       </c>
       <c r="AI45" s="514"/>
       <c r="AJ45" s="514"/>
@@ -22122,7 +22797,7 @@
       </c>
       <c r="M50" s="484">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="N50" s="484">
         <f t="shared" si="8"/>
@@ -22203,7 +22878,7 @@
       <c r="AG50" s="484"/>
       <c r="AH50" s="484">
         <f>SUM($B50:AF50)</f>
-        <v>2767</v>
+        <v>3086</v>
       </c>
       <c r="AI50" s="484"/>
     </row>
@@ -22343,9 +23018,9 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="M54" s="545" t="str">
+      <c r="M54" s="545">
         <f t="shared" si="10"/>
-        <v/>
+        <v>3.0362067656807428</v>
       </c>
       <c r="N54" s="545" t="str">
         <f t="shared" si="10"/>
@@ -22426,14 +23101,14 @@
       <c r="AG54" s="545"/>
       <c r="AH54" s="546">
         <f>+(AH36*10)/AH$9</f>
-        <v>6.1594621283915618</v>
+        <v>5.8797699208644154</v>
       </c>
       <c r="AI54" s="546">
         <v>3.2</v>
       </c>
       <c r="AJ54" s="547">
         <f t="shared" ref="AJ54:AJ67" si="11">AI54-AH54</f>
-        <v>-2.9594621283915616</v>
+        <v>-2.6797699208644152</v>
       </c>
     </row>
     <row r="55" spans="1:59" s="553" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -22555,9 +23230,9 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="M56" s="545" t="str">
+      <c r="M56" s="545">
         <f t="shared" si="16"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N56" s="545" t="str">
         <f t="shared" si="16"/>
@@ -22719,9 +23394,9 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="M57" s="549" t="str">
+      <c r="M57" s="549">
         <f t="shared" si="19"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N57" s="549" t="str">
         <f t="shared" si="19"/>
@@ -22883,9 +23558,9 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="M58" s="545" t="str">
+      <c r="M58" s="545">
         <f t="shared" si="20"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N58" s="545" t="str">
         <f t="shared" si="20"/>
@@ -23049,9 +23724,9 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="M59" s="549" t="str">
+      <c r="M59" s="549">
         <f t="shared" si="21"/>
-        <v/>
+        <v>1.2229166139547436</v>
       </c>
       <c r="N59" s="549" t="str">
         <f t="shared" si="21"/>
@@ -23132,14 +23807,14 @@
       <c r="AG59" s="549"/>
       <c r="AH59" s="549">
         <f t="shared" si="12"/>
-        <v>1.4226905791503743</v>
+        <v>1.4048005205918834</v>
       </c>
       <c r="AI59" s="550">
         <v>0.7</v>
       </c>
       <c r="AJ59" s="551">
         <f t="shared" si="11"/>
-        <v>-0.72269057915037438</v>
+        <v>-0.70480052059188347</v>
       </c>
       <c r="AK59" s="474"/>
       <c r="AL59" s="474"/>
@@ -23213,9 +23888,9 @@
         <f>IF(L$9=0,"",+(L42*10)/L$9)</f>
         <v/>
       </c>
-      <c r="M60" s="545" t="str">
+      <c r="M60" s="545">
         <f t="shared" si="22"/>
-        <v/>
+        <v>5.0181750710556718</v>
       </c>
       <c r="N60" s="545" t="str">
         <f t="shared" si="22"/>
@@ -23296,14 +23971,14 @@
       <c r="AG60" s="545"/>
       <c r="AH60" s="568">
         <f t="shared" si="12"/>
-        <v>2.7043564361692245</v>
+        <v>2.911562369291242</v>
       </c>
       <c r="AI60" s="555">
         <v>2.1</v>
       </c>
       <c r="AJ60" s="547">
         <f t="shared" si="11"/>
-        <v>-0.60435643616922441</v>
+        <v>-0.81156236929124193</v>
       </c>
     </row>
     <row r="61" spans="1:59" s="504" customFormat="1" x14ac:dyDescent="0.35">
@@ -23354,9 +24029,9 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="M61" s="549" t="str">
+      <c r="M61" s="549">
         <f t="shared" si="23"/>
-        <v/>
+        <v>0.96989938348134841</v>
       </c>
       <c r="N61" s="549" t="str">
         <f t="shared" si="23"/>
@@ -23437,14 +24112,14 @@
       <c r="AG61" s="549"/>
       <c r="AH61" s="550">
         <f t="shared" si="12"/>
-        <v>0.47699538368015465</v>
+        <v>0.52113567699376317</v>
       </c>
       <c r="AI61" s="550">
         <v>0.7</v>
       </c>
       <c r="AJ61" s="551">
         <f t="shared" si="11"/>
-        <v>0.22300461631984531</v>
+        <v>0.17886432300623678</v>
       </c>
       <c r="AK61" s="474"/>
       <c r="AL61" s="474"/>
@@ -23518,9 +24193,9 @@
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="M62" s="545" t="str">
+      <c r="M62" s="545">
         <f t="shared" si="24"/>
-        <v/>
+        <v>0.21084769206116269</v>
       </c>
       <c r="N62" s="545" t="str">
         <f t="shared" si="24"/>
@@ -23601,14 +24276,14 @@
       <c r="AG62" s="545"/>
       <c r="AH62" s="555">
         <f>+(AH44*10)/AH$9</f>
-        <v>7.8807932955851631E-2</v>
+        <v>9.0632291651089256E-2</v>
       </c>
       <c r="AI62" s="555">
         <v>0.1</v>
       </c>
       <c r="AJ62" s="547">
         <f t="shared" si="11"/>
-        <v>2.1192067044148374E-2</v>
+        <v>9.3677083489107499E-3</v>
       </c>
     </row>
     <row r="63" spans="1:59" s="504" customFormat="1" x14ac:dyDescent="0.35">
@@ -23659,9 +24334,9 @@
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="M63" s="569" t="str">
+      <c r="M63" s="569">
         <f t="shared" si="25"/>
-        <v/>
+        <v>2.9940372272685103</v>
       </c>
       <c r="N63" s="569" t="str">
         <f t="shared" si="25"/>
@@ -23742,14 +24417,14 @@
       <c r="AG63" s="549"/>
       <c r="AH63" s="550">
         <f>+(AH45*10)/AH$9</f>
-        <v>0.63461124959185788</v>
+        <v>0.84590138874349974</v>
       </c>
       <c r="AI63" s="550">
         <v>0.6</v>
       </c>
       <c r="AJ63" s="551">
         <f t="shared" si="11"/>
-        <v>-3.4611249591857907E-2</v>
+        <v>-0.24590138874349976</v>
       </c>
       <c r="AK63" s="474"/>
       <c r="AL63" s="474"/>
@@ -23891,9 +24566,9 @@
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="M65" s="549" t="str">
+      <c r="M65" s="549">
         <f t="shared" si="26"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N65" s="549" t="str">
         <f t="shared" si="26"/>
@@ -24193,7 +24868,7 @@
       </c>
       <c r="M68" s="585">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>13.452082753502181</v>
       </c>
       <c r="N68" s="585">
         <f t="shared" si="27"/>
@@ -24274,7 +24949,7 @@
       <c r="AG68" s="585"/>
       <c r="AH68" s="584">
         <f t="shared" si="27"/>
-        <v>11.476923709939026</v>
+        <v>11.653802168135892</v>
       </c>
       <c r="AI68" s="584">
         <f>SUM(AI54:AI63,AI65)</f>
@@ -24282,7 +24957,7 @@
       </c>
       <c r="AJ68" s="547">
         <f t="shared" si="27"/>
-        <v>-1.8769237099390239</v>
+        <v>-2.0538021681358929</v>
       </c>
       <c r="AK68" s="468"/>
       <c r="AL68" s="291"/>
@@ -24358,7 +25033,7 @@
       </c>
       <c r="M69" s="588">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>6.198922146598183</v>
       </c>
       <c r="N69" s="588">
         <f t="shared" si="28"/>
@@ -24439,7 +25114,7 @@
       <c r="AG69" s="588"/>
       <c r="AH69" s="587">
         <f t="shared" si="28"/>
-        <v>3.2601597528052308</v>
+        <v>3.5233303379360947</v>
       </c>
       <c r="AI69" s="587">
         <f t="shared" si="28"/>
@@ -24447,7 +25122,7 @@
       </c>
       <c r="AJ69" s="587">
         <f t="shared" si="28"/>
-        <v>-0.36015975280523072</v>
+        <v>-0.62333033793609438</v>
       </c>
       <c r="AK69" s="589"/>
       <c r="AL69" s="291"/>
@@ -24556,9 +25231,9 @@
         <f>+'Water '!$F17</f>
         <v>5</v>
       </c>
-      <c r="M71" s="593" t="str">
+      <c r="M71" s="593">
         <f>+'Water '!$F18</f>
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="N71" s="593" t="str">
         <f>+'Water '!$F19</f>
@@ -24639,7 +25314,7 @@
       <c r="AG71" s="593"/>
       <c r="AH71" s="594">
         <f>SUM($B71:AF71)</f>
-        <v>1433</v>
+        <v>1680</v>
       </c>
       <c r="AI71" s="594"/>
       <c r="AJ71" s="595"/>
@@ -24779,11 +25454,11 @@
       <c r="K74" s="877">
         <v>800</v>
       </c>
-      <c r="L74" s="877">
-        <v>0</v>
-      </c>
-      <c r="M74" s="1027">
-        <v>0</v>
+      <c r="L74" s="900">
+        <v>300</v>
+      </c>
+      <c r="M74" s="898">
+        <v>1300</v>
       </c>
       <c r="N74" s="877"/>
       <c r="O74" s="877"/>
@@ -24809,7 +25484,7 @@
       </c>
       <c r="AH74" s="516">
         <f>SUM(B74:AF74)</f>
-        <v>12800</v>
+        <v>14400</v>
       </c>
       <c r="AI74" s="537"/>
       <c r="AJ74" s="537"/>
@@ -24875,8 +25550,8 @@
       <c r="L75" s="601" t="str">
         <v>0</v>
       </c>
-      <c r="M75" s="601" t="str">
-        <v>0</v>
+      <c r="M75" s="601">
+        <v>1256.1700000000419</v>
       </c>
       <c r="N75" s="601" t="str">
         <v>0</v>
@@ -24938,7 +25613,7 @@
       <c r="AG75" s="599"/>
       <c r="AH75" s="516">
         <f>SUM(B75:AF75)</f>
-        <v>10888.429999999935</v>
+        <v>12144.599999999977</v>
       </c>
       <c r="AI75" s="600"/>
       <c r="AJ75" s="600"/>
@@ -25003,8 +25678,8 @@
       <c r="L76" s="604" t="str">
         <v>0</v>
       </c>
-      <c r="M76" s="604" t="str">
-        <v>0</v>
+      <c r="M76" s="604">
+        <v>244.5399999999936</v>
       </c>
       <c r="N76" s="604" t="str">
         <v>0</v>
@@ -25066,7 +25741,7 @@
       <c r="AG76" s="604"/>
       <c r="AH76" s="604">
         <f>SUM($B76:AF76)</f>
-        <v>1350.3500000000058</v>
+        <v>1594.8899999999994</v>
       </c>
       <c r="AI76" s="605"/>
       <c r="AJ76" s="606"/>
@@ -25132,8 +25807,8 @@
       <c r="L77" s="607" t="str">
         <v>0</v>
       </c>
-      <c r="M77" s="607" t="str">
-        <v>0</v>
+      <c r="M77" s="607">
+        <v>591.47999999999593</v>
       </c>
       <c r="N77" s="607" t="str">
         <v>0</v>
@@ -25195,7 +25870,7 @@
       <c r="AG77" s="607"/>
       <c r="AH77" s="604">
         <f>SUM($B77:AF77)</f>
-        <v>3764.1000000000058</v>
+        <v>4355.5800000000017</v>
       </c>
       <c r="AI77" s="757"/>
       <c r="AJ77" s="757" t="s">
@@ -25274,7 +25949,7 @@
       </c>
       <c r="M78" s="788">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>420.15000000005239</v>
       </c>
       <c r="N78" s="788">
         <f t="shared" si="29"/>
@@ -25358,7 +26033,7 @@
       </c>
       <c r="AH78" s="484">
         <f>AH75-AH76-AH77</f>
-        <v>5773.9799999999232</v>
+        <v>6194.1299999999756</v>
       </c>
       <c r="AI78" s="484"/>
     </row>
@@ -25411,7 +26086,7 @@
       </c>
       <c r="M79" s="610">
         <f>'Daily KPIs CO2'!M47</f>
-        <v>0</v>
+        <v>1256.1700000000419</v>
       </c>
       <c r="N79" s="610"/>
       <c r="O79" s="610">
@@ -25530,7 +26205,7 @@
         <v>2914</v>
       </c>
       <c r="M80" s="613">
-        <v>0</v>
+        <v>8829</v>
       </c>
       <c r="N80" s="613">
         <v>0</v>
@@ -25592,7 +26267,7 @@
       <c r="AG80" s="613"/>
       <c r="AH80" s="594">
         <f>SUM(B80:AF80)</f>
-        <v>62240</v>
+        <v>71069</v>
       </c>
       <c r="AI80" s="594"/>
       <c r="AJ80" s="614"/>
@@ -25720,7 +26395,7 @@
         <v>4033.5</v>
       </c>
       <c r="K82" s="617">
-        <v>0</v>
+        <v>10110.299999999999</v>
       </c>
       <c r="L82" s="617">
         <v>0</v>
@@ -25780,7 +26455,7 @@
         <v>0</v>
       </c>
       <c r="AE82" s="617">
-        <v>75752.199999999983</v>
+        <v>85862.499999999985</v>
       </c>
       <c r="AF82" s="617">
         <v>0</v>
@@ -25788,7 +26463,7 @@
       <c r="AG82" s="617"/>
       <c r="AH82" s="594">
         <f>SUM(B82:AF82)</f>
-        <v>134417.59999999998</v>
+        <v>154638.20000000001</v>
       </c>
       <c r="AI82" s="594"/>
       <c r="AJ82" s="614"/>
@@ -25855,7 +26530,7 @@
         <v>1119.5</v>
       </c>
       <c r="M83" s="621">
-        <v>0</v>
+        <v>1281.3</v>
       </c>
       <c r="N83" s="621">
         <v>0</v>
@@ -25917,7 +26592,7 @@
       <c r="AG83" s="621"/>
       <c r="AH83" s="594">
         <f>SUM(B83:AF83)</f>
-        <v>13512.199999999999</v>
+        <v>14793.499999999998</v>
       </c>
       <c r="AI83" s="594"/>
       <c r="AJ83" s="594"/>
@@ -25983,8 +26658,8 @@
       <c r="L84" s="620">
         <v>542.10000000009313</v>
       </c>
-      <c r="M84" s="620" t="str">
-        <v>0</v>
+      <c r="M84" s="620">
+        <v>3450.3000000000466</v>
       </c>
       <c r="N84" s="620" t="str">
         <v>0</v>
@@ -26046,7 +26721,7 @@
       <c r="AG84" s="620"/>
       <c r="AH84" s="621">
         <f>SUM($B84:AF84)</f>
-        <v>22851</v>
+        <v>26301.300000000047</v>
       </c>
       <c r="AI84" s="594"/>
       <c r="AJ84" s="614"/>
@@ -26467,9 +27142,9 @@
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="M90" s="653" t="str">
+      <c r="M90" s="653">
         <f t="shared" si="33"/>
-        <v/>
+        <v>16.066594135060598</v>
       </c>
       <c r="N90" s="653" t="str">
         <f t="shared" si="33"/>
@@ -26550,18 +27225,18 @@
       <c r="AG90" s="627"/>
       <c r="AH90" s="659">
         <f>IF(AH$9=0,"0",+(AH22*10)/AH$9)</f>
-        <v>12.480687908639872</v>
+        <v>12.801811195716358</v>
       </c>
       <c r="AI90" s="662">
         <v>10.199999999999999</v>
       </c>
       <c r="AJ90" s="665">
         <f>+AI90-AH90</f>
-        <v>-2.280687908639873</v>
+        <v>-2.6018111957163583</v>
       </c>
       <c r="AK90" s="667">
         <f>AH90/AI90*100</f>
-        <v>122.35968537882229</v>
+        <v>125.50795289917997</v>
       </c>
       <c r="AL90" s="629"/>
       <c r="AM90" s="630"/>
@@ -26701,9 +27376,9 @@
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="M92" s="653" t="str">
+      <c r="M92" s="653">
         <f t="shared" si="35"/>
-        <v/>
+        <v>5.48203999359023</v>
       </c>
       <c r="N92" s="653" t="str">
         <f t="shared" si="35"/>
@@ -26784,18 +27459,18 @@
       <c r="AG92" s="628"/>
       <c r="AH92" s="670">
         <f>IF(AH$9=0,"0",+(AH74)/AH$9)</f>
-        <v>5.3091660096573738</v>
+        <v>5.4379374990653551</v>
       </c>
       <c r="AI92" s="674">
         <v>5</v>
       </c>
       <c r="AJ92" s="675">
         <f>AI92-AH92</f>
-        <v>-0.30916600965737384</v>
+        <v>-0.43793749906535506</v>
       </c>
       <c r="AK92" s="673">
         <f t="shared" si="34"/>
-        <v>106.18332019314747</v>
+        <v>108.7587499813071</v>
       </c>
       <c r="AL92" s="629"/>
       <c r="AM92" s="630"/>
@@ -26870,9 +27545,9 @@
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="M93" s="653" t="str">
+      <c r="M93" s="653">
         <f t="shared" si="36"/>
-        <v/>
+        <v>1.0312138923327074</v>
       </c>
       <c r="N93" s="653" t="str">
         <f t="shared" si="36"/>
@@ -26953,18 +27628,18 @@
       <c r="AG93" s="628"/>
       <c r="AH93" s="670">
         <f>IF(AH$9=0,"0",+AH76/AH$9)</f>
-        <v>0.56009627508913007</v>
+        <v>0.60228556513085707</v>
       </c>
       <c r="AI93" s="674">
         <v>1.7</v>
       </c>
       <c r="AJ93" s="676">
         <f>AI93-AH93</f>
-        <v>1.1399037249108699</v>
+        <v>1.0977144348691428</v>
       </c>
       <c r="AK93" s="673">
         <f t="shared" si="34"/>
-        <v>32.9468397111253</v>
+        <v>35.428562654756298</v>
       </c>
       <c r="AL93" s="635"/>
       <c r="AM93" s="636"/>
@@ -27037,9 +27712,9 @@
         <f t="shared" si="37"/>
         <v/>
       </c>
-      <c r="M94" s="653" t="str">
+      <c r="M94" s="653">
         <f t="shared" si="37"/>
-        <v/>
+        <v>42.634668420919461</v>
       </c>
       <c r="N94" s="653" t="str">
         <f t="shared" si="37"/>
@@ -27120,18 +27795,18 @@
       <c r="AG94" s="627"/>
       <c r="AH94" s="670">
         <f>IF(AH$9=0,"0",+(AH80+AH83)/AH$9)</f>
-        <v>31.420391046622441</v>
+        <v>32.424646424548548</v>
       </c>
       <c r="AI94" s="674">
         <v>22</v>
       </c>
       <c r="AJ94" s="675">
         <f>AI94-AH94</f>
-        <v>-9.4203910466224414</v>
+        <v>-10.424646424548548</v>
       </c>
       <c r="AK94" s="673">
         <f>AH94/AI94*100</f>
-        <v>142.81995930282926</v>
+        <v>147.38475647522066</v>
       </c>
       <c r="AL94" s="629"/>
       <c r="AM94" s="630"/>
@@ -27191,7 +27866,7 @@
       <c r="AG95" s="637"/>
       <c r="AH95" s="670">
         <f>IF(AH$9=0,"0",+(AH78*10)/AH$9)</f>
-        <v>23.949233090969589</v>
+        <v>23.391174861864968</v>
       </c>
       <c r="AI95" s="674"/>
       <c r="AJ95" s="676"/>
@@ -27270,9 +27945,9 @@
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="M96" s="654" t="str">
+      <c r="M96" s="654">
         <f t="shared" si="39"/>
-        <v/>
+        <v>14.549755838372789</v>
       </c>
       <c r="N96" s="654" t="str">
         <f t="shared" si="39"/>
@@ -27353,18 +28028,18 @@
       <c r="AG96" s="627"/>
       <c r="AH96" s="660">
         <f>IF(AH$9=0,"0",+(AH84)/AH$9)</f>
-        <v>9.4781056630219247</v>
+        <v>9.9322795516783255</v>
       </c>
       <c r="AI96" s="663">
         <v>7.2</v>
       </c>
       <c r="AJ96" s="677">
         <f>AI96-AH96</f>
-        <v>-2.2781056630219245</v>
+        <v>-2.7322795516783254</v>
       </c>
       <c r="AK96" s="668">
         <f t="shared" si="34"/>
-        <v>131.64035643086007</v>
+        <v>137.9483271066434</v>
       </c>
       <c r="AL96" s="629"/>
       <c r="AM96" s="630"/>
@@ -27864,7 +28539,7 @@
       </c>
       <c r="M103" s="650">
         <f>IF('Entries October 2026'!L18-'Entries October 2026'!L17&lt;1,0,'Entries October 2026'!L18-'Entries October 2026'!L17)</f>
-        <v>0</v>
+        <v>591.47999999999593</v>
       </c>
       <c r="N103" s="521">
         <f>IF('Entries October 2026'!L19-'Entries October 2026'!L18&lt;1,0,'Entries October 2026'!L19-'Entries October 2026'!L18)</f>
@@ -28009,9 +28684,9 @@
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="M105" s="652" t="str">
+      <c r="M105" s="652">
         <f t="shared" si="41"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N105" s="652" t="str">
         <f t="shared" si="41"/>
@@ -28327,7 +29002,7 @@
       </c>
       <c r="M116" s="650">
         <f>'Daily KPIs'!M80</f>
-        <v>0</v>
+        <v>8829</v>
       </c>
       <c r="N116" s="650">
         <f>'Daily KPIs'!N80</f>
@@ -28408,7 +29083,7 @@
       <c r="AG116" s="650"/>
       <c r="AH116" s="649">
         <f>'Daily KPIs'!AH80</f>
-        <v>62240</v>
+        <v>71069</v>
       </c>
     </row>
     <row r="117" spans="2:34" hidden="1" x14ac:dyDescent="0.35">
@@ -28498,7 +29173,7 @@
       </c>
       <c r="AH140" s="870">
         <f>AH83/(AH83+AH80)</f>
-        <v>0.17837369739756731</v>
+        <v>0.17229291017615372</v>
       </c>
       <c r="AM140" s="751"/>
     </row>
@@ -28635,45 +29310,45 @@
   </mergeCells>
   <phoneticPr fontId="32" type="noConversion"/>
   <conditionalFormatting sqref="B93:C93 AH93">
-    <cfRule type="cellIs" dxfId="35" priority="127" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="82" priority="127" operator="greaterThan">
       <formula>$AI$93</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B90:AF90">
-    <cfRule type="cellIs" dxfId="34" priority="36" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="81" priority="36" operator="greaterThan">
       <formula>10.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92:AF92">
-    <cfRule type="cellIs" dxfId="33" priority="26" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="80" priority="26" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="27" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="79" priority="27" operator="lessThanOrEqual">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:AF93">
-    <cfRule type="cellIs" dxfId="31" priority="34" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="78" priority="34" operator="greaterThan">
       <formula>1.7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B94:AF94">
-    <cfRule type="cellIs" dxfId="30" priority="33" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="77" priority="33" operator="greaterThan">
       <formula>22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96:AF96">
-    <cfRule type="cellIs" dxfId="29" priority="32" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="76" priority="32" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:AG22">
-    <cfRule type="cellIs" dxfId="28" priority="101" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="75" priority="101" operator="greaterThan">
       <formula>400</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42:AG42">
-    <cfRule type="cellIs" dxfId="27" priority="47" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="74" priority="47" operator="greaterThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28688,129 +29363,129 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B94:AG94">
-    <cfRule type="cellIs" dxfId="26" priority="1174" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="73" priority="1174" operator="greaterThan">
       <formula>$AI$94</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96:AG96">
-    <cfRule type="cellIs" dxfId="25" priority="1176" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="72" priority="1176" operator="greaterThan">
       <formula>$AI$96</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:AH15">
-    <cfRule type="cellIs" dxfId="24" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="71" priority="1" operator="greaterThan">
       <formula>3.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54:AH54">
-    <cfRule type="cellIs" dxfId="23" priority="123" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="70" priority="123" operator="greaterThan">
       <formula>3.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B56:AH56">
-    <cfRule type="cellIs" dxfId="22" priority="61" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="69" priority="61" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B57:AH57 B59:AH59 B61:AH61">
-    <cfRule type="cellIs" dxfId="21" priority="62" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="68" priority="62" operator="greaterThan">
       <formula>0.7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58:AH58 B62:AH62">
-    <cfRule type="cellIs" dxfId="20" priority="63" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="67" priority="63" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B60:AH60">
-    <cfRule type="cellIs" dxfId="19" priority="22" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="66" priority="22" operator="greaterThan">
       <formula>2.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B65:AH65">
-    <cfRule type="cellIs" dxfId="18" priority="56" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="65" priority="56" operator="greaterThan">
       <formula>0.3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68:AH68">
-    <cfRule type="cellIs" dxfId="17" priority="58" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="64" priority="58" operator="greaterThan">
       <formula>9.6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69:AH69">
-    <cfRule type="cellIs" dxfId="16" priority="59" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="63" priority="59" operator="greaterThan">
       <formula>2.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92:AH92">
-    <cfRule type="cellIs" dxfId="15" priority="48" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="62" priority="48" operator="greaterThan">
       <formula>5.04</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:AH93">
-    <cfRule type="cellIs" dxfId="14" priority="44" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="61" priority="44" operator="greaterThan">
       <formula>1.7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="43" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="60" priority="43" operator="greaterThan">
       <formula>1.7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96:AH96">
-    <cfRule type="cellIs" dxfId="12" priority="37" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="59" priority="37" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E96">
-    <cfRule type="cellIs" dxfId="11" priority="39" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="39" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I63:AH63">
-    <cfRule type="cellIs" dxfId="10" priority="68" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="57" priority="68" operator="greaterThan">
       <formula>0.6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC54:AG54">
-    <cfRule type="cellIs" dxfId="9" priority="82" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="56" priority="82" operator="greaterThan">
       <formula>$AI$54</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC55:AG59 AC61:AG61 AC63:AG63 B64:AG64">
-    <cfRule type="cellIs" dxfId="8" priority="1135" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="55" priority="1135" operator="greaterThan">
       <formula>$AI59</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH94">
-    <cfRule type="cellIs" dxfId="7" priority="28" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="54" priority="28" operator="lessThanOrEqual">
       <formula>22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH94:AH96 B90:AH90 AH91">
-    <cfRule type="cellIs" dxfId="6" priority="1168" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="53" priority="1168" operator="greaterThan">
       <formula>$AI$90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH96">
-    <cfRule type="cellIs" dxfId="5" priority="29" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="52" priority="29" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="30" operator="lessThan">
+    <cfRule type="cellIs" dxfId="51" priority="30" operator="lessThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="40" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="50" priority="40" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ8">
-    <cfRule type="cellIs" dxfId="2" priority="105" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="49" priority="105" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="106" operator="lessThan">
+    <cfRule type="cellIs" dxfId="48" priority="106" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK90:AK96">
-    <cfRule type="cellIs" dxfId="0" priority="50" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="47" priority="50" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29786,11 +30461,11 @@
       </c>
       <c r="C18" s="55">
         <f t="shared" si="1"/>
-        <v>-254694</v>
+        <v>144</v>
       </c>
       <c r="D18" s="55">
         <f t="shared" si="2"/>
-        <v>1112775</v>
+        <v>-103</v>
       </c>
       <c r="E18" s="56">
         <f>'Entries October 2026'!W17</f>
@@ -29802,7 +30477,7 @@
       </c>
       <c r="G18" s="57">
         <f t="shared" si="7"/>
-        <v>-1367469</v>
+        <v>247</v>
       </c>
       <c r="H18" s="57">
         <f>'Entries October 2026'!AA17</f>
@@ -29810,7 +30485,7 @@
       </c>
       <c r="I18" s="58">
         <f t="shared" si="3"/>
-        <v>-97122</v>
+        <v>0</v>
       </c>
       <c r="J18" s="57">
         <f>'Entries October 2026'!T17</f>
@@ -29822,7 +30497,7 @@
       </c>
       <c r="L18" s="58">
         <f t="shared" si="6"/>
-        <v>-97122</v>
+        <v>0</v>
       </c>
       <c r="M18" s="57">
         <f>'Entries October 2026'!R17</f>
@@ -29830,11 +30505,11 @@
       </c>
       <c r="N18" s="57">
         <f>'Entries October 2026'!AC18-'Entries October 2026'!AC17</f>
-        <v>-6865</v>
+        <v>23</v>
       </c>
       <c r="O18" s="57">
         <f t="shared" si="5"/>
-        <v>-509388</v>
+        <v>288</v>
       </c>
       <c r="P18" s="62"/>
       <c r="Q18" s="45"/>
@@ -29849,15 +30524,15 @@
       </c>
       <c r="B19" s="55">
         <f>'Entries October 2026'!O18</f>
-        <v>0</v>
+        <v>254838</v>
       </c>
       <c r="C19" s="55">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-254838</v>
       </c>
       <c r="D19" s="55">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1112878</v>
       </c>
       <c r="E19" s="56">
         <f>'Entries October 2026'!W18</f>
@@ -29865,19 +30540,19 @@
       </c>
       <c r="F19" s="57">
         <f>'Entries October 2026'!V18</f>
-        <v>0</v>
+        <v>1367716</v>
       </c>
       <c r="G19" s="57">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-1367716</v>
       </c>
       <c r="H19" s="57">
         <f>'Entries October 2026'!AA18</f>
-        <v>0</v>
+        <v>97122</v>
       </c>
       <c r="I19" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-97122</v>
       </c>
       <c r="J19" s="57">
         <f>'Entries October 2026'!T18</f>
@@ -29889,7 +30564,7 @@
       </c>
       <c r="L19" s="58">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-97122</v>
       </c>
       <c r="M19" s="57">
         <f>'Entries October 2026'!R18</f>
@@ -29897,11 +30572,11 @@
       </c>
       <c r="N19" s="57">
         <f>'Entries October 2026'!AC19-'Entries October 2026'!AC18</f>
-        <v>0</v>
+        <v>-6888</v>
       </c>
       <c r="O19" s="57">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-509676</v>
       </c>
       <c r="P19" s="62"/>
       <c r="Q19" s="45"/>
@@ -31113,24 +31788,24 @@
     </row>
     <row r="6" spans="1:20" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="927" t="s">
+      <c r="A7" s="930" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="383"/>
       <c r="C7" s="383"/>
-      <c r="D7" s="940" t="s">
+      <c r="D7" s="943" t="s">
         <v>254</v>
       </c>
-      <c r="E7" s="943" t="s">
+      <c r="E7" s="946" t="s">
         <v>286</v>
       </c>
-      <c r="F7" s="937" t="s">
+      <c r="F7" s="940" t="s">
         <v>287</v>
       </c>
-      <c r="G7" s="933" t="s">
+      <c r="G7" s="936" t="s">
         <v>255</v>
       </c>
-      <c r="H7" s="933" t="s">
+      <c r="H7" s="936" t="s">
         <v>256</v>
       </c>
       <c r="I7" s="383" t="s">
@@ -31142,33 +31817,33 @@
       <c r="K7" s="390" t="s">
         <v>53</v>
       </c>
-      <c r="L7" s="934" t="s">
+      <c r="L7" s="937" t="s">
         <v>17</v>
       </c>
-      <c r="M7" s="935"/>
-      <c r="N7" s="935"/>
-      <c r="O7" s="935"/>
-      <c r="P7" s="936"/>
-      <c r="Q7" s="931" t="s">
+      <c r="M7" s="938"/>
+      <c r="N7" s="938"/>
+      <c r="O7" s="938"/>
+      <c r="P7" s="939"/>
+      <c r="Q7" s="934" t="s">
         <v>11</v>
       </c>
-      <c r="R7" s="932"/>
-      <c r="S7" s="932"/>
-      <c r="T7" s="932"/>
+      <c r="R7" s="935"/>
+      <c r="S7" s="935"/>
+      <c r="T7" s="935"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="928"/>
+      <c r="A8" s="931"/>
       <c r="B8" s="384" t="s">
         <v>257</v>
       </c>
       <c r="C8" s="384" t="s">
         <v>258</v>
       </c>
-      <c r="D8" s="941"/>
-      <c r="E8" s="944"/>
-      <c r="F8" s="938"/>
-      <c r="G8" s="933"/>
-      <c r="H8" s="933"/>
+      <c r="D8" s="944"/>
+      <c r="E8" s="947"/>
+      <c r="F8" s="941"/>
+      <c r="G8" s="936"/>
+      <c r="H8" s="936"/>
       <c r="I8" s="383"/>
       <c r="J8" s="383"/>
       <c r="K8" s="390"/>
@@ -31191,12 +31866,12 @@
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A9" s="929"/>
+      <c r="A9" s="932"/>
       <c r="B9" s="385"/>
       <c r="C9" s="385"/>
-      <c r="D9" s="942"/>
-      <c r="E9" s="945"/>
-      <c r="F9" s="939"/>
+      <c r="D9" s="945"/>
+      <c r="E9" s="948"/>
+      <c r="F9" s="942"/>
       <c r="G9" s="383" t="s">
         <v>56</v>
       </c>
@@ -32072,7 +32747,7 @@
       </c>
       <c r="K20" s="775">
         <f>'CO2'!E17</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L20" s="776">
         <f>+'PROD.FIG. '!F15</f>
@@ -32114,9 +32789,9 @@
       <c r="A21" s="719">
         <v>12</v>
       </c>
-      <c r="B21" s="719" t="str">
+      <c r="B21" s="719">
         <f>IF('Entries October 2026'!I18&lt;'Entries October 2026'!I17,"0",(IF('Entries October 2026'!I18&gt;='Entries October 2026'!I17,'Entries October 2026'!I18-'Entries October 2026'!I17,(999999-'Entries October 2026'!I17)+'Entries October 2026'!I18+1)))</f>
-        <v>0</v>
+        <v>8829</v>
       </c>
       <c r="C21" s="719" t="str">
         <f>IF('Entries October 2026'!J18&lt;='Entries October 2026'!J17,"0",IF('Entries October 2026'!J18&gt;='Entries October 2026'!J17,'Entries October 2026'!J18-'Entries October 2026'!J17,(999999-'Entries October 2026'!J17)+'Entries October 2026'!J18+1))</f>
@@ -32124,24 +32799,26 @@
       </c>
       <c r="D21" s="720">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E21" s="873"/>
-      <c r="F21" s="721" t="str">
+        <v>8829</v>
+      </c>
+      <c r="E21" s="873">
+        <v>1281.3</v>
+      </c>
+      <c r="F21" s="721">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="737" t="str">
+        <v>0.12673214444675232</v>
+      </c>
+      <c r="G21" s="737">
         <f>IF('Entries October 2026'!K18&lt;'Entries October 2026'!K17,"0",IF('Entries October 2026'!K18&gt;='Entries October 2026'!K17,'Entries October 2026'!K18-'Entries October 2026'!K17,(999999-'Entries October 2026'!K17)+'Entries October 2026'!K18+1))</f>
         <v>0</v>
       </c>
       <c r="H21" s="720">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10110.299999999999</v>
       </c>
       <c r="I21" s="737">
         <f>'Water '!Z18*10</f>
-        <v>0</v>
+        <v>3810</v>
       </c>
       <c r="J21" s="720" t="str">
         <f>IF('Entries October 2026'!B18-'Entries October 2026'!B17&lt;1,"0",'Entries October 2026'!B18-'Entries October 2026'!B17)</f>
@@ -32149,7 +32826,7 @@
       </c>
       <c r="K21" s="722">
         <f>'CO2'!E18</f>
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="L21" s="723">
         <f>+'PROD.FIG. '!F16</f>
@@ -32168,15 +32845,15 @@
         <v>0</v>
       </c>
       <c r="P21" s="724">
-        <v>0</v>
+        <v>237.13800000000001</v>
       </c>
       <c r="Q21" s="393">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>42.634668420919461</v>
       </c>
       <c r="R21" s="393">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16.066594135060598</v>
       </c>
       <c r="S21" s="393">
         <f t="shared" si="5"/>
@@ -32191,7 +32868,7 @@
       <c r="A22" s="719">
         <v>13</v>
       </c>
-      <c r="B22" s="719">
+      <c r="B22" s="719" t="str">
         <f>IF('Entries October 2026'!I19&lt;'Entries October 2026'!I18,"0",(IF('Entries October 2026'!I19&gt;='Entries October 2026'!I18,'Entries October 2026'!I19-'Entries October 2026'!I18,(999999-'Entries October 2026'!I18)+'Entries October 2026'!I19+1)))</f>
         <v>0</v>
       </c>
@@ -32208,7 +32885,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G22" s="737">
+      <c r="G22" s="737" t="str">
         <f>IF('Entries October 2026'!K19&lt;'Entries October 2026'!K18,"0",IF('Entries October 2026'!K19&gt;='Entries October 2026'!K18,'Entries October 2026'!K19-'Entries October 2026'!K18,(999999-'Entries October 2026'!K18)+'Entries October 2026'!K19+1))</f>
         <v>0</v>
       </c>
@@ -33731,15 +34408,15 @@
       <c r="C43" s="19"/>
       <c r="D43" s="20">
         <f>SUM(D10:D40)</f>
-        <v>62240</v>
+        <v>71069</v>
       </c>
       <c r="E43" s="741">
         <f>SUM(E10:E40)</f>
-        <v>13512.199999999999</v>
+        <v>14793.499999999998</v>
       </c>
       <c r="F43" s="754">
         <f>IF((E43+D43)=0,"0",E43/(D43+E43))</f>
-        <v>0.17837369739756731</v>
+        <v>0.17229291017615372</v>
       </c>
       <c r="G43" s="20">
         <f t="shared" ref="G43:P43" si="7">SUM(G10:G40)</f>
@@ -33747,11 +34424,11 @@
       </c>
       <c r="H43" s="20">
         <f t="shared" si="7"/>
-        <v>75752.199999999983</v>
+        <v>85862.499999999985</v>
       </c>
       <c r="I43" s="20">
         <f t="shared" si="7"/>
-        <v>30090</v>
+        <v>33900</v>
       </c>
       <c r="J43" s="20">
         <f t="shared" si="7"/>
@@ -33759,7 +34436,7 @@
       </c>
       <c r="K43" s="20">
         <f t="shared" si="7"/>
-        <v>12800</v>
+        <v>14400</v>
       </c>
       <c r="L43" s="20">
         <f t="shared" si="7"/>
@@ -33779,7 +34456,7 @@
       </c>
       <c r="P43" s="403">
         <f t="shared" si="7"/>
-        <v>2410.9247999999998</v>
+        <v>2648.0627999999997</v>
       </c>
       <c r="Q43" s="408" t="s">
         <v>13</v>
@@ -33807,7 +34484,7 @@
       </c>
       <c r="E44" s="728">
         <f>D43+E43</f>
-        <v>75752.2</v>
+        <v>85862.5</v>
       </c>
       <c r="F44" s="708"/>
       <c r="G44" s="7"/>
@@ -33822,19 +34499,19 @@
       <c r="P44" s="401"/>
       <c r="Q44" s="397">
         <f>IF(P43=0,0,H43/P43)</f>
-        <v>31.420391046622438</v>
+        <v>32.424646424548541</v>
       </c>
       <c r="R44" s="398">
         <f>IF(Q44=0,0,I43/P43)</f>
-        <v>12.480687908639872</v>
+        <v>12.801811195716358</v>
       </c>
       <c r="S44" s="398">
         <f>IF(R44=0,0,J43/P43)</f>
-        <v>0.398187450724303</v>
+        <v>0.36252916660435702</v>
       </c>
       <c r="T44" s="399">
         <f>IF(S44=0,0,K43/P43)</f>
-        <v>5.3091660096573738</v>
+        <v>5.4379374990653551</v>
       </c>
     </row>
     <row r="45" spans="1:32" ht="15" x14ac:dyDescent="0.2">
@@ -33867,12 +34544,12 @@
       <c r="T46" s="2"/>
     </row>
     <row r="47" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="D47" s="930"/>
-      <c r="E47" s="930"/>
-      <c r="F47" s="930"/>
-      <c r="G47" s="930"/>
-      <c r="H47" s="930"/>
-      <c r="I47" s="930"/>
+      <c r="D47" s="933"/>
+      <c r="E47" s="933"/>
+      <c r="F47" s="933"/>
+      <c r="G47" s="933"/>
+      <c r="H47" s="933"/>
+      <c r="I47" s="933"/>
       <c r="AF47" t="s">
         <v>55</v>
       </c>
@@ -33911,41 +34588,41 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="Q10:Q44">
-    <cfRule type="cellIs" dxfId="62" priority="7" operator="between">
+    <cfRule type="cellIs" dxfId="109" priority="7" operator="between">
       <formula>0</formula>
       <formula>22</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="108" priority="8" operator="greaterThan">
       <formula>22</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="107" priority="9" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:R44">
-    <cfRule type="cellIs" dxfId="59" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="106" priority="1" operator="between">
       <formula>0</formula>
       <formula>10.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="105" priority="2" operator="greaterThan">
       <formula>10.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S10:S44">
-    <cfRule type="cellIs" dxfId="57" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="104" priority="3" operator="between">
       <formula>0</formula>
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="103" priority="4" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T10:T44">
-    <cfRule type="cellIs" dxfId="55" priority="5" operator="between">
+    <cfRule type="cellIs" dxfId="102" priority="5" operator="between">
       <formula>0</formula>
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="101" priority="6" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -33977,16 +34654,16 @@
       <c r="B2" s="8"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="946" t="s">
+      <c r="A3" s="949" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="948" t="s">
+      <c r="B3" s="951" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="947"/>
-      <c r="B4" s="949"/>
+      <c r="A4" s="950"/>
+      <c r="B4" s="952"/>
     </row>
     <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="36">
@@ -34350,31 +35027,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="958" t="s">
+      <c r="A1" s="961" t="s">
         <v>304</v>
       </c>
-      <c r="B1" s="959"/>
-      <c r="C1" s="959"/>
-      <c r="D1" s="959"/>
-      <c r="E1" s="959"/>
-      <c r="F1" s="959"/>
-      <c r="G1" s="959"/>
-      <c r="H1" s="959"/>
-      <c r="I1" s="959"/>
-      <c r="J1" s="959"/>
-      <c r="K1" s="959"/>
-      <c r="L1" s="959"/>
-      <c r="M1" s="959"/>
+      <c r="B1" s="962"/>
+      <c r="C1" s="962"/>
+      <c r="D1" s="962"/>
+      <c r="E1" s="962"/>
+      <c r="F1" s="962"/>
+      <c r="G1" s="962"/>
+      <c r="H1" s="962"/>
+      <c r="I1" s="962"/>
+      <c r="J1" s="962"/>
+      <c r="K1" s="962"/>
+      <c r="L1" s="962"/>
+      <c r="M1" s="962"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
       <c r="F2" s="9"/>
-      <c r="M2" s="950" t="s">
+      <c r="M2" s="953" t="s">
         <v>296</v>
       </c>
-      <c r="N2" s="950" t="s">
+      <c r="N2" s="953" t="s">
         <v>297</v>
       </c>
     </row>
@@ -34383,11 +35060,11 @@
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="9"/>
-      <c r="M3" s="951"/>
-      <c r="N3" s="951"/>
+      <c r="M3" s="954"/>
+      <c r="N3" s="954"/>
     </row>
     <row r="4" spans="1:17" s="339" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="964" t="s">
+      <c r="A4" s="967" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="847" t="s">
@@ -34420,22 +35097,22 @@
       <c r="K4" s="848" t="s">
         <v>40</v>
       </c>
-      <c r="L4" s="960" t="s">
+      <c r="L4" s="963" t="s">
         <v>243</v>
       </c>
-      <c r="M4" s="962" t="s">
+      <c r="M4" s="965" t="s">
         <v>246</v>
       </c>
-      <c r="N4" s="952" t="s">
+      <c r="N4" s="955" t="s">
         <v>246</v>
       </c>
-      <c r="O4" s="955" t="s">
+      <c r="O4" s="958" t="s">
         <v>298</v>
       </c>
       <c r="P4" s="350"/>
     </row>
     <row r="5" spans="1:17" s="339" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="965"/>
+      <c r="A5" s="968"/>
       <c r="B5" s="864" t="s">
         <v>41</v>
       </c>
@@ -34466,10 +35143,10 @@
       <c r="K5" s="865" t="s">
         <v>44</v>
       </c>
-      <c r="L5" s="961"/>
-      <c r="M5" s="963"/>
-      <c r="N5" s="953"/>
-      <c r="O5" s="956"/>
+      <c r="L5" s="964"/>
+      <c r="M5" s="966"/>
+      <c r="N5" s="956"/>
+      <c r="O5" s="959"/>
       <c r="P5" s="350"/>
     </row>
     <row r="6" spans="1:17" s="73" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -34486,8 +35163,8 @@
       <c r="K6" s="836"/>
       <c r="L6" s="869"/>
       <c r="M6" s="833"/>
-      <c r="N6" s="954"/>
-      <c r="O6" s="957"/>
+      <c r="N6" s="957"/>
+      <c r="O6" s="960"/>
       <c r="P6" s="350"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
@@ -35105,13 +35782,13 @@
         <f>IF('Entries October 2026'!B18-'Entries October 2026'!B17&lt;1,"0",'Entries October 2026'!B18-'Entries October 2026'!B17)</f>
         <v>0</v>
       </c>
-      <c r="C18" s="739" t="str">
+      <c r="C18" s="739">
         <f>IF('Entries October 2026'!F18-'Entries October 2026'!F17&lt;1,"0",'Entries October 2026'!F18-'Entries October 2026'!F17)</f>
-        <v>0</v>
-      </c>
-      <c r="D18" s="839" t="str">
+        <v>18.100000000000364</v>
+      </c>
+      <c r="D18" s="839">
         <f>IF('Entries October 2026'!C18-'Entries October 2026'!C17&lt;1,"0",'Entries October 2026'!C18-'Entries October 2026'!C17)</f>
-        <v>0</v>
+        <v>3450.3000000000466</v>
       </c>
       <c r="E18" s="843" t="str">
         <f t="shared" si="0"/>
@@ -35123,7 +35800,7 @@
       </c>
       <c r="G18" s="837"/>
       <c r="H18" s="739"/>
-      <c r="I18" s="740" t="str">
+      <c r="I18" s="740">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -35135,20 +35812,20 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L18" s="831" t="str">
-        <v>0</v>
-      </c>
-      <c r="M18" s="829" t="str">
+      <c r="L18" s="831">
+        <v>237.13800000000001</v>
+      </c>
+      <c r="M18" s="829">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N18" s="829" t="str">
+      <c r="N18" s="829">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>14.549755838372789</v>
       </c>
       <c r="O18" s="830">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-3450.3000000000466</v>
       </c>
       <c r="P18" s="333"/>
       <c r="R18" s="8" t="s">
@@ -36205,11 +36882,11 @@
       </c>
       <c r="C38" s="388">
         <f>SUM(C7:C37)</f>
-        <v>157.80000000000109</v>
+        <v>175.90000000000146</v>
       </c>
       <c r="D38" s="840">
         <f t="shared" si="7"/>
-        <v>22851</v>
+        <v>26301.300000000047</v>
       </c>
       <c r="E38" s="845"/>
       <c r="F38" s="846">
@@ -36226,7 +36903,7 @@
       </c>
       <c r="I38" s="797">
         <f>B38/C38</f>
-        <v>6.0836501901140263</v>
+        <v>5.4576463899942702</v>
       </c>
       <c r="J38" s="355"/>
       <c r="K38" s="356">
@@ -36235,15 +36912,15 @@
       </c>
       <c r="L38" s="828">
         <f>SUM(L7:L37)</f>
-        <v>2410.9247999999998</v>
+        <v>2648.0627999999997</v>
       </c>
       <c r="M38" s="834">
         <f>IF(L38=0,"0",(K38/L38))</f>
-        <v>0.398187450724303</v>
+        <v>0.36252916660435702</v>
       </c>
       <c r="N38" s="834">
         <f>IF(L38=0,"0",(D38/L38))</f>
-        <v>9.4781056630219247</v>
+        <v>9.9322795516783255</v>
       </c>
       <c r="O38" s="835"/>
     </row>
@@ -36257,7 +36934,7 @@
       </c>
       <c r="C39" s="802">
         <f>AVERAGE(C7:C37)</f>
-        <v>14.345454545454645</v>
+        <v>14.658333333333454</v>
       </c>
       <c r="D39" s="30"/>
       <c r="E39" s="30"/>
@@ -36877,27 +37554,27 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="C7:C37">
-    <cfRule type="cellIs" dxfId="53" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="100" priority="13" operator="greaterThan">
       <formula>24</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7:N37">
-    <cfRule type="cellIs" dxfId="52" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="99" priority="9" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="11" operator="between">
+    <cfRule type="cellIs" dxfId="98" priority="11" operator="between">
       <formula>0</formula>
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7:N38">
-    <cfRule type="cellIs" dxfId="50" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="97" priority="1" operator="lessThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="96" priority="2" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="95" priority="4" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36941,120 +37618,120 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="958"/>
-      <c r="B1" s="959"/>
-      <c r="C1" s="959"/>
-      <c r="D1" s="959"/>
-      <c r="E1" s="959"/>
-      <c r="F1" s="959"/>
-      <c r="G1" s="959"/>
-      <c r="H1" s="959"/>
-      <c r="I1" s="959"/>
-      <c r="J1" s="959"/>
-      <c r="K1" s="959"/>
-      <c r="L1" s="959"/>
-      <c r="M1" s="959"/>
-      <c r="N1" s="959"/>
-      <c r="O1" s="959"/>
-      <c r="P1" s="959"/>
-      <c r="Q1" s="959"/>
-      <c r="R1" s="959"/>
-      <c r="S1" s="959"/>
-      <c r="T1" s="959"/>
-      <c r="U1" s="959"/>
-      <c r="V1" s="959"/>
-      <c r="W1" s="959"/>
-      <c r="X1" s="959"/>
-      <c r="Y1" s="959"/>
-      <c r="Z1" s="959"/>
-      <c r="AA1" s="959"/>
+      <c r="A1" s="961"/>
+      <c r="B1" s="962"/>
+      <c r="C1" s="962"/>
+      <c r="D1" s="962"/>
+      <c r="E1" s="962"/>
+      <c r="F1" s="962"/>
+      <c r="G1" s="962"/>
+      <c r="H1" s="962"/>
+      <c r="I1" s="962"/>
+      <c r="J1" s="962"/>
+      <c r="K1" s="962"/>
+      <c r="L1" s="962"/>
+      <c r="M1" s="962"/>
+      <c r="N1" s="962"/>
+      <c r="O1" s="962"/>
+      <c r="P1" s="962"/>
+      <c r="Q1" s="962"/>
+      <c r="R1" s="962"/>
+      <c r="S1" s="962"/>
+      <c r="T1" s="962"/>
+      <c r="U1" s="962"/>
+      <c r="V1" s="962"/>
+      <c r="W1" s="962"/>
+      <c r="X1" s="962"/>
+      <c r="Y1" s="962"/>
+      <c r="Z1" s="962"/>
+      <c r="AA1" s="962"/>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C2" s="17"/>
     </row>
     <row r="3" spans="1:31" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="978" t="s">
+      <c r="B4" s="973" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="970" t="s">
+      <c r="C4" s="971" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="975" t="s">
+      <c r="D4" s="969" t="s">
         <v>106</v>
       </c>
-      <c r="E4" s="970" t="s">
+      <c r="E4" s="971" t="s">
         <v>107</v>
       </c>
-      <c r="F4" s="975" t="s">
+      <c r="F4" s="969" t="s">
         <v>239</v>
       </c>
-      <c r="G4" s="975" t="s">
+      <c r="G4" s="969" t="s">
         <v>108</v>
       </c>
-      <c r="H4" s="975" t="s">
+      <c r="H4" s="969" t="s">
         <v>161</v>
       </c>
-      <c r="I4" s="970" t="s">
+      <c r="I4" s="971" t="s">
         <v>207</v>
       </c>
-      <c r="J4" s="970" t="s">
+      <c r="J4" s="971" t="s">
         <v>109</v>
       </c>
-      <c r="K4" s="970" t="s">
+      <c r="K4" s="971" t="s">
         <v>174</v>
       </c>
-      <c r="L4" s="970" t="s">
+      <c r="L4" s="971" t="s">
         <v>173</v>
       </c>
-      <c r="M4" s="970" t="s">
+      <c r="M4" s="971" t="s">
         <v>103</v>
       </c>
       <c r="N4" s="48"/>
       <c r="O4" s="48"/>
       <c r="P4" s="48"/>
       <c r="Q4" s="48"/>
-      <c r="R4" s="975" t="s">
+      <c r="R4" s="969" t="s">
         <v>110</v>
       </c>
-      <c r="S4" s="975" t="s">
+      <c r="S4" s="969" t="s">
         <v>240</v>
       </c>
       <c r="T4" s="48"/>
-      <c r="U4" s="970" t="s">
+      <c r="U4" s="971" t="s">
         <v>153</v>
       </c>
       <c r="V4" s="48"/>
       <c r="W4" s="48"/>
-      <c r="X4" s="970" t="s">
+      <c r="X4" s="971" t="s">
         <v>175</v>
       </c>
-      <c r="Y4" s="970" t="s">
+      <c r="Y4" s="971" t="s">
         <v>176</v>
       </c>
-      <c r="Z4" s="968" t="s">
+      <c r="Z4" s="978" t="s">
         <v>247</v>
       </c>
-      <c r="AA4" s="972" t="s">
+      <c r="AA4" s="980" t="s">
         <v>243</v>
       </c>
-      <c r="AB4" s="966" t="s">
+      <c r="AB4" s="976" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:31" s="300" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="979"/>
-      <c r="C5" s="977"/>
-      <c r="D5" s="976"/>
-      <c r="E5" s="971"/>
-      <c r="F5" s="976"/>
-      <c r="G5" s="976"/>
-      <c r="H5" s="976"/>
-      <c r="I5" s="971"/>
-      <c r="J5" s="971"/>
-      <c r="K5" s="971"/>
-      <c r="L5" s="971"/>
-      <c r="M5" s="971"/>
+      <c r="B5" s="974"/>
+      <c r="C5" s="972"/>
+      <c r="D5" s="970"/>
+      <c r="E5" s="975"/>
+      <c r="F5" s="970"/>
+      <c r="G5" s="970"/>
+      <c r="H5" s="970"/>
+      <c r="I5" s="975"/>
+      <c r="J5" s="975"/>
+      <c r="K5" s="975"/>
+      <c r="L5" s="975"/>
+      <c r="M5" s="975"/>
       <c r="N5" s="50" t="s">
         <v>111</v>
       </c>
@@ -37067,23 +37744,23 @@
       <c r="Q5" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="R5" s="976"/>
-      <c r="S5" s="976"/>
+      <c r="R5" s="970"/>
+      <c r="S5" s="970"/>
       <c r="T5" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="U5" s="974"/>
+      <c r="U5" s="982"/>
       <c r="V5" s="80" t="s">
         <v>156</v>
       </c>
       <c r="W5" s="80" t="s">
         <v>157</v>
       </c>
-      <c r="X5" s="971"/>
-      <c r="Y5" s="971"/>
-      <c r="Z5" s="969"/>
-      <c r="AA5" s="973"/>
-      <c r="AB5" s="967"/>
+      <c r="X5" s="975"/>
+      <c r="Y5" s="975"/>
+      <c r="Z5" s="979"/>
+      <c r="AA5" s="981"/>
+      <c r="AB5" s="977"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="21" t="s">
@@ -38321,33 +38998,33 @@
         <f>IF('Entries October 2026'!W18-'Entries October 2026'!W17&lt;1,"0",'Entries October 2026'!W18-'Entries October 2026'!W17)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="693" t="str">
+      <c r="D18" s="693">
         <f>IF('Entries October 2026'!O18-'Entries October 2026'!O17&lt;1,"0",'Entries October 2026'!O18-'Entries October 2026'!O17)</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="693" t="str">
+        <v>144</v>
+      </c>
+      <c r="E18" s="693">
         <f>IF('Entries October 2026'!P18-'Entries October 2026'!P17&lt;1,"0",'Entries October 2026'!P18-'Entries October 2026'!P17)</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="693" t="str">
+        <v>237</v>
+      </c>
+      <c r="F18" s="693">
         <f>IF('Entries October 2026'!V18-'Entries October 2026'!V17&lt;1,"0",'Entries October 2026'!V18-'Entries October 2026'!V17)</f>
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="G18" s="693">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="H18" s="693">
         <f>IF('Entries October 2026'!Q18-'Entries October 2026'!Q17&lt;1,0,'Entries October 2026'!Q18-'Entries October 2026'!Q17)</f>
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="I18" s="693">
         <f>IF('Entries October 2026'!AG18-'Entries October 2026'!AG17&lt;1,0,'Entries October 2026'!AG18-'Entries October 2026'!AG17)</f>
         <v>0</v>
       </c>
-      <c r="J18" s="693" t="str">
+      <c r="J18" s="693">
         <f>IF('Entries October 2026'!S18-'Entries October 2026'!S17&lt;1,"0",'Entries October 2026'!S18-'Entries October 2026'!S17)</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="K18" s="693" t="str">
         <f>IF('Entries October 2026'!R18-'Entries October 2026'!R17&lt;1,"0",'Entries October 2026'!R18-'Entries October 2026'!R17)</f>
@@ -38357,25 +39034,25 @@
         <f>IF('Entries October 2026'!T18-'Entries October 2026'!T17&lt;1,"0",'Entries October 2026'!T18-'Entries October 2026'!T17)</f>
         <v>0</v>
       </c>
-      <c r="M18" s="693" t="str">
+      <c r="M18" s="693">
         <f>IF('Entries October 2026'!U18-'Entries October 2026'!U17&lt;1,"0",'Entries October 2026'!U18-'Entries October 2026'!U17)</f>
-        <v>0</v>
-      </c>
-      <c r="N18" s="693" t="str">
+        <v>5</v>
+      </c>
+      <c r="N18" s="693">
         <f>IF('Entries October 2026'!X18-'Entries October 2026'!X17&lt;1,"0",'Entries October 2026'!X18-'Entries October 2026'!X17)</f>
-        <v>0</v>
-      </c>
-      <c r="O18" s="693" t="str">
+        <v>29</v>
+      </c>
+      <c r="O18" s="693">
         <f>IF('Entries October 2026'!Y18-'Entries October 2026'!Y17&lt;1,"0",'Entries October 2026'!Y18-'Entries October 2026'!Y17)</f>
-        <v>0</v>
-      </c>
-      <c r="P18" s="693" t="str">
+        <v>119</v>
+      </c>
+      <c r="P18" s="693">
         <f>IF('Entries October 2026'!AC18-'Entries October 2026'!AC17&lt;1,"0",'Entries October 2026'!AC18-'Entries October 2026'!AC17)</f>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="693" t="str">
+        <v>23</v>
+      </c>
+      <c r="Q18" s="693">
         <f>IF('Entries October 2026'!Z18-'Entries October 2026'!Z17&lt;1,"0",'Entries October 2026'!Z18-'Entries October 2026'!Z17)</f>
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="R18" s="693" t="str">
         <f>IF(('Entries October 2026'!AA18-'Entries October 2026'!AA17)+('Entries October 2026'!AB18-'Entries October 2026'!AB17)&lt;1,"0",('Entries October 2026'!AA18-'Entries October 2026'!AA17)+('Entries October 2026'!AB18-'Entries October 2026'!AB17))</f>
@@ -38383,15 +39060,15 @@
       </c>
       <c r="S18" s="692">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1340</v>
       </c>
       <c r="T18" s="692">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U18" s="693" t="str">
+        <v>153</v>
+      </c>
+      <c r="U18" s="693">
         <f>IF('Entries October 2026'!AC18-'Entries October 2026'!AC17&lt;1,"0",'Entries October 2026'!AC18-'Entries October 2026'!AC17)</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V18" s="693" t="str">
         <f>IF('Entries October 2026'!AD18-'Entries October 2026'!AD17&lt;1,"0",'Entries October 2026'!AD18-'Entries October 2026'!AD17)</f>
@@ -38411,14 +39088,14 @@
       </c>
       <c r="Z18" s="329">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AA18" s="330" t="str">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="331" t="str">
+        <v>381</v>
+      </c>
+      <c r="AA18" s="330">
+        <v>237.13800000000001</v>
+      </c>
+      <c r="AB18" s="331">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>16.066594135060598</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.2">
@@ -40485,28 +41162,28 @@
       </c>
       <c r="D38" s="303">
         <f>SUM(D7:D37)</f>
-        <v>1700</v>
+        <v>1844</v>
       </c>
       <c r="E38" s="303">
         <f>SUM(E7:E37)</f>
-        <v>1309</v>
+        <v>1546</v>
       </c>
       <c r="F38" s="303">
         <f>SUM(F7:F37)</f>
-        <v>1433</v>
+        <v>1680</v>
       </c>
       <c r="G38" s="304">
         <f>SUM(G7:G37)</f>
-        <v>1576</v>
+        <v>1710</v>
       </c>
       <c r="H38" s="303">
         <f t="shared" si="5"/>
-        <v>1663</v>
+        <v>1832</v>
       </c>
       <c r="I38" s="303"/>
       <c r="J38" s="303">
         <f t="shared" si="5"/>
-        <v>1485</v>
+        <v>1557</v>
       </c>
       <c r="K38" s="303"/>
       <c r="L38" s="303">
@@ -40515,23 +41192,23 @@
       </c>
       <c r="M38" s="303">
         <f>SUM(M7:M37)</f>
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="N38" s="303">
         <f t="shared" si="5"/>
-        <v>343</v>
+        <v>372</v>
       </c>
       <c r="O38" s="303">
         <f t="shared" si="5"/>
-        <v>652</v>
+        <v>771</v>
       </c>
       <c r="P38" s="303">
         <f>SUM(P7:P37)</f>
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="Q38" s="303">
         <f>SUM(Q7:Q37)</f>
-        <v>153</v>
+        <v>224</v>
       </c>
       <c r="R38" s="303">
         <f>SUM(R7:R34)</f>
@@ -40539,15 +41216,15 @@
       </c>
       <c r="S38" s="304">
         <f>SUM(S7:S37)</f>
-        <v>15760</v>
+        <v>17100</v>
       </c>
       <c r="T38" s="304">
         <f>SUM(T7:T37)</f>
-        <v>1014</v>
+        <v>1167</v>
       </c>
       <c r="U38" s="303">
         <f>SUM(U7:U37)</f>
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="V38" s="303">
         <f>SUM(V7:V37)</f>
@@ -40558,22 +41235,22 @@
       <c r="Y38" s="303"/>
       <c r="Z38" s="332">
         <f>SUM(Z7:Z37)</f>
-        <v>3009</v>
+        <v>3390</v>
       </c>
       <c r="AA38" s="332">
         <f>SUM(AA7:AA37)</f>
-        <v>2410.9247999999998</v>
+        <v>2648.0627999999997</v>
       </c>
       <c r="AB38" s="331">
         <f>IF(AA38=0,"0",(Z38*10/AA38))</f>
-        <v>12.480687908639872</v>
+        <v>12.801811195716358</v>
       </c>
       <c r="AC38" s="321">
         <v>10.199999999999999</v>
       </c>
       <c r="AD38" s="340">
         <f>AB38/AC38*100</f>
-        <v>122.35968537882229</v>
+        <v>125.50795289917997</v>
       </c>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.2">
@@ -40612,7 +41289,7 @@
       <c r="C40" s="15"/>
       <c r="D40" s="15">
         <f>D38*220</f>
-        <v>374000</v>
+        <v>405680</v>
       </c>
       <c r="E40" s="15"/>
       <c r="F40" s="15"/>
@@ -40704,7 +41381,7 @@
       <c r="C43" s="17"/>
       <c r="D43" s="17">
         <f>+D41*D40</f>
-        <v>5912.9400000000005</v>
+        <v>6413.8008000000009</v>
       </c>
       <c r="E43" s="17"/>
       <c r="F43" s="36"/>
@@ -40757,7 +41434,7 @@
     <row r="45" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D45" s="17">
         <f>SUM(D43:D44)</f>
-        <v>6191.9100000000008</v>
+        <v>6692.7708000000011</v>
       </c>
       <c r="E45" s="17"/>
       <c r="F45" s="36"/>
@@ -40779,7 +41456,7 @@
       </c>
       <c r="D47" s="23">
         <f>+D45*2/3</f>
-        <v>4127.9400000000005</v>
+        <v>4461.8472000000011</v>
       </c>
       <c r="E47" s="324"/>
       <c r="F47" s="36"/>
@@ -40802,7 +41479,7 @@
       <c r="C49" s="24"/>
       <c r="D49" s="28">
         <f>SUM(D47,D45)</f>
-        <v>10319.850000000002</v>
+        <v>11154.618000000002</v>
       </c>
       <c r="E49" s="325"/>
       <c r="F49" s="36"/>
@@ -41167,16 +41844,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:AA1"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="R4:R5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="E4:E5"/>
     <mergeCell ref="AB4:AB5"/>
     <mergeCell ref="Z4:Z5"/>
     <mergeCell ref="L4:L5"/>
@@ -41188,13 +41855,23 @@
     <mergeCell ref="Y4:Y5"/>
     <mergeCell ref="S4:S5"/>
     <mergeCell ref="M4:M5"/>
+    <mergeCell ref="A1:AA1"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="R4:R5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="E4:E5"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="AB6:AB38">
-    <cfRule type="cellIs" dxfId="47" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="94" priority="1" operator="lessThan">
       <formula>10.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="93" priority="2" operator="greaterThan">
       <formula>10.2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -41225,15 +41902,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="980" t="s">
+      <c r="A1" s="983" t="s">
         <v>303</v>
       </c>
-      <c r="B1" s="981"/>
-      <c r="C1" s="981"/>
-      <c r="D1" s="982"/>
-      <c r="E1" s="981"/>
-      <c r="F1" s="981"/>
-      <c r="G1" s="983"/>
+      <c r="B1" s="984"/>
+      <c r="C1" s="984"/>
+      <c r="D1" s="985"/>
+      <c r="E1" s="984"/>
+      <c r="F1" s="984"/>
+      <c r="G1" s="986"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B2" s="9"/>
@@ -41246,7 +41923,7 @@
       <c r="D3" s="359"/>
     </row>
     <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="994" t="s">
+      <c r="A4" s="997" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="39" t="s">
@@ -41258,19 +41935,19 @@
       <c r="D4" s="361" t="s">
         <v>285</v>
       </c>
-      <c r="E4" s="984" t="s">
+      <c r="E4" s="987" t="s">
         <v>245</v>
       </c>
-      <c r="F4" s="987" t="s">
+      <c r="F4" s="990" t="s">
         <v>243</v>
       </c>
-      <c r="G4" s="990" t="s">
+      <c r="G4" s="993" t="s">
         <v>253</v>
       </c>
-      <c r="H4" s="993"/>
+      <c r="H4" s="996"/>
     </row>
     <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="995"/>
+      <c r="A5" s="998"/>
       <c r="B5" s="34" t="s">
         <v>48</v>
       </c>
@@ -41280,20 +41957,20 @@
       <c r="D5" s="361" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="985"/>
-      <c r="F5" s="988"/>
-      <c r="G5" s="991"/>
-      <c r="H5" s="993"/>
+      <c r="E5" s="988"/>
+      <c r="F5" s="991"/>
+      <c r="G5" s="994"/>
+      <c r="H5" s="996"/>
     </row>
     <row r="6" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="996"/>
+      <c r="A6" s="999"/>
       <c r="B6" s="40"/>
       <c r="C6" s="362"/>
       <c r="D6" s="361"/>
-      <c r="E6" s="986"/>
-      <c r="F6" s="989"/>
-      <c r="G6" s="992"/>
-      <c r="H6" s="993"/>
+      <c r="E6" s="989"/>
+      <c r="F6" s="992"/>
+      <c r="G6" s="995"/>
+      <c r="H6" s="996"/>
     </row>
     <row r="7" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A7" s="686">
@@ -41633,27 +42310,26 @@
       </c>
       <c r="B18" s="761">
         <f>'Utility Analysis October 2026'!D21</f>
-        <v>0</v>
-      </c>
-      <c r="C18" s="762" t="str">
+        <v>8829</v>
+      </c>
+      <c r="C18" s="762">
         <f>'Utility Analysis October 2026'!G21</f>
         <v>0</v>
       </c>
       <c r="D18" s="763">
-        <f>'Utility Analysis October 2026'!E21</f>
-        <v>0</v>
+        <v>1281.3</v>
       </c>
       <c r="E18" s="764">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F18" s="765" t="str">
+        <v>10110.299999999999</v>
+      </c>
+      <c r="F18" s="765">
         <f>'PROD.FIG. '!H16</f>
-        <v>0</v>
-      </c>
-      <c r="G18" s="456" t="str">
+        <v>237.13800000000001</v>
+      </c>
+      <c r="G18" s="456">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>42.634668420919461</v>
       </c>
       <c r="J18" s="30"/>
     </row>
@@ -41665,7 +42341,7 @@
         <f>'Utility Analysis October 2026'!D22</f>
         <v>0</v>
       </c>
-      <c r="C19" s="762">
+      <c r="C19" s="762" t="str">
         <f>'Utility Analysis October 2026'!G22</f>
         <v>0</v>
       </c>
@@ -42230,7 +42906,7 @@
       </c>
       <c r="B38" s="308">
         <f>SUM(B7:B37)</f>
-        <v>62240</v>
+        <v>71069</v>
       </c>
       <c r="C38" s="308">
         <f>SUM(C7:C37)</f>
@@ -42238,26 +42914,26 @@
       </c>
       <c r="D38" s="308">
         <f>SUM(D7:D37)</f>
-        <v>13512.199999999999</v>
+        <v>14793.499999999998</v>
       </c>
       <c r="E38" s="337">
         <f>SUM(E7:E37)</f>
-        <v>75752.199999999983</v>
+        <v>85862.499999999985</v>
       </c>
       <c r="F38" s="358">
         <f>SUM(F7:F37)</f>
-        <v>2410.9247999999998</v>
+        <v>2648.0627999999997</v>
       </c>
       <c r="G38" s="338">
         <f>IF(F38=0,"0",(E38/F38))</f>
-        <v>31.420391046622438</v>
+        <v>32.424646424548541</v>
       </c>
       <c r="H38" s="335">
         <v>22</v>
       </c>
       <c r="I38" s="340">
         <f>G38/H38*100</f>
-        <v>142.81995930282926</v>
+        <v>147.38475647522066</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
@@ -42298,12 +42974,12 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="cellIs" dxfId="45" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="92" priority="1" operator="lessThan">
       <formula>22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7:G38">
-    <cfRule type="cellIs" dxfId="44" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="91" priority="2" operator="greaterThan">
       <formula>21</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42334,16 +43010,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="997" t="s">
+      <c r="A1" s="1000" t="s">
         <v>302</v>
       </c>
-      <c r="B1" s="959"/>
-      <c r="C1" s="959"/>
-      <c r="D1" s="959"/>
-      <c r="E1" s="959"/>
-      <c r="F1" s="959"/>
-      <c r="G1" s="959"/>
-      <c r="H1" s="959"/>
+      <c r="B1" s="962"/>
+      <c r="C1" s="962"/>
+      <c r="D1" s="962"/>
+      <c r="E1" s="962"/>
+      <c r="F1" s="962"/>
+      <c r="G1" s="962"/>
+      <c r="H1" s="962"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D2" s="12"/>
@@ -42595,8 +43271,8 @@
       <c r="E16" s="809"/>
       <c r="F16" s="756"/>
       <c r="G16" s="756"/>
-      <c r="H16" s="808" t="str">
-        <v>0</v>
+      <c r="H16" s="808">
+        <v>237.13800000000001</v>
       </c>
       <c r="I16" s="298"/>
       <c r="J16" s="299"/>
@@ -42956,7 +43632,7 @@
       </c>
       <c r="H36" s="736">
         <f>SUM(H5:H35)</f>
-        <v>2410.9247999999998</v>
+        <v>2648.0627999999997</v>
       </c>
       <c r="I36" s="298"/>
       <c r="J36" s="299"/>
@@ -43072,11 +43748,11 @@
       <c r="D3" s="85"/>
       <c r="E3" s="85"/>
       <c r="F3" s="1"/>
-      <c r="I3" s="1010" t="s">
+      <c r="I3" s="1005" t="s">
         <v>267</v>
       </c>
-      <c r="J3" s="1011"/>
-      <c r="K3" s="1012"/>
+      <c r="J3" s="1006"/>
+      <c r="K3" s="1007"/>
     </row>
     <row r="4" spans="1:24" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
@@ -43089,46 +43765,46 @@
         <v>250</v>
       </c>
       <c r="H4" s="347"/>
-      <c r="I4" s="1013" t="s">
+      <c r="I4" s="1008" t="s">
         <v>262</v>
       </c>
-      <c r="J4" s="1014"/>
-      <c r="K4" s="1015"/>
+      <c r="J4" s="1009"/>
+      <c r="K4" s="1010"/>
       <c r="M4" s="417"/>
       <c r="N4" s="417"/>
       <c r="O4" s="418"/>
       <c r="P4" s="418"/>
-      <c r="Q4" s="1025" t="s">
+      <c r="Q4" s="1020" t="s">
         <v>283</v>
       </c>
-      <c r="R4" s="1025"/>
-      <c r="S4" s="1025"/>
-      <c r="T4" s="1025"/>
+      <c r="R4" s="1020"/>
+      <c r="S4" s="1020"/>
+      <c r="T4" s="1020"/>
       <c r="U4" s="191"/>
       <c r="V4" s="417"/>
       <c r="W4" s="191"/>
       <c r="X4" s="191"/>
     </row>
     <row r="5" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="946" t="s">
+      <c r="A5" s="949" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="948" t="s">
+      <c r="B5" s="951" t="s">
         <v>251</v>
       </c>
-      <c r="C5" s="948" t="s">
+      <c r="C5" s="951" t="s">
         <v>282</v>
       </c>
-      <c r="D5" s="1004" t="s">
+      <c r="D5" s="1027" t="s">
         <v>279</v>
       </c>
-      <c r="E5" s="1004" t="s">
+      <c r="E5" s="1027" t="s">
         <v>280</v>
       </c>
-      <c r="F5" s="1002" t="s">
+      <c r="F5" s="1025" t="s">
         <v>243</v>
       </c>
-      <c r="G5" s="999" t="s">
+      <c r="G5" s="1022" t="s">
         <v>249</v>
       </c>
       <c r="I5" s="419" t="s">
@@ -43140,43 +43816,43 @@
       <c r="K5" s="421" t="s">
         <v>265</v>
       </c>
-      <c r="M5" s="1016" t="s">
+      <c r="M5" s="1011" t="s">
         <v>266</v>
       </c>
-      <c r="N5" s="1017"/>
-      <c r="O5" s="1018"/>
+      <c r="N5" s="1012"/>
+      <c r="O5" s="1013"/>
       <c r="P5" s="422"/>
-      <c r="Q5" s="1019" t="s">
+      <c r="Q5" s="1014" t="s">
         <v>7</v>
       </c>
-      <c r="R5" s="1021" t="s">
+      <c r="R5" s="1016" t="s">
         <v>267</v>
       </c>
-      <c r="S5" s="1022"/>
+      <c r="S5" s="1017"/>
       <c r="T5" s="452" t="s">
         <v>268</v>
       </c>
       <c r="U5" s="423" t="s">
         <v>269</v>
       </c>
-      <c r="V5" s="1023" t="s">
+      <c r="V5" s="1018" t="s">
         <v>277</v>
       </c>
-      <c r="W5" s="1006" t="s">
+      <c r="W5" s="1001" t="s">
         <v>270</v>
       </c>
-      <c r="X5" s="1008" t="s">
+      <c r="X5" s="1003" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="998"/>
-      <c r="B6" s="1001"/>
-      <c r="C6" s="1001"/>
-      <c r="D6" s="1005"/>
-      <c r="E6" s="1005"/>
-      <c r="F6" s="1003"/>
-      <c r="G6" s="1000"/>
+      <c r="A6" s="1021"/>
+      <c r="B6" s="1024"/>
+      <c r="C6" s="1024"/>
+      <c r="D6" s="1028"/>
+      <c r="E6" s="1028"/>
+      <c r="F6" s="1026"/>
+      <c r="G6" s="1023"/>
       <c r="I6" s="424">
         <v>10</v>
       </c>
@@ -43195,7 +43871,7 @@
         <v>273</v>
       </c>
       <c r="P6" s="418"/>
-      <c r="Q6" s="1020"/>
+      <c r="Q6" s="1015"/>
       <c r="R6" s="448" t="s">
         <v>274</v>
       </c>
@@ -43208,9 +43884,9 @@
       <c r="U6" s="429" t="s">
         <v>275</v>
       </c>
-      <c r="V6" s="1024"/>
-      <c r="W6" s="1007"/>
-      <c r="X6" s="1009"/>
+      <c r="V6" s="1019"/>
+      <c r="W6" s="1002"/>
+      <c r="X6" s="1004"/>
     </row>
     <row r="7" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="715">
@@ -43972,7 +44648,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="716">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F17" s="717">
         <v>0</v>
@@ -44032,27 +44708,27 @@
       <c r="A18" s="767">
         <v>12</v>
       </c>
-      <c r="B18" s="768" t="str">
+      <c r="B18" s="768">
         <f>IF('Entries October 2026'!N18-'Entries October 2026'!N17&lt;1,"0",'Entries October 2026'!N18-'Entries October 2026'!N17)</f>
-        <v>0</v>
-      </c>
-      <c r="C18" s="768" t="str">
+        <v>244.5399999999936</v>
+      </c>
+      <c r="C18" s="768">
         <f>IF('Entries October 2026'!L18-'Entries October 2026'!L17&lt;1,"0",'Entries October 2026'!L18-'Entries October 2026'!L17)</f>
-        <v>0</v>
-      </c>
-      <c r="D18" s="768" t="str">
+        <v>591.47999999999593</v>
+      </c>
+      <c r="D18" s="768">
         <f>IF('Entries October 2026'!M18-'Entries October 2026'!M17&lt;1,"0",'Entries October 2026'!M18-'Entries October 2026'!M17)</f>
-        <v>0</v>
+        <v>1256.1700000000419</v>
       </c>
       <c r="E18" s="768">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="F18" s="769">
-        <v>0</v>
-      </c>
-      <c r="G18" s="336" t="str">
+        <v>237.13800000000001</v>
+      </c>
+      <c r="G18" s="336">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5.48203999359023</v>
       </c>
       <c r="I18" s="430">
         <v>130</v>
@@ -45497,27 +46173,27 @@
       </c>
       <c r="B38" s="713">
         <f>SUM(B7:B37)</f>
-        <v>1350.3500000000058</v>
+        <v>1594.8899999999994</v>
       </c>
       <c r="C38" s="713">
         <f>SUM(C7:C37)</f>
-        <v>3764.1000000000058</v>
+        <v>4355.5800000000017</v>
       </c>
       <c r="D38" s="713">
         <f>SUM(D7:D37)</f>
-        <v>10888.429999999935</v>
+        <v>12144.599999999977</v>
       </c>
       <c r="E38" s="713">
         <f>SUM(E7:E37)</f>
-        <v>12800</v>
+        <v>14400</v>
       </c>
       <c r="F38" s="714">
         <f>SUM(F7:F37)</f>
-        <v>2410.9247999999998</v>
+        <v>2648.0627999999997</v>
       </c>
       <c r="G38" s="345">
         <f>IF(F38=0,"0",(E38/F38))</f>
-        <v>5.3091660096573738</v>
+        <v>5.4379374990653551</v>
       </c>
       <c r="H38" s="348">
         <v>5</v>
@@ -45679,6 +46355,13 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="C5:C6"/>
     <mergeCell ref="W5:W6"/>
     <mergeCell ref="X5:X6"/>
     <mergeCell ref="I3:K3"/>
@@ -45688,20 +46371,13 @@
     <mergeCell ref="R5:S5"/>
     <mergeCell ref="V5:V6"/>
     <mergeCell ref="Q4:T4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="C5:C6"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="G7:G38">
-    <cfRule type="cellIs" dxfId="43" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="90" priority="1" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="89" priority="3" operator="greaterThan">
       <formula>21</formula>
     </cfRule>
   </conditionalFormatting>
@@ -45995,7 +46671,7 @@
         <v>31</v>
       </c>
       <c r="AG6" s="293"/>
-      <c r="AH6" s="898" t="s">
+      <c r="AH6" s="901" t="s">
         <v>216</v>
       </c>
       <c r="AI6" s="291"/>
@@ -46100,7 +46776,7 @@
       <c r="AG7" s="212" t="s">
         <v>19</v>
       </c>
-      <c r="AH7" s="898"/>
+      <c r="AH7" s="901"/>
       <c r="AI7" s="292" t="s">
         <v>229</v>
       </c>
@@ -46154,7 +46830,7 @@
       </c>
       <c r="M8" s="99">
         <f>'Daily KPIs'!M8</f>
-        <v>0</v>
+        <v>3593</v>
       </c>
       <c r="N8" s="99">
         <f>'Daily KPIs'!N8</f>
@@ -46228,14 +46904,14 @@
       </c>
       <c r="AG8" s="213">
         <f>SUM($B8:AF8)</f>
-        <v>30960</v>
+        <v>34553</v>
       </c>
       <c r="AH8" s="293">
         <v>96325</v>
       </c>
       <c r="AI8" s="294">
         <f>AG8-AH8</f>
-        <v>-65365</v>
+        <v>-61772</v>
       </c>
       <c r="AJ8" s="266"/>
       <c r="AK8" s="266"/>
@@ -46290,7 +46966,7 @@
       </c>
       <c r="M9" s="99">
         <f>'Daily KPIs'!M9</f>
-        <v>0</v>
+        <v>237.13800000000001</v>
       </c>
       <c r="N9" s="99">
         <f>'Daily KPIs'!N9</f>
@@ -46364,7 +47040,7 @@
       </c>
       <c r="AG9" s="215">
         <f>SUM($B9:AF9)</f>
-        <v>2410.9247999999998</v>
+        <v>2648.0627999999997</v>
       </c>
       <c r="AH9" s="214"/>
       <c r="AI9" s="265"/>
@@ -46417,9 +47093,9 @@
         <f>'Daily KPIs'!L10</f>
         <v>0</v>
       </c>
-      <c r="M10" s="163">
+      <c r="M10" s="163" t="str">
         <f>'Daily KPIs'!M10</f>
-        <v>0</v>
+        <v>Rose/CBfl</v>
       </c>
       <c r="N10" s="163">
         <f>'Daily KPIs'!N10</f>
@@ -46465,11 +47141,11 @@
         <f>'Daily KPIs'!X10</f>
         <v>0</v>
       </c>
-      <c r="Y10" s="1026">
+      <c r="Y10" s="1029">
         <f>'Daily KPIs'!Y10</f>
         <v>0</v>
       </c>
-      <c r="Z10" s="1026"/>
+      <c r="Z10" s="1029"/>
       <c r="AA10" s="163">
         <f>'Daily KPIs'!AA10</f>
         <v>0</v>
@@ -46864,9 +47540,9 @@
         <f>+'Water '!$D17</f>
         <v>0</v>
       </c>
-      <c r="M16" s="111" t="str">
+      <c r="M16" s="111">
         <f>+'Water '!$D18</f>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="N16" s="110" t="str">
         <f>+'Water '!$D19</f>
@@ -46946,7 +47622,7 @@
       </c>
       <c r="AG16" s="220">
         <f>SUM($B16:AF16)</f>
-        <v>1700</v>
+        <v>1844</v>
       </c>
       <c r="AH16" s="221"/>
     </row>
@@ -46998,9 +47674,9 @@
         <f>+'Water '!$E17</f>
         <v>3</v>
       </c>
-      <c r="M17" s="115" t="str">
+      <c r="M17" s="115">
         <f>+'Water '!$E18</f>
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="N17" s="112" t="str">
         <f>+'Water '!$E19</f>
@@ -47080,7 +47756,7 @@
       </c>
       <c r="AG17" s="222">
         <f>SUM($B17:AF17)</f>
-        <v>1309</v>
+        <v>1546</v>
       </c>
       <c r="AH17" s="223"/>
       <c r="AI17" s="268"/>
@@ -47135,7 +47811,7 @@
       </c>
       <c r="M18" s="118">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="N18" s="175">
         <f t="shared" si="0"/>
@@ -47215,7 +47891,7 @@
       </c>
       <c r="AG18" s="224">
         <f>SUM($B18:AF18)</f>
-        <v>3009</v>
+        <v>3390</v>
       </c>
       <c r="AH18" s="224"/>
       <c r="AI18" s="269"/>
@@ -47349,7 +48025,7 @@
       </c>
       <c r="M21" s="119">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>180.31</v>
       </c>
       <c r="N21" s="119">
         <f>0.73*(N96+N15)</f>
@@ -47429,16 +48105,16 @@
       </c>
       <c r="AG21" s="220">
         <f>SUM($B21:AF21)</f>
-        <v>1046.0900000000001</v>
+        <v>1226.4000000000001</v>
       </c>
       <c r="AH21" s="225">
         <f>AG24+AG37+AG28</f>
-        <v>3301</v>
+        <v>3613</v>
       </c>
       <c r="AI21" s="271"/>
       <c r="AJ21" s="272">
         <f>(AH21*10)/AG9</f>
-        <v>13.69184140459296</v>
+        <v>13.643936238974394</v>
       </c>
     </row>
     <row r="22" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -47666,7 +48342,7 @@
       </c>
       <c r="M24" s="123">
         <f>'Water '!H18</f>
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="N24" s="112">
         <f>'Water '!H19</f>
@@ -47746,7 +48422,7 @@
       </c>
       <c r="AG24" s="222">
         <f>SUM($B24:AF24)</f>
-        <v>1663</v>
+        <v>1832</v>
       </c>
       <c r="AH24" s="222"/>
       <c r="AI24" s="222"/>
@@ -47801,7 +48477,7 @@
       </c>
       <c r="M25" s="118">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="N25" s="118">
         <f t="shared" si="2"/>
@@ -47881,7 +48557,7 @@
       </c>
       <c r="AG25" s="224">
         <f>SUM($B25:AF25)</f>
-        <v>1663</v>
+        <v>1832</v>
       </c>
       <c r="AH25" s="224"/>
       <c r="AI25" s="269"/>
@@ -47934,9 +48610,9 @@
         <f>IF(L$9=0,"",+(L25*10)/L$9)</f>
         <v/>
       </c>
-      <c r="M26" s="125" t="str">
+      <c r="M26" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>7.1266519916672992</v>
       </c>
       <c r="N26" s="125" t="str">
         <f t="shared" si="3"/>
@@ -48108,9 +48784,9 @@
         <f>+'Water '!$J17</f>
         <v>18</v>
       </c>
-      <c r="M28" s="111" t="str">
+      <c r="M28" s="111">
         <f>+'Water '!$J18</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="N28" s="127" t="str">
         <f>+'Water '!$J19</f>
@@ -48190,7 +48866,7 @@
       </c>
       <c r="AG28" s="220">
         <f>SUM($B28:AF28)</f>
-        <v>1485</v>
+        <v>1557</v>
       </c>
       <c r="AH28" s="220"/>
       <c r="AI28" s="271"/>
@@ -48687,9 +49363,9 @@
         <f>+'Water '!$N17</f>
         <v>0</v>
       </c>
-      <c r="M33" s="131" t="str">
+      <c r="M33" s="131">
         <f>+'Water '!$N18</f>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="N33" s="131" t="str">
         <f>+'Water '!$N19</f>
@@ -48769,7 +49445,7 @@
       </c>
       <c r="AG33" s="227">
         <f>SUM($B33:AF33)</f>
-        <v>343</v>
+        <v>372</v>
       </c>
       <c r="AH33" s="227"/>
       <c r="AI33" s="227"/>
@@ -48826,9 +49502,9 @@
         <f>+'Water '!$O17</f>
         <v>0</v>
       </c>
-      <c r="M34" s="134" t="str">
+      <c r="M34" s="134">
         <f>+'Water '!$O18</f>
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="N34" s="134" t="str">
         <f>+'Water '!$O19</f>
@@ -48908,7 +49584,7 @@
       </c>
       <c r="AG34" s="228">
         <f>SUM($B34:AF34)</f>
-        <v>652</v>
+        <v>771</v>
       </c>
       <c r="AH34" s="228"/>
       <c r="AI34" s="228"/>
@@ -48963,7 +49639,7 @@
       </c>
       <c r="M35" s="119">
         <f>IF('Entries October 2026'!AC18-'Entries October 2026'!AC17&lt;1,0,'Entries October 2026'!AC18-'Entries October 2026'!AC17)</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="N35" s="95">
         <f>IF('Entries October 2026'!AC19-'Entries October 2026'!AC18&lt;1,0,'Entries October 2026'!AC19-'Entries October 2026'!AC18)</f>
@@ -49043,7 +49719,7 @@
       </c>
       <c r="AG35" s="220">
         <f>SUM($B35:AF35)</f>
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="AH35" s="220"/>
       <c r="AI35" s="271"/>
@@ -49096,9 +49772,9 @@
         <f>+'Water '!$M17</f>
         <v>0</v>
       </c>
-      <c r="M36" s="110" t="str">
+      <c r="M36" s="110">
         <f>+'Water '!$M18</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N36" s="110" t="str">
         <f>+'Water '!$M19</f>
@@ -49178,7 +49854,7 @@
       </c>
       <c r="AG36" s="220">
         <f>SUM($B36:AF36)</f>
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AH36" s="220"/>
       <c r="AI36" s="271"/>
@@ -49231,9 +49907,9 @@
         <f>+'Water '!$Q17</f>
         <v>9</v>
       </c>
-      <c r="M37" s="131" t="str">
+      <c r="M37" s="131">
         <f>+'Water '!$Q18</f>
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="N37" s="131" t="str">
         <f>+'Water '!$Q19</f>
@@ -49313,7 +49989,7 @@
       </c>
       <c r="AG37" s="227">
         <f>SUM($B37:AF37)</f>
-        <v>153</v>
+        <v>224</v>
       </c>
       <c r="AH37" s="227"/>
       <c r="AI37" s="227"/>
@@ -49721,7 +50397,7 @@
       </c>
       <c r="M42" s="138">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="N42" s="138">
         <f>SUM(N28:N41)</f>
@@ -49801,7 +50477,7 @@
       </c>
       <c r="AG42" s="230">
         <f>SUM($B42:AF42)</f>
-        <v>2929</v>
+        <v>3248</v>
       </c>
       <c r="AH42" s="230"/>
       <c r="AI42" s="276"/>
@@ -50004,7 +50680,7 @@
       </c>
       <c r="M47" s="178">
         <f>IF('Entries October 2026'!M18-'Entries October 2026'!M17&lt;1,0,'Entries October 2026'!M18-'Entries October 2026'!M17)</f>
-        <v>0</v>
+        <v>1256.1700000000419</v>
       </c>
       <c r="N47" s="178">
         <f>IF('Entries October 2026'!M19-'Entries October 2026'!M18&lt;1,0,'Entries October 2026'!M19-'Entries October 2026'!M18)</f>
@@ -50176,9 +50852,9 @@
         <f>'Daily KPIs'!L76</f>
         <v>0</v>
       </c>
-      <c r="M49" s="187" t="str">
+      <c r="M49" s="187">
         <f>'Daily KPIs'!M76</f>
-        <v>0</v>
+        <v>244.5399999999936</v>
       </c>
       <c r="N49" s="187" t="str">
         <f>'Daily KPIs'!N76</f>
@@ -50258,7 +50934,7 @@
       </c>
       <c r="AG49" s="235">
         <f>SUM($B49:AF49)</f>
-        <v>1350.3500000000058</v>
+        <v>1594.8899999999994</v>
       </c>
       <c r="AH49" s="236"/>
       <c r="AI49" s="280"/>
@@ -50387,7 +51063,7 @@
       </c>
       <c r="M52" s="141">
         <f>'Elec.OCTOBER 2026'!$B$18</f>
-        <v>0</v>
+        <v>8829</v>
       </c>
       <c r="N52" s="141">
         <f>'Elec.OCTOBER 2026'!$B$19</f>
@@ -50467,7 +51143,7 @@
       </c>
       <c r="AG52" s="224">
         <f>SUM(B52:AC52)</f>
-        <v>62240</v>
+        <v>71069</v>
       </c>
       <c r="AH52" s="224"/>
       <c r="AI52" s="276"/>
@@ -50913,9 +51589,9 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="M59" s="144" t="str">
+      <c r="M59" s="144">
         <f t="shared" si="6"/>
-        <v/>
+        <v>16.066594135060598</v>
       </c>
       <c r="N59" s="144" t="str">
         <f t="shared" si="6"/>
@@ -50995,7 +51671,7 @@
       </c>
       <c r="AG59" s="238">
         <f>IF(AG$9=0,"",+(AG18*10)/AG$9)</f>
-        <v>12.480687908639872</v>
+        <v>12.801811195716358</v>
       </c>
       <c r="AH59" s="239">
         <f>'Daily KPIs'!AI90</f>
@@ -51003,7 +51679,7 @@
       </c>
       <c r="AI59" s="282">
         <f>+AH59-AG59</f>
-        <v>-2.280687908639873</v>
+        <v>-2.6018111957163583</v>
       </c>
       <c r="AJ59" s="270"/>
       <c r="AK59" s="270"/>
@@ -51078,9 +51754,9 @@
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="M62" s="145" t="str">
+      <c r="M62" s="145">
         <f t="shared" ref="M62:S62" si="9">IF(M$9=0,"",+(M28*10)/M$9)</f>
-        <v/>
+        <v>3.0362067656807428</v>
       </c>
       <c r="N62" s="145" t="str">
         <f t="shared" si="9"/>
@@ -51160,14 +51836,14 @@
       </c>
       <c r="AG62" s="241">
         <f>IF(+(AG28*10)/AG$9&lt;1,0,+(AG28*10)/AG$9)</f>
-        <v>6.1594621283915618</v>
+        <v>5.8797699208644154</v>
       </c>
       <c r="AH62" s="241">
         <v>2.5</v>
       </c>
       <c r="AI62" s="242">
         <f t="shared" ref="AI62:AI78" si="11">AH62-AG62</f>
-        <v>-3.6594621283915618</v>
+        <v>-3.3797699208644154</v>
       </c>
     </row>
     <row r="63" spans="1:37" ht="18.75" x14ac:dyDescent="0.3">
@@ -51300,14 +51976,14 @@
       </c>
       <c r="AG63" s="243">
         <f>IF(+(AG28*10)/AG$93&lt;1,0,+(AG28*10)/AG$93)</f>
-        <v>5.508160237388724</v>
+        <v>5.775222551928783</v>
       </c>
       <c r="AH63" s="243">
         <v>2.5</v>
       </c>
       <c r="AI63" s="244">
         <f t="shared" si="11"/>
-        <v>-3.008160237388724</v>
+        <v>-3.275222551928783</v>
       </c>
     </row>
     <row r="64" spans="1:37" s="90" customFormat="1" ht="18" x14ac:dyDescent="0.25">
@@ -51358,9 +52034,9 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="M64" s="147" t="str">
+      <c r="M64" s="147">
         <f>IF(M$9=0,"",+(M29*10)/M$9)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N64" s="147" t="str">
         <f t="shared" si="14"/>
@@ -51546,9 +52222,9 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="M66" s="145" t="str">
+      <c r="M66" s="145">
         <f t="shared" si="16"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N66" s="145" t="str">
         <f t="shared" si="16"/>
@@ -51658,9 +52334,9 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="M67" s="150" t="str">
+      <c r="M67" s="150">
         <f t="shared" si="18"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N67" s="150" t="str">
         <f t="shared" si="18"/>
@@ -51800,9 +52476,9 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="M68" s="145" t="str">
+      <c r="M68" s="145">
         <f t="shared" si="20"/>
-        <v/>
+        <v>1.2229166139547436</v>
       </c>
       <c r="N68" s="145" t="str">
         <f t="shared" si="20"/>
@@ -51882,14 +52558,14 @@
       </c>
       <c r="AG68" s="241">
         <f>+(AG33*10)/AG$9</f>
-        <v>1.4226905791503743</v>
+        <v>1.4048005205918834</v>
       </c>
       <c r="AH68" s="241">
         <v>0.7</v>
       </c>
       <c r="AI68" s="242">
         <f t="shared" si="11"/>
-        <v>-0.72269057915037438</v>
+        <v>-0.70480052059188347</v>
       </c>
     </row>
     <row r="69" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -51940,9 +52616,9 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="M69" s="145" t="str">
+      <c r="M69" s="145">
         <f t="shared" si="22"/>
-        <v/>
+        <v>5.0181750710556718</v>
       </c>
       <c r="N69" s="145" t="str">
         <f t="shared" si="22"/>
@@ -52022,14 +52698,14 @@
       </c>
       <c r="AG69" s="241">
         <f>+(AG34*10)/AG$9</f>
-        <v>2.7043564361692245</v>
+        <v>2.911562369291242</v>
       </c>
       <c r="AH69" s="241">
         <v>2.6</v>
       </c>
       <c r="AI69" s="242">
         <f t="shared" si="11"/>
-        <v>-0.10435643616922441</v>
+        <v>-0.31156236929124193</v>
       </c>
     </row>
     <row r="70" spans="1:37" ht="18.75" x14ac:dyDescent="0.3">
@@ -52217,9 +52893,9 @@
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="M71" s="145" t="str">
+      <c r="M71" s="145">
         <f t="shared" si="26"/>
-        <v/>
+        <v>0.96989938348134841</v>
       </c>
       <c r="N71" s="145" t="str">
         <f t="shared" si="26"/>
@@ -52299,14 +52975,14 @@
       </c>
       <c r="AG71" s="241">
         <f>+(AG35*10)/AG$9</f>
-        <v>0.47699538368015465</v>
+        <v>0.52113567699376317</v>
       </c>
       <c r="AH71" s="241">
         <v>0.7</v>
       </c>
       <c r="AI71" s="242">
         <f>AH71-AG71</f>
-        <v>0.22300461631984531</v>
+        <v>0.17886432300623678</v>
       </c>
     </row>
     <row r="72" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -52357,9 +53033,9 @@
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="M72" s="145" t="str">
+      <c r="M72" s="145">
         <f t="shared" si="29"/>
-        <v/>
+        <v>0.21084769206116269</v>
       </c>
       <c r="N72" s="145" t="str">
         <f t="shared" si="29"/>
@@ -52439,14 +53115,14 @@
       </c>
       <c r="AG72" s="241">
         <f>+(AG36*10)/AG$9</f>
-        <v>7.8807932955851631E-2</v>
+        <v>9.0632291651089256E-2</v>
       </c>
       <c r="AH72" s="241">
         <v>0.1</v>
       </c>
       <c r="AI72" s="242">
         <f>AH72-AG72</f>
-        <v>2.1192067044148374E-2</v>
+        <v>9.3677083489107499E-3</v>
       </c>
     </row>
     <row r="73" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -52497,9 +53173,9 @@
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="M73" s="145" t="str">
+      <c r="M73" s="145">
         <f t="shared" si="31"/>
-        <v/>
+        <v>2.9940372272685103</v>
       </c>
       <c r="N73" s="145" t="str">
         <f t="shared" si="31"/>
@@ -52579,14 +53255,14 @@
       </c>
       <c r="AG73" s="241">
         <f>+(AG37*10)/AG$9</f>
-        <v>0.63461124959185788</v>
+        <v>0.84590138874349974</v>
       </c>
       <c r="AH73" s="241">
         <v>0.6</v>
       </c>
       <c r="AI73" s="242">
         <f t="shared" si="11"/>
-        <v>-3.4611249591857907E-2</v>
+        <v>-0.24590138874349976</v>
       </c>
     </row>
     <row r="74" spans="1:37" s="91" customFormat="1" ht="18" x14ac:dyDescent="0.25">
@@ -52637,9 +53313,9 @@
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="M74" s="150" t="str">
+      <c r="M74" s="150">
         <f t="shared" si="33"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N74" s="150" t="str">
         <f t="shared" si="33"/>
@@ -52779,9 +53455,9 @@
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="M75" s="145" t="str">
+      <c r="M75" s="145">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N75" s="145" t="str">
         <f t="shared" si="35"/>
@@ -53013,7 +53689,7 @@
       </c>
       <c r="M78" s="152">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>13.452082753502181</v>
       </c>
       <c r="N78" s="152">
         <f>SUM(N62:N77)</f>
@@ -53093,7 +53769,7 @@
       </c>
       <c r="AG78" s="253">
         <f>SUM(AG62:AG77)</f>
-        <v>16.985083947327745</v>
+        <v>17.429024720064675</v>
       </c>
       <c r="AH78" s="253">
         <f t="shared" si="37"/>
@@ -53101,7 +53777,7 @@
       </c>
       <c r="AI78" s="253">
         <f t="shared" si="11"/>
-        <v>-1.3850839473277468</v>
+        <v>-1.8290247200646768</v>
       </c>
       <c r="AJ78" s="210"/>
       <c r="AK78" s="210"/>
@@ -53156,7 +53832,7 @@
       </c>
       <c r="M79" s="154">
         <f>SUM(M69:M72)</f>
-        <v>0</v>
+        <v>6.198922146598183</v>
       </c>
       <c r="N79" s="154">
         <f t="shared" si="38"/>
@@ -53236,7 +53912,7 @@
       </c>
       <c r="AG79" s="254">
         <f t="shared" si="38"/>
-        <v>3.2601597528052308</v>
+        <v>3.5233303379360947</v>
       </c>
       <c r="AH79" s="254">
         <f t="shared" si="38"/>
@@ -53244,7 +53920,7 @@
       </c>
       <c r="AI79" s="254">
         <f t="shared" si="38"/>
-        <v>2.7398402471947696</v>
+        <v>2.4766696620639057</v>
       </c>
       <c r="AJ79" s="285"/>
       <c r="AK79" s="285"/>
@@ -53297,9 +53973,9 @@
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="M80" s="155" t="str">
+      <c r="M80" s="155">
         <f t="shared" si="39"/>
-        <v/>
+        <v>5.2972109067295916</v>
       </c>
       <c r="N80" s="155" t="str">
         <f t="shared" si="39"/>
@@ -53440,9 +54116,9 @@
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="M81" s="157" t="str">
+      <c r="M81" s="157">
         <f t="shared" si="41"/>
-        <v/>
+        <v>1.0312138923327074</v>
       </c>
       <c r="N81" s="157" t="str">
         <f t="shared" si="41"/>
@@ -53522,7 +54198,7 @@
       </c>
       <c r="AG81" s="287">
         <f>IF(AG$9=0,"",+AG49/AG$9)</f>
-        <v>0.56009627508913007</v>
+        <v>0.60228556513085707</v>
       </c>
       <c r="AH81" s="287">
         <f>'Daily KPIs'!AI93</f>
@@ -53530,7 +54206,7 @@
       </c>
       <c r="AI81" s="286">
         <f>AH81-AG81</f>
-        <v>1.1399037249108699</v>
+        <v>1.0977144348691428</v>
       </c>
       <c r="AJ81" s="210"/>
       <c r="AK81" s="210"/>
@@ -53583,9 +54259,9 @@
         <f t="shared" si="43"/>
         <v/>
       </c>
-      <c r="M82" s="144" t="str">
+      <c r="M82" s="144">
         <f t="shared" si="43"/>
-        <v/>
+        <v>37.231485464160109</v>
       </c>
       <c r="N82" s="144" t="str">
         <f t="shared" ref="N82:S82" si="44">IF(N$9=0,"",N52/N$9)</f>
@@ -53665,7 +54341,7 @@
       </c>
       <c r="AG82" s="238">
         <f>+(AG52)/AG$9</f>
-        <v>25.815819721958977</v>
+        <v>26.838109730630258</v>
       </c>
       <c r="AH82" s="239">
         <f>'Daily KPIs'!AI94</f>
@@ -53673,7 +54349,7 @@
       </c>
       <c r="AI82" s="286">
         <f>AH82-AG82</f>
-        <v>-3.8158197219589773</v>
+        <v>-4.8381097306302578</v>
       </c>
       <c r="AJ82" s="270"/>
       <c r="AK82" s="270"/>
@@ -53771,9 +54447,9 @@
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="M84" s="144" t="str">
+      <c r="M84" s="144">
         <f t="shared" si="46"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N84" s="144" t="str">
         <f t="shared" ref="N84:S84" si="47">IF(N$9=0,"",N54/N$9)</f>
@@ -53853,7 +54529,7 @@
       </c>
       <c r="AG84" s="255">
         <f>+(AG54)/AG$9</f>
-        <v>0.398187450724303</v>
+        <v>0.36252916660435702</v>
       </c>
       <c r="AH84" s="256">
         <f>'Daily KPIs'!AI96</f>
@@ -53861,7 +54537,7 @@
       </c>
       <c r="AI84" s="286">
         <f>AH84-AG84</f>
-        <v>6.8018125492756969</v>
+        <v>6.8374708333956429</v>
       </c>
       <c r="AJ84" s="270"/>
       <c r="AK84" s="270"/>
@@ -54092,7 +54768,7 @@
       </c>
       <c r="M87" s="159">
         <f>IF('Entries October 2026'!L18-'Entries October 2026'!L17&lt;1,0,'Entries October 2026'!L18-'Entries October 2026'!L17)</f>
-        <v>0</v>
+        <v>591.47999999999593</v>
       </c>
       <c r="N87" s="119">
         <f>IF('Entries October 2026'!L19-'Entries October 2026'!L18&lt;1,0,'Entries October 2026'!L19-'Entries October 2026'!L18)</f>
@@ -54172,7 +54848,7 @@
       </c>
       <c r="AG87" s="220">
         <f>SUM($B87:AF87)</f>
-        <v>550302.09000000008</v>
+        <v>550893.57000000007</v>
       </c>
       <c r="AH87" s="220"/>
       <c r="AI87" s="271"/>
@@ -54267,9 +54943,9 @@
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="M89" s="160" t="str">
+      <c r="M89" s="160">
         <f t="shared" si="49"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N89" s="160" t="str">
         <f t="shared" si="49"/>
@@ -54748,9 +55424,9 @@
         <f>'Daily KPIs'!L13</f>
         <v>0</v>
       </c>
-      <c r="M94" s="166">
+      <c r="M94" s="166" t="str">
         <f>'Daily KPIs'!M13</f>
-        <v>0</v>
+        <v>ST</v>
       </c>
       <c r="N94" s="166">
         <f>'Daily KPIs'!N13</f>
@@ -54882,7 +55558,7 @@
       </c>
       <c r="M95" s="174">
         <f>'Daily KPIs'!M14</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N95" s="174">
         <f>'Daily KPIs'!N14</f>
@@ -54962,7 +55638,7 @@
       </c>
       <c r="AG95" s="262">
         <f>SUM($B95:AF95)</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AH95" s="262"/>
       <c r="AI95" s="290"/>
@@ -55015,9 +55691,9 @@
         <f>+'Water '!$F17</f>
         <v>5</v>
       </c>
-      <c r="M96" s="110" t="str">
+      <c r="M96" s="110">
         <f>+'Water '!$F18</f>
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="N96" s="110" t="str">
         <f>+'Water '!$F19</f>
@@ -55097,7 +55773,7 @@
       </c>
       <c r="AG96" s="220">
         <f>SUM($B96:AF96)</f>
-        <v>1433</v>
+        <v>1680</v>
       </c>
       <c r="AH96" s="220"/>
       <c r="AI96" s="271"/>
@@ -55305,7 +55981,7 @@
       </c>
       <c r="M101" s="159">
         <f>'Daily KPIs CO2'!M52</f>
-        <v>0</v>
+        <v>8829</v>
       </c>
       <c r="N101" s="159">
         <f>'Daily KPIs CO2'!N52</f>
@@ -55385,7 +56061,7 @@
       </c>
       <c r="AG101" s="263">
         <f>'Daily KPIs CO2'!AG52</f>
-        <v>62240</v>
+        <v>71069</v>
       </c>
       <c r="AH101" s="211"/>
       <c r="AI101" s="271"/>
@@ -55526,30 +56202,30 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B82:AF82">
-    <cfRule type="cellIs" dxfId="41" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="88" priority="3" operator="greaterThan">
       <formula>26</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B84:AF84">
-    <cfRule type="cellIs" dxfId="40" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="87" priority="4" operator="greaterThan">
       <formula>6.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D64:D65 D67 T69:AI70 D71 D73:D77">
-    <cfRule type="cellIs" dxfId="39" priority="5" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="86" priority="5" stopIfTrue="1" operator="greaterThan">
       <formula>3.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D69:S69 B70:S70">
-    <cfRule type="cellIs" dxfId="38" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="85" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>3.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI8">
-    <cfRule type="cellIs" dxfId="37" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="84" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="83" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/data/raw/October_26_Utilities_Tracking.xlsx
+++ b/data/raw/October_26_Utilities_Tracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UTILITIES\Tracking\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F12A63-4C04-4D16-B520-93C3B609AEC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34675391-AC48-4C06-99BA-A61CDDAB0C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="579" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -416,7 +416,40 @@
 Tank B 0 kgs
 Tank C 22400 Kgs
 mobile approx 19800 Kgs
-0 kgs after adjustment for MT mobile weight
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N74" authorId="2" shapeId="0" xr:uid="{CA10FF27-BDE7-4421-B4C9-FE176C49B2B6}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tank A 11500 kgs 
+Tank B 6800 kgs full theoretical
+Tank C 22400 Kgs
+mobile approx0 Kgs
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O74" authorId="2" shapeId="0" xr:uid="{D76ADC42-B6B4-4B28-9ECD-1ECA3E8D4897}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tank A 11500 kgs 
+Tank B 4700 kgs calculated
+Tank C 22400 Kgs
+mobile approx 0Kgs
 </t>
         </r>
       </text>
@@ -492,7 +525,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="316">
   <si>
     <t>UTILITY ANALYSIS</t>
   </si>
@@ -3055,9 +3088,6 @@
     <t>VM/VMg</t>
   </si>
   <si>
-    <t>CB/ST</t>
-  </si>
-  <si>
     <t>ST</t>
   </si>
   <si>
@@ -3074,9 +3104,6 @@
       </rPr>
       <t>ST</t>
     </r>
-  </si>
-  <si>
-    <t>ST/CB</t>
   </si>
   <si>
     <t>GU</t>
@@ -3101,6 +3128,63 @@
         <family val="2"/>
       </rPr>
       <t>/CBfl</t>
+    </r>
+  </si>
+  <si>
+    <t>SM</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FF00A44A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ST</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/CB</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="9" tint="-0.499984740745262"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>SM</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FF00A44A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ST</t>
     </r>
   </si>
 </sst>
@@ -4090,7 +4174,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="42">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4326,12 +4410,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -8651,9 +8729,6 @@
     <xf numFmtId="167" fontId="95" fillId="31" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="75" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="78" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8666,9 +8741,51 @@
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="50" fillId="10" borderId="43" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="10" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="10" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="29" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="124" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="77" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="78" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="79" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="100" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="41" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8690,9 +8807,6 @@
     <xf numFmtId="0" fontId="19" fillId="4" borderId="42" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="41" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8708,45 +8822,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="124" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="77" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="78" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="79" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="100" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="10" borderId="43" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="10" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="10" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="29" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="118" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8864,15 +8939,39 @@
     <xf numFmtId="0" fontId="70" fillId="12" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="52" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="53" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="49" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8882,30 +8981,6 @@
     <xf numFmtId="0" fontId="19" fillId="4" borderId="33" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="52" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="53" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -8960,6 +9035,30 @@
     <xf numFmtId="2" fontId="17" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="47" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="72" fillId="18" borderId="56" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="72" fillId="18" borderId="123" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="32" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="32" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="122" fillId="16" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9020,32 +9119,11 @@
     <xf numFmtId="0" fontId="95" fillId="16" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="47" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="72" fillId="18" borderId="56" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="72" fillId="18" borderId="123" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="32" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="32" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="167" fontId="69" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="131" fillId="31" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -9056,477 +9134,7 @@
     <cellStyle name="Normal_February04" xfId="3" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
     <cellStyle name="Percent" xfId="4" builtinId="5"/>
   </cellStyles>
-  <dxfs count="167">
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="119">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -10568,23 +10176,13 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF00A44A"/>
+      <color rgb="FF0000FF"/>
       <color rgb="FFFF00FF"/>
-      <color rgb="FF0000FF"/>
-      <color rgb="FF00A44A"/>
       <color rgb="FF170EC2"/>
       <color rgb="FFFF3300"/>
       <color rgb="FFC09200"/>
@@ -10895,7 +10493,7 @@
                   <c:v>8829</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>5822</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0</c:v>
@@ -12835,53 +12433,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="18" x14ac:dyDescent="0.2">
-      <c r="B1" s="905" t="s">
+      <c r="B1" s="918" t="s">
         <v>209</v>
       </c>
-      <c r="C1" s="905"/>
-      <c r="D1" s="905"/>
-      <c r="E1" s="905"/>
-      <c r="F1" s="905"/>
-      <c r="G1" s="905"/>
-      <c r="H1" s="905"/>
-      <c r="I1" s="905"/>
-      <c r="J1" s="905"/>
-      <c r="K1" s="905"/>
-      <c r="L1" s="905"/>
-      <c r="M1" s="905"/>
+      <c r="C1" s="918"/>
+      <c r="D1" s="918"/>
+      <c r="E1" s="918"/>
+      <c r="F1" s="918"/>
+      <c r="G1" s="918"/>
+      <c r="H1" s="918"/>
+      <c r="I1" s="918"/>
+      <c r="J1" s="918"/>
+      <c r="K1" s="918"/>
+      <c r="L1" s="918"/>
+      <c r="M1" s="918"/>
       <c r="N1" s="363"/>
-      <c r="O1" s="906" t="str">
+      <c r="O1" s="919" t="str">
         <f>B1</f>
         <v>ENTRIES FOR DAILY CONS. MONITOR</v>
       </c>
-      <c r="P1" s="906"/>
-      <c r="Q1" s="906"/>
-      <c r="R1" s="906"/>
-      <c r="S1" s="906"/>
-      <c r="T1" s="906"/>
-      <c r="U1" s="906"/>
-      <c r="V1" s="906"/>
-      <c r="W1" s="906"/>
-      <c r="X1" s="906"/>
-      <c r="Y1" s="906"/>
-      <c r="Z1" s="906"/>
-      <c r="AA1" s="906"/>
-      <c r="AB1" s="906"/>
+      <c r="P1" s="919"/>
+      <c r="Q1" s="919"/>
+      <c r="R1" s="919"/>
+      <c r="S1" s="919"/>
+      <c r="T1" s="919"/>
+      <c r="U1" s="919"/>
+      <c r="V1" s="919"/>
+      <c r="W1" s="919"/>
+      <c r="X1" s="919"/>
+      <c r="Y1" s="919"/>
+      <c r="Z1" s="919"/>
+      <c r="AA1" s="919"/>
+      <c r="AB1" s="919"/>
     </row>
     <row r="2" spans="1:44" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C2" s="810"/>
       <c r="F2" s="364"/>
       <c r="G2" s="365"/>
-      <c r="O2" s="914" t="s">
+      <c r="O2" s="926" t="s">
         <v>231</v>
       </c>
-      <c r="P2" s="914"/>
-      <c r="Q2" s="914"/>
-      <c r="R2" s="914"/>
-      <c r="S2" s="914"/>
-      <c r="T2" s="914"/>
-      <c r="U2" s="914"/>
-      <c r="V2" s="914"/>
+      <c r="P2" s="926"/>
+      <c r="Q2" s="926"/>
+      <c r="R2" s="926"/>
+      <c r="S2" s="926"/>
+      <c r="T2" s="926"/>
+      <c r="U2" s="926"/>
+      <c r="V2" s="926"/>
     </row>
     <row r="3" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="366"/>
@@ -12899,50 +12497,50 @@
         <v>22</v>
       </c>
       <c r="K3" s="369"/>
-      <c r="L3" s="919" t="s">
+      <c r="L3" s="909" t="s">
         <v>53</v>
       </c>
-      <c r="M3" s="920"/>
-      <c r="N3" s="921"/>
-      <c r="O3" s="907" t="s">
+      <c r="M3" s="910"/>
+      <c r="N3" s="911"/>
+      <c r="O3" s="920" t="s">
         <v>3</v>
       </c>
-      <c r="P3" s="907"/>
-      <c r="Q3" s="907"/>
-      <c r="R3" s="907"/>
-      <c r="S3" s="907"/>
-      <c r="T3" s="907"/>
-      <c r="U3" s="907"/>
-      <c r="V3" s="907"/>
-      <c r="W3" s="907"/>
-      <c r="X3" s="907"/>
-      <c r="Y3" s="907"/>
-      <c r="Z3" s="907"/>
-      <c r="AA3" s="907"/>
-      <c r="AB3" s="907"/>
-      <c r="AC3" s="907"/>
+      <c r="P3" s="920"/>
+      <c r="Q3" s="920"/>
+      <c r="R3" s="920"/>
+      <c r="S3" s="920"/>
+      <c r="T3" s="920"/>
+      <c r="U3" s="920"/>
+      <c r="V3" s="920"/>
+      <c r="W3" s="920"/>
+      <c r="X3" s="920"/>
+      <c r="Y3" s="920"/>
+      <c r="Z3" s="920"/>
+      <c r="AA3" s="920"/>
+      <c r="AB3" s="920"/>
+      <c r="AC3" s="920"/>
       <c r="AD3" s="372"/>
       <c r="AE3" s="373"/>
       <c r="AF3" s="372"/>
-      <c r="AG3" s="927" t="s">
+      <c r="AG3" s="904" t="s">
         <v>206</v>
       </c>
-      <c r="AH3" s="925" t="s">
+      <c r="AH3" s="902" t="s">
         <v>204</v>
       </c>
-      <c r="AI3" s="925" t="s">
+      <c r="AI3" s="902" t="s">
         <v>205</v>
       </c>
-      <c r="AJ3" s="928" t="s">
+      <c r="AJ3" s="905" t="s">
         <v>233</v>
       </c>
       <c r="AK3" s="416"/>
-      <c r="AL3" s="929" t="s">
+      <c r="AL3" s="906" t="s">
         <v>178</v>
       </c>
-      <c r="AM3" s="929"/>
-      <c r="AN3" s="929"/>
-      <c r="AO3" s="929"/>
+      <c r="AM3" s="906"/>
+      <c r="AN3" s="906"/>
+      <c r="AO3" s="906"/>
     </row>
     <row r="4" spans="1:44" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="374"/>
@@ -12976,40 +12574,40 @@
       <c r="K4" s="372" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="915" t="s">
+      <c r="L4" s="927" t="s">
         <v>289</v>
       </c>
       <c r="M4" s="376" t="s">
         <v>260</v>
       </c>
-      <c r="N4" s="922" t="s">
+      <c r="N4" s="912" t="s">
         <v>167</v>
       </c>
-      <c r="O4" s="903" t="s">
+      <c r="O4" s="914" t="s">
         <v>100</v>
       </c>
-      <c r="P4" s="903" t="s">
+      <c r="P4" s="914" t="s">
         <v>101</v>
       </c>
-      <c r="Q4" s="903" t="s">
+      <c r="Q4" s="914" t="s">
         <v>160</v>
       </c>
-      <c r="R4" s="903" t="s">
+      <c r="R4" s="914" t="s">
         <v>171</v>
       </c>
-      <c r="S4" s="903" t="s">
+      <c r="S4" s="914" t="s">
         <v>102</v>
       </c>
-      <c r="T4" s="903" t="s">
+      <c r="T4" s="914" t="s">
         <v>172</v>
       </c>
-      <c r="U4" s="903" t="s">
+      <c r="U4" s="914" t="s">
         <v>103</v>
       </c>
-      <c r="V4" s="912" t="s">
+      <c r="V4" s="924" t="s">
         <v>236</v>
       </c>
-      <c r="W4" s="903" t="s">
+      <c r="W4" s="914" t="s">
         <v>177</v>
       </c>
       <c r="X4" s="372" t="s">
@@ -13021,28 +12619,28 @@
       <c r="Z4" s="372" t="s">
         <v>98</v>
       </c>
-      <c r="AA4" s="907" t="s">
+      <c r="AA4" s="920" t="s">
         <v>68</v>
       </c>
-      <c r="AB4" s="909" t="s">
+      <c r="AB4" s="922" t="s">
         <v>69</v>
       </c>
-      <c r="AC4" s="913" t="s">
+      <c r="AC4" s="925" t="s">
         <v>151</v>
       </c>
-      <c r="AD4" s="903" t="s">
+      <c r="AD4" s="914" t="s">
         <v>154</v>
       </c>
-      <c r="AE4" s="903" t="s">
+      <c r="AE4" s="914" t="s">
         <v>155</v>
       </c>
-      <c r="AF4" s="903" t="s">
+      <c r="AF4" s="914" t="s">
         <v>159</v>
       </c>
-      <c r="AG4" s="927"/>
-      <c r="AH4" s="926"/>
-      <c r="AI4" s="926"/>
-      <c r="AJ4" s="928"/>
+      <c r="AG4" s="904"/>
+      <c r="AH4" s="903"/>
+      <c r="AI4" s="903"/>
+      <c r="AJ4" s="905"/>
       <c r="AK4" s="416"/>
       <c r="AL4" s="378" t="s">
         <v>276</v>
@@ -13091,20 +12689,20 @@
       <c r="K5" s="465" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="916"/>
+      <c r="L5" s="928"/>
       <c r="M5" s="466" t="s">
         <v>261</v>
       </c>
-      <c r="N5" s="923"/>
-      <c r="O5" s="911"/>
-      <c r="P5" s="903"/>
-      <c r="Q5" s="903"/>
-      <c r="R5" s="903"/>
-      <c r="S5" s="911"/>
-      <c r="T5" s="911"/>
-      <c r="U5" s="911"/>
-      <c r="V5" s="912"/>
-      <c r="W5" s="924"/>
+      <c r="N5" s="913"/>
+      <c r="O5" s="915"/>
+      <c r="P5" s="914"/>
+      <c r="Q5" s="914"/>
+      <c r="R5" s="914"/>
+      <c r="S5" s="915"/>
+      <c r="T5" s="915"/>
+      <c r="U5" s="915"/>
+      <c r="V5" s="924"/>
+      <c r="W5" s="916"/>
       <c r="X5" s="372" t="s">
         <v>104</v>
       </c>
@@ -13114,16 +12712,16 @@
       <c r="Z5" s="372" t="s">
         <v>104</v>
       </c>
-      <c r="AA5" s="908"/>
-      <c r="AB5" s="910"/>
-      <c r="AC5" s="913"/>
-      <c r="AD5" s="903"/>
-      <c r="AE5" s="903"/>
-      <c r="AF5" s="904"/>
-      <c r="AG5" s="927"/>
-      <c r="AH5" s="926"/>
-      <c r="AI5" s="926"/>
-      <c r="AJ5" s="928"/>
+      <c r="AA5" s="921"/>
+      <c r="AB5" s="923"/>
+      <c r="AC5" s="925"/>
+      <c r="AD5" s="914"/>
+      <c r="AE5" s="914"/>
+      <c r="AF5" s="917"/>
+      <c r="AG5" s="904"/>
+      <c r="AH5" s="903"/>
+      <c r="AI5" s="903"/>
+      <c r="AJ5" s="905"/>
       <c r="AK5" s="416"/>
       <c r="AL5" s="378" t="s">
         <v>263</v>
@@ -14330,41 +13928,87 @@
       <c r="A19" s="378">
         <v>14</v>
       </c>
-      <c r="B19" s="815"/>
-      <c r="C19" s="816"/>
+      <c r="B19" s="815">
+        <v>8522020</v>
+      </c>
+      <c r="C19" s="816">
+        <v>1692682.9</v>
+      </c>
       <c r="D19" s="817"/>
-      <c r="E19" s="817"/>
-      <c r="F19" s="817"/>
-      <c r="G19" s="817"/>
+      <c r="E19" s="817">
+        <v>64</v>
+      </c>
+      <c r="F19" s="817">
+        <v>11454</v>
+      </c>
+      <c r="G19" s="817">
+        <v>68225</v>
+      </c>
       <c r="H19" s="818"/>
-      <c r="I19" s="819"/>
+      <c r="I19" s="819">
+        <v>1956257</v>
+      </c>
       <c r="J19" s="876"/>
-      <c r="K19" s="818"/>
-      <c r="L19" s="817"/>
-      <c r="M19" s="821"/>
-      <c r="N19" s="819"/>
-      <c r="O19" s="822"/>
-      <c r="P19" s="823"/>
-      <c r="Q19" s="817"/>
+      <c r="K19" s="818">
+        <v>468000</v>
+      </c>
+      <c r="L19" s="817">
+        <v>91256</v>
+      </c>
+      <c r="M19" s="821">
+        <v>644517</v>
+      </c>
+      <c r="N19" s="819">
+        <v>86516</v>
+      </c>
+      <c r="O19" s="822">
+        <v>255073</v>
+      </c>
+      <c r="P19" s="823">
+        <v>87434</v>
+      </c>
+      <c r="Q19" s="817">
+        <v>991574</v>
+      </c>
       <c r="R19" s="817"/>
-      <c r="S19" s="817"/>
+      <c r="S19" s="817">
+        <v>98876</v>
+      </c>
       <c r="T19" s="817"/>
-      <c r="U19" s="817"/>
-      <c r="V19" s="824"/>
+      <c r="U19" s="817">
+        <v>565</v>
+      </c>
+      <c r="V19" s="824">
+        <v>1367830</v>
+      </c>
       <c r="W19" s="817"/>
-      <c r="X19" s="825"/>
-      <c r="Y19" s="817"/>
-      <c r="Z19" s="817"/>
-      <c r="AA19" s="817"/>
+      <c r="X19" s="825">
+        <v>49529</v>
+      </c>
+      <c r="Y19" s="817">
+        <v>71643</v>
+      </c>
+      <c r="Z19" s="817">
+        <v>15936</v>
+      </c>
+      <c r="AA19" s="817">
+        <v>97122</v>
+      </c>
       <c r="AB19" s="817"/>
-      <c r="AC19" s="817"/>
-      <c r="AD19" s="817"/>
+      <c r="AC19" s="817">
+        <v>6914</v>
+      </c>
+      <c r="AD19" s="817">
+        <v>263787</v>
+      </c>
       <c r="AE19" s="817"/>
       <c r="AF19" s="819"/>
       <c r="AG19" s="817"/>
       <c r="AH19" s="817"/>
       <c r="AI19" s="817"/>
-      <c r="AJ19" s="880"/>
+      <c r="AJ19" s="880">
+        <v>7383613.8779999996</v>
+      </c>
       <c r="AK19" s="192"/>
       <c r="AL19" s="387"/>
       <c r="AM19" s="387"/>
@@ -15186,8 +14830,8 @@
     <row r="38" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B38" s="190"/>
       <c r="G38" s="190"/>
-      <c r="I38" s="917"/>
-      <c r="J38" s="917"/>
+      <c r="I38" s="907"/>
+      <c r="J38" s="907"/>
       <c r="R38" s="190"/>
       <c r="S38" s="190"/>
       <c r="T38" s="190"/>
@@ -15195,8 +14839,8 @@
       <c r="V38" s="190"/>
       <c r="W38" s="190"/>
       <c r="Z38" s="190"/>
-      <c r="AA38" s="918"/>
-      <c r="AB38" s="918"/>
+      <c r="AA38" s="908"/>
+      <c r="AB38" s="908"/>
       <c r="AC38" s="190"/>
       <c r="AD38" s="190"/>
       <c r="AI38" s="380"/>
@@ -16862,19 +16506,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="AH3:AH5"/>
-    <mergeCell ref="AG3:AG5"/>
-    <mergeCell ref="AI3:AI5"/>
-    <mergeCell ref="AJ3:AJ5"/>
-    <mergeCell ref="AL3:AO3"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="AA38:AB38"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="S4:S5"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="P4:P5"/>
-    <mergeCell ref="W4:W5"/>
     <mergeCell ref="AF4:AF5"/>
     <mergeCell ref="AE4:AE5"/>
     <mergeCell ref="AD4:AD5"/>
@@ -16891,401 +16522,299 @@
     <mergeCell ref="AC4:AC5"/>
     <mergeCell ref="O2:V2"/>
     <mergeCell ref="L4:L5"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="AA38:AB38"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="S4:S5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="P4:P5"/>
+    <mergeCell ref="W4:W5"/>
+    <mergeCell ref="AH3:AH5"/>
+    <mergeCell ref="AG3:AG5"/>
+    <mergeCell ref="AI3:AI5"/>
+    <mergeCell ref="AJ3:AJ5"/>
+    <mergeCell ref="AL3:AO3"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
-  <conditionalFormatting sqref="B19:B35">
-    <cfRule type="expression" dxfId="165" priority="75">
-      <formula>B19&lt;B18</formula>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="expression" dxfId="118" priority="14">
+      <formula>B6&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:B35">
+    <cfRule type="expression" dxfId="117" priority="28">
+      <formula>B7&lt;B6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:B19">
+    <cfRule type="expression" dxfId="116" priority="45">
+      <formula>B11&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C35 E35:E37">
-    <cfRule type="expression" dxfId="163" priority="427">
+    <cfRule type="expression" dxfId="115" priority="427">
       <formula>C35&lt;C34</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C6:D6">
+    <cfRule type="expression" dxfId="114" priority="16">
+      <formula>C6&lt;C5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7:D7 H7:J7 R7 T7 W7 AB7">
+    <cfRule type="expression" dxfId="113" priority="32">
+      <formula>C7&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8:D14">
+    <cfRule type="expression" dxfId="112" priority="36">
+      <formula>C8&lt;C7</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C36:D37">
-    <cfRule type="expression" dxfId="159" priority="1480">
+    <cfRule type="expression" dxfId="111" priority="1480">
       <formula>C36&lt;C35</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D35 B36:B37">
-    <cfRule type="expression" dxfId="158" priority="1467">
+    <cfRule type="expression" dxfId="110" priority="1467">
       <formula>B35&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F19:F37">
-    <cfRule type="expression" dxfId="156" priority="51">
-      <formula>F19&lt;#REF!</formula>
+  <conditionalFormatting sqref="E6:E14">
+    <cfRule type="expression" dxfId="109" priority="5">
+      <formula>E6&lt;E5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G19:G37">
-    <cfRule type="expression" dxfId="155" priority="49">
-      <formula>G19&lt;G18</formula>
+  <conditionalFormatting sqref="F6:F37">
+    <cfRule type="expression" dxfId="108" priority="4">
+      <formula>F6&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6:G37">
+    <cfRule type="expression" dxfId="107" priority="2">
+      <formula>G6&lt;G5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G36:J37 L36:O37">
-    <cfRule type="expression" dxfId="154" priority="1314">
+    <cfRule type="expression" dxfId="106" priority="1314">
       <formula>G36&lt;G35</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H19:I34">
-    <cfRule type="expression" dxfId="152" priority="428">
+  <conditionalFormatting sqref="G6:O6">
+    <cfRule type="expression" dxfId="105" priority="6">
+      <formula>G6&lt;G5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20:I34 H19">
+    <cfRule type="expression" dxfId="104" priority="428">
       <formula>H19&lt;H18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H35:I35 R35 T35 W35 AB35 AE35:AI35 P36:P37 S36:S37 X36:Y37">
-    <cfRule type="expression" dxfId="151" priority="1466">
+    <cfRule type="expression" dxfId="103" priority="1466">
       <formula>H35&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H8:J18 I19">
+    <cfRule type="expression" dxfId="102" priority="37">
+      <formula>H8&lt;H7</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J19:J35">
-    <cfRule type="expression" dxfId="149" priority="429">
+    <cfRule type="expression" dxfId="101" priority="429">
       <formula>J19&lt;J18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K19:L21">
-    <cfRule type="expression" dxfId="148" priority="87">
-      <formula>K19&lt;K18</formula>
+  <conditionalFormatting sqref="K11:L21">
+    <cfRule type="expression" dxfId="100" priority="40">
+      <formula>K11&lt;K10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K22:M22">
-    <cfRule type="expression" dxfId="147" priority="430">
+    <cfRule type="expression" dxfId="99" priority="430">
       <formula>K22&lt;K21</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K7:O10">
+    <cfRule type="expression" dxfId="98" priority="23">
+      <formula>K7&lt;K6</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="K23:Z23 K24:K37">
-    <cfRule type="expression" dxfId="145" priority="431">
+    <cfRule type="expression" dxfId="97" priority="431">
       <formula>K23&lt;K22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L24:Z27 L28:AC28">
-    <cfRule type="expression" dxfId="144" priority="433">
+    <cfRule type="expression" dxfId="96" priority="433">
       <formula>L24&lt;L23</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M19:M21">
-    <cfRule type="expression" dxfId="142" priority="426">
-      <formula>M19&lt;M18</formula>
+  <conditionalFormatting sqref="M11:M17">
+    <cfRule type="expression" dxfId="95" priority="42">
+      <formula>M11&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N19:T22">
-    <cfRule type="expression" dxfId="140" priority="91">
-      <formula>N19&lt;N18</formula>
+  <conditionalFormatting sqref="N11:O12">
+    <cfRule type="expression" dxfId="94" priority="41">
+      <formula>N11&lt;N10</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N13:T22">
+    <cfRule type="expression" dxfId="93" priority="44">
+      <formula>N13&lt;N12</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P8:P12 V8:V12">
+    <cfRule type="expression" dxfId="92" priority="39">
+      <formula>P8&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P6:Q6 X6:Y6 S6:S10">
+    <cfRule type="expression" dxfId="91" priority="13">
+      <formula>P6&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P7:Q7">
+    <cfRule type="expression" dxfId="90" priority="30">
+      <formula>P7&lt;P6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q36">
-    <cfRule type="expression" dxfId="136" priority="1483">
+    <cfRule type="expression" dxfId="89" priority="1483">
       <formula>Q36&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="Q8:R10">
+    <cfRule type="expression" dxfId="88" priority="38">
+      <formula>Q8&lt;Q7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q11:T12">
+    <cfRule type="expression" dxfId="87" priority="43">
+      <formula>Q11&lt;Q10</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R6">
+    <cfRule type="expression" dxfId="86" priority="15">
+      <formula>R6&lt;R5</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="R36">
-    <cfRule type="expression" dxfId="132" priority="1479">
+    <cfRule type="expression" dxfId="85" priority="1479">
       <formula>R36&lt;R35</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB19:AI27">
-    <cfRule type="expression" dxfId="131" priority="81">
-      <formula>AB19&lt;AB18</formula>
+  <conditionalFormatting sqref="T8:T10 AB8:AC10 AE8:AI10 AB11:AI27">
+    <cfRule type="expression" dxfId="84" priority="34">
+      <formula>T8&lt;T7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U19:U22">
-    <cfRule type="expression" dxfId="129" priority="56">
-      <formula>U19&lt;U18</formula>
+  <conditionalFormatting sqref="T6:W6 Z6 AB6">
+    <cfRule type="expression" dxfId="83" priority="12">
+      <formula>T6&lt;T5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C19:E34">
-    <cfRule type="expression" dxfId="127" priority="94">
-      <formula>C19&lt;C18</formula>
+  <conditionalFormatting sqref="U6:U22">
+    <cfRule type="expression" dxfId="82" priority="9">
+      <formula>U6&lt;U5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V19:Z22">
-    <cfRule type="expression" dxfId="126" priority="93">
-      <formula>V19&lt;V18</formula>
+  <conditionalFormatting sqref="V7">
+    <cfRule type="expression" dxfId="81" priority="25">
+      <formula>V7&lt;V6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V13:X14 C15:E34">
+    <cfRule type="expression" dxfId="80" priority="47">
+      <formula>C13&lt;C12</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M18:M21 V15:Z22">
+    <cfRule type="expression" dxfId="79" priority="46">
+      <formula>M15&lt;M14</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V29:AC29 AA30:AC30 Z30:Z31 V30:Y34 AA31:AB31 AC31:AC37 Z32:AB34 V35 X35:AA35">
-    <cfRule type="expression" dxfId="125" priority="437">
+    <cfRule type="expression" dxfId="78" priority="437">
       <formula>V29&lt;V28</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA19:AA37">
-    <cfRule type="expression" dxfId="121" priority="48">
-      <formula>AA19&lt;AA18</formula>
+  <conditionalFormatting sqref="W8:W12">
+    <cfRule type="expression" dxfId="77" priority="35">
+      <formula>W8&lt;W7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y7:Z14">
+    <cfRule type="expression" dxfId="76" priority="26">
+      <formula>Y7&lt;Y6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA6:AA12">
+    <cfRule type="expression" dxfId="75" priority="8">
+      <formula>AA6&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA6:AA37">
+    <cfRule type="expression" dxfId="74" priority="1">
+      <formula>AA6&lt;AA5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA28:AA37">
-    <cfRule type="expression" dxfId="120" priority="435">
+    <cfRule type="expression" dxfId="73" priority="435">
       <formula>AA28&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AC6:AC7">
+    <cfRule type="expression" dxfId="72" priority="10">
+      <formula>AC6&lt;AC5</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AD28:AD37">
-    <cfRule type="expression" dxfId="118" priority="432">
+    <cfRule type="expression" dxfId="71" priority="432">
       <formula>AD28&lt;AD27</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AD6:AI6">
+    <cfRule type="expression" dxfId="70" priority="7">
+      <formula>AD6&lt;AD5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD7:AI7 X7:X12 AD8:AD10">
+    <cfRule type="expression" dxfId="69" priority="27">
+      <formula>X7&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AE28:AI34 L29:T34 U29:U37 L35:Q35 S35">
-    <cfRule type="expression" dxfId="115" priority="436">
+    <cfRule type="expression" dxfId="68" priority="436">
       <formula>L28&lt;L27</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AJ19:AJ37">
-    <cfRule type="expression" dxfId="114" priority="50">
-      <formula>AJ19&lt;AJ18</formula>
+  <conditionalFormatting sqref="AJ6:AJ37">
+    <cfRule type="expression" dxfId="67" priority="3">
+      <formula>AJ6&lt;AJ5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK6:AK12">
-    <cfRule type="expression" dxfId="113" priority="1356">
+    <cfRule type="expression" dxfId="66" priority="1356">
       <formula>AK6&lt;AK5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK13:AL15">
-    <cfRule type="expression" dxfId="112" priority="1436">
+    <cfRule type="expression" dxfId="65" priority="1436">
       <formula>AK13&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL9:AL14 AL15:AN34 AK16:AK37 AK20:AN21 T36:W37 Z36:Z37 AB36:AB37 AE36:AI37 Q37:R37">
-    <cfRule type="expression" dxfId="111" priority="1373">
+    <cfRule type="expression" dxfId="64" priority="1373">
       <formula>Q9&lt;Q8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO9:AO34">
-    <cfRule type="expression" dxfId="110" priority="1381">
+    <cfRule type="expression" dxfId="63" priority="1381">
       <formula>AO9&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B7:B18">
-    <cfRule type="expression" dxfId="46" priority="28">
-      <formula>B7&lt;B6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B11:B18">
-    <cfRule type="expression" dxfId="45" priority="45">
-      <formula>B11&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C7:D7 H7:J7 R7 T7 W7 AB7">
-    <cfRule type="expression" dxfId="44" priority="32">
-      <formula>C7&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C8:D14">
-    <cfRule type="expression" dxfId="43" priority="36">
-      <formula>C8&lt;C7</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7:E14">
-    <cfRule type="expression" dxfId="42" priority="18">
-      <formula>E7&lt;E6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F18">
-    <cfRule type="expression" dxfId="41" priority="33">
-      <formula>F7&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G7:G18">
-    <cfRule type="expression" dxfId="40" priority="29">
-      <formula>G7&lt;G6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H8:J18">
-    <cfRule type="expression" dxfId="39" priority="37">
-      <formula>H8&lt;H7</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K11:L18">
-    <cfRule type="expression" dxfId="38" priority="40">
-      <formula>K11&lt;K10</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7:O8 K9:N10 O9">
-    <cfRule type="expression" dxfId="37" priority="23">
-      <formula>K7&lt;K6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M11:M17">
-    <cfRule type="expression" dxfId="36" priority="42">
-      <formula>M11&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N11:O12 O10">
-    <cfRule type="expression" dxfId="35" priority="41">
-      <formula>N10&lt;N9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N13:T18">
-    <cfRule type="expression" dxfId="34" priority="44">
-      <formula>N13&lt;N12</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S7:S10">
-    <cfRule type="expression" dxfId="33" priority="22">
-      <formula>S7&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P8:P12 V8:V12">
-    <cfRule type="expression" dxfId="32" priority="39">
-      <formula>P8&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P7:Q7">
-    <cfRule type="expression" dxfId="31" priority="30">
-      <formula>P7&lt;P6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q8:R8">
-    <cfRule type="expression" dxfId="30" priority="38">
-      <formula>Q8&lt;Q7</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q11:T12 Q9:R10 T9:T10">
-    <cfRule type="expression" dxfId="29" priority="43">
-      <formula>Q9&lt;Q8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T8 AB8:AC10 AE8:AI10 AB11:AI18">
-    <cfRule type="expression" dxfId="28" priority="34">
-      <formula>T8&lt;T7</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U7:U18">
-    <cfRule type="expression" dxfId="27" priority="20">
-      <formula>U7&lt;U6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V7">
-    <cfRule type="expression" dxfId="26" priority="25">
-      <formula>V7&lt;V6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V13:X14 C15:E18">
-    <cfRule type="expression" dxfId="25" priority="47">
-      <formula>C13&lt;C12</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V15:Z18 M18">
-    <cfRule type="expression" dxfId="24" priority="46">
-      <formula>M15&lt;M14</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W8:W12">
-    <cfRule type="expression" dxfId="23" priority="35">
-      <formula>W8&lt;W7</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y7:Z14">
-    <cfRule type="expression" dxfId="22" priority="26">
-      <formula>Y7&lt;Y6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA7:AA12">
-    <cfRule type="expression" dxfId="21" priority="19">
-      <formula>AA7&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA7:AA18">
-    <cfRule type="expression" dxfId="20" priority="24">
-      <formula>AA7&lt;AA6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC7">
-    <cfRule type="expression" dxfId="19" priority="21">
-      <formula>AC7&lt;AC6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD7:AI7 X7:X12 AD8:AD10">
-    <cfRule type="expression" dxfId="18" priority="27">
-      <formula>X7&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ12:AJ18">
-    <cfRule type="expression" dxfId="17" priority="31">
-      <formula>AJ12&lt;AJ11</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C6:D6">
-    <cfRule type="expression" dxfId="16" priority="16">
-      <formula>C6&lt;C5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="expression" dxfId="15" priority="14">
-      <formula>B6&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="14" priority="4">
-      <formula>F6&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G6">
-    <cfRule type="expression" dxfId="13" priority="2">
-      <formula>G6&lt;G5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G6:J6 L6:O6">
-    <cfRule type="expression" dxfId="12" priority="11">
-      <formula>G6&lt;G5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P6 S6 X6:Y6">
-    <cfRule type="expression" dxfId="11" priority="13">
-      <formula>P6&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K6">
-    <cfRule type="expression" dxfId="10" priority="6">
-      <formula>K6&lt;K5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q6">
-    <cfRule type="expression" dxfId="9" priority="17">
-      <formula>Q6&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R6">
-    <cfRule type="expression" dxfId="8" priority="15">
-      <formula>R6&lt;R5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="7" priority="5">
-      <formula>E6&lt;E5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC6">
-    <cfRule type="expression" dxfId="6" priority="10">
-      <formula>AC6&lt;AC5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA6">
-    <cfRule type="expression" dxfId="5" priority="1">
-      <formula>AA6&lt;AA5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA6">
-    <cfRule type="expression" dxfId="4" priority="8">
-      <formula>AA6&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD6">
-    <cfRule type="expression" dxfId="3" priority="7">
-      <formula>AD6&lt;AD5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U6">
-    <cfRule type="expression" dxfId="2" priority="9">
-      <formula>U6&lt;U5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ6:AJ11">
-    <cfRule type="expression" dxfId="1" priority="3">
-      <formula>AJ6&lt;AJ5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T6:W6 Z6 AB6 AE6:AI6">
-    <cfRule type="expression" dxfId="0" priority="12">
-      <formula>T6&lt;T5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.1" right="0.5" top="0.32" bottom="0.25" header="0.25" footer="0.25"/>
@@ -17323,8 +16852,8 @@
     <col min="11" max="11" width="29.7109375" style="469" customWidth="1"/>
     <col min="12" max="12" width="30.5703125" style="469" customWidth="1"/>
     <col min="13" max="13" width="29.7109375" style="470" customWidth="1"/>
-    <col min="14" max="32" width="29.7109375" style="469" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="29.7109375" style="469" customWidth="1"/>
+    <col min="14" max="15" width="29.7109375" style="469" customWidth="1"/>
+    <col min="16" max="33" width="29.7109375" style="469" hidden="1" customWidth="1"/>
     <col min="34" max="34" width="29.7109375" style="468" customWidth="1"/>
     <col min="35" max="35" width="24.7109375" style="468" customWidth="1"/>
     <col min="36" max="36" width="24.7109375" style="291" customWidth="1"/>
@@ -17354,8 +16883,8 @@
       </c>
       <c r="B3" s="468"/>
       <c r="C3" s="468"/>
-      <c r="K3" s="902"/>
-      <c r="L3" s="902"/>
+      <c r="K3" s="901"/>
+      <c r="L3" s="901"/>
       <c r="M3" s="498"/>
       <c r="AH3" s="291"/>
       <c r="AI3" s="291"/>
@@ -17501,7 +17030,7 @@
         <v>31</v>
       </c>
       <c r="AG6" s="291"/>
-      <c r="AI6" s="901" t="s">
+      <c r="AI6" s="900" t="s">
         <v>216</v>
       </c>
     </row>
@@ -17600,13 +17129,11 @@
       <c r="AF7" s="476" t="s">
         <v>91</v>
       </c>
-      <c r="AG7" s="476" t="s">
-        <v>92</v>
-      </c>
+      <c r="AG7" s="476"/>
       <c r="AH7" s="477" t="s">
         <v>19</v>
       </c>
-      <c r="AI7" s="901"/>
+      <c r="AI7" s="900"/>
       <c r="AJ7" s="292" t="s">
         <v>229</v>
       </c>
@@ -17673,7 +17200,10 @@
         <f>2979+614</f>
         <v>3593</v>
       </c>
-      <c r="N8" s="678"/>
+      <c r="N8" s="678">
+        <f>842+7777</f>
+        <v>8619</v>
+      </c>
       <c r="O8" s="678"/>
       <c r="P8" s="678"/>
       <c r="Q8" s="678"/>
@@ -17695,14 +17225,14 @@
       <c r="AG8" s="747"/>
       <c r="AH8" s="480">
         <f>SUM(B8:AG8)</f>
-        <v>40037</v>
+        <v>48656</v>
       </c>
       <c r="AI8" s="526">
         <v>123950</v>
       </c>
       <c r="AJ8" s="294">
         <f>AH8-AI8</f>
-        <v>-83913</v>
+        <v>-75294</v>
       </c>
       <c r="AK8" s="481"/>
       <c r="AL8" s="481"/>
@@ -17782,7 +17312,7 @@
       </c>
       <c r="N9" s="678">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>568.85400000000004</v>
       </c>
       <c r="O9" s="678">
         <f t="shared" si="1"/>
@@ -17850,7 +17380,7 @@
       <c r="AG9" s="748"/>
       <c r="AH9" s="484">
         <f>SUM(B9:AG9)</f>
-        <v>2648.0627999999997</v>
+        <v>3216.9168</v>
       </c>
       <c r="AI9" s="484"/>
       <c r="AL9" s="291" t="s">
@@ -17880,17 +17410,19 @@
         <v>307</v>
       </c>
       <c r="I10" s="770" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J10" s="894" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="K10" s="871"/>
       <c r="L10" s="871"/>
       <c r="M10" s="681" t="s">
-        <v>314</v>
-      </c>
-      <c r="N10" s="681"/>
+        <v>312</v>
+      </c>
+      <c r="N10" s="770" t="s">
+        <v>307</v>
+      </c>
       <c r="O10" s="878"/>
       <c r="P10" s="878"/>
       <c r="Q10" s="871"/>
@@ -18170,27 +17702,31 @@
       <c r="F13" s="669" t="s">
         <v>307</v>
       </c>
-      <c r="G13" s="669" t="s">
+      <c r="G13" s="770" t="s">
+        <v>310</v>
+      </c>
+      <c r="H13" s="682" t="s">
         <v>309</v>
       </c>
-      <c r="H13" s="682" t="s">
-        <v>310</v>
-      </c>
-      <c r="I13" s="682" t="s">
-        <v>312</v>
+      <c r="I13" s="770" t="s">
+        <v>314</v>
       </c>
       <c r="J13" s="669" t="s">
         <v>307</v>
       </c>
       <c r="K13" s="897" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="L13" s="669"/>
       <c r="M13" s="798" t="s">
-        <v>310</v>
-      </c>
-      <c r="N13" s="798"/>
-      <c r="O13" s="669"/>
+        <v>309</v>
+      </c>
+      <c r="N13" s="1029" t="s">
+        <v>313</v>
+      </c>
+      <c r="O13" s="770" t="s">
+        <v>315</v>
+      </c>
       <c r="P13" s="669"/>
       <c r="Q13" s="669"/>
       <c r="R13" s="681"/>
@@ -18248,15 +17784,19 @@
       <c r="J14" s="498">
         <v>7</v>
       </c>
-      <c r="K14" s="899">
+      <c r="K14" s="898">
         <v>8</v>
       </c>
       <c r="L14" s="498"/>
       <c r="M14" s="498">
         <v>1</v>
       </c>
-      <c r="N14" s="498"/>
-      <c r="O14" s="498"/>
+      <c r="N14" s="498">
+        <v>4</v>
+      </c>
+      <c r="O14" s="498">
+        <v>0</v>
+      </c>
       <c r="P14" s="498"/>
       <c r="R14" s="498"/>
       <c r="S14" s="498"/>
@@ -18276,7 +17816,7 @@
       <c r="AG14" s="498"/>
       <c r="AH14" s="468">
         <f>SUM(B14:AF14)</f>
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:149" s="504" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -18317,7 +17857,7 @@
       <c r="AG15" s="718"/>
       <c r="AH15" s="500">
         <f>IF(AH12=0,"",+(AH36*10)/AH12)</f>
-        <v>5.775222551928783</v>
+        <v>6.0942136498516319</v>
       </c>
       <c r="AI15" s="502"/>
       <c r="AJ15" s="503"/>
@@ -18699,9 +18239,9 @@
         <f>+'Water '!$D18</f>
         <v>144</v>
       </c>
-      <c r="N20" s="509" t="str">
+      <c r="N20" s="509">
         <f>+'Water '!$D19</f>
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="O20" s="509" t="str">
         <f>+'Water '!$D20</f>
@@ -18778,7 +18318,7 @@
       <c r="AG20" s="509"/>
       <c r="AH20" s="484">
         <f>SUM($B20:AF20)</f>
-        <v>1844</v>
+        <v>2079</v>
       </c>
       <c r="AI20" s="484"/>
       <c r="AJ20" s="485"/>
@@ -18835,9 +18375,9 @@
         <f>+'Water '!$E18</f>
         <v>237</v>
       </c>
-      <c r="N21" s="511" t="str">
+      <c r="N21" s="511">
         <f>+'Water '!$E19</f>
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="O21" s="511" t="str">
         <f>+'Water '!$E20</f>
@@ -18914,7 +18454,7 @@
       <c r="AG21" s="509"/>
       <c r="AH21" s="484">
         <f>SUM($B21:AF21)</f>
-        <v>1546</v>
+        <v>1658</v>
       </c>
       <c r="AI21" s="484"/>
     </row>
@@ -18972,7 +18512,7 @@
       </c>
       <c r="N22" s="514">
         <f>SUM(N19:N21)</f>
-        <v>0</v>
+        <v>347</v>
       </c>
       <c r="O22" s="514">
         <f t="shared" si="3"/>
@@ -19049,7 +18589,7 @@
       <c r="AG22" s="515"/>
       <c r="AH22" s="516">
         <f>SUM($B22:AF22)</f>
-        <v>3390</v>
+        <v>3737</v>
       </c>
       <c r="AI22" s="514"/>
       <c r="AJ22" s="517"/>
@@ -19336,7 +18876,7 @@
       </c>
       <c r="N26" s="521">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>83.22</v>
       </c>
       <c r="O26" s="521">
         <f t="shared" si="4"/>
@@ -19413,15 +18953,15 @@
       <c r="AG26" s="521"/>
       <c r="AH26" s="484">
         <f>SUM($B26:AF26)</f>
-        <v>1226.4000000000001</v>
+        <v>1309.6200000000001</v>
       </c>
       <c r="AI26" s="523">
         <f>AH29+AH45+AH36</f>
-        <v>3613</v>
+        <v>3953</v>
       </c>
       <c r="AK26" s="524">
         <f>(AI26*10)/AH9</f>
-        <v>13.643936238974394</v>
+        <v>12.288163623006973</v>
       </c>
     </row>
     <row r="27" spans="1:149" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -19624,7 +19164,7 @@
       </c>
       <c r="N29" s="509">
         <f>'Water '!H19</f>
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="O29" s="509">
         <f>'Water '!$H20</f>
@@ -19701,7 +19241,7 @@
       <c r="AG29" s="509"/>
       <c r="AH29" s="484">
         <f>SUM($B29:AF29)</f>
-        <v>1832</v>
+        <v>2071</v>
       </c>
       <c r="AI29" s="484"/>
       <c r="AJ29" s="484"/>
@@ -19759,9 +19299,9 @@
         <f t="shared" si="5"/>
         <v>72</v>
       </c>
-      <c r="N30" s="509" t="str">
+      <c r="N30" s="509">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="O30" s="509" t="str">
         <f t="shared" si="5"/>
@@ -19838,7 +19378,7 @@
       <c r="AG30" s="509"/>
       <c r="AH30" s="484">
         <f>AH36</f>
-        <v>1557</v>
+        <v>1643</v>
       </c>
       <c r="AI30" s="484"/>
       <c r="AJ30" s="484"/>
@@ -19896,9 +19436,9 @@
         <f>M45</f>
         <v>71</v>
       </c>
-      <c r="N31" s="509" t="str">
+      <c r="N31" s="509">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O31" s="509" t="str">
         <f t="shared" si="6"/>
@@ -19975,7 +19515,7 @@
       <c r="AG31" s="509"/>
       <c r="AH31" s="484">
         <f>AH45</f>
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="AI31" s="484"/>
       <c r="AJ31" s="484"/>
@@ -20034,7 +19574,7 @@
       </c>
       <c r="N32" s="527">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="O32" s="527">
         <f t="shared" si="7"/>
@@ -20111,7 +19651,7 @@
       <c r="AG32" s="527"/>
       <c r="AH32" s="526">
         <f>SUM($B32:AF32)</f>
-        <v>3613</v>
+        <v>3953</v>
       </c>
       <c r="AI32" s="526"/>
       <c r="AJ32" s="528"/>
@@ -20308,9 +19848,9 @@
         <f>+'Water '!$J18</f>
         <v>72</v>
       </c>
-      <c r="N36" s="535" t="str">
+      <c r="N36" s="535">
         <f>+'Water '!$J19</f>
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="O36" s="535" t="str">
         <f>+'Water '!$J20</f>
@@ -20387,7 +19927,7 @@
       <c r="AG36" s="508"/>
       <c r="AH36" s="484">
         <f>SUM($B36:AF36)</f>
-        <v>1557</v>
+        <v>1643</v>
       </c>
       <c r="AI36" s="484"/>
     </row>
@@ -21118,9 +20658,9 @@
         <f>+'Water '!$N18</f>
         <v>29</v>
       </c>
-      <c r="N41" s="539" t="str">
+      <c r="N41" s="539">
         <f>+'Water '!$N19</f>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="O41" s="539" t="str">
         <f>+'Water '!$N20</f>
@@ -21197,7 +20737,7 @@
       <c r="AG41" s="539"/>
       <c r="AH41" s="514">
         <f>SUM($B41:AF41)</f>
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="AI41" s="514"/>
       <c r="AJ41" s="514"/>
@@ -21367,9 +20907,9 @@
         <f>+'Water '!$O18</f>
         <v>119</v>
       </c>
-      <c r="N42" s="508" t="str">
+      <c r="N42" s="508">
         <f>+'Water '!$O19</f>
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="O42" s="508" t="str">
         <f>+'Water '!$O20</f>
@@ -21446,7 +20986,7 @@
       <c r="AG42" s="508"/>
       <c r="AH42" s="540">
         <f>SUM($B42:AF42)</f>
-        <v>771</v>
+        <v>870</v>
       </c>
       <c r="AI42" s="508"/>
       <c r="AJ42" s="508"/>
@@ -21605,8 +21145,8 @@
       <c r="M43" s="542">
         <v>23</v>
       </c>
-      <c r="N43" s="542" t="str">
-        <v>0</v>
+      <c r="N43" s="542">
+        <v>26</v>
       </c>
       <c r="O43" s="542" t="str">
         <v>0</v>
@@ -21665,7 +21205,7 @@
       <c r="AG43" s="542"/>
       <c r="AH43" s="543">
         <f>SUM($B43:AF43)</f>
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="AI43" s="544"/>
       <c r="AJ43" s="474"/>
@@ -21835,9 +21375,9 @@
         <f>+'Water '!$M18</f>
         <v>5</v>
       </c>
-      <c r="N44" s="508" t="str">
+      <c r="N44" s="508">
         <f>+'Water '!$M19</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O44" s="657" t="str">
         <f>+'Water '!$M20</f>
@@ -21914,7 +21454,7 @@
       <c r="AG44" s="508"/>
       <c r="AH44" s="484">
         <f>SUM($B44:AF44)</f>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AI44" s="484"/>
       <c r="AJ44" s="291"/>
@@ -22084,9 +21624,9 @@
         <f>+'Water '!$Q18</f>
         <v>71</v>
       </c>
-      <c r="N45" s="539" t="str">
+      <c r="N45" s="539">
         <f>+'Water '!$Q19</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O45" s="539" t="str">
         <f>'Water '!$Q20</f>
@@ -22163,7 +21703,7 @@
       <c r="AG45" s="539"/>
       <c r="AH45" s="514">
         <f>SUM($B45:AF45)</f>
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="AI45" s="514"/>
       <c r="AJ45" s="514"/>
@@ -22801,7 +22341,7 @@
       </c>
       <c r="N50" s="484">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="O50" s="484">
         <f t="shared" si="8"/>
@@ -22878,7 +22418,7 @@
       <c r="AG50" s="484"/>
       <c r="AH50" s="484">
         <f>SUM($B50:AF50)</f>
-        <v>3086</v>
+        <v>3342</v>
       </c>
       <c r="AI50" s="484"/>
     </row>
@@ -23022,9 +22562,9 @@
         <f t="shared" si="10"/>
         <v>3.0362067656807428</v>
       </c>
-      <c r="N54" s="545" t="str">
+      <c r="N54" s="545">
         <f t="shared" si="10"/>
-        <v/>
+        <v>1.5118114665625977</v>
       </c>
       <c r="O54" s="545" t="str">
         <f t="shared" si="10"/>
@@ -23101,14 +22641,14 @@
       <c r="AG54" s="545"/>
       <c r="AH54" s="546">
         <f>+(AH36*10)/AH$9</f>
-        <v>5.8797699208644154</v>
+        <v>5.1073748627878723</v>
       </c>
       <c r="AI54" s="546">
         <v>3.2</v>
       </c>
       <c r="AJ54" s="547">
         <f t="shared" ref="AJ54:AJ67" si="11">AI54-AH54</f>
-        <v>-2.6797699208644152</v>
+        <v>-1.9073748627878722</v>
       </c>
     </row>
     <row r="55" spans="1:59" s="553" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -23234,9 +22774,9 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="N56" s="545" t="str">
+      <c r="N56" s="545">
         <f t="shared" si="16"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O56" s="545" t="str">
         <f t="shared" si="16"/>
@@ -23398,9 +22938,9 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N57" s="549" t="str">
+      <c r="N57" s="549">
         <f t="shared" si="19"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O57" s="549" t="str">
         <f t="shared" si="19"/>
@@ -23562,9 +23102,9 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="N58" s="545" t="str">
+      <c r="N58" s="545">
         <f t="shared" si="20"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O58" s="545" t="str">
         <f t="shared" si="20"/>
@@ -23728,9 +23268,9 @@
         <f t="shared" si="21"/>
         <v>1.2229166139547436</v>
       </c>
-      <c r="N59" s="549" t="str">
+      <c r="N59" s="549">
         <f t="shared" si="21"/>
-        <v/>
+        <v>0.4746384836882574</v>
       </c>
       <c r="O59" s="549" t="str">
         <f t="shared" si="21"/>
@@ -23807,14 +23347,14 @@
       <c r="AG59" s="549"/>
       <c r="AH59" s="549">
         <f t="shared" si="12"/>
-        <v>1.4048005205918834</v>
+        <v>1.2403180585832994</v>
       </c>
       <c r="AI59" s="550">
         <v>0.7</v>
       </c>
       <c r="AJ59" s="551">
         <f t="shared" si="11"/>
-        <v>-0.70480052059188347</v>
+        <v>-0.5403180585832994</v>
       </c>
       <c r="AK59" s="474"/>
       <c r="AL59" s="474"/>
@@ -23892,9 +23432,9 @@
         <f t="shared" si="22"/>
         <v>5.0181750710556718</v>
       </c>
-      <c r="N60" s="545" t="str">
+      <c r="N60" s="545">
         <f t="shared" si="22"/>
-        <v/>
+        <v>1.7403411068569439</v>
       </c>
       <c r="O60" s="545" t="str">
         <f t="shared" si="22"/>
@@ -23971,14 +23511,14 @@
       <c r="AG60" s="545"/>
       <c r="AH60" s="568">
         <f t="shared" si="12"/>
-        <v>2.911562369291242</v>
+        <v>2.7044529096929084</v>
       </c>
       <c r="AI60" s="555">
         <v>2.1</v>
       </c>
       <c r="AJ60" s="547">
         <f t="shared" si="11"/>
-        <v>-0.81156236929124193</v>
+        <v>-0.60445290969290832</v>
       </c>
     </row>
     <row r="61" spans="1:59" s="504" customFormat="1" x14ac:dyDescent="0.35">
@@ -24033,9 +23573,9 @@
         <f t="shared" si="23"/>
         <v>0.96989938348134841</v>
       </c>
-      <c r="N61" s="549" t="str">
+      <c r="N61" s="549">
         <f t="shared" si="23"/>
-        <v/>
+        <v>0.45705928058869233</v>
       </c>
       <c r="O61" s="549" t="str">
         <f t="shared" si="23"/>
@@ -24112,14 +23652,14 @@
       <c r="AG61" s="549"/>
       <c r="AH61" s="550">
         <f t="shared" si="12"/>
-        <v>0.52113567699376317</v>
+        <v>0.50980491630992752</v>
       </c>
       <c r="AI61" s="550">
         <v>0.7</v>
       </c>
       <c r="AJ61" s="551">
         <f t="shared" si="11"/>
-        <v>0.17886432300623678</v>
+        <v>0.19019508369007243</v>
       </c>
       <c r="AK61" s="474"/>
       <c r="AL61" s="474"/>
@@ -24197,9 +23737,9 @@
         <f t="shared" si="24"/>
         <v>0.21084769206116269</v>
       </c>
-      <c r="N62" s="545" t="str">
+      <c r="N62" s="545">
         <f t="shared" si="24"/>
-        <v/>
+        <v>5.2737609298695268E-2</v>
       </c>
       <c r="O62" s="545" t="str">
         <f>IF(O$9=0,"",+(O44*10)/O$9)</f>
@@ -24276,14 +23816,14 @@
       <c r="AG62" s="545"/>
       <c r="AH62" s="555">
         <f>+(AH44*10)/AH$9</f>
-        <v>9.0632291651089256E-2</v>
+        <v>8.3931297197366125E-2</v>
       </c>
       <c r="AI62" s="555">
         <v>0.1</v>
       </c>
       <c r="AJ62" s="547">
         <f t="shared" si="11"/>
-        <v>9.3677083489107499E-3</v>
+        <v>1.606870280263388E-2</v>
       </c>
     </row>
     <row r="63" spans="1:59" s="504" customFormat="1" x14ac:dyDescent="0.35">
@@ -24338,9 +23878,9 @@
         <f t="shared" si="25"/>
         <v>2.9940372272685103</v>
       </c>
-      <c r="N63" s="569" t="str">
+      <c r="N63" s="569">
         <f t="shared" si="25"/>
-        <v/>
+        <v>0.26368804649347632</v>
       </c>
       <c r="O63" s="569" t="str">
         <f t="shared" si="25"/>
@@ -24417,14 +23957,14 @@
       <c r="AG63" s="549"/>
       <c r="AH63" s="550">
         <f>+(AH45*10)/AH$9</f>
-        <v>0.84590138874349974</v>
+        <v>0.74294740852483343</v>
       </c>
       <c r="AI63" s="550">
         <v>0.6</v>
       </c>
       <c r="AJ63" s="551">
         <f t="shared" si="11"/>
-        <v>-0.24590138874349976</v>
+        <v>-0.14294740852483345</v>
       </c>
       <c r="AK63" s="474"/>
       <c r="AL63" s="474"/>
@@ -24570,9 +24110,9 @@
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="N65" s="549" t="str">
+      <c r="N65" s="549">
         <f t="shared" si="26"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O65" s="549" t="str">
         <f t="shared" si="26"/>
@@ -24872,7 +24412,7 @@
       </c>
       <c r="N68" s="585">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>4.5002759934886623</v>
       </c>
       <c r="O68" s="585">
         <f t="shared" si="27"/>
@@ -24949,7 +24489,7 @@
       <c r="AG68" s="585"/>
       <c r="AH68" s="584">
         <f t="shared" si="27"/>
-        <v>11.653802168135892</v>
+        <v>10.388829453096209</v>
       </c>
       <c r="AI68" s="584">
         <f>SUM(AI54:AI63,AI65)</f>
@@ -24957,7 +24497,7 @@
       </c>
       <c r="AJ68" s="547">
         <f t="shared" si="27"/>
-        <v>-2.0538021681358929</v>
+        <v>-0.78882945309620678</v>
       </c>
       <c r="AK68" s="468"/>
       <c r="AL68" s="291"/>
@@ -25037,7 +24577,7 @@
       </c>
       <c r="N69" s="588">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>2.2501379967443311</v>
       </c>
       <c r="O69" s="588">
         <f t="shared" si="28"/>
@@ -25114,7 +24654,7 @@
       <c r="AG69" s="588"/>
       <c r="AH69" s="587">
         <f t="shared" si="28"/>
-        <v>3.5233303379360947</v>
+        <v>3.2981891232002019</v>
       </c>
       <c r="AI69" s="587">
         <f t="shared" si="28"/>
@@ -25122,7 +24662,7 @@
       </c>
       <c r="AJ69" s="587">
         <f t="shared" si="28"/>
-        <v>-0.62333033793609438</v>
+        <v>-0.398189123200202</v>
       </c>
       <c r="AK69" s="589"/>
       <c r="AL69" s="291"/>
@@ -25235,9 +24775,9 @@
         <f>+'Water '!$F18</f>
         <v>247</v>
       </c>
-      <c r="N71" s="593" t="str">
+      <c r="N71" s="593">
         <f>+'Water '!$F19</f>
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="O71" s="593" t="str">
         <f>+'Water '!$F20</f>
@@ -25314,7 +24854,7 @@
       <c r="AG71" s="593"/>
       <c r="AH71" s="594">
         <f>SUM($B71:AF71)</f>
-        <v>1680</v>
+        <v>1794</v>
       </c>
       <c r="AI71" s="594"/>
       <c r="AJ71" s="595"/>
@@ -25454,13 +24994,13 @@
       <c r="K74" s="877">
         <v>800</v>
       </c>
-      <c r="L74" s="900">
-        <v>300</v>
-      </c>
-      <c r="M74" s="898">
-        <v>1300</v>
-      </c>
-      <c r="N74" s="877"/>
+      <c r="L74" s="899"/>
+      <c r="M74" s="896">
+        <v>1500</v>
+      </c>
+      <c r="N74" s="877">
+        <v>2100</v>
+      </c>
       <c r="O74" s="877"/>
       <c r="P74" s="877"/>
       <c r="Q74" s="791"/>
@@ -25484,7 +25024,7 @@
       </c>
       <c r="AH74" s="516">
         <f>SUM(B74:AF74)</f>
-        <v>14400</v>
+        <v>16400</v>
       </c>
       <c r="AI74" s="537"/>
       <c r="AJ74" s="537"/>
@@ -25553,8 +25093,8 @@
       <c r="M75" s="601">
         <v>1256.1700000000419</v>
       </c>
-      <c r="N75" s="601" t="str">
-        <v>0</v>
+      <c r="N75" s="601">
+        <v>2027.25</v>
       </c>
       <c r="O75" s="601" t="str">
         <v>0</v>
@@ -25613,7 +25153,7 @@
       <c r="AG75" s="599"/>
       <c r="AH75" s="516">
         <f>SUM(B75:AF75)</f>
-        <v>12144.599999999977</v>
+        <v>14171.849999999977</v>
       </c>
       <c r="AI75" s="600"/>
       <c r="AJ75" s="600"/>
@@ -25681,8 +25221,8 @@
       <c r="M76" s="604">
         <v>244.5399999999936</v>
       </c>
-      <c r="N76" s="604" t="str">
-        <v>0</v>
+      <c r="N76" s="604">
+        <v>285.63000000000466</v>
       </c>
       <c r="O76" s="604" t="str">
         <v>0</v>
@@ -25741,7 +25281,7 @@
       <c r="AG76" s="604"/>
       <c r="AH76" s="604">
         <f>SUM($B76:AF76)</f>
-        <v>1594.8899999999994</v>
+        <v>1880.5200000000041</v>
       </c>
       <c r="AI76" s="605"/>
       <c r="AJ76" s="606"/>
@@ -25810,8 +25350,8 @@
       <c r="M77" s="607">
         <v>591.47999999999593</v>
       </c>
-      <c r="N77" s="607" t="str">
-        <v>0</v>
+      <c r="N77" s="607">
+        <v>282.16000000000349</v>
       </c>
       <c r="O77" s="607" t="str">
         <v>0</v>
@@ -25870,7 +25410,7 @@
       <c r="AG77" s="607"/>
       <c r="AH77" s="604">
         <f>SUM($B77:AF77)</f>
-        <v>4355.5800000000017</v>
+        <v>4637.7400000000052</v>
       </c>
       <c r="AI77" s="757"/>
       <c r="AJ77" s="757" t="s">
@@ -25953,7 +25493,7 @@
       </c>
       <c r="N78" s="788">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1459.4599999999919</v>
       </c>
       <c r="O78" s="788">
         <f t="shared" si="29"/>
@@ -26033,7 +25573,7 @@
       </c>
       <c r="AH78" s="484">
         <f>AH75-AH76-AH77</f>
-        <v>6194.1299999999756</v>
+        <v>7653.5899999999674</v>
       </c>
       <c r="AI78" s="484"/>
     </row>
@@ -26208,7 +25748,7 @@
         <v>8829</v>
       </c>
       <c r="N80" s="613">
-        <v>0</v>
+        <v>5822</v>
       </c>
       <c r="O80" s="613">
         <v>0</v>
@@ -26267,7 +25807,7 @@
       <c r="AG80" s="613"/>
       <c r="AH80" s="594">
         <f>SUM(B80:AF80)</f>
-        <v>71069</v>
+        <v>76891</v>
       </c>
       <c r="AI80" s="594"/>
       <c r="AJ80" s="614"/>
@@ -26398,7 +25938,7 @@
         <v>10110.299999999999</v>
       </c>
       <c r="L82" s="617">
-        <v>0</v>
+        <v>7167.4</v>
       </c>
       <c r="M82" s="617">
         <v>0</v>
@@ -26455,7 +25995,7 @@
         <v>0</v>
       </c>
       <c r="AE82" s="617">
-        <v>85862.499999999985</v>
+        <v>93029.89999999998</v>
       </c>
       <c r="AF82" s="617">
         <v>0</v>
@@ -26463,7 +26003,7 @@
       <c r="AG82" s="617"/>
       <c r="AH82" s="594">
         <f>SUM(B82:AF82)</f>
-        <v>154638.20000000001</v>
+        <v>168973</v>
       </c>
       <c r="AI82" s="594"/>
       <c r="AJ82" s="614"/>
@@ -26533,7 +26073,7 @@
         <v>1281.3</v>
       </c>
       <c r="N83" s="621">
-        <v>0</v>
+        <v>1345.4</v>
       </c>
       <c r="O83" s="621">
         <v>0</v>
@@ -26592,7 +26132,7 @@
       <c r="AG83" s="621"/>
       <c r="AH83" s="594">
         <f>SUM(B83:AF83)</f>
-        <v>14793.499999999998</v>
+        <v>16138.899999999998</v>
       </c>
       <c r="AI83" s="594"/>
       <c r="AJ83" s="594"/>
@@ -26661,8 +26201,8 @@
       <c r="M84" s="620">
         <v>3450.3000000000466</v>
       </c>
-      <c r="N84" s="620" t="str">
-        <v>0</v>
+      <c r="N84" s="620">
+        <v>2133.5999999998603</v>
       </c>
       <c r="O84" s="620" t="str">
         <v>0</v>
@@ -26721,7 +26261,7 @@
       <c r="AG84" s="620"/>
       <c r="AH84" s="621">
         <f>SUM($B84:AF84)</f>
-        <v>26301.300000000047</v>
+        <v>28434.899999999907</v>
       </c>
       <c r="AI84" s="594"/>
       <c r="AJ84" s="614"/>
@@ -27146,9 +26686,9 @@
         <f t="shared" si="33"/>
         <v>16.066594135060598</v>
       </c>
-      <c r="N90" s="653" t="str">
+      <c r="N90" s="653">
         <f t="shared" si="33"/>
-        <v/>
+        <v>6.0999834755490863</v>
       </c>
       <c r="O90" s="653" t="str">
         <f>IF(O$9=0,"",+(O22*10)/O$9)</f>
@@ -27225,18 +26765,18 @@
       <c r="AG90" s="627"/>
       <c r="AH90" s="659">
         <f>IF(AH$9=0,"0",+(AH22*10)/AH$9)</f>
-        <v>12.801811195716358</v>
+        <v>11.616713245428045</v>
       </c>
       <c r="AI90" s="662">
         <v>10.199999999999999</v>
       </c>
       <c r="AJ90" s="665">
         <f>+AI90-AH90</f>
-        <v>-2.6018111957163583</v>
+        <v>-1.4167132454280456</v>
       </c>
       <c r="AK90" s="667">
         <f>AH90/AI90*100</f>
-        <v>125.50795289917997</v>
+        <v>113.88934554341222</v>
       </c>
       <c r="AL90" s="629"/>
       <c r="AM90" s="630"/>
@@ -27378,11 +26918,11 @@
       </c>
       <c r="M92" s="653">
         <f t="shared" si="35"/>
-        <v>5.48203999359023</v>
-      </c>
-      <c r="N92" s="653" t="str">
+        <v>6.3254307618348804</v>
+      </c>
+      <c r="N92" s="653">
         <f t="shared" si="35"/>
-        <v/>
+        <v>3.6916326509086685</v>
       </c>
       <c r="O92" s="653" t="str">
         <f t="shared" si="35"/>
@@ -27459,18 +26999,18 @@
       <c r="AG92" s="628"/>
       <c r="AH92" s="670">
         <f>IF(AH$9=0,"0",+(AH74)/AH$9)</f>
-        <v>5.4379374990653551</v>
+        <v>5.0980491630992759</v>
       </c>
       <c r="AI92" s="674">
         <v>5</v>
       </c>
       <c r="AJ92" s="675">
         <f>AI92-AH92</f>
-        <v>-0.43793749906535506</v>
+        <v>-9.8049163099275916E-2</v>
       </c>
       <c r="AK92" s="673">
         <f t="shared" si="34"/>
-        <v>108.7587499813071</v>
+        <v>101.96098326198553</v>
       </c>
       <c r="AL92" s="629"/>
       <c r="AM92" s="630"/>
@@ -27549,9 +27089,9 @@
         <f t="shared" si="36"/>
         <v>1.0312138923327074</v>
       </c>
-      <c r="N93" s="653" t="str">
+      <c r="N93" s="653">
         <f t="shared" si="36"/>
-        <v/>
+        <v>0.50211477813288585</v>
       </c>
       <c r="O93" s="653" t="str">
         <f t="shared" si="36"/>
@@ -27628,18 +27168,18 @@
       <c r="AG93" s="628"/>
       <c r="AH93" s="670">
         <f>IF(AH$9=0,"0",+AH76/AH$9)</f>
-        <v>0.60228556513085707</v>
+        <v>0.58457215927996775</v>
       </c>
       <c r="AI93" s="674">
         <v>1.7</v>
       </c>
       <c r="AJ93" s="676">
         <f>AI93-AH93</f>
-        <v>1.0977144348691428</v>
+        <v>1.1154278407200322</v>
       </c>
       <c r="AK93" s="673">
         <f t="shared" si="34"/>
-        <v>35.428562654756298</v>
+        <v>34.386597604703987</v>
       </c>
       <c r="AL93" s="635"/>
       <c r="AM93" s="636"/>
@@ -27716,9 +27256,9 @@
         <f t="shared" si="37"/>
         <v>42.634668420919461</v>
       </c>
-      <c r="N94" s="653" t="str">
+      <c r="N94" s="653">
         <f t="shared" si="37"/>
-        <v/>
+        <v>12.599718029582281</v>
       </c>
       <c r="O94" s="653" t="str">
         <f>IF(O$9=0,"",(O80+O83)/O$9)</f>
@@ -27795,18 +27335,18 @@
       <c r="AG94" s="627"/>
       <c r="AH94" s="670">
         <f>IF(AH$9=0,"0",+(AH80+AH83)/AH$9)</f>
-        <v>32.424646424548548</v>
+        <v>28.918963648671298</v>
       </c>
       <c r="AI94" s="674">
         <v>22</v>
       </c>
       <c r="AJ94" s="675">
         <f>AI94-AH94</f>
-        <v>-10.424646424548548</v>
+        <v>-6.9189636486712978</v>
       </c>
       <c r="AK94" s="673">
         <f>AH94/AI94*100</f>
-        <v>147.38475647522066</v>
+        <v>131.44983476668773</v>
       </c>
       <c r="AL94" s="629"/>
       <c r="AM94" s="630"/>
@@ -27866,7 +27406,7 @@
       <c r="AG95" s="637"/>
       <c r="AH95" s="670">
         <f>IF(AH$9=0,"0",+(AH78*10)/AH$9)</f>
-        <v>23.391174861864968</v>
+        <v>23.791693959880988</v>
       </c>
       <c r="AI95" s="674"/>
       <c r="AJ95" s="676"/>
@@ -27949,9 +27489,9 @@
         <f t="shared" si="39"/>
         <v>14.549755838372789</v>
       </c>
-      <c r="N96" s="654" t="str">
+      <c r="N96" s="654">
         <f t="shared" si="39"/>
-        <v/>
+        <v>3.750698773322962</v>
       </c>
       <c r="O96" s="654" t="str">
         <f t="shared" si="39"/>
@@ -28028,18 +27568,18 @@
       <c r="AG96" s="627"/>
       <c r="AH96" s="660">
         <f>IF(AH$9=0,"0",+(AH84)/AH$9)</f>
-        <v>9.9322795516783255</v>
+        <v>8.839177935842141</v>
       </c>
       <c r="AI96" s="663">
         <v>7.2</v>
       </c>
       <c r="AJ96" s="677">
         <f>AI96-AH96</f>
-        <v>-2.7322795516783254</v>
+        <v>-1.6391779358421408</v>
       </c>
       <c r="AK96" s="668">
         <f t="shared" si="34"/>
-        <v>137.9483271066434</v>
+        <v>122.76636022002974</v>
       </c>
       <c r="AL96" s="629"/>
       <c r="AM96" s="630"/>
@@ -28543,7 +28083,7 @@
       </c>
       <c r="N103" s="521">
         <f>IF('Entries October 2026'!L19-'Entries October 2026'!L18&lt;1,0,'Entries October 2026'!L19-'Entries October 2026'!L18)</f>
-        <v>0</v>
+        <v>282.16000000000349</v>
       </c>
       <c r="O103" s="521">
         <f>IF('Entries October 2026'!L20-'Entries October 2026'!L19&lt;1,0,'Entries October 2026'!L20-'Entries October 2026'!L19)</f>
@@ -28688,9 +28228,9 @@
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="N105" s="652" t="str">
+      <c r="N105" s="652">
         <f t="shared" si="41"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O105" s="652" t="str">
         <f t="shared" si="41"/>
@@ -29006,7 +28546,7 @@
       </c>
       <c r="N116" s="650">
         <f>'Daily KPIs'!N80</f>
-        <v>0</v>
+        <v>5822</v>
       </c>
       <c r="O116" s="650">
         <f>'Daily KPIs'!O80</f>
@@ -29083,7 +28623,7 @@
       <c r="AG116" s="650"/>
       <c r="AH116" s="649">
         <f>'Daily KPIs'!AH80</f>
-        <v>71069</v>
+        <v>76891</v>
       </c>
     </row>
     <row r="117" spans="2:34" hidden="1" x14ac:dyDescent="0.35">
@@ -29173,7 +28713,7 @@
       </c>
       <c r="AH140" s="870">
         <f>AH83/(AH83+AH80)</f>
-        <v>0.17229291017615372</v>
+        <v>0.17348078413499315</v>
       </c>
       <c r="AM140" s="751"/>
     </row>
@@ -29310,45 +28850,45 @@
   </mergeCells>
   <phoneticPr fontId="32" type="noConversion"/>
   <conditionalFormatting sqref="B93:C93 AH93">
-    <cfRule type="cellIs" dxfId="82" priority="127" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="35" priority="127" operator="greaterThan">
       <formula>$AI$93</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B90:AF90">
-    <cfRule type="cellIs" dxfId="81" priority="36" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="34" priority="36" operator="greaterThan">
       <formula>10.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92:AF92">
-    <cfRule type="cellIs" dxfId="80" priority="26" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="33" priority="26" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="27" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="32" priority="27" operator="lessThanOrEqual">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:AF93">
-    <cfRule type="cellIs" dxfId="78" priority="34" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="34" operator="greaterThan">
       <formula>1.7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B94:AF94">
-    <cfRule type="cellIs" dxfId="77" priority="33" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="30" priority="33" operator="greaterThan">
       <formula>22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96:AF96">
-    <cfRule type="cellIs" dxfId="76" priority="32" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="29" priority="32" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:AG22">
-    <cfRule type="cellIs" dxfId="75" priority="101" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="28" priority="101" operator="greaterThan">
       <formula>400</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42:AG42">
-    <cfRule type="cellIs" dxfId="74" priority="47" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="27" priority="47" operator="greaterThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29363,129 +28903,129 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B94:AG94">
-    <cfRule type="cellIs" dxfId="73" priority="1174" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="1174" operator="greaterThan">
       <formula>$AI$94</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96:AG96">
-    <cfRule type="cellIs" dxfId="72" priority="1176" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="25" priority="1176" operator="greaterThan">
       <formula>$AI$96</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:AH15">
-    <cfRule type="cellIs" dxfId="71" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="greaterThan">
       <formula>3.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54:AH54">
-    <cfRule type="cellIs" dxfId="70" priority="123" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="23" priority="123" operator="greaterThan">
       <formula>3.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B56:AH56">
-    <cfRule type="cellIs" dxfId="69" priority="61" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="22" priority="61" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B57:AH57 B59:AH59 B61:AH61">
-    <cfRule type="cellIs" dxfId="68" priority="62" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="21" priority="62" operator="greaterThan">
       <formula>0.7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58:AH58 B62:AH62">
-    <cfRule type="cellIs" dxfId="67" priority="63" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="63" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B60:AH60">
-    <cfRule type="cellIs" dxfId="66" priority="22" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="19" priority="22" operator="greaterThan">
       <formula>2.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B65:AH65">
-    <cfRule type="cellIs" dxfId="65" priority="56" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="56" operator="greaterThan">
       <formula>0.3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68:AH68">
-    <cfRule type="cellIs" dxfId="64" priority="58" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="58" operator="greaterThan">
       <formula>9.6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69:AH69">
-    <cfRule type="cellIs" dxfId="63" priority="59" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="59" operator="greaterThan">
       <formula>2.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92:AH92">
-    <cfRule type="cellIs" dxfId="62" priority="48" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="48" operator="greaterThan">
       <formula>5.04</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:AH93">
-    <cfRule type="cellIs" dxfId="61" priority="44" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="44" operator="greaterThan">
       <formula>1.7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="43" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="43" operator="greaterThan">
       <formula>1.7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96:AH96">
-    <cfRule type="cellIs" dxfId="59" priority="37" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="37" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E96">
-    <cfRule type="cellIs" dxfId="58" priority="39" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="39" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I63:AH63">
-    <cfRule type="cellIs" dxfId="57" priority="68" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="68" operator="greaterThan">
       <formula>0.6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC54:AG54">
-    <cfRule type="cellIs" dxfId="56" priority="82" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="82" operator="greaterThan">
       <formula>$AI$54</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC55:AG59 AC61:AG61 AC63:AG63 B64:AG64">
-    <cfRule type="cellIs" dxfId="55" priority="1135" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="1135" operator="greaterThan">
       <formula>$AI59</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH94">
-    <cfRule type="cellIs" dxfId="54" priority="28" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="28" operator="lessThanOrEqual">
       <formula>22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH94:AH96 B90:AH90 AH91">
-    <cfRule type="cellIs" dxfId="53" priority="1168" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="1168" operator="greaterThan">
       <formula>$AI$90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH96">
-    <cfRule type="cellIs" dxfId="52" priority="29" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="29" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="30" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="30" operator="lessThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="40" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="40" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ8">
-    <cfRule type="cellIs" dxfId="49" priority="105" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="105" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="106" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="106" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK90:AK96">
-    <cfRule type="cellIs" dxfId="47" priority="50" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="50" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30528,11 +30068,11 @@
       </c>
       <c r="C19" s="55">
         <f t="shared" si="1"/>
-        <v>-254838</v>
+        <v>235</v>
       </c>
       <c r="D19" s="55">
         <f t="shared" si="2"/>
-        <v>1112878</v>
+        <v>121</v>
       </c>
       <c r="E19" s="56">
         <f>'Entries October 2026'!W18</f>
@@ -30544,7 +30084,7 @@
       </c>
       <c r="G19" s="57">
         <f t="shared" si="7"/>
-        <v>-1367716</v>
+        <v>114</v>
       </c>
       <c r="H19" s="57">
         <f>'Entries October 2026'!AA18</f>
@@ -30552,7 +30092,7 @@
       </c>
       <c r="I19" s="58">
         <f t="shared" si="3"/>
-        <v>-97122</v>
+        <v>0</v>
       </c>
       <c r="J19" s="57">
         <f>'Entries October 2026'!T18</f>
@@ -30564,7 +30104,7 @@
       </c>
       <c r="L19" s="58">
         <f t="shared" si="6"/>
-        <v>-97122</v>
+        <v>0</v>
       </c>
       <c r="M19" s="57">
         <f>'Entries October 2026'!R18</f>
@@ -30572,11 +30112,11 @@
       </c>
       <c r="N19" s="57">
         <f>'Entries October 2026'!AC19-'Entries October 2026'!AC18</f>
-        <v>-6888</v>
+        <v>26</v>
       </c>
       <c r="O19" s="57">
         <f t="shared" si="5"/>
-        <v>-509676</v>
+        <v>470</v>
       </c>
       <c r="P19" s="62"/>
       <c r="Q19" s="45"/>
@@ -30591,15 +30131,15 @@
       </c>
       <c r="B20" s="55">
         <f>'Entries October 2026'!O19</f>
-        <v>0</v>
+        <v>255073</v>
       </c>
       <c r="C20" s="55">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-255073</v>
       </c>
       <c r="D20" s="55">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1112757</v>
       </c>
       <c r="E20" s="56">
         <f>'Entries October 2026'!W19</f>
@@ -30607,19 +30147,19 @@
       </c>
       <c r="F20" s="57">
         <f>'Entries October 2026'!V19</f>
-        <v>0</v>
+        <v>1367830</v>
       </c>
       <c r="G20" s="57">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-1367830</v>
       </c>
       <c r="H20" s="57">
         <f>'Entries October 2026'!AA19</f>
-        <v>0</v>
+        <v>97122</v>
       </c>
       <c r="I20" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-97122</v>
       </c>
       <c r="J20" s="57">
         <f>'Entries October 2026'!T19</f>
@@ -30631,7 +30171,7 @@
       </c>
       <c r="L20" s="58">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-97122</v>
       </c>
       <c r="M20" s="57">
         <f>'Entries October 2026'!R19</f>
@@ -30639,11 +30179,11 @@
       </c>
       <c r="N20" s="57">
         <f>'Entries October 2026'!AC20-'Entries October 2026'!AC19</f>
-        <v>0</v>
+        <v>-6914</v>
       </c>
       <c r="O20" s="57">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-510146</v>
       </c>
       <c r="P20" s="62"/>
       <c r="Q20" s="45"/>
@@ -31788,24 +31328,24 @@
     </row>
     <row r="6" spans="1:20" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="930" t="s">
+      <c r="A7" s="929" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="383"/>
       <c r="C7" s="383"/>
-      <c r="D7" s="943" t="s">
+      <c r="D7" s="942" t="s">
         <v>254</v>
       </c>
-      <c r="E7" s="946" t="s">
+      <c r="E7" s="945" t="s">
         <v>286</v>
       </c>
-      <c r="F7" s="940" t="s">
+      <c r="F7" s="939" t="s">
         <v>287</v>
       </c>
-      <c r="G7" s="936" t="s">
+      <c r="G7" s="935" t="s">
         <v>255</v>
       </c>
-      <c r="H7" s="936" t="s">
+      <c r="H7" s="935" t="s">
         <v>256</v>
       </c>
       <c r="I7" s="383" t="s">
@@ -31817,33 +31357,33 @@
       <c r="K7" s="390" t="s">
         <v>53</v>
       </c>
-      <c r="L7" s="937" t="s">
+      <c r="L7" s="936" t="s">
         <v>17</v>
       </c>
-      <c r="M7" s="938"/>
-      <c r="N7" s="938"/>
-      <c r="O7" s="938"/>
-      <c r="P7" s="939"/>
-      <c r="Q7" s="934" t="s">
+      <c r="M7" s="937"/>
+      <c r="N7" s="937"/>
+      <c r="O7" s="937"/>
+      <c r="P7" s="938"/>
+      <c r="Q7" s="933" t="s">
         <v>11</v>
       </c>
-      <c r="R7" s="935"/>
-      <c r="S7" s="935"/>
-      <c r="T7" s="935"/>
+      <c r="R7" s="934"/>
+      <c r="S7" s="934"/>
+      <c r="T7" s="934"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="931"/>
+      <c r="A8" s="930"/>
       <c r="B8" s="384" t="s">
         <v>257</v>
       </c>
       <c r="C8" s="384" t="s">
         <v>258</v>
       </c>
-      <c r="D8" s="944"/>
-      <c r="E8" s="947"/>
-      <c r="F8" s="941"/>
-      <c r="G8" s="936"/>
-      <c r="H8" s="936"/>
+      <c r="D8" s="943"/>
+      <c r="E8" s="946"/>
+      <c r="F8" s="940"/>
+      <c r="G8" s="935"/>
+      <c r="H8" s="935"/>
       <c r="I8" s="383"/>
       <c r="J8" s="383"/>
       <c r="K8" s="390"/>
@@ -31866,12 +31406,12 @@
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A9" s="932"/>
+      <c r="A9" s="931"/>
       <c r="B9" s="385"/>
       <c r="C9" s="385"/>
-      <c r="D9" s="945"/>
-      <c r="E9" s="948"/>
-      <c r="F9" s="942"/>
+      <c r="D9" s="944"/>
+      <c r="E9" s="947"/>
+      <c r="F9" s="941"/>
       <c r="G9" s="383" t="s">
         <v>56</v>
       </c>
@@ -32747,7 +32287,7 @@
       </c>
       <c r="K20" s="775">
         <f>'CO2'!E17</f>
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="L20" s="776">
         <f>+'PROD.FIG. '!F15</f>
@@ -32826,7 +32366,7 @@
       </c>
       <c r="K21" s="722">
         <f>'CO2'!E18</f>
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="L21" s="723">
         <f>+'PROD.FIG. '!F16</f>
@@ -32868,9 +32408,9 @@
       <c r="A22" s="719">
         <v>13</v>
       </c>
-      <c r="B22" s="719" t="str">
+      <c r="B22" s="719">
         <f>IF('Entries October 2026'!I19&lt;'Entries October 2026'!I18,"0",(IF('Entries October 2026'!I19&gt;='Entries October 2026'!I18,'Entries October 2026'!I19-'Entries October 2026'!I18,(999999-'Entries October 2026'!I18)+'Entries October 2026'!I19+1)))</f>
-        <v>0</v>
+        <v>5822</v>
       </c>
       <c r="C22" s="719" t="str">
         <f>IF('Entries October 2026'!J19&lt;='Entries October 2026'!J18,"0",IF('Entries October 2026'!J19&gt;='Entries October 2026'!J18,'Entries October 2026'!J19-'Entries October 2026'!J18,(999999-'Entries October 2026'!J18)+'Entries October 2026'!J19+1))</f>
@@ -32878,24 +32418,24 @@
       </c>
       <c r="D22" s="720">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5822</v>
       </c>
       <c r="E22" s="873"/>
-      <c r="F22" s="721" t="str">
+      <c r="F22" s="721">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G22" s="737" t="str">
+      <c r="G22" s="737">
         <f>IF('Entries October 2026'!K19&lt;'Entries October 2026'!K18,"0",IF('Entries October 2026'!K19&gt;='Entries October 2026'!K18,'Entries October 2026'!K19-'Entries October 2026'!K18,(999999-'Entries October 2026'!K18)+'Entries October 2026'!K19+1))</f>
         <v>0</v>
       </c>
       <c r="H22" s="720">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5822</v>
       </c>
       <c r="I22" s="737">
         <f>'Water '!Z19*10</f>
-        <v>0</v>
+        <v>3470</v>
       </c>
       <c r="J22" s="720" t="str">
         <f>IF('Entries October 2026'!B19-'Entries October 2026'!B18&lt;1,"0",'Entries October 2026'!B19-'Entries October 2026'!B18)</f>
@@ -32903,7 +32443,7 @@
       </c>
       <c r="K22" s="722">
         <f>'CO2'!E19</f>
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="L22" s="723">
         <f>+'PROD.FIG. '!F17</f>
@@ -32922,15 +32462,15 @@
         <v>0</v>
       </c>
       <c r="P22" s="724">
-        <v>0</v>
+        <v>568.85400000000004</v>
       </c>
       <c r="Q22" s="393">
         <f>IF(P22=0,0,H22/P22)</f>
-        <v>0</v>
+        <v>10.234612044566795</v>
       </c>
       <c r="R22" s="393">
         <f>IF(Q22=0,0,I22/P22)</f>
-        <v>0</v>
+        <v>6.0999834755490863</v>
       </c>
       <c r="S22" s="393">
         <f>IF(R22=0,0,J22/P22)</f>
@@ -32945,7 +32485,7 @@
       <c r="A23" s="719">
         <v>14</v>
       </c>
-      <c r="B23" s="719">
+      <c r="B23" s="719" t="str">
         <f>IF('Entries October 2026'!I20&lt;'Entries October 2026'!I19,"0",(IF('Entries October 2026'!I20&gt;='Entries October 2026'!I19,'Entries October 2026'!I20-'Entries October 2026'!I19,(999999-'Entries October 2026'!I19)+'Entries October 2026'!I20+1)))</f>
         <v>0</v>
       </c>
@@ -32962,7 +32502,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G23" s="737">
+      <c r="G23" s="737" t="str">
         <f>IF('Entries October 2026'!K20&lt;'Entries October 2026'!K19,"0",IF('Entries October 2026'!K20&gt;='Entries October 2026'!K19,'Entries October 2026'!K20-'Entries October 2026'!K19,(999999-'Entries October 2026'!K19)+'Entries October 2026'!K20+1))</f>
         <v>0</v>
       </c>
@@ -34408,7 +33948,7 @@
       <c r="C43" s="19"/>
       <c r="D43" s="20">
         <f>SUM(D10:D40)</f>
-        <v>71069</v>
+        <v>76891</v>
       </c>
       <c r="E43" s="741">
         <f>SUM(E10:E40)</f>
@@ -34416,7 +33956,7 @@
       </c>
       <c r="F43" s="754">
         <f>IF((E43+D43)=0,"0",E43/(D43+E43))</f>
-        <v>0.17229291017615372</v>
+        <v>0.16135224601759293</v>
       </c>
       <c r="G43" s="20">
         <f t="shared" ref="G43:P43" si="7">SUM(G10:G40)</f>
@@ -34424,11 +33964,11 @@
       </c>
       <c r="H43" s="20">
         <f t="shared" si="7"/>
-        <v>85862.499999999985</v>
+        <v>91684.499999999985</v>
       </c>
       <c r="I43" s="20">
         <f t="shared" si="7"/>
-        <v>33900</v>
+        <v>37370</v>
       </c>
       <c r="J43" s="20">
         <f t="shared" si="7"/>
@@ -34436,7 +33976,7 @@
       </c>
       <c r="K43" s="20">
         <f t="shared" si="7"/>
-        <v>14400</v>
+        <v>16400</v>
       </c>
       <c r="L43" s="20">
         <f t="shared" si="7"/>
@@ -34456,7 +33996,7 @@
       </c>
       <c r="P43" s="403">
         <f t="shared" si="7"/>
-        <v>2648.0627999999997</v>
+        <v>3216.9168</v>
       </c>
       <c r="Q43" s="408" t="s">
         <v>13</v>
@@ -34484,7 +34024,7 @@
       </c>
       <c r="E44" s="728">
         <f>D43+E43</f>
-        <v>85862.5</v>
+        <v>91684.5</v>
       </c>
       <c r="F44" s="708"/>
       <c r="G44" s="7"/>
@@ -34499,19 +34039,19 @@
       <c r="P44" s="401"/>
       <c r="Q44" s="397">
         <f>IF(P43=0,0,H43/P43)</f>
-        <v>32.424646424548541</v>
+        <v>28.500737103303383</v>
       </c>
       <c r="R44" s="398">
         <f>IF(Q44=0,0,I43/P43)</f>
-        <v>12.801811195716358</v>
+        <v>11.616713245428045</v>
       </c>
       <c r="S44" s="398">
         <f>IF(R44=0,0,J43/P43)</f>
-        <v>0.36252916660435702</v>
+        <v>0.29842239003507953</v>
       </c>
       <c r="T44" s="399">
         <f>IF(S44=0,0,K43/P43)</f>
-        <v>5.4379374990653551</v>
+        <v>5.0980491630992759</v>
       </c>
     </row>
     <row r="45" spans="1:32" ht="15" x14ac:dyDescent="0.2">
@@ -34544,12 +34084,12 @@
       <c r="T46" s="2"/>
     </row>
     <row r="47" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="D47" s="933"/>
-      <c r="E47" s="933"/>
-      <c r="F47" s="933"/>
-      <c r="G47" s="933"/>
-      <c r="H47" s="933"/>
-      <c r="I47" s="933"/>
+      <c r="D47" s="932"/>
+      <c r="E47" s="932"/>
+      <c r="F47" s="932"/>
+      <c r="G47" s="932"/>
+      <c r="H47" s="932"/>
+      <c r="I47" s="932"/>
       <c r="AF47" t="s">
         <v>55</v>
       </c>
@@ -34588,41 +34128,41 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="Q10:Q44">
-    <cfRule type="cellIs" dxfId="109" priority="7" operator="between">
+    <cfRule type="cellIs" dxfId="62" priority="7" operator="between">
       <formula>0</formula>
       <formula>22</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="61" priority="8" operator="greaterThan">
       <formula>22</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="107" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="60" priority="9" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:R44">
-    <cfRule type="cellIs" dxfId="106" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="59" priority="1" operator="between">
       <formula>0</formula>
       <formula>10.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="2" operator="greaterThan">
       <formula>10.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S10:S44">
-    <cfRule type="cellIs" dxfId="104" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="57" priority="3" operator="between">
       <formula>0</formula>
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="56" priority="4" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T10:T44">
-    <cfRule type="cellIs" dxfId="102" priority="5" operator="between">
+    <cfRule type="cellIs" dxfId="55" priority="5" operator="between">
       <formula>0</formula>
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="54" priority="6" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34654,16 +34194,16 @@
       <c r="B2" s="8"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="949" t="s">
+      <c r="A3" s="948" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="951" t="s">
+      <c r="B3" s="950" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="950"/>
-      <c r="B4" s="952"/>
+      <c r="A4" s="949"/>
+      <c r="B4" s="951"/>
     </row>
     <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="36">
@@ -35027,31 +34567,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="961" t="s">
+      <c r="A1" s="960" t="s">
         <v>304</v>
       </c>
-      <c r="B1" s="962"/>
-      <c r="C1" s="962"/>
-      <c r="D1" s="962"/>
-      <c r="E1" s="962"/>
-      <c r="F1" s="962"/>
-      <c r="G1" s="962"/>
-      <c r="H1" s="962"/>
-      <c r="I1" s="962"/>
-      <c r="J1" s="962"/>
-      <c r="K1" s="962"/>
-      <c r="L1" s="962"/>
-      <c r="M1" s="962"/>
+      <c r="B1" s="961"/>
+      <c r="C1" s="961"/>
+      <c r="D1" s="961"/>
+      <c r="E1" s="961"/>
+      <c r="F1" s="961"/>
+      <c r="G1" s="961"/>
+      <c r="H1" s="961"/>
+      <c r="I1" s="961"/>
+      <c r="J1" s="961"/>
+      <c r="K1" s="961"/>
+      <c r="L1" s="961"/>
+      <c r="M1" s="961"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
       <c r="F2" s="9"/>
-      <c r="M2" s="953" t="s">
+      <c r="M2" s="952" t="s">
         <v>296</v>
       </c>
-      <c r="N2" s="953" t="s">
+      <c r="N2" s="952" t="s">
         <v>297</v>
       </c>
     </row>
@@ -35060,11 +34600,11 @@
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="9"/>
-      <c r="M3" s="954"/>
-      <c r="N3" s="954"/>
+      <c r="M3" s="953"/>
+      <c r="N3" s="953"/>
     </row>
     <row r="4" spans="1:17" s="339" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="967" t="s">
+      <c r="A4" s="966" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="847" t="s">
@@ -35097,22 +34637,22 @@
       <c r="K4" s="848" t="s">
         <v>40</v>
       </c>
-      <c r="L4" s="963" t="s">
+      <c r="L4" s="962" t="s">
         <v>243</v>
       </c>
-      <c r="M4" s="965" t="s">
+      <c r="M4" s="964" t="s">
         <v>246</v>
       </c>
-      <c r="N4" s="955" t="s">
+      <c r="N4" s="954" t="s">
         <v>246</v>
       </c>
-      <c r="O4" s="958" t="s">
+      <c r="O4" s="957" t="s">
         <v>298</v>
       </c>
       <c r="P4" s="350"/>
     </row>
     <row r="5" spans="1:17" s="339" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="968"/>
+      <c r="A5" s="967"/>
       <c r="B5" s="864" t="s">
         <v>41</v>
       </c>
@@ -35143,10 +34683,10 @@
       <c r="K5" s="865" t="s">
         <v>44</v>
       </c>
-      <c r="L5" s="964"/>
-      <c r="M5" s="966"/>
-      <c r="N5" s="956"/>
-      <c r="O5" s="959"/>
+      <c r="L5" s="963"/>
+      <c r="M5" s="965"/>
+      <c r="N5" s="955"/>
+      <c r="O5" s="958"/>
       <c r="P5" s="350"/>
     </row>
     <row r="6" spans="1:17" s="73" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -35163,8 +34703,8 @@
       <c r="K6" s="836"/>
       <c r="L6" s="869"/>
       <c r="M6" s="833"/>
-      <c r="N6" s="957"/>
-      <c r="O6" s="960"/>
+      <c r="N6" s="956"/>
+      <c r="O6" s="959"/>
       <c r="P6" s="350"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
@@ -35840,13 +35380,13 @@
         <f>IF('Entries October 2026'!B19-'Entries October 2026'!B18&lt;1,"0",'Entries October 2026'!B19-'Entries October 2026'!B18)</f>
         <v>0</v>
       </c>
-      <c r="C19" s="739" t="str">
+      <c r="C19" s="739">
         <f>IF('Entries October 2026'!F19-'Entries October 2026'!F18&lt;1,"0",'Entries October 2026'!F19-'Entries October 2026'!F18)</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="839" t="str">
+        <v>20.299999999999272</v>
+      </c>
+      <c r="D19" s="839">
         <f>IF('Entries October 2026'!C19-'Entries October 2026'!C18&lt;1,"0",'Entries October 2026'!C19-'Entries October 2026'!C18)</f>
-        <v>0</v>
+        <v>2133.5999999998603</v>
       </c>
       <c r="E19" s="843" t="str">
         <f t="shared" si="0"/>
@@ -35858,7 +35398,7 @@
       </c>
       <c r="G19" s="837"/>
       <c r="H19" s="739"/>
-      <c r="I19" s="740" t="str">
+      <c r="I19" s="740">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -35870,20 +35410,20 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L19" s="831" t="str">
-        <v>0</v>
-      </c>
-      <c r="M19" s="829" t="str">
+      <c r="L19" s="831">
+        <v>568.85400000000004</v>
+      </c>
+      <c r="M19" s="829">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N19" s="829" t="str">
+      <c r="N19" s="829">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.750698773322962</v>
       </c>
       <c r="O19" s="830">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-2133.5999999998603</v>
       </c>
       <c r="P19" s="333"/>
     </row>
@@ -36882,11 +36422,11 @@
       </c>
       <c r="C38" s="388">
         <f>SUM(C7:C37)</f>
-        <v>175.90000000000146</v>
+        <v>196.20000000000073</v>
       </c>
       <c r="D38" s="840">
         <f t="shared" si="7"/>
-        <v>26301.300000000047</v>
+        <v>28434.899999999907</v>
       </c>
       <c r="E38" s="845"/>
       <c r="F38" s="846">
@@ -36903,7 +36443,7 @@
       </c>
       <c r="I38" s="797">
         <f>B38/C38</f>
-        <v>5.4576463899942702</v>
+        <v>4.892966360856251</v>
       </c>
       <c r="J38" s="355"/>
       <c r="K38" s="356">
@@ -36912,15 +36452,15 @@
       </c>
       <c r="L38" s="828">
         <f>SUM(L7:L37)</f>
-        <v>2648.0627999999997</v>
+        <v>3216.9168</v>
       </c>
       <c r="M38" s="834">
         <f>IF(L38=0,"0",(K38/L38))</f>
-        <v>0.36252916660435702</v>
+        <v>0.29842239003507953</v>
       </c>
       <c r="N38" s="834">
         <f>IF(L38=0,"0",(D38/L38))</f>
-        <v>9.9322795516783255</v>
+        <v>8.839177935842141</v>
       </c>
       <c r="O38" s="835"/>
     </row>
@@ -36934,7 +36474,7 @@
       </c>
       <c r="C39" s="802">
         <f>AVERAGE(C7:C37)</f>
-        <v>14.658333333333454</v>
+        <v>15.092307692307749</v>
       </c>
       <c r="D39" s="30"/>
       <c r="E39" s="30"/>
@@ -37554,27 +37094,27 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="C7:C37">
-    <cfRule type="cellIs" dxfId="100" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="53" priority="13" operator="greaterThan">
       <formula>24</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7:N37">
-    <cfRule type="cellIs" dxfId="99" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="52" priority="9" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="11" operator="between">
+    <cfRule type="cellIs" dxfId="51" priority="11" operator="between">
       <formula>0</formula>
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7:N38">
-    <cfRule type="cellIs" dxfId="97" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="1" operator="lessThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="49" priority="2" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="95" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="48" priority="4" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -37618,120 +37158,120 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="961"/>
-      <c r="B1" s="962"/>
-      <c r="C1" s="962"/>
-      <c r="D1" s="962"/>
-      <c r="E1" s="962"/>
-      <c r="F1" s="962"/>
-      <c r="G1" s="962"/>
-      <c r="H1" s="962"/>
-      <c r="I1" s="962"/>
-      <c r="J1" s="962"/>
-      <c r="K1" s="962"/>
-      <c r="L1" s="962"/>
-      <c r="M1" s="962"/>
-      <c r="N1" s="962"/>
-      <c r="O1" s="962"/>
-      <c r="P1" s="962"/>
-      <c r="Q1" s="962"/>
-      <c r="R1" s="962"/>
-      <c r="S1" s="962"/>
-      <c r="T1" s="962"/>
-      <c r="U1" s="962"/>
-      <c r="V1" s="962"/>
-      <c r="W1" s="962"/>
-      <c r="X1" s="962"/>
-      <c r="Y1" s="962"/>
-      <c r="Z1" s="962"/>
-      <c r="AA1" s="962"/>
+      <c r="A1" s="960"/>
+      <c r="B1" s="961"/>
+      <c r="C1" s="961"/>
+      <c r="D1" s="961"/>
+      <c r="E1" s="961"/>
+      <c r="F1" s="961"/>
+      <c r="G1" s="961"/>
+      <c r="H1" s="961"/>
+      <c r="I1" s="961"/>
+      <c r="J1" s="961"/>
+      <c r="K1" s="961"/>
+      <c r="L1" s="961"/>
+      <c r="M1" s="961"/>
+      <c r="N1" s="961"/>
+      <c r="O1" s="961"/>
+      <c r="P1" s="961"/>
+      <c r="Q1" s="961"/>
+      <c r="R1" s="961"/>
+      <c r="S1" s="961"/>
+      <c r="T1" s="961"/>
+      <c r="U1" s="961"/>
+      <c r="V1" s="961"/>
+      <c r="W1" s="961"/>
+      <c r="X1" s="961"/>
+      <c r="Y1" s="961"/>
+      <c r="Z1" s="961"/>
+      <c r="AA1" s="961"/>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C2" s="17"/>
     </row>
     <row r="3" spans="1:31" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="973" t="s">
+      <c r="B4" s="980" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="971" t="s">
+      <c r="C4" s="972" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="969" t="s">
+      <c r="D4" s="977" t="s">
         <v>106</v>
       </c>
-      <c r="E4" s="971" t="s">
+      <c r="E4" s="972" t="s">
         <v>107</v>
       </c>
-      <c r="F4" s="969" t="s">
+      <c r="F4" s="977" t="s">
         <v>239</v>
       </c>
-      <c r="G4" s="969" t="s">
+      <c r="G4" s="977" t="s">
         <v>108</v>
       </c>
-      <c r="H4" s="969" t="s">
+      <c r="H4" s="977" t="s">
         <v>161</v>
       </c>
-      <c r="I4" s="971" t="s">
+      <c r="I4" s="972" t="s">
         <v>207</v>
       </c>
-      <c r="J4" s="971" t="s">
+      <c r="J4" s="972" t="s">
         <v>109</v>
       </c>
-      <c r="K4" s="971" t="s">
+      <c r="K4" s="972" t="s">
         <v>174</v>
       </c>
-      <c r="L4" s="971" t="s">
+      <c r="L4" s="972" t="s">
         <v>173</v>
       </c>
-      <c r="M4" s="971" t="s">
+      <c r="M4" s="972" t="s">
         <v>103</v>
       </c>
       <c r="N4" s="48"/>
       <c r="O4" s="48"/>
       <c r="P4" s="48"/>
       <c r="Q4" s="48"/>
-      <c r="R4" s="969" t="s">
+      <c r="R4" s="977" t="s">
         <v>110</v>
       </c>
-      <c r="S4" s="969" t="s">
+      <c r="S4" s="977" t="s">
         <v>240</v>
       </c>
       <c r="T4" s="48"/>
-      <c r="U4" s="971" t="s">
+      <c r="U4" s="972" t="s">
         <v>153</v>
       </c>
       <c r="V4" s="48"/>
       <c r="W4" s="48"/>
-      <c r="X4" s="971" t="s">
+      <c r="X4" s="972" t="s">
         <v>175</v>
       </c>
-      <c r="Y4" s="971" t="s">
+      <c r="Y4" s="972" t="s">
         <v>176</v>
       </c>
-      <c r="Z4" s="978" t="s">
+      <c r="Z4" s="970" t="s">
         <v>247</v>
       </c>
-      <c r="AA4" s="980" t="s">
+      <c r="AA4" s="974" t="s">
         <v>243</v>
       </c>
-      <c r="AB4" s="976" t="s">
+      <c r="AB4" s="968" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:31" s="300" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="974"/>
-      <c r="C5" s="972"/>
-      <c r="D5" s="970"/>
-      <c r="E5" s="975"/>
-      <c r="F5" s="970"/>
-      <c r="G5" s="970"/>
-      <c r="H5" s="970"/>
-      <c r="I5" s="975"/>
-      <c r="J5" s="975"/>
-      <c r="K5" s="975"/>
-      <c r="L5" s="975"/>
-      <c r="M5" s="975"/>
+      <c r="B5" s="981"/>
+      <c r="C5" s="979"/>
+      <c r="D5" s="978"/>
+      <c r="E5" s="973"/>
+      <c r="F5" s="978"/>
+      <c r="G5" s="978"/>
+      <c r="H5" s="978"/>
+      <c r="I5" s="973"/>
+      <c r="J5" s="973"/>
+      <c r="K5" s="973"/>
+      <c r="L5" s="973"/>
+      <c r="M5" s="973"/>
       <c r="N5" s="50" t="s">
         <v>111</v>
       </c>
@@ -37744,23 +37284,23 @@
       <c r="Q5" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="R5" s="970"/>
-      <c r="S5" s="970"/>
+      <c r="R5" s="978"/>
+      <c r="S5" s="978"/>
       <c r="T5" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="U5" s="982"/>
+      <c r="U5" s="976"/>
       <c r="V5" s="80" t="s">
         <v>156</v>
       </c>
       <c r="W5" s="80" t="s">
         <v>157</v>
       </c>
-      <c r="X5" s="975"/>
-      <c r="Y5" s="975"/>
-      <c r="Z5" s="979"/>
-      <c r="AA5" s="981"/>
-      <c r="AB5" s="977"/>
+      <c r="X5" s="973"/>
+      <c r="Y5" s="973"/>
+      <c r="Z5" s="971"/>
+      <c r="AA5" s="975"/>
+      <c r="AB5" s="969"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="21" t="s">
@@ -39107,33 +38647,33 @@
         <f>IF('Entries October 2026'!W19-'Entries October 2026'!W18&lt;1,"0",'Entries October 2026'!W19-'Entries October 2026'!W18)</f>
         <v>0</v>
       </c>
-      <c r="D19" s="693" t="str">
+      <c r="D19" s="693">
         <f>IF('Entries October 2026'!O19-'Entries October 2026'!O18&lt;1,"0",'Entries October 2026'!O19-'Entries October 2026'!O18)</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="693" t="str">
+        <v>235</v>
+      </c>
+      <c r="E19" s="693">
         <f>IF('Entries October 2026'!P19-'Entries October 2026'!P18&lt;1,"0",'Entries October 2026'!P19-'Entries October 2026'!P18)</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="693" t="str">
+        <v>112</v>
+      </c>
+      <c r="F19" s="693">
         <f>IF('Entries October 2026'!V19-'Entries October 2026'!V18&lt;1,"0",'Entries October 2026'!V19-'Entries October 2026'!V18)</f>
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="G19" s="693">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="H19" s="693">
         <f>IF('Entries October 2026'!Q19-'Entries October 2026'!Q18&lt;1,0,'Entries October 2026'!Q19-'Entries October 2026'!Q18)</f>
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="I19" s="693">
         <f>IF('Entries October 2026'!AG19-'Entries October 2026'!AG18&lt;1,0,'Entries October 2026'!AG19-'Entries October 2026'!AG18)</f>
         <v>0</v>
       </c>
-      <c r="J19" s="693" t="str">
+      <c r="J19" s="693">
         <f>IF('Entries October 2026'!S19-'Entries October 2026'!S18&lt;1,"0",'Entries October 2026'!S19-'Entries October 2026'!S18)</f>
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="K19" s="693" t="str">
         <f>IF('Entries October 2026'!R19-'Entries October 2026'!R18&lt;1,"0",'Entries October 2026'!R19-'Entries October 2026'!R18)</f>
@@ -39143,25 +38683,25 @@
         <f>IF('Entries October 2026'!T19-'Entries October 2026'!T18&lt;1,"0",'Entries October 2026'!T19-'Entries October 2026'!T18)</f>
         <v>0</v>
       </c>
-      <c r="M19" s="693" t="str">
+      <c r="M19" s="693">
         <f>IF('Entries October 2026'!U19-'Entries October 2026'!U18&lt;1,"0",'Entries October 2026'!U19-'Entries October 2026'!U18)</f>
-        <v>0</v>
-      </c>
-      <c r="N19" s="693" t="str">
+        <v>3</v>
+      </c>
+      <c r="N19" s="693">
         <f>IF('Entries October 2026'!X19-'Entries October 2026'!X18&lt;1,"0",'Entries October 2026'!X19-'Entries October 2026'!X18)</f>
-        <v>0</v>
-      </c>
-      <c r="O19" s="693" t="str">
+        <v>27</v>
+      </c>
+      <c r="O19" s="693">
         <f>IF('Entries October 2026'!Y19-'Entries October 2026'!Y18&lt;1,"0",'Entries October 2026'!Y19-'Entries October 2026'!Y18)</f>
-        <v>0</v>
-      </c>
-      <c r="P19" s="693" t="str">
+        <v>99</v>
+      </c>
+      <c r="P19" s="693">
         <f>IF('Entries October 2026'!AC19-'Entries October 2026'!AC18&lt;1,"0",'Entries October 2026'!AC19-'Entries October 2026'!AC18)</f>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="693" t="str">
+        <v>26</v>
+      </c>
+      <c r="Q19" s="693">
         <f>IF('Entries October 2026'!Z19-'Entries October 2026'!Z18&lt;1,"0",'Entries October 2026'!Z19-'Entries October 2026'!Z18)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R19" s="693" t="str">
         <f>IF(('Entries October 2026'!AA19-'Entries October 2026'!AA18)+('Entries October 2026'!AB19-'Entries October 2026'!AB18)&lt;1,"0",('Entries October 2026'!AA19-'Entries October 2026'!AA18)+('Entries October 2026'!AB19-'Entries October 2026'!AB18))</f>
@@ -39169,15 +38709,15 @@
       </c>
       <c r="S19" s="692">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2330</v>
       </c>
       <c r="T19" s="692">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U19" s="693" t="str">
+        <v>129</v>
+      </c>
+      <c r="U19" s="693">
         <f>IF('Entries October 2026'!AC19-'Entries October 2026'!AC18&lt;1,"0",'Entries October 2026'!AC19-'Entries October 2026'!AC18)</f>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="V19" s="693" t="str">
         <f>IF('Entries October 2026'!AD19-'Entries October 2026'!AD18&lt;1,"0",'Entries October 2026'!AD19-'Entries October 2026'!AD18)</f>
@@ -39197,14 +38737,14 @@
       </c>
       <c r="Z19" s="329">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AA19" s="330" t="str">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="331" t="str">
+        <v>347</v>
+      </c>
+      <c r="AA19" s="330">
+        <v>568.85400000000004</v>
+      </c>
+      <c r="AB19" s="331">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.0999834755490863</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.2">
@@ -41162,28 +40702,28 @@
       </c>
       <c r="D38" s="303">
         <f>SUM(D7:D37)</f>
-        <v>1844</v>
+        <v>2079</v>
       </c>
       <c r="E38" s="303">
         <f>SUM(E7:E37)</f>
-        <v>1546</v>
+        <v>1658</v>
       </c>
       <c r="F38" s="303">
         <f>SUM(F7:F37)</f>
-        <v>1680</v>
+        <v>1794</v>
       </c>
       <c r="G38" s="304">
         <f>SUM(G7:G37)</f>
-        <v>1710</v>
+        <v>1943</v>
       </c>
       <c r="H38" s="303">
         <f t="shared" si="5"/>
-        <v>1832</v>
+        <v>2071</v>
       </c>
       <c r="I38" s="303"/>
       <c r="J38" s="303">
         <f t="shared" si="5"/>
-        <v>1557</v>
+        <v>1643</v>
       </c>
       <c r="K38" s="303"/>
       <c r="L38" s="303">
@@ -41192,23 +40732,23 @@
       </c>
       <c r="M38" s="303">
         <f>SUM(M7:M37)</f>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="N38" s="303">
         <f t="shared" si="5"/>
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="O38" s="303">
         <f t="shared" si="5"/>
-        <v>771</v>
+        <v>870</v>
       </c>
       <c r="P38" s="303">
         <f>SUM(P7:P37)</f>
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="Q38" s="303">
         <f>SUM(Q7:Q37)</f>
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="R38" s="303">
         <f>SUM(R7:R34)</f>
@@ -41216,15 +40756,15 @@
       </c>
       <c r="S38" s="304">
         <f>SUM(S7:S37)</f>
-        <v>17100</v>
+        <v>19430</v>
       </c>
       <c r="T38" s="304">
         <f>SUM(T7:T37)</f>
-        <v>1167</v>
+        <v>1296</v>
       </c>
       <c r="U38" s="303">
         <f>SUM(U7:U37)</f>
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="V38" s="303">
         <f>SUM(V7:V37)</f>
@@ -41235,22 +40775,22 @@
       <c r="Y38" s="303"/>
       <c r="Z38" s="332">
         <f>SUM(Z7:Z37)</f>
-        <v>3390</v>
+        <v>3737</v>
       </c>
       <c r="AA38" s="332">
         <f>SUM(AA7:AA37)</f>
-        <v>2648.0627999999997</v>
+        <v>3216.9168</v>
       </c>
       <c r="AB38" s="331">
         <f>IF(AA38=0,"0",(Z38*10/AA38))</f>
-        <v>12.801811195716358</v>
+        <v>11.616713245428045</v>
       </c>
       <c r="AC38" s="321">
         <v>10.199999999999999</v>
       </c>
       <c r="AD38" s="340">
         <f>AB38/AC38*100</f>
-        <v>125.50795289917997</v>
+        <v>113.88934554341222</v>
       </c>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.2">
@@ -41289,7 +40829,7 @@
       <c r="C40" s="15"/>
       <c r="D40" s="15">
         <f>D38*220</f>
-        <v>405680</v>
+        <v>457380</v>
       </c>
       <c r="E40" s="15"/>
       <c r="F40" s="15"/>
@@ -41381,7 +40921,7 @@
       <c r="C43" s="17"/>
       <c r="D43" s="17">
         <f>+D41*D40</f>
-        <v>6413.8008000000009</v>
+        <v>7231.1778000000004</v>
       </c>
       <c r="E43" s="17"/>
       <c r="F43" s="36"/>
@@ -41434,7 +40974,7 @@
     <row r="45" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D45" s="17">
         <f>SUM(D43:D44)</f>
-        <v>6692.7708000000011</v>
+        <v>7510.1478000000006</v>
       </c>
       <c r="E45" s="17"/>
       <c r="F45" s="36"/>
@@ -41456,7 +40996,7 @@
       </c>
       <c r="D47" s="23">
         <f>+D45*2/3</f>
-        <v>4461.8472000000011</v>
+        <v>5006.7652000000007</v>
       </c>
       <c r="E47" s="324"/>
       <c r="F47" s="36"/>
@@ -41479,7 +41019,7 @@
       <c r="C49" s="24"/>
       <c r="D49" s="28">
         <f>SUM(D47,D45)</f>
-        <v>11154.618000000002</v>
+        <v>12516.913</v>
       </c>
       <c r="E49" s="325"/>
       <c r="F49" s="36"/>
@@ -41844,6 +41384,16 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:AA1"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="R4:R5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="E4:E5"/>
     <mergeCell ref="AB4:AB5"/>
     <mergeCell ref="Z4:Z5"/>
     <mergeCell ref="L4:L5"/>
@@ -41855,23 +41405,13 @@
     <mergeCell ref="Y4:Y5"/>
     <mergeCell ref="S4:S5"/>
     <mergeCell ref="M4:M5"/>
-    <mergeCell ref="A1:AA1"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="R4:R5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="E4:E5"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="AB6:AB38">
-    <cfRule type="cellIs" dxfId="94" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="1" operator="lessThan">
       <formula>10.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="46" priority="2" operator="greaterThan">
       <formula>10.2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -41902,15 +41442,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="983" t="s">
+      <c r="A1" s="982" t="s">
         <v>303</v>
       </c>
-      <c r="B1" s="984"/>
-      <c r="C1" s="984"/>
-      <c r="D1" s="985"/>
-      <c r="E1" s="984"/>
-      <c r="F1" s="984"/>
-      <c r="G1" s="986"/>
+      <c r="B1" s="983"/>
+      <c r="C1" s="983"/>
+      <c r="D1" s="984"/>
+      <c r="E1" s="983"/>
+      <c r="F1" s="983"/>
+      <c r="G1" s="985"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B2" s="9"/>
@@ -41923,7 +41463,7 @@
       <c r="D3" s="359"/>
     </row>
     <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="997" t="s">
+      <c r="A4" s="996" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="39" t="s">
@@ -41935,19 +41475,19 @@
       <c r="D4" s="361" t="s">
         <v>285</v>
       </c>
-      <c r="E4" s="987" t="s">
+      <c r="E4" s="986" t="s">
         <v>245</v>
       </c>
-      <c r="F4" s="990" t="s">
+      <c r="F4" s="989" t="s">
         <v>243</v>
       </c>
-      <c r="G4" s="993" t="s">
+      <c r="G4" s="992" t="s">
         <v>253</v>
       </c>
-      <c r="H4" s="996"/>
+      <c r="H4" s="995"/>
     </row>
     <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="998"/>
+      <c r="A5" s="997"/>
       <c r="B5" s="34" t="s">
         <v>48</v>
       </c>
@@ -41957,20 +41497,20 @@
       <c r="D5" s="361" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="988"/>
-      <c r="F5" s="991"/>
-      <c r="G5" s="994"/>
-      <c r="H5" s="996"/>
+      <c r="E5" s="987"/>
+      <c r="F5" s="990"/>
+      <c r="G5" s="993"/>
+      <c r="H5" s="995"/>
     </row>
     <row r="6" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="999"/>
+      <c r="A6" s="998"/>
       <c r="B6" s="40"/>
       <c r="C6" s="362"/>
       <c r="D6" s="361"/>
-      <c r="E6" s="989"/>
-      <c r="F6" s="992"/>
-      <c r="G6" s="995"/>
-      <c r="H6" s="996"/>
+      <c r="E6" s="988"/>
+      <c r="F6" s="991"/>
+      <c r="G6" s="994"/>
+      <c r="H6" s="995"/>
     </row>
     <row r="7" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A7" s="686">
@@ -42339,27 +41879,26 @@
       </c>
       <c r="B19" s="761">
         <f>'Utility Analysis October 2026'!D22</f>
-        <v>0</v>
-      </c>
-      <c r="C19" s="762" t="str">
+        <v>5822</v>
+      </c>
+      <c r="C19" s="762">
         <f>'Utility Analysis October 2026'!G22</f>
         <v>0</v>
       </c>
       <c r="D19" s="763">
-        <f>'Utility Analysis October 2026'!E22</f>
-        <v>0</v>
+        <v>1345.4</v>
       </c>
       <c r="E19" s="764">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F19" s="765" t="str">
+        <v>7167.4</v>
+      </c>
+      <c r="F19" s="765">
         <f>'PROD.FIG. '!H17</f>
-        <v>0</v>
-      </c>
-      <c r="G19" s="456" t="str">
+        <v>568.85400000000004</v>
+      </c>
+      <c r="G19" s="456">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>12.599718029582281</v>
       </c>
       <c r="J19" s="30"/>
     </row>
@@ -42371,7 +41910,7 @@
         <f>'Utility Analysis October 2026'!D23</f>
         <v>0</v>
       </c>
-      <c r="C20" s="743">
+      <c r="C20" s="743" t="str">
         <f>'Utility Analysis October 2026'!G23</f>
         <v>0</v>
       </c>
@@ -42906,7 +42445,7 @@
       </c>
       <c r="B38" s="308">
         <f>SUM(B7:B37)</f>
-        <v>71069</v>
+        <v>76891</v>
       </c>
       <c r="C38" s="308">
         <f>SUM(C7:C37)</f>
@@ -42914,26 +42453,26 @@
       </c>
       <c r="D38" s="308">
         <f>SUM(D7:D37)</f>
-        <v>14793.499999999998</v>
+        <v>16138.899999999998</v>
       </c>
       <c r="E38" s="337">
         <f>SUM(E7:E37)</f>
-        <v>85862.499999999985</v>
+        <v>93029.89999999998</v>
       </c>
       <c r="F38" s="358">
         <f>SUM(F7:F37)</f>
-        <v>2648.0627999999997</v>
+        <v>3216.9168</v>
       </c>
       <c r="G38" s="338">
         <f>IF(F38=0,"0",(E38/F38))</f>
-        <v>32.424646424548541</v>
+        <v>28.918963648671294</v>
       </c>
       <c r="H38" s="335">
         <v>22</v>
       </c>
       <c r="I38" s="340">
         <f>G38/H38*100</f>
-        <v>147.38475647522066</v>
+        <v>131.4498347666877</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
@@ -42974,12 +42513,12 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="cellIs" dxfId="92" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="1" operator="lessThan">
       <formula>22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7:G38">
-    <cfRule type="cellIs" dxfId="91" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="44" priority="2" operator="greaterThan">
       <formula>21</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43010,16 +42549,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="1000" t="s">
+      <c r="A1" s="999" t="s">
         <v>302</v>
       </c>
-      <c r="B1" s="962"/>
-      <c r="C1" s="962"/>
-      <c r="D1" s="962"/>
-      <c r="E1" s="962"/>
-      <c r="F1" s="962"/>
-      <c r="G1" s="962"/>
-      <c r="H1" s="962"/>
+      <c r="B1" s="961"/>
+      <c r="C1" s="961"/>
+      <c r="D1" s="961"/>
+      <c r="E1" s="961"/>
+      <c r="F1" s="961"/>
+      <c r="G1" s="961"/>
+      <c r="H1" s="961"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D2" s="12"/>
@@ -43289,8 +42828,8 @@
       <c r="E17" s="756"/>
       <c r="F17" s="756"/>
       <c r="G17" s="756"/>
-      <c r="H17" s="808" t="str">
-        <v>0</v>
+      <c r="H17" s="808">
+        <v>568.85400000000004</v>
       </c>
       <c r="I17" s="298"/>
       <c r="J17" s="299"/>
@@ -43632,7 +43171,7 @@
       </c>
       <c r="H36" s="736">
         <f>SUM(H5:H35)</f>
-        <v>2648.0627999999997</v>
+        <v>3216.9168</v>
       </c>
       <c r="I36" s="298"/>
       <c r="J36" s="299"/>
@@ -43748,11 +43287,11 @@
       <c r="D3" s="85"/>
       <c r="E3" s="85"/>
       <c r="F3" s="1"/>
-      <c r="I3" s="1005" t="s">
+      <c r="I3" s="1012" t="s">
         <v>267</v>
       </c>
-      <c r="J3" s="1006"/>
-      <c r="K3" s="1007"/>
+      <c r="J3" s="1013"/>
+      <c r="K3" s="1014"/>
     </row>
     <row r="4" spans="1:24" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
@@ -43765,46 +43304,46 @@
         <v>250</v>
       </c>
       <c r="H4" s="347"/>
-      <c r="I4" s="1008" t="s">
+      <c r="I4" s="1015" t="s">
         <v>262</v>
       </c>
-      <c r="J4" s="1009"/>
-      <c r="K4" s="1010"/>
+      <c r="J4" s="1016"/>
+      <c r="K4" s="1017"/>
       <c r="M4" s="417"/>
       <c r="N4" s="417"/>
       <c r="O4" s="418"/>
       <c r="P4" s="418"/>
-      <c r="Q4" s="1020" t="s">
+      <c r="Q4" s="1027" t="s">
         <v>283</v>
       </c>
-      <c r="R4" s="1020"/>
-      <c r="S4" s="1020"/>
-      <c r="T4" s="1020"/>
+      <c r="R4" s="1027"/>
+      <c r="S4" s="1027"/>
+      <c r="T4" s="1027"/>
       <c r="U4" s="191"/>
       <c r="V4" s="417"/>
       <c r="W4" s="191"/>
       <c r="X4" s="191"/>
     </row>
     <row r="5" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="949" t="s">
+      <c r="A5" s="948" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="951" t="s">
+      <c r="B5" s="950" t="s">
         <v>251</v>
       </c>
-      <c r="C5" s="951" t="s">
+      <c r="C5" s="950" t="s">
         <v>282</v>
       </c>
-      <c r="D5" s="1027" t="s">
+      <c r="D5" s="1006" t="s">
         <v>279</v>
       </c>
-      <c r="E5" s="1027" t="s">
+      <c r="E5" s="1006" t="s">
         <v>280</v>
       </c>
-      <c r="F5" s="1025" t="s">
+      <c r="F5" s="1004" t="s">
         <v>243</v>
       </c>
-      <c r="G5" s="1022" t="s">
+      <c r="G5" s="1001" t="s">
         <v>249</v>
       </c>
       <c r="I5" s="419" t="s">
@@ -43816,43 +43355,43 @@
       <c r="K5" s="421" t="s">
         <v>265</v>
       </c>
-      <c r="M5" s="1011" t="s">
+      <c r="M5" s="1018" t="s">
         <v>266</v>
       </c>
-      <c r="N5" s="1012"/>
-      <c r="O5" s="1013"/>
+      <c r="N5" s="1019"/>
+      <c r="O5" s="1020"/>
       <c r="P5" s="422"/>
-      <c r="Q5" s="1014" t="s">
+      <c r="Q5" s="1021" t="s">
         <v>7</v>
       </c>
-      <c r="R5" s="1016" t="s">
+      <c r="R5" s="1023" t="s">
         <v>267</v>
       </c>
-      <c r="S5" s="1017"/>
+      <c r="S5" s="1024"/>
       <c r="T5" s="452" t="s">
         <v>268</v>
       </c>
       <c r="U5" s="423" t="s">
         <v>269</v>
       </c>
-      <c r="V5" s="1018" t="s">
+      <c r="V5" s="1025" t="s">
         <v>277</v>
       </c>
-      <c r="W5" s="1001" t="s">
+      <c r="W5" s="1008" t="s">
         <v>270</v>
       </c>
-      <c r="X5" s="1003" t="s">
+      <c r="X5" s="1010" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1021"/>
-      <c r="B6" s="1024"/>
-      <c r="C6" s="1024"/>
-      <c r="D6" s="1028"/>
-      <c r="E6" s="1028"/>
-      <c r="F6" s="1026"/>
-      <c r="G6" s="1023"/>
+      <c r="A6" s="1000"/>
+      <c r="B6" s="1003"/>
+      <c r="C6" s="1003"/>
+      <c r="D6" s="1007"/>
+      <c r="E6" s="1007"/>
+      <c r="F6" s="1005"/>
+      <c r="G6" s="1002"/>
       <c r="I6" s="424">
         <v>10</v>
       </c>
@@ -43871,7 +43410,7 @@
         <v>273</v>
       </c>
       <c r="P6" s="418"/>
-      <c r="Q6" s="1015"/>
+      <c r="Q6" s="1022"/>
       <c r="R6" s="448" t="s">
         <v>274</v>
       </c>
@@ -43884,9 +43423,9 @@
       <c r="U6" s="429" t="s">
         <v>275</v>
       </c>
-      <c r="V6" s="1019"/>
-      <c r="W6" s="1002"/>
-      <c r="X6" s="1004"/>
+      <c r="V6" s="1026"/>
+      <c r="W6" s="1009"/>
+      <c r="X6" s="1011"/>
     </row>
     <row r="7" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="715">
@@ -44648,7 +44187,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="716">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F17" s="717">
         <v>0</v>
@@ -44721,14 +44260,14 @@
         <v>1256.1700000000419</v>
       </c>
       <c r="E18" s="768">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="F18" s="769">
         <v>237.13800000000001</v>
       </c>
       <c r="G18" s="336">
         <f t="shared" si="1"/>
-        <v>5.48203999359023</v>
+        <v>6.3254307618348804</v>
       </c>
       <c r="I18" s="430">
         <v>130</v>
@@ -44781,27 +44320,27 @@
       <c r="A19" s="767">
         <v>13</v>
       </c>
-      <c r="B19" s="768" t="str">
+      <c r="B19" s="768">
         <f>IF('Entries October 2026'!N19-'Entries October 2026'!N18&lt;1,"0",'Entries October 2026'!N19-'Entries October 2026'!N18)</f>
-        <v>0</v>
-      </c>
-      <c r="C19" s="768" t="str">
+        <v>285.63000000000466</v>
+      </c>
+      <c r="C19" s="768">
         <f>IF('Entries October 2026'!L19-'Entries October 2026'!L18&lt;1,"0",'Entries October 2026'!L19-'Entries October 2026'!L18)</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="768" t="str">
+        <v>282.16000000000349</v>
+      </c>
+      <c r="D19" s="768">
         <f>IF('Entries October 2026'!M19-'Entries October 2026'!M18&lt;1,"0",'Entries October 2026'!M19-'Entries October 2026'!M18)</f>
-        <v>0</v>
+        <v>2027.25</v>
       </c>
       <c r="E19" s="768">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="F19" s="769">
-        <v>0</v>
-      </c>
-      <c r="G19" s="336" t="str">
+        <v>568.85400000000004</v>
+      </c>
+      <c r="G19" s="336">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3.6916326509086685</v>
       </c>
       <c r="I19" s="430">
         <v>140</v>
@@ -46173,27 +45712,27 @@
       </c>
       <c r="B38" s="713">
         <f>SUM(B7:B37)</f>
-        <v>1594.8899999999994</v>
+        <v>1880.5200000000041</v>
       </c>
       <c r="C38" s="713">
         <f>SUM(C7:C37)</f>
-        <v>4355.5800000000017</v>
+        <v>4637.7400000000052</v>
       </c>
       <c r="D38" s="713">
         <f>SUM(D7:D37)</f>
-        <v>12144.599999999977</v>
+        <v>14171.849999999977</v>
       </c>
       <c r="E38" s="713">
         <f>SUM(E7:E37)</f>
-        <v>14400</v>
+        <v>16400</v>
       </c>
       <c r="F38" s="714">
         <f>SUM(F7:F37)</f>
-        <v>2648.0627999999997</v>
+        <v>3216.9168</v>
       </c>
       <c r="G38" s="345">
         <f>IF(F38=0,"0",(E38/F38))</f>
-        <v>5.4379374990653551</v>
+        <v>5.0980491630992759</v>
       </c>
       <c r="H38" s="348">
         <v>5</v>
@@ -46355,13 +45894,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="C5:C6"/>
     <mergeCell ref="W5:W6"/>
     <mergeCell ref="X5:X6"/>
     <mergeCell ref="I3:K3"/>
@@ -46371,13 +45903,20 @@
     <mergeCell ref="R5:S5"/>
     <mergeCell ref="V5:V6"/>
     <mergeCell ref="Q4:T4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="C5:C6"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="G7:G38">
-    <cfRule type="cellIs" dxfId="90" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="43" priority="1" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="42" priority="3" operator="greaterThan">
       <formula>21</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46671,7 +46210,7 @@
         <v>31</v>
       </c>
       <c r="AG6" s="293"/>
-      <c r="AH6" s="901" t="s">
+      <c r="AH6" s="900" t="s">
         <v>216</v>
       </c>
       <c r="AI6" s="291"/>
@@ -46776,7 +46315,7 @@
       <c r="AG7" s="212" t="s">
         <v>19</v>
       </c>
-      <c r="AH7" s="901"/>
+      <c r="AH7" s="900"/>
       <c r="AI7" s="292" t="s">
         <v>229</v>
       </c>
@@ -46834,7 +46373,7 @@
       </c>
       <c r="N8" s="99">
         <f>'Daily KPIs'!N8</f>
-        <v>0</v>
+        <v>8619</v>
       </c>
       <c r="O8" s="99">
         <f>'Daily KPIs'!O8</f>
@@ -46904,14 +46443,14 @@
       </c>
       <c r="AG8" s="213">
         <f>SUM($B8:AF8)</f>
-        <v>34553</v>
+        <v>43172</v>
       </c>
       <c r="AH8" s="293">
         <v>96325</v>
       </c>
       <c r="AI8" s="294">
         <f>AG8-AH8</f>
-        <v>-61772</v>
+        <v>-53153</v>
       </c>
       <c r="AJ8" s="266"/>
       <c r="AK8" s="266"/>
@@ -46970,7 +46509,7 @@
       </c>
       <c r="N9" s="99">
         <f>'Daily KPIs'!N9</f>
-        <v>0</v>
+        <v>568.85400000000004</v>
       </c>
       <c r="O9" s="99">
         <f>'Daily KPIs'!O9</f>
@@ -47040,7 +46579,7 @@
       </c>
       <c r="AG9" s="215">
         <f>SUM($B9:AF9)</f>
-        <v>2648.0627999999997</v>
+        <v>3216.9168</v>
       </c>
       <c r="AH9" s="214"/>
       <c r="AI9" s="265"/>
@@ -47097,9 +46636,9 @@
         <f>'Daily KPIs'!M10</f>
         <v>Rose/CBfl</v>
       </c>
-      <c r="N10" s="163">
+      <c r="N10" s="163" t="str">
         <f>'Daily KPIs'!N10</f>
-        <v>0</v>
+        <v>CB</v>
       </c>
       <c r="O10" s="163">
         <f>'Daily KPIs'!O10</f>
@@ -47141,11 +46680,11 @@
         <f>'Daily KPIs'!X10</f>
         <v>0</v>
       </c>
-      <c r="Y10" s="1029">
+      <c r="Y10" s="1028">
         <f>'Daily KPIs'!Y10</f>
         <v>0</v>
       </c>
-      <c r="Z10" s="1029"/>
+      <c r="Z10" s="1028"/>
       <c r="AA10" s="163">
         <f>'Daily KPIs'!AA10</f>
         <v>0</v>
@@ -47544,9 +47083,9 @@
         <f>+'Water '!$D18</f>
         <v>144</v>
       </c>
-      <c r="N16" s="110" t="str">
+      <c r="N16" s="110">
         <f>+'Water '!$D19</f>
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="O16" s="110" t="str">
         <f>+'Water '!$D20</f>
@@ -47622,7 +47161,7 @@
       </c>
       <c r="AG16" s="220">
         <f>SUM($B16:AF16)</f>
-        <v>1844</v>
+        <v>2079</v>
       </c>
       <c r="AH16" s="221"/>
     </row>
@@ -47678,9 +47217,9 @@
         <f>+'Water '!$E18</f>
         <v>237</v>
       </c>
-      <c r="N17" s="112" t="str">
+      <c r="N17" s="112">
         <f>+'Water '!$E19</f>
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="O17" s="114" t="str">
         <f>+'Water '!$E20</f>
@@ -47756,7 +47295,7 @@
       </c>
       <c r="AG17" s="222">
         <f>SUM($B17:AF17)</f>
-        <v>1546</v>
+        <v>1658</v>
       </c>
       <c r="AH17" s="223"/>
       <c r="AI17" s="268"/>
@@ -47815,7 +47354,7 @@
       </c>
       <c r="N18" s="175">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>347</v>
       </c>
       <c r="O18" s="175">
         <f t="shared" si="0"/>
@@ -47891,7 +47430,7 @@
       </c>
       <c r="AG18" s="224">
         <f>SUM($B18:AF18)</f>
-        <v>3390</v>
+        <v>3737</v>
       </c>
       <c r="AH18" s="224"/>
       <c r="AI18" s="269"/>
@@ -48029,27 +47568,27 @@
       </c>
       <c r="N21" s="119">
         <f>0.73*(N96+N15)</f>
-        <v>0</v>
+        <v>83.22</v>
       </c>
       <c r="O21" s="119">
         <f>0.73*(O96+O15)</f>
-        <v>0</v>
+        <v>83.22</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>83.22</v>
       </c>
       <c r="Q21" s="119">
         <f>0.73*(Q96+Q15)</f>
-        <v>0</v>
+        <v>83.22</v>
       </c>
       <c r="R21" s="119">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>83.22</v>
       </c>
       <c r="S21" s="119">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>83.22</v>
       </c>
       <c r="T21" s="119">
         <f t="shared" si="1"/>
@@ -48105,16 +47644,16 @@
       </c>
       <c r="AG21" s="220">
         <f>SUM($B21:AF21)</f>
-        <v>1226.4000000000001</v>
+        <v>1725.7200000000003</v>
       </c>
       <c r="AH21" s="225">
         <f>AG24+AG37+AG28</f>
-        <v>3613</v>
+        <v>3968</v>
       </c>
       <c r="AI21" s="271"/>
       <c r="AJ21" s="272">
         <f>(AH21*10)/AG9</f>
-        <v>13.643936238974394</v>
+        <v>12.334792121449954</v>
       </c>
     </row>
     <row r="22" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -48346,7 +47885,7 @@
       </c>
       <c r="N24" s="112">
         <f>'Water '!H19</f>
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="O24" s="112">
         <f>'Water '!H20</f>
@@ -48422,7 +47961,7 @@
       </c>
       <c r="AG24" s="222">
         <f>SUM($B24:AF24)</f>
-        <v>1832</v>
+        <v>2071</v>
       </c>
       <c r="AH24" s="222"/>
       <c r="AI24" s="222"/>
@@ -48481,7 +48020,7 @@
       </c>
       <c r="N25" s="118">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="O25" s="118">
         <f t="shared" si="2"/>
@@ -48557,7 +48096,7 @@
       </c>
       <c r="AG25" s="224">
         <f>SUM($B25:AF25)</f>
-        <v>1832</v>
+        <v>2071</v>
       </c>
       <c r="AH25" s="224"/>
       <c r="AI25" s="269"/>
@@ -48614,9 +48153,9 @@
         <f t="shared" si="3"/>
         <v>7.1266519916672992</v>
       </c>
-      <c r="N26" s="125" t="str">
+      <c r="N26" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>4.201429540796056</v>
       </c>
       <c r="O26" s="125" t="str">
         <f>IF(O$9=0,"",+(O25*10)/O$9)</f>
@@ -48788,9 +48327,9 @@
         <f>+'Water '!$J18</f>
         <v>72</v>
       </c>
-      <c r="N28" s="127" t="str">
+      <c r="N28" s="127">
         <f>+'Water '!$J19</f>
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="O28" s="127" t="str">
         <f>+'Water '!$J20</f>
@@ -48866,7 +48405,7 @@
       </c>
       <c r="AG28" s="220">
         <f>SUM($B28:AF28)</f>
-        <v>1557</v>
+        <v>1643</v>
       </c>
       <c r="AH28" s="220"/>
       <c r="AI28" s="271"/>
@@ -49236,13 +48775,13 @@
         <f>'Water '!L19</f>
         <v>0</v>
       </c>
-      <c r="O32" s="133" t="str">
+      <c r="O32" s="133">
         <f>'Water '!M19</f>
-        <v>0</v>
-      </c>
-      <c r="P32" s="133" t="str">
+        <v>3</v>
+      </c>
+      <c r="P32" s="133">
         <f>'Water '!N19</f>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Q32" s="133" t="str">
         <f>'Water '!L22</f>
@@ -49310,7 +48849,7 @@
       </c>
       <c r="AG32" s="227">
         <f>SUM($B32:AF32)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AH32" s="227"/>
       <c r="AI32" s="227"/>
@@ -49367,17 +48906,17 @@
         <f>+'Water '!$N18</f>
         <v>29</v>
       </c>
-      <c r="N33" s="131" t="str">
+      <c r="N33" s="131">
         <f>+'Water '!$N19</f>
-        <v>0</v>
-      </c>
-      <c r="O33" s="131" t="str">
+        <v>27</v>
+      </c>
+      <c r="O33" s="131">
         <f>+'Water '!$N19</f>
-        <v>0</v>
-      </c>
-      <c r="P33" s="131" t="str">
+        <v>27</v>
+      </c>
+      <c r="P33" s="131">
         <f>+'Water '!$N19</f>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Q33" s="131" t="str">
         <f>+'Water '!$N22</f>
@@ -49445,7 +48984,7 @@
       </c>
       <c r="AG33" s="227">
         <f>SUM($B33:AF33)</f>
-        <v>372</v>
+        <v>453</v>
       </c>
       <c r="AH33" s="227"/>
       <c r="AI33" s="227"/>
@@ -49506,29 +49045,29 @@
         <f>+'Water '!$O18</f>
         <v>119</v>
       </c>
-      <c r="N34" s="134" t="str">
+      <c r="N34" s="134">
         <f>+'Water '!$O19</f>
-        <v>0</v>
-      </c>
-      <c r="O34" s="134" t="str">
+        <v>99</v>
+      </c>
+      <c r="O34" s="134">
         <f>+'Water '!$O19</f>
-        <v>0</v>
-      </c>
-      <c r="P34" s="134" t="str">
+        <v>99</v>
+      </c>
+      <c r="P34" s="134">
         <f>+'Water '!$O19</f>
-        <v>0</v>
-      </c>
-      <c r="Q34" s="134" t="str">
+        <v>99</v>
+      </c>
+      <c r="Q34" s="134">
         <f>+'Water '!$O19</f>
-        <v>0</v>
-      </c>
-      <c r="R34" s="134" t="str">
+        <v>99</v>
+      </c>
+      <c r="R34" s="134">
         <f>+'Water '!$O19</f>
-        <v>0</v>
-      </c>
-      <c r="S34" s="134" t="str">
+        <v>99</v>
+      </c>
+      <c r="S34" s="134">
         <f>+'Water '!$O19</f>
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="T34" s="134" t="str">
         <f>+'Water '!$O25</f>
@@ -49584,7 +49123,7 @@
       </c>
       <c r="AG34" s="228">
         <f>SUM($B34:AF34)</f>
-        <v>771</v>
+        <v>1365</v>
       </c>
       <c r="AH34" s="228"/>
       <c r="AI34" s="228"/>
@@ -49643,7 +49182,7 @@
       </c>
       <c r="N35" s="95">
         <f>IF('Entries October 2026'!AC19-'Entries October 2026'!AC18&lt;1,0,'Entries October 2026'!AC19-'Entries October 2026'!AC18)</f>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="O35" s="95">
         <f>IF('Entries October 2026'!AC20-'Entries October 2026'!AC19&lt;1,0,'Entries October 2026'!AC20-'Entries October 2026'!AC19)</f>
@@ -49719,7 +49258,7 @@
       </c>
       <c r="AG35" s="220">
         <f>SUM($B35:AF35)</f>
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="AH35" s="220"/>
       <c r="AI35" s="271"/>
@@ -49776,9 +49315,9 @@
         <f>+'Water '!$M18</f>
         <v>5</v>
       </c>
-      <c r="N36" s="110" t="str">
+      <c r="N36" s="110">
         <f>+'Water '!$M19</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O36" s="110" t="str">
         <f>+'Water '!$M20</f>
@@ -49854,7 +49393,7 @@
       </c>
       <c r="AG36" s="220">
         <f>SUM($B36:AF36)</f>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AH36" s="220"/>
       <c r="AI36" s="271"/>
@@ -49911,13 +49450,13 @@
         <f>+'Water '!$Q18</f>
         <v>71</v>
       </c>
-      <c r="N37" s="131" t="str">
+      <c r="N37" s="131">
         <f>+'Water '!$Q19</f>
-        <v>0</v>
-      </c>
-      <c r="O37" s="131" t="str">
+        <v>15</v>
+      </c>
+      <c r="O37" s="131">
         <f>+'Water '!$Q19</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P37" s="131" t="str">
         <f>+'Water '!$Q21</f>
@@ -49989,7 +49528,7 @@
       </c>
       <c r="AG37" s="227">
         <f>SUM($B37:AF37)</f>
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="AH37" s="227"/>
       <c r="AI37" s="227"/>
@@ -50401,27 +49940,27 @@
       </c>
       <c r="N42" s="138">
         <f>SUM(N28:N41)</f>
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="O42" s="138">
         <f>SUM(O28:O41)</f>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="P42" s="138">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="Q42" s="138">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="R42" s="138">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="S42" s="138">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="T42" s="138">
         <f t="shared" si="4"/>
@@ -50477,7 +50016,7 @@
       </c>
       <c r="AG42" s="230">
         <f>SUM($B42:AF42)</f>
-        <v>3248</v>
+        <v>4098</v>
       </c>
       <c r="AH42" s="230"/>
       <c r="AI42" s="276"/>
@@ -50684,7 +50223,7 @@
       </c>
       <c r="N47" s="178">
         <f>IF('Entries October 2026'!M19-'Entries October 2026'!M18&lt;1,0,'Entries October 2026'!M19-'Entries October 2026'!M18)</f>
-        <v>0</v>
+        <v>2027.25</v>
       </c>
       <c r="O47" s="178">
         <f>IF('Entries October 2026'!M20-'Entries October 2026'!M19&lt;1,0,'Entries October 2026'!M20-'Entries October 2026'!M19)</f>
@@ -50856,9 +50395,9 @@
         <f>'Daily KPIs'!M76</f>
         <v>244.5399999999936</v>
       </c>
-      <c r="N49" s="187" t="str">
+      <c r="N49" s="187">
         <f>'Daily KPIs'!N76</f>
-        <v>0</v>
+        <v>285.63000000000466</v>
       </c>
       <c r="O49" s="187" t="str">
         <f>'Daily KPIs'!O76</f>
@@ -50934,7 +50473,7 @@
       </c>
       <c r="AG49" s="235">
         <f>SUM($B49:AF49)</f>
-        <v>1594.8899999999994</v>
+        <v>1880.5200000000041</v>
       </c>
       <c r="AH49" s="236"/>
       <c r="AI49" s="280"/>
@@ -51067,7 +50606,7 @@
       </c>
       <c r="N52" s="141">
         <f>'Elec.OCTOBER 2026'!$B$19</f>
-        <v>0</v>
+        <v>5822</v>
       </c>
       <c r="O52" s="141">
         <f>'Elec.OCTOBER 2026'!$B$20</f>
@@ -51143,7 +50682,7 @@
       </c>
       <c r="AG52" s="224">
         <f>SUM(B52:AC52)</f>
-        <v>71069</v>
+        <v>76891</v>
       </c>
       <c r="AH52" s="224"/>
       <c r="AI52" s="276"/>
@@ -51593,9 +51132,9 @@
         <f t="shared" si="6"/>
         <v>16.066594135060598</v>
       </c>
-      <c r="N59" s="144" t="str">
+      <c r="N59" s="144">
         <f t="shared" si="6"/>
-        <v/>
+        <v>6.0999834755490863</v>
       </c>
       <c r="O59" s="144" t="str">
         <f t="shared" si="6"/>
@@ -51671,7 +51210,7 @@
       </c>
       <c r="AG59" s="238">
         <f>IF(AG$9=0,"",+(AG18*10)/AG$9)</f>
-        <v>12.801811195716358</v>
+        <v>11.616713245428045</v>
       </c>
       <c r="AH59" s="239">
         <f>'Daily KPIs'!AI90</f>
@@ -51679,7 +51218,7 @@
       </c>
       <c r="AI59" s="282">
         <f>+AH59-AG59</f>
-        <v>-2.6018111957163583</v>
+        <v>-1.4167132454280456</v>
       </c>
       <c r="AJ59" s="270"/>
       <c r="AK59" s="270"/>
@@ -51758,9 +51297,9 @@
         <f t="shared" ref="M62:S62" si="9">IF(M$9=0,"",+(M28*10)/M$9)</f>
         <v>3.0362067656807428</v>
       </c>
-      <c r="N62" s="145" t="str">
+      <c r="N62" s="145">
         <f t="shared" si="9"/>
-        <v/>
+        <v>1.5118114665625977</v>
       </c>
       <c r="O62" s="145" t="str">
         <f t="shared" si="9"/>
@@ -51836,14 +51375,14 @@
       </c>
       <c r="AG62" s="241">
         <f>IF(+(AG28*10)/AG$9&lt;1,0,+(AG28*10)/AG$9)</f>
-        <v>5.8797699208644154</v>
+        <v>5.1073748627878723</v>
       </c>
       <c r="AH62" s="241">
         <v>2.5</v>
       </c>
       <c r="AI62" s="242">
         <f t="shared" ref="AI62:AI78" si="11">AH62-AG62</f>
-        <v>-3.3797699208644154</v>
+        <v>-2.6073748627878723</v>
       </c>
     </row>
     <row r="63" spans="1:37" ht="18.75" x14ac:dyDescent="0.3">
@@ -51976,14 +51515,14 @@
       </c>
       <c r="AG63" s="243">
         <f>IF(+(AG28*10)/AG$93&lt;1,0,+(AG28*10)/AG$93)</f>
-        <v>5.775222551928783</v>
+        <v>6.0942136498516319</v>
       </c>
       <c r="AH63" s="243">
         <v>2.5</v>
       </c>
       <c r="AI63" s="244">
         <f t="shared" si="11"/>
-        <v>-3.275222551928783</v>
+        <v>-3.5942136498516319</v>
       </c>
     </row>
     <row r="64" spans="1:37" s="90" customFormat="1" ht="18" x14ac:dyDescent="0.25">
@@ -52038,9 +51577,9 @@
         <f>IF(M$9=0,"",+(M29*10)/M$9)</f>
         <v>0</v>
       </c>
-      <c r="N64" s="147" t="str">
+      <c r="N64" s="147">
         <f t="shared" si="14"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O64" s="147" t="str">
         <f>IF(O$9=0,"",+(O29*10)/O$9)</f>
@@ -52226,9 +51765,9 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="N66" s="145" t="str">
+      <c r="N66" s="145">
         <f t="shared" si="16"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O66" s="145" t="str">
         <f t="shared" ref="O66:S69" si="17">IF(O$9=0,"",+(O31*10)/O$9)</f>
@@ -52338,9 +51877,9 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="N67" s="150" t="str">
+      <c r="N67" s="150">
         <f t="shared" si="18"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O67" s="150" t="str">
         <f t="shared" si="17"/>
@@ -52416,14 +51955,14 @@
       </c>
       <c r="AG67" s="249">
         <f>+(AG32*10)/AG$9</f>
-        <v>0</v>
+        <v>9.3256996885962368E-2</v>
       </c>
       <c r="AH67" s="249">
         <v>1</v>
       </c>
       <c r="AI67" s="250">
         <f>AH67-AG67</f>
-        <v>1</v>
+        <v>0.90674300311403766</v>
       </c>
       <c r="AJ67" s="284"/>
       <c r="AK67" s="284"/>
@@ -52480,9 +52019,9 @@
         <f t="shared" si="20"/>
         <v>1.2229166139547436</v>
       </c>
-      <c r="N68" s="145" t="str">
+      <c r="N68" s="145">
         <f t="shared" si="20"/>
-        <v/>
+        <v>0.4746384836882574</v>
       </c>
       <c r="O68" s="145" t="str">
         <f t="shared" si="17"/>
@@ -52558,14 +52097,14 @@
       </c>
       <c r="AG68" s="241">
         <f>+(AG33*10)/AG$9</f>
-        <v>1.4048005205918834</v>
+        <v>1.4081806529780316</v>
       </c>
       <c r="AH68" s="241">
         <v>0.7</v>
       </c>
       <c r="AI68" s="242">
         <f t="shared" si="11"/>
-        <v>-0.70480052059188347</v>
+        <v>-0.70818065297803168</v>
       </c>
     </row>
     <row r="69" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -52620,9 +52159,9 @@
         <f t="shared" si="22"/>
         <v>5.0181750710556718</v>
       </c>
-      <c r="N69" s="145" t="str">
+      <c r="N69" s="145">
         <f t="shared" si="22"/>
-        <v/>
+        <v>1.7403411068569439</v>
       </c>
       <c r="O69" s="145" t="str">
         <f t="shared" si="17"/>
@@ -52698,14 +52237,14 @@
       </c>
       <c r="AG69" s="241">
         <f>+(AG34*10)/AG$9</f>
-        <v>2.911562369291242</v>
+        <v>4.2431933583112871</v>
       </c>
       <c r="AH69" s="241">
         <v>2.6</v>
       </c>
       <c r="AI69" s="242">
         <f t="shared" si="11"/>
-        <v>-0.31156236929124193</v>
+        <v>-1.643193358311287</v>
       </c>
     </row>
     <row r="70" spans="1:37" ht="18.75" x14ac:dyDescent="0.3">
@@ -52897,9 +52436,9 @@
         <f t="shared" si="26"/>
         <v>0.96989938348134841</v>
       </c>
-      <c r="N71" s="145" t="str">
+      <c r="N71" s="145">
         <f t="shared" si="26"/>
-        <v/>
+        <v>0.45705928058869233</v>
       </c>
       <c r="O71" s="145" t="str">
         <f t="shared" ref="O71:S75" si="27">IF(O$9=0,"",+(O35*10)/O$9)</f>
@@ -52975,14 +52514,14 @@
       </c>
       <c r="AG71" s="241">
         <f>+(AG35*10)/AG$9</f>
-        <v>0.52113567699376317</v>
+        <v>0.50980491630992752</v>
       </c>
       <c r="AH71" s="241">
         <v>0.7</v>
       </c>
       <c r="AI71" s="242">
         <f>AH71-AG71</f>
-        <v>0.17886432300623678</v>
+        <v>0.19019508369007243</v>
       </c>
     </row>
     <row r="72" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -53037,9 +52576,9 @@
         <f t="shared" si="29"/>
         <v>0.21084769206116269</v>
       </c>
-      <c r="N72" s="145" t="str">
+      <c r="N72" s="145">
         <f t="shared" si="29"/>
-        <v/>
+        <v>5.2737609298695268E-2</v>
       </c>
       <c r="O72" s="145" t="str">
         <f t="shared" si="27"/>
@@ -53115,14 +52654,14 @@
       </c>
       <c r="AG72" s="241">
         <f>+(AG36*10)/AG$9</f>
-        <v>9.0632291651089256E-2</v>
+        <v>8.3931297197366125E-2</v>
       </c>
       <c r="AH72" s="241">
         <v>0.1</v>
       </c>
       <c r="AI72" s="242">
         <f>AH72-AG72</f>
-        <v>9.3677083489107499E-3</v>
+        <v>1.606870280263388E-2</v>
       </c>
     </row>
     <row r="73" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -53177,9 +52716,9 @@
         <f t="shared" si="31"/>
         <v>2.9940372272685103</v>
       </c>
-      <c r="N73" s="145" t="str">
+      <c r="N73" s="145">
         <f t="shared" si="31"/>
-        <v/>
+        <v>0.26368804649347632</v>
       </c>
       <c r="O73" s="145" t="str">
         <f t="shared" si="27"/>
@@ -53255,14 +52794,14 @@
       </c>
       <c r="AG73" s="241">
         <f>+(AG37*10)/AG$9</f>
-        <v>0.84590138874349974</v>
+        <v>0.78957590696781466</v>
       </c>
       <c r="AH73" s="241">
         <v>0.6</v>
       </c>
       <c r="AI73" s="242">
         <f t="shared" si="11"/>
-        <v>-0.24590138874349976</v>
+        <v>-0.18957590696781468</v>
       </c>
     </row>
     <row r="74" spans="1:37" s="91" customFormat="1" ht="18" x14ac:dyDescent="0.25">
@@ -53317,9 +52856,9 @@
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="N74" s="150" t="str">
+      <c r="N74" s="150">
         <f t="shared" si="33"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O74" s="150" t="str">
         <f t="shared" si="27"/>
@@ -53459,9 +52998,9 @@
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="N75" s="145" t="str">
+      <c r="N75" s="145">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O75" s="145" t="str">
         <f t="shared" si="27"/>
@@ -53693,7 +53232,7 @@
       </c>
       <c r="N78" s="152">
         <f>SUM(N62:N77)</f>
-        <v>0</v>
+        <v>4.5002759934886623</v>
       </c>
       <c r="O78" s="152">
         <f t="shared" si="37"/>
@@ -53769,7 +53308,7 @@
       </c>
       <c r="AG78" s="253">
         <f>SUM(AG62:AG77)</f>
-        <v>17.429024720064675</v>
+        <v>18.329531641289897</v>
       </c>
       <c r="AH78" s="253">
         <f t="shared" si="37"/>
@@ -53777,7 +53316,7 @@
       </c>
       <c r="AI78" s="253">
         <f t="shared" si="11"/>
-        <v>-1.8290247200646768</v>
+        <v>-2.7295316412898991</v>
       </c>
       <c r="AJ78" s="210"/>
       <c r="AK78" s="210"/>
@@ -53836,7 +53375,7 @@
       </c>
       <c r="N79" s="154">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>2.2501379967443311</v>
       </c>
       <c r="O79" s="154">
         <f t="shared" si="38"/>
@@ -53912,7 +53451,7 @@
       </c>
       <c r="AG79" s="254">
         <f t="shared" si="38"/>
-        <v>3.5233303379360947</v>
+        <v>4.8369295718185805</v>
       </c>
       <c r="AH79" s="254">
         <f t="shared" si="38"/>
@@ -53920,7 +53459,7 @@
       </c>
       <c r="AI79" s="254">
         <f t="shared" si="38"/>
-        <v>2.4766696620639057</v>
+        <v>1.1630704281814193</v>
       </c>
       <c r="AJ79" s="285"/>
       <c r="AK79" s="285"/>
@@ -53977,9 +53516,9 @@
         <f t="shared" si="39"/>
         <v>5.2972109067295916</v>
       </c>
-      <c r="N80" s="155" t="str">
+      <c r="N80" s="155">
         <f t="shared" si="39"/>
-        <v/>
+        <v>3.5637439483593325</v>
       </c>
       <c r="O80" s="155" t="str">
         <f t="shared" si="39"/>
@@ -54120,9 +53659,9 @@
         <f t="shared" si="41"/>
         <v>1.0312138923327074</v>
       </c>
-      <c r="N81" s="157" t="str">
+      <c r="N81" s="157">
         <f t="shared" si="41"/>
-        <v/>
+        <v>0.50211477813288585</v>
       </c>
       <c r="O81" s="157" t="str">
         <f>IF(O$9=0,"",+O49/O$9)</f>
@@ -54198,7 +53737,7 @@
       </c>
       <c r="AG81" s="287">
         <f>IF(AG$9=0,"",+AG49/AG$9)</f>
-        <v>0.60228556513085707</v>
+        <v>0.58457215927996775</v>
       </c>
       <c r="AH81" s="287">
         <f>'Daily KPIs'!AI93</f>
@@ -54206,7 +53745,7 @@
       </c>
       <c r="AI81" s="286">
         <f>AH81-AG81</f>
-        <v>1.0977144348691428</v>
+        <v>1.1154278407200322</v>
       </c>
       <c r="AJ81" s="210"/>
       <c r="AK81" s="210"/>
@@ -54263,9 +53802,9 @@
         <f t="shared" si="43"/>
         <v>37.231485464160109</v>
       </c>
-      <c r="N82" s="144" t="str">
+      <c r="N82" s="144">
         <f t="shared" ref="N82:S82" si="44">IF(N$9=0,"",N52/N$9)</f>
-        <v/>
+        <v>10.234612044566795</v>
       </c>
       <c r="O82" s="144" t="str">
         <f t="shared" si="44"/>
@@ -54341,7 +53880,7 @@
       </c>
       <c r="AG82" s="238">
         <f>+(AG52)/AG$9</f>
-        <v>26.838109730630258</v>
+        <v>23.902079158528441</v>
       </c>
       <c r="AH82" s="239">
         <f>'Daily KPIs'!AI94</f>
@@ -54349,7 +53888,7 @@
       </c>
       <c r="AI82" s="286">
         <f>AH82-AG82</f>
-        <v>-4.8381097306302578</v>
+        <v>-1.9020791585284407</v>
       </c>
       <c r="AJ82" s="270"/>
       <c r="AK82" s="270"/>
@@ -54451,9 +53990,9 @@
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="N84" s="144" t="str">
+      <c r="N84" s="144">
         <f t="shared" ref="N84:S84" si="47">IF(N$9=0,"",N54/N$9)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O84" s="144" t="str">
         <f t="shared" si="47"/>
@@ -54529,7 +54068,7 @@
       </c>
       <c r="AG84" s="255">
         <f>+(AG54)/AG$9</f>
-        <v>0.36252916660435702</v>
+        <v>0.29842239003507953</v>
       </c>
       <c r="AH84" s="256">
         <f>'Daily KPIs'!AI96</f>
@@ -54537,7 +54076,7 @@
       </c>
       <c r="AI84" s="286">
         <f>AH84-AG84</f>
-        <v>6.8374708333956429</v>
+        <v>6.9015776099649209</v>
       </c>
       <c r="AJ84" s="270"/>
       <c r="AK84" s="270"/>
@@ -54772,7 +54311,7 @@
       </c>
       <c r="N87" s="119">
         <f>IF('Entries October 2026'!L19-'Entries October 2026'!L18&lt;1,0,'Entries October 2026'!L19-'Entries October 2026'!L18)</f>
-        <v>0</v>
+        <v>282.16000000000349</v>
       </c>
       <c r="O87" s="119">
         <f>IF('Entries October 2026'!L20-'Entries October 2026'!L19&lt;1,0,'Entries October 2026'!L20-'Entries October 2026'!L19)</f>
@@ -54848,7 +54387,7 @@
       </c>
       <c r="AG87" s="220">
         <f>SUM($B87:AF87)</f>
-        <v>550893.57000000007</v>
+        <v>551175.7300000001</v>
       </c>
       <c r="AH87" s="220"/>
       <c r="AI87" s="271"/>
@@ -54947,9 +54486,9 @@
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="N89" s="160" t="str">
+      <c r="N89" s="160">
         <f t="shared" si="49"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O89" s="160" t="str">
         <f>IF(O87=0,"",O88/O87)</f>
@@ -55428,13 +54967,13 @@
         <f>'Daily KPIs'!M13</f>
         <v>ST</v>
       </c>
-      <c r="N94" s="166">
+      <c r="N94" s="166" t="str">
         <f>'Daily KPIs'!N13</f>
-        <v>0</v>
-      </c>
-      <c r="O94" s="166">
+        <v>SM</v>
+      </c>
+      <c r="O94" s="166" t="str">
         <f>'Daily KPIs'!O13</f>
-        <v>0</v>
+        <v>SM/ST</v>
       </c>
       <c r="P94" s="166">
         <f>'Daily KPIs'!P13</f>
@@ -55562,7 +55101,7 @@
       </c>
       <c r="N95" s="174">
         <f>'Daily KPIs'!N14</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O95" s="174">
         <f>'Daily KPIs'!O14</f>
@@ -55638,7 +55177,7 @@
       </c>
       <c r="AG95" s="262">
         <f>SUM($B95:AF95)</f>
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="AH95" s="262"/>
       <c r="AI95" s="290"/>
@@ -55695,29 +55234,29 @@
         <f>+'Water '!$F18</f>
         <v>247</v>
       </c>
-      <c r="N96" s="110" t="str">
+      <c r="N96" s="110">
         <f>+'Water '!$F19</f>
-        <v>0</v>
-      </c>
-      <c r="O96" s="110" t="str">
+        <v>114</v>
+      </c>
+      <c r="O96" s="110">
         <f>+'Water '!$F19</f>
-        <v>0</v>
-      </c>
-      <c r="P96" s="110" t="str">
+        <v>114</v>
+      </c>
+      <c r="P96" s="110">
         <f>+'Water '!$F19</f>
-        <v>0</v>
-      </c>
-      <c r="Q96" s="110" t="str">
+        <v>114</v>
+      </c>
+      <c r="Q96" s="110">
         <f>+'Water '!$F19</f>
-        <v>0</v>
-      </c>
-      <c r="R96" s="110" t="str">
+        <v>114</v>
+      </c>
+      <c r="R96" s="110">
         <f>+'Water '!$F19</f>
-        <v>0</v>
-      </c>
-      <c r="S96" s="110" t="str">
+        <v>114</v>
+      </c>
+      <c r="S96" s="110">
         <f>+'Water '!$F19</f>
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="T96" s="110" t="str">
         <f>+'Water '!$F25</f>
@@ -55773,7 +55312,7 @@
       </c>
       <c r="AG96" s="220">
         <f>SUM($B96:AF96)</f>
-        <v>1680</v>
+        <v>2364</v>
       </c>
       <c r="AH96" s="220"/>
       <c r="AI96" s="271"/>
@@ -55985,7 +55524,7 @@
       </c>
       <c r="N101" s="159">
         <f>'Daily KPIs CO2'!N52</f>
-        <v>0</v>
+        <v>5822</v>
       </c>
       <c r="O101" s="159">
         <f>'Daily KPIs CO2'!O52</f>
@@ -56061,7 +55600,7 @@
       </c>
       <c r="AG101" s="263">
         <f>'Daily KPIs CO2'!AG52</f>
-        <v>71069</v>
+        <v>76891</v>
       </c>
       <c r="AH101" s="211"/>
       <c r="AI101" s="271"/>
@@ -56202,30 +55741,30 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B82:AF82">
-    <cfRule type="cellIs" dxfId="88" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="41" priority="3" operator="greaterThan">
       <formula>26</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B84:AF84">
-    <cfRule type="cellIs" dxfId="87" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="40" priority="4" operator="greaterThan">
       <formula>6.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D64:D65 D67 T69:AI70 D71 D73:D77">
-    <cfRule type="cellIs" dxfId="86" priority="5" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="39" priority="5" stopIfTrue="1" operator="greaterThan">
       <formula>3.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D69:S69 B70:S70">
-    <cfRule type="cellIs" dxfId="85" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>3.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI8">
-    <cfRule type="cellIs" dxfId="84" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="37" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/data/raw/October_26_Utilities_Tracking.xlsx
+++ b/data/raw/October_26_Utilities_Tracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UTILITIES\Tracking\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF2CC311-16A1-462A-8732-20AAC9066EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB12C24-720D-4027-A906-12CC0BB1AE25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="579" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
     <author>Alexander Dominguez-Ramon</author>
   </authors>
   <commentList>
-    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{8B2A281D-B5C8-4152-97AF-1CD29DC5D0BE}">
+    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{4DD8895D-E903-46C4-A720-FE319DEF9132}">
       <text>
         <r>
           <rPr>
@@ -80,7 +80,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{03E10757-3B83-4D1C-B4B9-4BFDF7D5EB25}">
+    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{4876613E-B24F-466B-8D3E-D87291D21C52}">
       <text>
         <r>
           <rPr>
@@ -581,6 +581,40 @@
         </r>
       </text>
     </comment>
+    <comment ref="V74" authorId="2" shapeId="0" xr:uid="{8F2354C5-E2D1-4A26-9DB1-ACF6ADBCC68C}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tank A 6200 kgs 
+Tank B 0 kgs calculated
+Tank C 22400 Kgs
+mobile approx 0Kgs
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W74" authorId="2" shapeId="0" xr:uid="{2AD1B525-2FC1-4328-828C-CF9B35F2BA6D}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tank A 4000 kgs 
+Tank B 0 kgs calculated
+Tank C 22400 Kgs
+mobile approx 0Kgs
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -633,7 +667,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="323">
   <si>
     <t>UTILITY ANALYSIS</t>
   </si>
@@ -3347,6 +3381,61 @@
       <t>/CB</t>
     </r>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FF170EC2"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>CB</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FF00A44A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/ST</t>
+    </r>
+  </si>
+  <si>
+    <t>GN</t>
+  </si>
+  <si>
+    <r>
+      <t>CB/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>VM</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>VM/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>CB</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -3367,7 +3456,7 @@
     <numFmt numFmtId="173" formatCode="0.0000000"/>
     <numFmt numFmtId="174" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="147" x14ac:knownFonts="1">
+  <fonts count="148" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -4330,6 +4419,13 @@
       <b/>
       <sz val="20"/>
       <color rgb="FFFF00FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF170EC2"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -6448,7 +6544,7 @@
     <xf numFmtId="9" fontId="49" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1029">
+  <cellXfs count="1030">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8901,9 +8997,51 @@
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="50" fillId="10" borderId="43" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="10" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="10" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="29" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="124" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="77" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="78" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="79" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="100" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="41" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8925,9 +9063,6 @@
     <xf numFmtId="0" fontId="19" fillId="4" borderId="42" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="41" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8943,45 +9078,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="124" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="77" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="78" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="79" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="100" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="10" borderId="43" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="10" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="10" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="29" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="118" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -9099,15 +9195,39 @@
     <xf numFmtId="0" fontId="70" fillId="12" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="52" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="53" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="49" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9117,30 +9237,6 @@
     <xf numFmtId="0" fontId="19" fillId="4" borderId="33" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="52" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="53" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -9195,6 +9291,30 @@
     <xf numFmtId="2" fontId="17" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="47" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="72" fillId="18" borderId="56" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="72" fillId="18" borderId="123" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="32" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="32" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="122" fillId="16" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9255,32 +9375,11 @@
     <xf numFmtId="0" fontId="95" fillId="16" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="47" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="72" fillId="18" borderId="56" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="72" fillId="18" borderId="123" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="32" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="32" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="167" fontId="69" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -9291,407 +9390,7 @@
     <cellStyle name="Normal_February04" xfId="3" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
     <cellStyle name="Percent" xfId="4" builtinId="5"/>
   </cellStyles>
-  <dxfs count="157">
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="118">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -10713,6 +10412,16 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -11054,7 +10763,7 @@
                   <c:v>7790</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>7481</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>0</c:v>
@@ -11380,6 +11089,9 @@
                 <c:pt idx="19">
                   <c:v>1486.3</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>1494.6</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -11556,7 +11268,7 @@
                   <c:v>0.16022552095124135</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>0.16651811578056061</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>0</c:v>
@@ -12994,53 +12706,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="18" x14ac:dyDescent="0.2">
-      <c r="B1" s="904" t="s">
+      <c r="B1" s="918" t="s">
         <v>209</v>
       </c>
-      <c r="C1" s="904"/>
-      <c r="D1" s="904"/>
-      <c r="E1" s="904"/>
-      <c r="F1" s="904"/>
-      <c r="G1" s="904"/>
-      <c r="H1" s="904"/>
-      <c r="I1" s="904"/>
-      <c r="J1" s="904"/>
-      <c r="K1" s="904"/>
-      <c r="L1" s="904"/>
-      <c r="M1" s="904"/>
+      <c r="C1" s="918"/>
+      <c r="D1" s="918"/>
+      <c r="E1" s="918"/>
+      <c r="F1" s="918"/>
+      <c r="G1" s="918"/>
+      <c r="H1" s="918"/>
+      <c r="I1" s="918"/>
+      <c r="J1" s="918"/>
+      <c r="K1" s="918"/>
+      <c r="L1" s="918"/>
+      <c r="M1" s="918"/>
       <c r="N1" s="363"/>
-      <c r="O1" s="905" t="str">
+      <c r="O1" s="919" t="str">
         <f>B1</f>
         <v>ENTRIES FOR DAILY CONS. MONITOR</v>
       </c>
-      <c r="P1" s="905"/>
-      <c r="Q1" s="905"/>
-      <c r="R1" s="905"/>
-      <c r="S1" s="905"/>
-      <c r="T1" s="905"/>
-      <c r="U1" s="905"/>
-      <c r="V1" s="905"/>
-      <c r="W1" s="905"/>
-      <c r="X1" s="905"/>
-      <c r="Y1" s="905"/>
-      <c r="Z1" s="905"/>
-      <c r="AA1" s="905"/>
-      <c r="AB1" s="905"/>
+      <c r="P1" s="919"/>
+      <c r="Q1" s="919"/>
+      <c r="R1" s="919"/>
+      <c r="S1" s="919"/>
+      <c r="T1" s="919"/>
+      <c r="U1" s="919"/>
+      <c r="V1" s="919"/>
+      <c r="W1" s="919"/>
+      <c r="X1" s="919"/>
+      <c r="Y1" s="919"/>
+      <c r="Z1" s="919"/>
+      <c r="AA1" s="919"/>
+      <c r="AB1" s="919"/>
     </row>
     <row r="2" spans="1:44" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C2" s="810"/>
       <c r="F2" s="364"/>
       <c r="G2" s="365"/>
-      <c r="O2" s="913" t="s">
+      <c r="O2" s="926" t="s">
         <v>231</v>
       </c>
-      <c r="P2" s="913"/>
-      <c r="Q2" s="913"/>
-      <c r="R2" s="913"/>
-      <c r="S2" s="913"/>
-      <c r="T2" s="913"/>
-      <c r="U2" s="913"/>
-      <c r="V2" s="913"/>
+      <c r="P2" s="926"/>
+      <c r="Q2" s="926"/>
+      <c r="R2" s="926"/>
+      <c r="S2" s="926"/>
+      <c r="T2" s="926"/>
+      <c r="U2" s="926"/>
+      <c r="V2" s="926"/>
     </row>
     <row r="3" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="366"/>
@@ -13058,50 +12770,50 @@
         <v>22</v>
       </c>
       <c r="K3" s="369"/>
-      <c r="L3" s="918" t="s">
+      <c r="L3" s="909" t="s">
         <v>53</v>
       </c>
-      <c r="M3" s="919"/>
-      <c r="N3" s="920"/>
-      <c r="O3" s="906" t="s">
+      <c r="M3" s="910"/>
+      <c r="N3" s="911"/>
+      <c r="O3" s="920" t="s">
         <v>3</v>
       </c>
-      <c r="P3" s="906"/>
-      <c r="Q3" s="906"/>
-      <c r="R3" s="906"/>
-      <c r="S3" s="906"/>
-      <c r="T3" s="906"/>
-      <c r="U3" s="906"/>
-      <c r="V3" s="906"/>
-      <c r="W3" s="906"/>
-      <c r="X3" s="906"/>
-      <c r="Y3" s="906"/>
-      <c r="Z3" s="906"/>
-      <c r="AA3" s="906"/>
-      <c r="AB3" s="906"/>
-      <c r="AC3" s="906"/>
+      <c r="P3" s="920"/>
+      <c r="Q3" s="920"/>
+      <c r="R3" s="920"/>
+      <c r="S3" s="920"/>
+      <c r="T3" s="920"/>
+      <c r="U3" s="920"/>
+      <c r="V3" s="920"/>
+      <c r="W3" s="920"/>
+      <c r="X3" s="920"/>
+      <c r="Y3" s="920"/>
+      <c r="Z3" s="920"/>
+      <c r="AA3" s="920"/>
+      <c r="AB3" s="920"/>
+      <c r="AC3" s="920"/>
       <c r="AD3" s="372"/>
       <c r="AE3" s="373"/>
       <c r="AF3" s="372"/>
-      <c r="AG3" s="926" t="s">
+      <c r="AG3" s="904" t="s">
         <v>206</v>
       </c>
-      <c r="AH3" s="924" t="s">
+      <c r="AH3" s="902" t="s">
         <v>204</v>
       </c>
-      <c r="AI3" s="924" t="s">
+      <c r="AI3" s="902" t="s">
         <v>205</v>
       </c>
-      <c r="AJ3" s="927" t="s">
+      <c r="AJ3" s="905" t="s">
         <v>233</v>
       </c>
       <c r="AK3" s="416"/>
-      <c r="AL3" s="928" t="s">
+      <c r="AL3" s="906" t="s">
         <v>178</v>
       </c>
-      <c r="AM3" s="928"/>
-      <c r="AN3" s="928"/>
-      <c r="AO3" s="928"/>
+      <c r="AM3" s="906"/>
+      <c r="AN3" s="906"/>
+      <c r="AO3" s="906"/>
     </row>
     <row r="4" spans="1:44" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="374"/>
@@ -13135,40 +12847,40 @@
       <c r="K4" s="372" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="914" t="s">
+      <c r="L4" s="927" t="s">
         <v>289</v>
       </c>
       <c r="M4" s="376" t="s">
         <v>260</v>
       </c>
-      <c r="N4" s="921" t="s">
+      <c r="N4" s="912" t="s">
         <v>167</v>
       </c>
-      <c r="O4" s="902" t="s">
+      <c r="O4" s="914" t="s">
         <v>100</v>
       </c>
-      <c r="P4" s="902" t="s">
+      <c r="P4" s="914" t="s">
         <v>101</v>
       </c>
-      <c r="Q4" s="902" t="s">
+      <c r="Q4" s="914" t="s">
         <v>160</v>
       </c>
-      <c r="R4" s="902" t="s">
+      <c r="R4" s="914" t="s">
         <v>171</v>
       </c>
-      <c r="S4" s="902" t="s">
+      <c r="S4" s="914" t="s">
         <v>102</v>
       </c>
-      <c r="T4" s="902" t="s">
+      <c r="T4" s="914" t="s">
         <v>172</v>
       </c>
-      <c r="U4" s="902" t="s">
+      <c r="U4" s="914" t="s">
         <v>103</v>
       </c>
-      <c r="V4" s="911" t="s">
+      <c r="V4" s="924" t="s">
         <v>236</v>
       </c>
-      <c r="W4" s="902" t="s">
+      <c r="W4" s="914" t="s">
         <v>177</v>
       </c>
       <c r="X4" s="372" t="s">
@@ -13180,28 +12892,28 @@
       <c r="Z4" s="372" t="s">
         <v>98</v>
       </c>
-      <c r="AA4" s="906" t="s">
+      <c r="AA4" s="920" t="s">
         <v>68</v>
       </c>
-      <c r="AB4" s="908" t="s">
+      <c r="AB4" s="922" t="s">
         <v>69</v>
       </c>
-      <c r="AC4" s="912" t="s">
+      <c r="AC4" s="925" t="s">
         <v>151</v>
       </c>
-      <c r="AD4" s="902" t="s">
+      <c r="AD4" s="914" t="s">
         <v>154</v>
       </c>
-      <c r="AE4" s="902" t="s">
+      <c r="AE4" s="914" t="s">
         <v>155</v>
       </c>
-      <c r="AF4" s="902" t="s">
+      <c r="AF4" s="914" t="s">
         <v>159</v>
       </c>
-      <c r="AG4" s="926"/>
-      <c r="AH4" s="925"/>
-      <c r="AI4" s="925"/>
-      <c r="AJ4" s="927"/>
+      <c r="AG4" s="904"/>
+      <c r="AH4" s="903"/>
+      <c r="AI4" s="903"/>
+      <c r="AJ4" s="905"/>
       <c r="AK4" s="416"/>
       <c r="AL4" s="378" t="s">
         <v>276</v>
@@ -13250,20 +12962,20 @@
       <c r="K5" s="465" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="915"/>
+      <c r="L5" s="928"/>
       <c r="M5" s="466" t="s">
         <v>261</v>
       </c>
-      <c r="N5" s="922"/>
-      <c r="O5" s="910"/>
-      <c r="P5" s="902"/>
-      <c r="Q5" s="902"/>
-      <c r="R5" s="902"/>
-      <c r="S5" s="910"/>
-      <c r="T5" s="910"/>
-      <c r="U5" s="910"/>
-      <c r="V5" s="911"/>
-      <c r="W5" s="923"/>
+      <c r="N5" s="913"/>
+      <c r="O5" s="915"/>
+      <c r="P5" s="914"/>
+      <c r="Q5" s="914"/>
+      <c r="R5" s="914"/>
+      <c r="S5" s="915"/>
+      <c r="T5" s="915"/>
+      <c r="U5" s="915"/>
+      <c r="V5" s="924"/>
+      <c r="W5" s="916"/>
       <c r="X5" s="372" t="s">
         <v>104</v>
       </c>
@@ -13273,16 +12985,16 @@
       <c r="Z5" s="372" t="s">
         <v>104</v>
       </c>
-      <c r="AA5" s="907"/>
-      <c r="AB5" s="909"/>
-      <c r="AC5" s="912"/>
-      <c r="AD5" s="902"/>
-      <c r="AE5" s="902"/>
-      <c r="AF5" s="903"/>
-      <c r="AG5" s="926"/>
-      <c r="AH5" s="925"/>
-      <c r="AI5" s="925"/>
-      <c r="AJ5" s="927"/>
+      <c r="AA5" s="921"/>
+      <c r="AB5" s="923"/>
+      <c r="AC5" s="925"/>
+      <c r="AD5" s="914"/>
+      <c r="AE5" s="914"/>
+      <c r="AF5" s="917"/>
+      <c r="AG5" s="904"/>
+      <c r="AH5" s="903"/>
+      <c r="AI5" s="903"/>
+      <c r="AJ5" s="905"/>
       <c r="AK5" s="416"/>
       <c r="AL5" s="378" t="s">
         <v>263</v>
@@ -15217,41 +14929,87 @@
       <c r="A27" s="378">
         <v>22</v>
       </c>
-      <c r="B27" s="815"/>
-      <c r="C27" s="816"/>
+      <c r="B27" s="815">
+        <v>8522020</v>
+      </c>
+      <c r="C27" s="816">
+        <v>1710623.6</v>
+      </c>
       <c r="D27" s="817"/>
-      <c r="E27" s="817"/>
-      <c r="F27" s="817"/>
-      <c r="G27" s="817"/>
+      <c r="E27" s="817">
+        <v>44</v>
+      </c>
+      <c r="F27" s="817">
+        <v>11569.9</v>
+      </c>
+      <c r="G27" s="817">
+        <v>68225</v>
+      </c>
       <c r="H27" s="818"/>
-      <c r="I27" s="819"/>
+      <c r="I27" s="819">
+        <v>2002598</v>
+      </c>
       <c r="J27" s="876"/>
-      <c r="K27" s="818"/>
-      <c r="L27" s="817"/>
-      <c r="M27" s="821"/>
-      <c r="N27" s="819"/>
-      <c r="O27" s="822"/>
-      <c r="P27" s="823"/>
-      <c r="Q27" s="817"/>
+      <c r="K27" s="818">
+        <v>468000</v>
+      </c>
+      <c r="L27" s="817">
+        <v>94511.2</v>
+      </c>
+      <c r="M27" s="821">
+        <v>655288.88</v>
+      </c>
+      <c r="N27" s="819">
+        <v>87895.8</v>
+      </c>
+      <c r="O27" s="822">
+        <v>256505</v>
+      </c>
+      <c r="P27" s="823">
+        <v>88446</v>
+      </c>
+      <c r="Q27" s="817">
+        <v>992891</v>
+      </c>
       <c r="R27" s="817"/>
-      <c r="S27" s="817"/>
+      <c r="S27" s="817">
+        <v>99871</v>
+      </c>
       <c r="T27" s="817"/>
-      <c r="U27" s="817"/>
-      <c r="V27" s="824"/>
+      <c r="U27" s="817">
+        <v>591</v>
+      </c>
+      <c r="V27" s="824">
+        <v>1368887</v>
+      </c>
       <c r="W27" s="817"/>
-      <c r="X27" s="825"/>
-      <c r="Y27" s="817"/>
-      <c r="Z27" s="817"/>
-      <c r="AA27" s="817"/>
+      <c r="X27" s="825">
+        <v>49673</v>
+      </c>
+      <c r="Y27" s="817">
+        <v>72271</v>
+      </c>
+      <c r="Z27" s="817">
+        <v>16089</v>
+      </c>
+      <c r="AA27" s="817">
+        <v>97122</v>
+      </c>
       <c r="AB27" s="817"/>
-      <c r="AC27" s="817"/>
-      <c r="AD27" s="817"/>
+      <c r="AC27" s="817">
+        <v>7056</v>
+      </c>
+      <c r="AD27" s="817">
+        <v>263787</v>
+      </c>
       <c r="AE27" s="817"/>
       <c r="AF27" s="819"/>
       <c r="AG27" s="817"/>
       <c r="AH27" s="817"/>
       <c r="AI27" s="817"/>
-      <c r="AJ27" s="880"/>
+      <c r="AJ27" s="880">
+        <v>7383613.8779999996</v>
+      </c>
       <c r="AK27" s="192"/>
       <c r="AL27" s="387"/>
       <c r="AM27" s="387"/>
@@ -15713,8 +15471,8 @@
     <row r="38" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B38" s="190"/>
       <c r="G38" s="190"/>
-      <c r="I38" s="916"/>
-      <c r="J38" s="916"/>
+      <c r="I38" s="907"/>
+      <c r="J38" s="907"/>
       <c r="R38" s="190"/>
       <c r="S38" s="190"/>
       <c r="T38" s="190"/>
@@ -15722,8 +15480,8 @@
       <c r="V38" s="190"/>
       <c r="W38" s="190"/>
       <c r="Z38" s="190"/>
-      <c r="AA38" s="917"/>
-      <c r="AB38" s="917"/>
+      <c r="AA38" s="908"/>
+      <c r="AB38" s="908"/>
       <c r="AC38" s="190"/>
       <c r="AD38" s="190"/>
       <c r="AI38" s="380"/>
@@ -17389,19 +17147,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="AH3:AH5"/>
-    <mergeCell ref="AG3:AG5"/>
-    <mergeCell ref="AI3:AI5"/>
-    <mergeCell ref="AJ3:AJ5"/>
-    <mergeCell ref="AL3:AO3"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="AA38:AB38"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="S4:S5"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="P4:P5"/>
-    <mergeCell ref="W4:W5"/>
     <mergeCell ref="AF4:AF5"/>
     <mergeCell ref="AE4:AE5"/>
     <mergeCell ref="AD4:AD5"/>
@@ -17418,336 +17163,294 @@
     <mergeCell ref="AC4:AC5"/>
     <mergeCell ref="O2:V2"/>
     <mergeCell ref="L4:L5"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="AA38:AB38"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="S4:S5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="P4:P5"/>
+    <mergeCell ref="W4:W5"/>
+    <mergeCell ref="AH3:AH5"/>
+    <mergeCell ref="AG3:AG5"/>
+    <mergeCell ref="AI3:AI5"/>
+    <mergeCell ref="AJ3:AJ5"/>
+    <mergeCell ref="AL3:AO3"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
-  <conditionalFormatting sqref="B27:B35">
-    <cfRule type="expression" dxfId="155" priority="60">
-      <formula>B27&lt;B26</formula>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="expression" dxfId="117" priority="13">
+      <formula>B6&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:B35">
+    <cfRule type="expression" dxfId="116" priority="20">
+      <formula>B7&lt;B6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:B27">
+    <cfRule type="expression" dxfId="115" priority="34">
+      <formula>B11&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C35 E35:E37">
-    <cfRule type="expression" dxfId="153" priority="545">
+    <cfRule type="expression" dxfId="114" priority="585">
       <formula>C35&lt;C34</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C6:D6">
+    <cfRule type="expression" dxfId="113" priority="15">
+      <formula>C6&lt;C5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7:D7 H7:J7 R7 T7 W7 AB7">
+    <cfRule type="expression" dxfId="112" priority="22">
+      <formula>C7&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8:D14">
+    <cfRule type="expression" dxfId="111" priority="25">
+      <formula>C8&lt;C7</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C36:D37">
-    <cfRule type="expression" dxfId="149" priority="1598">
+    <cfRule type="expression" dxfId="110" priority="1638">
       <formula>C36&lt;C35</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D35 B36:B37">
-    <cfRule type="expression" dxfId="148" priority="1585">
+    <cfRule type="expression" dxfId="109" priority="1625">
       <formula>B35&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F27:F37">
-    <cfRule type="expression" dxfId="146" priority="44">
-      <formula>F27&lt;#REF!</formula>
+  <conditionalFormatting sqref="E6:E14">
+    <cfRule type="expression" dxfId="108" priority="5">
+      <formula>E6&lt;E5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G27:G37">
-    <cfRule type="expression" dxfId="145" priority="42">
-      <formula>G27&lt;G26</formula>
+  <conditionalFormatting sqref="F6:F37">
+    <cfRule type="expression" dxfId="107" priority="4">
+      <formula>F6&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6:G37">
+    <cfRule type="expression" dxfId="106" priority="2">
+      <formula>G6&lt;G5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G36:J37 L36:O37">
-    <cfRule type="expression" dxfId="144" priority="1432">
+    <cfRule type="expression" dxfId="105" priority="1472">
       <formula>G36&lt;G35</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="G6:O6">
+    <cfRule type="expression" dxfId="104" priority="6">
+      <formula>G6&lt;G5</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="H35:I35 R35 T35 W35 AB35 AE35:AI35 P36:P37 S36:S37 X36:Y37">
-    <cfRule type="expression" dxfId="142" priority="1584">
+    <cfRule type="expression" dxfId="103" priority="1624">
       <formula>H35&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H27:I34">
-    <cfRule type="expression" dxfId="141" priority="66">
-      <formula>H27&lt;H26</formula>
+  <conditionalFormatting sqref="H8:J18 H19:I34">
+    <cfRule type="expression" dxfId="102" priority="26">
+      <formula>H8&lt;H7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J27:J35">
-    <cfRule type="expression" dxfId="140" priority="77">
-      <formula>J27&lt;J26</formula>
+  <conditionalFormatting sqref="J19:J35">
+    <cfRule type="expression" dxfId="101" priority="37">
+      <formula>J19&lt;J18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K27:K37">
-    <cfRule type="expression" dxfId="139" priority="69">
-      <formula>K27&lt;K26</formula>
+  <conditionalFormatting sqref="K11:L21 K22:K37">
+    <cfRule type="expression" dxfId="100" priority="29">
+      <formula>K11&lt;K10</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L27:Z27 L28:AC28">
-    <cfRule type="expression" dxfId="136" priority="551">
-      <formula>L27&lt;L26</formula>
+  <conditionalFormatting sqref="K7:O10">
+    <cfRule type="expression" dxfId="99" priority="16">
+      <formula>K7&lt;K6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L22:M25">
+    <cfRule type="expression" dxfId="98" priority="38">
+      <formula>L22&lt;L21</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L26:Z27">
+    <cfRule type="expression" dxfId="97" priority="40">
+      <formula>L26&lt;L25</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L28:AC28">
+    <cfRule type="expression" dxfId="96" priority="591">
+      <formula>L28&lt;L27</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M11:M17">
+    <cfRule type="expression" dxfId="95" priority="31">
+      <formula>M11&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N11:O12">
+    <cfRule type="expression" dxfId="94" priority="30">
+      <formula>N11&lt;N10</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N13:T24 N25:Z25">
+    <cfRule type="expression" dxfId="93" priority="33">
+      <formula>N13&lt;N12</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P8:P12 V8:V12">
+    <cfRule type="expression" dxfId="92" priority="28">
+      <formula>P8&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P6:Q6 X6:Y6 S6:S10">
+    <cfRule type="expression" dxfId="91" priority="12">
+      <formula>P6&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P7:Q7">
+    <cfRule type="expression" dxfId="90" priority="21">
+      <formula>P7&lt;P6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q36">
-    <cfRule type="expression" dxfId="129" priority="1601">
+    <cfRule type="expression" dxfId="89" priority="1641">
       <formula>Q36&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="Q8:R10">
+    <cfRule type="expression" dxfId="88" priority="27">
+      <formula>Q8&lt;Q7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q11:T12">
+    <cfRule type="expression" dxfId="87" priority="32">
+      <formula>Q11&lt;Q10</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R6">
+    <cfRule type="expression" dxfId="86" priority="14">
+      <formula>R6&lt;R5</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="R36">
-    <cfRule type="expression" dxfId="125" priority="1597">
+    <cfRule type="expression" dxfId="85" priority="1637">
       <formula>R36&lt;R35</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB27:AI27">
-    <cfRule type="expression" dxfId="124" priority="63">
-      <formula>AB27&lt;AB26</formula>
+  <conditionalFormatting sqref="T8:T10 AB8:AC10 AE8:AI10 AB11:AI27">
+    <cfRule type="expression" dxfId="84" priority="23">
+      <formula>T8&lt;T7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C27:E34">
-    <cfRule type="expression" dxfId="120" priority="76">
-      <formula>C27&lt;C26</formula>
+  <conditionalFormatting sqref="T6:W6 Z6 AB6">
+    <cfRule type="expression" dxfId="83" priority="11">
+      <formula>T6&lt;T5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U6:U24">
+    <cfRule type="expression" dxfId="82" priority="9">
+      <formula>U6&lt;U5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V7">
+    <cfRule type="expression" dxfId="81" priority="17">
+      <formula>V7&lt;V6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V13:X14 C15:E34">
+    <cfRule type="expression" dxfId="80" priority="36">
+      <formula>C13&lt;C12</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V15:Z24 M18:M21">
+    <cfRule type="expression" dxfId="79" priority="35">
+      <formula>M15&lt;M14</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V29:AC29 AA30:AC30 Z30:Z31 V30:Y34 AA31:AB31 AC31:AC37 Z32:AB34 V35 X35:AA35">
-    <cfRule type="expression" dxfId="118" priority="555">
+    <cfRule type="expression" dxfId="78" priority="595">
       <formula>V29&lt;V28</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA27:AA37">
-    <cfRule type="expression" dxfId="114" priority="41">
-      <formula>AA27&lt;AA26</formula>
+  <conditionalFormatting sqref="W8:W12">
+    <cfRule type="expression" dxfId="77" priority="24">
+      <formula>W8&lt;W7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y7:Z14">
+    <cfRule type="expression" dxfId="76" priority="18">
+      <formula>Y7&lt;Y6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA6:AA12">
+    <cfRule type="expression" dxfId="75" priority="8">
+      <formula>AA6&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA6:AA37">
+    <cfRule type="expression" dxfId="74" priority="1">
+      <formula>AA6&lt;AA5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA28:AA37">
-    <cfRule type="expression" dxfId="113" priority="553">
+    <cfRule type="expression" dxfId="73" priority="593">
       <formula>AA28&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AC6:AC7">
+    <cfRule type="expression" dxfId="72" priority="10">
+      <formula>AC6&lt;AC5</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AD28:AD37">
-    <cfRule type="expression" dxfId="111" priority="550">
+    <cfRule type="expression" dxfId="71" priority="590">
       <formula>AD28&lt;AD27</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AD6:AI6">
+    <cfRule type="expression" dxfId="70" priority="7">
+      <formula>AD6&lt;AD5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD7:AI7 X7:X12 AD8:AD10">
+    <cfRule type="expression" dxfId="69" priority="19">
+      <formula>X7&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AE28:AI34 L29:T34 U29:U37 L35:Q35 S35">
-    <cfRule type="expression" dxfId="108" priority="554">
+    <cfRule type="expression" dxfId="68" priority="594">
       <formula>L28&lt;L27</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AJ27:AJ37">
-    <cfRule type="expression" dxfId="107" priority="43">
-      <formula>AJ27&lt;AJ26</formula>
+  <conditionalFormatting sqref="AJ6:AJ37">
+    <cfRule type="expression" dxfId="67" priority="3">
+      <formula>AJ6&lt;AJ5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK6:AK12">
-    <cfRule type="expression" dxfId="106" priority="1474">
+    <cfRule type="expression" dxfId="66" priority="1514">
       <formula>AK6&lt;AK5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK13:AL15">
-    <cfRule type="expression" dxfId="105" priority="1554">
+    <cfRule type="expression" dxfId="65" priority="1594">
       <formula>AK13&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL9:AL14 AL15:AN34 AK16:AK37 AK20:AN21 T36:W37 Z36:Z37 AB36:AB37 AE36:AI37 Q37:R37">
-    <cfRule type="expression" dxfId="104" priority="1491">
+    <cfRule type="expression" dxfId="64" priority="1531">
       <formula>Q9&lt;Q8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO9:AO34">
-    <cfRule type="expression" dxfId="103" priority="1499">
+    <cfRule type="expression" dxfId="63" priority="1539">
       <formula>AO9&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="expression" dxfId="39" priority="13">
-      <formula>B6&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B7:B26">
-    <cfRule type="expression" dxfId="38" priority="20">
-      <formula>B7&lt;B6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B11:B26">
-    <cfRule type="expression" dxfId="37" priority="34">
-      <formula>B11&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C6:D6">
-    <cfRule type="expression" dxfId="36" priority="15">
-      <formula>C6&lt;C5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C7:D7 H7:J7 R7 T7 W7 AB7">
-    <cfRule type="expression" dxfId="35" priority="22">
-      <formula>C7&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C8:D14">
-    <cfRule type="expression" dxfId="34" priority="25">
-      <formula>C8&lt;C7</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6:E14">
-    <cfRule type="expression" dxfId="33" priority="5">
-      <formula>E6&lt;E5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6:F26">
-    <cfRule type="expression" dxfId="32" priority="4">
-      <formula>F6&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G6:G26">
-    <cfRule type="expression" dxfId="31" priority="2">
-      <formula>G6&lt;G5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G6:O6">
-    <cfRule type="expression" dxfId="30" priority="6">
-      <formula>G6&lt;G5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H8:J18 H19:I26">
-    <cfRule type="expression" dxfId="29" priority="26">
-      <formula>H8&lt;H7</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J19:J26">
-    <cfRule type="expression" dxfId="28" priority="37">
-      <formula>J19&lt;J18</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K11:L21 K22:K24">
-    <cfRule type="expression" dxfId="27" priority="29">
-      <formula>K11&lt;K10</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L22:M25">
-    <cfRule type="expression" dxfId="26" priority="38">
-      <formula>L22&lt;L21</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7:O10">
-    <cfRule type="expression" dxfId="25" priority="16">
-      <formula>K7&lt;K6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q23:T23 K25:K26 W23:Z23">
-    <cfRule type="expression" dxfId="24" priority="39">
-      <formula>K23&lt;K22</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L26:Z26 Q24:T24 W24:Z24 O25:Z25">
-    <cfRule type="expression" dxfId="23" priority="40">
-      <formula>L24&lt;L23</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M11:M17">
-    <cfRule type="expression" dxfId="22" priority="31">
-      <formula>M11&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N11:O12">
-    <cfRule type="expression" dxfId="21" priority="30">
-      <formula>N11&lt;N10</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N13:T22 N23:P24 N25">
-    <cfRule type="expression" dxfId="20" priority="33">
-      <formula>N13&lt;N12</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P8:P12 V8:V12">
-    <cfRule type="expression" dxfId="19" priority="28">
-      <formula>P8&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P6:Q6 X6:Y6 S6:S10">
-    <cfRule type="expression" dxfId="18" priority="12">
-      <formula>P6&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P7:Q7">
-    <cfRule type="expression" dxfId="17" priority="21">
-      <formula>P7&lt;P6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q8:R10">
-    <cfRule type="expression" dxfId="16" priority="27">
-      <formula>Q8&lt;Q7</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q11:T12">
-    <cfRule type="expression" dxfId="15" priority="32">
-      <formula>Q11&lt;Q10</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R6">
-    <cfRule type="expression" dxfId="14" priority="14">
-      <formula>R6&lt;R5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T8:T10 AB8:AC10 AE8:AI10 AB11:AI26">
-    <cfRule type="expression" dxfId="13" priority="23">
-      <formula>T8&lt;T7</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T6:W6 Z6 AB6">
-    <cfRule type="expression" dxfId="12" priority="11">
-      <formula>T6&lt;T5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U6:U24">
-    <cfRule type="expression" dxfId="11" priority="9">
-      <formula>U6&lt;U5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V7">
-    <cfRule type="expression" dxfId="10" priority="17">
-      <formula>V7&lt;V6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V13:X14 C15:E26">
-    <cfRule type="expression" dxfId="9" priority="36">
-      <formula>C13&lt;C12</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V15:Z22 M18:M21 V23:V24">
-    <cfRule type="expression" dxfId="8" priority="35">
-      <formula>M15&lt;M14</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W8:W12">
-    <cfRule type="expression" dxfId="7" priority="24">
-      <formula>W8&lt;W7</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y7:Z14">
-    <cfRule type="expression" dxfId="6" priority="18">
-      <formula>Y7&lt;Y6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA6:AA12">
-    <cfRule type="expression" dxfId="5" priority="8">
-      <formula>AA6&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA6:AA26">
-    <cfRule type="expression" dxfId="4" priority="1">
-      <formula>AA6&lt;AA5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC6:AC7">
-    <cfRule type="expression" dxfId="3" priority="10">
-      <formula>AC6&lt;AC5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD6:AI6">
-    <cfRule type="expression" dxfId="2" priority="7">
-      <formula>AD6&lt;AD5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD7:AI7 X7:X12 AD8:AD10">
-    <cfRule type="expression" dxfId="1" priority="19">
-      <formula>X7&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ6:AJ26">
-    <cfRule type="expression" dxfId="0" priority="3">
-      <formula>AJ6&lt;AJ5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.1" right="0.5" top="0.32" bottom="0.25" header="0.25" footer="0.25"/>
@@ -17785,8 +17488,8 @@
     <col min="11" max="11" width="29.7109375" style="469" customWidth="1"/>
     <col min="12" max="12" width="30.5703125" style="469" customWidth="1"/>
     <col min="13" max="13" width="29.7109375" style="470" customWidth="1"/>
-    <col min="14" max="22" width="29.7109375" style="469" customWidth="1"/>
-    <col min="23" max="33" width="29.7109375" style="469" hidden="1" customWidth="1"/>
+    <col min="14" max="25" width="29.7109375" style="469" customWidth="1"/>
+    <col min="26" max="33" width="29.7109375" style="469" hidden="1" customWidth="1"/>
     <col min="34" max="34" width="29.7109375" style="468" customWidth="1"/>
     <col min="35" max="35" width="24.7109375" style="468" customWidth="1"/>
     <col min="36" max="36" width="24.7109375" style="291" customWidth="1"/>
@@ -18155,7 +17858,10 @@
         <f>4295+2763</f>
         <v>7058</v>
       </c>
-      <c r="V8" s="678"/>
+      <c r="V8" s="678">
+        <f>2842+7025</f>
+        <v>9867</v>
+      </c>
       <c r="W8" s="678"/>
       <c r="X8" s="678"/>
       <c r="Y8" s="678"/>
@@ -18169,14 +17875,14 @@
       <c r="AG8" s="747"/>
       <c r="AH8" s="480">
         <f>SUM(B8:AG8)</f>
-        <v>74224</v>
+        <v>84091</v>
       </c>
       <c r="AI8" s="526">
         <v>123950</v>
       </c>
       <c r="AJ8" s="294">
         <f>AH8-AI8</f>
-        <v>-49726</v>
+        <v>-39859</v>
       </c>
       <c r="AK8" s="481"/>
       <c r="AL8" s="481"/>
@@ -18279,58 +17985,58 @@
         <v>0</v>
       </c>
       <c r="T9" s="678">
-        <f t="shared" ref="T9:U9" si="2">T8*0.066</f>
+        <f t="shared" ref="T9" si="2">T8*0.066</f>
         <v>0</v>
       </c>
       <c r="U9" s="678">
-        <f>U8*0.066</f>
+        <f t="shared" ref="U9:Z9" si="3">U8*0.066</f>
         <v>465.82800000000003</v>
       </c>
       <c r="V9" s="678">
         <f>V8*0.066</f>
-        <v>0</v>
+        <v>651.22199999999998</v>
       </c>
       <c r="W9" s="678">
-        <f>W8*0.066</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X9" s="678">
-        <f>X8*0.066</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Y9" s="678">
-        <f>Y8*0.066</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z9" s="678">
-        <f>Z8*0.066</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA9" s="678">
-        <f t="shared" ref="AA9:AE9" si="3">AA8*0.066</f>
+        <f t="shared" ref="AA9:AE9" si="4">AA8*0.066</f>
         <v>0</v>
       </c>
       <c r="AB9" s="678">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AC9" s="678">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AD9" s="678">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AE9" s="678">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AF9" s="778"/>
       <c r="AG9" s="748"/>
       <c r="AH9" s="484">
         <f>SUM(B9:AG9)</f>
-        <v>4904.4048000000003</v>
+        <v>5555.6268</v>
       </c>
       <c r="AI9" s="484"/>
       <c r="AL9" s="291" t="s">
@@ -18388,8 +18094,12 @@
       <c r="U10" s="800" t="s">
         <v>318</v>
       </c>
-      <c r="V10" s="796"/>
-      <c r="W10" s="881"/>
+      <c r="V10" s="796" t="s">
+        <v>319</v>
+      </c>
+      <c r="W10" s="878" t="s">
+        <v>320</v>
+      </c>
       <c r="X10" s="881"/>
       <c r="Y10" s="871"/>
       <c r="Z10" s="871"/>
@@ -18697,8 +18407,12 @@
       <c r="U13" s="669" t="s">
         <v>307</v>
       </c>
-      <c r="V13" s="800"/>
-      <c r="W13" s="669"/>
+      <c r="V13" s="770" t="s">
+        <v>321</v>
+      </c>
+      <c r="W13" s="1029" t="s">
+        <v>322</v>
+      </c>
       <c r="X13" s="669"/>
       <c r="Y13" s="669"/>
       <c r="Z13" s="669"/>
@@ -18772,9 +18486,11 @@
       <c r="S14" s="498"/>
       <c r="T14" s="498"/>
       <c r="U14" s="469">
-        <v>8</v>
-      </c>
-      <c r="V14" s="498"/>
+        <v>4</v>
+      </c>
+      <c r="V14" s="498">
+        <v>4</v>
+      </c>
       <c r="W14" s="726"/>
       <c r="X14" s="498"/>
       <c r="Y14" s="498"/>
@@ -18829,7 +18545,7 @@
       <c r="AG15" s="718"/>
       <c r="AH15" s="500">
         <f>IF(AH12=0,"",+(AH36*10)/AH12)</f>
-        <v>9.0059347181008906</v>
+        <v>9.7848664688427291</v>
       </c>
       <c r="AI15" s="502"/>
       <c r="AJ15" s="503"/>
@@ -19243,9 +18959,9 @@
         <f>+'Water '!$D26</f>
         <v>266</v>
       </c>
-      <c r="V20" s="509" t="str">
+      <c r="V20" s="509">
         <f>+'Water '!$D27</f>
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="W20" s="509" t="str">
         <f>+'Water '!$D28</f>
@@ -19290,7 +19006,7 @@
       <c r="AG20" s="509"/>
       <c r="AH20" s="484">
         <f>SUM($B20:AF20)</f>
-        <v>3071</v>
+        <v>3511</v>
       </c>
       <c r="AI20" s="484"/>
       <c r="AJ20" s="485"/>
@@ -19379,9 +19095,9 @@
         <f>+'Water '!$E26</f>
         <v>130</v>
       </c>
-      <c r="V21" s="511" t="str">
+      <c r="V21" s="511">
         <f>+'Water '!$E27</f>
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="W21" s="511" t="str">
         <f>+'Water '!$E28</f>
@@ -19426,7 +19142,7 @@
       <c r="AG21" s="509"/>
       <c r="AH21" s="484">
         <f>SUM($B21:AF21)</f>
-        <v>2536</v>
+        <v>2670</v>
       </c>
       <c r="AI21" s="484"/>
     </row>
@@ -19451,15 +19167,15 @@
         <v>64</v>
       </c>
       <c r="F22" s="514">
-        <f t="shared" ref="F22:AF22" si="4">SUM(F19:F21)</f>
+        <f t="shared" ref="F22:AF22" si="5">SUM(F19:F21)</f>
         <v>142</v>
       </c>
       <c r="G22" s="514">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>342</v>
       </c>
       <c r="H22" s="514">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>381</v>
       </c>
       <c r="I22" s="514">
@@ -19471,7 +19187,7 @@
         <v>639</v>
       </c>
       <c r="K22" s="514">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>315</v>
       </c>
       <c r="L22" s="514">
@@ -19479,7 +19195,7 @@
         <v>3</v>
       </c>
       <c r="M22" s="514">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>381</v>
       </c>
       <c r="N22" s="514">
@@ -19487,7 +19203,7 @@
         <v>347</v>
       </c>
       <c r="O22" s="514">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>348</v>
       </c>
       <c r="P22" s="514">
@@ -19495,7 +19211,7 @@
         <v>459</v>
       </c>
       <c r="Q22" s="514">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>549</v>
       </c>
       <c r="R22" s="514">
@@ -19507,23 +19223,23 @@
         <v>0</v>
       </c>
       <c r="T22" s="514">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>118</v>
       </c>
       <c r="U22" s="514">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>396</v>
       </c>
       <c r="V22" s="514">
         <f>SUM(V19:V21)</f>
-        <v>0</v>
+        <v>574</v>
       </c>
       <c r="W22" s="514">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="X22" s="514">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Y22" s="514">
@@ -19531,7 +19247,7 @@
         <v>0</v>
       </c>
       <c r="Z22" s="514">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA22" s="515">
@@ -19551,17 +19267,17 @@
         <v>0</v>
       </c>
       <c r="AE22" s="515">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AF22" s="515">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AG22" s="515"/>
       <c r="AH22" s="516">
         <f>SUM($B22:AF22)</f>
-        <v>5607</v>
+        <v>6181</v>
       </c>
       <c r="AI22" s="514"/>
       <c r="AJ22" s="517"/>
@@ -19807,31 +19523,31 @@
         <v>139.43</v>
       </c>
       <c r="D26" s="485">
-        <f t="shared" ref="D26:AF26" si="5">0.73*(D71+D19)</f>
+        <f t="shared" ref="D26:AF26" si="6">0.73*(D71+D19)</f>
         <v>97.82</v>
       </c>
       <c r="E26" s="485">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F26" s="485">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G26" s="485">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>123.36999999999999</v>
       </c>
       <c r="H26" s="485">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>110.23</v>
       </c>
       <c r="I26" s="485">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>151.10999999999999</v>
       </c>
       <c r="J26" s="521">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>115.34</v>
       </c>
       <c r="K26" s="521">
@@ -19839,101 +19555,101 @@
         <v>124.1</v>
       </c>
       <c r="L26" s="521">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.65</v>
       </c>
       <c r="M26" s="521">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>180.31</v>
       </c>
       <c r="N26" s="521">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>83.22</v>
       </c>
       <c r="O26" s="521">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>127.75</v>
       </c>
       <c r="P26" s="521">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>160.6</v>
       </c>
       <c r="Q26" s="521">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>219</v>
       </c>
       <c r="R26" s="521">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S26" s="521">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T26" s="521">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>64.239999999999995</v>
       </c>
       <c r="U26" s="521">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>97.82</v>
       </c>
       <c r="V26" s="521">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>102.2</v>
       </c>
       <c r="W26" s="521">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="X26" s="521">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Y26" s="521">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z26" s="521">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AA26" s="521">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AB26" s="521">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AC26" s="521">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD26" s="521">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE26" s="521">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AF26" s="521">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AG26" s="521"/>
       <c r="AH26" s="484">
         <f>SUM($B26:AF26)</f>
-        <v>1979.03</v>
+        <v>2081.23</v>
       </c>
       <c r="AI26" s="523">
         <f>AH29+AH45+AH36</f>
-        <v>5886</v>
+        <v>6418</v>
       </c>
       <c r="AK26" s="524">
         <f>(AI26*10)/AH9</f>
-        <v>12.001456323507391</v>
+        <v>11.552251853922225</v>
       </c>
     </row>
     <row r="27" spans="1:149" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -20168,7 +19884,7 @@
       </c>
       <c r="V29" s="509">
         <f>'Water '!$H27</f>
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="W29" s="509">
         <f>'Water '!$H28</f>
@@ -20213,38 +19929,38 @@
       <c r="AG29" s="509"/>
       <c r="AH29" s="484">
         <f>SUM($B29:AF29)</f>
-        <v>3096</v>
+        <v>3388</v>
       </c>
       <c r="AI29" s="484"/>
       <c r="AJ29" s="484"/>
     </row>
     <row r="30" spans="1:149" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A30" s="507" t="str">
-        <f t="shared" ref="A30:AF30" si="6">A36</f>
+        <f t="shared" ref="A30:AF30" si="7">A36</f>
         <v>Brewhouse</v>
       </c>
       <c r="B30" s="508">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>157</v>
       </c>
       <c r="C30" s="508">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>126</v>
       </c>
       <c r="D30" s="508" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E30" s="508" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F30" s="508">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>182</v>
       </c>
       <c r="G30" s="508">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>234</v>
       </c>
       <c r="H30" s="508">
@@ -20252,67 +19968,67 @@
         <v>227</v>
       </c>
       <c r="I30" s="508">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>187</v>
       </c>
       <c r="J30" s="509">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>192</v>
       </c>
       <c r="K30" s="509">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>162</v>
       </c>
       <c r="L30" s="509">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>18</v>
       </c>
       <c r="M30" s="509">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>72</v>
       </c>
       <c r="N30" s="509">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>86</v>
       </c>
       <c r="O30" s="509">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>216</v>
       </c>
       <c r="P30" s="509">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>220</v>
       </c>
       <c r="Q30" s="509">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>187</v>
       </c>
       <c r="R30" s="509">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>22</v>
       </c>
       <c r="S30" s="509" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T30" s="509" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="U30" s="509">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>140</v>
       </c>
-      <c r="V30" s="509" t="str">
-        <f t="shared" si="6"/>
-        <v>0</v>
+      <c r="V30" s="509">
+        <f t="shared" si="7"/>
+        <v>210</v>
       </c>
       <c r="W30" s="509" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="X30" s="509" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Y30" s="509" t="str">
@@ -20320,15 +20036,15 @@
         <v>0</v>
       </c>
       <c r="Z30" s="509" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AA30" s="509" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AB30" s="509" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AC30" s="509" t="str">
@@ -20336,60 +20052,60 @@
         <v>0</v>
       </c>
       <c r="AD30" s="509" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AE30" s="509" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AF30" s="509" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AG30" s="509"/>
       <c r="AH30" s="484">
         <f>AH36</f>
-        <v>2428</v>
+        <v>2638</v>
       </c>
       <c r="AI30" s="484"/>
       <c r="AJ30" s="484"/>
     </row>
     <row r="31" spans="1:149" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A31" s="507" t="str">
-        <f t="shared" ref="A31:AF31" si="7">A45</f>
+        <f t="shared" ref="A31:AF31" si="8">A45</f>
         <v>Boiler Supply</v>
       </c>
       <c r="B31" s="508">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
       <c r="C31" s="508">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="D31" s="508">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="E31" s="508">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="F31" s="508">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="G31" s="508">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="H31" s="508">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="I31" s="508">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
       <c r="J31" s="509">
@@ -20401,7 +20117,7 @@
         <v>11</v>
       </c>
       <c r="L31" s="509">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="M31" s="509">
@@ -20409,85 +20125,85 @@
         <v>71</v>
       </c>
       <c r="N31" s="509">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>15</v>
       </c>
       <c r="O31" s="509">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
       <c r="P31" s="509">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>27</v>
       </c>
       <c r="Q31" s="509">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="R31" s="509">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="S31" s="509" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T31" s="509">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="U31" s="509">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>47</v>
       </c>
-      <c r="V31" s="509" t="str">
+      <c r="V31" s="509">
         <f>V45</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="W31" s="509" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X31" s="509" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Y31" s="509" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Z31" s="509" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AA31" s="509" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AB31" s="509" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AC31" s="509" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AD31" s="509" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE31" s="509" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AF31" s="509" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AG31" s="509"/>
       <c r="AH31" s="484">
         <f>AH45</f>
-        <v>362</v>
+        <v>392</v>
       </c>
       <c r="AI31" s="484"/>
       <c r="AJ31" s="484"/>
@@ -20505,31 +20221,31 @@
         <v>332</v>
       </c>
       <c r="D32" s="526">
-        <f t="shared" ref="D32:AF32" si="8">SUM(D28:D31)</f>
+        <f t="shared" ref="D32:AF32" si="9">SUM(D28:D31)</f>
         <v>48</v>
       </c>
       <c r="E32" s="526">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>49</v>
       </c>
       <c r="F32" s="526">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>388</v>
       </c>
       <c r="G32" s="526">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>453</v>
       </c>
       <c r="H32" s="526">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>462</v>
       </c>
       <c r="I32" s="526">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>422</v>
       </c>
       <c r="J32" s="527">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>422</v>
       </c>
       <c r="K32" s="527">
@@ -20537,23 +20253,23 @@
         <v>230</v>
       </c>
       <c r="L32" s="527">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>70</v>
       </c>
       <c r="M32" s="527">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>312</v>
       </c>
       <c r="N32" s="527">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>340</v>
       </c>
       <c r="O32" s="527">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>458</v>
       </c>
       <c r="P32" s="527">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>472</v>
       </c>
       <c r="Q32" s="527">
@@ -20561,47 +20277,47 @@
         <v>408</v>
       </c>
       <c r="R32" s="527">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>61</v>
       </c>
       <c r="S32" s="527">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>67</v>
       </c>
       <c r="T32" s="527">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>202</v>
       </c>
       <c r="U32" s="527">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>265</v>
       </c>
       <c r="V32" s="527">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>532</v>
       </c>
       <c r="W32" s="526">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="X32" s="527">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Y32" s="527">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z32" s="527">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AA32" s="527">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AB32" s="527">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AC32" s="527">
@@ -20609,21 +20325,21 @@
         <v>0</v>
       </c>
       <c r="AD32" s="527">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AE32" s="527">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AF32" s="527">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AG32" s="527"/>
       <c r="AH32" s="526">
         <f>SUM($B32:AF32)</f>
-        <v>5886</v>
+        <v>6418</v>
       </c>
       <c r="AI32" s="526"/>
       <c r="AJ32" s="528"/>
@@ -20852,9 +20568,9 @@
         <f>+'Water '!$J26</f>
         <v>140</v>
       </c>
-      <c r="V36" s="535" t="str">
+      <c r="V36" s="535">
         <f>+'Water '!$J27</f>
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="W36" s="535" t="str">
         <f>+'Water '!$J28</f>
@@ -20899,7 +20615,7 @@
       <c r="AG36" s="508"/>
       <c r="AH36" s="484">
         <f>SUM($B36:AF36)</f>
-        <v>2428</v>
+        <v>2638</v>
       </c>
       <c r="AI36" s="484"/>
     </row>
@@ -21662,9 +21378,9 @@
         <f>+'Water '!$N26</f>
         <v>41</v>
       </c>
-      <c r="V41" s="539" t="str">
+      <c r="V41" s="539">
         <f>+'Water '!$N27</f>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="W41" s="539" t="str">
         <f>+'Water '!$N28</f>
@@ -21709,7 +21425,7 @@
       <c r="AG41" s="539"/>
       <c r="AH41" s="514">
         <f>SUM($B41:AF41)</f>
-        <v>524</v>
+        <v>543</v>
       </c>
       <c r="AI41" s="514"/>
       <c r="AJ41" s="514"/>
@@ -21911,9 +21627,9 @@
         <f>+'Water '!$O26</f>
         <v>135</v>
       </c>
-      <c r="V42" s="508" t="str">
+      <c r="V42" s="508">
         <f>+'Water '!$O27</f>
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="W42" s="508" t="str">
         <f>+'Water '!$O28</f>
@@ -21958,7 +21674,7 @@
       <c r="AG42" s="508"/>
       <c r="AH42" s="540">
         <f>SUM($B42:AF42)</f>
-        <v>1340</v>
+        <v>1498</v>
       </c>
       <c r="AI42" s="508"/>
       <c r="AJ42" s="508"/>
@@ -22141,8 +21857,8 @@
       <c r="U43" s="542">
         <v>29</v>
       </c>
-      <c r="V43" s="542" t="str">
-        <v>0</v>
+      <c r="V43" s="542">
+        <v>31</v>
       </c>
       <c r="W43" s="542" t="str">
         <v>0</v>
@@ -22177,7 +21893,7 @@
       <c r="AG43" s="542"/>
       <c r="AH43" s="543">
         <f>SUM($B43:AF43)</f>
-        <v>275</v>
+        <v>306</v>
       </c>
       <c r="AI43" s="544"/>
       <c r="AJ43" s="474"/>
@@ -22628,9 +22344,9 @@
         <f>+'Water '!$Q26</f>
         <v>47</v>
       </c>
-      <c r="V45" s="539" t="str">
+      <c r="V45" s="539">
         <f>+'Water '!$Q27</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="W45" s="539" t="str">
         <f>+'Water '!$Q28</f>
@@ -22675,7 +22391,7 @@
       <c r="AG45" s="539"/>
       <c r="AH45" s="514">
         <f>SUM($B45:AF45)</f>
-        <v>362</v>
+        <v>392</v>
       </c>
       <c r="AI45" s="514"/>
       <c r="AJ45" s="514"/>
@@ -23268,19 +22984,19 @@
         <v>352</v>
       </c>
       <c r="C50" s="484">
-        <f t="shared" ref="C50:AE50" si="9">SUM(C36:C48)</f>
+        <f t="shared" ref="C50:AE50" si="10">SUM(C36:C48)</f>
         <v>285</v>
       </c>
       <c r="D50" s="484">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="E50" s="484">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="F50" s="484">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>370</v>
       </c>
       <c r="G50" s="484">
@@ -23288,39 +23004,39 @@
         <v>408</v>
       </c>
       <c r="H50" s="484">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>404</v>
       </c>
       <c r="I50" s="484">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>382</v>
       </c>
       <c r="J50" s="484">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>350</v>
       </c>
       <c r="K50" s="484">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>184</v>
       </c>
       <c r="L50" s="484">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>27</v>
       </c>
       <c r="M50" s="484">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>319</v>
       </c>
       <c r="N50" s="484">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>256</v>
       </c>
       <c r="O50" s="484">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>397</v>
       </c>
       <c r="P50" s="484">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>422</v>
       </c>
       <c r="Q50" s="484">
@@ -23328,7 +23044,7 @@
         <v>344</v>
       </c>
       <c r="R50" s="484">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>36</v>
       </c>
       <c r="S50" s="484">
@@ -23336,43 +23052,43 @@
         <v>35</v>
       </c>
       <c r="T50" s="484">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8</v>
       </c>
       <c r="U50" s="484">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>398</v>
       </c>
       <c r="V50" s="484">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>448</v>
       </c>
       <c r="W50" s="484">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X50" s="484">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="Y50" s="484">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="Z50" s="484">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AA50" s="484">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AB50" s="484">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AC50" s="484">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AD50" s="484">
@@ -23380,7 +23096,7 @@
         <v>0</v>
       </c>
       <c r="AE50" s="484">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AF50" s="484">
@@ -23390,7 +23106,7 @@
       <c r="AG50" s="484"/>
       <c r="AH50" s="484">
         <f>SUM($B50:AF50)</f>
-        <v>4982</v>
+        <v>5430</v>
       </c>
       <c r="AI50" s="484"/>
     </row>
@@ -23487,23 +23203,23 @@
         <v>225</v>
       </c>
       <c r="B54" s="545">
-        <f t="shared" ref="B54:F54" si="10">IF(B$9=0,"",+(B36*10)/B$9)</f>
+        <f t="shared" ref="B54:F54" si="11">IF(B$9=0,"",+(B36*10)/B$9)</f>
         <v>4.2713556902075496</v>
       </c>
       <c r="C54" s="545">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.4438801422041649</v>
       </c>
       <c r="D54" s="545" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="E54" s="545" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="F54" s="545">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.5742384426435363</v>
       </c>
       <c r="G54" s="545">
@@ -23515,67 +23231,67 @@
         <v>5.5852451110651824</v>
       </c>
       <c r="I54" s="545">
-        <f t="shared" ref="I54:AF54" si="11">IF(I$9=0,"",+(I36*10)/I$9)</f>
+        <f t="shared" ref="I54:AF54" si="12">IF(I$9=0,"",+(I36*10)/I$9)</f>
         <v>5.1769291674279794</v>
       </c>
       <c r="J54" s="545">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>6.2239856848329245</v>
       </c>
       <c r="K54" s="545" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="L54" s="545" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="M54" s="545">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3.0362067656807428</v>
       </c>
       <c r="N54" s="545">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.5118114665625977</v>
       </c>
       <c r="O54" s="545">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4.2403825767391456</v>
       </c>
       <c r="P54" s="545">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4.6008741660915575</v>
       </c>
       <c r="Q54" s="545">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7.9879710553519407</v>
       </c>
       <c r="R54" s="545" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="S54" s="545" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="T54" s="545" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="U54" s="545">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3.0054011351829431</v>
       </c>
-      <c r="V54" s="545" t="str">
-        <f t="shared" si="11"/>
-        <v/>
+      <c r="V54" s="545">
+        <f t="shared" si="12"/>
+        <v>3.2247067820190352</v>
       </c>
       <c r="W54" s="545" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="X54" s="545" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="Y54" s="545" t="str">
@@ -23583,15 +23299,15 @@
         <v/>
       </c>
       <c r="Z54" s="545" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AA54" s="545" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AB54" s="545" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AC54" s="545" t="str">
@@ -23599,28 +23315,28 @@
         <v/>
       </c>
       <c r="AD54" s="545" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AE54" s="545" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AF54" s="545" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AG54" s="545"/>
       <c r="AH54" s="546">
         <f>+(AH36*10)/AH$9</f>
-        <v>4.9506517080319306</v>
+        <v>4.7483391072992882</v>
       </c>
       <c r="AI54" s="546">
         <v>3.2</v>
       </c>
       <c r="AJ54" s="547">
-        <f t="shared" ref="AJ54:AJ67" si="12">AI54-AH54</f>
-        <v>-1.7506517080319304</v>
+        <f t="shared" ref="AJ54:AJ67" si="13">AI54-AH54</f>
+        <v>-1.548339107299288</v>
       </c>
     </row>
     <row r="55" spans="1:59" s="553" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -23660,14 +23376,14 @@
       <c r="AF55" s="549"/>
       <c r="AG55" s="549"/>
       <c r="AH55" s="550">
-        <f t="shared" ref="AH55:AH61" si="13">+(AH37*10)/AH$9</f>
+        <f t="shared" ref="AH55:AH61" si="14">+(AH37*10)/AH$9</f>
         <v>0</v>
       </c>
       <c r="AI55" s="550">
         <v>0.1</v>
       </c>
       <c r="AJ55" s="551">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.1</v>
       </c>
       <c r="AK55" s="552"/>
@@ -23699,139 +23415,139 @@
         <v>185</v>
       </c>
       <c r="B56" s="545">
-        <f t="shared" ref="B56:C63" si="14">IF(B$9=0,"",+(B38*10)/B$9)</f>
+        <f t="shared" ref="B56:C63" si="15">IF(B$9=0,"",+(B38*10)/B$9)</f>
         <v>0</v>
       </c>
       <c r="C56" s="545">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D56" s="545" t="str">
-        <f t="shared" ref="D56:F62" si="15">IF(D$9=0,"",+(D38*10)/D$9)</f>
+        <f t="shared" ref="D56:F62" si="16">IF(D$9=0,"",+(D38*10)/D$9)</f>
         <v/>
       </c>
       <c r="E56" s="545" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="F56" s="545">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="G56" s="545">
-        <f t="shared" ref="G56:H63" si="16">IF(G$9=0,"",+(G38*10)/G$9)</f>
+        <f t="shared" ref="G56:H63" si="17">IF(G$9=0,"",+(G38*10)/G$9)</f>
         <v>0</v>
       </c>
       <c r="H56" s="545">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="I56" s="545">
-        <f t="shared" ref="I56:AF56" si="17">IF(I$9=0,"",+(I38*10)/I$9)</f>
+        <f t="shared" ref="I56:AF56" si="18">IF(I$9=0,"",+(I38*10)/I$9)</f>
         <v>0</v>
       </c>
       <c r="J56" s="545">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="K56" s="545" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="L56" s="545" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="M56" s="545">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N56" s="545">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="O56" s="545">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P56" s="545">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q56" s="545">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="R56" s="545" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="S56" s="545" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="T56" s="545" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="U56" s="545">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V56" s="545" t="str">
-        <f t="shared" si="17"/>
-        <v/>
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V56" s="545">
+        <f t="shared" si="18"/>
+        <v>0</v>
       </c>
       <c r="W56" s="545" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="X56" s="545" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="Y56" s="545" t="str">
-        <f t="shared" ref="Y56:Y63" si="18">IF(Y$9=0,"",+(Y38*10)/Y$9)</f>
+        <f t="shared" ref="Y56:Y63" si="19">IF(Y$9=0,"",+(Y38*10)/Y$9)</f>
         <v/>
       </c>
       <c r="Z56" s="545" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AA56" s="545" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AB56" s="545" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AC56" s="545" t="str">
-        <f t="shared" ref="AC56:AC63" si="19">IF(AC$9=0,"",+(AC38*10)/AC$9)</f>
+        <f t="shared" ref="AC56:AC63" si="20">IF(AC$9=0,"",+(AC38*10)/AC$9)</f>
         <v/>
       </c>
       <c r="AD56" s="545" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE56" s="545" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AF56" s="545" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AG56" s="545"/>
       <c r="AH56" s="555">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AI56" s="556">
         <v>0.1</v>
       </c>
       <c r="AJ56" s="557">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.1</v>
       </c>
       <c r="AK56" s="558"/>
@@ -23863,123 +23579,123 @@
         <v>217</v>
       </c>
       <c r="B57" s="549">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="C57" s="549">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D57" s="549" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="E57" s="549" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="F57" s="549">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="G57" s="549">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="H57" s="549">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="I57" s="549">
-        <f t="shared" ref="I57:AE57" si="20">IF(I$9=0,"",+(I39*10)/I$9)</f>
+        <f t="shared" ref="I57:AE57" si="21">IF(I$9=0,"",+(I39*10)/I$9)</f>
         <v>0</v>
       </c>
       <c r="J57" s="549">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="549" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="L57" s="549" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="M57" s="549">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="N57" s="549">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="O57" s="549">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="P57" s="549">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="Q57" s="549">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R57" s="549" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="S57" s="549" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="T57" s="549" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="U57" s="549">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="V57" s="549">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="W57" s="549" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="X57" s="549" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="Y57" s="549" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="Z57" s="549" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AA57" s="549" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AB57" s="549" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AC57" s="549" t="str">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K57" s="549" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="L57" s="549" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="M57" s="549">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="N57" s="549">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O57" s="549">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="P57" s="549">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="Q57" s="549">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="R57" s="549" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="S57" s="549" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="T57" s="549" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="U57" s="549">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="V57" s="549" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="W57" s="549" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="X57" s="549" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="Y57" s="549" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="Z57" s="549" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="AA57" s="549" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="AB57" s="549" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="AC57" s="549" t="str">
-        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AD57" s="549" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="AE57" s="549" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="AF57" s="549" t="str">
@@ -23988,14 +23704,14 @@
       </c>
       <c r="AG57" s="549"/>
       <c r="AH57" s="550">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AI57" s="550">
         <v>0.7</v>
       </c>
       <c r="AJ57" s="551">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="AK57" s="474"/>
@@ -24027,139 +23743,139 @@
         <v>170</v>
       </c>
       <c r="B58" s="545">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="C58" s="545">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D58" s="545" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="E58" s="545" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="F58" s="545">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="G58" s="545">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="H58" s="545">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="I58" s="545">
-        <f t="shared" ref="I58:AF58" si="21">IF(I$9=0,"",+(I40*10)/I$9)</f>
+        <f t="shared" ref="I58:AF58" si="22">IF(I$9=0,"",+(I40*10)/I$9)</f>
         <v>0</v>
       </c>
       <c r="J58" s="545">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K58" s="545" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="L58" s="545" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="M58" s="545">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N58" s="545">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="O58" s="545">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="P58" s="545">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Q58" s="545">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="R58" s="545" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="S58" s="545" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="T58" s="545" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="U58" s="545">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="V58" s="545" t="str">
-        <f t="shared" si="21"/>
-        <v/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="V58" s="545">
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="W58" s="545" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="X58" s="545" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="Y58" s="545" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Z58" s="545" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AA58" s="545" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AB58" s="545" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AC58" s="545" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AD58" s="545" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AE58" s="545" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AF58" s="545" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="AG58" s="545"/>
       <c r="AH58" s="555">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AI58" s="562">
         <v>1</v>
       </c>
       <c r="AJ58" s="563">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="AK58" s="564"/>
@@ -24193,75 +23909,75 @@
         <v>96</v>
       </c>
       <c r="B59" s="549">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.6051591447276781</v>
       </c>
       <c r="C59" s="549">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.5518311607697082</v>
       </c>
       <c r="D59" s="549" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="E59" s="549" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="F59" s="549">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.1638519825299691</v>
       </c>
       <c r="G59" s="549">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1.0918497614728213</v>
       </c>
       <c r="H59" s="549">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1.2302302006751504</v>
       </c>
       <c r="I59" s="549">
-        <f t="shared" ref="I59:AF59" si="22">IF(I$9=0,"",+(I41*10)/I$9)</f>
+        <f t="shared" ref="I59:AF59" si="23">IF(I$9=0,"",+(I41*10)/I$9)</f>
         <v>1.8548355840517359</v>
       </c>
       <c r="J59" s="549">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1.3290802764486973</v>
       </c>
       <c r="K59" s="549" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="L59" s="549" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M59" s="549">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1.2229166139547436</v>
       </c>
       <c r="N59" s="549">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.4746384836882574</v>
       </c>
       <c r="O59" s="549">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.21594540900060463</v>
       </c>
       <c r="P59" s="549">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.41826128782650518</v>
       </c>
       <c r="Q59" s="549">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>2.0503882922828511</v>
       </c>
       <c r="R59" s="549" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="S59" s="549" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="T59" s="549" t="str">
@@ -24269,64 +23985,64 @@
         <v/>
       </c>
       <c r="U59" s="549">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.88015318958929045</v>
       </c>
-      <c r="V59" s="549" t="str">
-        <f t="shared" si="22"/>
-        <v/>
+      <c r="V59" s="549">
+        <f t="shared" si="23"/>
+        <v>0.29175918503981746</v>
       </c>
       <c r="W59" s="549" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="X59" s="549" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="Y59" s="549" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Z59" s="549" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AA59" s="549" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AB59" s="549" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AC59" s="549" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AD59" s="549" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AE59" s="549" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AF59" s="549" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="AG59" s="549"/>
       <c r="AH59" s="549">
-        <f t="shared" si="13"/>
-        <v>1.0684273043693293</v>
+        <f t="shared" si="14"/>
+        <v>0.97738746598313619</v>
       </c>
       <c r="AI59" s="550">
         <v>0.7</v>
       </c>
       <c r="AJ59" s="551">
-        <f t="shared" si="12"/>
-        <v>-0.36842730436932936</v>
+        <f t="shared" si="13"/>
+        <v>-0.27738746598313624</v>
       </c>
       <c r="AK59" s="474"/>
       <c r="AL59" s="474"/>
@@ -24357,43 +24073,43 @@
         <v>125</v>
       </c>
       <c r="B60" s="545">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2.6934026326786462</v>
       </c>
       <c r="C60" s="545">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2.856780091416963</v>
       </c>
       <c r="D60" s="545" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="E60" s="545" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="F60" s="567">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3.4303005800883302</v>
       </c>
       <c r="G60" s="545">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2.7716186252771617</v>
       </c>
       <c r="H60" s="545">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2.2390189652287735</v>
       </c>
       <c r="I60" s="545">
-        <f t="shared" ref="I60:AF60" si="23">IF(I$9=0,"",+(I42*10)/I$9)</f>
+        <f t="shared" ref="I60:AF60" si="24">IF(I$9=0,"",+(I42*10)/I$9)</f>
         <v>2.4638860743373807</v>
       </c>
       <c r="J60" s="545">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>2.4636610002463657</v>
       </c>
       <c r="K60" s="545" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="L60" s="545" t="str">
@@ -24401,96 +24117,96 @@
         <v/>
       </c>
       <c r="M60" s="545">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>5.0181750710556718</v>
       </c>
       <c r="N60" s="545">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1.7403411068569439</v>
       </c>
       <c r="O60" s="545">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>2.2379796932789935</v>
       </c>
       <c r="P60" s="545">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>2.4468285337850553</v>
       </c>
       <c r="Q60" s="545">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>2.7338510563771345</v>
       </c>
       <c r="R60" s="545" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="S60" s="545" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="T60" s="545" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="U60" s="545">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>2.8980653803549807</v>
       </c>
-      <c r="V60" s="545" t="str">
-        <f t="shared" si="23"/>
-        <v/>
+      <c r="V60" s="545">
+        <f t="shared" si="24"/>
+        <v>2.4262079598047976</v>
       </c>
       <c r="W60" s="545" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="X60" s="545" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="Y60" s="545" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Z60" s="545" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AA60" s="545" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AB60" s="545" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AC60" s="545" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AD60" s="545" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AE60" s="545" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AF60" s="545" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AG60" s="545"/>
       <c r="AH60" s="568">
-        <f t="shared" si="13"/>
-        <v>2.7322377630818728</v>
+        <f t="shared" si="14"/>
+        <v>2.6963654218098307</v>
       </c>
       <c r="AI60" s="555">
         <v>2.1</v>
       </c>
       <c r="AJ60" s="547">
-        <f t="shared" si="12"/>
-        <v>-0.63223776308187274</v>
+        <f t="shared" si="13"/>
+        <v>-0.59636542180983065</v>
       </c>
     </row>
     <row r="61" spans="1:59" s="504" customFormat="1" x14ac:dyDescent="0.35">
@@ -24498,140 +24214,140 @@
         <v>166</v>
       </c>
       <c r="B61" s="549">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.43529739518038724</v>
       </c>
       <c r="C61" s="549">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.5290333502624005</v>
       </c>
       <c r="D61" s="549" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="E61" s="549" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="F61" s="549">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.52067062376340723</v>
       </c>
       <c r="G61" s="549">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.47593451141122983</v>
       </c>
       <c r="H61" s="549">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.41827826822955111</v>
       </c>
       <c r="I61" s="549">
-        <f t="shared" ref="I61:AF61" si="24">IF(I$9=0,"",+(I43*10)/I$9)</f>
+        <f t="shared" ref="I61:AF61" si="25">IF(I$9=0,"",+(I43*10)/I$9)</f>
         <v>0.49831403750643655</v>
       </c>
       <c r="J61" s="549">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.4538322895190674</v>
       </c>
       <c r="K61" s="549" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="L61" s="549" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="M61" s="549">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.96989938348134841</v>
       </c>
       <c r="N61" s="549">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.45705928058869233</v>
       </c>
       <c r="O61" s="549">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.56931062372886676</v>
       </c>
       <c r="P61" s="549">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.64830499613108306</v>
       </c>
       <c r="Q61" s="549">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.76889560960606917</v>
       </c>
       <c r="R61" s="549" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="S61" s="549" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="T61" s="549" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="U61" s="549">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.62254737800218107</v>
       </c>
-      <c r="V61" s="549" t="str">
-        <f t="shared" si="24"/>
-        <v/>
+      <c r="V61" s="549">
+        <f t="shared" si="25"/>
+        <v>0.47602814401233373</v>
       </c>
       <c r="W61" s="549" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="X61" s="549" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Y61" s="549" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Z61" s="549" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AA61" s="549" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AB61" s="549" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AC61" s="549" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AD61" s="549" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AE61" s="549" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AF61" s="549" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AG61" s="549"/>
       <c r="AH61" s="550">
-        <f t="shared" si="13"/>
-        <v>0.56072043645336944</v>
+        <f t="shared" si="14"/>
+        <v>0.55079293663138063</v>
       </c>
       <c r="AI61" s="550">
         <v>0.7</v>
       </c>
       <c r="AJ61" s="551">
-        <f t="shared" si="12"/>
-        <v>0.13927956354663051</v>
+        <f t="shared" si="13"/>
+        <v>0.14920706336861933</v>
       </c>
       <c r="AK61" s="474"/>
       <c r="AL61" s="474"/>
@@ -24670,47 +24386,47 @@
         <v>0.10580667005248011</v>
       </c>
       <c r="D62" s="545" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="E62" s="545" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="F62" s="545">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3.0627683750788663E-2</v>
       </c>
       <c r="G62" s="545">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>8.3988443190217019E-2</v>
       </c>
       <c r="H62" s="545">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>7.3813812040509019E-2</v>
       </c>
       <c r="I62" s="545">
-        <f t="shared" ref="I62:AF62" si="25">IF(I$9=0,"",+(I44*10)/I$9)</f>
+        <f t="shared" ref="I62:AF62" si="26">IF(I$9=0,"",+(I44*10)/I$9)</f>
         <v>0.11073645277920811</v>
       </c>
       <c r="J62" s="545">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>9.7249776325514445E-2</v>
       </c>
       <c r="K62" s="545" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="L62" s="545" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="M62" s="545">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.21084769206116269</v>
       </c>
       <c r="N62" s="545">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>5.2737609298695268E-2</v>
       </c>
       <c r="O62" s="545">
@@ -24718,84 +24434,84 @@
         <v>0.1177884049094207</v>
       </c>
       <c r="P62" s="545">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.14639145073927681</v>
       </c>
       <c r="Q62" s="545">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.29901495929124911</v>
       </c>
       <c r="R62" s="545" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="S62" s="545" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="T62" s="545" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="U62" s="545">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.12880290579355469</v>
       </c>
-      <c r="V62" s="545" t="str">
-        <f t="shared" si="25"/>
-        <v/>
+      <c r="V62" s="545">
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="W62" s="545" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="X62" s="545" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="Y62" s="545" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Z62" s="545" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA62" s="545" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AB62" s="545" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AC62" s="545" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AD62" s="545" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AE62" s="545" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AF62" s="545" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AG62" s="545"/>
       <c r="AH62" s="555">
         <f>+(AH44*10)/AH$9</f>
-        <v>0.10806612048010392</v>
+        <v>9.5398776606088809E-2</v>
       </c>
       <c r="AI62" s="555">
         <v>0.1</v>
       </c>
       <c r="AJ62" s="547">
-        <f t="shared" si="12"/>
-        <v>-8.066120480103911E-3</v>
+        <f t="shared" si="13"/>
+        <v>4.6012233939111968E-3</v>
       </c>
     </row>
     <row r="63" spans="1:59" s="504" customFormat="1" x14ac:dyDescent="0.35">
@@ -24803,11 +24519,11 @@
         <v>126</v>
       </c>
       <c r="B63" s="549">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.51691565677670981</v>
       </c>
       <c r="C63" s="549">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.56430224027989395</v>
       </c>
       <c r="D63" s="549" t="str">
@@ -24815,128 +24531,128 @@
         <v/>
       </c>
       <c r="E63" s="569" t="str">
-        <f t="shared" ref="E63:AF63" si="26">IF(E$9=0,"",+(E45*10)/E$9)</f>
+        <f t="shared" ref="E63:AF63" si="27">IF(E$9=0,"",+(E45*10)/E$9)</f>
         <v/>
       </c>
       <c r="F63" s="569">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.61255367501577329</v>
       </c>
       <c r="G63" s="569">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.44793836368115747</v>
       </c>
       <c r="H63" s="569">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.3936736642160481</v>
       </c>
       <c r="I63" s="569">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.47062992431163453</v>
       </c>
       <c r="J63" s="569">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.77799821060411556</v>
       </c>
       <c r="K63" s="569" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="L63" s="569" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="M63" s="569">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>2.9940372272685103</v>
       </c>
       <c r="N63" s="569">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.26368804649347632</v>
       </c>
       <c r="O63" s="569">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.41225941718297249</v>
       </c>
       <c r="P63" s="549">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.56465273856578202</v>
       </c>
       <c r="Q63" s="549">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.8543284551178546</v>
       </c>
       <c r="R63" s="569" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="S63" s="569" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="T63" s="549" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="U63" s="549">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1.0089560953828451</v>
       </c>
-      <c r="V63" s="549" t="str">
-        <f t="shared" si="26"/>
-        <v/>
+      <c r="V63" s="549">
+        <f t="shared" si="27"/>
+        <v>0.46067239743129074</v>
       </c>
       <c r="W63" s="549" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="X63" s="549" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="Y63" s="549" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Z63" s="549" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AA63" s="549" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AB63" s="549" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AC63" s="549" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AD63" s="549" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AE63" s="549" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AF63" s="549" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="AG63" s="549"/>
       <c r="AH63" s="550">
         <f>+(AH45*10)/AH$9</f>
-        <v>0.73811199271316263</v>
+        <v>0.70559095150163798</v>
       </c>
       <c r="AI63" s="550">
         <v>0.6</v>
       </c>
       <c r="AJ63" s="551">
-        <f t="shared" si="12"/>
-        <v>-0.13811199271316266</v>
+        <f t="shared" si="13"/>
+        <v>-0.105590951501638</v>
       </c>
       <c r="AK63" s="474"/>
       <c r="AL63" s="474"/>
@@ -25003,7 +24719,7 @@
         <v>0.5</v>
       </c>
       <c r="AJ64" s="572">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.5</v>
       </c>
       <c r="AK64" s="573"/>
@@ -25047,11 +24763,11 @@
         <v/>
       </c>
       <c r="E65" s="575" t="str">
-        <f t="shared" ref="E65:AF65" si="27">IF(E$9=0,"",+(E46*10)/E$9)</f>
+        <f t="shared" ref="E65:AF65" si="28">IF(E$9=0,"",+(E46*10)/E$9)</f>
         <v/>
       </c>
       <c r="F65" s="575">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="G65" s="575">
@@ -25063,7 +24779,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="549">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="J65" s="549">
@@ -25071,59 +24787,59 @@
         <v>0</v>
       </c>
       <c r="K65" s="549" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="L65" s="575" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="M65" s="549">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="N65" s="549">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="O65" s="549">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="P65" s="549">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="Q65" s="549">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="R65" s="549" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="S65" s="549" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="T65" s="549" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U65" s="549">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="V65" s="575" t="str">
-        <f t="shared" si="27"/>
-        <v/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="V65" s="575">
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="W65" s="575" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="X65" s="575" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="Y65" s="575" t="str">
@@ -25131,15 +24847,15 @@
         <v/>
       </c>
       <c r="Z65" s="575" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AA65" s="575" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AB65" s="575" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AC65" s="575" t="str">
@@ -25147,15 +24863,15 @@
         <v/>
       </c>
       <c r="AD65" s="575" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AE65" s="575" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AF65" s="575" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AG65" s="575"/>
@@ -25167,7 +24883,7 @@
         <v>0.3</v>
       </c>
       <c r="AJ65" s="551">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.3</v>
       </c>
       <c r="AK65" s="474"/>
@@ -25235,7 +24951,7 @@
         <v>0.4</v>
       </c>
       <c r="AJ66" s="572">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.4</v>
       </c>
       <c r="AK66" s="573"/>
@@ -25303,7 +25019,7 @@
         <v>0.2</v>
       </c>
       <c r="AJ67" s="582">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.2</v>
       </c>
       <c r="AK67" s="552"/>
@@ -25351,125 +25067,125 @@
         <v>0</v>
       </c>
       <c r="F68" s="584">
-        <f t="shared" ref="F68:AJ68" si="28">SUM(F54:F63,F65)</f>
+        <f t="shared" ref="F68:AJ68" si="29">SUM(F54:F63,F65)</f>
         <v>11.332242987791805</v>
       </c>
       <c r="G68" s="584">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>11.422428273869516</v>
       </c>
       <c r="H68" s="584">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>9.940260021455213</v>
       </c>
       <c r="I68" s="584">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>10.575331240414375</v>
       </c>
       <c r="J68" s="585">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>11.345807237976683</v>
       </c>
       <c r="K68" s="585">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="L68" s="585">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="M68" s="585">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>13.452082753502181</v>
       </c>
       <c r="N68" s="585">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>4.5002759934886623</v>
       </c>
       <c r="O68" s="585">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>7.7936661248400032</v>
       </c>
       <c r="P68" s="585">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>8.8253131731392589</v>
       </c>
       <c r="Q68" s="585">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>14.694449428027099</v>
       </c>
       <c r="R68" s="585">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="S68" s="585">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T68" s="585">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="U68" s="585">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>8.5439260843057951</v>
       </c>
       <c r="V68" s="585">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" si="29"/>
+        <v>6.8793744683072742</v>
       </c>
       <c r="W68" s="585">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="X68" s="585">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="Y68" s="585">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="Z68" s="585">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AA68" s="585">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AB68" s="585">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AC68" s="585">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AD68" s="585">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AE68" s="585">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AF68" s="585">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG68" s="585"/>
       <c r="AH68" s="584">
-        <f t="shared" si="28"/>
-        <v>10.158215325129769</v>
+        <f t="shared" si="29"/>
+        <v>9.7738746598313622</v>
       </c>
       <c r="AI68" s="584">
         <f>SUM(AI54:AI63,AI65)</f>
         <v>9.6</v>
       </c>
       <c r="AJ68" s="547">
-        <f t="shared" si="28"/>
-        <v>-0.55821532512976835</v>
+        <f t="shared" si="29"/>
+        <v>-0.17387465983136224</v>
       </c>
       <c r="AK68" s="468"/>
       <c r="AL68" s="291"/>
@@ -25508,133 +25224,133 @@
         <v>3.4916201117318435</v>
       </c>
       <c r="D69" s="587">
-        <f t="shared" ref="D69:AJ69" si="29">SUM(D60:D62)</f>
+        <f t="shared" ref="D69:AJ69" si="30">SUM(D60:D62)</f>
         <v>0</v>
       </c>
       <c r="E69" s="587">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F69" s="587">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>3.9815988876025261</v>
       </c>
       <c r="G69" s="587">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>3.3315415798786088</v>
       </c>
       <c r="H69" s="587">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2.7311110454988334</v>
       </c>
       <c r="I69" s="587">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>3.0729365646230251</v>
       </c>
       <c r="J69" s="588">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>3.0147430660909476</v>
       </c>
       <c r="K69" s="588">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="L69" s="588">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M69" s="588">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>6.198922146598183</v>
       </c>
       <c r="N69" s="588">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2.2501379967443311</v>
       </c>
       <c r="O69" s="588">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2.9250787219172807</v>
       </c>
       <c r="P69" s="588">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>3.2415249806554152</v>
       </c>
       <c r="Q69" s="588">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>3.801761625274453</v>
       </c>
       <c r="R69" s="588">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="S69" s="588">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="T69" s="588">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="U69" s="588">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>3.6494156641507165</v>
       </c>
       <c r="V69" s="588">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="30"/>
+        <v>2.9022361038171312</v>
       </c>
       <c r="W69" s="588">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="X69" s="588">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Y69" s="588">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z69" s="588">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AA69" s="588">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AB69" s="588">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AC69" s="588">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AD69" s="588">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AE69" s="588">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AF69" s="588">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AG69" s="588"/>
       <c r="AH69" s="587">
-        <f t="shared" si="29"/>
-        <v>3.4010243200153463</v>
+        <f t="shared" si="30"/>
+        <v>3.3425571350473002</v>
       </c>
       <c r="AI69" s="587">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2.9</v>
       </c>
       <c r="AJ69" s="587">
-        <f t="shared" si="29"/>
-        <v>-0.50102432001534614</v>
+        <f t="shared" si="30"/>
+        <v>-0.4425571350473001</v>
       </c>
       <c r="AK69" s="589"/>
       <c r="AL69" s="291"/>
@@ -25779,9 +25495,9 @@
         <f>+'Water '!$F26</f>
         <v>134</v>
       </c>
-      <c r="V71" s="593" t="str">
+      <c r="V71" s="593">
         <f>+'Water '!$F27</f>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="W71" s="593" t="str">
         <f>+'Water '!$F28</f>
@@ -25826,7 +25542,7 @@
       <c r="AG71" s="593"/>
       <c r="AH71" s="594">
         <f>SUM($B71:AF71)</f>
-        <v>2711</v>
+        <v>2851</v>
       </c>
       <c r="AI71" s="594"/>
       <c r="AJ71" s="595"/>
@@ -25993,10 +25709,14 @@
         <v>0</v>
       </c>
       <c r="U74" s="790">
-        <v>2224</v>
-      </c>
-      <c r="V74" s="790"/>
-      <c r="W74" s="790"/>
+        <v>2300</v>
+      </c>
+      <c r="V74" s="790">
+        <v>2200</v>
+      </c>
+      <c r="W74" s="790">
+        <v>0</v>
+      </c>
       <c r="X74" s="790"/>
       <c r="Y74" s="790"/>
       <c r="Z74" s="790"/>
@@ -26009,7 +25729,7 @@
       <c r="AG74" s="790"/>
       <c r="AH74" s="516">
         <f>SUM(B74:AF74)</f>
-        <v>26224</v>
+        <v>28500</v>
       </c>
       <c r="AI74" s="537"/>
       <c r="AJ74" s="537"/>
@@ -26102,8 +25822,8 @@
       <c r="U75" s="601">
         <v>2224.3099999999395</v>
       </c>
-      <c r="V75" s="601" t="str">
-        <v>0</v>
+      <c r="V75" s="601">
+        <v>2463.6900000000605</v>
       </c>
       <c r="W75" s="601" t="str">
         <v>0</v>
@@ -26138,7 +25858,7 @@
       <c r="AG75" s="599"/>
       <c r="AH75" s="516">
         <f>SUM(B75:AF75)</f>
-        <v>22480.039999999921</v>
+        <v>24943.729999999981</v>
       </c>
       <c r="AI75" s="600"/>
       <c r="AJ75" s="600"/>
@@ -26230,8 +25950,8 @@
       <c r="U76" s="604">
         <v>305.16000000000349</v>
       </c>
-      <c r="V76" s="604" t="str">
-        <v>0</v>
+      <c r="V76" s="604">
+        <v>354.58999999999651</v>
       </c>
       <c r="W76" s="604" t="str">
         <v>0</v>
@@ -26266,7 +25986,7 @@
       <c r="AG76" s="604"/>
       <c r="AH76" s="604">
         <f>SUM($B76:AF76)</f>
-        <v>2905.7300000000105</v>
+        <v>3260.320000000007</v>
       </c>
       <c r="AI76" s="605"/>
       <c r="AJ76" s="606"/>
@@ -26359,8 +26079,8 @@
       <c r="U77" s="607">
         <v>977.27999999999884</v>
       </c>
-      <c r="V77" s="607" t="str">
-        <v>0</v>
+      <c r="V77" s="607">
+        <v>408.61999999999534</v>
       </c>
       <c r="W77" s="607" t="str">
         <v>0</v>
@@ -26395,7 +26115,7 @@
       <c r="AG77" s="607"/>
       <c r="AH77" s="604">
         <f>SUM($B77:AF77)</f>
-        <v>7484.320000000007</v>
+        <v>7892.9400000000023</v>
       </c>
       <c r="AI77" s="757"/>
       <c r="AJ77" s="757" t="s">
@@ -26433,75 +26153,75 @@
         <v>821.00999999996566</v>
       </c>
       <c r="C78" s="788">
-        <f t="shared" ref="C78:T78" si="30">C75-C76-C77</f>
+        <f t="shared" ref="C78:T78" si="31">C75-C76-C77</f>
         <v>520.11000000000058</v>
       </c>
       <c r="D78" s="788">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="E78" s="788">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="F78" s="788">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>996.7000000000553</v>
       </c>
       <c r="G78" s="788">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>834.80999999993946</v>
       </c>
       <c r="H78" s="788">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>891.06000000005588</v>
       </c>
       <c r="I78" s="788">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>770.74000000000524</v>
       </c>
       <c r="J78" s="788">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>911.41999999999825</v>
       </c>
       <c r="K78" s="788">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>28.129999999902793</v>
       </c>
       <c r="L78" s="788">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M78" s="788">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>420.15000000005239</v>
       </c>
       <c r="N78" s="788">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1459.4599999999919</v>
       </c>
       <c r="O78" s="788">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1140.6000000000058</v>
       </c>
       <c r="P78" s="788">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1628.5899999999674</v>
       </c>
       <c r="Q78" s="788">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>725.34000000002561</v>
       </c>
       <c r="R78" s="788">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="S78" s="788">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="T78" s="788">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="U78" s="788">
@@ -26510,30 +26230,30 @@
       </c>
       <c r="V78" s="788">
         <f>V75-V76-V77</f>
-        <v>0</v>
+        <v>1700.4800000000687</v>
       </c>
       <c r="W78" s="882">
-        <f t="shared" ref="W78:AB78" si="31">W75-W76-W77</f>
+        <f t="shared" ref="W78:AB78" si="32">W75-W76-W77</f>
         <v>0</v>
       </c>
       <c r="X78" s="788">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="Y78" s="788">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="Z78" s="788">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AA78" s="788">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AB78" s="788">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AC78" s="788">
@@ -26541,11 +26261,11 @@
         <v>0</v>
       </c>
       <c r="AD78" s="788">
-        <f t="shared" ref="AD78:AE78" si="32">AD75-AD76-AD77</f>
+        <f t="shared" ref="AD78:AE78" si="33">AD75-AD76-AD77</f>
         <v>0</v>
       </c>
       <c r="AE78" s="788">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AF78" s="789">
@@ -26553,12 +26273,12 @@
         <v>0</v>
       </c>
       <c r="AG78" s="485">
-        <f t="shared" ref="AG78" si="33">AG75-AG76-AG77</f>
+        <f t="shared" ref="AG78" si="34">AG75-AG76-AG77</f>
         <v>0</v>
       </c>
       <c r="AH78" s="484">
         <f>AH75-AH76-AH77</f>
-        <v>12089.989999999903</v>
+        <v>13790.469999999972</v>
       </c>
       <c r="AI78" s="484"/>
     </row>
@@ -26757,7 +26477,7 @@
         <v>7790</v>
       </c>
       <c r="V80" s="613">
-        <v>0</v>
+        <v>7481</v>
       </c>
       <c r="W80" s="613">
         <v>0</v>
@@ -26792,7 +26512,7 @@
       <c r="AG80" s="613"/>
       <c r="AH80" s="594">
         <f>SUM(B80:AF80)</f>
-        <v>115751</v>
+        <v>123232</v>
       </c>
       <c r="AI80" s="594"/>
       <c r="AJ80" s="614"/>
@@ -26947,7 +26667,7 @@
         <v>9276.2999999999993</v>
       </c>
       <c r="T82" s="617">
-        <v>0</v>
+        <v>8975.6</v>
       </c>
       <c r="U82" s="617">
         <v>0</v>
@@ -26980,7 +26700,7 @@
         <v>0</v>
       </c>
       <c r="AE82" s="617">
-        <v>141439.99999999997</v>
+        <v>150415.59999999998</v>
       </c>
       <c r="AF82" s="617">
         <v>0</v>
@@ -26988,7 +26708,7 @@
       <c r="AG82" s="617"/>
       <c r="AH82" s="594">
         <f>SUM(B82:AF82)</f>
-        <v>265793.19999999995</v>
+        <v>283744.40000000002</v>
       </c>
       <c r="AI82" s="594"/>
       <c r="AJ82" s="614"/>
@@ -27082,7 +26802,7 @@
         <v>1486.3</v>
       </c>
       <c r="V83" s="621">
-        <v>0</v>
+        <v>1494.6</v>
       </c>
       <c r="W83" s="621">
         <v>0</v>
@@ -27117,7 +26837,7 @@
       <c r="AG83" s="621"/>
       <c r="AH83" s="594">
         <f>SUM(B83:AF83)</f>
-        <v>25688.999999999996</v>
+        <v>27183.599999999995</v>
       </c>
       <c r="AI83" s="594"/>
       <c r="AJ83" s="594"/>
@@ -27210,8 +26930,8 @@
       <c r="U84" s="620">
         <v>3811.4000000001397</v>
       </c>
-      <c r="V84" s="620" t="str">
-        <v>0</v>
+      <c r="V84" s="620">
+        <v>3661</v>
       </c>
       <c r="W84" s="620" t="str">
         <v>0</v>
@@ -27246,7 +26966,7 @@
       <c r="AG84" s="620"/>
       <c r="AH84" s="621">
         <f>SUM($B84:AF84)</f>
-        <v>42714.600000000093</v>
+        <v>46375.600000000093</v>
       </c>
       <c r="AI84" s="594"/>
       <c r="AJ84" s="614"/>
@@ -27624,7 +27344,7 @@
         <v>134</v>
       </c>
       <c r="B90" s="653">
-        <f t="shared" ref="B90:AF90" si="34">IF(B$9=0,"",+(B22*10)/B$9)</f>
+        <f t="shared" ref="B90:AF90" si="35">IF(B$9=0,"",+(B22*10)/B$9)</f>
         <v>6.3934304917119373</v>
       </c>
       <c r="C90" s="653">
@@ -27632,15 +27352,15 @@
         <v>11.003893685457932</v>
       </c>
       <c r="D90" s="653" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="E90" s="653" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="F90" s="653">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>4.3491310926119899</v>
       </c>
       <c r="G90" s="653">
@@ -27652,27 +27372,27 @@
         <v>9.3743541291446455</v>
       </c>
       <c r="I90" s="653">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>12.430166824466111</v>
       </c>
       <c r="J90" s="653">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>20.714202357334575</v>
       </c>
       <c r="K90" s="653" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="L90" s="653" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="M90" s="653">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>16.066594135060598</v>
       </c>
       <c r="N90" s="653">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>6.0999834755490863</v>
       </c>
       <c r="O90" s="653">
@@ -27680,11 +27400,11 @@
         <v>6.8317274847464011</v>
       </c>
       <c r="P90" s="653">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>9.5990965556182939</v>
       </c>
       <c r="Q90" s="653">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>23.45131609298511</v>
       </c>
       <c r="R90" s="653" t="str">
@@ -27692,51 +27412,51 @@
         <v/>
       </c>
       <c r="S90" s="653" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="T90" s="653" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="U90" s="653">
         <f>IF(U$9=0,"",+(U22*10)/U$9)</f>
         <v>8.5009917823746104</v>
       </c>
-      <c r="V90" s="653" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+      <c r="V90" s="653">
+        <f t="shared" si="35"/>
+        <v>8.8141985375186955</v>
       </c>
       <c r="W90" s="653" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="X90" s="653" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Y90" s="653" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Z90" s="653" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA90" s="653" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AB90" s="653" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AC90" s="653" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AD90" s="653" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AE90" s="653" t="str">
@@ -27744,24 +27464,24 @@
         <v/>
       </c>
       <c r="AF90" s="654" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AG90" s="627"/>
       <c r="AH90" s="659">
         <f>IF(AH$9=0,"0",+(AH22*10)/AH$9)</f>
-        <v>11.432579953432882</v>
+        <v>11.12565732457047</v>
       </c>
       <c r="AI90" s="662">
         <v>10.199999999999999</v>
       </c>
       <c r="AJ90" s="665">
         <f>+AI90-AH90</f>
-        <v>-1.2325799534328823</v>
+        <v>-0.92565732457047112</v>
       </c>
       <c r="AK90" s="667">
         <f>AH90/AI90*100</f>
-        <v>112.08411719051846</v>
+        <v>109.07507180951441</v>
       </c>
       <c r="AL90" s="629"/>
       <c r="AM90" s="630"/>
@@ -27827,7 +27547,7 @@
       <c r="AI91" s="671"/>
       <c r="AJ91" s="672"/>
       <c r="AK91" s="673" t="e">
-        <f t="shared" ref="AK91:AK96" si="35">AH91/AI91*100</f>
+        <f t="shared" ref="AK91:AK96" si="36">AH91/AI91*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AL91" s="629"/>
@@ -27858,23 +27578,23 @@
         <v>222</v>
       </c>
       <c r="B92" s="653">
-        <f t="shared" ref="B92:AF92" si="36">IF(B$9=0,"",+B74/B$9)</f>
+        <f t="shared" ref="B92:AF92" si="37">IF(B$9=0,"",+B74/B$9)</f>
         <v>4.3529739518038726</v>
       </c>
       <c r="C92" s="653">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>4.232266802099204</v>
       </c>
       <c r="D92" s="653" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="E92" s="653" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="F92" s="653">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>4.9004294001261863</v>
       </c>
       <c r="G92" s="653">
@@ -27886,116 +27606,116 @@
         <v>3.4446445618904211</v>
       </c>
       <c r="I92" s="653">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>8.3052339584406081</v>
       </c>
       <c r="J92" s="653">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5.5108206584458186</v>
       </c>
       <c r="K92" s="653" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="L92" s="653" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="M92" s="653">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>6.3254307618348804</v>
       </c>
       <c r="N92" s="653">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>3.6916326509086685</v>
       </c>
       <c r="O92" s="653">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>4.122594171829725</v>
       </c>
       <c r="P92" s="653">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>7.5287031808770939</v>
       </c>
       <c r="Q92" s="653">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>8.1161203236196187</v>
       </c>
       <c r="R92" s="653" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="S92" s="653" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="T92" s="653" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="U92" s="653">
-        <f t="shared" si="36"/>
-        <v>4.7742943747477611</v>
-      </c>
-      <c r="V92" s="653" t="str">
-        <f t="shared" si="36"/>
-        <v/>
+        <f t="shared" si="37"/>
+        <v>4.9374447220862629</v>
+      </c>
+      <c r="V92" s="653">
+        <f t="shared" si="37"/>
+        <v>3.3782642478294651</v>
       </c>
       <c r="W92" s="653" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="X92" s="653" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="Y92" s="653" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="Z92" s="653" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AA92" s="653" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AB92" s="653" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AC92" s="653" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD92" s="653" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AE92" s="653" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AF92" s="653" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AG92" s="628"/>
       <c r="AH92" s="670">
         <f>IF(AH$9=0,"0",+(AH74)/AH$9)</f>
-        <v>5.3470300820193302</v>
+        <v>5.1299342137236428</v>
       </c>
       <c r="AI92" s="674">
         <v>5</v>
       </c>
       <c r="AJ92" s="675">
         <f>AI92-AH92</f>
-        <v>-0.34703008201933017</v>
+        <v>-0.12993421372364278</v>
       </c>
       <c r="AK92" s="673">
-        <f t="shared" si="35"/>
-        <v>106.94060164038662</v>
+        <f t="shared" si="36"/>
+        <v>102.59868427447284</v>
       </c>
       <c r="AL92" s="629"/>
       <c r="AM92" s="630"/>
@@ -28031,19 +27751,19 @@
         <v>0.52872309862100797</v>
       </c>
       <c r="C93" s="653">
-        <f t="shared" ref="C93:AF93" si="37">IF(C$9=0,"",+C76/C$9)</f>
+        <f t="shared" ref="C93:AF93" si="38">IF(C$9=0,"",+C76/C$9)</f>
         <v>0.51527848315554736</v>
       </c>
       <c r="D93" s="653" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="E93" s="653" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="F93" s="653">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.54768424083162426</v>
       </c>
       <c r="G93" s="653">
@@ -28055,116 +27775,116 @@
         <v>0.54231007706162837</v>
       </c>
       <c r="I93" s="653">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.61785403828157237</v>
       </c>
       <c r="J93" s="653">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.58641615124288038</v>
       </c>
       <c r="K93" s="653" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="L93" s="653" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="M93" s="653">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1.0312138923327074</v>
       </c>
       <c r="N93" s="653">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.50211477813288585</v>
       </c>
       <c r="O93" s="653">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.55360550307427736</v>
       </c>
       <c r="P93" s="653">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.64322312148400562</v>
       </c>
       <c r="Q93" s="653">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.55736388411887094</v>
       </c>
       <c r="R93" s="653" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="S93" s="653" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="T93" s="653" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="U93" s="653">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.65509157886602665</v>
       </c>
-      <c r="V93" s="653" t="str">
-        <f t="shared" si="37"/>
-        <v/>
+      <c r="V93" s="653">
+        <f t="shared" si="38"/>
+        <v>0.54449941801719925</v>
       </c>
       <c r="W93" s="653" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="X93" s="653" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="Y93" s="653" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="Z93" s="653" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AA93" s="653" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AB93" s="653" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AC93" s="653" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AD93" s="653" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE93" s="653" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AF93" s="653" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AG93" s="628"/>
       <c r="AH93" s="670">
         <f>IF(AH$9=0,"0",+AH76/AH$9)</f>
-        <v>0.59247352502387451</v>
+        <v>0.5868500742346493</v>
       </c>
       <c r="AI93" s="674">
         <v>1.7</v>
       </c>
       <c r="AJ93" s="676">
         <f>AI93-AH93</f>
-        <v>1.1075264749761256</v>
+        <v>1.1131499257653505</v>
       </c>
       <c r="AK93" s="673">
-        <f t="shared" si="35"/>
-        <v>34.851383824933798</v>
+        <f t="shared" si="36"/>
+        <v>34.520592602038199</v>
       </c>
       <c r="AL93" s="635"/>
       <c r="AM93" s="636"/>
@@ -28206,11 +27926,11 @@
         <v/>
       </c>
       <c r="E94" s="653" t="str">
-        <f t="shared" ref="E94:AF94" si="38">IF(E$9=0,"",(E80+E83)/E$9)</f>
+        <f t="shared" ref="E94:AF94" si="39">IF(E$9=0,"",(E80+E83)/E$9)</f>
         <v/>
       </c>
       <c r="F94" s="653">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>18.973850083613577</v>
       </c>
       <c r="G94" s="653">
@@ -28222,11 +27942,11 @@
         <v>19.566073203617862</v>
       </c>
       <c r="I94" s="653">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>24.763716093882365</v>
       </c>
       <c r="J94" s="653">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>25.007455816184951</v>
       </c>
       <c r="K94" s="653" t="str">
@@ -28234,11 +27954,11 @@
         <v/>
       </c>
       <c r="L94" s="653" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="M94" s="653">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>42.634668420919461</v>
       </c>
       <c r="N94" s="653">
@@ -28250,35 +27970,35 @@
         <v>15.088890982904976</v>
       </c>
       <c r="P94" s="653">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>20.481418742288309</v>
       </c>
       <c r="Q94" s="653">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>36.947569862709415</v>
       </c>
       <c r="R94" s="653" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="S94" s="653" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="T94" s="653" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="U94" s="653">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>19.913573250212522</v>
       </c>
-      <c r="V94" s="653" t="str">
-        <f t="shared" si="38"/>
-        <v/>
+      <c r="V94" s="653">
+        <f t="shared" si="39"/>
+        <v>13.782703901280977</v>
       </c>
       <c r="W94" s="653" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="X94" s="653" t="str">
@@ -28286,15 +28006,15 @@
         <v/>
       </c>
       <c r="Y94" s="653" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="Z94" s="653" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AA94" s="653" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AB94" s="653" t="str">
@@ -28306,32 +28026,32 @@
         <v/>
       </c>
       <c r="AD94" s="653" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AE94" s="653" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AF94" s="653" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AG94" s="627"/>
       <c r="AH94" s="670">
         <f>IF(AH$9=0,"0",+(AH80+AH83)/AH$9)</f>
-        <v>28.83938128435075</v>
+        <v>27.074460797114739</v>
       </c>
       <c r="AI94" s="674">
         <v>22</v>
       </c>
       <c r="AJ94" s="675">
         <f>AI94-AH94</f>
-        <v>-6.8393812843507504</v>
+        <v>-5.0744607971147389</v>
       </c>
       <c r="AK94" s="673">
         <f>AH94/AI94*100</f>
-        <v>131.08809674704887</v>
+        <v>123.06573089597607</v>
       </c>
       <c r="AL94" s="629"/>
       <c r="AM94" s="630"/>
@@ -28391,12 +28111,12 @@
       <c r="AG95" s="637"/>
       <c r="AH95" s="670">
         <f>IF(AH$9=0,"0",+(AH78*10)/AH$9)</f>
-        <v>24.651288980061153</v>
+        <v>24.822527675905032</v>
       </c>
       <c r="AI95" s="674"/>
       <c r="AJ95" s="676"/>
       <c r="AK95" s="673" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL95" s="629"/>
@@ -28427,23 +28147,23 @@
         <v>187</v>
       </c>
       <c r="B96" s="653">
-        <f t="shared" ref="B96:I96" si="39">IF(B$9=0,"",B84/B$9)</f>
+        <f t="shared" ref="B96:I96" si="40">IF(B$9=0,"",B84/B$9)</f>
         <v>9.0248032455772513</v>
       </c>
       <c r="C96" s="653">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>7.8829496078102714</v>
       </c>
       <c r="D96" s="654" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="E96" s="653" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="F96" s="653">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>10.265174485914613</v>
       </c>
       <c r="G96" s="653">
@@ -28455,31 +28175,31 @@
         <v>6.767742379953793</v>
       </c>
       <c r="I96" s="654">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>8.2243963479119166</v>
       </c>
       <c r="J96" s="654">
-        <f t="shared" ref="J96:AE96" si="40">IF(J$9=0,"",J84/J$9)</f>
+        <f t="shared" ref="J96:AE96" si="41">IF(J$9=0,"",J84/J$9)</f>
         <v>9.4209099985735172</v>
       </c>
       <c r="K96" s="654" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="L96" s="654" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="M96" s="654">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>14.549755838372789</v>
       </c>
       <c r="N96" s="654">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>3.750698773322962</v>
       </c>
       <c r="O96" s="654">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>5.8821566271683796</v>
       </c>
       <c r="P96" s="654">
@@ -28487,15 +28207,15 @@
         <v>6.4454064454064453</v>
       </c>
       <c r="Q96" s="654">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>12.538978735765349</v>
       </c>
       <c r="R96" s="654" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="S96" s="654" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="T96" s="654" t="str">
@@ -28503,19 +28223,19 @@
         <v/>
       </c>
       <c r="U96" s="654">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>8.181989919026206</v>
       </c>
-      <c r="V96" s="654" t="str">
-        <f t="shared" si="40"/>
-        <v/>
+      <c r="V96" s="654">
+        <f t="shared" si="41"/>
+        <v>5.6217388233198511</v>
       </c>
       <c r="W96" s="654" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="X96" s="654" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="Y96" s="654" t="str">
@@ -28523,7 +28243,7 @@
         <v/>
       </c>
       <c r="Z96" s="654" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AA96" s="654" t="str">
@@ -28531,7 +28251,7 @@
         <v/>
       </c>
       <c r="AB96" s="654" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AC96" s="654" t="str">
@@ -28539,11 +28259,11 @@
         <v/>
       </c>
       <c r="AD96" s="654" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AE96" s="654" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AF96" s="654" t="str">
@@ -28553,18 +28273,18 @@
       <c r="AG96" s="627"/>
       <c r="AH96" s="660">
         <f>IF(AH$9=0,"0",+(AH84)/AH$9)</f>
-        <v>8.709436056338598</v>
+        <v>8.3475009516478131</v>
       </c>
       <c r="AI96" s="663">
         <v>7.2</v>
       </c>
       <c r="AJ96" s="677">
         <f>AI96-AH96</f>
-        <v>-1.5094360563385978</v>
+        <v>-1.147500951647813</v>
       </c>
       <c r="AK96" s="668">
-        <f t="shared" si="35"/>
-        <v>120.96438967136942</v>
+        <f t="shared" si="36"/>
+        <v>115.93751321733075</v>
       </c>
       <c r="AL96" s="629"/>
       <c r="AM96" s="630"/>
@@ -28759,127 +28479,127 @@
         <v>215</v>
       </c>
       <c r="B100" s="500" t="str">
-        <f t="shared" ref="B100:AF100" si="41">IF(B$99=0,"",+(B42*10)/B$99)</f>
+        <f t="shared" ref="B100:AF100" si="42">IF(B$99=0,"",+(B42*10)/B$99)</f>
         <v/>
       </c>
       <c r="C100" s="500" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="D100" s="500" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="E100" s="500" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="F100" s="500" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="G100" s="500" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="H100" s="500" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="I100" s="500" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J100" s="501" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="K100" s="501" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="L100" s="501" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="M100" s="501" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="N100" s="501" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="O100" s="501" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="P100" s="501" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="Q100" s="501" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="R100" s="501" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="S100" s="501" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="T100" s="501" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="U100" s="501" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="V100" s="501" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="W100" s="501" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="X100" s="501" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="Y100" s="501" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="Z100" s="501" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AA100" s="501" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AB100" s="501" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AC100" s="501" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AD100" s="501" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AE100" s="501" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AF100" s="501" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AG100" s="501"/>
@@ -29100,7 +28820,7 @@
       </c>
       <c r="V103" s="521">
         <f>IF('Entries October 2026'!L27-'Entries October 2026'!L26&lt;1,0,'Entries October 2026'!L27-'Entries October 2026'!L26)</f>
-        <v>0</v>
+        <v>408.61999999999534</v>
       </c>
       <c r="W103" s="521">
         <f>IF('Entries October 2026'!L28-'Entries October 2026'!L27&lt;1,0,'Entries October 2026'!L28-'Entries October 2026'!L27)</f>
@@ -29167,7 +28887,7 @@
         <v>203</v>
       </c>
       <c r="B105" s="651">
-        <f t="shared" ref="B105:AF105" si="42">IF(B103=0,"",B104/B103)</f>
+        <f t="shared" ref="B105:AF105" si="43">IF(B103=0,"",B104/B103)</f>
         <v>0</v>
       </c>
       <c r="C105" s="651">
@@ -29175,22 +28895,22 @@
         <v>0</v>
       </c>
       <c r="D105" s="651" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="E105" s="651" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="F105" s="651">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="G105" s="651" t="s">
         <v>55</v>
       </c>
       <c r="H105" s="651">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="I105" s="651" t="str">
@@ -29198,95 +28918,95 @@
         <v/>
       </c>
       <c r="J105" s="652">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="K105" s="652">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="L105" s="652" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="M105" s="652">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N105" s="652">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="O105" s="652">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P105" s="652">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="Q105" s="652">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="R105" s="652" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="S105" s="652" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="T105" s="652" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="U105" s="652">
         <f>IF(U103=0,"",U104/U103)</f>
         <v>0</v>
       </c>
-      <c r="V105" s="652" t="str">
-        <f t="shared" si="42"/>
-        <v/>
+      <c r="V105" s="652">
+        <f t="shared" si="43"/>
+        <v>0</v>
       </c>
       <c r="W105" s="652" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="X105" s="652" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="Y105" s="652" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="Z105" s="652" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AA105" s="652" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AB105" s="652" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AC105" s="652" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AD105" s="652" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>#REF!</v>
       </c>
       <c r="AE105" s="652" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>#REF!</v>
       </c>
       <c r="AF105" s="652" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AG105" s="652"/>
@@ -29563,7 +29283,7 @@
       </c>
       <c r="V116" s="650">
         <f>'Daily KPIs'!V80</f>
-        <v>0</v>
+        <v>7481</v>
       </c>
       <c r="W116" s="650">
         <f>'Daily KPIs'!W80</f>
@@ -29608,7 +29328,7 @@
       <c r="AG116" s="650"/>
       <c r="AH116" s="649">
         <f>'Daily KPIs'!AH80</f>
-        <v>115751</v>
+        <v>123232</v>
       </c>
     </row>
     <row r="117" spans="2:34" hidden="1" x14ac:dyDescent="0.35">
@@ -29698,7 +29418,7 @@
       </c>
       <c r="AH140" s="870">
         <f>AH83/(AH83+AH80)</f>
-        <v>0.1816247171945701</v>
+        <v>0.18072327604317634</v>
       </c>
       <c r="AM140" s="751"/>
     </row>
@@ -29835,45 +29555,45 @@
   </mergeCells>
   <phoneticPr fontId="32" type="noConversion"/>
   <conditionalFormatting sqref="B93:C93 AH93">
-    <cfRule type="cellIs" dxfId="75" priority="127" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="35" priority="127" operator="greaterThan">
       <formula>$AI$93</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B90:AF90">
-    <cfRule type="cellIs" dxfId="74" priority="36" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="34" priority="36" operator="greaterThan">
       <formula>10.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92:AF92">
-    <cfRule type="cellIs" dxfId="73" priority="26" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="33" priority="26" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="27" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="32" priority="27" operator="lessThanOrEqual">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:AF93">
-    <cfRule type="cellIs" dxfId="71" priority="34" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="34" operator="greaterThan">
       <formula>1.7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B94:AF94">
-    <cfRule type="cellIs" dxfId="70" priority="33" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="30" priority="33" operator="greaterThan">
       <formula>22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96:AF96">
-    <cfRule type="cellIs" dxfId="69" priority="32" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="29" priority="32" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:AG22">
-    <cfRule type="cellIs" dxfId="68" priority="101" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="28" priority="101" operator="greaterThan">
       <formula>400</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42:AG42">
-    <cfRule type="cellIs" dxfId="67" priority="47" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="27" priority="47" operator="greaterThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29888,129 +29608,129 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B94:AG94">
-    <cfRule type="cellIs" dxfId="66" priority="1174" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="1174" operator="greaterThan">
       <formula>$AI$94</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96:AG96">
-    <cfRule type="cellIs" dxfId="65" priority="1176" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="25" priority="1176" operator="greaterThan">
       <formula>$AI$96</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:AH15">
-    <cfRule type="cellIs" dxfId="64" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="greaterThan">
       <formula>3.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54:AH54">
-    <cfRule type="cellIs" dxfId="63" priority="123" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="23" priority="123" operator="greaterThan">
       <formula>3.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B56:AH56">
-    <cfRule type="cellIs" dxfId="62" priority="61" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="22" priority="61" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B57:AH57 B59:AH59 B61:AH61">
-    <cfRule type="cellIs" dxfId="61" priority="62" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="21" priority="62" operator="greaterThan">
       <formula>0.7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58:AH58 B62:AH62">
-    <cfRule type="cellIs" dxfId="60" priority="63" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="63" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B60:AH60">
-    <cfRule type="cellIs" dxfId="59" priority="22" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="19" priority="22" operator="greaterThan">
       <formula>2.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B65:AH65">
-    <cfRule type="cellIs" dxfId="58" priority="56" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="56" operator="greaterThan">
       <formula>0.3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68:AH68">
-    <cfRule type="cellIs" dxfId="57" priority="58" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="58" operator="greaterThan">
       <formula>9.6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69:AH69">
-    <cfRule type="cellIs" dxfId="56" priority="59" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="59" operator="greaterThan">
       <formula>2.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92:AH92">
-    <cfRule type="cellIs" dxfId="55" priority="48" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="48" operator="greaterThan">
       <formula>5.04</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:AH93">
-    <cfRule type="cellIs" dxfId="54" priority="44" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="44" operator="greaterThan">
       <formula>1.7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="43" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="43" operator="greaterThan">
       <formula>1.7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96:AH96">
-    <cfRule type="cellIs" dxfId="52" priority="37" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="37" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E96">
-    <cfRule type="cellIs" dxfId="51" priority="39" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="39" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I63:AH63">
-    <cfRule type="cellIs" dxfId="50" priority="68" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="68" operator="greaterThan">
       <formula>0.6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC54:AG54">
-    <cfRule type="cellIs" dxfId="49" priority="82" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="82" operator="greaterThan">
       <formula>$AI$54</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC55:AG59 AC61:AG61 AC63:AG63 B64:AG64">
-    <cfRule type="cellIs" dxfId="48" priority="1135" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="1135" operator="greaterThan">
       <formula>$AI59</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH94">
-    <cfRule type="cellIs" dxfId="47" priority="28" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="28" operator="lessThanOrEqual">
       <formula>22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH94:AH96 B90:AH90 AH91">
-    <cfRule type="cellIs" dxfId="46" priority="1168" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="1168" operator="greaterThan">
       <formula>$AI$90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH96">
-    <cfRule type="cellIs" dxfId="45" priority="29" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="29" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="30" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="30" operator="lessThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="40" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="40" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ8">
-    <cfRule type="cellIs" dxfId="42" priority="105" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="105" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="106" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="106" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK90:AK96">
-    <cfRule type="cellIs" dxfId="40" priority="50" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="50" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
@@ -31589,11 +31309,11 @@
       </c>
       <c r="C27" s="55">
         <f t="shared" si="1"/>
-        <v>-256065</v>
+        <v>440</v>
       </c>
       <c r="D27" s="55">
         <f t="shared" si="2"/>
-        <v>1112682</v>
+        <v>300</v>
       </c>
       <c r="E27" s="56">
         <f>'Entries October 2026'!W26</f>
@@ -31605,7 +31325,7 @@
       </c>
       <c r="G27" s="57">
         <f t="shared" si="7"/>
-        <v>-1368747</v>
+        <v>140</v>
       </c>
       <c r="H27" s="57">
         <f>'Entries October 2026'!AA26</f>
@@ -31613,7 +31333,7 @@
       </c>
       <c r="I27" s="58">
         <f t="shared" si="3"/>
-        <v>-97122</v>
+        <v>0</v>
       </c>
       <c r="J27" s="57">
         <f>'Entries October 2026'!T26</f>
@@ -31625,7 +31345,7 @@
       </c>
       <c r="L27" s="58">
         <f t="shared" si="6"/>
-        <v>-97122</v>
+        <v>0</v>
       </c>
       <c r="M27" s="57">
         <f>'Entries October 2026'!R26</f>
@@ -31633,11 +31353,11 @@
       </c>
       <c r="N27" s="57">
         <f>'Entries October 2026'!AC27-'Entries October 2026'!AC26</f>
-        <v>-7025</v>
+        <v>31</v>
       </c>
       <c r="O27" s="57">
         <f t="shared" si="5"/>
-        <v>-512130</v>
+        <v>880</v>
       </c>
       <c r="P27" s="62"/>
       <c r="Q27" s="45"/>
@@ -31652,15 +31372,15 @@
       </c>
       <c r="B28" s="55">
         <f>'Entries October 2026'!O27</f>
-        <v>0</v>
+        <v>256505</v>
       </c>
       <c r="C28" s="55">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-256505</v>
       </c>
       <c r="D28" s="55">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1112382</v>
       </c>
       <c r="E28" s="56">
         <f>'Entries October 2026'!W27</f>
@@ -31668,19 +31388,19 @@
       </c>
       <c r="F28" s="57">
         <f>'Entries October 2026'!V27</f>
-        <v>0</v>
+        <v>1368887</v>
       </c>
       <c r="G28" s="57">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-1368887</v>
       </c>
       <c r="H28" s="57">
         <f>'Entries October 2026'!AA27</f>
-        <v>0</v>
+        <v>97122</v>
       </c>
       <c r="I28" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-97122</v>
       </c>
       <c r="J28" s="57">
         <f>'Entries October 2026'!T27</f>
@@ -31692,7 +31412,7 @@
       </c>
       <c r="L28" s="58">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-97122</v>
       </c>
       <c r="M28" s="57">
         <f>'Entries October 2026'!R27</f>
@@ -31700,11 +31420,11 @@
       </c>
       <c r="N28" s="57">
         <f>'Entries October 2026'!AC28-'Entries October 2026'!AC27</f>
-        <v>0</v>
+        <v>-7056</v>
       </c>
       <c r="O28" s="57">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-513010</v>
       </c>
       <c r="P28" s="62"/>
       <c r="Q28" s="45"/>
@@ -33986,7 +33706,7 @@
       </c>
       <c r="K29" s="722">
         <f>'CO2'!E26</f>
-        <v>2224</v>
+        <v>2300</v>
       </c>
       <c r="L29" s="723">
         <f>+'PROD.FIG. '!F24</f>
@@ -34028,9 +33748,9 @@
       <c r="A30" s="719">
         <v>21</v>
       </c>
-      <c r="B30" s="719" t="str">
+      <c r="B30" s="719">
         <f>IF('Entries October 2026'!I27&lt;'Entries October 2026'!I26,"0",(IF('Entries October 2026'!I27&gt;='Entries October 2026'!I26,'Entries October 2026'!I27-'Entries October 2026'!I26,(999999-'Entries October 2026'!I26)+'Entries October 2026'!I27+1)))</f>
-        <v>0</v>
+        <v>7481</v>
       </c>
       <c r="C30" s="719" t="str">
         <f>IF('Entries October 2026'!J27&lt;='Entries October 2026'!J26,"0",IF('Entries October 2026'!J27&gt;='Entries October 2026'!J26,'Entries October 2026'!J27-'Entries October 2026'!J26,(999999-'Entries October 2026'!J26)+'Entries October 2026'!J27+1))</f>
@@ -34038,24 +33758,26 @@
       </c>
       <c r="D30" s="720">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E30" s="873"/>
-      <c r="F30" s="721" t="str">
+        <v>7481</v>
+      </c>
+      <c r="E30" s="873">
+        <v>1494.6</v>
+      </c>
+      <c r="F30" s="721">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G30" s="737" t="str">
+        <v>0.16651811578056061</v>
+      </c>
+      <c r="G30" s="737">
         <f>IF('Entries October 2026'!K27&lt;'Entries October 2026'!K26,"0",IF('Entries October 2026'!K27&gt;='Entries October 2026'!K26,'Entries October 2026'!K27-'Entries October 2026'!K26,(999999-'Entries October 2026'!K26)+'Entries October 2026'!K27+1))</f>
         <v>0</v>
       </c>
       <c r="H30" s="720">
         <f>D30+G30+E30</f>
-        <v>0</v>
+        <v>8975.6</v>
       </c>
       <c r="I30" s="737">
         <f>'Water '!Z27*10</f>
-        <v>0</v>
+        <v>5740</v>
       </c>
       <c r="J30" s="720" t="str">
         <f>IF('Entries October 2026'!B27-'Entries October 2026'!B26&lt;1,"0",'Entries October 2026'!B27-'Entries October 2026'!B26)</f>
@@ -34063,7 +33785,7 @@
       </c>
       <c r="K30" s="722">
         <f>'CO2'!E27</f>
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="L30" s="723">
         <f>+'PROD.FIG. '!F25</f>
@@ -34082,15 +33804,15 @@
         <v>0</v>
       </c>
       <c r="P30" s="724">
-        <v>0</v>
+        <v>651.22199999999998</v>
       </c>
       <c r="Q30" s="393">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>13.782703901280977</v>
       </c>
       <c r="R30" s="393">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.8141985375186955</v>
       </c>
       <c r="S30" s="393">
         <f t="shared" si="5"/>
@@ -34108,7 +33830,7 @@
       <c r="A31" s="719">
         <v>22</v>
       </c>
-      <c r="B31" s="719">
+      <c r="B31" s="719" t="str">
         <f>IF('Entries October 2026'!I28&lt;'Entries October 2026'!I27,"0",(IF('Entries October 2026'!I28&gt;='Entries October 2026'!I27,'Entries October 2026'!I28-'Entries October 2026'!I27,(999999-'Entries October 2026'!I27)+'Entries October 2026'!I28+1)))</f>
         <v>0</v>
       </c>
@@ -34125,7 +33847,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G31" s="737">
+      <c r="G31" s="737" t="str">
         <f>IF('Entries October 2026'!K28&lt;'Entries October 2026'!K27,"0",IF('Entries October 2026'!K28&gt;='Entries October 2026'!K27,'Entries October 2026'!K28-'Entries October 2026'!K27,(999999-'Entries October 2026'!K27)+'Entries October 2026'!K28+1))</f>
         <v>0</v>
       </c>
@@ -34949,15 +34671,15 @@
       <c r="C43" s="19"/>
       <c r="D43" s="20">
         <f>SUM(D10:D40)</f>
-        <v>115751</v>
+        <v>123232</v>
       </c>
       <c r="E43" s="741">
         <f>SUM(E10:E40)</f>
-        <v>25688.999999999996</v>
+        <v>27183.599999999995</v>
       </c>
       <c r="F43" s="754">
         <f>IF((E43+D43)=0,"0",E43/(D43+E43))</f>
-        <v>0.1816247171945701</v>
+        <v>0.18072327604317634</v>
       </c>
       <c r="G43" s="20">
         <f t="shared" ref="G43:P43" si="7">SUM(G10:G40)</f>
@@ -34965,11 +34687,11 @@
       </c>
       <c r="H43" s="20">
         <f t="shared" si="7"/>
-        <v>141439.99999999997</v>
+        <v>150415.59999999998</v>
       </c>
       <c r="I43" s="20">
         <f t="shared" si="7"/>
-        <v>56070</v>
+        <v>61810</v>
       </c>
       <c r="J43" s="20">
         <f t="shared" si="7"/>
@@ -34977,7 +34699,7 @@
       </c>
       <c r="K43" s="20">
         <f t="shared" si="7"/>
-        <v>26224</v>
+        <v>28500</v>
       </c>
       <c r="L43" s="20">
         <f t="shared" si="7"/>
@@ -34997,7 +34719,7 @@
       </c>
       <c r="P43" s="403">
         <f t="shared" si="7"/>
-        <v>4904.4048000000003</v>
+        <v>5555.6268</v>
       </c>
       <c r="Q43" s="408" t="s">
         <v>13</v>
@@ -35025,7 +34747,7 @@
       </c>
       <c r="E44" s="728">
         <f>D43+E43</f>
-        <v>141440</v>
+        <v>150415.6</v>
       </c>
       <c r="F44" s="708"/>
       <c r="G44" s="7"/>
@@ -35040,19 +34762,19 @@
       <c r="P44" s="401"/>
       <c r="Q44" s="397">
         <f>IF(P43=0,0,H43/P43)</f>
-        <v>28.839381284350747</v>
+        <v>27.074460797114735</v>
       </c>
       <c r="R44" s="398">
         <f>IF(Q44=0,0,I43/P43)</f>
-        <v>11.432579953432882</v>
+        <v>11.12565732457047</v>
       </c>
       <c r="S44" s="398">
         <f>IF(R44=0,0,J43/P43)</f>
-        <v>0.19574240690735806</v>
+        <v>0.17279778404121746</v>
       </c>
       <c r="T44" s="399">
         <f>IF(S44=0,0,K43/P43)</f>
-        <v>5.3470300820193302</v>
+        <v>5.1299342137236428</v>
       </c>
     </row>
     <row r="45" spans="1:32" ht="15" x14ac:dyDescent="0.2">
@@ -35129,41 +34851,41 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="Q10:Q44">
-    <cfRule type="cellIs" dxfId="102" priority="7" operator="between">
+    <cfRule type="cellIs" dxfId="62" priority="7" operator="between">
       <formula>0</formula>
       <formula>22</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="61" priority="8" operator="greaterThan">
       <formula>22</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="60" priority="9" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:R44">
-    <cfRule type="cellIs" dxfId="99" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="59" priority="1" operator="between">
       <formula>0</formula>
       <formula>10.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="2" operator="greaterThan">
       <formula>10.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S10:S44">
-    <cfRule type="cellIs" dxfId="97" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="57" priority="3" operator="between">
       <formula>0</formula>
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="56" priority="4" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T10:T44">
-    <cfRule type="cellIs" dxfId="95" priority="5" operator="between">
+    <cfRule type="cellIs" dxfId="55" priority="5" operator="between">
       <formula>0</formula>
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="54" priority="6" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36821,13 +36543,13 @@
         <f>IF('Entries October 2026'!B27-'Entries October 2026'!B26&lt;1,"0",'Entries October 2026'!B27-'Entries October 2026'!B26)</f>
         <v>0</v>
       </c>
-      <c r="C27" s="739" t="str">
+      <c r="C27" s="739">
         <f>IF('Entries October 2026'!F27-'Entries October 2026'!F26&lt;1,"0",'Entries October 2026'!F27-'Entries October 2026'!F26)</f>
-        <v>0</v>
-      </c>
-      <c r="D27" s="839" t="str">
+        <v>21.199999999998909</v>
+      </c>
+      <c r="D27" s="839">
         <f>IF('Entries October 2026'!C27-'Entries October 2026'!C26&lt;1,"0",'Entries October 2026'!C27-'Entries October 2026'!C26)</f>
-        <v>0</v>
+        <v>3661</v>
       </c>
       <c r="E27" s="843" t="str">
         <f t="shared" si="0"/>
@@ -36839,7 +36561,7 @@
       </c>
       <c r="G27" s="837"/>
       <c r="H27" s="739"/>
-      <c r="I27" s="740" t="str">
+      <c r="I27" s="740">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -36851,20 +36573,20 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L27" s="831" t="str">
-        <v>0</v>
-      </c>
-      <c r="M27" s="829" t="str">
+      <c r="L27" s="831">
+        <v>651.22199999999998</v>
+      </c>
+      <c r="M27" s="829">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N27" s="829" t="str">
+      <c r="N27" s="829">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.6217388233198511</v>
       </c>
       <c r="O27" s="830">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-3661</v>
       </c>
       <c r="P27" s="333"/>
     </row>
@@ -37423,11 +37145,11 @@
       </c>
       <c r="C38" s="388">
         <f>SUM(C7:C37)</f>
-        <v>290.90000000000146</v>
+        <v>312.10000000000036</v>
       </c>
       <c r="D38" s="840">
         <f t="shared" si="7"/>
-        <v>42714.600000000093</v>
+        <v>46375.600000000093</v>
       </c>
       <c r="E38" s="845"/>
       <c r="F38" s="846">
@@ -37444,7 +37166,7 @@
       </c>
       <c r="I38" s="797">
         <f>B38/C38</f>
-        <v>3.3001031282227404</v>
+        <v>3.0759371996155043</v>
       </c>
       <c r="J38" s="355"/>
       <c r="K38" s="356">
@@ -37453,15 +37175,15 @@
       </c>
       <c r="L38" s="828">
         <f>SUM(L7:L37)</f>
-        <v>4904.4048000000003</v>
+        <v>5555.6268</v>
       </c>
       <c r="M38" s="834">
         <f>IF(L38=0,"0",(K38/L38))</f>
-        <v>0.19574240690735806</v>
+        <v>0.17279778404121746</v>
       </c>
       <c r="N38" s="834">
         <f>IF(L38=0,"0",(D38/L38))</f>
-        <v>8.709436056338598</v>
+        <v>8.3475009516478131</v>
       </c>
       <c r="O38" s="835"/>
     </row>
@@ -37475,7 +37197,7 @@
       </c>
       <c r="C39" s="802">
         <f>AVERAGE(C7:C37)</f>
-        <v>15.31052631578955</v>
+        <v>15.605000000000018</v>
       </c>
       <c r="D39" s="30"/>
       <c r="E39" s="30"/>
@@ -38095,27 +37817,27 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="C7:C37">
-    <cfRule type="cellIs" dxfId="93" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="53" priority="13" operator="greaterThan">
       <formula>24</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7:N37">
-    <cfRule type="cellIs" dxfId="92" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="52" priority="9" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="11" operator="between">
+    <cfRule type="cellIs" dxfId="51" priority="11" operator="between">
       <formula>0</formula>
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7:N38">
-    <cfRule type="cellIs" dxfId="90" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="1" operator="lessThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="49" priority="2" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="48" priority="4" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38192,87 +37914,87 @@
     </row>
     <row r="3" spans="1:31" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="972" t="s">
+      <c r="B4" s="980" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="970" t="s">
+      <c r="C4" s="972" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="968" t="s">
+      <c r="D4" s="977" t="s">
         <v>106</v>
       </c>
-      <c r="E4" s="970" t="s">
+      <c r="E4" s="972" t="s">
         <v>107</v>
       </c>
-      <c r="F4" s="968" t="s">
+      <c r="F4" s="977" t="s">
         <v>239</v>
       </c>
-      <c r="G4" s="968" t="s">
+      <c r="G4" s="977" t="s">
         <v>108</v>
       </c>
-      <c r="H4" s="968" t="s">
+      <c r="H4" s="977" t="s">
         <v>161</v>
       </c>
-      <c r="I4" s="970" t="s">
+      <c r="I4" s="972" t="s">
         <v>207</v>
       </c>
-      <c r="J4" s="970" t="s">
+      <c r="J4" s="972" t="s">
         <v>109</v>
       </c>
-      <c r="K4" s="970" t="s">
+      <c r="K4" s="972" t="s">
         <v>174</v>
       </c>
-      <c r="L4" s="970" t="s">
+      <c r="L4" s="972" t="s">
         <v>173</v>
       </c>
-      <c r="M4" s="970" t="s">
+      <c r="M4" s="972" t="s">
         <v>103</v>
       </c>
       <c r="N4" s="48"/>
       <c r="O4" s="48"/>
       <c r="P4" s="48"/>
       <c r="Q4" s="48"/>
-      <c r="R4" s="968" t="s">
+      <c r="R4" s="977" t="s">
         <v>110</v>
       </c>
-      <c r="S4" s="968" t="s">
+      <c r="S4" s="977" t="s">
         <v>240</v>
       </c>
       <c r="T4" s="48"/>
-      <c r="U4" s="970" t="s">
+      <c r="U4" s="972" t="s">
         <v>153</v>
       </c>
       <c r="V4" s="48"/>
       <c r="W4" s="48"/>
-      <c r="X4" s="970" t="s">
+      <c r="X4" s="972" t="s">
         <v>175</v>
       </c>
-      <c r="Y4" s="970" t="s">
+      <c r="Y4" s="972" t="s">
         <v>176</v>
       </c>
-      <c r="Z4" s="977" t="s">
+      <c r="Z4" s="970" t="s">
         <v>247</v>
       </c>
-      <c r="AA4" s="979" t="s">
+      <c r="AA4" s="974" t="s">
         <v>243</v>
       </c>
-      <c r="AB4" s="975" t="s">
+      <c r="AB4" s="968" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:31" s="300" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="973"/>
-      <c r="C5" s="971"/>
-      <c r="D5" s="969"/>
-      <c r="E5" s="974"/>
-      <c r="F5" s="969"/>
-      <c r="G5" s="969"/>
-      <c r="H5" s="969"/>
-      <c r="I5" s="974"/>
-      <c r="J5" s="974"/>
-      <c r="K5" s="974"/>
-      <c r="L5" s="974"/>
-      <c r="M5" s="974"/>
+      <c r="B5" s="981"/>
+      <c r="C5" s="979"/>
+      <c r="D5" s="978"/>
+      <c r="E5" s="973"/>
+      <c r="F5" s="978"/>
+      <c r="G5" s="978"/>
+      <c r="H5" s="978"/>
+      <c r="I5" s="973"/>
+      <c r="J5" s="973"/>
+      <c r="K5" s="973"/>
+      <c r="L5" s="973"/>
+      <c r="M5" s="973"/>
       <c r="N5" s="50" t="s">
         <v>111</v>
       </c>
@@ -38285,23 +38007,23 @@
       <c r="Q5" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="R5" s="969"/>
-      <c r="S5" s="969"/>
+      <c r="R5" s="978"/>
+      <c r="S5" s="978"/>
       <c r="T5" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="U5" s="981"/>
+      <c r="U5" s="976"/>
       <c r="V5" s="80" t="s">
         <v>156</v>
       </c>
       <c r="W5" s="80" t="s">
         <v>157</v>
       </c>
-      <c r="X5" s="974"/>
-      <c r="Y5" s="974"/>
-      <c r="Z5" s="978"/>
-      <c r="AA5" s="980"/>
-      <c r="AB5" s="976"/>
+      <c r="X5" s="973"/>
+      <c r="Y5" s="973"/>
+      <c r="Z5" s="971"/>
+      <c r="AA5" s="975"/>
+      <c r="AB5" s="969"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="21" t="s">
@@ -40515,33 +40237,33 @@
         <f>IF('Entries October 2026'!W27-'Entries October 2026'!W26&lt;1,"0",'Entries October 2026'!W27-'Entries October 2026'!W26)</f>
         <v>0</v>
       </c>
-      <c r="D27" s="693" t="str">
+      <c r="D27" s="693">
         <f>IF('Entries October 2026'!O27-'Entries October 2026'!O26&lt;1,"0",'Entries October 2026'!O27-'Entries October 2026'!O26)</f>
-        <v>0</v>
-      </c>
-      <c r="E27" s="693" t="str">
+        <v>440</v>
+      </c>
+      <c r="E27" s="693">
         <f>IF('Entries October 2026'!P27-'Entries October 2026'!P26&lt;1,"0",'Entries October 2026'!P27-'Entries October 2026'!P26)</f>
-        <v>0</v>
-      </c>
-      <c r="F27" s="693" t="str">
+        <v>134</v>
+      </c>
+      <c r="F27" s="693">
         <f>IF('Entries October 2026'!V27-'Entries October 2026'!V26&lt;1,"0",'Entries October 2026'!V27-'Entries October 2026'!V26)</f>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="G27" s="693">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>434</v>
       </c>
       <c r="H27" s="693">
         <f>IF('Entries October 2026'!Q27-'Entries October 2026'!Q26&lt;1,0,'Entries October 2026'!Q27-'Entries October 2026'!Q26)</f>
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="I27" s="693">
         <f>IF('Entries October 2026'!AG27-'Entries October 2026'!AG26&lt;1,0,'Entries October 2026'!AG27-'Entries October 2026'!AG26)</f>
         <v>0</v>
       </c>
-      <c r="J27" s="693" t="str">
+      <c r="J27" s="693">
         <f>IF('Entries October 2026'!S27-'Entries October 2026'!S26&lt;1,"0",'Entries October 2026'!S27-'Entries October 2026'!S26)</f>
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="K27" s="693" t="str">
         <f>IF('Entries October 2026'!R27-'Entries October 2026'!R26&lt;1,"0",'Entries October 2026'!R27-'Entries October 2026'!R26)</f>
@@ -40555,21 +40277,21 @@
         <f>IF('Entries October 2026'!U27-'Entries October 2026'!U26&lt;1,"0",'Entries October 2026'!U27-'Entries October 2026'!U26)</f>
         <v>0</v>
       </c>
-      <c r="N27" s="693" t="str">
+      <c r="N27" s="693">
         <f>IF('Entries October 2026'!X27-'Entries October 2026'!X26&lt;1,"0",'Entries October 2026'!X27-'Entries October 2026'!X26)</f>
-        <v>0</v>
-      </c>
-      <c r="O27" s="693" t="str">
+        <v>19</v>
+      </c>
+      <c r="O27" s="693">
         <f>IF('Entries October 2026'!Y27-'Entries October 2026'!Y26&lt;1,"0",'Entries October 2026'!Y27-'Entries October 2026'!Y26)</f>
-        <v>0</v>
-      </c>
-      <c r="P27" s="693" t="str">
+        <v>158</v>
+      </c>
+      <c r="P27" s="693">
         <f>IF('Entries October 2026'!AC27-'Entries October 2026'!AC26&lt;1,"0",'Entries October 2026'!AC27-'Entries October 2026'!AC26)</f>
-        <v>0</v>
-      </c>
-      <c r="Q27" s="693" t="str">
+        <v>31</v>
+      </c>
+      <c r="Q27" s="693">
         <f>IF('Entries October 2026'!Z27-'Entries October 2026'!Z26&lt;1,"0",'Entries October 2026'!Z27-'Entries October 2026'!Z26)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R27" s="693" t="str">
         <f>IF(('Entries October 2026'!AA27-'Entries October 2026'!AA26)+('Entries October 2026'!AB27-'Entries October 2026'!AB26)&lt;1,"0",('Entries October 2026'!AA27-'Entries October 2026'!AA26)+('Entries October 2026'!AB27-'Entries October 2026'!AB26))</f>
@@ -40577,15 +40299,15 @@
       </c>
       <c r="S27" s="692">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4340</v>
       </c>
       <c r="T27" s="692">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U27" s="693" t="str">
+        <v>177</v>
+      </c>
+      <c r="U27" s="693">
         <f>IF('Entries October 2026'!AC27-'Entries October 2026'!AC26&lt;1,"0",'Entries October 2026'!AC27-'Entries October 2026'!AC26)</f>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="V27" s="693" t="str">
         <f>IF('Entries October 2026'!AD27-'Entries October 2026'!AD26&lt;1,"0",'Entries October 2026'!AD27-'Entries October 2026'!AD26)</f>
@@ -40605,14 +40327,14 @@
       </c>
       <c r="Z27" s="329">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AA27" s="330" t="str">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="331" t="str">
+        <v>574</v>
+      </c>
+      <c r="AA27" s="330">
+        <v>651.22199999999998</v>
+      </c>
+      <c r="AB27" s="331">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8.8141985375186955</v>
       </c>
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.2">
@@ -41703,28 +41425,28 @@
       </c>
       <c r="D38" s="303">
         <f>SUM(D7:D37)</f>
-        <v>3071</v>
+        <v>3511</v>
       </c>
       <c r="E38" s="303">
         <f>SUM(E7:E37)</f>
-        <v>2536</v>
+        <v>2670</v>
       </c>
       <c r="F38" s="303">
         <f>SUM(F7:F37)</f>
-        <v>2711</v>
+        <v>2851</v>
       </c>
       <c r="G38" s="304">
         <f>SUM(G7:G37)</f>
-        <v>2896</v>
+        <v>3330</v>
       </c>
       <c r="H38" s="303">
         <f t="shared" si="5"/>
-        <v>3096</v>
+        <v>3388</v>
       </c>
       <c r="I38" s="303"/>
       <c r="J38" s="303">
         <f t="shared" si="5"/>
-        <v>2428</v>
+        <v>2638</v>
       </c>
       <c r="K38" s="303"/>
       <c r="L38" s="303">
@@ -41737,19 +41459,19 @@
       </c>
       <c r="N38" s="303">
         <f t="shared" si="5"/>
-        <v>524</v>
+        <v>543</v>
       </c>
       <c r="O38" s="303">
         <f t="shared" si="5"/>
-        <v>1340</v>
+        <v>1498</v>
       </c>
       <c r="P38" s="303">
         <f>SUM(P7:P37)</f>
-        <v>275</v>
+        <v>306</v>
       </c>
       <c r="Q38" s="303">
         <f>SUM(Q7:Q37)</f>
-        <v>362</v>
+        <v>392</v>
       </c>
       <c r="R38" s="303">
         <f>SUM(R7:R34)</f>
@@ -41757,15 +41479,15 @@
       </c>
       <c r="S38" s="304">
         <f>SUM(S7:S37)</f>
-        <v>28960</v>
+        <v>33300</v>
       </c>
       <c r="T38" s="304">
         <f>SUM(T7:T37)</f>
-        <v>1917</v>
+        <v>2094</v>
       </c>
       <c r="U38" s="303">
         <f>SUM(U7:U37)</f>
-        <v>275</v>
+        <v>306</v>
       </c>
       <c r="V38" s="303">
         <f>SUM(V7:V37)</f>
@@ -41776,22 +41498,22 @@
       <c r="Y38" s="303"/>
       <c r="Z38" s="332">
         <f>SUM(Z7:Z37)</f>
-        <v>5607</v>
+        <v>6181</v>
       </c>
       <c r="AA38" s="332">
         <f>SUM(AA7:AA37)</f>
-        <v>4904.4048000000003</v>
+        <v>5555.6268</v>
       </c>
       <c r="AB38" s="331">
         <f>IF(AA38=0,"0",(Z38*10/AA38))</f>
-        <v>11.432579953432882</v>
+        <v>11.12565732457047</v>
       </c>
       <c r="AC38" s="321">
         <v>10.199999999999999</v>
       </c>
       <c r="AD38" s="340">
         <f>AB38/AC38*100</f>
-        <v>112.08411719051846</v>
+        <v>109.07507180951441</v>
       </c>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.2">
@@ -41830,7 +41552,7 @@
       <c r="C40" s="15"/>
       <c r="D40" s="15">
         <f>D38*220</f>
-        <v>675620</v>
+        <v>772420</v>
       </c>
       <c r="E40" s="15"/>
       <c r="F40" s="15"/>
@@ -41922,7 +41644,7 @@
       <c r="C43" s="17"/>
       <c r="D43" s="17">
         <f>+D41*D40</f>
-        <v>10681.5522</v>
+        <v>12211.960200000001</v>
       </c>
       <c r="E43" s="17"/>
       <c r="F43" s="36"/>
@@ -41975,7 +41697,7 @@
     <row r="45" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D45" s="17">
         <f>SUM(D43:D44)</f>
-        <v>10960.522199999999</v>
+        <v>12490.930200000001</v>
       </c>
       <c r="E45" s="17"/>
       <c r="F45" s="36"/>
@@ -41997,7 +41719,7 @@
       </c>
       <c r="D47" s="23">
         <f>+D45*2/3</f>
-        <v>7307.0147999999999</v>
+        <v>8327.2867999999999</v>
       </c>
       <c r="E47" s="324"/>
       <c r="F47" s="36"/>
@@ -42020,7 +41742,7 @@
       <c r="C49" s="24"/>
       <c r="D49" s="28">
         <f>SUM(D47,D45)</f>
-        <v>18267.537</v>
+        <v>20818.217000000001</v>
       </c>
       <c r="E49" s="325"/>
       <c r="F49" s="36"/>
@@ -42385,6 +42107,16 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:AA1"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="R4:R5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="E4:E5"/>
     <mergeCell ref="AB4:AB5"/>
     <mergeCell ref="Z4:Z5"/>
     <mergeCell ref="L4:L5"/>
@@ -42396,23 +42128,13 @@
     <mergeCell ref="Y4:Y5"/>
     <mergeCell ref="S4:S5"/>
     <mergeCell ref="M4:M5"/>
-    <mergeCell ref="A1:AA1"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="R4:R5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="E4:E5"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="AB6:AB38">
-    <cfRule type="cellIs" dxfId="87" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="1" operator="lessThan">
       <formula>10.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="46" priority="2" operator="greaterThan">
       <formula>10.2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43118,27 +42840,27 @@
       </c>
       <c r="B27" s="742">
         <f>'Utility Analysis October 2026'!D30</f>
-        <v>0</v>
-      </c>
-      <c r="C27" s="743" t="str">
+        <v>7481</v>
+      </c>
+      <c r="C27" s="743">
         <f>'Utility Analysis October 2026'!G30</f>
         <v>0</v>
       </c>
       <c r="D27" s="744">
         <f>'Utility Analysis October 2026'!E30</f>
-        <v>0</v>
+        <v>1494.6</v>
       </c>
       <c r="E27" s="745">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F27" s="746" t="str">
+        <v>8975.6</v>
+      </c>
+      <c r="F27" s="746">
         <f>'PROD.FIG. '!H25</f>
-        <v>0</v>
-      </c>
-      <c r="G27" s="336" t="str">
+        <v>651.22199999999998</v>
+      </c>
+      <c r="G27" s="336">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>13.782703901280977</v>
       </c>
       <c r="J27" s="30"/>
     </row>
@@ -43150,7 +42872,7 @@
         <f>'Utility Analysis October 2026'!D31</f>
         <v>0</v>
       </c>
-      <c r="C28" s="743">
+      <c r="C28" s="743" t="str">
         <f>'Utility Analysis October 2026'!G31</f>
         <v>0</v>
       </c>
@@ -43445,7 +43167,7 @@
       </c>
       <c r="B38" s="308">
         <f>SUM(B7:B37)</f>
-        <v>115751</v>
+        <v>123232</v>
       </c>
       <c r="C38" s="308">
         <f>SUM(C7:C37)</f>
@@ -43453,26 +43175,26 @@
       </c>
       <c r="D38" s="308">
         <f>SUM(D7:D37)</f>
-        <v>25688.999999999996</v>
+        <v>27183.599999999995</v>
       </c>
       <c r="E38" s="337">
         <f>SUM(E7:E37)</f>
-        <v>141439.99999999997</v>
+        <v>150415.59999999998</v>
       </c>
       <c r="F38" s="358">
         <f>SUM(F7:F37)</f>
-        <v>4904.4048000000003</v>
+        <v>5555.6268</v>
       </c>
       <c r="G38" s="338">
         <f>IF(F38=0,"0",(E38/F38))</f>
-        <v>28.839381284350747</v>
+        <v>27.074460797114735</v>
       </c>
       <c r="H38" s="335">
         <v>22</v>
       </c>
       <c r="I38" s="340">
         <f>G38/H38*100</f>
-        <v>131.08809674704884</v>
+        <v>123.06573089597607</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
@@ -43513,12 +43235,12 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="cellIs" dxfId="85" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="1" operator="lessThan">
       <formula>22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7:G38">
-    <cfRule type="cellIs" dxfId="84" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="44" priority="2" operator="greaterThan">
       <formula>21</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43972,8 +43694,8 @@
       <c r="E25" s="686"/>
       <c r="F25" s="686"/>
       <c r="G25" s="686"/>
-      <c r="H25" s="689" t="str">
-        <v>0</v>
+      <c r="H25" s="689">
+        <v>651.22199999999998</v>
       </c>
       <c r="I25" s="298"/>
       <c r="J25" s="299"/>
@@ -44171,7 +43893,7 @@
       </c>
       <c r="H36" s="736">
         <f>SUM(H5:H35)</f>
-        <v>4904.4048000000003</v>
+        <v>5555.6268</v>
       </c>
       <c r="I36" s="298"/>
       <c r="J36" s="299"/>
@@ -44287,11 +44009,11 @@
       <c r="D3" s="85"/>
       <c r="E3" s="85"/>
       <c r="F3" s="1"/>
-      <c r="I3" s="1004" t="s">
+      <c r="I3" s="1012" t="s">
         <v>267</v>
       </c>
-      <c r="J3" s="1005"/>
-      <c r="K3" s="1006"/>
+      <c r="J3" s="1013"/>
+      <c r="K3" s="1014"/>
     </row>
     <row r="4" spans="1:24" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
@@ -44304,21 +44026,21 @@
         <v>250</v>
       </c>
       <c r="H4" s="347"/>
-      <c r="I4" s="1007" t="s">
+      <c r="I4" s="1015" t="s">
         <v>262</v>
       </c>
-      <c r="J4" s="1008"/>
-      <c r="K4" s="1009"/>
+      <c r="J4" s="1016"/>
+      <c r="K4" s="1017"/>
       <c r="M4" s="417"/>
       <c r="N4" s="417"/>
       <c r="O4" s="418"/>
       <c r="P4" s="418"/>
-      <c r="Q4" s="1019" t="s">
+      <c r="Q4" s="1027" t="s">
         <v>283</v>
       </c>
-      <c r="R4" s="1019"/>
-      <c r="S4" s="1019"/>
-      <c r="T4" s="1019"/>
+      <c r="R4" s="1027"/>
+      <c r="S4" s="1027"/>
+      <c r="T4" s="1027"/>
       <c r="U4" s="191"/>
       <c r="V4" s="417"/>
       <c r="W4" s="191"/>
@@ -44334,16 +44056,16 @@
       <c r="C5" s="950" t="s">
         <v>282</v>
       </c>
-      <c r="D5" s="1026" t="s">
+      <c r="D5" s="1006" t="s">
         <v>279</v>
       </c>
-      <c r="E5" s="1026" t="s">
+      <c r="E5" s="1006" t="s">
         <v>280</v>
       </c>
-      <c r="F5" s="1024" t="s">
+      <c r="F5" s="1004" t="s">
         <v>243</v>
       </c>
-      <c r="G5" s="1021" t="s">
+      <c r="G5" s="1001" t="s">
         <v>249</v>
       </c>
       <c r="I5" s="419" t="s">
@@ -44355,43 +44077,43 @@
       <c r="K5" s="421" t="s">
         <v>265</v>
       </c>
-      <c r="M5" s="1010" t="s">
+      <c r="M5" s="1018" t="s">
         <v>266</v>
       </c>
-      <c r="N5" s="1011"/>
-      <c r="O5" s="1012"/>
+      <c r="N5" s="1019"/>
+      <c r="O5" s="1020"/>
       <c r="P5" s="422"/>
-      <c r="Q5" s="1013" t="s">
+      <c r="Q5" s="1021" t="s">
         <v>7</v>
       </c>
-      <c r="R5" s="1015" t="s">
+      <c r="R5" s="1023" t="s">
         <v>267</v>
       </c>
-      <c r="S5" s="1016"/>
+      <c r="S5" s="1024"/>
       <c r="T5" s="452" t="s">
         <v>268</v>
       </c>
       <c r="U5" s="423" t="s">
         <v>269</v>
       </c>
-      <c r="V5" s="1017" t="s">
+      <c r="V5" s="1025" t="s">
         <v>277</v>
       </c>
-      <c r="W5" s="1000" t="s">
+      <c r="W5" s="1008" t="s">
         <v>270</v>
       </c>
-      <c r="X5" s="1002" t="s">
+      <c r="X5" s="1010" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1020"/>
-      <c r="B6" s="1023"/>
-      <c r="C6" s="1023"/>
-      <c r="D6" s="1027"/>
-      <c r="E6" s="1027"/>
-      <c r="F6" s="1025"/>
-      <c r="G6" s="1022"/>
+      <c r="A6" s="1000"/>
+      <c r="B6" s="1003"/>
+      <c r="C6" s="1003"/>
+      <c r="D6" s="1007"/>
+      <c r="E6" s="1007"/>
+      <c r="F6" s="1005"/>
+      <c r="G6" s="1002"/>
       <c r="I6" s="424">
         <v>10</v>
       </c>
@@ -44410,7 +44132,7 @@
         <v>273</v>
       </c>
       <c r="P6" s="418"/>
-      <c r="Q6" s="1014"/>
+      <c r="Q6" s="1022"/>
       <c r="R6" s="448" t="s">
         <v>274</v>
       </c>
@@ -44423,9 +44145,9 @@
       <c r="U6" s="429" t="s">
         <v>275</v>
       </c>
-      <c r="V6" s="1018"/>
-      <c r="W6" s="1001"/>
-      <c r="X6" s="1003"/>
+      <c r="V6" s="1026"/>
+      <c r="W6" s="1009"/>
+      <c r="X6" s="1011"/>
     </row>
     <row r="7" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="715">
@@ -45844,14 +45566,14 @@
         <v>2224.3099999999395</v>
       </c>
       <c r="E26" s="768">
-        <v>2224</v>
+        <v>2300</v>
       </c>
       <c r="F26" s="769">
         <v>465.82800000000003</v>
       </c>
       <c r="G26" s="336">
         <f t="shared" si="1"/>
-        <v>4.7742943747477611</v>
+        <v>4.9374447220862629</v>
       </c>
       <c r="I26" s="430">
         <v>210</v>
@@ -45904,27 +45626,27 @@
       <c r="A27" s="715">
         <v>21</v>
       </c>
-      <c r="B27" s="716" t="str">
+      <c r="B27" s="716">
         <f>IF('Entries October 2026'!N27-'Entries October 2026'!N26&lt;1,"0",'Entries October 2026'!N27-'Entries October 2026'!N26)</f>
-        <v>0</v>
-      </c>
-      <c r="C27" s="716" t="str">
+        <v>354.58999999999651</v>
+      </c>
+      <c r="C27" s="716">
         <f>IF('Entries October 2026'!L27-'Entries October 2026'!L26&lt;1,"0",'Entries October 2026'!L27-'Entries October 2026'!L26)</f>
-        <v>0</v>
-      </c>
-      <c r="D27" s="716" t="str">
+        <v>408.61999999999534</v>
+      </c>
+      <c r="D27" s="716">
         <f>IF('Entries October 2026'!M27-'Entries October 2026'!M26&lt;1,"0",'Entries October 2026'!M27-'Entries October 2026'!M26)</f>
-        <v>0</v>
+        <v>2463.6900000000605</v>
       </c>
       <c r="E27" s="716">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="F27" s="717">
-        <v>0</v>
-      </c>
-      <c r="G27" s="336" t="str">
+        <v>651.22199999999998</v>
+      </c>
+      <c r="G27" s="336">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3.3782642478294651</v>
       </c>
       <c r="I27" s="430">
         <v>220</v>
@@ -46712,27 +46434,27 @@
       </c>
       <c r="B38" s="713">
         <f>SUM(B7:B37)</f>
-        <v>2905.7300000000105</v>
+        <v>3260.320000000007</v>
       </c>
       <c r="C38" s="713">
         <f>SUM(C7:C37)</f>
-        <v>7484.320000000007</v>
+        <v>7892.9400000000023</v>
       </c>
       <c r="D38" s="713">
         <f>SUM(D7:D37)</f>
-        <v>22480.039999999921</v>
+        <v>24943.729999999981</v>
       </c>
       <c r="E38" s="713">
         <f>SUM(E7:E37)</f>
-        <v>26224</v>
+        <v>28500</v>
       </c>
       <c r="F38" s="714">
         <f>SUM(F7:F37)</f>
-        <v>4904.4048000000003</v>
+        <v>5555.6268</v>
       </c>
       <c r="G38" s="345">
         <f>IF(F38=0,"0",(E38/F38))</f>
-        <v>5.3470300820193302</v>
+        <v>5.1299342137236428</v>
       </c>
       <c r="H38" s="348">
         <v>5</v>
@@ -46894,13 +46616,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="C5:C6"/>
     <mergeCell ref="W5:W6"/>
     <mergeCell ref="X5:X6"/>
     <mergeCell ref="I3:K3"/>
@@ -46910,13 +46625,20 @@
     <mergeCell ref="R5:S5"/>
     <mergeCell ref="V5:V6"/>
     <mergeCell ref="Q4:T4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="C5:C6"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="G7:G38">
-    <cfRule type="cellIs" dxfId="83" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="43" priority="1" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="42" priority="3" operator="greaterThan">
       <formula>21</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47405,7 +47127,7 @@
       </c>
       <c r="V8" s="99">
         <f>'Daily KPIs'!V8</f>
-        <v>0</v>
+        <v>9867</v>
       </c>
       <c r="W8" s="101">
         <f>'Daily KPIs'!W8</f>
@@ -47443,14 +47165,14 @@
       </c>
       <c r="AG8" s="213">
         <f>SUM($B8:AF8)</f>
-        <v>68740</v>
+        <v>78607</v>
       </c>
       <c r="AH8" s="293">
         <v>96325</v>
       </c>
       <c r="AI8" s="294">
         <f>AG8-AH8</f>
-        <v>-27585</v>
+        <v>-17718</v>
       </c>
       <c r="AJ8" s="266"/>
       <c r="AK8" s="266"/>
@@ -47541,7 +47263,7 @@
       </c>
       <c r="V9" s="99">
         <f>'Daily KPIs'!V9</f>
-        <v>0</v>
+        <v>651.22199999999998</v>
       </c>
       <c r="W9" s="99">
         <f>'Daily KPIs'!W9</f>
@@ -47579,7 +47301,7 @@
       </c>
       <c r="AG9" s="215">
         <f>SUM($B9:AF9)</f>
-        <v>4904.4048000000003</v>
+        <v>5555.6268</v>
       </c>
       <c r="AH9" s="214"/>
       <c r="AI9" s="265"/>
@@ -47668,13 +47390,13 @@
         <f>'Daily KPIs'!U10</f>
         <v>SM/CB</v>
       </c>
-      <c r="V10" s="163">
+      <c r="V10" s="163" t="str">
         <f>'Daily KPIs'!V10</f>
-        <v>0</v>
-      </c>
-      <c r="W10" s="163">
+        <v>CB/ST</v>
+      </c>
+      <c r="W10" s="163" t="str">
         <f>'Daily KPIs'!W10</f>
-        <v>0</v>
+        <v>GN</v>
       </c>
       <c r="X10" s="163">
         <f>'Daily KPIs'!X10</f>
@@ -48115,9 +47837,9 @@
         <f>+'Water '!$D26</f>
         <v>266</v>
       </c>
-      <c r="V16" s="110" t="str">
+      <c r="V16" s="110">
         <f>+'Water '!$D27</f>
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="W16" s="110" t="str">
         <f>+'Water '!$D28</f>
@@ -48161,7 +47883,7 @@
       </c>
       <c r="AG16" s="220">
         <f>SUM($B16:AF16)</f>
-        <v>3071</v>
+        <v>3511</v>
       </c>
       <c r="AH16" s="221"/>
     </row>
@@ -48249,9 +47971,9 @@
         <f>+'Water '!$E26</f>
         <v>130</v>
       </c>
-      <c r="V17" s="114" t="str">
+      <c r="V17" s="114">
         <f>+'Water '!$E27</f>
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="W17" s="114" t="str">
         <f>+'Water '!$E28</f>
@@ -48295,7 +48017,7 @@
       </c>
       <c r="AG17" s="222">
         <f>SUM($B17:AF17)</f>
-        <v>2536</v>
+        <v>2670</v>
       </c>
       <c r="AH17" s="223"/>
       <c r="AI17" s="268"/>
@@ -48386,7 +48108,7 @@
       </c>
       <c r="V18" s="175">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>574</v>
       </c>
       <c r="W18" s="175">
         <f t="shared" si="0"/>
@@ -48430,7 +48152,7 @@
       </c>
       <c r="AG18" s="224">
         <f>SUM($B18:AF18)</f>
-        <v>5607</v>
+        <v>6181</v>
       </c>
       <c r="AH18" s="224"/>
       <c r="AI18" s="269"/>
@@ -48600,7 +48322,7 @@
       </c>
       <c r="V21" s="119">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>102.2</v>
       </c>
       <c r="W21" s="119">
         <f>0.73*(W96+W15)</f>
@@ -48644,16 +48366,16 @@
       </c>
       <c r="AG21" s="220">
         <f>SUM($B21:AF21)</f>
-        <v>1887.7800000000002</v>
+        <v>1989.9800000000002</v>
       </c>
       <c r="AH21" s="225">
         <f>AG24+AG37+AG28</f>
-        <v>5896</v>
+        <v>6428</v>
       </c>
       <c r="AI21" s="271"/>
       <c r="AJ21" s="272">
         <f>(AH21*10)/AG9</f>
-        <v>12.02184615756024</v>
+        <v>11.570251623093185</v>
       </c>
     </row>
     <row r="22" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -48917,7 +48639,7 @@
       </c>
       <c r="V24" s="112">
         <f>'Water '!H27</f>
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="W24" s="112">
         <f>'Water '!H28</f>
@@ -48961,7 +48683,7 @@
       </c>
       <c r="AG24" s="222">
         <f>SUM($B24:AF24)</f>
-        <v>3096</v>
+        <v>3388</v>
       </c>
       <c r="AH24" s="222"/>
       <c r="AI24" s="222"/>
@@ -49052,7 +48774,7 @@
       </c>
       <c r="V25" s="118">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="W25" s="118">
         <f t="shared" si="2"/>
@@ -49096,7 +48818,7 @@
       </c>
       <c r="AG25" s="224">
         <f>SUM($B25:AF25)</f>
-        <v>3096</v>
+        <v>3388</v>
       </c>
       <c r="AH25" s="224"/>
       <c r="AI25" s="269"/>
@@ -49185,9 +48907,9 @@
         <f t="shared" si="3"/>
         <v>1.674437775316211</v>
       </c>
-      <c r="V26" s="125" t="str">
+      <c r="V26" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>4.4838780016645634</v>
       </c>
       <c r="W26" s="125" t="str">
         <f t="shared" si="3"/>
@@ -49359,9 +49081,9 @@
         <f>+'Water '!$J26</f>
         <v>140</v>
       </c>
-      <c r="V28" s="127" t="str">
+      <c r="V28" s="127">
         <f>+'Water '!$J27</f>
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="W28" s="127" t="str">
         <f>+'Water '!$J28</f>
@@ -49405,7 +49127,7 @@
       </c>
       <c r="AG28" s="220">
         <f>SUM($B28:AF28)</f>
-        <v>2428</v>
+        <v>2638</v>
       </c>
       <c r="AH28" s="220"/>
       <c r="AI28" s="271"/>
@@ -49938,9 +49660,9 @@
         <f>+'Water '!$N26</f>
         <v>41</v>
       </c>
-      <c r="V33" s="131" t="str">
+      <c r="V33" s="131">
         <f>+'Water '!$N27</f>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="W33" s="131" t="str">
         <f>+'Water '!$N28</f>
@@ -49984,7 +49706,7 @@
       </c>
       <c r="AG33" s="227">
         <f>SUM($B33:AF33)</f>
-        <v>638</v>
+        <v>657</v>
       </c>
       <c r="AH33" s="227"/>
       <c r="AI33" s="227"/>
@@ -50077,9 +49799,9 @@
         <f>+'Water '!$O26</f>
         <v>135</v>
       </c>
-      <c r="V34" s="134" t="str">
+      <c r="V34" s="134">
         <f>+'Water '!$O27</f>
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="W34" s="134" t="str">
         <f>+'Water '!$O28</f>
@@ -50123,7 +49845,7 @@
       </c>
       <c r="AG34" s="228">
         <f>SUM($B34:AF34)</f>
-        <v>1500</v>
+        <v>1658</v>
       </c>
       <c r="AH34" s="228"/>
       <c r="AI34" s="228"/>
@@ -50214,7 +49936,7 @@
       </c>
       <c r="V35" s="95">
         <f>IF('Entries October 2026'!AC27-'Entries October 2026'!AC26&lt;1,0,'Entries October 2026'!AC27-'Entries October 2026'!AC26)</f>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="W35" s="95">
         <f>IF('Entries October 2026'!$AC28-'Entries October 2026'!$AC27&lt;1,0,'Entries October 2026'!$AC28-'Entries October 2026'!$AC27)</f>
@@ -50258,7 +49980,7 @@
       </c>
       <c r="AG35" s="220">
         <f>SUM($B35:AF35)</f>
-        <v>275</v>
+        <v>306</v>
       </c>
       <c r="AH35" s="220"/>
       <c r="AI35" s="271"/>
@@ -50482,9 +50204,9 @@
         <f>+'Water '!$Q26</f>
         <v>47</v>
       </c>
-      <c r="V37" s="131" t="str">
+      <c r="V37" s="131">
         <f>+'Water '!$Q27</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="W37" s="131" t="str">
         <f>+'Water '!$Q28</f>
@@ -50528,7 +50250,7 @@
       </c>
       <c r="AG37" s="227">
         <f>SUM($B37:AF37)</f>
-        <v>372</v>
+        <v>402</v>
       </c>
       <c r="AH37" s="227"/>
       <c r="AI37" s="227"/>
@@ -50972,7 +50694,7 @@
       </c>
       <c r="V42" s="138">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="W42" s="138">
         <f t="shared" si="4"/>
@@ -51016,7 +50738,7 @@
       </c>
       <c r="AG42" s="230">
         <f>SUM($B42:AF42)</f>
-        <v>5513</v>
+        <v>5961</v>
       </c>
       <c r="AH42" s="230"/>
       <c r="AI42" s="276"/>
@@ -51427,9 +51149,9 @@
         <f>'Daily KPIs'!U76</f>
         <v>305.16000000000349</v>
       </c>
-      <c r="V49" s="187" t="str">
+      <c r="V49" s="187">
         <f>'Daily KPIs'!V76</f>
-        <v>0</v>
+        <v>354.58999999999651</v>
       </c>
       <c r="W49" s="187" t="str">
         <f>'Daily KPIs'!W76</f>
@@ -51473,7 +51195,7 @@
       </c>
       <c r="AG49" s="235">
         <f>SUM($B49:AF49)</f>
-        <v>2905.7300000000105</v>
+        <v>3260.320000000007</v>
       </c>
       <c r="AH49" s="236"/>
       <c r="AI49" s="280"/>
@@ -52164,9 +51886,9 @@
         <f t="shared" si="5"/>
         <v>8.5009917823746104</v>
       </c>
-      <c r="V59" s="144" t="str">
+      <c r="V59" s="144">
         <f t="shared" si="5"/>
-        <v/>
+        <v>8.8141985375186955</v>
       </c>
       <c r="W59" s="144" t="str">
         <f t="shared" si="5"/>
@@ -52210,7 +51932,7 @@
       </c>
       <c r="AG59" s="238">
         <f>IF(AG$9=0,"",+(AG18*10)/AG$9)</f>
-        <v>11.432579953432882</v>
+        <v>11.12565732457047</v>
       </c>
       <c r="AH59" s="239">
         <f>'Daily KPIs'!AI90</f>
@@ -52218,7 +51940,7 @@
       </c>
       <c r="AI59" s="282">
         <f>+AH59-AG59</f>
-        <v>-1.2325799534328823</v>
+        <v>-0.92565732457047112</v>
       </c>
       <c r="AJ59" s="270"/>
       <c r="AK59" s="270"/>
@@ -52329,9 +52051,9 @@
         <f t="shared" si="8"/>
         <v>3.0054011351829431</v>
       </c>
-      <c r="V62" s="145" t="str">
+      <c r="V62" s="145">
         <f t="shared" si="8"/>
-        <v/>
+        <v>3.2247067820190352</v>
       </c>
       <c r="W62" s="145" t="str">
         <f t="shared" si="8"/>
@@ -52375,14 +52097,14 @@
       </c>
       <c r="AG62" s="241">
         <f>IF(+(AG28*10)/AG$9&lt;1,0,+(AG28*10)/AG$9)</f>
-        <v>4.9506517080319306</v>
+        <v>4.7483391072992882</v>
       </c>
       <c r="AH62" s="241">
         <v>2.5</v>
       </c>
       <c r="AI62" s="242">
         <f t="shared" ref="AI62:AI78" si="11">AH62-AG62</f>
-        <v>-2.4506517080319306</v>
+        <v>-2.2483391072992882</v>
       </c>
     </row>
     <row r="63" spans="1:37" ht="18.75" x14ac:dyDescent="0.3">
@@ -52515,14 +52237,14 @@
       </c>
       <c r="AG63" s="243">
         <f>IF(+(AG28*10)/AG$93&lt;1,0,+(AG28*10)/AG$93)</f>
-        <v>9.0059347181008906</v>
+        <v>9.7848664688427291</v>
       </c>
       <c r="AH63" s="243">
         <v>2.5</v>
       </c>
       <c r="AI63" s="244">
         <f t="shared" si="11"/>
-        <v>-6.5059347181008906</v>
+        <v>-7.2848664688427291</v>
       </c>
     </row>
     <row r="64" spans="1:37" s="90" customFormat="1" ht="18" x14ac:dyDescent="0.25">
@@ -52609,9 +52331,9 @@
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="V64" s="147" t="str">
+      <c r="V64" s="147">
         <f t="shared" si="14"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W64" s="147" t="str">
         <f t="shared" si="14"/>
@@ -52797,9 +52519,9 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="V66" s="145" t="str">
+      <c r="V66" s="145">
         <f t="shared" si="16"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W66" s="145" t="s">
         <v>208</v>
@@ -52909,9 +52631,9 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="V67" s="150" t="str">
+      <c r="V67" s="150">
         <f t="shared" si="18"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W67" s="150" t="str">
         <f t="shared" si="18"/>
@@ -52955,14 +52677,14 @@
       </c>
       <c r="AG67" s="249">
         <f>+(AG32*10)/AG$9</f>
-        <v>0.17331358944922326</v>
+        <v>0.15299803795316128</v>
       </c>
       <c r="AH67" s="249">
         <v>1</v>
       </c>
       <c r="AI67" s="250">
         <f>AH67-AG67</f>
-        <v>0.82668641055077674</v>
+        <v>0.84700196204683875</v>
       </c>
       <c r="AJ67" s="284"/>
       <c r="AK67" s="284"/>
@@ -53051,9 +52773,9 @@
         <f t="shared" si="20"/>
         <v>0.88015318958929045</v>
       </c>
-      <c r="V68" s="145" t="str">
+      <c r="V68" s="145">
         <f t="shared" si="20"/>
-        <v/>
+        <v>0.29175918503981746</v>
       </c>
       <c r="W68" s="145" t="str">
         <f t="shared" si="20"/>
@@ -53097,14 +52819,14 @@
       </c>
       <c r="AG68" s="241">
         <f>+(AG33*10)/AG$9</f>
-        <v>1.300871412571817</v>
+        <v>1.182584834532082</v>
       </c>
       <c r="AH68" s="241">
         <v>0.7</v>
       </c>
       <c r="AI68" s="242">
         <f t="shared" si="11"/>
-        <v>-0.60087141257181709</v>
+        <v>-0.48258483453208201</v>
       </c>
     </row>
     <row r="69" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -53191,9 +52913,9 @@
         <f t="shared" si="22"/>
         <v>2.8980653803549807</v>
       </c>
-      <c r="V69" s="145" t="str">
+      <c r="V69" s="145">
         <f t="shared" si="22"/>
-        <v/>
+        <v>2.4262079598047976</v>
       </c>
       <c r="W69" s="145" t="str">
         <f t="shared" si="22"/>
@@ -53237,14 +52959,14 @@
       </c>
       <c r="AG69" s="241">
         <f>+(AG34*10)/AG$9</f>
-        <v>3.0584751079274692</v>
+        <v>2.9843617285451933</v>
       </c>
       <c r="AH69" s="241">
         <v>2.6</v>
       </c>
       <c r="AI69" s="242">
         <f t="shared" si="11"/>
-        <v>-0.45847510792746915</v>
+        <v>-0.38436172854519324</v>
       </c>
     </row>
     <row r="70" spans="1:37" ht="18.75" x14ac:dyDescent="0.3">
@@ -53468,9 +53190,9 @@
         <f t="shared" si="26"/>
         <v>0.62254737800218107</v>
       </c>
-      <c r="V71" s="145" t="str">
+      <c r="V71" s="145">
         <f t="shared" si="26"/>
-        <v/>
+        <v>0.47602814401233373</v>
       </c>
       <c r="W71" s="145" t="str">
         <f t="shared" si="26"/>
@@ -53514,14 +53236,14 @@
       </c>
       <c r="AG71" s="241">
         <f>+(AG35*10)/AG$9</f>
-        <v>0.56072043645336944</v>
+        <v>0.55079293663138063</v>
       </c>
       <c r="AH71" s="241">
         <v>0.7</v>
       </c>
       <c r="AI71" s="242">
         <f>AH71-AG71</f>
-        <v>0.13927956354663051</v>
+        <v>0.14920706336861933</v>
       </c>
     </row>
     <row r="72" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -53608,9 +53330,9 @@
         <f t="shared" si="29"/>
         <v>0.12880290579355469</v>
       </c>
-      <c r="V72" s="145" t="str">
+      <c r="V72" s="145">
         <f t="shared" si="29"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W72" s="145" t="str">
         <f t="shared" si="29"/>
@@ -53654,14 +53376,14 @@
       </c>
       <c r="AG72" s="241">
         <f>+(AG36*10)/AG$9</f>
-        <v>0.10806612048010392</v>
+        <v>9.5398776606088809E-2</v>
       </c>
       <c r="AH72" s="241">
         <v>0.1</v>
       </c>
       <c r="AI72" s="242">
         <f>AH72-AG72</f>
-        <v>-8.066120480103911E-3</v>
+        <v>4.6012233939111968E-3</v>
       </c>
     </row>
     <row r="73" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -53748,9 +53470,9 @@
         <f t="shared" si="31"/>
         <v>1.0089560953828451</v>
       </c>
-      <c r="V73" s="145" t="str">
+      <c r="V73" s="145">
         <f t="shared" si="31"/>
-        <v/>
+        <v>0.46067239743129074</v>
       </c>
       <c r="W73" s="145" t="str">
         <f t="shared" si="31"/>
@@ -53794,14 +53516,14 @@
       </c>
       <c r="AG73" s="241">
         <f>+(AG37*10)/AG$9</f>
-        <v>0.75850182676601241</v>
+        <v>0.72359072067259811</v>
       </c>
       <c r="AH73" s="241">
         <v>0.6</v>
       </c>
       <c r="AI73" s="242">
         <f t="shared" si="11"/>
-        <v>-0.15850182676601243</v>
+        <v>-0.12359072067259813</v>
       </c>
     </row>
     <row r="74" spans="1:37" s="91" customFormat="1" ht="18" x14ac:dyDescent="0.25">
@@ -53888,9 +53610,9 @@
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="V74" s="150" t="str">
+      <c r="V74" s="150">
         <f t="shared" si="33"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W74" s="150" t="str">
         <f t="shared" si="33"/>
@@ -54030,9 +53752,9 @@
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="V75" s="145" t="str">
+      <c r="V75" s="145">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W75" s="145" t="str">
         <f t="shared" si="35"/>
@@ -54264,7 +53986,7 @@
       </c>
       <c r="V78" s="152">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>6.8793744683072742</v>
       </c>
       <c r="W78" s="152">
         <f>SUM(W62:W77)</f>
@@ -54308,7 +54030,7 @@
       </c>
       <c r="AG78" s="253">
         <f>SUM(AG62:AG77)</f>
-        <v>19.916534919780815</v>
+        <v>20.22293261108252</v>
       </c>
       <c r="AH78" s="253">
         <f t="shared" si="37"/>
@@ -54316,7 +54038,7 @@
       </c>
       <c r="AI78" s="253">
         <f t="shared" si="11"/>
-        <v>-4.3165349197808176</v>
+        <v>-4.622932611082522</v>
       </c>
       <c r="AJ78" s="210"/>
       <c r="AK78" s="210"/>
@@ -54407,7 +54129,7 @@
       </c>
       <c r="V79" s="154">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>2.9022361038171312</v>
       </c>
       <c r="W79" s="154">
         <f t="shared" si="38"/>
@@ -54451,7 +54173,7 @@
       </c>
       <c r="AG79" s="254">
         <f t="shared" si="38"/>
-        <v>3.7272616648609427</v>
+        <v>3.6305534417826624</v>
       </c>
       <c r="AH79" s="254">
         <f t="shared" si="38"/>
@@ -54459,7 +54181,7 @@
       </c>
       <c r="AI79" s="254">
         <f t="shared" si="38"/>
-        <v>2.2727383351390573</v>
+        <v>2.3694465582173372</v>
       </c>
       <c r="AJ79" s="285"/>
       <c r="AK79" s="285"/>
@@ -54548,9 +54270,9 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="V80" s="155" t="str">
+      <c r="V80" s="155">
         <f t="shared" si="39"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W80" s="155" t="str">
         <f t="shared" si="39"/>
@@ -54691,9 +54413,9 @@
         <f t="shared" si="41"/>
         <v>0.65509157886602665</v>
       </c>
-      <c r="V81" s="157" t="str">
+      <c r="V81" s="157">
         <f>IF(V$9=0,"",+V49/V$9)</f>
-        <v/>
+        <v>0.54449941801719925</v>
       </c>
       <c r="W81" s="157" t="str">
         <f t="shared" si="41"/>
@@ -54737,7 +54459,7 @@
       </c>
       <c r="AG81" s="287">
         <f>IF(AG$9=0,"",+AG49/AG$9)</f>
-        <v>0.59247352502387451</v>
+        <v>0.5868500742346493</v>
       </c>
       <c r="AH81" s="287">
         <f>'Daily KPIs'!AI93</f>
@@ -54745,7 +54467,7 @@
       </c>
       <c r="AI81" s="286">
         <f>AH81-AG81</f>
-        <v>1.1075264749761256</v>
+        <v>1.1131499257653505</v>
       </c>
       <c r="AJ81" s="210"/>
       <c r="AK81" s="210"/>
@@ -54834,9 +54556,9 @@
         <f t="shared" si="43"/>
         <v>5.265892131859828</v>
       </c>
-      <c r="V82" s="144" t="str">
+      <c r="V82" s="144">
         <f t="shared" si="43"/>
-        <v/>
+        <v>3.7667646363298539</v>
       </c>
       <c r="W82" s="144" t="str">
         <f t="shared" si="43"/>
@@ -54880,7 +54602,7 @@
       </c>
       <c r="AG82" s="238">
         <f>+(AG52)/AG$9</f>
-        <v>26.383221874344464</v>
+        <v>23.29062132107218</v>
       </c>
       <c r="AH82" s="239">
         <f>'Daily KPIs'!AI94</f>
@@ -54888,7 +54610,7 @@
       </c>
       <c r="AI82" s="286">
         <f>AH82-AG82</f>
-        <v>-4.3832218743444642</v>
+        <v>-1.2906213210721802</v>
       </c>
       <c r="AJ82" s="270"/>
       <c r="AK82" s="270"/>
@@ -55022,9 +54744,9 @@
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="V84" s="144" t="str">
+      <c r="V84" s="144">
         <f t="shared" si="46"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W84" s="144" t="str">
         <f t="shared" si="46"/>
@@ -55068,7 +54790,7 @@
       </c>
       <c r="AG84" s="255">
         <f>+(AG54)/AG$9</f>
-        <v>0.19574240690735806</v>
+        <v>0.17279778404121746</v>
       </c>
       <c r="AH84" s="256">
         <f>'Daily KPIs'!AI96</f>
@@ -55076,7 +54798,7 @@
       </c>
       <c r="AI84" s="286">
         <f>AH84-AG84</f>
-        <v>7.0042575930926425</v>
+        <v>7.0272022159587824</v>
       </c>
       <c r="AJ84" s="270"/>
       <c r="AK84" s="270"/>
@@ -55343,7 +55065,7 @@
       </c>
       <c r="V87" s="119">
         <f>IF('Entries October 2026'!L27-'Entries October 2026'!L26&lt;1,0,'Entries October 2026'!L27-'Entries October 2026'!L26)</f>
-        <v>0</v>
+        <v>408.61999999999534</v>
       </c>
       <c r="W87" s="119">
         <f>IF('Entries October 2026'!L28-'Entries October 2026'!L27&lt;1,0,'Entries October 2026'!L28-'Entries October 2026'!L27)</f>
@@ -55387,7 +55109,7 @@
       </c>
       <c r="AG87" s="220">
         <f>SUM($B87:AF87)</f>
-        <v>554022.31000000017</v>
+        <v>554430.93000000017</v>
       </c>
       <c r="AH87" s="220"/>
       <c r="AI87" s="271"/>
@@ -55518,9 +55240,9 @@
         <f>IF(U87=0,"",U88/U87)</f>
         <v>0</v>
       </c>
-      <c r="V89" s="160" t="str">
+      <c r="V89" s="160">
         <f t="shared" si="49"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W89" s="160" t="str">
         <f t="shared" si="49"/>
@@ -55999,13 +55721,13 @@
         <f>'Daily KPIs'!U13</f>
         <v>CB</v>
       </c>
-      <c r="V94" s="166">
+      <c r="V94" s="166" t="str">
         <f>'Daily KPIs'!V13</f>
-        <v>0</v>
-      </c>
-      <c r="W94" s="166">
+        <v>CB/VM</v>
+      </c>
+      <c r="W94" s="166" t="str">
         <f>'Daily KPIs'!W13</f>
-        <v>0</v>
+        <v>VM/CB</v>
       </c>
       <c r="X94" s="166">
         <f>'Daily KPIs'!X13</f>
@@ -56129,11 +55851,11 @@
       </c>
       <c r="U95" s="174">
         <f>'Daily KPIs'!U14</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V95" s="174">
         <f>'Daily KPIs'!V14</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W95" s="174">
         <f>'Daily KPIs'!W14</f>
@@ -56266,9 +55988,9 @@
         <f>+'Water '!$F26</f>
         <v>134</v>
       </c>
-      <c r="V96" s="110" t="str">
+      <c r="V96" s="110">
         <f>+'Water '!$F27</f>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="W96" s="110" t="str">
         <f>+'Water '!$F28</f>
@@ -56312,7 +56034,7 @@
       </c>
       <c r="AG96" s="220">
         <f>SUM($B96:AF96)</f>
-        <v>2586</v>
+        <v>2726</v>
       </c>
       <c r="AH96" s="220"/>
       <c r="AI96" s="271"/>
@@ -56741,30 +56463,30 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B82:AF82">
-    <cfRule type="cellIs" dxfId="81" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="41" priority="3" operator="greaterThan">
       <formula>26</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B84:AF84">
-    <cfRule type="cellIs" dxfId="80" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="40" priority="4" operator="greaterThan">
       <formula>6.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D64:D65 D67 T69:AI70 D71 D73:D77">
-    <cfRule type="cellIs" dxfId="79" priority="5" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="39" priority="5" stopIfTrue="1" operator="greaterThan">
       <formula>3.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D69:S69 B70:S70">
-    <cfRule type="cellIs" dxfId="78" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>3.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI8">
-    <cfRule type="cellIs" dxfId="77" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="37" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/data/raw/October_26_Utilities_Tracking.xlsx
+++ b/data/raw/October_26_Utilities_Tracking.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UTILITIES\Tracking\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB12C24-720D-4027-A906-12CC0BB1AE25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{671EA45D-C2FA-4FB6-9626-7CD8F00332BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="579" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
     <author>Alexander Dominguez-Ramon</author>
   </authors>
   <commentList>
-    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{4DD8895D-E903-46C4-A720-FE319DEF9132}">
+    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{B21E4652-3C64-4886-B747-45EC64E26654}">
       <text>
         <r>
           <rPr>
@@ -80,7 +80,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{4876613E-B24F-466B-8D3E-D87291D21C52}">
+    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{70D71AB5-31BF-4066-BE4E-F85202A05576}">
       <text>
         <r>
           <rPr>
@@ -615,6 +615,91 @@
         </r>
       </text>
     </comment>
+    <comment ref="X74" authorId="2" shapeId="0" xr:uid="{C3D8D712-E652-4B86-9B1F-E3CE87269744}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tank A 3000 kgs 
+Tank B 0 kgs calculated
+Tank C 22400 Kgs
+mobile approx 0Kgs
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Y74" authorId="2" shapeId="0" xr:uid="{F7509078-3BDC-4C3C-AC44-65C038734AFC}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tank A 1000 kgs 
+Tank B 0 kgs calculated
+Tank C 22400 Kgs
+mobile approx 0Kgs
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Z74" authorId="2" shapeId="0" xr:uid="{41656B7B-610D-407E-91D2-0F20C0A45BBB}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tank A 1000 kgs 
+Tank B 0 kgs calculated
+Tank C 22400 Kgs
+mobile approx 0Kgs
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AA74" authorId="2" shapeId="0" xr:uid="{73C85986-F487-4094-854C-3094E6F808BF}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tank A 1000 kgs 
+Tank B 0 kgs calculated
+Tank C 22400 Kgs
+mobile approx 0Kgs
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AB74" authorId="2" shapeId="0" xr:uid="{ECB9A05E-F0CF-4D08-8A6D-99E9CC06FEC3}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tank A 1000 kgs 
+Tank B 0 kgs calculated
+Tank C 22400 Kgs
+mobile approx 0Kgs
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -667,7 +752,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="324">
   <si>
     <t>UTILITY ANALYSIS</t>
   </si>
@@ -3436,6 +3521,21 @@
       <t>CB</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t>GN/VM/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FF92D050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>VMG</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -3456,7 +3556,7 @@
     <numFmt numFmtId="173" formatCode="0.0000000"/>
     <numFmt numFmtId="174" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="148" x14ac:knownFonts="1">
+  <fonts count="149" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -4426,6 +4526,13 @@
       <b/>
       <sz val="20"/>
       <color rgb="FF170EC2"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF92D050"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -6544,7 +6651,7 @@
     <xf numFmtId="9" fontId="49" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1030">
+  <cellXfs count="1029">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8934,9 +9041,6 @@
     <xf numFmtId="174" fontId="15" fillId="0" borderId="130" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="104" fillId="31" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="76" fillId="31" borderId="104" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8991,6 +9095,9 @@
     <xf numFmtId="167" fontId="131" fillId="31" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9377,9 +9484,6 @@
     </xf>
     <xf numFmtId="167" fontId="69" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -10766,10 +10870,10 @@
                   <c:v>7481</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0</c:v>
+                  <c:v>7284</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0</c:v>
+                  <c:v>7265</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0</c:v>
@@ -11092,6 +11196,12 @@
                 <c:pt idx="20">
                   <c:v>1494.6</c:v>
                 </c:pt>
+                <c:pt idx="21">
+                  <c:v>1414.7</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1429.6</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -11271,10 +11381,10 @@
                   <c:v>0.16651811578056061</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0</c:v>
+                  <c:v>0.16263349695931575</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0</c:v>
+                  <c:v>0.16442389529133022</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0</c:v>
@@ -13107,7 +13217,7 @@
       <c r="B7" s="815">
         <v>8522020</v>
       </c>
-      <c r="C7" s="888">
+      <c r="C7" s="887">
         <v>1667565.2</v>
       </c>
       <c r="D7" s="817"/>
@@ -15020,41 +15130,87 @@
       <c r="A28" s="378">
         <v>23</v>
       </c>
-      <c r="B28" s="815"/>
-      <c r="C28" s="816"/>
+      <c r="B28" s="815">
+        <v>8522020</v>
+      </c>
+      <c r="C28" s="816">
+        <v>1713571.8</v>
+      </c>
       <c r="D28" s="817"/>
-      <c r="E28" s="817"/>
-      <c r="F28" s="817"/>
-      <c r="G28" s="817"/>
+      <c r="E28" s="817">
+        <v>44</v>
+      </c>
+      <c r="F28" s="817">
+        <v>11591.8</v>
+      </c>
+      <c r="G28" s="817">
+        <v>68225</v>
+      </c>
       <c r="H28" s="818"/>
-      <c r="I28" s="819"/>
+      <c r="I28" s="819">
+        <v>2009882</v>
+      </c>
       <c r="J28" s="876"/>
-      <c r="K28" s="818"/>
-      <c r="L28" s="817"/>
-      <c r="M28" s="821"/>
-      <c r="N28" s="819"/>
-      <c r="O28" s="822"/>
-      <c r="P28" s="823"/>
-      <c r="Q28" s="817"/>
+      <c r="K28" s="818">
+        <v>468000</v>
+      </c>
+      <c r="L28" s="817">
+        <v>94863.41</v>
+      </c>
+      <c r="M28" s="821">
+        <v>656484.12</v>
+      </c>
+      <c r="N28" s="819">
+        <v>88068.75</v>
+      </c>
+      <c r="O28" s="822">
+        <v>256702</v>
+      </c>
+      <c r="P28" s="823">
+        <v>88654</v>
+      </c>
+      <c r="Q28" s="817">
+        <v>993087</v>
+      </c>
       <c r="R28" s="817"/>
-      <c r="S28" s="817"/>
+      <c r="S28" s="817">
+        <v>100087</v>
+      </c>
       <c r="T28" s="817"/>
-      <c r="U28" s="817"/>
-      <c r="V28" s="824"/>
+      <c r="U28" s="817">
+        <v>594</v>
+      </c>
+      <c r="V28" s="824">
+        <v>1369103</v>
+      </c>
       <c r="W28" s="817"/>
-      <c r="X28" s="825"/>
-      <c r="Y28" s="817"/>
-      <c r="Z28" s="817"/>
-      <c r="AA28" s="817"/>
+      <c r="X28" s="825">
+        <v>49699</v>
+      </c>
+      <c r="Y28" s="817">
+        <v>72365</v>
+      </c>
+      <c r="Z28" s="817">
+        <v>16118</v>
+      </c>
+      <c r="AA28" s="817">
+        <v>97122</v>
+      </c>
       <c r="AB28" s="817"/>
-      <c r="AC28" s="817"/>
-      <c r="AD28" s="817"/>
+      <c r="AC28" s="817">
+        <v>7079</v>
+      </c>
+      <c r="AD28" s="817">
+        <v>263787</v>
+      </c>
       <c r="AE28" s="817"/>
       <c r="AF28" s="819"/>
       <c r="AG28" s="817"/>
       <c r="AH28" s="817"/>
       <c r="AI28" s="817"/>
-      <c r="AJ28" s="880"/>
+      <c r="AJ28" s="880">
+        <v>7383613.8779999996</v>
+      </c>
       <c r="AK28" s="192"/>
       <c r="AL28" s="387" t="s">
         <v>55</v>
@@ -15067,41 +15223,87 @@
       <c r="A29" s="378">
         <v>24</v>
       </c>
-      <c r="B29" s="815"/>
-      <c r="C29" s="816"/>
+      <c r="B29" s="815">
+        <v>8522020</v>
+      </c>
+      <c r="C29" s="816">
+        <v>1716643.4</v>
+      </c>
       <c r="D29" s="817"/>
-      <c r="E29" s="817"/>
-      <c r="F29" s="817"/>
-      <c r="G29" s="817"/>
+      <c r="E29" s="817">
+        <v>44</v>
+      </c>
+      <c r="F29" s="817">
+        <v>11613.2</v>
+      </c>
+      <c r="G29" s="817">
+        <v>68225</v>
+      </c>
       <c r="H29" s="818"/>
-      <c r="I29" s="819"/>
+      <c r="I29" s="819">
+        <v>2017147</v>
+      </c>
       <c r="J29" s="876"/>
-      <c r="K29" s="818"/>
-      <c r="L29" s="817"/>
-      <c r="M29" s="821"/>
-      <c r="N29" s="819"/>
-      <c r="O29" s="822"/>
-      <c r="P29" s="823"/>
-      <c r="Q29" s="817"/>
+      <c r="K29" s="818">
+        <v>468000</v>
+      </c>
+      <c r="L29" s="817">
+        <v>95511.79</v>
+      </c>
+      <c r="M29" s="821">
+        <v>658415.18999999994</v>
+      </c>
+      <c r="N29" s="819">
+        <v>88314.54</v>
+      </c>
+      <c r="O29" s="822">
+        <v>256912</v>
+      </c>
+      <c r="P29" s="823">
+        <v>88847</v>
+      </c>
+      <c r="Q29" s="817">
+        <v>993332</v>
+      </c>
       <c r="R29" s="817"/>
-      <c r="S29" s="817"/>
+      <c r="S29" s="817">
+        <v>100266</v>
+      </c>
       <c r="T29" s="817"/>
-      <c r="U29" s="817"/>
-      <c r="V29" s="824"/>
+      <c r="U29" s="817">
+        <v>598</v>
+      </c>
+      <c r="V29" s="824">
+        <v>1369305</v>
+      </c>
       <c r="W29" s="817"/>
-      <c r="X29" s="825"/>
-      <c r="Y29" s="817"/>
-      <c r="Z29" s="817"/>
-      <c r="AA29" s="817"/>
+      <c r="X29" s="825">
+        <v>49740</v>
+      </c>
+      <c r="Y29" s="817">
+        <v>72477</v>
+      </c>
+      <c r="Z29" s="817">
+        <v>16144</v>
+      </c>
+      <c r="AA29" s="817">
+        <v>97122</v>
+      </c>
       <c r="AB29" s="817"/>
-      <c r="AC29" s="817"/>
-      <c r="AD29" s="817"/>
+      <c r="AC29" s="817">
+        <v>7099</v>
+      </c>
+      <c r="AD29" s="817">
+        <v>263787</v>
+      </c>
       <c r="AE29" s="817"/>
       <c r="AF29" s="819"/>
       <c r="AG29" s="817"/>
       <c r="AH29" s="817"/>
       <c r="AI29" s="817"/>
-      <c r="AJ29" s="880"/>
+      <c r="AJ29" s="880">
+        <v>7383617.4119999995</v>
+      </c>
       <c r="AK29" s="192"/>
       <c r="AL29" s="387"/>
       <c r="AM29" s="387"/>
@@ -15219,7 +15421,7 @@
       <c r="P32" s="823"/>
       <c r="Q32" s="817"/>
       <c r="R32" s="817"/>
-      <c r="S32" s="883"/>
+      <c r="S32" s="882"/>
       <c r="T32" s="817"/>
       <c r="U32" s="817"/>
       <c r="V32" s="824"/>
@@ -15264,7 +15466,7 @@
       <c r="P33" s="823"/>
       <c r="Q33" s="817"/>
       <c r="R33" s="817"/>
-      <c r="S33" s="883"/>
+      <c r="S33" s="882"/>
       <c r="T33" s="817"/>
       <c r="U33" s="817"/>
       <c r="V33" s="824"/>
@@ -17188,13 +17390,13 @@
       <formula>B7&lt;B6</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B11:B27">
+  <conditionalFormatting sqref="B11:B29">
     <cfRule type="expression" dxfId="115" priority="34">
       <formula>B11&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C35 E35:E37">
-    <cfRule type="expression" dxfId="114" priority="585">
+    <cfRule type="expression" dxfId="114" priority="671">
       <formula>C35&lt;C34</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17214,12 +17416,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36:D37">
-    <cfRule type="expression" dxfId="110" priority="1638">
+    <cfRule type="expression" dxfId="110" priority="1724">
       <formula>C36&lt;C35</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D35 B36:B37">
-    <cfRule type="expression" dxfId="109" priority="1625">
+    <cfRule type="expression" dxfId="109" priority="1711">
       <formula>B35&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17239,7 +17441,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G36:J37 L36:O37">
-    <cfRule type="expression" dxfId="105" priority="1472">
+    <cfRule type="expression" dxfId="105" priority="1558">
       <formula>G36&lt;G35</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17249,7 +17451,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H35:I35 R35 T35 W35 AB35 AE35:AI35 P36:P37 S36:S37 X36:Y37">
-    <cfRule type="expression" dxfId="103" priority="1624">
+    <cfRule type="expression" dxfId="103" priority="1710">
       <formula>H35&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17278,14 +17480,14 @@
       <formula>L22&lt;L21</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L26:Z27">
-    <cfRule type="expression" dxfId="97" priority="40">
-      <formula>L26&lt;L25</formula>
+  <conditionalFormatting sqref="L30:T34 U30:U37 L35:Q35 S35">
+    <cfRule type="expression" dxfId="97" priority="680">
+      <formula>L30&lt;L29</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L28:AC28">
-    <cfRule type="expression" dxfId="96" priority="591">
-      <formula>L28&lt;L27</formula>
+  <conditionalFormatting sqref="L26:Z27 L28:AC29">
+    <cfRule type="expression" dxfId="96" priority="40">
+      <formula>L26&lt;L25</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M11:M17">
@@ -17319,7 +17521,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q36">
-    <cfRule type="expression" dxfId="89" priority="1641">
+    <cfRule type="expression" dxfId="89" priority="1727">
       <formula>Q36&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17339,7 +17541,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R36">
-    <cfRule type="expression" dxfId="85" priority="1637">
+    <cfRule type="expression" dxfId="85" priority="1723">
       <formula>R36&lt;R35</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17373,34 +17575,34 @@
       <formula>M15&lt;M14</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V29:AC29 AA30:AC30 Z30:Z31 V30:Y34 AA31:AB31 AC31:AC37 Z32:AB34 V35 X35:AA35">
-    <cfRule type="expression" dxfId="78" priority="595">
-      <formula>V29&lt;V28</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="W8:W12">
-    <cfRule type="expression" dxfId="77" priority="24">
+    <cfRule type="expression" dxfId="78" priority="24">
       <formula>W8&lt;W7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y7:Z14">
-    <cfRule type="expression" dxfId="76" priority="18">
+    <cfRule type="expression" dxfId="77" priority="18">
       <formula>Y7&lt;Y6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA6:AA12">
-    <cfRule type="expression" dxfId="75" priority="8">
+    <cfRule type="expression" dxfId="76" priority="8">
       <formula>AA6&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA6:AA37">
-    <cfRule type="expression" dxfId="74" priority="1">
+    <cfRule type="expression" dxfId="75" priority="1">
       <formula>AA6&lt;AA5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA28:AA37">
-    <cfRule type="expression" dxfId="73" priority="593">
+    <cfRule type="expression" dxfId="74" priority="41">
       <formula>AA28&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA30:AC30 Z30:Z31 V30:Y34 AA31:AB31 AC31:AC37 Z32:AB34 V35 X35:AA35">
+    <cfRule type="expression" dxfId="73" priority="681">
+      <formula>V30&lt;V29</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC6:AC7">
@@ -17409,7 +17611,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD28:AD37">
-    <cfRule type="expression" dxfId="71" priority="590">
+    <cfRule type="expression" dxfId="71" priority="39">
       <formula>AD28&lt;AD27</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17423,9 +17625,9 @@
       <formula>X7&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE28:AI34 L29:T34 U29:U37 L35:Q35 S35">
-    <cfRule type="expression" dxfId="68" priority="594">
-      <formula>L28&lt;L27</formula>
+  <conditionalFormatting sqref="AE28:AI34">
+    <cfRule type="expression" dxfId="68" priority="42">
+      <formula>AE28&lt;AE27</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ6:AJ37">
@@ -17434,22 +17636,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK6:AK12">
-    <cfRule type="expression" dxfId="66" priority="1514">
+    <cfRule type="expression" dxfId="66" priority="1600">
       <formula>AK6&lt;AK5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK13:AL15">
-    <cfRule type="expression" dxfId="65" priority="1594">
+    <cfRule type="expression" dxfId="65" priority="1680">
       <formula>AK13&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL9:AL14 AL15:AN34 AK16:AK37 AK20:AN21 T36:W37 Z36:Z37 AB36:AB37 AE36:AI37 Q37:R37">
-    <cfRule type="expression" dxfId="64" priority="1531">
+    <cfRule type="expression" dxfId="64" priority="1617">
       <formula>Q9&lt;Q8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO9:AO34">
-    <cfRule type="expression" dxfId="63" priority="1539">
+    <cfRule type="expression" dxfId="63" priority="1625">
       <formula>AO9&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17488,8 +17690,8 @@
     <col min="11" max="11" width="29.7109375" style="469" customWidth="1"/>
     <col min="12" max="12" width="30.5703125" style="469" customWidth="1"/>
     <col min="13" max="13" width="29.7109375" style="470" customWidth="1"/>
-    <col min="14" max="25" width="29.7109375" style="469" customWidth="1"/>
-    <col min="26" max="33" width="29.7109375" style="469" hidden="1" customWidth="1"/>
+    <col min="14" max="28" width="29.7109375" style="469" customWidth="1"/>
+    <col min="29" max="33" width="29.7109375" style="469" hidden="1" customWidth="1"/>
     <col min="34" max="34" width="29.7109375" style="468" customWidth="1"/>
     <col min="35" max="35" width="24.7109375" style="468" customWidth="1"/>
     <col min="36" max="36" width="24.7109375" style="291" customWidth="1"/>
@@ -17862,8 +18064,14 @@
         <f>2842+7025</f>
         <v>9867</v>
       </c>
-      <c r="W8" s="678"/>
-      <c r="X8" s="678"/>
+      <c r="W8" s="678">
+        <f>3955</f>
+        <v>3955</v>
+      </c>
+      <c r="X8" s="678">
+        <f>2020+(2064+1941)</f>
+        <v>6025</v>
+      </c>
       <c r="Y8" s="678"/>
       <c r="Z8" s="678"/>
       <c r="AA8" s="678"/>
@@ -17871,18 +18079,18 @@
       <c r="AC8" s="678"/>
       <c r="AD8" s="678"/>
       <c r="AE8" s="678"/>
-      <c r="AF8" s="885"/>
+      <c r="AF8" s="884"/>
       <c r="AG8" s="747"/>
       <c r="AH8" s="480">
         <f>SUM(B8:AG8)</f>
-        <v>84091</v>
+        <v>94071</v>
       </c>
       <c r="AI8" s="526">
         <v>123950</v>
       </c>
       <c r="AJ8" s="294">
         <f>AH8-AI8</f>
-        <v>-39859</v>
+        <v>-29879</v>
       </c>
       <c r="AK8" s="481"/>
       <c r="AL8" s="481"/>
@@ -17997,12 +18205,12 @@
         <v>651.22199999999998</v>
       </c>
       <c r="W9" s="678">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>W8*0.066</f>
+        <v>261.03000000000003</v>
       </c>
       <c r="X9" s="678">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>2020*0.066+(2064+1941)*0.0708</f>
+        <v>416.87400000000002</v>
       </c>
       <c r="Y9" s="678">
         <f t="shared" si="3"/>
@@ -18036,7 +18244,7 @@
       <c r="AG9" s="748"/>
       <c r="AH9" s="484">
         <f>SUM(B9:AG9)</f>
-        <v>5555.6268</v>
+        <v>6233.5307999999995</v>
       </c>
       <c r="AI9" s="484"/>
       <c r="AL9" s="291" t="s">
@@ -18068,7 +18276,7 @@
       <c r="I10" s="770" t="s">
         <v>310</v>
       </c>
-      <c r="J10" s="893" t="s">
+      <c r="J10" s="892" t="s">
         <v>309</v>
       </c>
       <c r="K10" s="871"/>
@@ -18085,7 +18293,7 @@
       <c r="P10" s="770" t="s">
         <v>316</v>
       </c>
-      <c r="Q10" s="893" t="s">
+      <c r="Q10" s="892" t="s">
         <v>317</v>
       </c>
       <c r="R10" s="879"/>
@@ -18100,7 +18308,9 @@
       <c r="W10" s="878" t="s">
         <v>320</v>
       </c>
-      <c r="X10" s="881"/>
+      <c r="X10" s="878" t="s">
+        <v>323</v>
+      </c>
       <c r="Y10" s="871"/>
       <c r="Z10" s="871"/>
       <c r="AA10" s="796"/>
@@ -18108,7 +18318,7 @@
       <c r="AC10" s="878"/>
       <c r="AD10" s="878"/>
       <c r="AE10" s="871"/>
-      <c r="AF10" s="886"/>
+      <c r="AF10" s="885"/>
       <c r="AG10" s="749"/>
       <c r="AH10" s="487"/>
       <c r="AI10" s="487"/>
@@ -18382,14 +18592,14 @@
       <c r="J13" s="669" t="s">
         <v>307</v>
       </c>
-      <c r="K13" s="896" t="s">
+      <c r="K13" s="895" t="s">
         <v>311</v>
       </c>
       <c r="L13" s="669"/>
       <c r="M13" s="798" t="s">
         <v>309</v>
       </c>
-      <c r="N13" s="899" t="s">
+      <c r="N13" s="898" t="s">
         <v>313</v>
       </c>
       <c r="O13" s="770" t="s">
@@ -18410,16 +18620,18 @@
       <c r="V13" s="770" t="s">
         <v>321</v>
       </c>
-      <c r="W13" s="1029" t="s">
+      <c r="W13" s="899" t="s">
         <v>322</v>
       </c>
-      <c r="X13" s="669"/>
+      <c r="X13" s="770" t="s">
+        <v>310</v>
+      </c>
       <c r="Y13" s="669"/>
       <c r="Z13" s="669"/>
       <c r="AA13" s="669"/>
       <c r="AB13" s="794"/>
       <c r="AC13" s="878"/>
-      <c r="AD13" s="884"/>
+      <c r="AD13" s="883"/>
       <c r="AE13" s="682"/>
       <c r="AF13" s="682"/>
       <c r="AG13" s="685"/>
@@ -18462,7 +18674,7 @@
       <c r="J14" s="498">
         <v>7</v>
       </c>
-      <c r="K14" s="897">
+      <c r="K14" s="896">
         <v>8</v>
       </c>
       <c r="L14" s="498"/>
@@ -18489,10 +18701,17 @@
         <v>4</v>
       </c>
       <c r="V14" s="498">
-        <v>4</v>
-      </c>
-      <c r="W14" s="726"/>
-      <c r="X14" s="498"/>
+        <f>4+4</f>
+        <v>8</v>
+      </c>
+      <c r="W14" s="726">
+        <f>2+7</f>
+        <v>9</v>
+      </c>
+      <c r="X14" s="498">
+        <f>1+8</f>
+        <v>9</v>
+      </c>
       <c r="Y14" s="498"/>
       <c r="Z14" s="498"/>
       <c r="AA14" s="498"/>
@@ -18504,7 +18723,7 @@
       <c r="AG14" s="498"/>
       <c r="AH14" s="468">
         <f>SUM(B14:AF14)</f>
-        <v>87</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:149" s="504" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -18545,7 +18764,7 @@
       <c r="AG15" s="718"/>
       <c r="AH15" s="500">
         <f>IF(AH12=0,"",+(AH36*10)/AH12)</f>
-        <v>9.7848664688427291</v>
+        <v>11.25</v>
       </c>
       <c r="AI15" s="502"/>
       <c r="AJ15" s="503"/>
@@ -18963,13 +19182,13 @@
         <f>+'Water '!$D27</f>
         <v>440</v>
       </c>
-      <c r="W20" s="509" t="str">
+      <c r="W20" s="509">
         <f>+'Water '!$D28</f>
-        <v>0</v>
-      </c>
-      <c r="X20" s="509" t="str">
+        <v>197</v>
+      </c>
+      <c r="X20" s="509">
         <f>+'Water '!$D29</f>
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="Y20" s="509" t="str">
         <f>+'Water '!$D30</f>
@@ -19006,7 +19225,7 @@
       <c r="AG20" s="509"/>
       <c r="AH20" s="484">
         <f>SUM($B20:AF20)</f>
-        <v>3511</v>
+        <v>3918</v>
       </c>
       <c r="AI20" s="484"/>
       <c r="AJ20" s="485"/>
@@ -19099,13 +19318,13 @@
         <f>+'Water '!$E27</f>
         <v>134</v>
       </c>
-      <c r="W21" s="511" t="str">
+      <c r="W21" s="511">
         <f>+'Water '!$E28</f>
-        <v>0</v>
-      </c>
-      <c r="X21" s="511" t="str">
+        <v>208</v>
+      </c>
+      <c r="X21" s="511">
         <f>+'Water '!$E29</f>
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="Y21" s="512" t="str">
         <f>+'Water '!$E30</f>
@@ -19142,7 +19361,7 @@
       <c r="AG21" s="509"/>
       <c r="AH21" s="484">
         <f>SUM($B21:AF21)</f>
-        <v>2670</v>
+        <v>3071</v>
       </c>
       <c r="AI21" s="484"/>
     </row>
@@ -19236,11 +19455,11 @@
       </c>
       <c r="W22" s="514">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>405</v>
       </c>
       <c r="X22" s="514">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>403</v>
       </c>
       <c r="Y22" s="514">
         <f>SUM(Y19:Y21)</f>
@@ -19277,7 +19496,7 @@
       <c r="AG22" s="515"/>
       <c r="AH22" s="516">
         <f>SUM($B22:AF22)</f>
-        <v>6181</v>
+        <v>6989</v>
       </c>
       <c r="AI22" s="514"/>
       <c r="AJ22" s="517"/>
@@ -19600,11 +19819,11 @@
       </c>
       <c r="W26" s="521">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>157.68</v>
       </c>
       <c r="X26" s="521">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>147.46</v>
       </c>
       <c r="Y26" s="521">
         <f t="shared" si="6"/>
@@ -19641,15 +19860,15 @@
       <c r="AG26" s="521"/>
       <c r="AH26" s="484">
         <f>SUM($B26:AF26)</f>
-        <v>2081.23</v>
+        <v>2386.37</v>
       </c>
       <c r="AI26" s="523">
         <f>AH29+AH45+AH36</f>
-        <v>6418</v>
+        <v>7309</v>
       </c>
       <c r="AK26" s="524">
         <f>(AI26*10)/AH9</f>
-        <v>11.552251853922225</v>
+        <v>11.725297001821184</v>
       </c>
     </row>
     <row r="27" spans="1:149" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -19888,11 +20107,11 @@
       </c>
       <c r="W29" s="509">
         <f>'Water '!$H28</f>
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="X29" s="509">
         <f>'Water '!$H29</f>
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="Y29" s="509">
         <f>'Water '!$H30</f>
@@ -19929,7 +20148,7 @@
       <c r="AG29" s="509"/>
       <c r="AH29" s="484">
         <f>SUM($B29:AF29)</f>
-        <v>3388</v>
+        <v>3829</v>
       </c>
       <c r="AI29" s="484"/>
       <c r="AJ29" s="484"/>
@@ -20023,13 +20242,13 @@
         <f t="shared" si="7"/>
         <v>210</v>
       </c>
-      <c r="W30" s="509" t="str">
+      <c r="W30" s="509">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X30" s="509" t="str">
+        <v>216</v>
+      </c>
+      <c r="X30" s="509">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="Y30" s="509" t="str">
         <f>Y36</f>
@@ -20066,7 +20285,7 @@
       <c r="AG30" s="509"/>
       <c r="AH30" s="484">
         <f>AH36</f>
-        <v>2638</v>
+        <v>3033</v>
       </c>
       <c r="AI30" s="484"/>
       <c r="AJ30" s="484"/>
@@ -20160,13 +20379,13 @@
         <f>V45</f>
         <v>30</v>
       </c>
-      <c r="W31" s="509" t="str">
+      <c r="W31" s="509">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="X31" s="509" t="str">
+        <v>29</v>
+      </c>
+      <c r="X31" s="509">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Y31" s="509" t="str">
         <f t="shared" si="8"/>
@@ -20203,7 +20422,7 @@
       <c r="AG31" s="509"/>
       <c r="AH31" s="484">
         <f>AH45</f>
-        <v>392</v>
+        <v>447</v>
       </c>
       <c r="AI31" s="484"/>
       <c r="AJ31" s="484"/>
@@ -20298,11 +20517,11 @@
       </c>
       <c r="W32" s="526">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>441</v>
       </c>
       <c r="X32" s="527">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="Y32" s="527">
         <f t="shared" si="9"/>
@@ -20339,7 +20558,7 @@
       <c r="AG32" s="527"/>
       <c r="AH32" s="526">
         <f>SUM($B32:AF32)</f>
-        <v>6418</v>
+        <v>7309</v>
       </c>
       <c r="AI32" s="526"/>
       <c r="AJ32" s="528"/>
@@ -20572,13 +20791,13 @@
         <f>+'Water '!$J27</f>
         <v>210</v>
       </c>
-      <c r="W36" s="535" t="str">
+      <c r="W36" s="535">
         <f>+'Water '!$J28</f>
-        <v>0</v>
-      </c>
-      <c r="X36" s="535" t="str">
+        <v>216</v>
+      </c>
+      <c r="X36" s="535">
         <f>+'Water '!$J29</f>
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="Y36" s="535" t="str">
         <f>+'Water '!$J30</f>
@@ -20615,7 +20834,7 @@
       <c r="AG36" s="508"/>
       <c r="AH36" s="484">
         <f>SUM($B36:AF36)</f>
-        <v>2638</v>
+        <v>3033</v>
       </c>
       <c r="AI36" s="484"/>
     </row>
@@ -21382,13 +21601,13 @@
         <f>+'Water '!$N27</f>
         <v>19</v>
       </c>
-      <c r="W41" s="539" t="str">
+      <c r="W41" s="539">
         <f>+'Water '!$N28</f>
-        <v>0</v>
-      </c>
-      <c r="X41" s="539" t="str">
+        <v>26</v>
+      </c>
+      <c r="X41" s="539">
         <f>+'Water '!$N29</f>
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="Y41" s="539" t="str">
         <f>+'Water '!$N30</f>
@@ -21425,7 +21644,7 @@
       <c r="AG41" s="539"/>
       <c r="AH41" s="514">
         <f>SUM($B41:AF41)</f>
-        <v>543</v>
+        <v>610</v>
       </c>
       <c r="AI41" s="514"/>
       <c r="AJ41" s="514"/>
@@ -21631,13 +21850,13 @@
         <f>+'Water '!$O27</f>
         <v>158</v>
       </c>
-      <c r="W42" s="508" t="str">
+      <c r="W42" s="508">
         <f>+'Water '!$O28</f>
-        <v>0</v>
-      </c>
-      <c r="X42" s="508" t="str">
+        <v>94</v>
+      </c>
+      <c r="X42" s="508">
         <f>+'Water '!$O29</f>
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="Y42" s="508" t="str">
         <f>+'Water '!$O30</f>
@@ -21674,7 +21893,7 @@
       <c r="AG42" s="508"/>
       <c r="AH42" s="540">
         <f>SUM($B42:AF42)</f>
-        <v>1498</v>
+        <v>1704</v>
       </c>
       <c r="AI42" s="508"/>
       <c r="AJ42" s="508"/>
@@ -21860,11 +22079,11 @@
       <c r="V43" s="542">
         <v>31</v>
       </c>
-      <c r="W43" s="542" t="str">
-        <v>0</v>
-      </c>
-      <c r="X43" s="542" t="str">
-        <v>0</v>
+      <c r="W43" s="542">
+        <v>23</v>
+      </c>
+      <c r="X43" s="542">
+        <v>20</v>
       </c>
       <c r="Y43" s="542" t="str">
         <v>0</v>
@@ -21893,7 +22112,7 @@
       <c r="AG43" s="542"/>
       <c r="AH43" s="543">
         <f>SUM($B43:AF43)</f>
-        <v>306</v>
+        <v>349</v>
       </c>
       <c r="AI43" s="544"/>
       <c r="AJ43" s="474"/>
@@ -22099,13 +22318,13 @@
         <f>+'Water '!$M27</f>
         <v>0</v>
       </c>
-      <c r="W44" s="508" t="str">
+      <c r="W44" s="508">
         <f>+'Water '!$M28</f>
-        <v>0</v>
-      </c>
-      <c r="X44" s="508" t="str">
+        <v>3</v>
+      </c>
+      <c r="X44" s="508">
         <f>+'Water '!$M29</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y44" s="508" t="str">
         <f>+'Water '!$M30</f>
@@ -22142,7 +22361,7 @@
       <c r="AG44" s="508"/>
       <c r="AH44" s="484">
         <f>SUM($B44:AF44)</f>
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="AI44" s="484"/>
       <c r="AJ44" s="291"/>
@@ -22348,13 +22567,13 @@
         <f>+'Water '!$Q27</f>
         <v>30</v>
       </c>
-      <c r="W45" s="539" t="str">
+      <c r="W45" s="539">
         <f>+'Water '!$Q28</f>
-        <v>0</v>
-      </c>
-      <c r="X45" s="539" t="str">
+        <v>29</v>
+      </c>
+      <c r="X45" s="539">
         <f>+'Water '!$Q29</f>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Y45" s="539" t="str">
         <f>+'Water '!$Q30</f>
@@ -22391,7 +22610,7 @@
       <c r="AG45" s="539"/>
       <c r="AH45" s="514">
         <f>SUM($B45:AF45)</f>
-        <v>392</v>
+        <v>447</v>
       </c>
       <c r="AI45" s="514"/>
       <c r="AJ45" s="514"/>
@@ -23065,11 +23284,11 @@
       </c>
       <c r="W50" s="484">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>391</v>
       </c>
       <c r="X50" s="484">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="Y50" s="484">
         <f t="shared" si="10"/>
@@ -23106,7 +23325,7 @@
       <c r="AG50" s="484"/>
       <c r="AH50" s="484">
         <f>SUM($B50:AF50)</f>
-        <v>5430</v>
+        <v>6203</v>
       </c>
       <c r="AI50" s="484"/>
     </row>
@@ -23286,13 +23505,13 @@
         <f t="shared" si="12"/>
         <v>3.2247067820190352</v>
       </c>
-      <c r="W54" s="545" t="str">
+      <c r="W54" s="545">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="X54" s="545" t="str">
+        <v>8.2749109297781853</v>
+      </c>
+      <c r="X54" s="545">
         <f t="shared" si="12"/>
-        <v/>
+        <v>4.293863373585304</v>
       </c>
       <c r="Y54" s="545" t="str">
         <f>IF(Y$9=0,"",+(Y36*10)/Y$9)</f>
@@ -23329,14 +23548,14 @@
       <c r="AG54" s="545"/>
       <c r="AH54" s="546">
         <f>+(AH36*10)/AH$9</f>
-        <v>4.7483391072992882</v>
+        <v>4.8656212623510262</v>
       </c>
       <c r="AI54" s="546">
         <v>3.2</v>
       </c>
       <c r="AJ54" s="547">
         <f t="shared" ref="AJ54:AJ67" si="13">AI54-AH54</f>
-        <v>-1.548339107299288</v>
+        <v>-1.665621262351026</v>
       </c>
     </row>
     <row r="55" spans="1:59" s="553" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -23498,13 +23717,13 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="W56" s="545" t="str">
+      <c r="W56" s="545">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="X56" s="545" t="str">
+        <v>0</v>
+      </c>
+      <c r="X56" s="545">
         <f t="shared" si="18"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y56" s="545" t="str">
         <f t="shared" ref="Y56:Y63" si="19">IF(Y$9=0,"",+(Y38*10)/Y$9)</f>
@@ -23662,13 +23881,13 @@
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="W57" s="549" t="str">
+      <c r="W57" s="549">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="X57" s="549" t="str">
+        <v>0</v>
+      </c>
+      <c r="X57" s="549">
         <f t="shared" si="21"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y57" s="549" t="str">
         <f t="shared" si="19"/>
@@ -23826,13 +24045,13 @@
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="W58" s="545" t="str">
+      <c r="W58" s="545">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="X58" s="545" t="str">
+        <v>0</v>
+      </c>
+      <c r="X58" s="545">
         <f t="shared" si="22"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y58" s="545" t="str">
         <f t="shared" si="19"/>
@@ -23992,13 +24211,13 @@
         <f t="shared" si="23"/>
         <v>0.29175918503981746</v>
       </c>
-      <c r="W59" s="549" t="str">
+      <c r="W59" s="549">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="X59" s="549" t="str">
+        <v>0.99605409339922601</v>
+      </c>
+      <c r="X59" s="549">
         <f t="shared" si="23"/>
-        <v/>
+        <v>0.98351060512289079</v>
       </c>
       <c r="Y59" s="549" t="str">
         <f t="shared" si="19"/>
@@ -24035,14 +24254,14 @@
       <c r="AG59" s="549"/>
       <c r="AH59" s="549">
         <f t="shared" si="14"/>
-        <v>0.97738746598313619</v>
+        <v>0.97857862513489147</v>
       </c>
       <c r="AI59" s="550">
         <v>0.7</v>
       </c>
       <c r="AJ59" s="551">
         <f t="shared" si="13"/>
-        <v>-0.27738746598313624</v>
+        <v>-0.27857862513489151</v>
       </c>
       <c r="AK59" s="474"/>
       <c r="AL59" s="474"/>
@@ -24156,13 +24375,13 @@
         <f t="shared" si="24"/>
         <v>2.4262079598047976</v>
       </c>
-      <c r="W60" s="545" t="str">
+      <c r="W60" s="545">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="X60" s="545" t="str">
+        <v>3.6011186453664328</v>
+      </c>
+      <c r="X60" s="545">
         <f t="shared" si="24"/>
-        <v/>
+        <v>2.6866631164332628</v>
       </c>
       <c r="Y60" s="545" t="str">
         <f t="shared" si="19"/>
@@ -24199,14 +24418,14 @@
       <c r="AG60" s="545"/>
       <c r="AH60" s="568">
         <f t="shared" si="14"/>
-        <v>2.6963654218098307</v>
+        <v>2.7336032413604183</v>
       </c>
       <c r="AI60" s="555">
         <v>2.1</v>
       </c>
       <c r="AJ60" s="547">
         <f t="shared" si="13"/>
-        <v>-0.59636542180983065</v>
+        <v>-0.63360324136041823</v>
       </c>
     </row>
     <row r="61" spans="1:59" s="504" customFormat="1" x14ac:dyDescent="0.35">
@@ -24297,13 +24516,13 @@
         <f t="shared" si="25"/>
         <v>0.47602814401233373</v>
       </c>
-      <c r="W61" s="549" t="str">
+      <c r="W61" s="549">
         <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="X61" s="549" t="str">
+        <v>0.88112477493008456</v>
+      </c>
+      <c r="X61" s="549">
         <f t="shared" si="25"/>
-        <v/>
+        <v>0.47976127079165404</v>
       </c>
       <c r="Y61" s="549" t="str">
         <f t="shared" si="19"/>
@@ -24340,14 +24559,14 @@
       <c r="AG61" s="549"/>
       <c r="AH61" s="550">
         <f t="shared" si="14"/>
-        <v>0.55079293663138063</v>
+        <v>0.55987531175750349</v>
       </c>
       <c r="AI61" s="550">
         <v>0.7</v>
       </c>
       <c r="AJ61" s="551">
         <f t="shared" si="13"/>
-        <v>0.14920706336861933</v>
+        <v>0.14012468824249646</v>
       </c>
       <c r="AK61" s="474"/>
       <c r="AL61" s="474"/>
@@ -24461,13 +24680,13 @@
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="W62" s="545" t="str">
+      <c r="W62" s="545">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="X62" s="545" t="str">
+        <v>0.11492931846914146</v>
+      </c>
+      <c r="X62" s="545">
         <f t="shared" si="26"/>
-        <v/>
+        <v>9.5952254158330808E-2</v>
       </c>
       <c r="Y62" s="545" t="str">
         <f t="shared" si="19"/>
@@ -24504,14 +24723,14 @@
       <c r="AG62" s="545"/>
       <c r="AH62" s="555">
         <f>+(AH44*10)/AH$9</f>
-        <v>9.5398776606088809E-2</v>
+        <v>9.6253635259169662E-2</v>
       </c>
       <c r="AI62" s="555">
         <v>0.1</v>
       </c>
       <c r="AJ62" s="547">
         <f t="shared" si="13"/>
-        <v>4.6012233939111968E-3</v>
+        <v>3.7463647408303435E-3</v>
       </c>
     </row>
     <row r="63" spans="1:59" s="504" customFormat="1" x14ac:dyDescent="0.35">
@@ -24602,13 +24821,13 @@
         <f t="shared" si="27"/>
         <v>0.46067239743129074</v>
       </c>
-      <c r="W63" s="549" t="str">
+      <c r="W63" s="549">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="X63" s="549" t="str">
+        <v>1.1109834118683675</v>
+      </c>
+      <c r="X63" s="549">
         <f t="shared" si="27"/>
-        <v/>
+        <v>0.62368965202915028</v>
       </c>
       <c r="Y63" s="549" t="str">
         <f t="shared" si="19"/>
@@ -24645,14 +24864,14 @@
       <c r="AG63" s="549"/>
       <c r="AH63" s="550">
         <f>+(AH45*10)/AH$9</f>
-        <v>0.70559095150163798</v>
+        <v>0.71708958268081391</v>
       </c>
       <c r="AI63" s="550">
         <v>0.6</v>
       </c>
       <c r="AJ63" s="551">
         <f t="shared" si="13"/>
-        <v>-0.105590951501638</v>
+        <v>-0.11708958268081393</v>
       </c>
       <c r="AK63" s="474"/>
       <c r="AL63" s="474"/>
@@ -24834,13 +25053,13 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="W65" s="575" t="str">
+      <c r="W65" s="575">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="X65" s="575" t="str">
+        <v>0</v>
+      </c>
+      <c r="X65" s="575">
         <f t="shared" si="28"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y65" s="575" t="str">
         <f>IF(Y$9=0,"",+(Y46*10)/Y$9)</f>
@@ -25136,11 +25355,11 @@
       </c>
       <c r="W68" s="585">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>14.979121173811437</v>
       </c>
       <c r="X68" s="585">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>9.1634402721205905</v>
       </c>
       <c r="Y68" s="585">
         <f t="shared" si="29"/>
@@ -25177,7 +25396,7 @@
       <c r="AG68" s="585"/>
       <c r="AH68" s="584">
         <f t="shared" si="29"/>
-        <v>9.7738746598313622</v>
+        <v>9.9510216585438229</v>
       </c>
       <c r="AI68" s="584">
         <f>SUM(AI54:AI63,AI65)</f>
@@ -25185,7 +25404,7 @@
       </c>
       <c r="AJ68" s="547">
         <f t="shared" si="29"/>
-        <v>-0.17387465983136224</v>
+        <v>-0.35102165854382278</v>
       </c>
       <c r="AK68" s="468"/>
       <c r="AL68" s="291"/>
@@ -25301,11 +25520,11 @@
       </c>
       <c r="W69" s="588">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>4.5971727387656589</v>
       </c>
       <c r="X69" s="588">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>3.2623766413832476</v>
       </c>
       <c r="Y69" s="588">
         <f t="shared" si="30"/>
@@ -25342,7 +25561,7 @@
       <c r="AG69" s="588"/>
       <c r="AH69" s="587">
         <f t="shared" si="30"/>
-        <v>3.3425571350473002</v>
+        <v>3.3897321883770912</v>
       </c>
       <c r="AI69" s="587">
         <f t="shared" si="30"/>
@@ -25350,7 +25569,7 @@
       </c>
       <c r="AJ69" s="587">
         <f t="shared" si="30"/>
-        <v>-0.4425571350473001</v>
+        <v>-0.48973218837709143</v>
       </c>
       <c r="AK69" s="589"/>
       <c r="AL69" s="291"/>
@@ -25499,13 +25718,13 @@
         <f>+'Water '!$F27</f>
         <v>140</v>
       </c>
-      <c r="W71" s="593" t="str">
+      <c r="W71" s="593">
         <f>+'Water '!$F28</f>
-        <v>0</v>
-      </c>
-      <c r="X71" s="593" t="str">
+        <v>216</v>
+      </c>
+      <c r="X71" s="593">
         <f>+'Water '!$F29</f>
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="Y71" s="593" t="str">
         <f>+'Water '!$F30</f>
@@ -25542,7 +25761,7 @@
       <c r="AG71" s="593"/>
       <c r="AH71" s="594">
         <f>SUM($B71:AF71)</f>
-        <v>2851</v>
+        <v>3269</v>
       </c>
       <c r="AI71" s="594"/>
       <c r="AJ71" s="595"/>
@@ -25654,25 +25873,25 @@
       <c r="B74" s="791">
         <v>1600</v>
       </c>
-      <c r="C74" s="887">
+      <c r="C74" s="886">
         <v>1200</v>
       </c>
-      <c r="D74" s="894">
-        <v>0</v>
-      </c>
-      <c r="E74" s="894">
-        <v>0</v>
-      </c>
-      <c r="F74" s="894">
+      <c r="D74" s="893">
+        <v>0</v>
+      </c>
+      <c r="E74" s="893">
+        <v>0</v>
+      </c>
+      <c r="F74" s="893">
         <v>1600</v>
       </c>
-      <c r="G74" s="894">
+      <c r="G74" s="893">
         <v>1500</v>
       </c>
-      <c r="H74" s="894">
+      <c r="H74" s="893">
         <v>1400</v>
       </c>
-      <c r="I74" s="895">
+      <c r="I74" s="894">
         <f>2200+800</f>
         <v>3000</v>
       </c>
@@ -25682,17 +25901,17 @@
       <c r="K74" s="877">
         <v>800</v>
       </c>
-      <c r="L74" s="898"/>
-      <c r="M74" s="895">
+      <c r="L74" s="897"/>
+      <c r="M74" s="894">
         <v>1500</v>
       </c>
-      <c r="N74" s="894">
+      <c r="N74" s="893">
         <v>2100</v>
       </c>
-      <c r="O74" s="894">
+      <c r="O74" s="893">
         <v>2100</v>
       </c>
-      <c r="P74" s="895">
+      <c r="P74" s="894">
         <f>2500+1100</f>
         <v>3600</v>
       </c>
@@ -25715,13 +25934,23 @@
         <v>2200</v>
       </c>
       <c r="W74" s="790">
-        <v>0</v>
-      </c>
-      <c r="X74" s="790"/>
-      <c r="Y74" s="790"/>
-      <c r="Z74" s="790"/>
-      <c r="AA74" s="790"/>
-      <c r="AB74" s="790"/>
+        <v>1000</v>
+      </c>
+      <c r="X74" s="790">
+        <v>2000</v>
+      </c>
+      <c r="Y74" s="790">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="790">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="790">
+        <v>0</v>
+      </c>
+      <c r="AB74" s="790">
+        <v>0</v>
+      </c>
       <c r="AC74" s="790"/>
       <c r="AD74" s="790"/>
       <c r="AE74" s="790"/>
@@ -25729,7 +25958,7 @@
       <c r="AG74" s="790"/>
       <c r="AH74" s="516">
         <f>SUM(B74:AF74)</f>
-        <v>28500</v>
+        <v>31500</v>
       </c>
       <c r="AI74" s="537"/>
       <c r="AJ74" s="537"/>
@@ -25825,11 +26054,11 @@
       <c r="V75" s="601">
         <v>2463.6900000000605</v>
       </c>
-      <c r="W75" s="601" t="str">
-        <v>0</v>
-      </c>
-      <c r="X75" s="601" t="str">
-        <v>0</v>
+      <c r="W75" s="601">
+        <v>1195.2399999999907</v>
+      </c>
+      <c r="X75" s="601">
+        <v>1931.0699999999488</v>
       </c>
       <c r="Y75" s="599" t="str">
         <v>0</v>
@@ -25858,7 +26087,7 @@
       <c r="AG75" s="599"/>
       <c r="AH75" s="516">
         <f>SUM(B75:AF75)</f>
-        <v>24943.729999999981</v>
+        <v>28070.039999999921</v>
       </c>
       <c r="AI75" s="600"/>
       <c r="AJ75" s="600"/>
@@ -25953,11 +26182,11 @@
       <c r="V76" s="604">
         <v>354.58999999999651</v>
       </c>
-      <c r="W76" s="604" t="str">
-        <v>0</v>
-      </c>
-      <c r="X76" s="604" t="str">
-        <v>0</v>
+      <c r="W76" s="604">
+        <v>172.94999999999709</v>
+      </c>
+      <c r="X76" s="604">
+        <v>245.7899999999936</v>
       </c>
       <c r="Y76" s="604" t="str">
         <v>0</v>
@@ -25986,7 +26215,7 @@
       <c r="AG76" s="604"/>
       <c r="AH76" s="604">
         <f>SUM($B76:AF76)</f>
-        <v>3260.320000000007</v>
+        <v>3679.0599999999977</v>
       </c>
       <c r="AI76" s="605"/>
       <c r="AJ76" s="606"/>
@@ -26082,11 +26311,11 @@
       <c r="V77" s="607">
         <v>408.61999999999534</v>
       </c>
-      <c r="W77" s="607" t="str">
-        <v>0</v>
-      </c>
-      <c r="X77" s="607" t="str">
-        <v>0</v>
+      <c r="W77" s="607">
+        <v>352.2100000000064</v>
+      </c>
+      <c r="X77" s="607">
+        <v>648.3799999999901</v>
       </c>
       <c r="Y77" s="607" t="str">
         <v>0</v>
@@ -26115,7 +26344,7 @@
       <c r="AG77" s="607"/>
       <c r="AH77" s="604">
         <f>SUM($B77:AF77)</f>
-        <v>7892.9400000000023</v>
+        <v>8893.5299999999988</v>
       </c>
       <c r="AI77" s="757"/>
       <c r="AJ77" s="757" t="s">
@@ -26232,13 +26461,13 @@
         <f>V75-V76-V77</f>
         <v>1700.4800000000687</v>
       </c>
-      <c r="W78" s="882">
+      <c r="W78" s="881">
         <f t="shared" ref="W78:AB78" si="32">W75-W76-W77</f>
-        <v>0</v>
+        <v>670.07999999998719</v>
       </c>
       <c r="X78" s="788">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1036.8999999999651</v>
       </c>
       <c r="Y78" s="788">
         <f t="shared" si="32"/>
@@ -26278,7 +26507,7 @@
       </c>
       <c r="AH78" s="484">
         <f>AH75-AH76-AH77</f>
-        <v>13790.469999999972</v>
+        <v>15497.449999999924</v>
       </c>
       <c r="AI78" s="484"/>
     </row>
@@ -26480,10 +26709,10 @@
         <v>7481</v>
       </c>
       <c r="W80" s="613">
-        <v>0</v>
+        <v>7284</v>
       </c>
       <c r="X80" s="613">
-        <v>0</v>
+        <v>7265</v>
       </c>
       <c r="Y80" s="613">
         <v>0</v>
@@ -26512,7 +26741,7 @@
       <c r="AG80" s="613"/>
       <c r="AH80" s="594">
         <f>SUM(B80:AF80)</f>
-        <v>123232</v>
+        <v>137781</v>
       </c>
       <c r="AI80" s="594"/>
       <c r="AJ80" s="614"/>
@@ -26670,10 +26899,10 @@
         <v>8975.6</v>
       </c>
       <c r="U82" s="617">
-        <v>0</v>
+        <v>8698.7000000000007</v>
       </c>
       <c r="V82" s="617">
-        <v>0</v>
+        <v>8694.6</v>
       </c>
       <c r="W82" s="617">
         <v>0</v>
@@ -26700,7 +26929,7 @@
         <v>0</v>
       </c>
       <c r="AE82" s="617">
-        <v>150415.59999999998</v>
+        <v>167808.9</v>
       </c>
       <c r="AF82" s="617">
         <v>0</v>
@@ -26708,7 +26937,7 @@
       <c r="AG82" s="617"/>
       <c r="AH82" s="594">
         <f>SUM(B82:AF82)</f>
-        <v>283744.40000000002</v>
+        <v>318531</v>
       </c>
       <c r="AI82" s="594"/>
       <c r="AJ82" s="614"/>
@@ -26805,10 +27034,10 @@
         <v>1494.6</v>
       </c>
       <c r="W83" s="621">
-        <v>0</v>
+        <v>1414.7</v>
       </c>
       <c r="X83" s="621">
-        <v>0</v>
+        <v>1429.6</v>
       </c>
       <c r="Y83" s="702">
         <v>0</v>
@@ -26837,7 +27066,7 @@
       <c r="AG83" s="621"/>
       <c r="AH83" s="594">
         <f>SUM(B83:AF83)</f>
-        <v>27183.599999999995</v>
+        <v>30027.899999999994</v>
       </c>
       <c r="AI83" s="594"/>
       <c r="AJ83" s="594"/>
@@ -26933,11 +27162,11 @@
       <c r="V84" s="620">
         <v>3661</v>
       </c>
-      <c r="W84" s="620" t="str">
-        <v>0</v>
-      </c>
-      <c r="X84" s="620" t="str">
-        <v>0</v>
+      <c r="W84" s="620">
+        <v>2948.1999999999534</v>
+      </c>
+      <c r="X84" s="620">
+        <v>3071.5999999998603</v>
       </c>
       <c r="Y84" s="620" t="str">
         <v>0</v>
@@ -26966,7 +27195,7 @@
       <c r="AG84" s="620"/>
       <c r="AH84" s="621">
         <f>SUM($B84:AF84)</f>
-        <v>46375.600000000093</v>
+        <v>52395.399999999907</v>
       </c>
       <c r="AI84" s="594"/>
       <c r="AJ84" s="614"/>
@@ -27086,9 +27315,9 @@
         <f>'Steam Mass Flow '!B26</f>
         <v>0</v>
       </c>
-      <c r="X85" s="622" t="str">
+      <c r="X85" s="622">
         <f>'Steam Mass Flow '!B27</f>
-        <v>0</v>
+        <v>3.5339999999850988</v>
       </c>
       <c r="Y85" s="622" t="str">
         <f>'Steam Mass Flow '!B28</f>
@@ -27125,7 +27354,7 @@
       <c r="AG85" s="622"/>
       <c r="AH85" s="623">
         <f>SUM($B85:AF85)</f>
-        <v>116.67799999937415</v>
+        <v>120.21199999935925</v>
       </c>
       <c r="AI85" s="622"/>
       <c r="AJ85" s="624"/>
@@ -27427,13 +27656,13 @@
         <f t="shared" si="35"/>
         <v>8.8141985375186955</v>
       </c>
-      <c r="W90" s="653" t="str">
+      <c r="W90" s="653">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="X90" s="653" t="str">
+        <v>15.515457993334097</v>
+      </c>
+      <c r="X90" s="653">
         <f t="shared" si="35"/>
-        <v/>
+        <v>9.6671896064518297</v>
       </c>
       <c r="Y90" s="653" t="str">
         <f t="shared" si="35"/>
@@ -27470,18 +27699,18 @@
       <c r="AG90" s="627"/>
       <c r="AH90" s="659">
         <f>IF(AH$9=0,"0",+(AH22*10)/AH$9)</f>
-        <v>11.12565732457047</v>
+        <v>11.211944280438946</v>
       </c>
       <c r="AI90" s="662">
         <v>10.199999999999999</v>
       </c>
       <c r="AJ90" s="665">
         <f>+AI90-AH90</f>
-        <v>-0.92565732457047112</v>
+        <v>-1.0119442804389465</v>
       </c>
       <c r="AK90" s="667">
         <f>AH90/AI90*100</f>
-        <v>109.07507180951441</v>
+        <v>109.92102235724457</v>
       </c>
       <c r="AL90" s="629"/>
       <c r="AM90" s="630"/>
@@ -27661,13 +27890,13 @@
         <f t="shared" si="37"/>
         <v>3.3782642478294651</v>
       </c>
-      <c r="W92" s="653" t="str">
+      <c r="W92" s="653">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="X92" s="653" t="str">
+        <v>3.8309772823047155</v>
+      </c>
+      <c r="X92" s="653">
         <f t="shared" si="37"/>
-        <v/>
+        <v>4.7976127079165405</v>
       </c>
       <c r="Y92" s="653" t="str">
         <f t="shared" si="37"/>
@@ -27704,18 +27933,18 @@
       <c r="AG92" s="628"/>
       <c r="AH92" s="670">
         <f>IF(AH$9=0,"0",+(AH74)/AH$9)</f>
-        <v>5.1299342137236428</v>
+        <v>5.0533158511064071</v>
       </c>
       <c r="AI92" s="674">
         <v>5</v>
       </c>
       <c r="AJ92" s="675">
         <f>AI92-AH92</f>
-        <v>-0.12993421372364278</v>
+        <v>-5.3315851106407131E-2</v>
       </c>
       <c r="AK92" s="673">
         <f t="shared" si="36"/>
-        <v>102.59868427447284</v>
+        <v>101.06631702212813</v>
       </c>
       <c r="AL92" s="629"/>
       <c r="AM92" s="630"/>
@@ -27830,13 +28059,13 @@
         <f t="shared" si="38"/>
         <v>0.54449941801719925</v>
       </c>
-      <c r="W93" s="653" t="str">
+      <c r="W93" s="653">
         <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="X93" s="653" t="str">
+        <v>0.66256752097458937</v>
+      </c>
+      <c r="X93" s="653">
         <f t="shared" si="38"/>
-        <v/>
+        <v>0.58960261373938783</v>
       </c>
       <c r="Y93" s="653" t="str">
         <f t="shared" si="38"/>
@@ -27873,18 +28102,18 @@
       <c r="AG93" s="628"/>
       <c r="AH93" s="670">
         <f>IF(AH$9=0,"0",+AH76/AH$9)</f>
-        <v>0.5868500742346493</v>
+        <v>0.59020483222766751</v>
       </c>
       <c r="AI93" s="674">
         <v>1.7</v>
       </c>
       <c r="AJ93" s="676">
         <f>AI93-AH93</f>
-        <v>1.1131499257653505</v>
+        <v>1.1097951677723326</v>
       </c>
       <c r="AK93" s="673">
         <f t="shared" si="36"/>
-        <v>34.520592602038199</v>
+        <v>34.717931307509851</v>
       </c>
       <c r="AL93" s="635"/>
       <c r="AM93" s="636"/>
@@ -27997,13 +28226,13 @@
         <f t="shared" si="39"/>
         <v>13.782703901280977</v>
       </c>
-      <c r="W94" s="653" t="str">
+      <c r="W94" s="653">
         <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="X94" s="653" t="str">
+        <v>33.324522085584029</v>
+      </c>
+      <c r="X94" s="653">
         <f>IF(X$9=0,"",(X80+X83)/X$9)</f>
-        <v/>
+        <v>20.856661725125576</v>
       </c>
       <c r="Y94" s="653" t="str">
         <f t="shared" si="39"/>
@@ -28040,18 +28269,18 @@
       <c r="AG94" s="627"/>
       <c r="AH94" s="670">
         <f>IF(AH$9=0,"0",+(AH80+AH83)/AH$9)</f>
-        <v>27.074460797114739</v>
+        <v>26.920361089737458</v>
       </c>
       <c r="AI94" s="674">
         <v>22</v>
       </c>
       <c r="AJ94" s="675">
         <f>AI94-AH94</f>
-        <v>-5.0744607971147389</v>
+        <v>-4.9203610897374581</v>
       </c>
       <c r="AK94" s="673">
         <f>AH94/AI94*100</f>
-        <v>123.06573089597607</v>
+        <v>122.36527768062481</v>
       </c>
       <c r="AL94" s="629"/>
       <c r="AM94" s="630"/>
@@ -28111,7 +28340,7 @@
       <c r="AG95" s="637"/>
       <c r="AH95" s="670">
         <f>IF(AH$9=0,"0",+(AH78*10)/AH$9)</f>
-        <v>24.822527675905032</v>
+        <v>24.861431662453526</v>
       </c>
       <c r="AI95" s="674"/>
       <c r="AJ95" s="676"/>
@@ -28230,13 +28459,13 @@
         <f t="shared" si="41"/>
         <v>5.6217388233198511</v>
       </c>
-      <c r="W96" s="654" t="str">
+      <c r="W96" s="654">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="X96" s="654" t="str">
+        <v>11.294487223690584</v>
+      </c>
+      <c r="X96" s="654">
         <f t="shared" si="41"/>
-        <v/>
+        <v>7.3681735968178881</v>
       </c>
       <c r="Y96" s="654" t="str">
         <f>IF(Y$9=0,"",Y84/Y$9)</f>
@@ -28273,18 +28502,18 @@
       <c r="AG96" s="627"/>
       <c r="AH96" s="660">
         <f>IF(AH$9=0,"0",+(AH84)/AH$9)</f>
-        <v>8.3475009516478131</v>
+        <v>8.405412868097148</v>
       </c>
       <c r="AI96" s="663">
         <v>7.2</v>
       </c>
       <c r="AJ96" s="677">
         <f>AI96-AH96</f>
-        <v>-1.147500951647813</v>
+        <v>-1.2054128680971479</v>
       </c>
       <c r="AK96" s="668">
         <f t="shared" si="36"/>
-        <v>115.93751321733075</v>
+        <v>116.74184539023817</v>
       </c>
       <c r="AL96" s="629"/>
       <c r="AM96" s="630"/>
@@ -28824,11 +29053,11 @@
       </c>
       <c r="W103" s="521">
         <f>IF('Entries October 2026'!L28-'Entries October 2026'!L27&lt;1,0,'Entries October 2026'!L28-'Entries October 2026'!L27)</f>
-        <v>0</v>
+        <v>352.2100000000064</v>
       </c>
       <c r="X103" s="521">
         <f>IF('Entries October 2026'!L29-'Entries October 2026'!L28&lt;1,0,'Entries October 2026'!L29-'Entries October 2026'!L28)</f>
-        <v>0</v>
+        <v>648.3799999999901</v>
       </c>
       <c r="Y103" s="521">
         <f>IF('Entries October 2026'!L30-'Entries October 2026'!L29&lt;1,0,'Entries October 2026'!L30-'Entries October 2026'!L29)</f>
@@ -28969,13 +29198,13 @@
         <f t="shared" si="43"/>
         <v>0</v>
       </c>
-      <c r="W105" s="652" t="str">
+      <c r="W105" s="652">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="X105" s="652" t="str">
+        <v>0</v>
+      </c>
+      <c r="X105" s="652">
         <f t="shared" si="43"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y105" s="652" t="str">
         <f t="shared" si="43"/>
@@ -29287,11 +29516,11 @@
       </c>
       <c r="W116" s="650">
         <f>'Daily KPIs'!W80</f>
-        <v>0</v>
+        <v>7284</v>
       </c>
       <c r="X116" s="650">
         <f>'Daily KPIs'!X80</f>
-        <v>0</v>
+        <v>7265</v>
       </c>
       <c r="Y116" s="650">
         <f>'Daily KPIs'!Y80</f>
@@ -29328,7 +29557,7 @@
       <c r="AG116" s="650"/>
       <c r="AH116" s="649">
         <f>'Daily KPIs'!AH80</f>
-        <v>123232</v>
+        <v>137781</v>
       </c>
     </row>
     <row r="117" spans="2:34" hidden="1" x14ac:dyDescent="0.35">
@@ -29418,7 +29647,7 @@
       </c>
       <c r="AH140" s="870">
         <f>AH83/(AH83+AH80)</f>
-        <v>0.18072327604317634</v>
+        <v>0.17894104543918704</v>
       </c>
       <c r="AM140" s="751"/>
     </row>
@@ -31376,11 +31605,11 @@
       </c>
       <c r="C28" s="55">
         <f t="shared" si="1"/>
-        <v>-256505</v>
+        <v>197</v>
       </c>
       <c r="D28" s="55">
         <f t="shared" si="2"/>
-        <v>1112382</v>
+        <v>-19</v>
       </c>
       <c r="E28" s="56">
         <f>'Entries October 2026'!W27</f>
@@ -31392,7 +31621,7 @@
       </c>
       <c r="G28" s="57">
         <f t="shared" si="7"/>
-        <v>-1368887</v>
+        <v>216</v>
       </c>
       <c r="H28" s="57">
         <f>'Entries October 2026'!AA27</f>
@@ -31400,7 +31629,7 @@
       </c>
       <c r="I28" s="58">
         <f t="shared" si="3"/>
-        <v>-97122</v>
+        <v>0</v>
       </c>
       <c r="J28" s="57">
         <f>'Entries October 2026'!T27</f>
@@ -31412,7 +31641,7 @@
       </c>
       <c r="L28" s="58">
         <f t="shared" si="6"/>
-        <v>-97122</v>
+        <v>0</v>
       </c>
       <c r="M28" s="57">
         <f>'Entries October 2026'!R27</f>
@@ -31420,11 +31649,11 @@
       </c>
       <c r="N28" s="57">
         <f>'Entries October 2026'!AC28-'Entries October 2026'!AC27</f>
-        <v>-7056</v>
+        <v>23</v>
       </c>
       <c r="O28" s="57">
         <f t="shared" si="5"/>
-        <v>-513010</v>
+        <v>394</v>
       </c>
       <c r="P28" s="62"/>
       <c r="Q28" s="45"/>
@@ -31439,15 +31668,15 @@
       </c>
       <c r="B29" s="55">
         <f>'Entries October 2026'!O28</f>
-        <v>0</v>
+        <v>256702</v>
       </c>
       <c r="C29" s="55">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="D29" s="55">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E29" s="56">
         <f>'Entries October 2026'!W28</f>
@@ -31455,15 +31684,15 @@
       </c>
       <c r="F29" s="57">
         <f>'Entries October 2026'!V28</f>
-        <v>0</v>
+        <v>1369103</v>
       </c>
       <c r="G29" s="57">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="H29" s="57">
         <f>'Entries October 2026'!AA28</f>
-        <v>0</v>
+        <v>97122</v>
       </c>
       <c r="I29" s="58">
         <f t="shared" si="3"/>
@@ -31487,11 +31716,11 @@
       </c>
       <c r="N29" s="57">
         <f>'Entries October 2026'!AC29-'Entries October 2026'!AC28</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O29" s="57">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="P29" s="62"/>
       <c r="Q29" s="45"/>
@@ -31506,15 +31735,15 @@
       </c>
       <c r="B30" s="55">
         <f>'Entries October 2026'!O29</f>
-        <v>0</v>
+        <v>256912</v>
       </c>
       <c r="C30" s="55">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-256912</v>
       </c>
       <c r="D30" s="55">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1112393</v>
       </c>
       <c r="E30" s="56">
         <f>'Entries October 2026'!W29</f>
@@ -31522,19 +31751,19 @@
       </c>
       <c r="F30" s="57">
         <f>'Entries October 2026'!V29</f>
-        <v>0</v>
+        <v>1369305</v>
       </c>
       <c r="G30" s="57">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-1369305</v>
       </c>
       <c r="H30" s="57">
         <f>'Entries October 2026'!AA29</f>
-        <v>0</v>
+        <v>97122</v>
       </c>
       <c r="I30" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-97122</v>
       </c>
       <c r="J30" s="57">
         <f>'Entries October 2026'!T29</f>
@@ -31546,7 +31775,7 @@
       </c>
       <c r="L30" s="58">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-97122</v>
       </c>
       <c r="M30" s="57">
         <f>'Entries October 2026'!R29</f>
@@ -31554,11 +31783,11 @@
       </c>
       <c r="N30" s="57">
         <f>'Entries October 2026'!AC30-'Entries October 2026'!AC29</f>
-        <v>0</v>
+        <v>-7099</v>
       </c>
       <c r="O30" s="57">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-513824</v>
       </c>
       <c r="P30" s="62"/>
       <c r="Q30" s="45"/>
@@ -33830,9 +34059,9 @@
       <c r="A31" s="719">
         <v>22</v>
       </c>
-      <c r="B31" s="719" t="str">
+      <c r="B31" s="719">
         <f>IF('Entries October 2026'!I28&lt;'Entries October 2026'!I27,"0",(IF('Entries October 2026'!I28&gt;='Entries October 2026'!I27,'Entries October 2026'!I28-'Entries October 2026'!I27,(999999-'Entries October 2026'!I27)+'Entries October 2026'!I28+1)))</f>
-        <v>0</v>
+        <v>7284</v>
       </c>
       <c r="C31" s="719" t="str">
         <f>IF('Entries October 2026'!J28&lt;='Entries October 2026'!J27,"0",IF('Entries October 2026'!J28&gt;='Entries October 2026'!J27,'Entries October 2026'!J28-'Entries October 2026'!J27,(999999-'Entries October 2026'!J27)+'Entries October 2026'!J28+1))</f>
@@ -33840,24 +34069,26 @@
       </c>
       <c r="D31" s="720">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E31" s="873"/>
-      <c r="F31" s="721" t="str">
+        <v>7284</v>
+      </c>
+      <c r="E31" s="873">
+        <v>1414.7</v>
+      </c>
+      <c r="F31" s="721">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G31" s="737" t="str">
+        <v>0.16263349695931575</v>
+      </c>
+      <c r="G31" s="737">
         <f>IF('Entries October 2026'!K28&lt;'Entries October 2026'!K27,"0",IF('Entries October 2026'!K28&gt;='Entries October 2026'!K27,'Entries October 2026'!K28-'Entries October 2026'!K27,(999999-'Entries October 2026'!K27)+'Entries October 2026'!K28+1))</f>
         <v>0</v>
       </c>
       <c r="H31" s="720">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8698.7000000000007</v>
       </c>
       <c r="I31" s="737">
         <f>'Water '!Z28*10</f>
-        <v>0</v>
+        <v>4050</v>
       </c>
       <c r="J31" s="720" t="str">
         <f>IF('Entries October 2026'!B28-'Entries October 2026'!B27&lt;1,"0",'Entries October 2026'!B28-'Entries October 2026'!B27)</f>
@@ -33865,7 +34096,7 @@
       </c>
       <c r="K31" s="722">
         <f>'CO2'!E28</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L31" s="723">
         <f>+'PROD.FIG. '!F26</f>
@@ -33884,15 +34115,15 @@
         <v>0</v>
       </c>
       <c r="P31" s="724">
-        <v>0</v>
+        <v>261.03000000000003</v>
       </c>
       <c r="Q31" s="393">
         <f>IF(P31=0,0,H31/P31)</f>
-        <v>0</v>
+        <v>33.324522085584029</v>
       </c>
       <c r="R31" s="393">
         <f>IF(Q31=0,0,I31/P31)</f>
-        <v>0</v>
+        <v>15.515457993334097</v>
       </c>
       <c r="S31" s="393">
         <f>IF(R31=0,0,J31/P31)</f>
@@ -33909,7 +34140,7 @@
       </c>
       <c r="B32" s="719">
         <f>IF('Entries October 2026'!I29&lt;'Entries October 2026'!I28,"0",(IF('Entries October 2026'!I29&gt;='Entries October 2026'!I28,'Entries October 2026'!I29-'Entries October 2026'!I28,(999999-'Entries October 2026'!I28)+'Entries October 2026'!I29+1)))</f>
-        <v>0</v>
+        <v>7265</v>
       </c>
       <c r="C32" s="719" t="str">
         <f>IF('Entries October 2026'!J29&lt;='Entries October 2026'!J28,"0",IF('Entries October 2026'!J29&gt;='Entries October 2026'!J28,'Entries October 2026'!J29-'Entries October 2026'!J28,(999999-'Entries October 2026'!J28)+'Entries October 2026'!J29+1))</f>
@@ -33917,12 +34148,14 @@
       </c>
       <c r="D32" s="720">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E32" s="873"/>
-      <c r="F32" s="721" t="str">
+        <v>7265</v>
+      </c>
+      <c r="E32" s="873">
+        <v>1429.6</v>
+      </c>
+      <c r="F32" s="721">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.16442389529133022</v>
       </c>
       <c r="G32" s="737">
         <f>IF('Entries October 2026'!K29&lt;'Entries October 2026'!K28,"0",IF('Entries October 2026'!K29&gt;='Entries October 2026'!K28,'Entries October 2026'!K29-'Entries October 2026'!K28,(999999-'Entries October 2026'!K28)+'Entries October 2026'!K29+1))</f>
@@ -33930,11 +34163,11 @@
       </c>
       <c r="H32" s="720">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8694.6</v>
       </c>
       <c r="I32" s="737">
         <f>'Water '!Z29*10</f>
-        <v>0</v>
+        <v>4030</v>
       </c>
       <c r="J32" s="720" t="str">
         <f>IF('Entries October 2026'!B29-'Entries October 2026'!B28&lt;1,"0",'Entries October 2026'!B29-'Entries October 2026'!B28)</f>
@@ -33942,7 +34175,7 @@
       </c>
       <c r="K32" s="722">
         <f>'CO2'!E29</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="L32" s="723">
         <f>+'PROD.FIG. '!F27</f>
@@ -33961,15 +34194,15 @@
         <v>0</v>
       </c>
       <c r="P32" s="724">
-        <v>0</v>
+        <v>416.87400000000002</v>
       </c>
       <c r="Q32" s="393">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>20.856661725125576</v>
       </c>
       <c r="R32" s="393">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9.6671896064518297</v>
       </c>
       <c r="S32" s="393">
         <f t="shared" si="5"/>
@@ -33984,7 +34217,7 @@
       <c r="A33" s="771">
         <v>24</v>
       </c>
-      <c r="B33" s="771">
+      <c r="B33" s="771" t="str">
         <f>IF('Entries October 2026'!I30&lt;'Entries October 2026'!I29,"0",(IF('Entries October 2026'!I30&gt;='Entries October 2026'!I29,'Entries October 2026'!I30-'Entries October 2026'!I29,(999999-'Entries October 2026'!I29)+'Entries October 2026'!I30+1)))</f>
         <v>0</v>
       </c>
@@ -34001,7 +34234,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G33" s="774">
+      <c r="G33" s="774" t="str">
         <f>IF('Entries October 2026'!K30&lt;'Entries October 2026'!K29,"0",IF('Entries October 2026'!K30&gt;='Entries October 2026'!K29,'Entries October 2026'!K30-'Entries October 2026'!K29,(999999-'Entries October 2026'!K29)+'Entries October 2026'!K30+1))</f>
         <v>0</v>
       </c>
@@ -34535,7 +34768,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E40" s="889"/>
+      <c r="E40" s="888"/>
       <c r="F40" s="773" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -34560,11 +34793,11 @@
         <f>'CO2'!E37</f>
         <v>0</v>
       </c>
-      <c r="L40" s="890"/>
-      <c r="M40" s="891"/>
-      <c r="N40" s="891"/>
-      <c r="O40" s="891"/>
-      <c r="P40" s="892">
+      <c r="L40" s="889"/>
+      <c r="M40" s="890"/>
+      <c r="N40" s="890"/>
+      <c r="O40" s="890"/>
+      <c r="P40" s="891">
         <v>0</v>
       </c>
       <c r="Q40" s="394">
@@ -34671,15 +34904,15 @@
       <c r="C43" s="19"/>
       <c r="D43" s="20">
         <f>SUM(D10:D40)</f>
-        <v>123232</v>
+        <v>137781</v>
       </c>
       <c r="E43" s="741">
         <f>SUM(E10:E40)</f>
-        <v>27183.599999999995</v>
+        <v>30027.899999999994</v>
       </c>
       <c r="F43" s="754">
         <f>IF((E43+D43)=0,"0",E43/(D43+E43))</f>
-        <v>0.18072327604317634</v>
+        <v>0.17894104543918704</v>
       </c>
       <c r="G43" s="20">
         <f t="shared" ref="G43:P43" si="7">SUM(G10:G40)</f>
@@ -34687,11 +34920,11 @@
       </c>
       <c r="H43" s="20">
         <f t="shared" si="7"/>
-        <v>150415.59999999998</v>
+        <v>167808.9</v>
       </c>
       <c r="I43" s="20">
         <f t="shared" si="7"/>
-        <v>61810</v>
+        <v>69890</v>
       </c>
       <c r="J43" s="20">
         <f t="shared" si="7"/>
@@ -34699,7 +34932,7 @@
       </c>
       <c r="K43" s="20">
         <f t="shared" si="7"/>
-        <v>28500</v>
+        <v>31500</v>
       </c>
       <c r="L43" s="20">
         <f t="shared" si="7"/>
@@ -34719,7 +34952,7 @@
       </c>
       <c r="P43" s="403">
         <f t="shared" si="7"/>
-        <v>5555.6268</v>
+        <v>6233.5307999999995</v>
       </c>
       <c r="Q43" s="408" t="s">
         <v>13</v>
@@ -34747,7 +34980,7 @@
       </c>
       <c r="E44" s="728">
         <f>D43+E43</f>
-        <v>150415.6</v>
+        <v>167808.9</v>
       </c>
       <c r="F44" s="708"/>
       <c r="G44" s="7"/>
@@ -34762,19 +34995,19 @@
       <c r="P44" s="401"/>
       <c r="Q44" s="397">
         <f>IF(P43=0,0,H43/P43)</f>
-        <v>27.074460797114735</v>
+        <v>26.920361089737458</v>
       </c>
       <c r="R44" s="398">
         <f>IF(Q44=0,0,I43/P43)</f>
-        <v>11.12565732457047</v>
+        <v>11.211944280438946</v>
       </c>
       <c r="S44" s="398">
         <f>IF(R44=0,0,J43/P43)</f>
-        <v>0.17279778404121746</v>
+        <v>0.15400581641467145</v>
       </c>
       <c r="T44" s="399">
         <f>IF(S44=0,0,K43/P43)</f>
-        <v>5.1299342137236428</v>
+        <v>5.0533158511064071</v>
       </c>
     </row>
     <row r="45" spans="1:32" ht="15" x14ac:dyDescent="0.2">
@@ -35152,9 +35385,9 @@
       <c r="A27" s="36">
         <v>23</v>
       </c>
-      <c r="B27" s="44" t="str">
+      <c r="B27" s="44">
         <f>IF('Entries October 2026'!AJ29-'Entries October 2026'!AJ28&lt;1,"0",'Entries October 2026'!AJ29-'Entries October 2026'!AJ28)</f>
-        <v>0</v>
+        <v>3.5339999999850988</v>
       </c>
       <c r="D27" s="343"/>
     </row>
@@ -35239,7 +35472,7 @@
       <c r="A36" s="41"/>
       <c r="B36" s="352">
         <f>SUM(B5:B35)</f>
-        <v>116.67799999937415</v>
+        <v>120.21199999935925</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -36598,13 +36831,13 @@
         <f>IF('Entries October 2026'!B28-'Entries October 2026'!B27&lt;1,"0",'Entries October 2026'!B28-'Entries October 2026'!B27)</f>
         <v>0</v>
       </c>
-      <c r="C28" s="739" t="str">
+      <c r="C28" s="739">
         <f>IF('Entries October 2026'!F28-'Entries October 2026'!F27&lt;1,"0",'Entries October 2026'!F28-'Entries October 2026'!F27)</f>
-        <v>0</v>
-      </c>
-      <c r="D28" s="839" t="str">
+        <v>21.899999999999636</v>
+      </c>
+      <c r="D28" s="839">
         <f>IF('Entries October 2026'!C28-'Entries October 2026'!C27&lt;1,"0",'Entries October 2026'!C28-'Entries October 2026'!C27)</f>
-        <v>0</v>
+        <v>2948.1999999999534</v>
       </c>
       <c r="E28" s="843" t="str">
         <f t="shared" si="0"/>
@@ -36616,7 +36849,7 @@
       </c>
       <c r="G28" s="837"/>
       <c r="H28" s="739"/>
-      <c r="I28" s="740" t="str">
+      <c r="I28" s="740">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -36628,20 +36861,20 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L28" s="831" t="str">
-        <v>0</v>
-      </c>
-      <c r="M28" s="829" t="str">
+      <c r="L28" s="831">
+        <v>261.03000000000003</v>
+      </c>
+      <c r="M28" s="829">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N28" s="829" t="str">
+      <c r="N28" s="829">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11.294487223690584</v>
       </c>
       <c r="O28" s="830">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-2948.1999999999534</v>
       </c>
       <c r="P28" s="333"/>
     </row>
@@ -36653,13 +36886,13 @@
         <f>IF('Entries October 2026'!B29-'Entries October 2026'!B28&lt;1,"0",'Entries October 2026'!B29-'Entries October 2026'!B28)</f>
         <v>0</v>
       </c>
-      <c r="C29" s="739" t="str">
+      <c r="C29" s="739">
         <f>IF('Entries October 2026'!F29-'Entries October 2026'!F28&lt;1,"0",'Entries October 2026'!F29-'Entries October 2026'!F28)</f>
-        <v>0</v>
-      </c>
-      <c r="D29" s="839" t="str">
+        <v>21.400000000001455</v>
+      </c>
+      <c r="D29" s="839">
         <f>IF('Entries October 2026'!C29-'Entries October 2026'!C28&lt;1,"0",'Entries October 2026'!C29-'Entries October 2026'!C28)</f>
-        <v>0</v>
+        <v>3071.5999999998603</v>
       </c>
       <c r="E29" s="843" t="str">
         <f t="shared" si="0"/>
@@ -36671,7 +36904,7 @@
       </c>
       <c r="G29" s="837"/>
       <c r="H29" s="739"/>
-      <c r="I29" s="740" t="str">
+      <c r="I29" s="740">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -36683,20 +36916,20 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L29" s="831" t="str">
-        <v>0</v>
-      </c>
-      <c r="M29" s="829" t="str">
+      <c r="L29" s="831">
+        <v>416.87400000000002</v>
+      </c>
+      <c r="M29" s="829">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N29" s="829" t="str">
+      <c r="N29" s="829">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.3681735968178881</v>
       </c>
       <c r="O29" s="830">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-3071.5999999998603</v>
       </c>
       <c r="P29" s="333"/>
     </row>
@@ -37145,11 +37378,11 @@
       </c>
       <c r="C38" s="388">
         <f>SUM(C7:C37)</f>
-        <v>312.10000000000036</v>
+        <v>355.40000000000146</v>
       </c>
       <c r="D38" s="840">
         <f t="shared" si="7"/>
-        <v>46375.600000000093</v>
+        <v>52395.399999999907</v>
       </c>
       <c r="E38" s="845"/>
       <c r="F38" s="846">
@@ -37166,7 +37399,7 @@
       </c>
       <c r="I38" s="797">
         <f>B38/C38</f>
-        <v>3.0759371996155043</v>
+        <v>2.7011817670230616</v>
       </c>
       <c r="J38" s="355"/>
       <c r="K38" s="356">
@@ -37175,15 +37408,15 @@
       </c>
       <c r="L38" s="828">
         <f>SUM(L7:L37)</f>
-        <v>5555.6268</v>
+        <v>6233.5307999999995</v>
       </c>
       <c r="M38" s="834">
         <f>IF(L38=0,"0",(K38/L38))</f>
-        <v>0.17279778404121746</v>
+        <v>0.15400581641467145</v>
       </c>
       <c r="N38" s="834">
         <f>IF(L38=0,"0",(D38/L38))</f>
-        <v>8.3475009516478131</v>
+        <v>8.405412868097148</v>
       </c>
       <c r="O38" s="835"/>
     </row>
@@ -37197,7 +37430,7 @@
       </c>
       <c r="C39" s="802">
         <f>AVERAGE(C7:C37)</f>
-        <v>15.605000000000018</v>
+        <v>16.15454545454552</v>
       </c>
       <c r="D39" s="30"/>
       <c r="E39" s="30"/>
@@ -40345,33 +40578,33 @@
         <f>IF('Entries October 2026'!W28-'Entries October 2026'!W27&lt;1,"0",'Entries October 2026'!W28-'Entries October 2026'!W27)</f>
         <v>0</v>
       </c>
-      <c r="D28" s="693" t="str">
+      <c r="D28" s="693">
         <f>IF('Entries October 2026'!O28-'Entries October 2026'!O27&lt;1,"0",'Entries October 2026'!O28-'Entries October 2026'!O27)</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="693" t="str">
+        <v>197</v>
+      </c>
+      <c r="E28" s="693">
         <f>IF('Entries October 2026'!P28-'Entries October 2026'!P27&lt;1,"0",'Entries October 2026'!P28-'Entries October 2026'!P27)</f>
-        <v>0</v>
-      </c>
-      <c r="F28" s="693" t="str">
+        <v>208</v>
+      </c>
+      <c r="F28" s="693">
         <f>IF('Entries October 2026'!V28-'Entries October 2026'!V27&lt;1,"0",'Entries October 2026'!V28-'Entries October 2026'!V27)</f>
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="G28" s="693">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="H28" s="693">
         <f>IF('Entries October 2026'!Q28-'Entries October 2026'!Q27&lt;1,0,'Entries October 2026'!Q28-'Entries October 2026'!Q27)</f>
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="I28" s="693">
         <f>IF('Entries October 2026'!AG28-'Entries October 2026'!AG27&lt;1,0,'Entries October 2026'!AG28-'Entries October 2026'!AG27)</f>
         <v>0</v>
       </c>
-      <c r="J28" s="693" t="str">
+      <c r="J28" s="693">
         <f>IF('Entries October 2026'!S28-'Entries October 2026'!S27&lt;1,"0",'Entries October 2026'!S28-'Entries October 2026'!S27)</f>
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="K28" s="693" t="str">
         <f>IF('Entries October 2026'!R28-'Entries October 2026'!R27&lt;1,"0",'Entries October 2026'!R28-'Entries October 2026'!R27)</f>
@@ -40381,25 +40614,25 @@
         <f>IF('Entries October 2026'!T28-'Entries October 2026'!T27&lt;1,"0",'Entries October 2026'!T28-'Entries October 2026'!T27)</f>
         <v>0</v>
       </c>
-      <c r="M28" s="693" t="str">
+      <c r="M28" s="693">
         <f>IF('Entries October 2026'!U28-'Entries October 2026'!U27&lt;1,"0",'Entries October 2026'!U28-'Entries October 2026'!U27)</f>
-        <v>0</v>
-      </c>
-      <c r="N28" s="693" t="str">
+        <v>3</v>
+      </c>
+      <c r="N28" s="693">
         <f>IF('Entries October 2026'!X28-'Entries October 2026'!X27&lt;1,"0",'Entries October 2026'!X28-'Entries October 2026'!X27)</f>
-        <v>0</v>
-      </c>
-      <c r="O28" s="693" t="str">
+        <v>26</v>
+      </c>
+      <c r="O28" s="693">
         <f>IF('Entries October 2026'!Y28-'Entries October 2026'!Y27&lt;1,"0",'Entries October 2026'!Y28-'Entries October 2026'!Y27)</f>
-        <v>0</v>
-      </c>
-      <c r="P28" s="693" t="str">
+        <v>94</v>
+      </c>
+      <c r="P28" s="693">
         <f>IF('Entries October 2026'!AC28-'Entries October 2026'!AC27&lt;1,"0",'Entries October 2026'!AC28-'Entries October 2026'!AC27)</f>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="693" t="str">
+        <v>23</v>
+      </c>
+      <c r="Q28" s="693">
         <f>IF('Entries October 2026'!Z28-'Entries October 2026'!Z27&lt;1,"0",'Entries October 2026'!Z28-'Entries October 2026'!Z27)</f>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="R28" s="693" t="str">
         <f>IF(('Entries October 2026'!AA28-'Entries October 2026'!AA27)+('Entries October 2026'!AB28-'Entries October 2026'!AB27)&lt;1,"0",('Entries October 2026'!AA28-'Entries October 2026'!AA27)+('Entries October 2026'!AB28-'Entries October 2026'!AB27))</f>
@@ -40407,15 +40640,15 @@
       </c>
       <c r="S28" s="692">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1890</v>
       </c>
       <c r="T28" s="692">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U28" s="693" t="str">
+        <v>123</v>
+      </c>
+      <c r="U28" s="693">
         <f>IF('Entries October 2026'!AC28-'Entries October 2026'!AC27&lt;1,"0",'Entries October 2026'!AC28-'Entries October 2026'!AC27)</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V28" s="693" t="str">
         <f>IF('Entries October 2026'!AD28-'Entries October 2026'!AD27&lt;1,"0",'Entries October 2026'!AD28-'Entries October 2026'!AD27)</f>
@@ -40435,14 +40668,14 @@
       </c>
       <c r="Z28" s="329">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AA28" s="330" t="str">
-        <v>0</v>
-      </c>
-      <c r="AB28" s="331" t="str">
+        <v>405</v>
+      </c>
+      <c r="AA28" s="330">
+        <v>261.03000000000003</v>
+      </c>
+      <c r="AB28" s="331">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>15.515457993334097</v>
       </c>
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.2">
@@ -40453,33 +40686,33 @@
         <f>IF('Entries October 2026'!W29-'Entries October 2026'!W28&lt;1,"0",'Entries October 2026'!W29-'Entries October 2026'!W28)</f>
         <v>0</v>
       </c>
-      <c r="D29" s="693" t="str">
+      <c r="D29" s="693">
         <f>IF('Entries October 2026'!O29-'Entries October 2026'!O28&lt;1,"0",'Entries October 2026'!O29-'Entries October 2026'!O28)</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="693" t="str">
+        <v>210</v>
+      </c>
+      <c r="E29" s="693">
         <f>IF('Entries October 2026'!P29-'Entries October 2026'!P28&lt;1,"0",'Entries October 2026'!P29-'Entries October 2026'!P28)</f>
-        <v>0</v>
-      </c>
-      <c r="F29" s="693" t="str">
+        <v>193</v>
+      </c>
+      <c r="F29" s="693">
         <f>IF('Entries October 2026'!V29-'Entries October 2026'!V28&lt;1,"0",'Entries October 2026'!V29-'Entries October 2026'!V28)</f>
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="G29" s="693">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="H29" s="693">
         <f>IF('Entries October 2026'!Q29-'Entries October 2026'!Q28&lt;1,0,'Entries October 2026'!Q29-'Entries October 2026'!Q28)</f>
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="I29" s="693">
         <f>IF('Entries October 2026'!AG29-'Entries October 2026'!AG28&lt;1,0,'Entries October 2026'!AG29-'Entries October 2026'!AG28)</f>
         <v>0</v>
       </c>
-      <c r="J29" s="693" t="str">
+      <c r="J29" s="693">
         <f>IF('Entries October 2026'!S29-'Entries October 2026'!S28&lt;1,"0",'Entries October 2026'!S29-'Entries October 2026'!S28)</f>
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="K29" s="693" t="str">
         <f>IF('Entries October 2026'!R29-'Entries October 2026'!R28&lt;1,"0",'Entries October 2026'!R29-'Entries October 2026'!R28)</f>
@@ -40489,25 +40722,25 @@
         <f>IF('Entries October 2026'!T29-'Entries October 2026'!T28&lt;1,"0",'Entries October 2026'!T29-'Entries October 2026'!T28)</f>
         <v>0</v>
       </c>
-      <c r="M29" s="693" t="str">
+      <c r="M29" s="693">
         <f>IF('Entries October 2026'!U29-'Entries October 2026'!U28&lt;1,"0",'Entries October 2026'!U29-'Entries October 2026'!U28)</f>
-        <v>0</v>
-      </c>
-      <c r="N29" s="693" t="str">
+        <v>4</v>
+      </c>
+      <c r="N29" s="693">
         <f>IF('Entries October 2026'!X29-'Entries October 2026'!X28&lt;1,"0",'Entries October 2026'!X29-'Entries October 2026'!X28)</f>
-        <v>0</v>
-      </c>
-      <c r="O29" s="693" t="str">
+        <v>41</v>
+      </c>
+      <c r="O29" s="693">
         <f>IF('Entries October 2026'!Y29-'Entries October 2026'!Y28&lt;1,"0",'Entries October 2026'!Y29-'Entries October 2026'!Y28)</f>
-        <v>0</v>
-      </c>
-      <c r="P29" s="693" t="str">
+        <v>112</v>
+      </c>
+      <c r="P29" s="693">
         <f>IF('Entries October 2026'!AC29-'Entries October 2026'!AC28&lt;1,"0",'Entries October 2026'!AC29-'Entries October 2026'!AC28)</f>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="693" t="str">
+        <v>20</v>
+      </c>
+      <c r="Q29" s="693">
         <f>IF('Entries October 2026'!Z29-'Entries October 2026'!Z28&lt;1,"0",'Entries October 2026'!Z29-'Entries October 2026'!Z28)</f>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="R29" s="693" t="str">
         <f>IF(('Entries October 2026'!AA29-'Entries October 2026'!AA28)+('Entries October 2026'!AB29-'Entries October 2026'!AB28)&lt;1,"0",('Entries October 2026'!AA29-'Entries October 2026'!AA28)+('Entries October 2026'!AB29-'Entries October 2026'!AB28))</f>
@@ -40515,15 +40748,15 @@
       </c>
       <c r="S29" s="692">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2010</v>
       </c>
       <c r="T29" s="692">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U29" s="693" t="str">
+        <v>157</v>
+      </c>
+      <c r="U29" s="693">
         <f>IF('Entries October 2026'!AC29-'Entries October 2026'!AC28&lt;1,"0",'Entries October 2026'!AC29-'Entries October 2026'!AC28)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V29" s="693" t="str">
         <f>IF('Entries October 2026'!AD29-'Entries October 2026'!AD28&lt;1,"0",'Entries October 2026'!AD29-'Entries October 2026'!AD28)</f>
@@ -40543,14 +40776,14 @@
       </c>
       <c r="Z29" s="329">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AA29" s="330" t="str">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="331" t="str">
+        <v>403</v>
+      </c>
+      <c r="AA29" s="330">
+        <v>416.87400000000002</v>
+      </c>
+      <c r="AB29" s="331">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.6671896064518297</v>
       </c>
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.2">
@@ -41425,28 +41658,28 @@
       </c>
       <c r="D38" s="303">
         <f>SUM(D7:D37)</f>
-        <v>3511</v>
+        <v>3918</v>
       </c>
       <c r="E38" s="303">
         <f>SUM(E7:E37)</f>
-        <v>2670</v>
+        <v>3071</v>
       </c>
       <c r="F38" s="303">
         <f>SUM(F7:F37)</f>
-        <v>2851</v>
+        <v>3269</v>
       </c>
       <c r="G38" s="304">
         <f>SUM(G7:G37)</f>
-        <v>3330</v>
+        <v>3720</v>
       </c>
       <c r="H38" s="303">
         <f t="shared" si="5"/>
-        <v>3388</v>
+        <v>3829</v>
       </c>
       <c r="I38" s="303"/>
       <c r="J38" s="303">
         <f t="shared" si="5"/>
-        <v>2638</v>
+        <v>3033</v>
       </c>
       <c r="K38" s="303"/>
       <c r="L38" s="303">
@@ -41455,23 +41688,23 @@
       </c>
       <c r="M38" s="303">
         <f>SUM(M7:M37)</f>
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="N38" s="303">
         <f t="shared" si="5"/>
-        <v>543</v>
+        <v>610</v>
       </c>
       <c r="O38" s="303">
         <f t="shared" si="5"/>
-        <v>1498</v>
+        <v>1704</v>
       </c>
       <c r="P38" s="303">
         <f>SUM(P7:P37)</f>
-        <v>306</v>
+        <v>349</v>
       </c>
       <c r="Q38" s="303">
         <f>SUM(Q7:Q37)</f>
-        <v>392</v>
+        <v>447</v>
       </c>
       <c r="R38" s="303">
         <f>SUM(R7:R34)</f>
@@ -41479,15 +41712,15 @@
       </c>
       <c r="S38" s="304">
         <f>SUM(S7:S37)</f>
-        <v>33300</v>
+        <v>37200</v>
       </c>
       <c r="T38" s="304">
         <f>SUM(T7:T37)</f>
-        <v>2094</v>
+        <v>2374</v>
       </c>
       <c r="U38" s="303">
         <f>SUM(U7:U37)</f>
-        <v>306</v>
+        <v>349</v>
       </c>
       <c r="V38" s="303">
         <f>SUM(V7:V37)</f>
@@ -41498,22 +41731,22 @@
       <c r="Y38" s="303"/>
       <c r="Z38" s="332">
         <f>SUM(Z7:Z37)</f>
-        <v>6181</v>
+        <v>6989</v>
       </c>
       <c r="AA38" s="332">
         <f>SUM(AA7:AA37)</f>
-        <v>5555.6268</v>
+        <v>6233.5307999999995</v>
       </c>
       <c r="AB38" s="331">
         <f>IF(AA38=0,"0",(Z38*10/AA38))</f>
-        <v>11.12565732457047</v>
+        <v>11.211944280438946</v>
       </c>
       <c r="AC38" s="321">
         <v>10.199999999999999</v>
       </c>
       <c r="AD38" s="340">
         <f>AB38/AC38*100</f>
-        <v>109.07507180951441</v>
+        <v>109.92102235724457</v>
       </c>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.2">
@@ -41552,7 +41785,7 @@
       <c r="C40" s="15"/>
       <c r="D40" s="15">
         <f>D38*220</f>
-        <v>772420</v>
+        <v>861960</v>
       </c>
       <c r="E40" s="15"/>
       <c r="F40" s="15"/>
@@ -41644,7 +41877,7 @@
       <c r="C43" s="17"/>
       <c r="D43" s="17">
         <f>+D41*D40</f>
-        <v>12211.960200000001</v>
+        <v>13627.587600000001</v>
       </c>
       <c r="E43" s="17"/>
       <c r="F43" s="36"/>
@@ -41697,7 +41930,7 @@
     <row r="45" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D45" s="17">
         <f>SUM(D43:D44)</f>
-        <v>12490.930200000001</v>
+        <v>13906.5576</v>
       </c>
       <c r="E45" s="17"/>
       <c r="F45" s="36"/>
@@ -41719,7 +41952,7 @@
       </c>
       <c r="D47" s="23">
         <f>+D45*2/3</f>
-        <v>8327.2867999999999</v>
+        <v>9271.0383999999995</v>
       </c>
       <c r="E47" s="324"/>
       <c r="F47" s="36"/>
@@ -41742,7 +41975,7 @@
       <c r="C49" s="24"/>
       <c r="D49" s="28">
         <f>SUM(D47,D45)</f>
-        <v>20818.217000000001</v>
+        <v>23177.595999999998</v>
       </c>
       <c r="E49" s="325"/>
       <c r="F49" s="36"/>
@@ -42870,27 +43103,27 @@
       </c>
       <c r="B28" s="742">
         <f>'Utility Analysis October 2026'!D31</f>
-        <v>0</v>
-      </c>
-      <c r="C28" s="743" t="str">
+        <v>7284</v>
+      </c>
+      <c r="C28" s="743">
         <f>'Utility Analysis October 2026'!G31</f>
         <v>0</v>
       </c>
       <c r="D28" s="744">
         <f>'Utility Analysis October 2026'!E31</f>
-        <v>0</v>
+        <v>1414.7</v>
       </c>
       <c r="E28" s="745">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F28" s="746" t="str">
+        <v>8698.7000000000007</v>
+      </c>
+      <c r="F28" s="746">
         <f>'PROD.FIG. '!H26</f>
-        <v>0</v>
-      </c>
-      <c r="G28" s="336" t="str">
+        <v>261.03000000000003</v>
+      </c>
+      <c r="G28" s="336">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>33.324522085584029</v>
       </c>
       <c r="J28" s="30"/>
     </row>
@@ -42900,7 +43133,7 @@
       </c>
       <c r="B29" s="742">
         <f>'Utility Analysis October 2026'!D32</f>
-        <v>0</v>
+        <v>7265</v>
       </c>
       <c r="C29" s="743">
         <f>'Utility Analysis October 2026'!G32</f>
@@ -42908,19 +43141,19 @@
       </c>
       <c r="D29" s="744">
         <f>'Utility Analysis October 2026'!E32</f>
-        <v>0</v>
+        <v>1429.6</v>
       </c>
       <c r="E29" s="745">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F29" s="746" t="str">
+        <v>8694.6</v>
+      </c>
+      <c r="F29" s="746">
         <f>'PROD.FIG. '!H27</f>
-        <v>0</v>
-      </c>
-      <c r="G29" s="336" t="str">
+        <v>416.87400000000002</v>
+      </c>
+      <c r="G29" s="336">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>20.856661725125576</v>
       </c>
       <c r="J29" s="30"/>
     </row>
@@ -42932,7 +43165,7 @@
         <f>'Utility Analysis October 2026'!D33</f>
         <v>0</v>
       </c>
-      <c r="C30" s="743">
+      <c r="C30" s="743" t="str">
         <f>'Utility Analysis October 2026'!G33</f>
         <v>0</v>
       </c>
@@ -43167,7 +43400,7 @@
       </c>
       <c r="B38" s="308">
         <f>SUM(B7:B37)</f>
-        <v>123232</v>
+        <v>137781</v>
       </c>
       <c r="C38" s="308">
         <f>SUM(C7:C37)</f>
@@ -43175,26 +43408,26 @@
       </c>
       <c r="D38" s="308">
         <f>SUM(D7:D37)</f>
-        <v>27183.599999999995</v>
+        <v>30027.899999999994</v>
       </c>
       <c r="E38" s="337">
         <f>SUM(E7:E37)</f>
-        <v>150415.59999999998</v>
+        <v>167808.9</v>
       </c>
       <c r="F38" s="358">
         <f>SUM(F7:F37)</f>
-        <v>5555.6268</v>
+        <v>6233.5307999999995</v>
       </c>
       <c r="G38" s="338">
         <f>IF(F38=0,"0",(E38/F38))</f>
-        <v>27.074460797114735</v>
+        <v>26.920361089737458</v>
       </c>
       <c r="H38" s="335">
         <v>22</v>
       </c>
       <c r="I38" s="340">
         <f>G38/H38*100</f>
-        <v>123.06573089597607</v>
+        <v>122.36527768062481</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
@@ -43712,8 +43945,8 @@
       <c r="E26" s="686"/>
       <c r="F26" s="686"/>
       <c r="G26" s="686"/>
-      <c r="H26" s="689" t="str">
-        <v>0</v>
+      <c r="H26" s="689">
+        <v>261.03000000000003</v>
       </c>
       <c r="I26" s="298"/>
       <c r="J26" s="299"/>
@@ -43733,8 +43966,8 @@
       <c r="E27" s="690"/>
       <c r="F27" s="686"/>
       <c r="G27" s="686"/>
-      <c r="H27" s="689" t="str">
-        <v>0</v>
+      <c r="H27" s="689">
+        <v>416.87400000000002</v>
       </c>
       <c r="I27" s="298"/>
       <c r="J27" s="299"/>
@@ -43893,7 +44126,7 @@
       </c>
       <c r="H36" s="736">
         <f>SUM(H5:H35)</f>
-        <v>5555.6268</v>
+        <v>6233.5307999999995</v>
       </c>
       <c r="I36" s="298"/>
       <c r="J36" s="299"/>
@@ -45699,27 +45932,27 @@
       <c r="A28" s="715">
         <v>22</v>
       </c>
-      <c r="B28" s="716" t="str">
+      <c r="B28" s="716">
         <f>IF('Entries October 2026'!N28-'Entries October 2026'!N27&lt;1,"0",'Entries October 2026'!N28-'Entries October 2026'!N27)</f>
-        <v>0</v>
-      </c>
-      <c r="C28" s="716" t="str">
+        <v>172.94999999999709</v>
+      </c>
+      <c r="C28" s="716">
         <f>IF('Entries October 2026'!L28-'Entries October 2026'!L27&lt;1,"0",'Entries October 2026'!L28-'Entries October 2026'!L27)</f>
-        <v>0</v>
-      </c>
-      <c r="D28" s="716" t="str">
+        <v>352.2100000000064</v>
+      </c>
+      <c r="D28" s="716">
         <f>IF('Entries October 2026'!M28-'Entries October 2026'!M27&lt;1,"0",'Entries October 2026'!M28-'Entries October 2026'!M27)</f>
-        <v>0</v>
+        <v>1195.2399999999907</v>
       </c>
       <c r="E28" s="716">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F28" s="717">
-        <v>0</v>
-      </c>
-      <c r="G28" s="336" t="str">
+        <v>261.03000000000003</v>
+      </c>
+      <c r="G28" s="336">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3.8309772823047155</v>
       </c>
       <c r="I28" s="430">
         <v>230</v>
@@ -45772,27 +46005,27 @@
       <c r="A29" s="715">
         <v>23</v>
       </c>
-      <c r="B29" s="716" t="str">
+      <c r="B29" s="716">
         <f>IF('Entries October 2026'!N29-'Entries October 2026'!N28&lt;1,"0",'Entries October 2026'!N29-'Entries October 2026'!N28)</f>
-        <v>0</v>
-      </c>
-      <c r="C29" s="716" t="str">
+        <v>245.7899999999936</v>
+      </c>
+      <c r="C29" s="716">
         <f>IF('Entries October 2026'!L29-'Entries October 2026'!L28&lt;1,"0",'Entries October 2026'!L29-'Entries October 2026'!L28)</f>
-        <v>0</v>
-      </c>
-      <c r="D29" s="716" t="str">
+        <v>648.3799999999901</v>
+      </c>
+      <c r="D29" s="716">
         <f>IF('Entries October 2026'!M29-'Entries October 2026'!M28&lt;1,"0",'Entries October 2026'!M29-'Entries October 2026'!M28)</f>
-        <v>0</v>
+        <v>1931.0699999999488</v>
       </c>
       <c r="E29" s="716">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F29" s="717">
-        <v>0</v>
-      </c>
-      <c r="G29" s="336" t="str">
+        <v>416.87400000000002</v>
+      </c>
+      <c r="G29" s="336">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4.7976127079165405</v>
       </c>
       <c r="I29" s="430">
         <v>240</v>
@@ -46434,27 +46667,27 @@
       </c>
       <c r="B38" s="713">
         <f>SUM(B7:B37)</f>
-        <v>3260.320000000007</v>
+        <v>3679.0599999999977</v>
       </c>
       <c r="C38" s="713">
         <f>SUM(C7:C37)</f>
-        <v>7892.9400000000023</v>
+        <v>8893.5299999999988</v>
       </c>
       <c r="D38" s="713">
         <f>SUM(D7:D37)</f>
-        <v>24943.729999999981</v>
+        <v>28070.039999999921</v>
       </c>
       <c r="E38" s="713">
         <f>SUM(E7:E37)</f>
-        <v>28500</v>
+        <v>31500</v>
       </c>
       <c r="F38" s="714">
         <f>SUM(F7:F37)</f>
-        <v>5555.6268</v>
+        <v>6233.5307999999995</v>
       </c>
       <c r="G38" s="345">
         <f>IF(F38=0,"0",(E38/F38))</f>
-        <v>5.1299342137236428</v>
+        <v>5.0533158511064071</v>
       </c>
       <c r="H38" s="348">
         <v>5</v>
@@ -47131,11 +47364,11 @@
       </c>
       <c r="W8" s="101">
         <f>'Daily KPIs'!W8</f>
-        <v>0</v>
+        <v>3955</v>
       </c>
       <c r="X8" s="101">
         <f>'Daily KPIs'!X8</f>
-        <v>0</v>
+        <v>6025</v>
       </c>
       <c r="Y8" s="99">
         <f>'Daily KPIs'!Y8</f>
@@ -47165,14 +47398,14 @@
       </c>
       <c r="AG8" s="213">
         <f>SUM($B8:AF8)</f>
-        <v>78607</v>
+        <v>88587</v>
       </c>
       <c r="AH8" s="293">
         <v>96325</v>
       </c>
       <c r="AI8" s="294">
         <f>AG8-AH8</f>
-        <v>-17718</v>
+        <v>-7738</v>
       </c>
       <c r="AJ8" s="266"/>
       <c r="AK8" s="266"/>
@@ -47267,11 +47500,11 @@
       </c>
       <c r="W9" s="99">
         <f>'Daily KPIs'!W9</f>
-        <v>0</v>
+        <v>261.03000000000003</v>
       </c>
       <c r="X9" s="99">
         <f>'Daily KPIs'!X9</f>
-        <v>0</v>
+        <v>416.87400000000002</v>
       </c>
       <c r="Y9" s="99">
         <f>'Daily KPIs'!Y9</f>
@@ -47301,7 +47534,7 @@
       </c>
       <c r="AG9" s="215">
         <f>SUM($B9:AF9)</f>
-        <v>5555.6268</v>
+        <v>6233.5307999999995</v>
       </c>
       <c r="AH9" s="214"/>
       <c r="AI9" s="265"/>
@@ -47398,9 +47631,9 @@
         <f>'Daily KPIs'!W10</f>
         <v>GN</v>
       </c>
-      <c r="X10" s="163">
+      <c r="X10" s="163" t="str">
         <f>'Daily KPIs'!X10</f>
-        <v>0</v>
+        <v>GN/VM/VMG</v>
       </c>
       <c r="Y10" s="1028">
         <f>'Daily KPIs'!Y10</f>
@@ -47841,13 +48074,13 @@
         <f>+'Water '!$D27</f>
         <v>440</v>
       </c>
-      <c r="W16" s="110" t="str">
+      <c r="W16" s="110">
         <f>+'Water '!$D28</f>
-        <v>0</v>
-      </c>
-      <c r="X16" s="110" t="str">
+        <v>197</v>
+      </c>
+      <c r="X16" s="110">
         <f>+'Water '!$D29</f>
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="Y16" s="110" t="str">
         <f>+'Water '!$D30</f>
@@ -47883,7 +48116,7 @@
       </c>
       <c r="AG16" s="220">
         <f>SUM($B16:AF16)</f>
-        <v>3511</v>
+        <v>3918</v>
       </c>
       <c r="AH16" s="221"/>
     </row>
@@ -47975,13 +48208,13 @@
         <f>+'Water '!$E27</f>
         <v>134</v>
       </c>
-      <c r="W17" s="114" t="str">
+      <c r="W17" s="114">
         <f>+'Water '!$E28</f>
-        <v>0</v>
-      </c>
-      <c r="X17" s="114" t="str">
+        <v>208</v>
+      </c>
+      <c r="X17" s="114">
         <f>+'Water '!$E29</f>
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="Y17" s="116" t="str">
         <f>+'Water '!$E30</f>
@@ -48017,7 +48250,7 @@
       </c>
       <c r="AG17" s="222">
         <f>SUM($B17:AF17)</f>
-        <v>2670</v>
+        <v>3071</v>
       </c>
       <c r="AH17" s="223"/>
       <c r="AI17" s="268"/>
@@ -48112,11 +48345,11 @@
       </c>
       <c r="W18" s="175">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>405</v>
       </c>
       <c r="X18" s="175">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>403</v>
       </c>
       <c r="Y18" s="175">
         <f t="shared" si="0"/>
@@ -48152,7 +48385,7 @@
       </c>
       <c r="AG18" s="224">
         <f>SUM($B18:AF18)</f>
-        <v>6181</v>
+        <v>6989</v>
       </c>
       <c r="AH18" s="224"/>
       <c r="AI18" s="269"/>
@@ -48326,11 +48559,11 @@
       </c>
       <c r="W21" s="119">
         <f>0.73*(W96+W15)</f>
-        <v>0</v>
+        <v>157.68</v>
       </c>
       <c r="X21" s="119">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>147.46</v>
       </c>
       <c r="Y21" s="119">
         <f>0.73*(Y96+Y15)</f>
@@ -48366,16 +48599,16 @@
       </c>
       <c r="AG21" s="220">
         <f>SUM($B21:AF21)</f>
-        <v>1989.9800000000002</v>
+        <v>2295.1200000000003</v>
       </c>
       <c r="AH21" s="225">
         <f>AG24+AG37+AG28</f>
-        <v>6428</v>
+        <v>7319</v>
       </c>
       <c r="AI21" s="271"/>
       <c r="AJ21" s="272">
         <f>(AH21*10)/AG9</f>
-        <v>11.570251623093185</v>
+        <v>11.741339274364378</v>
       </c>
     </row>
     <row r="22" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -48643,11 +48876,11 @@
       </c>
       <c r="W24" s="112">
         <f>'Water '!H28</f>
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="X24" s="112">
         <f>'Water '!H29</f>
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="Y24" s="112">
         <f>'Water '!H30</f>
@@ -48683,7 +48916,7 @@
       </c>
       <c r="AG24" s="222">
         <f>SUM($B24:AF24)</f>
-        <v>3388</v>
+        <v>3829</v>
       </c>
       <c r="AH24" s="222"/>
       <c r="AI24" s="222"/>
@@ -48778,11 +49011,11 @@
       </c>
       <c r="W25" s="118">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="X25" s="118">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="Y25" s="118">
         <f t="shared" si="2"/>
@@ -48818,7 +49051,7 @@
       </c>
       <c r="AG25" s="224">
         <f>SUM($B25:AF25)</f>
-        <v>3388</v>
+        <v>3829</v>
       </c>
       <c r="AH25" s="224"/>
       <c r="AI25" s="269"/>
@@ -48911,13 +49144,13 @@
         <f t="shared" si="3"/>
         <v>4.4838780016645634</v>
       </c>
-      <c r="W26" s="125" t="str">
+      <c r="W26" s="125">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="X26" s="125" t="str">
+        <v>7.5087154733172428</v>
+      </c>
+      <c r="X26" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>5.8770755671977621</v>
       </c>
       <c r="Y26" s="125" t="str">
         <f t="shared" si="3"/>
@@ -49085,13 +49318,13 @@
         <f>+'Water '!$J27</f>
         <v>210</v>
       </c>
-      <c r="W28" s="127" t="str">
+      <c r="W28" s="127">
         <f>+'Water '!$J28</f>
-        <v>0</v>
-      </c>
-      <c r="X28" s="127" t="str">
+        <v>216</v>
+      </c>
+      <c r="X28" s="127">
         <f>+'Water '!$J29</f>
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="Y28" s="127" t="str">
         <f>+'Water '!$J30</f>
@@ -49127,7 +49360,7 @@
       </c>
       <c r="AG28" s="220">
         <f>SUM($B28:AF28)</f>
-        <v>2638</v>
+        <v>3033</v>
       </c>
       <c r="AH28" s="220"/>
       <c r="AI28" s="271"/>
@@ -49664,13 +49897,13 @@
         <f>+'Water '!$N27</f>
         <v>19</v>
       </c>
-      <c r="W33" s="131" t="str">
+      <c r="W33" s="131">
         <f>+'Water '!$N28</f>
-        <v>0</v>
-      </c>
-      <c r="X33" s="131" t="str">
+        <v>26</v>
+      </c>
+      <c r="X33" s="131">
         <f>+'Water '!$N29</f>
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="Y33" s="131" t="str">
         <f>+'Water '!$N30</f>
@@ -49706,7 +49939,7 @@
       </c>
       <c r="AG33" s="227">
         <f>SUM($B33:AF33)</f>
-        <v>657</v>
+        <v>724</v>
       </c>
       <c r="AH33" s="227"/>
       <c r="AI33" s="227"/>
@@ -49803,13 +50036,13 @@
         <f>+'Water '!$O27</f>
         <v>158</v>
       </c>
-      <c r="W34" s="134" t="str">
+      <c r="W34" s="134">
         <f>+'Water '!$O28</f>
-        <v>0</v>
-      </c>
-      <c r="X34" s="134" t="str">
+        <v>94</v>
+      </c>
+      <c r="X34" s="134">
         <f>+'Water '!$O29</f>
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="Y34" s="134" t="str">
         <f>+'Water '!$O30</f>
@@ -49845,7 +50078,7 @@
       </c>
       <c r="AG34" s="228">
         <f>SUM($B34:AF34)</f>
-        <v>1658</v>
+        <v>1864</v>
       </c>
       <c r="AH34" s="228"/>
       <c r="AI34" s="228"/>
@@ -49940,11 +50173,11 @@
       </c>
       <c r="W35" s="95">
         <f>IF('Entries October 2026'!$AC28-'Entries October 2026'!$AC27&lt;1,0,'Entries October 2026'!$AC28-'Entries October 2026'!$AC27)</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="X35" s="95">
         <f>IF('Entries October 2026'!$AC29-'Entries October 2026'!$AC28&lt;1,0,'Entries October 2026'!$AC29-'Entries October 2026'!$AC28)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y35" s="95">
         <f>IF('Entries October 2026'!$AC30-'Entries October 2026'!$AC29&lt;1,0,'Entries October 2026'!$AC30-'Entries October 2026'!$AC29)</f>
@@ -49980,7 +50213,7 @@
       </c>
       <c r="AG35" s="220">
         <f>SUM($B35:AF35)</f>
-        <v>306</v>
+        <v>349</v>
       </c>
       <c r="AH35" s="220"/>
       <c r="AI35" s="271"/>
@@ -50073,13 +50306,13 @@
         <f>+'Water '!$M27</f>
         <v>0</v>
       </c>
-      <c r="W36" s="110" t="str">
+      <c r="W36" s="110">
         <f>+'Water '!$M28</f>
-        <v>0</v>
-      </c>
-      <c r="X36" s="110" t="str">
+        <v>3</v>
+      </c>
+      <c r="X36" s="110">
         <f>+'Water '!$M29</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y36" s="110" t="str">
         <f>+'Water '!$M30</f>
@@ -50115,7 +50348,7 @@
       </c>
       <c r="AG36" s="220">
         <f>SUM($B36:AF36)</f>
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="AH36" s="220"/>
       <c r="AI36" s="271"/>
@@ -50208,13 +50441,13 @@
         <f>+'Water '!$Q27</f>
         <v>30</v>
       </c>
-      <c r="W37" s="131" t="str">
+      <c r="W37" s="131">
         <f>+'Water '!$Q28</f>
-        <v>0</v>
-      </c>
-      <c r="X37" s="131" t="str">
+        <v>29</v>
+      </c>
+      <c r="X37" s="131">
         <f>+'Water '!$Q29</f>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Y37" s="131" t="str">
         <f>+'Water '!$Q30</f>
@@ -50250,7 +50483,7 @@
       </c>
       <c r="AG37" s="227">
         <f>SUM($B37:AF37)</f>
-        <v>402</v>
+        <v>457</v>
       </c>
       <c r="AH37" s="227"/>
       <c r="AI37" s="227"/>
@@ -50698,11 +50931,11 @@
       </c>
       <c r="W42" s="138">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>391</v>
       </c>
       <c r="X42" s="138">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="Y42" s="138">
         <f t="shared" si="4"/>
@@ -50738,7 +50971,7 @@
       </c>
       <c r="AG42" s="230">
         <f>SUM($B42:AF42)</f>
-        <v>5961</v>
+        <v>6734</v>
       </c>
       <c r="AH42" s="230"/>
       <c r="AI42" s="276"/>
@@ -51153,13 +51386,13 @@
         <f>'Daily KPIs'!V76</f>
         <v>354.58999999999651</v>
       </c>
-      <c r="W49" s="187" t="str">
+      <c r="W49" s="187">
         <f>'Daily KPIs'!W76</f>
-        <v>0</v>
-      </c>
-      <c r="X49" s="187" t="str">
+        <v>172.94999999999709</v>
+      </c>
+      <c r="X49" s="187">
         <f>'Daily KPIs'!X76</f>
-        <v>0</v>
+        <v>245.7899999999936</v>
       </c>
       <c r="Y49" s="187" t="str">
         <f>'Daily KPIs'!Y76</f>
@@ -51195,7 +51428,7 @@
       </c>
       <c r="AG49" s="235">
         <f>SUM($B49:AF49)</f>
-        <v>3260.320000000007</v>
+        <v>3679.0599999999977</v>
       </c>
       <c r="AH49" s="236"/>
       <c r="AI49" s="280"/>
@@ -51890,13 +52123,13 @@
         <f t="shared" si="5"/>
         <v>8.8141985375186955</v>
       </c>
-      <c r="W59" s="144" t="str">
+      <c r="W59" s="144">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="X59" s="144" t="str">
+        <v>15.515457993334097</v>
+      </c>
+      <c r="X59" s="144">
         <f t="shared" si="5"/>
-        <v/>
+        <v>9.6671896064518297</v>
       </c>
       <c r="Y59" s="144" t="str">
         <f t="shared" si="5"/>
@@ -51932,7 +52165,7 @@
       </c>
       <c r="AG59" s="238">
         <f>IF(AG$9=0,"",+(AG18*10)/AG$9)</f>
-        <v>11.12565732457047</v>
+        <v>11.211944280438946</v>
       </c>
       <c r="AH59" s="239">
         <f>'Daily KPIs'!AI90</f>
@@ -51940,7 +52173,7 @@
       </c>
       <c r="AI59" s="282">
         <f>+AH59-AG59</f>
-        <v>-0.92565732457047112</v>
+        <v>-1.0119442804389465</v>
       </c>
       <c r="AJ59" s="270"/>
       <c r="AK59" s="270"/>
@@ -52055,13 +52288,13 @@
         <f t="shared" si="8"/>
         <v>3.2247067820190352</v>
       </c>
-      <c r="W62" s="145" t="str">
+      <c r="W62" s="145">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X62" s="145" t="str">
+        <v>8.2749109297781853</v>
+      </c>
+      <c r="X62" s="145">
         <f>IF(X$9=0,"",+(X28*10)/X$9)</f>
-        <v/>
+        <v>4.293863373585304</v>
       </c>
       <c r="Y62" s="145" t="str">
         <f t="shared" ref="Y62:AF62" si="10">IF(Y$9=0,"",+(Y28*10)/Y$9)</f>
@@ -52097,14 +52330,14 @@
       </c>
       <c r="AG62" s="241">
         <f>IF(+(AG28*10)/AG$9&lt;1,0,+(AG28*10)/AG$9)</f>
-        <v>4.7483391072992882</v>
+        <v>4.8656212623510262</v>
       </c>
       <c r="AH62" s="241">
         <v>2.5</v>
       </c>
       <c r="AI62" s="242">
         <f t="shared" ref="AI62:AI78" si="11">AH62-AG62</f>
-        <v>-2.2483391072992882</v>
+        <v>-2.3656212623510262</v>
       </c>
     </row>
     <row r="63" spans="1:37" ht="18.75" x14ac:dyDescent="0.3">
@@ -52237,14 +52470,14 @@
       </c>
       <c r="AG63" s="243">
         <f>IF(+(AG28*10)/AG$93&lt;1,0,+(AG28*10)/AG$93)</f>
-        <v>9.7848664688427291</v>
+        <v>11.25</v>
       </c>
       <c r="AH63" s="243">
         <v>2.5</v>
       </c>
       <c r="AI63" s="244">
         <f t="shared" si="11"/>
-        <v>-7.2848664688427291</v>
+        <v>-8.75</v>
       </c>
     </row>
     <row r="64" spans="1:37" s="90" customFormat="1" ht="18" x14ac:dyDescent="0.25">
@@ -52335,13 +52568,13 @@
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="W64" s="147" t="str">
+      <c r="W64" s="147">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="X64" s="147" t="str">
+        <v>0</v>
+      </c>
+      <c r="X64" s="147">
         <f t="shared" si="14"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y64" s="147" t="str">
         <f t="shared" ref="Y64:AF64" si="15">IF(Y$9=0,"",+(Y29*10)/Y$9)</f>
@@ -52635,13 +52868,13 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="W67" s="150" t="str">
+      <c r="W67" s="150">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="X67" s="150" t="str">
+        <v>0</v>
+      </c>
+      <c r="X67" s="150">
         <f t="shared" si="18"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y67" s="150" t="str">
         <f t="shared" ref="Y67:AF67" si="19">IF(Y$9=0,"",+(Y32*10)/Y$9)</f>
@@ -52677,14 +52910,14 @@
       </c>
       <c r="AG67" s="249">
         <f>+(AG32*10)/AG$9</f>
-        <v>0.15299803795316128</v>
+        <v>0.13635931661715703</v>
       </c>
       <c r="AH67" s="249">
         <v>1</v>
       </c>
       <c r="AI67" s="250">
         <f>AH67-AG67</f>
-        <v>0.84700196204683875</v>
+        <v>0.86364068338284294</v>
       </c>
       <c r="AJ67" s="284"/>
       <c r="AK67" s="284"/>
@@ -52777,13 +53010,13 @@
         <f t="shared" si="20"/>
         <v>0.29175918503981746</v>
       </c>
-      <c r="W68" s="145" t="str">
+      <c r="W68" s="145">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="X68" s="145" t="str">
+        <v>0.99605409339922601</v>
+      </c>
+      <c r="X68" s="145">
         <f t="shared" si="20"/>
-        <v/>
+        <v>0.98351060512289079</v>
       </c>
       <c r="Y68" s="145" t="str">
         <f t="shared" ref="Y68:AF68" si="21">IF(Y$9=0,"",+(Y33*10)/Y$9)</f>
@@ -52819,14 +53052,14 @@
       </c>
       <c r="AG68" s="241">
         <f>+(AG33*10)/AG$9</f>
-        <v>1.182584834532082</v>
+        <v>1.1614605321273139</v>
       </c>
       <c r="AH68" s="241">
         <v>0.7</v>
       </c>
       <c r="AI68" s="242">
         <f t="shared" si="11"/>
-        <v>-0.48258483453208201</v>
+        <v>-0.46146053212731397</v>
       </c>
     </row>
     <row r="69" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -52917,13 +53150,13 @@
         <f t="shared" si="22"/>
         <v>2.4262079598047976</v>
       </c>
-      <c r="W69" s="145" t="str">
+      <c r="W69" s="145">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="X69" s="145" t="str">
+        <v>3.6011186453664328</v>
+      </c>
+      <c r="X69" s="145">
         <f t="shared" si="22"/>
-        <v/>
+        <v>2.6866631164332628</v>
       </c>
       <c r="Y69" s="145" t="str">
         <f t="shared" ref="Y69:AF69" si="23">IF(Y$9=0,"",+(Y34*10)/Y$9)</f>
@@ -52959,14 +53192,14 @@
       </c>
       <c r="AG69" s="241">
         <f>+(AG34*10)/AG$9</f>
-        <v>2.9843617285451933</v>
+        <v>2.9902796020515372</v>
       </c>
       <c r="AH69" s="241">
         <v>2.6</v>
       </c>
       <c r="AI69" s="242">
         <f t="shared" si="11"/>
-        <v>-0.38436172854519324</v>
+        <v>-0.39027960205153711</v>
       </c>
     </row>
     <row r="70" spans="1:37" ht="18.75" x14ac:dyDescent="0.3">
@@ -53194,13 +53427,13 @@
         <f t="shared" si="26"/>
         <v>0.47602814401233373</v>
       </c>
-      <c r="W71" s="145" t="str">
+      <c r="W71" s="145">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="X71" s="145" t="str">
+        <v>0.88112477493008456</v>
+      </c>
+      <c r="X71" s="145">
         <f t="shared" si="26"/>
-        <v/>
+        <v>0.47976127079165404</v>
       </c>
       <c r="Y71" s="145" t="str">
         <f t="shared" ref="Y71:AF71" si="28">IF(Y$9=0,"",+(Y35*10)/Y$9)</f>
@@ -53236,14 +53469,14 @@
       </c>
       <c r="AG71" s="241">
         <f>+(AG35*10)/AG$9</f>
-        <v>0.55079293663138063</v>
+        <v>0.55987531175750349</v>
       </c>
       <c r="AH71" s="241">
         <v>0.7</v>
       </c>
       <c r="AI71" s="242">
         <f>AH71-AG71</f>
-        <v>0.14920706336861933</v>
+        <v>0.14012468824249646</v>
       </c>
     </row>
     <row r="72" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -53334,13 +53567,13 @@
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="W72" s="145" t="str">
+      <c r="W72" s="145">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="X72" s="145" t="str">
+        <v>0.11492931846914146</v>
+      </c>
+      <c r="X72" s="145">
         <f t="shared" si="29"/>
-        <v/>
+        <v>9.5952254158330808E-2</v>
       </c>
       <c r="Y72" s="145" t="str">
         <f t="shared" ref="Y72:AF72" si="30">IF(Y$9=0,"",+(Y36*10)/Y$9)</f>
@@ -53376,14 +53609,14 @@
       </c>
       <c r="AG72" s="241">
         <f>+(AG36*10)/AG$9</f>
-        <v>9.5398776606088809E-2</v>
+        <v>9.6253635259169662E-2</v>
       </c>
       <c r="AH72" s="241">
         <v>0.1</v>
       </c>
       <c r="AI72" s="242">
         <f>AH72-AG72</f>
-        <v>4.6012233939111968E-3</v>
+        <v>3.7463647408303435E-3</v>
       </c>
     </row>
     <row r="73" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -53474,13 +53707,13 @@
         <f t="shared" si="31"/>
         <v>0.46067239743129074</v>
       </c>
-      <c r="W73" s="145" t="str">
+      <c r="W73" s="145">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="X73" s="145" t="str">
+        <v>1.1109834118683675</v>
+      </c>
+      <c r="X73" s="145">
         <f t="shared" si="31"/>
-        <v/>
+        <v>0.62368965202915028</v>
       </c>
       <c r="Y73" s="145" t="str">
         <f t="shared" ref="Y73:AF73" si="32">IF(Y$9=0,"",+(Y37*10)/Y$9)</f>
@@ -53516,14 +53749,14 @@
       </c>
       <c r="AG73" s="241">
         <f>+(AG37*10)/AG$9</f>
-        <v>0.72359072067259811</v>
+        <v>0.73313185522400892</v>
       </c>
       <c r="AH73" s="241">
         <v>0.6</v>
       </c>
       <c r="AI73" s="242">
         <f t="shared" si="11"/>
-        <v>-0.12359072067259813</v>
+        <v>-0.13313185522400894</v>
       </c>
     </row>
     <row r="74" spans="1:37" s="91" customFormat="1" ht="18" x14ac:dyDescent="0.25">
@@ -53614,13 +53847,13 @@
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="W74" s="150" t="str">
+      <c r="W74" s="150">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="X74" s="150" t="str">
+        <v>0</v>
+      </c>
+      <c r="X74" s="150">
         <f t="shared" si="33"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y74" s="150" t="str">
         <f t="shared" ref="Y74:AF74" si="34">IF(Y$9=0,"",+(Y38*10)/Y$9)</f>
@@ -53756,13 +53989,13 @@
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="W75" s="145" t="str">
+      <c r="W75" s="145">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="X75" s="145" t="str">
+        <v>0</v>
+      </c>
+      <c r="X75" s="145">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y75" s="145" t="str">
         <f t="shared" ref="Y75:AF75" si="36">IF(Y$9=0,"",+(Y39*10)/Y$9)</f>
@@ -53990,11 +54223,11 @@
       </c>
       <c r="W78" s="152">
         <f>SUM(W62:W77)</f>
-        <v>0</v>
+        <v>14.979121173811437</v>
       </c>
       <c r="X78" s="152">
         <f>SUM(X62:X77)</f>
-        <v>0</v>
+        <v>9.1634402721205905</v>
       </c>
       <c r="Y78" s="152">
         <f t="shared" si="37"/>
@@ -54030,7 +54263,7 @@
       </c>
       <c r="AG78" s="253">
         <f>SUM(AG62:AG77)</f>
-        <v>20.22293261108252</v>
+        <v>21.792981515387719</v>
       </c>
       <c r="AH78" s="253">
         <f t="shared" si="37"/>
@@ -54038,7 +54271,7 @@
       </c>
       <c r="AI78" s="253">
         <f t="shared" si="11"/>
-        <v>-4.622932611082522</v>
+        <v>-6.1929815153877215</v>
       </c>
       <c r="AJ78" s="210"/>
       <c r="AK78" s="210"/>
@@ -54133,11 +54366,11 @@
       </c>
       <c r="W79" s="154">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>4.5971727387656589</v>
       </c>
       <c r="X79" s="154">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>3.2623766413832476</v>
       </c>
       <c r="Y79" s="154">
         <f t="shared" si="38"/>
@@ -54173,7 +54406,7 @@
       </c>
       <c r="AG79" s="254">
         <f t="shared" si="38"/>
-        <v>3.6305534417826624</v>
+        <v>3.6464085490682105</v>
       </c>
       <c r="AH79" s="254">
         <f t="shared" si="38"/>
@@ -54181,7 +54414,7 @@
       </c>
       <c r="AI79" s="254">
         <f t="shared" si="38"/>
-        <v>2.3694465582173372</v>
+        <v>2.3535914509317899</v>
       </c>
       <c r="AJ79" s="285"/>
       <c r="AK79" s="285"/>
@@ -54274,13 +54507,13 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="W80" s="155" t="str">
+      <c r="W80" s="155">
         <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="X80" s="155" t="str">
+        <v>0</v>
+      </c>
+      <c r="X80" s="155">
         <f>IF(X$9=0,"",+X47/X$9)</f>
-        <v/>
+        <v>0.16072002571520411</v>
       </c>
       <c r="Y80" s="155" t="str">
         <f>IF(Y$9=0,"",+Y47/Y$9)</f>
@@ -54417,13 +54650,13 @@
         <f>IF(V$9=0,"",+V49/V$9)</f>
         <v>0.54449941801719925</v>
       </c>
-      <c r="W81" s="157" t="str">
+      <c r="W81" s="157">
         <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="X81" s="157" t="str">
+        <v>0.66256752097458937</v>
+      </c>
+      <c r="X81" s="157">
         <f t="shared" si="41"/>
-        <v/>
+        <v>0.58960261373938783</v>
       </c>
       <c r="Y81" s="157" t="str">
         <f t="shared" si="41"/>
@@ -54459,7 +54692,7 @@
       </c>
       <c r="AG81" s="287">
         <f>IF(AG$9=0,"",+AG49/AG$9)</f>
-        <v>0.5868500742346493</v>
+        <v>0.59020483222766751</v>
       </c>
       <c r="AH81" s="287">
         <f>'Daily KPIs'!AI93</f>
@@ -54467,7 +54700,7 @@
       </c>
       <c r="AI81" s="286">
         <f>AH81-AG81</f>
-        <v>1.1131499257653505</v>
+        <v>1.1097951677723326</v>
       </c>
       <c r="AJ81" s="210"/>
       <c r="AK81" s="210"/>
@@ -54560,13 +54793,13 @@
         <f t="shared" si="43"/>
         <v>3.7667646363298539</v>
       </c>
-      <c r="W82" s="144" t="str">
+      <c r="W82" s="144">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="X82" s="144" t="str">
+        <v>9.3973872734934663</v>
+      </c>
+      <c r="X82" s="144">
         <f t="shared" si="43"/>
-        <v/>
+        <v>5.8842719862596367</v>
       </c>
       <c r="Y82" s="144" t="str">
         <f t="shared" si="43"/>
@@ -54602,7 +54835,7 @@
       </c>
       <c r="AG82" s="238">
         <f>+(AG52)/AG$9</f>
-        <v>23.29062132107218</v>
+        <v>20.757738134541665</v>
       </c>
       <c r="AH82" s="239">
         <f>'Daily KPIs'!AI94</f>
@@ -54610,7 +54843,7 @@
       </c>
       <c r="AI82" s="286">
         <f>AH82-AG82</f>
-        <v>-1.2906213210721802</v>
+        <v>1.2422618654583353</v>
       </c>
       <c r="AJ82" s="270"/>
       <c r="AK82" s="270"/>
@@ -54748,13 +54981,13 @@
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="W84" s="144" t="str">
+      <c r="W84" s="144">
         <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="X84" s="144" t="str">
+        <v>0</v>
+      </c>
+      <c r="X84" s="144">
         <f t="shared" si="46"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y84" s="144" t="str">
         <f t="shared" si="46"/>
@@ -54790,7 +55023,7 @@
       </c>
       <c r="AG84" s="255">
         <f>+(AG54)/AG$9</f>
-        <v>0.17279778404121746</v>
+        <v>0.15400581641467145</v>
       </c>
       <c r="AH84" s="256">
         <f>'Daily KPIs'!AI96</f>
@@ -54798,7 +55031,7 @@
       </c>
       <c r="AI84" s="286">
         <f>AH84-AG84</f>
-        <v>7.0272022159587824</v>
+        <v>7.0459941835853286</v>
       </c>
       <c r="AJ84" s="270"/>
       <c r="AK84" s="270"/>
@@ -55069,11 +55302,11 @@
       </c>
       <c r="W87" s="119">
         <f>IF('Entries October 2026'!L28-'Entries October 2026'!L27&lt;1,0,'Entries October 2026'!L28-'Entries October 2026'!L27)</f>
-        <v>0</v>
+        <v>352.2100000000064</v>
       </c>
       <c r="X87" s="119">
         <f>IF('Entries October 2026'!L29-'Entries October 2026'!L28&lt;1,0,'Entries October 2026'!L29-'Entries October 2026'!L28)</f>
-        <v>0</v>
+        <v>648.3799999999901</v>
       </c>
       <c r="Y87" s="119">
         <f>IF('Entries October 2026'!L30-'Entries October 2026'!L29&lt;1,0,'Entries October 2026'!L30-'Entries October 2026'!L29)</f>
@@ -55109,7 +55342,7 @@
       </c>
       <c r="AG87" s="220">
         <f>SUM($B87:AF87)</f>
-        <v>554430.93000000017</v>
+        <v>555431.52000000014</v>
       </c>
       <c r="AH87" s="220"/>
       <c r="AI87" s="271"/>
@@ -55244,13 +55477,13 @@
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="W89" s="160" t="str">
+      <c r="W89" s="160">
         <f t="shared" si="49"/>
-        <v/>
-      </c>
-      <c r="X89" s="160" t="str">
+        <v>0</v>
+      </c>
+      <c r="X89" s="160">
         <f t="shared" si="49"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y89" s="160" t="str">
         <f t="shared" si="49"/>
@@ -55729,9 +55962,9 @@
         <f>'Daily KPIs'!W13</f>
         <v>VM/CB</v>
       </c>
-      <c r="X94" s="166">
+      <c r="X94" s="166" t="str">
         <f>'Daily KPIs'!X13</f>
-        <v>0</v>
+        <v>CB/ST</v>
       </c>
       <c r="Y94" s="166">
         <f>'Daily KPIs'!Y13</f>
@@ -55855,15 +56088,15 @@
       </c>
       <c r="V95" s="174">
         <f>'Daily KPIs'!V14</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="W95" s="174">
         <f>'Daily KPIs'!W14</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X95" s="174">
         <f>'Daily KPIs'!X14</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Y95" s="174">
         <f>'Daily KPIs'!Y14</f>
@@ -55899,7 +56132,7 @@
       </c>
       <c r="AG95" s="262">
         <f>SUM($B95:AF95)</f>
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="AH95" s="262"/>
       <c r="AI95" s="290"/>
@@ -55992,13 +56225,13 @@
         <f>+'Water '!$F27</f>
         <v>140</v>
       </c>
-      <c r="W96" s="110" t="str">
+      <c r="W96" s="110">
         <f>+'Water '!$F28</f>
-        <v>0</v>
-      </c>
-      <c r="X96" s="110" t="str">
+        <v>216</v>
+      </c>
+      <c r="X96" s="110">
         <f>+'Water '!$F29</f>
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="Y96" s="110" t="str">
         <f>+'Water '!$F30</f>
@@ -56034,7 +56267,7 @@
       </c>
       <c r="AG96" s="220">
         <f>SUM($B96:AF96)</f>
-        <v>2726</v>
+        <v>3144</v>
       </c>
       <c r="AH96" s="220"/>
       <c r="AI96" s="271"/>

--- a/data/raw/October_26_Utilities_Tracking.xlsx
+++ b/data/raw/October_26_Utilities_Tracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UTILITIES\Tracking\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{671EA45D-C2FA-4FB6-9626-7CD8F00332BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABCCDBF-CE6C-438C-AD5C-C3F1ACC38974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="579" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
     <author>Alexander Dominguez-Ramon</author>
   </authors>
   <commentList>
-    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{B21E4652-3C64-4886-B747-45EC64E26654}">
+    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{F913E988-F41B-4D83-A8A2-230D2042E2F9}">
       <text>
         <r>
           <rPr>
@@ -80,7 +80,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{70D71AB5-31BF-4066-BE4E-F85202A05576}">
+    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{5DBB80E5-E65D-431B-8047-CE8D04365EFF}">
       <text>
         <r>
           <rPr>
@@ -101,7 +101,33 @@
           </rPr>
           <t xml:space="preserve">
 25 inches, mean 832 liters of diesel consumed.
-</t>
+(33.3 liters/inch)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E31" authorId="0" shapeId="0" xr:uid="{47C576C4-D0E7-44DF-9BB8-143565BCE5E4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Alexander Dominguez-Ramon:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+2 inches, mean 67 liters of diesel consumed.
+Consumption= 2 inches of diesel = 66.6 liters
+(33.3 liters/inch)</t>
         </r>
       </text>
     </comment>
@@ -3556,7 +3582,7 @@
     <numFmt numFmtId="173" formatCode="0.0000000"/>
     <numFmt numFmtId="174" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="149" x14ac:knownFonts="1">
+  <fonts count="151" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -4535,6 +4561,19 @@
       <color rgb="FF92D050"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="41">
@@ -9104,6 +9143,72 @@
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="41" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="42" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="41" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="99" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="124" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="77" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="78" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="79" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="100" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="50" fillId="10" borderId="43" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9119,72 +9224,6 @@
     <xf numFmtId="0" fontId="9" fillId="11" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="124" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="77" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="78" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="79" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="100" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="41" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="41" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="42" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="99" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="118" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -9302,6 +9341,27 @@
     <xf numFmtId="0" fontId="70" fillId="12" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="49" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="51" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="33" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="18" borderId="52" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9314,12 +9374,6 @@
     <xf numFmtId="0" fontId="3" fillId="18" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="18" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9329,21 +9383,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="49" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="51" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="33" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -9398,6 +9437,66 @@
     <xf numFmtId="2" fontId="17" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="122" fillId="16" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="16" borderId="88" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="16" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="16" borderId="89" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="16" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="16" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="16" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="16" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="16" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="16" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="120" fillId="16" borderId="83" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="120" fillId="16" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="120" fillId="16" borderId="85" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="16" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="16" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="22" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="22" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="122" fillId="16" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="122" fillId="16" borderId="88" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="16" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9421,66 +9520,6 @@
     </xf>
     <xf numFmtId="0" fontId="111" fillId="32" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="16" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="16" borderId="88" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="16" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="16" borderId="89" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="16" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="16" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="16" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="16" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="16" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="16" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="120" fillId="16" borderId="83" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="120" fillId="16" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="120" fillId="16" borderId="85" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="16" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="16" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="22" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="22" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="122" fillId="16" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="122" fillId="16" borderId="88" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="16" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="69" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -9494,7 +9533,437 @@
     <cellStyle name="Normal_February04" xfId="3" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
     <cellStyle name="Percent" xfId="4" builtinId="5"/>
   </cellStyles>
-  <dxfs count="118">
+  <dxfs count="161">
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -10876,13 +11345,13 @@
                   <c:v>7265</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0</c:v>
+                  <c:v>3898</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0</c:v>
+                  <c:v>3808</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0</c:v>
+                  <c:v>2496</c:v>
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>0</c:v>
@@ -11202,6 +11671,18 @@
                 <c:pt idx="22">
                   <c:v>1429.6</c:v>
                 </c:pt>
+                <c:pt idx="23">
+                  <c:v>1431</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1084.3</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1172.7</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1431.7</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -11387,16 +11868,16 @@
                   <c:v>0.16442389529133022</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0</c:v>
+                  <c:v>0.26853068117845752</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0</c:v>
+                  <c:v>0.22163399627986835</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0</c:v>
+                  <c:v>0.31965001226592527</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>0</c:v>
@@ -12816,53 +13297,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="18" x14ac:dyDescent="0.2">
-      <c r="B1" s="918" t="s">
+      <c r="B1" s="904" t="s">
         <v>209</v>
       </c>
-      <c r="C1" s="918"/>
-      <c r="D1" s="918"/>
-      <c r="E1" s="918"/>
-      <c r="F1" s="918"/>
-      <c r="G1" s="918"/>
-      <c r="H1" s="918"/>
-      <c r="I1" s="918"/>
-      <c r="J1" s="918"/>
-      <c r="K1" s="918"/>
-      <c r="L1" s="918"/>
-      <c r="M1" s="918"/>
+      <c r="C1" s="904"/>
+      <c r="D1" s="904"/>
+      <c r="E1" s="904"/>
+      <c r="F1" s="904"/>
+      <c r="G1" s="904"/>
+      <c r="H1" s="904"/>
+      <c r="I1" s="904"/>
+      <c r="J1" s="904"/>
+      <c r="K1" s="904"/>
+      <c r="L1" s="904"/>
+      <c r="M1" s="904"/>
       <c r="N1" s="363"/>
-      <c r="O1" s="919" t="str">
+      <c r="O1" s="905" t="str">
         <f>B1</f>
         <v>ENTRIES FOR DAILY CONS. MONITOR</v>
       </c>
-      <c r="P1" s="919"/>
-      <c r="Q1" s="919"/>
-      <c r="R1" s="919"/>
-      <c r="S1" s="919"/>
-      <c r="T1" s="919"/>
-      <c r="U1" s="919"/>
-      <c r="V1" s="919"/>
-      <c r="W1" s="919"/>
-      <c r="X1" s="919"/>
-      <c r="Y1" s="919"/>
-      <c r="Z1" s="919"/>
-      <c r="AA1" s="919"/>
-      <c r="AB1" s="919"/>
+      <c r="P1" s="905"/>
+      <c r="Q1" s="905"/>
+      <c r="R1" s="905"/>
+      <c r="S1" s="905"/>
+      <c r="T1" s="905"/>
+      <c r="U1" s="905"/>
+      <c r="V1" s="905"/>
+      <c r="W1" s="905"/>
+      <c r="X1" s="905"/>
+      <c r="Y1" s="905"/>
+      <c r="Z1" s="905"/>
+      <c r="AA1" s="905"/>
+      <c r="AB1" s="905"/>
     </row>
     <row r="2" spans="1:44" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C2" s="810"/>
       <c r="F2" s="364"/>
       <c r="G2" s="365"/>
-      <c r="O2" s="926" t="s">
+      <c r="O2" s="913" t="s">
         <v>231</v>
       </c>
-      <c r="P2" s="926"/>
-      <c r="Q2" s="926"/>
-      <c r="R2" s="926"/>
-      <c r="S2" s="926"/>
-      <c r="T2" s="926"/>
-      <c r="U2" s="926"/>
-      <c r="V2" s="926"/>
+      <c r="P2" s="913"/>
+      <c r="Q2" s="913"/>
+      <c r="R2" s="913"/>
+      <c r="S2" s="913"/>
+      <c r="T2" s="913"/>
+      <c r="U2" s="913"/>
+      <c r="V2" s="913"/>
     </row>
     <row r="3" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="366"/>
@@ -12880,50 +13361,50 @@
         <v>22</v>
       </c>
       <c r="K3" s="369"/>
-      <c r="L3" s="909" t="s">
+      <c r="L3" s="918" t="s">
         <v>53</v>
       </c>
-      <c r="M3" s="910"/>
-      <c r="N3" s="911"/>
-      <c r="O3" s="920" t="s">
+      <c r="M3" s="919"/>
+      <c r="N3" s="920"/>
+      <c r="O3" s="906" t="s">
         <v>3</v>
       </c>
-      <c r="P3" s="920"/>
-      <c r="Q3" s="920"/>
-      <c r="R3" s="920"/>
-      <c r="S3" s="920"/>
-      <c r="T3" s="920"/>
-      <c r="U3" s="920"/>
-      <c r="V3" s="920"/>
-      <c r="W3" s="920"/>
-      <c r="X3" s="920"/>
-      <c r="Y3" s="920"/>
-      <c r="Z3" s="920"/>
-      <c r="AA3" s="920"/>
-      <c r="AB3" s="920"/>
-      <c r="AC3" s="920"/>
+      <c r="P3" s="906"/>
+      <c r="Q3" s="906"/>
+      <c r="R3" s="906"/>
+      <c r="S3" s="906"/>
+      <c r="T3" s="906"/>
+      <c r="U3" s="906"/>
+      <c r="V3" s="906"/>
+      <c r="W3" s="906"/>
+      <c r="X3" s="906"/>
+      <c r="Y3" s="906"/>
+      <c r="Z3" s="906"/>
+      <c r="AA3" s="906"/>
+      <c r="AB3" s="906"/>
+      <c r="AC3" s="906"/>
       <c r="AD3" s="372"/>
       <c r="AE3" s="373"/>
       <c r="AF3" s="372"/>
-      <c r="AG3" s="904" t="s">
+      <c r="AG3" s="926" t="s">
         <v>206</v>
       </c>
-      <c r="AH3" s="902" t="s">
+      <c r="AH3" s="924" t="s">
         <v>204</v>
       </c>
-      <c r="AI3" s="902" t="s">
+      <c r="AI3" s="924" t="s">
         <v>205</v>
       </c>
-      <c r="AJ3" s="905" t="s">
+      <c r="AJ3" s="927" t="s">
         <v>233</v>
       </c>
       <c r="AK3" s="416"/>
-      <c r="AL3" s="906" t="s">
+      <c r="AL3" s="928" t="s">
         <v>178</v>
       </c>
-      <c r="AM3" s="906"/>
-      <c r="AN3" s="906"/>
-      <c r="AO3" s="906"/>
+      <c r="AM3" s="928"/>
+      <c r="AN3" s="928"/>
+      <c r="AO3" s="928"/>
     </row>
     <row r="4" spans="1:44" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="374"/>
@@ -12957,40 +13438,40 @@
       <c r="K4" s="372" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="927" t="s">
+      <c r="L4" s="914" t="s">
         <v>289</v>
       </c>
       <c r="M4" s="376" t="s">
         <v>260</v>
       </c>
-      <c r="N4" s="912" t="s">
+      <c r="N4" s="921" t="s">
         <v>167</v>
       </c>
-      <c r="O4" s="914" t="s">
+      <c r="O4" s="902" t="s">
         <v>100</v>
       </c>
-      <c r="P4" s="914" t="s">
+      <c r="P4" s="902" t="s">
         <v>101</v>
       </c>
-      <c r="Q4" s="914" t="s">
+      <c r="Q4" s="902" t="s">
         <v>160</v>
       </c>
-      <c r="R4" s="914" t="s">
+      <c r="R4" s="902" t="s">
         <v>171</v>
       </c>
-      <c r="S4" s="914" t="s">
+      <c r="S4" s="902" t="s">
         <v>102</v>
       </c>
-      <c r="T4" s="914" t="s">
+      <c r="T4" s="902" t="s">
         <v>172</v>
       </c>
-      <c r="U4" s="914" t="s">
+      <c r="U4" s="902" t="s">
         <v>103</v>
       </c>
-      <c r="V4" s="924" t="s">
+      <c r="V4" s="911" t="s">
         <v>236</v>
       </c>
-      <c r="W4" s="914" t="s">
+      <c r="W4" s="902" t="s">
         <v>177</v>
       </c>
       <c r="X4" s="372" t="s">
@@ -13002,28 +13483,28 @@
       <c r="Z4" s="372" t="s">
         <v>98</v>
       </c>
-      <c r="AA4" s="920" t="s">
+      <c r="AA4" s="906" t="s">
         <v>68</v>
       </c>
-      <c r="AB4" s="922" t="s">
+      <c r="AB4" s="908" t="s">
         <v>69</v>
       </c>
-      <c r="AC4" s="925" t="s">
+      <c r="AC4" s="912" t="s">
         <v>151</v>
       </c>
-      <c r="AD4" s="914" t="s">
+      <c r="AD4" s="902" t="s">
         <v>154</v>
       </c>
-      <c r="AE4" s="914" t="s">
+      <c r="AE4" s="902" t="s">
         <v>155</v>
       </c>
-      <c r="AF4" s="914" t="s">
+      <c r="AF4" s="902" t="s">
         <v>159</v>
       </c>
-      <c r="AG4" s="904"/>
-      <c r="AH4" s="903"/>
-      <c r="AI4" s="903"/>
-      <c r="AJ4" s="905"/>
+      <c r="AG4" s="926"/>
+      <c r="AH4" s="925"/>
+      <c r="AI4" s="925"/>
+      <c r="AJ4" s="927"/>
       <c r="AK4" s="416"/>
       <c r="AL4" s="378" t="s">
         <v>276</v>
@@ -13072,20 +13553,20 @@
       <c r="K5" s="465" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="928"/>
+      <c r="L5" s="915"/>
       <c r="M5" s="466" t="s">
         <v>261</v>
       </c>
-      <c r="N5" s="913"/>
-      <c r="O5" s="915"/>
-      <c r="P5" s="914"/>
-      <c r="Q5" s="914"/>
-      <c r="R5" s="914"/>
-      <c r="S5" s="915"/>
-      <c r="T5" s="915"/>
-      <c r="U5" s="915"/>
-      <c r="V5" s="924"/>
-      <c r="W5" s="916"/>
+      <c r="N5" s="922"/>
+      <c r="O5" s="910"/>
+      <c r="P5" s="902"/>
+      <c r="Q5" s="902"/>
+      <c r="R5" s="902"/>
+      <c r="S5" s="910"/>
+      <c r="T5" s="910"/>
+      <c r="U5" s="910"/>
+      <c r="V5" s="911"/>
+      <c r="W5" s="923"/>
       <c r="X5" s="372" t="s">
         <v>104</v>
       </c>
@@ -13095,16 +13576,16 @@
       <c r="Z5" s="372" t="s">
         <v>104</v>
       </c>
-      <c r="AA5" s="921"/>
-      <c r="AB5" s="923"/>
-      <c r="AC5" s="925"/>
-      <c r="AD5" s="914"/>
-      <c r="AE5" s="914"/>
-      <c r="AF5" s="917"/>
-      <c r="AG5" s="904"/>
-      <c r="AH5" s="903"/>
-      <c r="AI5" s="903"/>
-      <c r="AJ5" s="905"/>
+      <c r="AA5" s="907"/>
+      <c r="AB5" s="909"/>
+      <c r="AC5" s="912"/>
+      <c r="AD5" s="902"/>
+      <c r="AE5" s="902"/>
+      <c r="AF5" s="903"/>
+      <c r="AG5" s="926"/>
+      <c r="AH5" s="925"/>
+      <c r="AI5" s="925"/>
+      <c r="AJ5" s="927"/>
       <c r="AK5" s="416"/>
       <c r="AL5" s="378" t="s">
         <v>263</v>
@@ -15314,41 +15795,87 @@
       <c r="A30" s="378">
         <v>25</v>
       </c>
-      <c r="B30" s="815"/>
-      <c r="C30" s="816"/>
+      <c r="B30" s="815">
+        <v>8522020</v>
+      </c>
+      <c r="C30" s="816">
+        <v>1717349.8</v>
+      </c>
       <c r="D30" s="817"/>
-      <c r="E30" s="817"/>
-      <c r="F30" s="817"/>
-      <c r="G30" s="817"/>
+      <c r="E30" s="817">
+        <v>44</v>
+      </c>
+      <c r="F30" s="817">
+        <v>11620.6</v>
+      </c>
+      <c r="G30" s="817">
+        <v>68225</v>
+      </c>
       <c r="H30" s="818"/>
-      <c r="I30" s="819"/>
+      <c r="I30" s="819">
+        <v>2021045</v>
+      </c>
       <c r="J30" s="876"/>
-      <c r="K30" s="818"/>
-      <c r="L30" s="817"/>
-      <c r="M30" s="821"/>
-      <c r="N30" s="819"/>
-      <c r="O30" s="822"/>
-      <c r="P30" s="823"/>
-      <c r="Q30" s="817"/>
+      <c r="K30" s="818">
+        <v>468000</v>
+      </c>
+      <c r="L30" s="817">
+        <v>95511.79</v>
+      </c>
+      <c r="M30" s="821">
+        <v>658415.18999999994</v>
+      </c>
+      <c r="N30" s="819">
+        <v>88314.54</v>
+      </c>
+      <c r="O30" s="822">
+        <v>256912</v>
+      </c>
+      <c r="P30" s="823">
+        <v>88890</v>
+      </c>
+      <c r="Q30" s="817">
+        <v>993405</v>
+      </c>
       <c r="R30" s="817"/>
-      <c r="S30" s="817"/>
+      <c r="S30" s="817">
+        <v>100304</v>
+      </c>
       <c r="T30" s="817"/>
-      <c r="U30" s="817"/>
-      <c r="V30" s="824"/>
+      <c r="U30" s="817">
+        <v>598</v>
+      </c>
+      <c r="V30" s="824">
+        <v>1369350</v>
+      </c>
       <c r="W30" s="817"/>
-      <c r="X30" s="825"/>
-      <c r="Y30" s="817"/>
-      <c r="Z30" s="817"/>
-      <c r="AA30" s="817"/>
+      <c r="X30" s="825">
+        <v>49746</v>
+      </c>
+      <c r="Y30" s="817">
+        <v>72508</v>
+      </c>
+      <c r="Z30" s="817">
+        <v>16152</v>
+      </c>
+      <c r="AA30" s="817">
+        <v>97122</v>
+      </c>
       <c r="AB30" s="817"/>
-      <c r="AC30" s="817"/>
-      <c r="AD30" s="817"/>
+      <c r="AC30" s="817">
+        <v>7099</v>
+      </c>
+      <c r="AD30" s="817">
+        <v>263787</v>
+      </c>
       <c r="AE30" s="817"/>
       <c r="AF30" s="819"/>
       <c r="AG30" s="817"/>
       <c r="AH30" s="817"/>
       <c r="AI30" s="817"/>
-      <c r="AJ30" s="880"/>
+      <c r="AJ30" s="880">
+        <v>7383617.4119999995</v>
+      </c>
       <c r="AK30" s="192"/>
       <c r="AL30" s="387"/>
       <c r="AM30" s="387"/>
@@ -15359,41 +15886,87 @@
       <c r="A31" s="378">
         <v>26</v>
       </c>
-      <c r="B31" s="815"/>
-      <c r="C31" s="816"/>
+      <c r="B31" s="815">
+        <v>8522020</v>
+      </c>
+      <c r="C31" s="816">
+        <v>1717349.8</v>
+      </c>
       <c r="D31" s="817"/>
-      <c r="E31" s="817"/>
-      <c r="F31" s="817"/>
-      <c r="G31" s="817"/>
+      <c r="E31" s="817">
+        <v>42</v>
+      </c>
+      <c r="F31" s="817">
+        <v>11620.6</v>
+      </c>
+      <c r="G31" s="817">
+        <v>68225</v>
+      </c>
       <c r="H31" s="818"/>
-      <c r="I31" s="819"/>
+      <c r="I31" s="819">
+        <v>2024853</v>
+      </c>
       <c r="J31" s="876"/>
-      <c r="K31" s="818"/>
-      <c r="L31" s="817"/>
-      <c r="M31" s="821"/>
-      <c r="N31" s="819"/>
-      <c r="O31" s="822"/>
-      <c r="P31" s="823"/>
-      <c r="Q31" s="817"/>
+      <c r="K31" s="818">
+        <v>468000</v>
+      </c>
+      <c r="L31" s="817">
+        <v>95511.79</v>
+      </c>
+      <c r="M31" s="821">
+        <v>658415.18999999994</v>
+      </c>
+      <c r="N31" s="819">
+        <v>88314.54</v>
+      </c>
+      <c r="O31" s="822">
+        <v>256923</v>
+      </c>
+      <c r="P31" s="823">
+        <v>88890</v>
+      </c>
+      <c r="Q31" s="817">
+        <v>993420</v>
+      </c>
       <c r="R31" s="817"/>
-      <c r="S31" s="817"/>
+      <c r="S31" s="817">
+        <v>100304</v>
+      </c>
       <c r="T31" s="817"/>
-      <c r="U31" s="817"/>
-      <c r="V31" s="824"/>
+      <c r="U31" s="817">
+        <v>598</v>
+      </c>
+      <c r="V31" s="824">
+        <v>1369350</v>
+      </c>
       <c r="W31" s="817"/>
-      <c r="X31" s="825"/>
-      <c r="Y31" s="817"/>
-      <c r="Z31" s="817"/>
-      <c r="AA31" s="817"/>
+      <c r="X31" s="825">
+        <v>49746</v>
+      </c>
+      <c r="Y31" s="817">
+        <v>72508</v>
+      </c>
+      <c r="Z31" s="817">
+        <v>16159</v>
+      </c>
+      <c r="AA31" s="817">
+        <v>97122</v>
+      </c>
       <c r="AB31" s="817"/>
-      <c r="AC31" s="817"/>
-      <c r="AD31" s="817"/>
+      <c r="AC31" s="817">
+        <v>7099</v>
+      </c>
+      <c r="AD31" s="817">
+        <v>263787</v>
+      </c>
       <c r="AE31" s="817"/>
       <c r="AF31" s="819"/>
       <c r="AG31" s="817"/>
       <c r="AH31" s="817"/>
       <c r="AI31" s="817"/>
-      <c r="AJ31" s="880"/>
+      <c r="AJ31" s="880">
+        <v>7383617.4119999995</v>
+      </c>
       <c r="AK31" s="192"/>
       <c r="AL31" s="387"/>
       <c r="AM31" s="387"/>
@@ -15404,41 +15977,87 @@
       <c r="A32" s="378">
         <v>27</v>
       </c>
-      <c r="B32" s="815"/>
-      <c r="C32" s="816"/>
+      <c r="B32" s="815">
+        <v>8522020</v>
+      </c>
+      <c r="C32" s="816">
+        <v>1717931.6</v>
+      </c>
       <c r="D32" s="817"/>
-      <c r="E32" s="817"/>
-      <c r="F32" s="817"/>
-      <c r="G32" s="817"/>
+      <c r="E32" s="817">
+        <v>42</v>
+      </c>
+      <c r="F32" s="817">
+        <v>11624.2</v>
+      </c>
+      <c r="G32" s="817">
+        <v>68225</v>
+      </c>
       <c r="H32" s="818"/>
-      <c r="I32" s="819"/>
+      <c r="I32" s="819">
+        <v>2027349</v>
+      </c>
       <c r="J32" s="876"/>
-      <c r="K32" s="818"/>
-      <c r="L32" s="817"/>
-      <c r="M32" s="821"/>
-      <c r="N32" s="819"/>
-      <c r="O32" s="822"/>
-      <c r="P32" s="823"/>
-      <c r="Q32" s="817"/>
+      <c r="K32" s="818">
+        <v>468000</v>
+      </c>
+      <c r="L32" s="817">
+        <v>95511.79</v>
+      </c>
+      <c r="M32" s="821">
+        <v>658415.18999999994</v>
+      </c>
+      <c r="N32" s="819">
+        <v>88314.54</v>
+      </c>
+      <c r="O32" s="822">
+        <v>256996</v>
+      </c>
+      <c r="P32" s="823">
+        <v>88956</v>
+      </c>
+      <c r="Q32" s="817">
+        <v>993448</v>
+      </c>
       <c r="R32" s="817"/>
-      <c r="S32" s="882"/>
+      <c r="S32" s="817">
+        <v>100304</v>
+      </c>
       <c r="T32" s="817"/>
-      <c r="U32" s="817"/>
-      <c r="V32" s="824"/>
+      <c r="U32" s="817">
+        <v>599</v>
+      </c>
+      <c r="V32" s="824">
+        <v>1369422</v>
+      </c>
       <c r="W32" s="817"/>
-      <c r="X32" s="825"/>
-      <c r="Y32" s="817"/>
-      <c r="Z32" s="817"/>
-      <c r="AA32" s="817"/>
+      <c r="X32" s="825">
+        <v>49746</v>
+      </c>
+      <c r="Y32" s="817">
+        <v>72508</v>
+      </c>
+      <c r="Z32" s="817">
+        <v>16165</v>
+      </c>
+      <c r="AA32" s="817">
+        <v>97122</v>
+      </c>
       <c r="AB32" s="817"/>
-      <c r="AC32" s="817"/>
-      <c r="AD32" s="817"/>
+      <c r="AC32" s="817">
+        <v>7099</v>
+      </c>
+      <c r="AD32" s="817">
+        <v>263787</v>
+      </c>
       <c r="AE32" s="817"/>
       <c r="AF32" s="819"/>
       <c r="AG32" s="817"/>
       <c r="AH32" s="817"/>
       <c r="AI32" s="817"/>
-      <c r="AJ32" s="880"/>
+      <c r="AJ32" s="880">
+        <v>7383617.4119999995</v>
+      </c>
       <c r="AK32" s="192"/>
       <c r="AL32" s="387"/>
       <c r="AM32" s="387"/>
@@ -15673,8 +16292,8 @@
     <row r="38" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B38" s="190"/>
       <c r="G38" s="190"/>
-      <c r="I38" s="907"/>
-      <c r="J38" s="907"/>
+      <c r="I38" s="916"/>
+      <c r="J38" s="916"/>
       <c r="R38" s="190"/>
       <c r="S38" s="190"/>
       <c r="T38" s="190"/>
@@ -15682,8 +16301,8 @@
       <c r="V38" s="190"/>
       <c r="W38" s="190"/>
       <c r="Z38" s="190"/>
-      <c r="AA38" s="908"/>
-      <c r="AB38" s="908"/>
+      <c r="AA38" s="917"/>
+      <c r="AB38" s="917"/>
       <c r="AC38" s="190"/>
       <c r="AD38" s="190"/>
       <c r="AI38" s="380"/>
@@ -17349,6 +17968,19 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="AH3:AH5"/>
+    <mergeCell ref="AG3:AG5"/>
+    <mergeCell ref="AI3:AI5"/>
+    <mergeCell ref="AJ3:AJ5"/>
+    <mergeCell ref="AL3:AO3"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="AA38:AB38"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="S4:S5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="P4:P5"/>
+    <mergeCell ref="W4:W5"/>
     <mergeCell ref="AF4:AF5"/>
     <mergeCell ref="AE4:AE5"/>
     <mergeCell ref="AD4:AD5"/>
@@ -17365,294 +17997,346 @@
     <mergeCell ref="AC4:AC5"/>
     <mergeCell ref="O2:V2"/>
     <mergeCell ref="L4:L5"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="AA38:AB38"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="S4:S5"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="P4:P5"/>
-    <mergeCell ref="W4:W5"/>
-    <mergeCell ref="AH3:AH5"/>
-    <mergeCell ref="AG3:AG5"/>
-    <mergeCell ref="AI3:AI5"/>
-    <mergeCell ref="AJ3:AJ5"/>
-    <mergeCell ref="AL3:AO3"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
+  <conditionalFormatting sqref="B33:B35">
+    <cfRule type="expression" dxfId="159" priority="63">
+      <formula>B33&lt;B32</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C35 E35:E37">
+    <cfRule type="expression" dxfId="157" priority="714">
+      <formula>C35&lt;C34</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C36:D37">
+    <cfRule type="expression" dxfId="153" priority="1767">
+      <formula>C36&lt;C35</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D35 B36:B37">
+    <cfRule type="expression" dxfId="152" priority="1754">
+      <formula>B35&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F33:F37">
+    <cfRule type="expression" dxfId="150" priority="47">
+      <formula>F33&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G33:G37">
+    <cfRule type="expression" dxfId="149" priority="45">
+      <formula>G33&lt;G32</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G36:J37 L36:O37">
+    <cfRule type="expression" dxfId="148" priority="1601">
+      <formula>G36&lt;G35</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H35:I35 R35 T35 W35 AB35 AE35:AI35 P36:P37 S36:S37 X36:Y37">
+    <cfRule type="expression" dxfId="146" priority="1753">
+      <formula>H35&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H33:I34">
+    <cfRule type="expression" dxfId="145" priority="69">
+      <formula>H33&lt;H32</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J33:J35">
+    <cfRule type="expression" dxfId="144" priority="80">
+      <formula>J33&lt;J32</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K33:K37">
+    <cfRule type="expression" dxfId="143" priority="72">
+      <formula>K33&lt;K32</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L33:T34 U33:U37 L35:Q35 S35">
+    <cfRule type="expression" dxfId="140" priority="723">
+      <formula>L33&lt;L32</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q36">
+    <cfRule type="expression" dxfId="132" priority="1770">
+      <formula>Q36&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R36">
+    <cfRule type="expression" dxfId="128" priority="1766">
+      <formula>R36&lt;R35</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C33:E34">
+    <cfRule type="expression" dxfId="123" priority="79">
+      <formula>C33&lt;C32</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA33:AA37">
+    <cfRule type="expression" dxfId="118" priority="44">
+      <formula>AA33&lt;AA32</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA33:AA37">
+    <cfRule type="expression" dxfId="117" priority="84">
+      <formula>AA33&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC33:AC37 V33:AB34 V35 X35:AA35">
+    <cfRule type="expression" dxfId="116" priority="724">
+      <formula>V33&lt;V32</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD33:AD37">
+    <cfRule type="expression" dxfId="114" priority="82">
+      <formula>AD33&lt;AD32</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE33:AI34">
+    <cfRule type="expression" dxfId="111" priority="85">
+      <formula>AE33&lt;AE32</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ33:AJ37">
+    <cfRule type="expression" dxfId="110" priority="46">
+      <formula>AJ33&lt;AJ32</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK6:AK12">
+    <cfRule type="expression" dxfId="109" priority="1643">
+      <formula>AK6&lt;AK5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK13:AL15">
+    <cfRule type="expression" dxfId="108" priority="1723">
+      <formula>AK13&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL9:AL14 AL15:AN34 AK16:AK37 AK20:AN21 T36:W37 Z36:Z37 AB36:AB37 AE36:AI37 Q37:R37">
+    <cfRule type="expression" dxfId="107" priority="1660">
+      <formula>Q9&lt;Q8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AO9:AO34">
+    <cfRule type="expression" dxfId="106" priority="1668">
+      <formula>AO9&lt;#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B6">
-    <cfRule type="expression" dxfId="117" priority="13">
+    <cfRule type="expression" dxfId="42" priority="13">
       <formula>B6&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7:B35">
-    <cfRule type="expression" dxfId="116" priority="20">
+  <conditionalFormatting sqref="B7:B32">
+    <cfRule type="expression" dxfId="41" priority="20">
       <formula>B7&lt;B6</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B11:B29">
-    <cfRule type="expression" dxfId="115" priority="34">
+  <conditionalFormatting sqref="B11:B32">
+    <cfRule type="expression" dxfId="40" priority="34">
       <formula>B11&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C35 E35:E37">
-    <cfRule type="expression" dxfId="114" priority="671">
-      <formula>C35&lt;C34</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C6:D6">
-    <cfRule type="expression" dxfId="113" priority="15">
+    <cfRule type="expression" dxfId="39" priority="15">
       <formula>C6&lt;C5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7:D7 H7:J7 R7 T7 W7 AB7">
-    <cfRule type="expression" dxfId="112" priority="22">
+    <cfRule type="expression" dxfId="38" priority="22">
       <formula>C7&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8:D14">
-    <cfRule type="expression" dxfId="111" priority="25">
+    <cfRule type="expression" dxfId="37" priority="25">
       <formula>C8&lt;C7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C36:D37">
-    <cfRule type="expression" dxfId="110" priority="1724">
-      <formula>C36&lt;C35</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D35 B36:B37">
-    <cfRule type="expression" dxfId="109" priority="1711">
-      <formula>B35&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="E6:E14">
-    <cfRule type="expression" dxfId="108" priority="5">
+    <cfRule type="expression" dxfId="36" priority="5">
       <formula>E6&lt;E5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6:F37">
-    <cfRule type="expression" dxfId="107" priority="4">
+  <conditionalFormatting sqref="F6:F32">
+    <cfRule type="expression" dxfId="35" priority="4">
       <formula>F6&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G6:G37">
-    <cfRule type="expression" dxfId="106" priority="2">
+  <conditionalFormatting sqref="G6:G32">
+    <cfRule type="expression" dxfId="34" priority="2">
       <formula>G6&lt;G5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G36:J37 L36:O37">
-    <cfRule type="expression" dxfId="105" priority="1558">
-      <formula>G36&lt;G35</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G6:O6">
-    <cfRule type="expression" dxfId="104" priority="6">
+    <cfRule type="expression" dxfId="33" priority="6">
       <formula>G6&lt;G5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H35:I35 R35 T35 W35 AB35 AE35:AI35 P36:P37 S36:S37 X36:Y37">
-    <cfRule type="expression" dxfId="103" priority="1710">
-      <formula>H35&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H8:J18 H19:I34">
-    <cfRule type="expression" dxfId="102" priority="26">
+  <conditionalFormatting sqref="H8:J18 H19:I32">
+    <cfRule type="expression" dxfId="32" priority="26">
       <formula>H8&lt;H7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J19:J35">
-    <cfRule type="expression" dxfId="101" priority="37">
+  <conditionalFormatting sqref="J19:J32">
+    <cfRule type="expression" dxfId="31" priority="37">
       <formula>J19&lt;J18</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K11:L21 K22:K37">
-    <cfRule type="expression" dxfId="100" priority="29">
+  <conditionalFormatting sqref="K11:L21 K22:K32">
+    <cfRule type="expression" dxfId="30" priority="29">
       <formula>K11&lt;K10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7:O10">
-    <cfRule type="expression" dxfId="99" priority="16">
+    <cfRule type="expression" dxfId="29" priority="16">
       <formula>K7&lt;K6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L22:M25">
-    <cfRule type="expression" dxfId="98" priority="38">
+    <cfRule type="expression" dxfId="28" priority="38">
       <formula>L22&lt;L21</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L30:T34 U30:U37 L35:Q35 S35">
-    <cfRule type="expression" dxfId="97" priority="680">
-      <formula>L30&lt;L29</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L26:Z27 L28:AC29">
-    <cfRule type="expression" dxfId="96" priority="40">
+  <conditionalFormatting sqref="L26:Z27 L28:AC28">
+    <cfRule type="expression" dxfId="27" priority="40">
       <formula>L26&lt;L25</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M11:M17">
-    <cfRule type="expression" dxfId="95" priority="31">
+    <cfRule type="expression" dxfId="26" priority="31">
       <formula>M11&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N11:O12">
-    <cfRule type="expression" dxfId="94" priority="30">
+    <cfRule type="expression" dxfId="25" priority="30">
       <formula>N11&lt;N10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N13:T24 N25:Z25">
-    <cfRule type="expression" dxfId="93" priority="33">
+    <cfRule type="expression" dxfId="24" priority="33">
       <formula>N13&lt;N12</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P8:P12 V8:V12">
-    <cfRule type="expression" dxfId="92" priority="28">
+    <cfRule type="expression" dxfId="23" priority="28">
       <formula>P8&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P6:Q6 X6:Y6 S6:S10">
-    <cfRule type="expression" dxfId="91" priority="12">
+    <cfRule type="expression" dxfId="22" priority="12">
       <formula>P6&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P7:Q7">
-    <cfRule type="expression" dxfId="90" priority="21">
+    <cfRule type="expression" dxfId="21" priority="21">
       <formula>P7&lt;P6</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q36">
-    <cfRule type="expression" dxfId="89" priority="1727">
-      <formula>Q36&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="Q8:R10">
-    <cfRule type="expression" dxfId="88" priority="27">
+    <cfRule type="expression" dxfId="20" priority="27">
       <formula>Q8&lt;Q7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q11:T12">
-    <cfRule type="expression" dxfId="87" priority="32">
+    <cfRule type="expression" dxfId="19" priority="32">
       <formula>Q11&lt;Q10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R6">
-    <cfRule type="expression" dxfId="86" priority="14">
+    <cfRule type="expression" dxfId="18" priority="14">
       <formula>R6&lt;R5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R36">
-    <cfRule type="expression" dxfId="85" priority="1723">
-      <formula>R36&lt;R35</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="T8:T10 AB8:AC10 AE8:AI10 AB11:AI27">
-    <cfRule type="expression" dxfId="84" priority="23">
+    <cfRule type="expression" dxfId="17" priority="23">
       <formula>T8&lt;T7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T6:W6 Z6 AB6">
-    <cfRule type="expression" dxfId="83" priority="11">
+    <cfRule type="expression" dxfId="16" priority="11">
       <formula>T6&lt;T5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U6:U24">
-    <cfRule type="expression" dxfId="82" priority="9">
+    <cfRule type="expression" dxfId="15" priority="9">
       <formula>U6&lt;U5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V7">
-    <cfRule type="expression" dxfId="81" priority="17">
+    <cfRule type="expression" dxfId="14" priority="17">
       <formula>V7&lt;V6</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V13:X14 C15:E34">
-    <cfRule type="expression" dxfId="80" priority="36">
+  <conditionalFormatting sqref="V13:X14 C15:E32">
+    <cfRule type="expression" dxfId="13" priority="36">
       <formula>C13&lt;C12</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V15:Z24 M18:M21">
-    <cfRule type="expression" dxfId="79" priority="35">
+    <cfRule type="expression" dxfId="12" priority="35">
       <formula>M15&lt;M14</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="V29:AC32">
+    <cfRule type="expression" dxfId="11" priority="43">
+      <formula>V29&lt;V28</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="W8:W12">
-    <cfRule type="expression" dxfId="78" priority="24">
+    <cfRule type="expression" dxfId="10" priority="24">
       <formula>W8&lt;W7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y7:Z14">
-    <cfRule type="expression" dxfId="77" priority="18">
+    <cfRule type="expression" dxfId="9" priority="18">
       <formula>Y7&lt;Y6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA6:AA12">
-    <cfRule type="expression" dxfId="76" priority="8">
+    <cfRule type="expression" dxfId="8" priority="8">
       <formula>AA6&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA6:AA37">
-    <cfRule type="expression" dxfId="75" priority="1">
+  <conditionalFormatting sqref="AA6:AA32">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>AA6&lt;AA5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA28:AA37">
-    <cfRule type="expression" dxfId="74" priority="41">
+  <conditionalFormatting sqref="AA28:AA32">
+    <cfRule type="expression" dxfId="6" priority="41">
       <formula>AA28&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA30:AC30 Z30:Z31 V30:Y34 AA31:AB31 AC31:AC37 Z32:AB34 V35 X35:AA35">
-    <cfRule type="expression" dxfId="73" priority="681">
-      <formula>V30&lt;V29</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="AC6:AC7">
-    <cfRule type="expression" dxfId="72" priority="10">
+    <cfRule type="expression" dxfId="5" priority="10">
       <formula>AC6&lt;AC5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD28:AD37">
-    <cfRule type="expression" dxfId="71" priority="39">
+  <conditionalFormatting sqref="AD28:AD32">
+    <cfRule type="expression" dxfId="4" priority="39">
       <formula>AD28&lt;AD27</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD6:AI6">
-    <cfRule type="expression" dxfId="70" priority="7">
+    <cfRule type="expression" dxfId="3" priority="7">
       <formula>AD6&lt;AD5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD7:AI7 X7:X12 AD8:AD10">
-    <cfRule type="expression" dxfId="69" priority="19">
+    <cfRule type="expression" dxfId="2" priority="19">
       <formula>X7&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE28:AI34">
-    <cfRule type="expression" dxfId="68" priority="42">
-      <formula>AE28&lt;AE27</formula>
+  <conditionalFormatting sqref="AE28:AI32 L29:U32">
+    <cfRule type="expression" dxfId="1" priority="42">
+      <formula>L28&lt;L27</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AJ6:AJ37">
-    <cfRule type="expression" dxfId="67" priority="3">
+  <conditionalFormatting sqref="AJ6:AJ32">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>AJ6&lt;AJ5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AK6:AK12">
-    <cfRule type="expression" dxfId="66" priority="1600">
-      <formula>AK6&lt;AK5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AK13:AL15">
-    <cfRule type="expression" dxfId="65" priority="1680">
-      <formula>AK13&lt;#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AL9:AL14 AL15:AN34 AK16:AK37 AK20:AN21 T36:W37 Z36:Z37 AB36:AB37 AE36:AI37 Q37:R37">
-    <cfRule type="expression" dxfId="64" priority="1617">
-      <formula>Q9&lt;Q8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AO9:AO34">
-    <cfRule type="expression" dxfId="63" priority="1625">
-      <formula>AO9&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.1" right="0.5" top="0.32" bottom="0.25" header="0.25" footer="0.25"/>
@@ -17690,8 +18374,7 @@
     <col min="11" max="11" width="29.7109375" style="469" customWidth="1"/>
     <col min="12" max="12" width="30.5703125" style="469" customWidth="1"/>
     <col min="13" max="13" width="29.7109375" style="470" customWidth="1"/>
-    <col min="14" max="28" width="29.7109375" style="469" customWidth="1"/>
-    <col min="29" max="33" width="29.7109375" style="469" hidden="1" customWidth="1"/>
+    <col min="14" max="33" width="29.7109375" style="469" customWidth="1"/>
     <col min="34" max="34" width="29.7109375" style="468" customWidth="1"/>
     <col min="35" max="35" width="24.7109375" style="468" customWidth="1"/>
     <col min="36" max="36" width="24.7109375" style="291" customWidth="1"/>
@@ -18764,7 +19447,7 @@
       <c r="AG15" s="718"/>
       <c r="AH15" s="500">
         <f>IF(AH12=0,"",+(AH36*10)/AH12)</f>
-        <v>11.25</v>
+        <v>11.390949554896142</v>
       </c>
       <c r="AI15" s="502"/>
       <c r="AJ15" s="503"/>
@@ -19194,13 +19877,13 @@
         <f>+'Water '!$D30</f>
         <v>0</v>
       </c>
-      <c r="Z20" s="509" t="str">
+      <c r="Z20" s="509">
         <f>+'Water '!$D31</f>
-        <v>0</v>
-      </c>
-      <c r="AA20" s="509" t="str">
+        <v>11</v>
+      </c>
+      <c r="AA20" s="509">
         <f>+'Water '!$D32</f>
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AB20" s="509" t="str">
         <f>+'Water '!$D33</f>
@@ -19225,7 +19908,7 @@
       <c r="AG20" s="509"/>
       <c r="AH20" s="484">
         <f>SUM($B20:AF20)</f>
-        <v>3918</v>
+        <v>4002</v>
       </c>
       <c r="AI20" s="484"/>
       <c r="AJ20" s="485"/>
@@ -19326,17 +20009,17 @@
         <f>+'Water '!$E29</f>
         <v>193</v>
       </c>
-      <c r="Y21" s="512" t="str">
+      <c r="Y21" s="512">
         <f>+'Water '!$E30</f>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="Z21" s="511" t="str">
         <f>+'Water '!$E31</f>
         <v>0</v>
       </c>
-      <c r="AA21" s="509" t="str">
+      <c r="AA21" s="509">
         <f>+'Water '!$E32</f>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AB21" s="509" t="str">
         <f>+'Water '!$E33</f>
@@ -19361,7 +20044,7 @@
       <c r="AG21" s="509"/>
       <c r="AH21" s="484">
         <f>SUM($B21:AF21)</f>
-        <v>3071</v>
+        <v>3180</v>
       </c>
       <c r="AI21" s="484"/>
     </row>
@@ -19463,15 +20146,15 @@
       </c>
       <c r="Y22" s="514">
         <f>SUM(Y19:Y21)</f>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="Z22" s="514">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA22" s="515">
         <f>SUM(AA19:AA21)</f>
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="AB22" s="515">
         <f>SUM(AB19:AB21)</f>
@@ -19496,7 +20179,7 @@
       <c r="AG22" s="515"/>
       <c r="AH22" s="516">
         <f>SUM($B22:AF22)</f>
-        <v>6989</v>
+        <v>7182</v>
       </c>
       <c r="AI22" s="514"/>
       <c r="AJ22" s="517"/>
@@ -19827,7 +20510,7 @@
       </c>
       <c r="Y26" s="521">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>32.85</v>
       </c>
       <c r="Z26" s="521">
         <f t="shared" si="6"/>
@@ -19835,7 +20518,7 @@
       </c>
       <c r="AA26" s="521">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>52.56</v>
       </c>
       <c r="AB26" s="521">
         <f t="shared" si="6"/>
@@ -19860,15 +20543,15 @@
       <c r="AG26" s="521"/>
       <c r="AH26" s="484">
         <f>SUM($B26:AF26)</f>
-        <v>2386.37</v>
+        <v>2471.7799999999997</v>
       </c>
       <c r="AI26" s="523">
         <f>AH29+AH45+AH36</f>
-        <v>7309</v>
+        <v>7484</v>
       </c>
       <c r="AK26" s="524">
         <f>(AI26*10)/AH9</f>
-        <v>11.725297001821184</v>
+        <v>12.006036771327095</v>
       </c>
     </row>
     <row r="27" spans="1:149" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -20115,15 +20798,15 @@
       </c>
       <c r="Y29" s="509">
         <f>'Water '!$H30</f>
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="Z29" s="509">
         <f>'Water '!$H31</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA29" s="509">
         <f>'Water '!$H32</f>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AB29" s="509">
         <f>'Water '!$H33</f>
@@ -20148,7 +20831,7 @@
       <c r="AG29" s="509"/>
       <c r="AH29" s="484">
         <f>SUM($B29:AF29)</f>
-        <v>3829</v>
+        <v>3945</v>
       </c>
       <c r="AI29" s="484"/>
       <c r="AJ29" s="484"/>
@@ -20250,9 +20933,9 @@
         <f t="shared" si="7"/>
         <v>179</v>
       </c>
-      <c r="Y30" s="509" t="str">
+      <c r="Y30" s="509">
         <f>Y36</f>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Z30" s="509" t="str">
         <f t="shared" si="7"/>
@@ -20285,7 +20968,7 @@
       <c r="AG30" s="509"/>
       <c r="AH30" s="484">
         <f>AH36</f>
-        <v>3033</v>
+        <v>3071</v>
       </c>
       <c r="AI30" s="484"/>
       <c r="AJ30" s="484"/>
@@ -20387,17 +21070,17 @@
         <f t="shared" si="8"/>
         <v>26</v>
       </c>
-      <c r="Y31" s="509" t="str">
+      <c r="Y31" s="509">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="Z31" s="509" t="str">
+        <v>8</v>
+      </c>
+      <c r="Z31" s="509">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AA31" s="509" t="str">
+        <v>7</v>
+      </c>
+      <c r="AA31" s="509">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB31" s="509" t="str">
         <f t="shared" si="8"/>
@@ -20422,7 +21105,7 @@
       <c r="AG31" s="509"/>
       <c r="AH31" s="484">
         <f>AH45</f>
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="AI31" s="484"/>
       <c r="AJ31" s="484"/>
@@ -20525,15 +21208,15 @@
       </c>
       <c r="Y32" s="527">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="Z32" s="527">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AA32" s="527">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AB32" s="527">
         <f t="shared" si="9"/>
@@ -20558,7 +21241,7 @@
       <c r="AG32" s="527"/>
       <c r="AH32" s="526">
         <f>SUM($B32:AF32)</f>
-        <v>7309</v>
+        <v>7484</v>
       </c>
       <c r="AI32" s="526"/>
       <c r="AJ32" s="528"/>
@@ -20799,9 +21482,9 @@
         <f>+'Water '!$J29</f>
         <v>179</v>
       </c>
-      <c r="Y36" s="535" t="str">
+      <c r="Y36" s="535">
         <f>+'Water '!$J30</f>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Z36" s="535" t="str">
         <f>+'Water '!$J31</f>
@@ -20834,7 +21517,7 @@
       <c r="AG36" s="508"/>
       <c r="AH36" s="484">
         <f>SUM($B36:AF36)</f>
-        <v>3033</v>
+        <v>3071</v>
       </c>
       <c r="AI36" s="484"/>
     </row>
@@ -21609,9 +22292,9 @@
         <f>+'Water '!$N29</f>
         <v>41</v>
       </c>
-      <c r="Y41" s="539" t="str">
+      <c r="Y41" s="539">
         <f>+'Water '!$N30</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z41" s="539" t="str">
         <f>+'Water '!$N31</f>
@@ -21644,7 +22327,7 @@
       <c r="AG41" s="539"/>
       <c r="AH41" s="514">
         <f>SUM($B41:AF41)</f>
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="AI41" s="514"/>
       <c r="AJ41" s="514"/>
@@ -21858,9 +22541,9 @@
         <f>+'Water '!$O29</f>
         <v>112</v>
       </c>
-      <c r="Y42" s="508" t="str">
+      <c r="Y42" s="508">
         <f>+'Water '!$O30</f>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="Z42" s="508" t="str">
         <f>+'Water '!$O31</f>
@@ -21893,7 +22576,7 @@
       <c r="AG42" s="508"/>
       <c r="AH42" s="540">
         <f>SUM($B42:AF42)</f>
-        <v>1704</v>
+        <v>1735</v>
       </c>
       <c r="AI42" s="508"/>
       <c r="AJ42" s="508"/>
@@ -22334,9 +23017,9 @@
         <f>+'Water '!$M31</f>
         <v>0</v>
       </c>
-      <c r="AA44" s="508" t="str">
+      <c r="AA44" s="508">
         <f>+'Water '!$M32</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB44" s="508" t="str">
         <f>+'Water '!$M33</f>
@@ -22361,7 +23044,7 @@
       <c r="AG44" s="508"/>
       <c r="AH44" s="484">
         <f>SUM($B44:AF44)</f>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AI44" s="484"/>
       <c r="AJ44" s="291"/>
@@ -22575,17 +23258,17 @@
         <f>+'Water '!$Q29</f>
         <v>26</v>
       </c>
-      <c r="Y45" s="539" t="str">
+      <c r="Y45" s="539">
         <f>+'Water '!$Q30</f>
-        <v>0</v>
-      </c>
-      <c r="Z45" s="539" t="str">
+        <v>8</v>
+      </c>
+      <c r="Z45" s="539">
         <f>+'Water '!$Q31</f>
-        <v>0</v>
-      </c>
-      <c r="AA45" s="539" t="str">
+        <v>7</v>
+      </c>
+      <c r="AA45" s="539">
         <f>+'Water '!$Q32</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB45" s="539" t="str">
         <f>+'Water '!$Q33</f>
@@ -22610,7 +23293,7 @@
       <c r="AG45" s="539"/>
       <c r="AH45" s="514">
         <f>SUM($B45:AF45)</f>
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="AI45" s="514"/>
       <c r="AJ45" s="514"/>
@@ -23292,15 +23975,15 @@
       </c>
       <c r="Y50" s="484">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="Z50" s="484">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA50" s="484">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AB50" s="484">
         <f t="shared" si="10"/>
@@ -23325,7 +24008,7 @@
       <c r="AG50" s="484"/>
       <c r="AH50" s="484">
         <f>SUM($B50:AF50)</f>
-        <v>6203</v>
+        <v>6300</v>
       </c>
       <c r="AI50" s="484"/>
     </row>
@@ -23548,14 +24231,14 @@
       <c r="AG54" s="545"/>
       <c r="AH54" s="546">
         <f>+(AH36*10)/AH$9</f>
-        <v>4.8656212623510262</v>
+        <v>4.9265818980151668</v>
       </c>
       <c r="AI54" s="546">
         <v>3.2</v>
       </c>
       <c r="AJ54" s="547">
         <f t="shared" ref="AJ54:AJ67" si="13">AI54-AH54</f>
-        <v>-1.665621262351026</v>
+        <v>-1.7265818980151666</v>
       </c>
     </row>
     <row r="55" spans="1:59" s="553" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -24254,14 +24937,14 @@
       <c r="AG59" s="549"/>
       <c r="AH59" s="549">
         <f t="shared" si="14"/>
-        <v>0.97857862513489147</v>
+        <v>0.9882039886608085</v>
       </c>
       <c r="AI59" s="550">
         <v>0.7</v>
       </c>
       <c r="AJ59" s="551">
         <f t="shared" si="13"/>
-        <v>-0.27857862513489151</v>
+        <v>-0.28820398866080854</v>
       </c>
       <c r="AK59" s="474"/>
       <c r="AL59" s="474"/>
@@ -24418,14 +25101,14 @@
       <c r="AG60" s="545"/>
       <c r="AH60" s="568">
         <f t="shared" si="14"/>
-        <v>2.7336032413604183</v>
+        <v>2.7833342862443224</v>
       </c>
       <c r="AI60" s="555">
         <v>2.1</v>
       </c>
       <c r="AJ60" s="547">
         <f t="shared" si="13"/>
-        <v>-0.63360324136041823</v>
+        <v>-0.68333428624432235</v>
       </c>
     </row>
     <row r="61" spans="1:59" s="504" customFormat="1" x14ac:dyDescent="0.35">
@@ -24723,14 +25406,14 @@
       <c r="AG62" s="545"/>
       <c r="AH62" s="555">
         <f>+(AH44*10)/AH$9</f>
-        <v>9.6253635259169662E-2</v>
+        <v>9.7857862513489158E-2</v>
       </c>
       <c r="AI62" s="555">
         <v>0.1</v>
       </c>
       <c r="AJ62" s="547">
         <f t="shared" si="13"/>
-        <v>3.7463647408303435E-3</v>
+        <v>2.1421374865108478E-3</v>
       </c>
     </row>
     <row r="63" spans="1:59" s="504" customFormat="1" x14ac:dyDescent="0.35">
@@ -24864,14 +25547,14 @@
       <c r="AG63" s="549"/>
       <c r="AH63" s="550">
         <f>+(AH45*10)/AH$9</f>
-        <v>0.71708958268081391</v>
+        <v>0.75077835502152335</v>
       </c>
       <c r="AI63" s="550">
         <v>0.6</v>
       </c>
       <c r="AJ63" s="551">
         <f t="shared" si="13"/>
-        <v>-0.11708958268081393</v>
+        <v>-0.15077835502152337</v>
       </c>
       <c r="AK63" s="474"/>
       <c r="AL63" s="474"/>
@@ -25396,7 +26079,7 @@
       <c r="AG68" s="585"/>
       <c r="AH68" s="584">
         <f t="shared" si="29"/>
-        <v>9.9510216585438229</v>
+        <v>10.106631702212814</v>
       </c>
       <c r="AI68" s="584">
         <f>SUM(AI54:AI63,AI65)</f>
@@ -25404,7 +26087,7 @@
       </c>
       <c r="AJ68" s="547">
         <f t="shared" si="29"/>
-        <v>-0.35102165854382278</v>
+        <v>-0.50663170221281351</v>
       </c>
       <c r="AK68" s="468"/>
       <c r="AL68" s="291"/>
@@ -25561,7 +26244,7 @@
       <c r="AG69" s="588"/>
       <c r="AH69" s="587">
         <f t="shared" si="30"/>
-        <v>3.3897321883770912</v>
+        <v>3.4410674605153151</v>
       </c>
       <c r="AI69" s="587">
         <f t="shared" si="30"/>
@@ -25569,7 +26252,7 @@
       </c>
       <c r="AJ69" s="587">
         <f t="shared" si="30"/>
-        <v>-0.48973218837709143</v>
+        <v>-0.54106746051531507</v>
       </c>
       <c r="AK69" s="589"/>
       <c r="AL69" s="291"/>
@@ -25726,17 +26409,17 @@
         <f>+'Water '!$F29</f>
         <v>202</v>
       </c>
-      <c r="Y71" s="593" t="str">
+      <c r="Y71" s="593">
         <f>+'Water '!$F30</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Z71" s="593" t="str">
         <f>+'Water '!$F31</f>
         <v>0</v>
       </c>
-      <c r="AA71" s="593" t="str">
+      <c r="AA71" s="593">
         <f>+'Water '!$F32</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AB71" s="593" t="str">
         <f>+'Water '!$F33</f>
@@ -25761,7 +26444,7 @@
       <c r="AG71" s="593"/>
       <c r="AH71" s="594">
         <f>SUM($B71:AF71)</f>
-        <v>3269</v>
+        <v>3386</v>
       </c>
       <c r="AI71" s="594"/>
       <c r="AJ71" s="595"/>
@@ -26715,13 +27398,13 @@
         <v>7265</v>
       </c>
       <c r="Y80" s="613">
-        <v>0</v>
+        <v>3898</v>
       </c>
       <c r="Z80" s="613">
-        <v>0</v>
+        <v>3808</v>
       </c>
       <c r="AA80" s="613">
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="AB80" s="613">
         <v>0</v>
@@ -26741,7 +27424,7 @@
       <c r="AG80" s="613"/>
       <c r="AH80" s="594">
         <f>SUM(B80:AF80)</f>
-        <v>137781</v>
+        <v>147983</v>
       </c>
       <c r="AI80" s="594"/>
       <c r="AJ80" s="614"/>
@@ -26905,16 +27588,16 @@
         <v>8694.6</v>
       </c>
       <c r="W82" s="617">
-        <v>0</v>
+        <v>5329</v>
       </c>
       <c r="X82" s="617">
-        <v>0</v>
+        <v>4892.3</v>
       </c>
       <c r="Y82" s="618">
-        <v>0</v>
+        <v>3668.7</v>
       </c>
       <c r="Z82" s="618">
-        <v>0</v>
+        <v>1431.7</v>
       </c>
       <c r="AA82" s="617">
         <v>0</v>
@@ -26929,7 +27612,7 @@
         <v>0</v>
       </c>
       <c r="AE82" s="617">
-        <v>167808.9</v>
+        <v>183130.6</v>
       </c>
       <c r="AF82" s="617">
         <v>0</v>
@@ -26937,7 +27620,7 @@
       <c r="AG82" s="617"/>
       <c r="AH82" s="594">
         <f>SUM(B82:AF82)</f>
-        <v>318531</v>
+        <v>349174.4</v>
       </c>
       <c r="AI82" s="594"/>
       <c r="AJ82" s="614"/>
@@ -27040,16 +27723,16 @@
         <v>1429.6</v>
       </c>
       <c r="Y83" s="702">
-        <v>0</v>
+        <v>1431</v>
       </c>
       <c r="Z83" s="702">
-        <v>0</v>
+        <v>1084.3</v>
       </c>
       <c r="AA83" s="621">
-        <v>0</v>
+        <v>1172.7</v>
       </c>
       <c r="AB83" s="621">
-        <v>0</v>
+        <v>1431.7</v>
       </c>
       <c r="AC83" s="621">
         <v>0</v>
@@ -27066,7 +27749,7 @@
       <c r="AG83" s="621"/>
       <c r="AH83" s="594">
         <f>SUM(B83:AF83)</f>
-        <v>30027.899999999994</v>
+        <v>35147.599999999991</v>
       </c>
       <c r="AI83" s="594"/>
       <c r="AJ83" s="594"/>
@@ -27168,14 +27851,14 @@
       <c r="X84" s="620">
         <v>3071.5999999998603</v>
       </c>
-      <c r="Y84" s="620" t="str">
-        <v>0</v>
+      <c r="Y84" s="620">
+        <v>706.4000000001397</v>
       </c>
       <c r="Z84" s="620" t="str">
         <v>0</v>
       </c>
-      <c r="AA84" s="620" t="str">
-        <v>0</v>
+      <c r="AA84" s="620">
+        <v>581.80000000004657</v>
       </c>
       <c r="AB84" s="620" t="str">
         <v>0</v>
@@ -27195,7 +27878,7 @@
       <c r="AG84" s="620"/>
       <c r="AH84" s="621">
         <f>SUM($B84:AF84)</f>
-        <v>52395.399999999907</v>
+        <v>53683.600000000093</v>
       </c>
       <c r="AI84" s="594"/>
       <c r="AJ84" s="614"/>
@@ -27699,18 +28382,18 @@
       <c r="AG90" s="627"/>
       <c r="AH90" s="659">
         <f>IF(AH$9=0,"0",+(AH22*10)/AH$9)</f>
-        <v>11.211944280438946</v>
+        <v>11.521560140522608</v>
       </c>
       <c r="AI90" s="662">
         <v>10.199999999999999</v>
       </c>
       <c r="AJ90" s="665">
         <f>+AI90-AH90</f>
-        <v>-1.0119442804389465</v>
+        <v>-1.3215601405226085</v>
       </c>
       <c r="AK90" s="667">
         <f>AH90/AI90*100</f>
-        <v>109.92102235724457</v>
+        <v>112.95647196590792</v>
       </c>
       <c r="AL90" s="629"/>
       <c r="AM90" s="630"/>
@@ -28269,18 +28952,18 @@
       <c r="AG94" s="627"/>
       <c r="AH94" s="670">
         <f>IF(AH$9=0,"0",+(AH80+AH83)/AH$9)</f>
-        <v>26.920361089737458</v>
+        <v>29.378309961988155</v>
       </c>
       <c r="AI94" s="674">
         <v>22</v>
       </c>
       <c r="AJ94" s="675">
         <f>AI94-AH94</f>
-        <v>-4.9203610897374581</v>
+        <v>-7.3783099619881547</v>
       </c>
       <c r="AK94" s="673">
         <f>AH94/AI94*100</f>
-        <v>122.36527768062481</v>
+        <v>133.53777255449162</v>
       </c>
       <c r="AL94" s="629"/>
       <c r="AM94" s="630"/>
@@ -28502,18 +29185,18 @@
       <c r="AG96" s="627"/>
       <c r="AH96" s="660">
         <f>IF(AH$9=0,"0",+(AH84)/AH$9)</f>
-        <v>8.405412868097148</v>
+        <v>8.6120694229986157</v>
       </c>
       <c r="AI96" s="663">
         <v>7.2</v>
       </c>
       <c r="AJ96" s="677">
         <f>AI96-AH96</f>
-        <v>-1.2054128680971479</v>
+        <v>-1.4120694229986155</v>
       </c>
       <c r="AK96" s="668">
         <f t="shared" si="36"/>
-        <v>116.74184539023817</v>
+        <v>119.61207531942522</v>
       </c>
       <c r="AL96" s="629"/>
       <c r="AM96" s="630"/>
@@ -29524,15 +30207,15 @@
       </c>
       <c r="Y116" s="650">
         <f>'Daily KPIs'!Y80</f>
-        <v>0</v>
+        <v>3898</v>
       </c>
       <c r="Z116" s="650">
         <f>'Daily KPIs'!Z80</f>
-        <v>0</v>
+        <v>3808</v>
       </c>
       <c r="AA116" s="650">
         <f>'Daily KPIs'!AA80</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="AB116" s="650">
         <f>'Daily KPIs'!AB80</f>
@@ -29557,7 +30240,7 @@
       <c r="AG116" s="650"/>
       <c r="AH116" s="649">
         <f>'Daily KPIs'!AH80</f>
-        <v>137781</v>
+        <v>147983</v>
       </c>
     </row>
     <row r="117" spans="2:34" hidden="1" x14ac:dyDescent="0.35">
@@ -29647,7 +30330,7 @@
       </c>
       <c r="AH140" s="870">
         <f>AH83/(AH83+AH80)</f>
-        <v>0.17894104543918704</v>
+        <v>0.19192641754026904</v>
       </c>
       <c r="AM140" s="751"/>
     </row>
@@ -29784,45 +30467,45 @@
   </mergeCells>
   <phoneticPr fontId="32" type="noConversion"/>
   <conditionalFormatting sqref="B93:C93 AH93">
-    <cfRule type="cellIs" dxfId="35" priority="127" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="78" priority="127" operator="greaterThan">
       <formula>$AI$93</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B90:AF90">
-    <cfRule type="cellIs" dxfId="34" priority="36" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="77" priority="36" operator="greaterThan">
       <formula>10.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92:AF92">
-    <cfRule type="cellIs" dxfId="33" priority="26" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="76" priority="26" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="27" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="75" priority="27" operator="lessThanOrEqual">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:AF93">
-    <cfRule type="cellIs" dxfId="31" priority="34" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="74" priority="34" operator="greaterThan">
       <formula>1.7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B94:AF94">
-    <cfRule type="cellIs" dxfId="30" priority="33" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="73" priority="33" operator="greaterThan">
       <formula>22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96:AF96">
-    <cfRule type="cellIs" dxfId="29" priority="32" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="72" priority="32" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:AG22">
-    <cfRule type="cellIs" dxfId="28" priority="101" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="71" priority="101" operator="greaterThan">
       <formula>400</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42:AG42">
-    <cfRule type="cellIs" dxfId="27" priority="47" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="70" priority="47" operator="greaterThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29837,129 +30520,129 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B94:AG94">
-    <cfRule type="cellIs" dxfId="26" priority="1174" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="69" priority="1174" operator="greaterThan">
       <formula>$AI$94</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96:AG96">
-    <cfRule type="cellIs" dxfId="25" priority="1176" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="68" priority="1176" operator="greaterThan">
       <formula>$AI$96</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:AH15">
-    <cfRule type="cellIs" dxfId="24" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="67" priority="1" operator="greaterThan">
       <formula>3.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54:AH54">
-    <cfRule type="cellIs" dxfId="23" priority="123" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="66" priority="123" operator="greaterThan">
       <formula>3.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B56:AH56">
-    <cfRule type="cellIs" dxfId="22" priority="61" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="65" priority="61" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B57:AH57 B59:AH59 B61:AH61">
-    <cfRule type="cellIs" dxfId="21" priority="62" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="64" priority="62" operator="greaterThan">
       <formula>0.7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58:AH58 B62:AH62">
-    <cfRule type="cellIs" dxfId="20" priority="63" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="63" priority="63" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B60:AH60">
-    <cfRule type="cellIs" dxfId="19" priority="22" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="62" priority="22" operator="greaterThan">
       <formula>2.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B65:AH65">
-    <cfRule type="cellIs" dxfId="18" priority="56" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="61" priority="56" operator="greaterThan">
       <formula>0.3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68:AH68">
-    <cfRule type="cellIs" dxfId="17" priority="58" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="60" priority="58" operator="greaterThan">
       <formula>9.6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69:AH69">
-    <cfRule type="cellIs" dxfId="16" priority="59" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="59" priority="59" operator="greaterThan">
       <formula>2.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92:AH92">
-    <cfRule type="cellIs" dxfId="15" priority="48" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="48" operator="greaterThan">
       <formula>5.04</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93:AH93">
-    <cfRule type="cellIs" dxfId="14" priority="44" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="57" priority="44" operator="greaterThan">
       <formula>1.7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="43" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="56" priority="43" operator="greaterThan">
       <formula>1.7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96:AH96">
-    <cfRule type="cellIs" dxfId="12" priority="37" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="55" priority="37" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E96">
-    <cfRule type="cellIs" dxfId="11" priority="39" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="54" priority="39" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I63:AH63">
-    <cfRule type="cellIs" dxfId="10" priority="68" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="53" priority="68" operator="greaterThan">
       <formula>0.6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC54:AG54">
-    <cfRule type="cellIs" dxfId="9" priority="82" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="52" priority="82" operator="greaterThan">
       <formula>$AI$54</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC55:AG59 AC61:AG61 AC63:AG63 B64:AG64">
-    <cfRule type="cellIs" dxfId="8" priority="1135" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="51" priority="1135" operator="greaterThan">
       <formula>$AI59</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH94">
-    <cfRule type="cellIs" dxfId="7" priority="28" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="50" priority="28" operator="lessThanOrEqual">
       <formula>22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH94:AH96 B90:AH90 AH91">
-    <cfRule type="cellIs" dxfId="6" priority="1168" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="49" priority="1168" operator="greaterThan">
       <formula>$AI$90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH96">
-    <cfRule type="cellIs" dxfId="5" priority="29" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="48" priority="29" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="30" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="30" operator="lessThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="40" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="46" priority="40" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ8">
-    <cfRule type="cellIs" dxfId="2" priority="105" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="45" priority="105" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="106" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="106" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK90:AK96">
-    <cfRule type="cellIs" dxfId="0" priority="50" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="43" priority="50" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
@@ -31739,11 +32422,11 @@
       </c>
       <c r="C30" s="55">
         <f t="shared" si="1"/>
-        <v>-256912</v>
+        <v>0</v>
       </c>
       <c r="D30" s="55">
         <f t="shared" si="2"/>
-        <v>1112393</v>
+        <v>-45</v>
       </c>
       <c r="E30" s="56">
         <f>'Entries October 2026'!W29</f>
@@ -31755,7 +32438,7 @@
       </c>
       <c r="G30" s="57">
         <f t="shared" si="7"/>
-        <v>-1369305</v>
+        <v>45</v>
       </c>
       <c r="H30" s="57">
         <f>'Entries October 2026'!AA29</f>
@@ -31763,7 +32446,7 @@
       </c>
       <c r="I30" s="58">
         <f t="shared" si="3"/>
-        <v>-97122</v>
+        <v>0</v>
       </c>
       <c r="J30" s="57">
         <f>'Entries October 2026'!T29</f>
@@ -31775,7 +32458,7 @@
       </c>
       <c r="L30" s="58">
         <f t="shared" si="6"/>
-        <v>-97122</v>
+        <v>0</v>
       </c>
       <c r="M30" s="57">
         <f>'Entries October 2026'!R29</f>
@@ -31783,11 +32466,11 @@
       </c>
       <c r="N30" s="57">
         <f>'Entries October 2026'!AC30-'Entries October 2026'!AC29</f>
-        <v>-7099</v>
+        <v>0</v>
       </c>
       <c r="O30" s="57">
         <f t="shared" si="5"/>
-        <v>-513824</v>
+        <v>0</v>
       </c>
       <c r="P30" s="62"/>
       <c r="Q30" s="45"/>
@@ -31802,15 +32485,15 @@
       </c>
       <c r="B31" s="55">
         <f>'Entries October 2026'!O30</f>
-        <v>0</v>
+        <v>256912</v>
       </c>
       <c r="C31" s="55">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D31" s="55">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E31" s="56">
         <f>'Entries October 2026'!W30</f>
@@ -31818,7 +32501,7 @@
       </c>
       <c r="F31" s="57">
         <f>'Entries October 2026'!V30</f>
-        <v>0</v>
+        <v>1369350</v>
       </c>
       <c r="G31" s="57">
         <f t="shared" si="7"/>
@@ -31826,7 +32509,7 @@
       </c>
       <c r="H31" s="57">
         <f>'Entries October 2026'!AA30</f>
-        <v>0</v>
+        <v>97122</v>
       </c>
       <c r="I31" s="58">
         <f t="shared" si="3"/>
@@ -31854,7 +32537,7 @@
       </c>
       <c r="O31" s="57">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="P31" s="62"/>
       <c r="Q31" s="45"/>
@@ -31869,15 +32552,15 @@
       </c>
       <c r="B32" s="55">
         <f>'Entries October 2026'!O31</f>
-        <v>0</v>
+        <v>256923</v>
       </c>
       <c r="C32" s="55">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="D32" s="55">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" s="56">
         <f>'Entries October 2026'!W31</f>
@@ -31885,15 +32568,15 @@
       </c>
       <c r="F32" s="57">
         <f>'Entries October 2026'!V31</f>
-        <v>0</v>
+        <v>1369350</v>
       </c>
       <c r="G32" s="57">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="H32" s="57">
         <f>'Entries October 2026'!AA31</f>
-        <v>0</v>
+        <v>97122</v>
       </c>
       <c r="I32" s="58">
         <f t="shared" si="3"/>
@@ -31921,7 +32604,7 @@
       </c>
       <c r="O32" s="57">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="P32" s="62"/>
       <c r="Q32" s="45"/>
@@ -31936,15 +32619,15 @@
       </c>
       <c r="B33" s="55">
         <f>'Entries October 2026'!O32</f>
-        <v>0</v>
+        <v>256996</v>
       </c>
       <c r="C33" s="55">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-256996</v>
       </c>
       <c r="D33" s="55">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1112426</v>
       </c>
       <c r="E33" s="56">
         <f>'Entries October 2026'!W32</f>
@@ -31952,19 +32635,19 @@
       </c>
       <c r="F33" s="57">
         <f>'Entries October 2026'!V32</f>
-        <v>0</v>
+        <v>1369422</v>
       </c>
       <c r="G33" s="57">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-1369422</v>
       </c>
       <c r="H33" s="57">
         <f>'Entries October 2026'!AA32</f>
-        <v>0</v>
+        <v>97122</v>
       </c>
       <c r="I33" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-97122</v>
       </c>
       <c r="J33" s="57">
         <f>'Entries October 2026'!T32</f>
@@ -31976,7 +32659,7 @@
       </c>
       <c r="L33" s="58">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-97122</v>
       </c>
       <c r="M33" s="57">
         <f>'Entries October 2026'!R32</f>
@@ -31984,11 +32667,11 @@
       </c>
       <c r="N33" s="57">
         <f>'Entries October 2026'!AC33-'Entries October 2026'!AC32</f>
-        <v>0</v>
+        <v>-7099</v>
       </c>
       <c r="O33" s="57">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-513992</v>
       </c>
       <c r="P33" s="62"/>
       <c r="Q33" s="45"/>
@@ -34217,9 +34900,9 @@
       <c r="A33" s="771">
         <v>24</v>
       </c>
-      <c r="B33" s="771" t="str">
+      <c r="B33" s="771">
         <f>IF('Entries October 2026'!I30&lt;'Entries October 2026'!I29,"0",(IF('Entries October 2026'!I30&gt;='Entries October 2026'!I29,'Entries October 2026'!I30-'Entries October 2026'!I29,(999999-'Entries October 2026'!I29)+'Entries October 2026'!I30+1)))</f>
-        <v>0</v>
+        <v>3898</v>
       </c>
       <c r="C33" s="771" t="str">
         <f>IF('Entries October 2026'!J30&lt;='Entries October 2026'!J29,"0",IF('Entries October 2026'!J30&gt;='Entries October 2026'!J29,'Entries October 2026'!J30-'Entries October 2026'!J29,(999999-'Entries October 2026'!J29)+'Entries October 2026'!J30+1))</f>
@@ -34227,24 +34910,26 @@
       </c>
       <c r="D33" s="772">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E33" s="874"/>
-      <c r="F33" s="773" t="str">
+        <v>3898</v>
+      </c>
+      <c r="E33" s="874">
+        <v>1431</v>
+      </c>
+      <c r="F33" s="773">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G33" s="774" t="str">
+        <v>0.26853068117845752</v>
+      </c>
+      <c r="G33" s="774">
         <f>IF('Entries October 2026'!K30&lt;'Entries October 2026'!K29,"0",IF('Entries October 2026'!K30&gt;='Entries October 2026'!K29,'Entries October 2026'!K30-'Entries October 2026'!K29,(999999-'Entries October 2026'!K29)+'Entries October 2026'!K30+1))</f>
         <v>0</v>
       </c>
       <c r="H33" s="772">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5329</v>
       </c>
       <c r="I33" s="774">
         <f>'Water '!Z30*10</f>
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="J33" s="772" t="str">
         <f>IF('Entries October 2026'!B30-'Entries October 2026'!B29&lt;1,"0",'Entries October 2026'!B30-'Entries October 2026'!B29)</f>
@@ -34296,7 +34981,7 @@
       </c>
       <c r="B34" s="771">
         <f>IF('Entries October 2026'!I31&lt;'Entries October 2026'!I30,"0",(IF('Entries October 2026'!I31&gt;='Entries October 2026'!I30,'Entries October 2026'!I31-'Entries October 2026'!I30,(999999-'Entries October 2026'!I30)+'Entries October 2026'!I31+1)))</f>
-        <v>0</v>
+        <v>3808</v>
       </c>
       <c r="C34" s="771" t="str">
         <f>IF('Entries October 2026'!J31&lt;='Entries October 2026'!J30,"0",IF('Entries October 2026'!J31&gt;='Entries October 2026'!J30,'Entries October 2026'!J31-'Entries October 2026'!J30,(999999-'Entries October 2026'!J30)+'Entries October 2026'!J31+1))</f>
@@ -34304,12 +34989,14 @@
       </c>
       <c r="D34" s="772">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E34" s="874"/>
-      <c r="F34" s="773" t="str">
+        <v>3808</v>
+      </c>
+      <c r="E34" s="874">
+        <v>1084.3</v>
+      </c>
+      <c r="F34" s="773">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.22163399627986835</v>
       </c>
       <c r="G34" s="774">
         <f>IF('Entries October 2026'!K31&lt;'Entries October 2026'!K30,"0",IF('Entries October 2026'!K31&gt;='Entries October 2026'!K30,'Entries October 2026'!K31-'Entries October 2026'!K30,(999999-'Entries October 2026'!K30)+'Entries October 2026'!K31+1))</f>
@@ -34317,11 +35004,11 @@
       </c>
       <c r="H34" s="772">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4892.3</v>
       </c>
       <c r="I34" s="774">
         <f>'Water '!Z31*10</f>
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J34" s="772" t="str">
         <f>IF('Entries October 2026'!B31-'Entries October 2026'!B30&lt;1,"0",'Entries October 2026'!B31-'Entries October 2026'!B30)</f>
@@ -34373,7 +35060,7 @@
       </c>
       <c r="B35" s="719">
         <f>IF('Entries October 2026'!I32&lt;'Entries October 2026'!I31,"0",(IF('Entries October 2026'!I32&gt;='Entries October 2026'!I31,'Entries October 2026'!I32-'Entries October 2026'!I31,(999999-'Entries October 2026'!I31)+'Entries October 2026'!I32+1)))</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="C35" s="719" t="str">
         <f>IF('Entries October 2026'!J32&lt;='Entries October 2026'!J31,"0",IF('Entries October 2026'!J32&gt;='Entries October 2026'!J31,'Entries October 2026'!J32-'Entries October 2026'!J31,(999999-'Entries October 2026'!J31)+'Entries October 2026'!J32+1))</f>
@@ -34381,12 +35068,14 @@
       </c>
       <c r="D35" s="720">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E35" s="873"/>
-      <c r="F35" s="721" t="str">
+        <v>2496</v>
+      </c>
+      <c r="E35" s="873">
+        <v>1172.7</v>
+      </c>
+      <c r="F35" s="721">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.31965001226592527</v>
       </c>
       <c r="G35" s="737">
         <f>IF('Entries October 2026'!K32&lt;'Entries October 2026'!K31,"0",IF('Entries October 2026'!K32&gt;='Entries October 2026'!K31,'Entries October 2026'!K32-'Entries October 2026'!K31,(999999-'Entries October 2026'!K31)+'Entries October 2026'!K32+1))</f>
@@ -34394,11 +35083,11 @@
       </c>
       <c r="H35" s="720">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3668.7</v>
       </c>
       <c r="I35" s="737">
         <f>'Water '!Z32*10</f>
-        <v>0</v>
+        <v>1390</v>
       </c>
       <c r="J35" s="720" t="str">
         <f>IF('Entries October 2026'!B32-'Entries October 2026'!B31&lt;1,"0",'Entries October 2026'!B32-'Entries October 2026'!B31)</f>
@@ -34448,7 +35137,7 @@
       <c r="A36" s="719">
         <v>27</v>
       </c>
-      <c r="B36" s="719">
+      <c r="B36" s="719" t="str">
         <f>IF('Entries October 2026'!I33&lt;'Entries October 2026'!I32,"0",(IF('Entries October 2026'!I33&gt;='Entries October 2026'!I32,'Entries October 2026'!I33-'Entries October 2026'!I32,(999999-'Entries October 2026'!I32)+'Entries October 2026'!I33+1)))</f>
         <v>0</v>
       </c>
@@ -34460,18 +35149,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E36" s="873"/>
-      <c r="F36" s="721" t="str">
+      <c r="E36" s="873">
+        <v>1431.7</v>
+      </c>
+      <c r="F36" s="721">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G36" s="737">
+        <v>1</v>
+      </c>
+      <c r="G36" s="737" t="str">
         <f>IF('Entries October 2026'!K33&lt;'Entries October 2026'!K32,"0",IF('Entries October 2026'!K33&gt;='Entries October 2026'!K32,'Entries October 2026'!K33-'Entries October 2026'!K32,(999999-'Entries October 2026'!K32)+'Entries October 2026'!K33+1))</f>
         <v>0</v>
       </c>
       <c r="H36" s="720">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1431.7</v>
       </c>
       <c r="I36" s="737">
         <f>'Water '!Z33*10</f>
@@ -34904,15 +35595,15 @@
       <c r="C43" s="19"/>
       <c r="D43" s="20">
         <f>SUM(D10:D40)</f>
-        <v>137781</v>
+        <v>147983</v>
       </c>
       <c r="E43" s="741">
         <f>SUM(E10:E40)</f>
-        <v>30027.899999999994</v>
+        <v>35147.599999999991</v>
       </c>
       <c r="F43" s="754">
         <f>IF((E43+D43)=0,"0",E43/(D43+E43))</f>
-        <v>0.17894104543918704</v>
+        <v>0.19192641754026904</v>
       </c>
       <c r="G43" s="20">
         <f t="shared" ref="G43:P43" si="7">SUM(G10:G40)</f>
@@ -34920,11 +35611,11 @@
       </c>
       <c r="H43" s="20">
         <f t="shared" si="7"/>
-        <v>167808.9</v>
+        <v>183130.6</v>
       </c>
       <c r="I43" s="20">
         <f t="shared" si="7"/>
-        <v>69890</v>
+        <v>71820</v>
       </c>
       <c r="J43" s="20">
         <f t="shared" si="7"/>
@@ -34980,7 +35671,7 @@
       </c>
       <c r="E44" s="728">
         <f>D43+E43</f>
-        <v>167808.9</v>
+        <v>183130.59999999998</v>
       </c>
       <c r="F44" s="708"/>
       <c r="G44" s="7"/>
@@ -34995,11 +35686,11 @@
       <c r="P44" s="401"/>
       <c r="Q44" s="397">
         <f>IF(P43=0,0,H43/P43)</f>
-        <v>26.920361089737458</v>
+        <v>29.378309961988158</v>
       </c>
       <c r="R44" s="398">
         <f>IF(Q44=0,0,I43/P43)</f>
-        <v>11.211944280438946</v>
+        <v>11.521560140522608</v>
       </c>
       <c r="S44" s="398">
         <f>IF(R44=0,0,J43/P43)</f>
@@ -35084,41 +35775,41 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="Q10:Q44">
-    <cfRule type="cellIs" dxfId="62" priority="7" operator="between">
+    <cfRule type="cellIs" dxfId="105" priority="7" operator="between">
       <formula>0</formula>
       <formula>22</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="104" priority="8" operator="greaterThan">
       <formula>22</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="103" priority="9" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:R44">
-    <cfRule type="cellIs" dxfId="59" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="102" priority="1" operator="between">
       <formula>0</formula>
       <formula>10.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="101" priority="2" operator="greaterThan">
       <formula>10.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S10:S44">
-    <cfRule type="cellIs" dxfId="57" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="100" priority="3" operator="between">
       <formula>0</formula>
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="99" priority="4" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T10:T44">
-    <cfRule type="cellIs" dxfId="55" priority="5" operator="between">
+    <cfRule type="cellIs" dxfId="98" priority="5" operator="between">
       <formula>0</formula>
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="97" priority="6" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36941,13 +37632,13 @@
         <f>IF('Entries October 2026'!B30-'Entries October 2026'!B29&lt;1,"0",'Entries October 2026'!B30-'Entries October 2026'!B29)</f>
         <v>0</v>
       </c>
-      <c r="C30" s="739" t="str">
+      <c r="C30" s="739">
         <f>IF('Entries October 2026'!F30-'Entries October 2026'!F29&lt;1,"0",'Entries October 2026'!F30-'Entries October 2026'!F29)</f>
-        <v>0</v>
-      </c>
-      <c r="D30" s="839" t="str">
+        <v>7.3999999999996362</v>
+      </c>
+      <c r="D30" s="839">
         <f>IF('Entries October 2026'!C30-'Entries October 2026'!C29&lt;1,"0",'Entries October 2026'!C30-'Entries October 2026'!C29)</f>
-        <v>0</v>
+        <v>706.4000000001397</v>
       </c>
       <c r="E30" s="843" t="str">
         <f t="shared" si="0"/>
@@ -36959,7 +37650,7 @@
       </c>
       <c r="G30" s="837"/>
       <c r="H30" s="739"/>
-      <c r="I30" s="740" t="str">
+      <c r="I30" s="740">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -36984,7 +37675,7 @@
       </c>
       <c r="O30" s="830">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-706.4000000001397</v>
       </c>
       <c r="P30" s="333"/>
     </row>
@@ -37051,13 +37742,13 @@
         <f>IF('Entries October 2026'!B32-'Entries October 2026'!B31&lt;1,"0",'Entries October 2026'!B32-'Entries October 2026'!B31)</f>
         <v>0</v>
       </c>
-      <c r="C32" s="739" t="str">
+      <c r="C32" s="739">
         <f>IF('Entries October 2026'!F32-'Entries October 2026'!F31&lt;1,"0",'Entries October 2026'!F32-'Entries October 2026'!F31)</f>
-        <v>0</v>
-      </c>
-      <c r="D32" s="839" t="str">
+        <v>3.6000000000003638</v>
+      </c>
+      <c r="D32" s="839">
         <f>IF('Entries October 2026'!C32-'Entries October 2026'!C31&lt;1,"0",'Entries October 2026'!C32-'Entries October 2026'!C31)</f>
-        <v>0</v>
+        <v>581.80000000004657</v>
       </c>
       <c r="E32" s="843" t="str">
         <f t="shared" si="0"/>
@@ -37069,7 +37760,7 @@
       </c>
       <c r="G32" s="837"/>
       <c r="H32" s="739"/>
-      <c r="I32" s="740" t="str">
+      <c r="I32" s="740">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -37094,7 +37785,7 @@
       </c>
       <c r="O32" s="830">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-581.80000000004657</v>
       </c>
       <c r="P32" s="333"/>
     </row>
@@ -37378,11 +38069,11 @@
       </c>
       <c r="C38" s="388">
         <f>SUM(C7:C37)</f>
-        <v>355.40000000000146</v>
+        <v>366.40000000000146</v>
       </c>
       <c r="D38" s="840">
         <f t="shared" si="7"/>
-        <v>52395.399999999907</v>
+        <v>53683.600000000093</v>
       </c>
       <c r="E38" s="845"/>
       <c r="F38" s="846">
@@ -37399,7 +38090,7 @@
       </c>
       <c r="I38" s="797">
         <f>B38/C38</f>
-        <v>2.7011817670230616</v>
+        <v>2.6200873362445312</v>
       </c>
       <c r="J38" s="355"/>
       <c r="K38" s="356">
@@ -37416,7 +38107,7 @@
       </c>
       <c r="N38" s="834">
         <f>IF(L38=0,"0",(D38/L38))</f>
-        <v>8.405412868097148</v>
+        <v>8.6120694229986157</v>
       </c>
       <c r="O38" s="835"/>
     </row>
@@ -37430,7 +38121,7 @@
       </c>
       <c r="C39" s="802">
         <f>AVERAGE(C7:C37)</f>
-        <v>16.15454545454552</v>
+        <v>15.266666666666728</v>
       </c>
       <c r="D39" s="30"/>
       <c r="E39" s="30"/>
@@ -38050,27 +38741,27 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="C7:C37">
-    <cfRule type="cellIs" dxfId="53" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="96" priority="13" operator="greaterThan">
       <formula>24</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7:N37">
-    <cfRule type="cellIs" dxfId="52" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="95" priority="9" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="11" operator="between">
+    <cfRule type="cellIs" dxfId="94" priority="11" operator="between">
       <formula>0</formula>
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7:N38">
-    <cfRule type="cellIs" dxfId="50" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="93" priority="1" operator="lessThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="92" priority="2" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="91" priority="4" operator="greaterThan">
       <formula>7.2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38147,87 +38838,87 @@
     </row>
     <row r="3" spans="1:31" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="980" t="s">
+      <c r="B4" s="972" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="972" t="s">
+      <c r="C4" s="970" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="977" t="s">
+      <c r="D4" s="968" t="s">
         <v>106</v>
       </c>
-      <c r="E4" s="972" t="s">
+      <c r="E4" s="970" t="s">
         <v>107</v>
       </c>
-      <c r="F4" s="977" t="s">
+      <c r="F4" s="968" t="s">
         <v>239</v>
       </c>
-      <c r="G4" s="977" t="s">
+      <c r="G4" s="968" t="s">
         <v>108</v>
       </c>
-      <c r="H4" s="977" t="s">
+      <c r="H4" s="968" t="s">
         <v>161</v>
       </c>
-      <c r="I4" s="972" t="s">
+      <c r="I4" s="970" t="s">
         <v>207</v>
       </c>
-      <c r="J4" s="972" t="s">
+      <c r="J4" s="970" t="s">
         <v>109</v>
       </c>
-      <c r="K4" s="972" t="s">
+      <c r="K4" s="970" t="s">
         <v>174</v>
       </c>
-      <c r="L4" s="972" t="s">
+      <c r="L4" s="970" t="s">
         <v>173</v>
       </c>
-      <c r="M4" s="972" t="s">
+      <c r="M4" s="970" t="s">
         <v>103</v>
       </c>
       <c r="N4" s="48"/>
       <c r="O4" s="48"/>
       <c r="P4" s="48"/>
       <c r="Q4" s="48"/>
-      <c r="R4" s="977" t="s">
+      <c r="R4" s="968" t="s">
         <v>110</v>
       </c>
-      <c r="S4" s="977" t="s">
+      <c r="S4" s="968" t="s">
         <v>240</v>
       </c>
       <c r="T4" s="48"/>
-      <c r="U4" s="972" t="s">
+      <c r="U4" s="970" t="s">
         <v>153</v>
       </c>
       <c r="V4" s="48"/>
       <c r="W4" s="48"/>
-      <c r="X4" s="972" t="s">
+      <c r="X4" s="970" t="s">
         <v>175</v>
       </c>
-      <c r="Y4" s="972" t="s">
+      <c r="Y4" s="970" t="s">
         <v>176</v>
       </c>
-      <c r="Z4" s="970" t="s">
+      <c r="Z4" s="977" t="s">
         <v>247</v>
       </c>
-      <c r="AA4" s="974" t="s">
+      <c r="AA4" s="979" t="s">
         <v>243</v>
       </c>
-      <c r="AB4" s="968" t="s">
+      <c r="AB4" s="975" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:31" s="300" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="981"/>
-      <c r="C5" s="979"/>
-      <c r="D5" s="978"/>
-      <c r="E5" s="973"/>
-      <c r="F5" s="978"/>
-      <c r="G5" s="978"/>
-      <c r="H5" s="978"/>
-      <c r="I5" s="973"/>
-      <c r="J5" s="973"/>
-      <c r="K5" s="973"/>
-      <c r="L5" s="973"/>
-      <c r="M5" s="973"/>
+      <c r="B5" s="973"/>
+      <c r="C5" s="971"/>
+      <c r="D5" s="969"/>
+      <c r="E5" s="974"/>
+      <c r="F5" s="969"/>
+      <c r="G5" s="969"/>
+      <c r="H5" s="969"/>
+      <c r="I5" s="974"/>
+      <c r="J5" s="974"/>
+      <c r="K5" s="974"/>
+      <c r="L5" s="974"/>
+      <c r="M5" s="974"/>
       <c r="N5" s="50" t="s">
         <v>111</v>
       </c>
@@ -38240,23 +38931,23 @@
       <c r="Q5" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="R5" s="978"/>
-      <c r="S5" s="978"/>
+      <c r="R5" s="969"/>
+      <c r="S5" s="969"/>
       <c r="T5" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="U5" s="976"/>
+      <c r="U5" s="981"/>
       <c r="V5" s="80" t="s">
         <v>156</v>
       </c>
       <c r="W5" s="80" t="s">
         <v>157</v>
       </c>
-      <c r="X5" s="973"/>
-      <c r="Y5" s="973"/>
-      <c r="Z5" s="971"/>
-      <c r="AA5" s="975"/>
-      <c r="AB5" s="969"/>
+      <c r="X5" s="974"/>
+      <c r="Y5" s="974"/>
+      <c r="Z5" s="978"/>
+      <c r="AA5" s="980"/>
+      <c r="AB5" s="976"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="21" t="s">
@@ -40798,29 +41489,29 @@
         <f>IF('Entries October 2026'!O30-'Entries October 2026'!O29&lt;1,"0",'Entries October 2026'!O30-'Entries October 2026'!O29)</f>
         <v>0</v>
       </c>
-      <c r="E30" s="693" t="str">
+      <c r="E30" s="693">
         <f>IF('Entries October 2026'!P30-'Entries October 2026'!P29&lt;1,"0",'Entries October 2026'!P30-'Entries October 2026'!P29)</f>
-        <v>0</v>
-      </c>
-      <c r="F30" s="693" t="str">
+        <v>43</v>
+      </c>
+      <c r="F30" s="693">
         <f>IF('Entries October 2026'!V30-'Entries October 2026'!V29&lt;1,"0",'Entries October 2026'!V30-'Entries October 2026'!V29)</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G30" s="693">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H30" s="693">
         <f>IF('Entries October 2026'!Q30-'Entries October 2026'!Q29&lt;1,0,'Entries October 2026'!Q30-'Entries October 2026'!Q29)</f>
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="I30" s="693">
         <f>IF('Entries October 2026'!AG30-'Entries October 2026'!AG29&lt;1,0,'Entries October 2026'!AG30-'Entries October 2026'!AG29)</f>
         <v>0</v>
       </c>
-      <c r="J30" s="693" t="str">
+      <c r="J30" s="693">
         <f>IF('Entries October 2026'!S30-'Entries October 2026'!S29&lt;1,"0",'Entries October 2026'!S30-'Entries October 2026'!S29)</f>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="K30" s="693" t="str">
         <f>IF('Entries October 2026'!R30-'Entries October 2026'!R29&lt;1,"0",'Entries October 2026'!R30-'Entries October 2026'!R29)</f>
@@ -40834,21 +41525,21 @@
         <f>IF('Entries October 2026'!U30-'Entries October 2026'!U29&lt;1,"0",'Entries October 2026'!U30-'Entries October 2026'!U29)</f>
         <v>0</v>
       </c>
-      <c r="N30" s="693" t="str">
+      <c r="N30" s="693">
         <f>IF('Entries October 2026'!X30-'Entries October 2026'!X29&lt;1,"0",'Entries October 2026'!X30-'Entries October 2026'!X29)</f>
-        <v>0</v>
-      </c>
-      <c r="O30" s="693" t="str">
+        <v>6</v>
+      </c>
+      <c r="O30" s="693">
         <f>IF('Entries October 2026'!Y30-'Entries October 2026'!Y29&lt;1,"0",'Entries October 2026'!Y30-'Entries October 2026'!Y29)</f>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="P30" s="693" t="str">
         <f>IF('Entries October 2026'!AC30-'Entries October 2026'!AC29&lt;1,"0",'Entries October 2026'!AC30-'Entries October 2026'!AC29)</f>
         <v>0</v>
       </c>
-      <c r="Q30" s="693" t="str">
+      <c r="Q30" s="693">
         <f>IF('Entries October 2026'!Z30-'Entries October 2026'!Z29&lt;1,"0",'Entries October 2026'!Z30-'Entries October 2026'!Z29)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R30" s="693" t="str">
         <f>IF(('Entries October 2026'!AA30-'Entries October 2026'!AA29)+('Entries October 2026'!AB30-'Entries October 2026'!AB29)&lt;1,"0",('Entries October 2026'!AA30-'Entries October 2026'!AA29)+('Entries October 2026'!AB30-'Entries October 2026'!AB29))</f>
@@ -40856,11 +41547,11 @@
       </c>
       <c r="S30" s="692">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="T30" s="692">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="U30" s="693" t="str">
         <f>IF('Entries October 2026'!AC30-'Entries October 2026'!AC29&lt;1,"0",'Entries October 2026'!AC30-'Entries October 2026'!AC29)</f>
@@ -40884,7 +41575,7 @@
       </c>
       <c r="Z30" s="329">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AA30" s="330" t="str">
         <v>0</v>
@@ -40902,9 +41593,9 @@
         <f>IF('Entries October 2026'!W31-'Entries October 2026'!W30&lt;1,"0",'Entries October 2026'!W31-'Entries October 2026'!W30)</f>
         <v>0</v>
       </c>
-      <c r="D31" s="693" t="str">
+      <c r="D31" s="693">
         <f>IF('Entries October 2026'!O31-'Entries October 2026'!O30&lt;1,"0",'Entries October 2026'!O31-'Entries October 2026'!O30)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E31" s="693" t="str">
         <f>IF('Entries October 2026'!P31-'Entries October 2026'!P30&lt;1,"0",'Entries October 2026'!P31-'Entries October 2026'!P30)</f>
@@ -40916,11 +41607,11 @@
       </c>
       <c r="G31" s="693">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H31" s="693">
         <f>IF('Entries October 2026'!Q31-'Entries October 2026'!Q30&lt;1,0,'Entries October 2026'!Q31-'Entries October 2026'!Q30)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I31" s="693">
         <f>IF('Entries October 2026'!AG31-'Entries October 2026'!AG30&lt;1,0,'Entries October 2026'!AG31-'Entries October 2026'!AG30)</f>
@@ -40954,9 +41645,9 @@
         <f>IF('Entries October 2026'!AC31-'Entries October 2026'!AC30&lt;1,"0",'Entries October 2026'!AC31-'Entries October 2026'!AC30)</f>
         <v>0</v>
       </c>
-      <c r="Q31" s="693" t="str">
+      <c r="Q31" s="693">
         <f>IF('Entries October 2026'!Z31-'Entries October 2026'!Z30&lt;1,"0",'Entries October 2026'!Z31-'Entries October 2026'!Z30)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R31" s="693" t="str">
         <f>IF(('Entries October 2026'!AA31-'Entries October 2026'!AA30)+('Entries October 2026'!AB31-'Entries October 2026'!AB30)&lt;1,"0",('Entries October 2026'!AA31-'Entries October 2026'!AA30)+('Entries October 2026'!AB31-'Entries October 2026'!AB30))</f>
@@ -40964,7 +41655,7 @@
       </c>
       <c r="S31" s="692">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="T31" s="692">
         <f t="shared" si="1"/>
@@ -40992,7 +41683,7 @@
       </c>
       <c r="Z31" s="329">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA31" s="330" t="str">
         <v>0</v>
@@ -41013,25 +41704,25 @@
         <f>IF('Entries October 2026'!W32-'Entries October 2026'!W31&lt;1,"0",'Entries October 2026'!W32-'Entries October 2026'!W31)</f>
         <v>0</v>
       </c>
-      <c r="D32" s="693" t="str">
+      <c r="D32" s="693">
         <f>IF('Entries October 2026'!O32-'Entries October 2026'!O31&lt;1,"0",'Entries October 2026'!O32-'Entries October 2026'!O31)</f>
-        <v>0</v>
-      </c>
-      <c r="E32" s="693" t="str">
+        <v>73</v>
+      </c>
+      <c r="E32" s="693">
         <f>IF('Entries October 2026'!P32-'Entries October 2026'!P31&lt;1,"0",'Entries October 2026'!P32-'Entries October 2026'!P31)</f>
-        <v>0</v>
-      </c>
-      <c r="F32" s="693" t="str">
+        <v>66</v>
+      </c>
+      <c r="F32" s="693">
         <f>IF('Entries October 2026'!V32-'Entries October 2026'!V31&lt;1,"0",'Entries October 2026'!V32-'Entries October 2026'!V31)</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="G32" s="693">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="H32" s="693">
         <f>IF('Entries October 2026'!Q32-'Entries October 2026'!Q31&lt;1,0,'Entries October 2026'!Q32-'Entries October 2026'!Q31)</f>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I32" s="693">
         <f>IF('Entries October 2026'!AG32-'Entries October 2026'!AG31&lt;1,0,'Entries October 2026'!AG32-'Entries October 2026'!AG31)</f>
@@ -41049,9 +41740,9 @@
         <f>IF('Entries October 2026'!T32-'Entries October 2026'!T31&lt;1,"0",'Entries October 2026'!T32-'Entries October 2026'!T31)</f>
         <v>0</v>
       </c>
-      <c r="M32" s="693" t="str">
+      <c r="M32" s="693">
         <f>IF('Entries October 2026'!U32-'Entries October 2026'!U31&lt;1,"0",'Entries October 2026'!U32-'Entries October 2026'!U31)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" s="693" t="str">
         <f>IF('Entries October 2026'!X32-'Entries October 2026'!X31&lt;1,"0",'Entries October 2026'!X32-'Entries October 2026'!X31)</f>
@@ -41065,9 +41756,9 @@
         <f>IF('Entries October 2026'!AC32-'Entries October 2026'!AC31&lt;1,"0",'Entries October 2026'!AC32-'Entries October 2026'!AC31)</f>
         <v>0</v>
       </c>
-      <c r="Q32" s="693" t="str">
+      <c r="Q32" s="693">
         <f>IF('Entries October 2026'!Z32-'Entries October 2026'!Z31&lt;1,"0",'Entries October 2026'!Z32-'Entries October 2026'!Z31)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R32" s="693" t="str">
         <f>IF(('Entries October 2026'!AA32-'Entries October 2026'!AA31)+('Entries October 2026'!AB32-'Entries October 2026'!AB31)&lt;1,"0",('Entries October 2026'!AA32-'Entries October 2026'!AA31)+('Entries October 2026'!AB32-'Entries October 2026'!AB31))</f>
@@ -41075,11 +41766,11 @@
       </c>
       <c r="S32" s="692">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>670</v>
       </c>
       <c r="T32" s="692">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U32" s="693" t="str">
         <f>IF('Entries October 2026'!AC32-'Entries October 2026'!AC31&lt;1,"0",'Entries October 2026'!AC32-'Entries October 2026'!AC31)</f>
@@ -41103,7 +41794,7 @@
       </c>
       <c r="Z32" s="329">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="AA32" s="330" t="str">
         <v>0</v>
@@ -41658,28 +42349,28 @@
       </c>
       <c r="D38" s="303">
         <f>SUM(D7:D37)</f>
-        <v>3918</v>
+        <v>4002</v>
       </c>
       <c r="E38" s="303">
         <f>SUM(E7:E37)</f>
-        <v>3071</v>
+        <v>3180</v>
       </c>
       <c r="F38" s="303">
         <f>SUM(F7:F37)</f>
-        <v>3269</v>
+        <v>3386</v>
       </c>
       <c r="G38" s="304">
         <f>SUM(G7:G37)</f>
-        <v>3720</v>
+        <v>3796</v>
       </c>
       <c r="H38" s="303">
         <f t="shared" si="5"/>
-        <v>3829</v>
+        <v>3945</v>
       </c>
       <c r="I38" s="303"/>
       <c r="J38" s="303">
         <f t="shared" si="5"/>
-        <v>3033</v>
+        <v>3071</v>
       </c>
       <c r="K38" s="303"/>
       <c r="L38" s="303">
@@ -41688,15 +42379,15 @@
       </c>
       <c r="M38" s="303">
         <f>SUM(M7:M37)</f>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N38" s="303">
         <f t="shared" si="5"/>
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="O38" s="303">
         <f t="shared" si="5"/>
-        <v>1704</v>
+        <v>1735</v>
       </c>
       <c r="P38" s="303">
         <f>SUM(P7:P37)</f>
@@ -41704,7 +42395,7 @@
       </c>
       <c r="Q38" s="303">
         <f>SUM(Q7:Q37)</f>
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="R38" s="303">
         <f>SUM(R7:R34)</f>
@@ -41712,11 +42403,11 @@
       </c>
       <c r="S38" s="304">
         <f>SUM(S7:S37)</f>
-        <v>37200</v>
+        <v>37960</v>
       </c>
       <c r="T38" s="304">
         <f>SUM(T7:T37)</f>
-        <v>2374</v>
+        <v>2412</v>
       </c>
       <c r="U38" s="303">
         <f>SUM(U7:U37)</f>
@@ -41731,7 +42422,7 @@
       <c r="Y38" s="303"/>
       <c r="Z38" s="332">
         <f>SUM(Z7:Z37)</f>
-        <v>6989</v>
+        <v>7182</v>
       </c>
       <c r="AA38" s="332">
         <f>SUM(AA7:AA37)</f>
@@ -41739,14 +42430,14 @@
       </c>
       <c r="AB38" s="331">
         <f>IF(AA38=0,"0",(Z38*10/AA38))</f>
-        <v>11.211944280438946</v>
+        <v>11.521560140522608</v>
       </c>
       <c r="AC38" s="321">
         <v>10.199999999999999</v>
       </c>
       <c r="AD38" s="340">
         <f>AB38/AC38*100</f>
-        <v>109.92102235724457</v>
+        <v>112.95647196590792</v>
       </c>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.2">
@@ -41785,7 +42476,7 @@
       <c r="C40" s="15"/>
       <c r="D40" s="15">
         <f>D38*220</f>
-        <v>861960</v>
+        <v>880440</v>
       </c>
       <c r="E40" s="15"/>
       <c r="F40" s="15"/>
@@ -41877,7 +42568,7 @@
       <c r="C43" s="17"/>
       <c r="D43" s="17">
         <f>+D41*D40</f>
-        <v>13627.587600000001</v>
+        <v>13919.7564</v>
       </c>
       <c r="E43" s="17"/>
       <c r="F43" s="36"/>
@@ -41930,7 +42621,7 @@
     <row r="45" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D45" s="17">
         <f>SUM(D43:D44)</f>
-        <v>13906.5576</v>
+        <v>14198.7264</v>
       </c>
       <c r="E45" s="17"/>
       <c r="F45" s="36"/>
@@ -41952,7 +42643,7 @@
       </c>
       <c r="D47" s="23">
         <f>+D45*2/3</f>
-        <v>9271.0383999999995</v>
+        <v>9465.8176000000003</v>
       </c>
       <c r="E47" s="324"/>
       <c r="F47" s="36"/>
@@ -41975,7 +42666,7 @@
       <c r="C49" s="24"/>
       <c r="D49" s="28">
         <f>SUM(D47,D45)</f>
-        <v>23177.595999999998</v>
+        <v>23664.544000000002</v>
       </c>
       <c r="E49" s="325"/>
       <c r="F49" s="36"/>
@@ -42340,16 +43031,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:AA1"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="R4:R5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="E4:E5"/>
     <mergeCell ref="AB4:AB5"/>
     <mergeCell ref="Z4:Z5"/>
     <mergeCell ref="L4:L5"/>
@@ -42361,13 +43042,23 @@
     <mergeCell ref="Y4:Y5"/>
     <mergeCell ref="S4:S5"/>
     <mergeCell ref="M4:M5"/>
+    <mergeCell ref="A1:AA1"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="R4:R5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="E4:E5"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="AB6:AB38">
-    <cfRule type="cellIs" dxfId="47" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="90" priority="1" operator="lessThan">
       <formula>10.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="89" priority="2" operator="greaterThan">
       <formula>10.2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43163,19 +43854,19 @@
       </c>
       <c r="B30" s="742">
         <f>'Utility Analysis October 2026'!D33</f>
-        <v>0</v>
-      </c>
-      <c r="C30" s="743" t="str">
+        <v>3898</v>
+      </c>
+      <c r="C30" s="743">
         <f>'Utility Analysis October 2026'!G33</f>
         <v>0</v>
       </c>
       <c r="D30" s="744">
         <f>'Utility Analysis October 2026'!E33</f>
-        <v>0</v>
+        <v>1431</v>
       </c>
       <c r="E30" s="745">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5329</v>
       </c>
       <c r="F30" s="746" t="str">
         <f>'PROD.FIG. '!H28</f>
@@ -43193,7 +43884,7 @@
       </c>
       <c r="B31" s="742">
         <f>'Utility Analysis October 2026'!D34</f>
-        <v>0</v>
+        <v>3808</v>
       </c>
       <c r="C31" s="743">
         <f>'Utility Analysis October 2026'!G34</f>
@@ -43201,11 +43892,11 @@
       </c>
       <c r="D31" s="744">
         <f>'Utility Analysis October 2026'!E34</f>
-        <v>0</v>
+        <v>1084.3</v>
       </c>
       <c r="E31" s="745">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4892.3</v>
       </c>
       <c r="F31" s="746" t="str">
         <f>'PROD.FIG. '!H29</f>
@@ -43223,7 +43914,7 @@
       </c>
       <c r="B32" s="761">
         <f>'Utility Analysis October 2026'!D35</f>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="C32" s="762">
         <f>'Utility Analysis October 2026'!G35</f>
@@ -43231,11 +43922,11 @@
       </c>
       <c r="D32" s="763">
         <f>'Utility Analysis October 2026'!E35</f>
-        <v>0</v>
+        <v>1172.7</v>
       </c>
       <c r="E32" s="764">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3668.7</v>
       </c>
       <c r="F32" s="765" t="str">
         <f>'PROD.FIG. '!H30</f>
@@ -43255,17 +43946,17 @@
         <f>'Utility Analysis October 2026'!D36</f>
         <v>0</v>
       </c>
-      <c r="C33" s="762">
+      <c r="C33" s="762" t="str">
         <f>'Utility Analysis October 2026'!G36</f>
         <v>0</v>
       </c>
       <c r="D33" s="763">
         <f>'Utility Analysis October 2026'!E36</f>
-        <v>0</v>
+        <v>1431.7</v>
       </c>
       <c r="E33" s="764">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1431.7</v>
       </c>
       <c r="F33" s="765" t="str">
         <f>'PROD.FIG. '!H31</f>
@@ -43400,7 +44091,7 @@
       </c>
       <c r="B38" s="308">
         <f>SUM(B7:B37)</f>
-        <v>137781</v>
+        <v>147983</v>
       </c>
       <c r="C38" s="308">
         <f>SUM(C7:C37)</f>
@@ -43408,11 +44099,11 @@
       </c>
       <c r="D38" s="308">
         <f>SUM(D7:D37)</f>
-        <v>30027.899999999994</v>
+        <v>35147.599999999991</v>
       </c>
       <c r="E38" s="337">
         <f>SUM(E7:E37)</f>
-        <v>167808.9</v>
+        <v>183130.6</v>
       </c>
       <c r="F38" s="358">
         <f>SUM(F7:F37)</f>
@@ -43420,14 +44111,14 @@
       </c>
       <c r="G38" s="338">
         <f>IF(F38=0,"0",(E38/F38))</f>
-        <v>26.920361089737458</v>
+        <v>29.378309961988158</v>
       </c>
       <c r="H38" s="335">
         <v>22</v>
       </c>
       <c r="I38" s="340">
         <f>G38/H38*100</f>
-        <v>122.36527768062481</v>
+        <v>133.53777255449162</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
@@ -43468,12 +44159,12 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="cellIs" dxfId="45" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="88" priority="1" operator="lessThan">
       <formula>22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7:G38">
-    <cfRule type="cellIs" dxfId="44" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="87" priority="2" operator="greaterThan">
       <formula>21</formula>
     </cfRule>
   </conditionalFormatting>
@@ -44242,11 +44933,11 @@
       <c r="D3" s="85"/>
       <c r="E3" s="85"/>
       <c r="F3" s="1"/>
-      <c r="I3" s="1012" t="s">
+      <c r="I3" s="1004" t="s">
         <v>267</v>
       </c>
-      <c r="J3" s="1013"/>
-      <c r="K3" s="1014"/>
+      <c r="J3" s="1005"/>
+      <c r="K3" s="1006"/>
     </row>
     <row r="4" spans="1:24" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
@@ -44259,21 +44950,21 @@
         <v>250</v>
       </c>
       <c r="H4" s="347"/>
-      <c r="I4" s="1015" t="s">
+      <c r="I4" s="1007" t="s">
         <v>262</v>
       </c>
-      <c r="J4" s="1016"/>
-      <c r="K4" s="1017"/>
+      <c r="J4" s="1008"/>
+      <c r="K4" s="1009"/>
       <c r="M4" s="417"/>
       <c r="N4" s="417"/>
       <c r="O4" s="418"/>
       <c r="P4" s="418"/>
-      <c r="Q4" s="1027" t="s">
+      <c r="Q4" s="1019" t="s">
         <v>283</v>
       </c>
-      <c r="R4" s="1027"/>
-      <c r="S4" s="1027"/>
-      <c r="T4" s="1027"/>
+      <c r="R4" s="1019"/>
+      <c r="S4" s="1019"/>
+      <c r="T4" s="1019"/>
       <c r="U4" s="191"/>
       <c r="V4" s="417"/>
       <c r="W4" s="191"/>
@@ -44289,16 +44980,16 @@
       <c r="C5" s="950" t="s">
         <v>282</v>
       </c>
-      <c r="D5" s="1006" t="s">
+      <c r="D5" s="1026" t="s">
         <v>279</v>
       </c>
-      <c r="E5" s="1006" t="s">
+      <c r="E5" s="1026" t="s">
         <v>280</v>
       </c>
-      <c r="F5" s="1004" t="s">
+      <c r="F5" s="1024" t="s">
         <v>243</v>
       </c>
-      <c r="G5" s="1001" t="s">
+      <c r="G5" s="1021" t="s">
         <v>249</v>
       </c>
       <c r="I5" s="419" t="s">
@@ -44310,43 +45001,43 @@
       <c r="K5" s="421" t="s">
         <v>265</v>
       </c>
-      <c r="M5" s="1018" t="s">
+      <c r="M5" s="1010" t="s">
         <v>266</v>
       </c>
-      <c r="N5" s="1019"/>
-      <c r="O5" s="1020"/>
+      <c r="N5" s="1011"/>
+      <c r="O5" s="1012"/>
       <c r="P5" s="422"/>
-      <c r="Q5" s="1021" t="s">
+      <c r="Q5" s="1013" t="s">
         <v>7</v>
       </c>
-      <c r="R5" s="1023" t="s">
+      <c r="R5" s="1015" t="s">
         <v>267</v>
       </c>
-      <c r="S5" s="1024"/>
+      <c r="S5" s="1016"/>
       <c r="T5" s="452" t="s">
         <v>268</v>
       </c>
       <c r="U5" s="423" t="s">
         <v>269</v>
       </c>
-      <c r="V5" s="1025" t="s">
+      <c r="V5" s="1017" t="s">
         <v>277</v>
       </c>
-      <c r="W5" s="1008" t="s">
+      <c r="W5" s="1000" t="s">
         <v>270</v>
       </c>
-      <c r="X5" s="1010" t="s">
+      <c r="X5" s="1002" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1000"/>
-      <c r="B6" s="1003"/>
-      <c r="C6" s="1003"/>
-      <c r="D6" s="1007"/>
-      <c r="E6" s="1007"/>
-      <c r="F6" s="1005"/>
-      <c r="G6" s="1002"/>
+      <c r="A6" s="1020"/>
+      <c r="B6" s="1023"/>
+      <c r="C6" s="1023"/>
+      <c r="D6" s="1027"/>
+      <c r="E6" s="1027"/>
+      <c r="F6" s="1025"/>
+      <c r="G6" s="1022"/>
       <c r="I6" s="424">
         <v>10</v>
       </c>
@@ -44365,7 +45056,7 @@
         <v>273</v>
       </c>
       <c r="P6" s="418"/>
-      <c r="Q6" s="1022"/>
+      <c r="Q6" s="1014"/>
       <c r="R6" s="448" t="s">
         <v>274</v>
       </c>
@@ -44378,9 +45069,9 @@
       <c r="U6" s="429" t="s">
         <v>275</v>
       </c>
-      <c r="V6" s="1026"/>
-      <c r="W6" s="1009"/>
-      <c r="X6" s="1011"/>
+      <c r="V6" s="1018"/>
+      <c r="W6" s="1001"/>
+      <c r="X6" s="1003"/>
     </row>
     <row r="7" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="715">
@@ -46849,6 +47540,13 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="C5:C6"/>
     <mergeCell ref="W5:W6"/>
     <mergeCell ref="X5:X6"/>
     <mergeCell ref="I3:K3"/>
@@ -46858,20 +47556,13 @@
     <mergeCell ref="R5:S5"/>
     <mergeCell ref="V5:V6"/>
     <mergeCell ref="Q4:T4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="C5:C6"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="G7:G38">
-    <cfRule type="cellIs" dxfId="43" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="86" priority="1" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="85" priority="3" operator="greaterThan">
       <formula>21</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48086,13 +48777,13 @@
         <f>+'Water '!$D30</f>
         <v>0</v>
       </c>
-      <c r="Z16" s="110" t="str">
+      <c r="Z16" s="110">
         <f>+'Water '!$D31</f>
-        <v>0</v>
-      </c>
-      <c r="AA16" s="110" t="str">
+        <v>11</v>
+      </c>
+      <c r="AA16" s="110">
         <f>+'Water '!$D32</f>
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AB16" s="110" t="str">
         <f>+'Water '!$D33</f>
@@ -48102,13 +48793,13 @@
         <f>+'Water '!$D34</f>
         <v>0</v>
       </c>
-      <c r="AD16" s="110" t="str">
+      <c r="AD16" s="110">
         <f>+'Water '!$D31</f>
-        <v>0</v>
-      </c>
-      <c r="AE16" s="110" t="str">
+        <v>11</v>
+      </c>
+      <c r="AE16" s="110">
         <f>+'Water '!$D32</f>
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AF16" s="110" t="str">
         <f>+'Water '!$D33</f>
@@ -48116,7 +48807,7 @@
       </c>
       <c r="AG16" s="220">
         <f>SUM($B16:AF16)</f>
-        <v>3918</v>
+        <v>4086</v>
       </c>
       <c r="AH16" s="221"/>
     </row>
@@ -48216,17 +48907,17 @@
         <f>+'Water '!$E29</f>
         <v>193</v>
       </c>
-      <c r="Y17" s="116" t="str">
+      <c r="Y17" s="116">
         <f>+'Water '!$E30</f>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="Z17" s="116" t="str">
         <f>+'Water '!$E31</f>
         <v>0</v>
       </c>
-      <c r="AA17" s="112" t="str">
+      <c r="AA17" s="112">
         <f>+'Water '!$E32</f>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AB17" s="114" t="str">
         <f>+'Water '!$E33</f>
@@ -48240,9 +48931,9 @@
         <f>+'Water '!$E31</f>
         <v>0</v>
       </c>
-      <c r="AE17" s="112" t="str">
+      <c r="AE17" s="112">
         <f>+'Water '!$E32</f>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AF17" s="114" t="str">
         <f>+'Water '!$E33</f>
@@ -48250,7 +48941,7 @@
       </c>
       <c r="AG17" s="222">
         <f>SUM($B17:AF17)</f>
-        <v>3071</v>
+        <v>3246</v>
       </c>
       <c r="AH17" s="223"/>
       <c r="AI17" s="268"/>
@@ -48353,15 +49044,15 @@
       </c>
       <c r="Y18" s="175">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="Z18" s="175">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA18" s="175">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="AB18" s="175">
         <f t="shared" si="0"/>
@@ -48373,11 +49064,11 @@
       </c>
       <c r="AD18" s="175">
         <f>SUM(AD15:AD17)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE18" s="175">
         <f>SUM(AE15:AE17)</f>
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="AF18" s="175">
         <f>SUM(AF15:AF17)</f>
@@ -48385,7 +49076,7 @@
       </c>
       <c r="AG18" s="224">
         <f>SUM($B18:AF18)</f>
-        <v>6989</v>
+        <v>7332</v>
       </c>
       <c r="AH18" s="224"/>
       <c r="AI18" s="269"/>
@@ -48567,7 +49258,7 @@
       </c>
       <c r="Y21" s="119">
         <f>0.73*(Y96+Y15)</f>
-        <v>0</v>
+        <v>32.85</v>
       </c>
       <c r="Z21" s="119">
         <f t="shared" si="1"/>
@@ -48599,16 +49290,16 @@
       </c>
       <c r="AG21" s="220">
         <f>SUM($B21:AF21)</f>
-        <v>2295.1200000000003</v>
+        <v>2327.9700000000003</v>
       </c>
       <c r="AH21" s="225">
         <f>AG24+AG37+AG28</f>
-        <v>7319</v>
+        <v>7507</v>
       </c>
       <c r="AI21" s="271"/>
       <c r="AJ21" s="272">
         <f>(AH21*10)/AG9</f>
-        <v>11.741339274364378</v>
+        <v>12.042933998176444</v>
       </c>
     </row>
     <row r="22" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -48884,15 +49575,15 @@
       </c>
       <c r="Y24" s="112">
         <f>'Water '!H30</f>
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="Z24" s="112">
         <f>'Water '!H31</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA24" s="112">
         <f>'Water '!H32</f>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AB24" s="112">
         <f>'Water '!H33</f>
@@ -48916,7 +49607,7 @@
       </c>
       <c r="AG24" s="222">
         <f>SUM($B24:AF24)</f>
-        <v>3829</v>
+        <v>3945</v>
       </c>
       <c r="AH24" s="222"/>
       <c r="AI24" s="222"/>
@@ -49019,15 +49710,15 @@
       </c>
       <c r="Y25" s="118">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="Z25" s="118">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA25" s="118">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AB25" s="118">
         <f t="shared" si="2"/>
@@ -49051,7 +49742,7 @@
       </c>
       <c r="AG25" s="224">
         <f>SUM($B25:AF25)</f>
-        <v>3829</v>
+        <v>3945</v>
       </c>
       <c r="AH25" s="224"/>
       <c r="AI25" s="269"/>
@@ -49326,9 +50017,9 @@
         <f>+'Water '!$J29</f>
         <v>179</v>
       </c>
-      <c r="Y28" s="127" t="str">
+      <c r="Y28" s="127">
         <f>+'Water '!$J30</f>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Z28" s="127" t="str">
         <f>+'Water '!$J31</f>
@@ -49360,7 +50051,7 @@
       </c>
       <c r="AG28" s="220">
         <f>SUM($B28:AF28)</f>
-        <v>3033</v>
+        <v>3071</v>
       </c>
       <c r="AH28" s="220"/>
       <c r="AI28" s="271"/>
@@ -49905,9 +50596,9 @@
         <f>+'Water '!$N29</f>
         <v>41</v>
       </c>
-      <c r="Y33" s="131" t="str">
+      <c r="Y33" s="131">
         <f>+'Water '!$N30</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z33" s="131" t="str">
         <f>+'Water '!$N31</f>
@@ -49939,7 +50630,7 @@
       </c>
       <c r="AG33" s="227">
         <f>SUM($B33:AF33)</f>
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="AH33" s="227"/>
       <c r="AI33" s="227"/>
@@ -50044,9 +50735,9 @@
         <f>+'Water '!$O29</f>
         <v>112</v>
       </c>
-      <c r="Y34" s="134" t="str">
+      <c r="Y34" s="134">
         <f>+'Water '!$O30</f>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="Z34" s="134" t="str">
         <f>+'Water '!$O31</f>
@@ -50078,7 +50769,7 @@
       </c>
       <c r="AG34" s="228">
         <f>SUM($B34:AF34)</f>
-        <v>1864</v>
+        <v>1895</v>
       </c>
       <c r="AH34" s="228"/>
       <c r="AI34" s="228"/>
@@ -50322,9 +51013,9 @@
         <f>+'Water '!$M31</f>
         <v>0</v>
       </c>
-      <c r="AA36" s="110" t="str">
+      <c r="AA36" s="110">
         <f>+'Water '!$M32</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB36" s="110" t="str">
         <f>+'Water '!$M33</f>
@@ -50338,9 +51029,9 @@
         <f>+'Water '!$M31</f>
         <v>0</v>
       </c>
-      <c r="AE36" s="110" t="str">
+      <c r="AE36" s="110">
         <f>+'Water '!$M32</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF36" s="110" t="str">
         <f>+'Water '!$M33</f>
@@ -50348,7 +51039,7 @@
       </c>
       <c r="AG36" s="220">
         <f>SUM($B36:AF36)</f>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AH36" s="220"/>
       <c r="AI36" s="271"/>
@@ -50449,17 +51140,17 @@
         <f>+'Water '!$Q29</f>
         <v>26</v>
       </c>
-      <c r="Y37" s="131" t="str">
+      <c r="Y37" s="131">
         <f>+'Water '!$Q30</f>
-        <v>0</v>
-      </c>
-      <c r="Z37" s="131" t="str">
+        <v>8</v>
+      </c>
+      <c r="Z37" s="131">
         <f>+'Water '!$Q31</f>
-        <v>0</v>
-      </c>
-      <c r="AA37" s="131" t="str">
+        <v>7</v>
+      </c>
+      <c r="AA37" s="131">
         <f>+'Water '!$Q32</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB37" s="131" t="str">
         <f>+'Water '!$Q33</f>
@@ -50469,13 +51160,13 @@
         <f>+'Water '!$Q34</f>
         <v>0</v>
       </c>
-      <c r="AD37" s="131" t="str">
+      <c r="AD37" s="131">
         <f>+'Water '!$Q31</f>
-        <v>0</v>
-      </c>
-      <c r="AE37" s="131" t="str">
+        <v>7</v>
+      </c>
+      <c r="AE37" s="131">
         <f>+'Water '!$Q32</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF37" s="131" t="str">
         <f>+'Water '!$Q33</f>
@@ -50483,7 +51174,7 @@
       </c>
       <c r="AG37" s="227">
         <f>SUM($B37:AF37)</f>
-        <v>457</v>
+        <v>491</v>
       </c>
       <c r="AH37" s="227"/>
       <c r="AI37" s="227"/>
@@ -50787,9 +51478,9 @@
         <f>'Water '!M31</f>
         <v>0</v>
       </c>
-      <c r="AE40" s="119" t="str">
+      <c r="AE40" s="119">
         <f>'Water '!M32</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF40" s="119" t="str">
         <f>'Water '!M33</f>
@@ -50797,7 +51488,7 @@
       </c>
       <c r="AG40" s="220">
         <f>SUM($B40:AF40)</f>
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AH40" s="220"/>
       <c r="AI40" s="271"/>
@@ -50939,15 +51630,15 @@
       </c>
       <c r="Y42" s="138">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="Z42" s="138">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA42" s="138">
         <f>SUM(AA28:AA41)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AB42" s="138">
         <f t="shared" si="4"/>
@@ -50959,11 +51650,11 @@
       </c>
       <c r="AD42" s="138">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AE42" s="138">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AF42" s="138">
         <f t="shared" si="4"/>
@@ -50971,7 +51662,7 @@
       </c>
       <c r="AG42" s="230">
         <f>SUM($B42:AF42)</f>
-        <v>6734</v>
+        <v>6846</v>
       </c>
       <c r="AH42" s="230"/>
       <c r="AI42" s="276"/>
@@ -52165,7 +52856,7 @@
       </c>
       <c r="AG59" s="238">
         <f>IF(AG$9=0,"",+(AG18*10)/AG$9)</f>
-        <v>11.211944280438946</v>
+        <v>11.762194228670532</v>
       </c>
       <c r="AH59" s="239">
         <f>'Daily KPIs'!AI90</f>
@@ -52173,7 +52864,7 @@
       </c>
       <c r="AI59" s="282">
         <f>+AH59-AG59</f>
-        <v>-1.0119442804389465</v>
+        <v>-1.562194228670533</v>
       </c>
       <c r="AJ59" s="270"/>
       <c r="AK59" s="270"/>
@@ -52330,14 +53021,14 @@
       </c>
       <c r="AG62" s="241">
         <f>IF(+(AG28*10)/AG$9&lt;1,0,+(AG28*10)/AG$9)</f>
-        <v>4.8656212623510262</v>
+        <v>4.9265818980151668</v>
       </c>
       <c r="AH62" s="241">
         <v>2.5</v>
       </c>
       <c r="AI62" s="242">
         <f t="shared" ref="AI62:AI78" si="11">AH62-AG62</f>
-        <v>-2.3656212623510262</v>
+        <v>-2.4265818980151668</v>
       </c>
     </row>
     <row r="63" spans="1:37" ht="18.75" x14ac:dyDescent="0.3">
@@ -52470,14 +53161,14 @@
       </c>
       <c r="AG63" s="243">
         <f>IF(+(AG28*10)/AG$93&lt;1,0,+(AG28*10)/AG$93)</f>
-        <v>11.25</v>
+        <v>11.390949554896142</v>
       </c>
       <c r="AH63" s="243">
         <v>2.5</v>
       </c>
       <c r="AI63" s="244">
         <f t="shared" si="11"/>
-        <v>-8.75</v>
+        <v>-8.8909495548961424</v>
       </c>
     </row>
     <row r="64" spans="1:37" s="90" customFormat="1" ht="18" x14ac:dyDescent="0.25">
@@ -53052,14 +53743,14 @@
       </c>
       <c r="AG68" s="241">
         <f>+(AG33*10)/AG$9</f>
-        <v>1.1614605321273139</v>
+        <v>1.1710858956532308</v>
       </c>
       <c r="AH68" s="241">
         <v>0.7</v>
       </c>
       <c r="AI68" s="242">
         <f t="shared" si="11"/>
-        <v>-0.46146053212731397</v>
+        <v>-0.47108589565323089</v>
       </c>
     </row>
     <row r="69" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -53192,14 +53883,14 @@
       </c>
       <c r="AG69" s="241">
         <f>+(AG34*10)/AG$9</f>
-        <v>2.9902796020515372</v>
+        <v>3.0400106469354418</v>
       </c>
       <c r="AH69" s="241">
         <v>2.6</v>
       </c>
       <c r="AI69" s="242">
         <f t="shared" si="11"/>
-        <v>-0.39027960205153711</v>
+        <v>-0.44001064693544167</v>
       </c>
     </row>
     <row r="70" spans="1:37" ht="18.75" x14ac:dyDescent="0.3">
@@ -53609,14 +54300,14 @@
       </c>
       <c r="AG72" s="241">
         <f>+(AG36*10)/AG$9</f>
-        <v>9.6253635259169662E-2</v>
+        <v>9.946208976780864E-2</v>
       </c>
       <c r="AH72" s="241">
         <v>0.1</v>
       </c>
       <c r="AI72" s="242">
         <f>AH72-AG72</f>
-        <v>3.7463647408303435E-3</v>
+        <v>5.3791023219136591E-4</v>
       </c>
     </row>
     <row r="73" spans="1:37" ht="18" x14ac:dyDescent="0.25">
@@ -53749,14 +54440,14 @@
       </c>
       <c r="AG73" s="241">
         <f>+(AG37*10)/AG$9</f>
-        <v>0.73313185522400892</v>
+        <v>0.78767558187087172</v>
       </c>
       <c r="AH73" s="241">
         <v>0.6</v>
       </c>
       <c r="AI73" s="242">
         <f t="shared" si="11"/>
-        <v>-0.13313185522400894</v>
+        <v>-0.18767558187087174</v>
       </c>
     </row>
     <row r="74" spans="1:37" s="91" customFormat="1" ht="18" x14ac:dyDescent="0.25">
@@ -54263,7 +54954,7 @@
       </c>
       <c r="AG78" s="253">
         <f>SUM(AG62:AG77)</f>
-        <v>21.792981515387719</v>
+        <v>22.112000295513326</v>
       </c>
       <c r="AH78" s="253">
         <f t="shared" si="37"/>
@@ -54271,7 +54962,7 @@
       </c>
       <c r="AI78" s="253">
         <f t="shared" si="11"/>
-        <v>-6.1929815153877215</v>
+        <v>-6.512000295513328</v>
       </c>
       <c r="AJ78" s="210"/>
       <c r="AK78" s="210"/>
@@ -54406,7 +55097,7 @@
       </c>
       <c r="AG79" s="254">
         <f t="shared" si="38"/>
-        <v>3.6464085490682105</v>
+        <v>3.6993480484607537</v>
       </c>
       <c r="AH79" s="254">
         <f t="shared" si="38"/>
@@ -54414,7 +55105,7 @@
       </c>
       <c r="AI79" s="254">
         <f t="shared" si="38"/>
-        <v>2.3535914509317899</v>
+        <v>2.3006519515392463</v>
       </c>
       <c r="AJ79" s="285"/>
       <c r="AK79" s="285"/>
@@ -56233,9 +56924,9 @@
         <f>+'Water '!$F29</f>
         <v>202</v>
       </c>
-      <c r="Y96" s="110" t="str">
+      <c r="Y96" s="110">
         <f>+'Water '!$F30</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Z96" s="110" t="str">
         <f>+'Water '!$F31</f>
@@ -56267,7 +56958,7 @@
       </c>
       <c r="AG96" s="220">
         <f>SUM($B96:AF96)</f>
-        <v>3144</v>
+        <v>3189</v>
       </c>
       <c r="AH96" s="220"/>
       <c r="AI96" s="271"/>
@@ -56696,30 +57387,30 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B82:AF82">
-    <cfRule type="cellIs" dxfId="41" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="84" priority="3" operator="greaterThan">
       <formula>26</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B84:AF84">
-    <cfRule type="cellIs" dxfId="40" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="83" priority="4" operator="greaterThan">
       <formula>6.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D64:D65 D67 T69:AI70 D71 D73:D77">
-    <cfRule type="cellIs" dxfId="39" priority="5" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="82" priority="5" stopIfTrue="1" operator="greaterThan">
       <formula>3.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D69:S69 B70:S70">
-    <cfRule type="cellIs" dxfId="38" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="81" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>3.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI8">
-    <cfRule type="cellIs" dxfId="37" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="80" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="79" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
